--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -397,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q363"/>
+  <dimension ref="A1:N363"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,19 +446,10 @@
       <c r="N1" t="str">
         <v>description</v>
       </c>
-      <c r="O1" t="str">
-        <v>__EMPTY</v>
-      </c>
-      <c r="P1" t="str">
-        <v>__EMPTY_1</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>__EMPTY_2</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>LF1000</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -495,19 +490,10 @@
       <c r="N2" t="str">
         <v/>
       </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>LF1001</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -548,19 +534,10 @@
       <c r="N3" t="str">
         <v/>
       </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>LF1002</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -601,19 +578,10 @@
       <c r="N4" t="str">
         <v/>
       </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>LF1003</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -654,19 +622,10 @@
       <c r="N5" t="str">
         <v/>
       </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>LF1004</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -707,19 +666,10 @@
       <c r="N6" t="str">
         <v/>
       </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>LF1005</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -760,19 +710,10 @@
       <c r="N7" t="str">
         <v/>
       </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>LF1006</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -813,19 +754,10 @@
       <c r="N8" t="str">
         <v/>
       </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>LF1007</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -866,19 +798,10 @@
       <c r="N9" t="str">
         <v/>
       </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>LF1008</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -919,19 +842,10 @@
       <c r="N10" t="str">
         <v/>
       </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>LF1009</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -972,19 +886,10 @@
       <c r="N11" t="str">
         <v/>
       </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>OSP1000</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -1025,19 +930,10 @@
       <c r="N12" t="str">
         <v/>
       </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>YY1000</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1076,15 +972,6 @@
         <v/>
       </c>
       <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
         <v/>
       </c>
     </row>
@@ -3991,15 +3878,6 @@
       <c r="N79" t="str">
         <v>Featuring a patented Double Inertial Balancer System for head-turning action, the DIAMANTE SONIC SLIDE delivers a dramatic 180-degree walk and extended sliding action. Generating aggressive turbulence and a deep metal knock with each turn, SONIC SLIDE calls fish up from surprising depths to trigger surface-breaching strikes. With a deep-cut keel design to enhance responsiveness and an aerodynamically optimized body, SONIC SLIDE is built for long-distance deployment in rough and calm waters alike.</v>
       </c>
-      <c r="O79" t="str">
-        <v/>
-      </c>
-      <c r="P79" t="str">
-        <v/>
-      </c>
-      <c r="Q79" t="str">
-        <v/>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4044,15 +3922,6 @@
       <c r="N80" t="str">
         <v>メガバス創世期に誕生し、数多の伝説を築き上げたDOG-Xシリーズ。メガバス創業者、伊東由樹が見出し、DOG-Xに宿した不変の原理とハイドロメカニクスを最大限に体現する、DOG-Xシリーズのグレートマザーが降臨。ブランドン・パラニュークと共に闘う米国フィールドから世界に解き放ち、DOGMAXがいよいよグローバルなフィールドでモンスターを制圧。 強大でトルクフルなターンインとテールアウトを生み出す、「重心分割式シーソーバランサーシステム（PAT.）」、超・長距離スライドを生み出す「タンデム慣性バランサーシステム（PAT.）」、徹底的に水を噛み込んで食らいつき、スタビリティを高めながらリアルなボイルサウンドを発生させる「ウォータースルー・ギル（PAT.）」、内部のボールウエイトがピンポイント接触する衝突によって引き起こす「衝撃波」と硬質な「ノッキングサウンド」が、深層のモンスターにも果敢にアピール。誰もが手軽に130mmのビッグボディを軽快に操作でき、メガバス・トップウォーターマジックの神髄に触れることができます。 あらゆるフィッシュイーターのMAXサイズをフィーディングモードに入れてバイトさせてしまう、ファンクショナルなペンシルベイトです。</v>
       </c>
-      <c r="O80" t="str">
-        <v/>
-      </c>
-      <c r="P80" t="str">
-        <v/>
-      </c>
-      <c r="Q80" t="str">
-        <v/>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4097,15 +3966,6 @@
       <c r="N81" t="str">
         <v>Introduced in 1996,POPX continues to dominate the high-end top-water bait markets of both Japan and the United States. Equipped with MEGABASS original SIDE-STEPPING BALANCER(PAT),POPX walks a rolling dog-walk unlike any other poppers, and the WATER DUCTS(PAT)which imitate the bubbly water coming out of gills and help create a natural"bio-sound", not an ordinary popping sound. POPX also spits, not splashes, quite a distance. Currently 16 colors are available."GG"stands for GUANIUM GHOST, the most shad-like finish, "PM"PEARL MICA(including SG CRACKED finish)and "GP"GUANIUM PHANTOM(including GP CRACKED finish),a see through phantom finish.</v>
       </c>
-      <c r="O81" t="str">
-        <v/>
-      </c>
-      <c r="P81" t="str">
-        <v/>
-      </c>
-      <c r="Q81" t="str">
-        <v/>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4150,15 +4010,6 @@
       <c r="N82" t="str">
         <v>The unique cup shape of the BABY POPX creates an irresistible water-pushing action. Its design produces a lively and engaging splash sound, perfectly complemented by its ability to respond with agility to even the most delicate rod work. With a nuanced short slide and splashing dog walk action, this diminutive popper is designed to captivate even the most elusive game. Despite its ultra-compact body, the BABY POPX offers incredible long-distance casting ability, allowing anglers to cover a wide area with ease and precision. Its centrally placed line eye adds dimension to the traditional popping retrieve, enabling a nimble dog walk to add another layer of allure to its presentation. Further, the BABY POPX’s micro form enables a stealthy splashdown at the end of a long cast, staying under the radar of easily spooked monsters until its pinpoint agility and splashing siren-song call explosive bites from below.</v>
       </c>
-      <c r="O82" t="str">
-        <v/>
-      </c>
-      <c r="P82" t="str">
-        <v/>
-      </c>
-      <c r="Q82" t="str">
-        <v/>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4203,15 +4054,6 @@
       <c r="N83" t="str">
         <v>KARASHI iGは、ハイドロダイナミクスから生まれた独特なキールヘッド(D.PAT.P)により、優れた直進性能を発揮。リトリーブ速度のわずかな変化に対し、あたかも船の揺れ戻しを抑制するような、ボディの姿勢変化を的確に微調整して補正するアクションを発生。 ただゆっくりと引くだけで生まれる幻惑の引き波と、卓越したスタビリティ効果が、これまでのi字系を見切ったクレバーフィッシュを的確にバイトに持ち込みます。 テールにセットした独自のフレアファイバーはキールヘッドの直進性を促進。 二度喰い、三度喰いさえ多発するKARASHI iGは、シビアなフィールドで使ってこそ差がつく、タフフィッシュを獲るために特化したスペシャルスペックが満載。勝つために使う、コンペティティブなi字系です。</v>
       </c>
-      <c r="O83" t="str">
-        <v/>
-      </c>
-      <c r="P83" t="str">
-        <v/>
-      </c>
-      <c r="Q83" t="str">
-        <v/>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4256,15 +4098,6 @@
       <c r="N84" t="str">
         <v>KARASHI 80は、オリジナルのKARASHI同様に水面直下のドッグウォークアクションを手軽かつ、ダイナミックに展開。さながら「リップレス・ジャークベイト」ともいうべき水面下で展開する規則的なロングダート性能は、水面までターゲットが出切らないシビアな状況下で新次元の釣獲パフォーマンスを発揮。 伊東由樹のハイドロダイナミクス理論が生み出したファンクショナルなボディ形態は、左右への規則正しいドッグウォークのリズムが刻みやすい節度ある水噛み抵抗感をもたらし、ジャークやトゥイッチによる水面直下での左右への規則的なロングダートを実現。 まさに、リップレス・ジャークベイトと呼べるＮＥＷジャンルを創造し、稀代のバージンインパクトを発揮します。 水面に出切らないナーバスなターゲットに対して、ダートアクションを仕掛けて喰わせる一撃必釣のシークレットパフォーマンスは圧巻。ぜひ、マジカルな釣果をご体感ください。</v>
       </c>
-      <c r="O84" t="str">
-        <v/>
-      </c>
-      <c r="P84" t="str">
-        <v/>
-      </c>
-      <c r="Q84" t="str">
-        <v/>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4309,15 +4142,6 @@
       <c r="N85" t="str">
         <v>The KARASHI is the embodiment of next-generation Japanese finesse. This secret worming bait will change the face of 3-inch finesse soft bait fishing. The super-natural feel of this bite-sized lure entices even the spookiest fish to bite and hold impulsively. For targets that see your other lures but hesitate to bite, the KARASHI is your secret “one shot, one kill” bite-triggering weapon. 1. With twitching, the KARASHI exhibits agile dog-walking and darting action. 2. With slow retrieves, KARASHI performs an I-shaped action. The defenseless wobbling action evokes injured bait, triggering bites from opportunistic feeders. The extremely natural minute-vibrations trigger bites from clever fish. KARASHI generates overwhelming performance from the combination of its darting action and I-shaped action.</v>
       </c>
-      <c r="O85" t="str">
-        <v/>
-      </c>
-      <c r="P85" t="str">
-        <v/>
-      </c>
-      <c r="Q85" t="str">
-        <v/>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4362,15 +4186,6 @@
       <c r="N86" t="str">
         <v>DOG-X Jr. is not simply a downsized version of our original DOG-X. It is certainly a bit smaller than DOG-X as the name indicates, but it is equipped with a new lengthwise moving balancer as well as the now familiar SIDE-STEPPING MOVING BALANCER (PAT.) of the original DOG-X. This new balancer pushes the bait while walking, so that the roll-walk action of DOG-X Jr. is sharper and more dynamic for its size. The point is that smaller bait does not have to suffer from a smaller action. The action of DOG-X Jr. will remind you of the baitfish chased by a predator, frantically ripping and skipping the water surface. Also, you will find out that casting and retrieving DOG-X Jr. with F1 or F2 class Destroyer bait rods is extremely enjoyable due to their high compatibility. If you want to experience the fastest and the smoothest dog-walk action of your life, you must go for DOG-X Jr.</v>
       </c>
-      <c r="O86" t="str">
-        <v/>
-      </c>
-      <c r="P86" t="str">
-        <v/>
-      </c>
-      <c r="Q86" t="str">
-        <v/>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4415,15 +4230,6 @@
       <c r="N87" t="str">
         <v>KARASHI SPINNERは、通常のI字系ルアーによるアプローチでは今一つ反応が得られなかった完全ニュートラルなバスに高い効果を発揮するプロップベイト。長距離リトリーブにおける優れた直進安定性と正姿勢への素早い復帰は、独自のキールヘッドデザインによるもの。ウィードボトムの表層～中層、シャローやオーバーハング下などで水面直下をスローにただ引きするだけでOKです。 また、水面へと浮上させ、軽くジャーク＆リトリーブすれば、稚鮎などナチュラルベイトの繊細なボイルを演出。通常のバズベイトやスイッシャーではインパクトが強すぎる時、KARASHI SPINNERなら的確にバイトに持ち込みます。</v>
       </c>
-      <c r="O87" t="str">
-        <v/>
-      </c>
-      <c r="P87" t="str">
-        <v/>
-      </c>
-      <c r="Q87" t="str">
-        <v/>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4468,15 +4274,6 @@
       <c r="N88" t="str">
         <v>As with other Megabass baits, POPMAX demands a lot of explaining. The original mold was again carved out by Yuki Ito rather than relying on computer design programs. And the paint works and the overall quality is impeccable as expected of Megabass. Also, POPMAX features a unique water flow system which consists of six water intakes and a water chamber. Instead of the regular water-through system used for POPX, this system utilizes the water pressure change inside the water chamber, making it act like a lip. Furthermore, when paused, the water in the chamber goes out and lifts its head, ready for a splash with a light rod action. With a gentle rod tip action POPMAX will roll-walk dynamically grabbing the water with each rolling action.</v>
       </c>
-      <c r="O88" t="str">
-        <v/>
-      </c>
-      <c r="P88" t="str">
-        <v/>
-      </c>
-      <c r="Q88" t="str">
-        <v/>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4521,15 +4318,6 @@
       <c r="N89" t="str">
         <v>The DOG-X QUICK WALKER supercharges the original DOG-X's dog walking prowess with a redesigned body, improved balancer system, and one-knock sound. It greatly surpasses the expectations for standard-sized pencil baits with its dynamic water displacement, sharp table turns and its one-knock sound, stimulating cruising fish in the mid range. The casting distance has been improved upon as well, to allow for speedy coverage of wide areas. This DOG-X will set fire to dormant beasts, even more so than the original.</v>
       </c>
-      <c r="O89" t="str">
-        <v/>
-      </c>
-      <c r="P89" t="str">
-        <v/>
-      </c>
-      <c r="Q89" t="str">
-        <v/>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4574,15 +4362,6 @@
       <c r="N90" t="str">
         <v>DOG-X has come into the world during Megabass genesis and has continued to send out Megabass engineering to the world. Taking over its legends, finally in year 2010 Super Dog-X has awakened. “High speed-dog walk” and the responsive “Quick slide &amp; turn” is achieved. Overturning the common sense of low water resistant compact pencil baits, the high level operability will not let the others follow. “See-saw balancing system PAT.” updated from the engineering of the first model is added, and the new design “Water through-Gill PAT.” which increases its stability by biting the water is applied. The original balancing body D.PAT.P by the high mounted-line eye that behaves responsively has been applied to achieve a real game. Many of Yuki Ito’s lure technology and design logic is loaded. DOG-X that caught fishes that could not be caught has evolved into a new generation DOG-X challenging clever and tough monsters in the 21st century. Not only with slow taper-light action rod, it is also possible to make dog walk actions with medium heavy action rods. Please check out the overwhelming “easy control ability” at all sorts of fields.</v>
       </c>
-      <c r="O90" t="str">
-        <v/>
-      </c>
-      <c r="P90" t="str">
-        <v/>
-      </c>
-      <c r="Q90" t="str">
-        <v/>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4627,15 +4406,6 @@
       <c r="N91" t="str">
         <v>Don’t be fooled by its size—this DOG-X was built for GIANTS. Powered by a patented SIDE-STEPPING BALANCER, the GIANT DOG-X is engineered to elevate the walking game of novices and experts alike. Featuring a tungsten balancer that moves laterally from left-to-right, the system throws its weight behind each turn for a sharper walk and a unique roll that flashes the GIANT DOG-X’s exquisite detail to monsters below. This effortlessly crisp and dynamic roll-walking action draws vicious strikes in even the toughest slick-calm conditions, bringing explosive performance to angling arsenals around the world.</v>
       </c>
-      <c r="O91" t="str">
-        <v/>
-      </c>
-      <c r="P91" t="str">
-        <v/>
-      </c>
-      <c r="Q91" t="str">
-        <v/>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4680,15 +4450,6 @@
       <c r="N92" t="str">
         <v>アンスラックスは、ローラージャイロ・バランサーシステム（PAT.P）によって、シャフトバランサー上を転位するボールウエイトが甲高いクリックサウンドを発生させ、多彩なマルチアクションを演出するウェイクベイト。 スローリトリーブでは、水面でスーパーローリングアクションを生み出し、腹部のフィン（尻ビレ）が左右にテイリングして水流を掻き分け、独自の三角波でアピール。リトリーブ速度を上げると、水面直下10～20㎝程度をローリング・スイムするサブサーフェスシャッドとして活躍。また、ジャークによるスラッピングでは、水面でスプラッシュやバブルを発生させるボイルベイトを演出。ストップ＆ゴーでは、ダイブ後にフラッタリングやライズアップするパニックベイトを再現。 多彩なアクションとダイナミックなパフォーマンスがもたらすアンスラックス独自の釣獲力を是非フィールドでご体感ください。</v>
       </c>
-      <c r="O92" t="str">
-        <v/>
-      </c>
-      <c r="P92" t="str">
-        <v/>
-      </c>
-      <c r="Q92" t="str">
-        <v/>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4733,15 +4494,6 @@
       <c r="N93" t="str">
         <v>The MEGADOG-X is a supercharged walking bait built to drive trophy　freshwater targets into a reactive frenzy. Clocking in at a hefty 180mm (7in), the MEGADOG-X powers a strategic topwater approach whenever big fish are keyed in on big meals. With a simple reel/stop retrieve, the MEGADOG-X will slide with surprising ease. With more vigorous rod work, the lure will explode into a fury of action, setting off an aggressive splash-walking chain reaction that calls to the largest predators in the area. Incorporating decades of dog-walking refinement, the MEGADOG-X makes big bait topwater angling even more accessible and explosive. * The photograph is a prototype</v>
       </c>
-      <c r="O93" t="str">
-        <v/>
-      </c>
-      <c r="P93" t="str">
-        <v/>
-      </c>
-      <c r="Q93" t="str">
-        <v/>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4786,15 +4538,6 @@
       <c r="N94" t="str">
         <v>アンスラックスは、ローラージャイロ・バランサーシステム（PAT.P）によって、シャフトバランサー上を転位するボールウエイトが甲高いクリックサウンドを発生させ、多彩なマルチアクションを演出するウェイクベイト。 スローリトリーブでは、水面でスーパーローリングアクションを生み出し、腹部のフィン（尻ビレ）が左右にテイリングして水流を掻き分け、独自の三角波でアピール。リトリーブ速度を上げると、水面直下10～20㎝程度をローリング・スイムするサブサーフェスシャッドとして活躍。また、ジャークによるスラッピングでは、水面でスプラッシュやバブルを発生させるボイルベイトを演出。ストップ＆ゴーでは、ダイブ後にフラッタリングやライズアップするパニックベイトを再現。 多彩なアクションとダイナミックなパフォーマンスがもたらすアンスラックス独自の釣獲力を是非フィールドでご体感ください。</v>
       </c>
-      <c r="O94" t="str">
-        <v/>
-      </c>
-      <c r="P94" t="str">
-        <v/>
-      </c>
-      <c r="Q94" t="str">
-        <v/>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4839,15 +4582,6 @@
       <c r="N95" t="str">
         <v>伊東由樹がプライベートゲーム用に手作りしていたランカーキラー・スイッシャーがエクスプローズ。 独特なひねり形状のプロペラには、独自のギアホール加工が施されており、スクラッチサウンドを発生。超低重心マウントしたフラットバランサーによって、激しいロッドワークによるジャークでもボディを回転させることなく、きっちりとラフウォーターに喰らいつく卓越したスタビリティを発揮。水面を激しく割るラフバイトにおいても確実なフックセットを実現します。 スローリトリーブによるタダ巻きでは、時折、ゆらりとウォブリング。凪の水面ではデッドリーベイトを効果的に演出します。 他のスイッシャーとは明らかに違う、一目瞭然のスペックを内包するプロップベイトのスペシャルエディションです。</v>
       </c>
-      <c r="O95" t="str">
-        <v/>
-      </c>
-      <c r="P95" t="str">
-        <v/>
-      </c>
-      <c r="Q95" t="str">
-        <v/>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4892,15 +4626,6 @@
       <c r="N96" t="str">
         <v>The XPOD is the world's first transformation-plug. The COMMAND BILL(PAT.), which has seven distinct settings, is adjustable according to angler preference and specific conditions. Each rugged setting alters the pressure and volume in the WATER INTAKE(PAT.), changing the lure's displacement, weight ratio, and body balance. By altering the properties of rod actino and lip setting, it can be adjusted for use in various situations. The XPOD is a multi-performance lure, allowing anglers to tap into its many abilities and applications. It can transform into 4 modes for top water: a roll-walking pencil bait, a dog-walking popper for targeting specific areas, a sliding pencil popper for targeting wide areas, and a splash head to lure in prey through sound and splashing. For the sub-surface it has 2 modes: a diving pencil and a diving popper. In addition, it has a special trick-darting dive mode using random trajectories and rolling action, allowing it to be used for slow retrieves as a diving swim-bait.</v>
       </c>
-      <c r="O96" t="str">
-        <v/>
-      </c>
-      <c r="P96" t="str">
-        <v/>
-      </c>
-      <c r="Q96" t="str">
-        <v/>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4945,15 +4670,6 @@
       <c r="N97" t="str">
         <v>The XPOD symbolizes the new era of Megabass top water baits. Loved across the world, it is now available in a smaller profile, retaining its captivating appearance and its situation-specific adaptability. Its realistic form will entice the most cunning of prey. While the profile may be small, it packs the same powerful punch as the original, and is ready to decisively bring down its targets.</v>
       </c>
-      <c r="O97" t="str">
-        <v/>
-      </c>
-      <c r="P97" t="str">
-        <v/>
-      </c>
-      <c r="Q97" t="str">
-        <v/>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -4998,15 +4714,6 @@
       <c r="N98" t="str">
         <v>Carefully honed for explosive walking action, DOG-X DIAMANTE cuts through water with unparalleled responsiveness. Featuring a Deep Cut Keel design to sharpen action and angler control, DIAMANTE walks with a lively commotion in calm and rough conditions alike. Designed to excel even at high speeds, DIAMANTE is ideally suited to rapid deployment, searching wide areas quickly and effectively. Rattle-tuned to the exacting specifications of veteran pros, DIAMANTE generates an enticing surface commotion, drawing strikes from afar.</v>
       </c>
-      <c r="O98" t="str">
-        <v/>
-      </c>
-      <c r="P98" t="str">
-        <v/>
-      </c>
-      <c r="Q98" t="str">
-        <v/>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -5051,15 +4758,6 @@
       <c r="N99" t="str">
         <v>MPWは、POPXとは異なるパフォーマンスを発揮する、「テーブルターンを高速化してなお、ネチることができる」異次元のクイックレスポンス・ポッパーを創生。 メガバスのカタログモデルには存在しない、POPXとBabyPOPXの「中間サイズ」は、極みのフィネスポッパーゲームをさらにコンプリート。 アナザーPOPXの魔力は、スレきったメジャーレイクのクレバーフィッシュを相手にお確かめください。</v>
       </c>
-      <c r="O99" t="str">
-        <v/>
-      </c>
-      <c r="P99" t="str">
-        <v/>
-      </c>
-      <c r="Q99" t="str">
-        <v/>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -5104,15 +4802,6 @@
       <c r="N100" t="str">
         <v>MEGADOGは、メガバスが誇る稀代の名作DOG-Xのポテンシャルを、異次元のレベルまで高めた対ビッグフィッシュ用のスペシャルウェポンです。200mmを超える大型のベイトを水面に追い込み捕食するモンスターフィッシュのみをターゲットとし、既成概念を破壊する強烈なインパクトとアピール力を発揮したメガサイズペンシルベイトです。</v>
       </c>
-      <c r="O100" t="str">
-        <v/>
-      </c>
-      <c r="P100" t="str">
-        <v/>
-      </c>
-      <c r="Q100" t="str">
-        <v/>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -5157,15 +4846,6 @@
       <c r="N101" t="str">
         <v>KIRINJIの生みの親、伊東由樹は、水面直下にウィードが迫る広域エリアにて、KIRINJIを表層でただゆっくりと引くだけで、スピナーベイトに連日叩かれてきたスプーキーなバスを驚異的に釣っています。KIRINJIが水面でもたらす独特なハイピッチ・ロール・スクリューは、タフなバスにとても効果的です。同エリアから連続して何度もチェイスしてくる様は、KIRINJIが発生させる絶妙なライブ波動によるものでしょう。 MPWでは、フレッシュウォーターによりアジャストする特別なKIRINJIを製作。鋭いポッピングやスプラッシュが出しやすい比重へとチューンし、あの独特なライブ波動に加わるスパイシーなインパクトがシャローに散発するランカーをより広域から惹き寄せます。</v>
       </c>
-      <c r="O101" t="str">
-        <v/>
-      </c>
-      <c r="P101" t="str">
-        <v/>
-      </c>
-      <c r="Q101" t="str">
-        <v/>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -5210,15 +4890,6 @@
       <c r="N102" t="str">
         <v>Orca はイージーなロッドワークによって、アングラーの意図を超えた「変幻アクション」を誰もが自然に生み出すことができる、数奇なプロップフォーム（プロペラの捻り形態）ベイトです。計算された捻りボディが水を的確に絡め取り、水流の巻き込みと剥離を適宜に発生させることで、アングラーが意図しないアクションを自然に生み出します。Orca には使い込むほどにハマってしまう、こだわりのトップウォータープラッガーを虜にする特別な魔力が潜んでいます。</v>
       </c>
-      <c r="O102" t="str">
-        <v/>
-      </c>
-      <c r="P102" t="str">
-        <v/>
-      </c>
-      <c r="Q102" t="str">
-        <v/>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5263,15 +4934,6 @@
       <c r="N103" t="str">
         <v>伊東由樹がプライベートゲーム用に手作りしていたランカーキラー・スイッシャーがエクスプローズ。 独特なひねり形状のプロペラには、独自のギアホール加工が施されており、スクラッチサウンドを発生。超低重心マウントしたフラットバランサーによって、激しいロッドワークによるジャークでもボディを回転させることなく、きっちりとラフウォーターに喰らいつく卓越したスタビリティを発揮。水面を激しく割るラフバイトにおいても確実なフックセットを実現します。 スローリトリーブによるタダ巻きでは、時折、ゆらりとウォブリング。凪の水面ではデッドリーベイトを効果的に演出します。 他のスイッシャーとは明らかに違う、一目瞭然のスペックを内包するプロップベイトのスペシャルエディションです。</v>
       </c>
-      <c r="O103" t="str">
-        <v/>
-      </c>
-      <c r="P103" t="str">
-        <v/>
-      </c>
-      <c r="Q103" t="str">
-        <v/>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5316,15 +4978,6 @@
       <c r="N104" t="str">
         <v>プロップフォーム(プロペラ形態)ボディが生み出す、独自のインパクト。 ボディがスパイラル形状を持つプロペラデザイン。ボディ自体がプロペラ・・・これがアイティオー流のスイッシャーです。 SCREAM-X 3/4oz.はロッドティップを水面近くに下げてジャークすると即座にダート。強めの連続トゥイッチを入れると、左右へと激しくボディを反転させながらドッグウォーク＆テーブルターン。しかもその激しいドッグウォークの最中には、ジュオッ！っと、激しいスクリーミングサウンドを伴います。この動きが、大型ベイトの激しいハタキ行動を連想させるかもしれません。 操作のキモは、ロッドティップを水面近くに下げること。SCREAM-Xは、ルアーとアングラーの距離が近いときにロッドティップを上げてリトリーブするとプロペラが回転しないようにセッティングされています。バランスウエイトをボディ後部にインサートし、フロントを浮かせているからです。 従来のスイッシャーは、スポットでバスがバイトしなかったとき、回収中もプロペラが激しく回転して水面を騒々しく滑走するため、エリア全体に不要な警戒心を与えていました。SCREAM-Xは、狙うべきスポットだけでペラが回転し、軽妙な首振りターンと激しいインパクトを放つ独特なセッティングを施しています。</v>
       </c>
-      <c r="O104" t="str">
-        <v/>
-      </c>
-      <c r="P104" t="str">
-        <v/>
-      </c>
-      <c r="Q104" t="str">
-        <v/>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5369,15 +5022,6 @@
       <c r="N105" t="str">
         <v>BEETLE-X enchants bug-eating monster bass with its enticing action and siren call. Featuring AIR wings crafted with a material selected both for low elasticity and specific gravity, BEETLE-X HOVER CRAWL is able to perform a high-pitched crawling action that practically dances across the surface, even in rough conditions. Carefully tuned sound profile features a precise mix of steel and glass rattles, for a multilayered sound that consistently draws targets from afar. Finished with unprecedented detail, the HOVER CRAWL shines with alluring realism. ※The photograph is a prototype.</v>
       </c>
-      <c r="O105" t="str">
-        <v/>
-      </c>
-      <c r="P105" t="str">
-        <v/>
-      </c>
-      <c r="Q105" t="str">
-        <v/>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -5422,15 +5066,6 @@
       <c r="N106" t="str">
         <v>プロップフォーム(プロペラ形態)ボディが生み出す、独自のインパクト。 ボディがスパイラル形状を持つプロペラデザイン。ボディ自体がプロペラ・・・これがアイティオー流のスイッシャーです。 SCREAM-X Jr. 1/2oz.は、プロップフォーム（プロペラ形態）をベイトライクなスリムなボディ形態にデザイン。水面に食らいつくスタビリティを極限まで高め、あえて直進性能に特化してセットアップ。小型スイッシャーながら、タイトなプロペラボディが常時、水流をに瞬時に絡め取り、装着した前後のWプロップが激しく高回転。水面でスクリームサウンドを放ち、激しいフィーディング＆ボイルをイミテートします。</v>
       </c>
-      <c r="O106" t="str">
-        <v/>
-      </c>
-      <c r="P106" t="str">
-        <v/>
-      </c>
-      <c r="Q106" t="str">
-        <v/>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5475,15 +5110,6 @@
       <c r="N107" t="str">
         <v>Nano SIGLETT, the featherweight bug-pattern dynamo made for instantaneous inhalation, is the result of ITO Engineering's ultra-precision NanoCraft Technology. This unrelenting attention to minutiae gives shape to exquisite hydrodynamics that enable an extremely consistent and appealing action that often escapes conventional tiny lures. At a few hairs over 2cm, the Nano SIGLETT crawls with a high-pitch action that few bass will be able to ignore. This is finesse bug-pattern angling at its finest.</v>
       </c>
-      <c r="O107" t="str">
-        <v/>
-      </c>
-      <c r="P107" t="str">
-        <v/>
-      </c>
-      <c r="Q107" t="str">
-        <v/>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5528,15 +5154,6 @@
       <c r="N108" t="str">
         <v>TINY SIGLETT is a micro bug bait that imitates the struggling movements of cicada and similar winged insects on the water surface. Steady retrieve creates a paddling walking-motion, with each wing dipping into the water as it turns, walks, and splashes on the surface. Shake the line to imitate the fluttering death throes of a struggling insect, and fool even the most cunning of predators. Decreased buoyancy helps fish take down TINY SIGLETT for higher hook up ratios. ※The photograph is a prototype.</v>
       </c>
-      <c r="O108" t="str">
-        <v/>
-      </c>
-      <c r="P108" t="str">
-        <v/>
-      </c>
-      <c r="Q108" t="str">
-        <v/>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -5581,15 +5198,6 @@
       <c r="N109" t="str">
         <v>Siglett is a winged bug-bait modeled after a Japanese cicada. Its tungsten alloy balancer inside its chamber is sound-tuned to mimic the Higurashi cicada of Japan. Also, it looks just like one, complete with a pair of translucent wings made of semi-hard plastic which not only slide up &amp; down, but also act as large lips for jittering bug action.</v>
       </c>
-      <c r="O109" t="str">
-        <v/>
-      </c>
-      <c r="P109" t="str">
-        <v/>
-      </c>
-      <c r="Q109" t="str">
-        <v/>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -5634,15 +5242,6 @@
       <c r="N110" t="str">
         <v>Siglett is a winged bug-bait modeled after a Japanese cicada. Its tungsten alloy balancer inside its chamber is sound-tuned to mimic the Higurashi cicada of Japan. Also, it looks just like one, complete with a pair of translucent wings made of semi-hard plastic which not only slide up &amp; down, but also act as large lips for jittering bug action. Since line eye is located at its tail, Siglett casts with the least air resistance, insuring surprisingly good casting distance and accuracy as a winged bug bait. When retrieved, Siglett’s wings naturally ‘open up’ and each ‘wing lip’ starts to crawl alternately as it jitters along. Fast to slow-steady retrieve in open areas and stop &amp; go twitching action under overhangs are the most effective application. Enjoy a relaxing top-water fishing day with Siglett.</v>
       </c>
-      <c r="O110" t="str">
-        <v/>
-      </c>
-      <c r="P110" t="str">
-        <v/>
-      </c>
-      <c r="Q110" t="str">
-        <v/>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5687,15 +5286,6 @@
       <c r="N111" t="str">
         <v>As the name OVER REV indicates, the limiter-breaking high-speed rotations of the ORC are next-level. Introducing a flat side shallow crank that has succeeded in dramatically increasing roll speed!  The ORC’s super high-speed rolling is thanks to the newly developed GYRO BALANCING LBO mechanism that generates a high-speed wobbling roll like that of a roly-poly toy. This eliminates the need for the high-speed retrieves seen in previous flat sides which were needed to generate flashing. The ORC emits intense flashing and screw waves even during slow retrieves. It’s able to maintain a position directly under the surface for long periods of time, creating many opportunities to trigger bites. The ORC significantly raises the potential for contact with fish in shallow areas. If you retrieve it very slowly, it can perform as a topwater crank. In that situation, the GYRO BALANCER rhythmically strikes the body emitting a hard attack sound below the surface garnering attention from target fish. The ORC is a true shallow game revolutionary that features heightened shallow cover evasion performance and the ability to effectively draw out bites even when maintaining distance from cover. * The photograph is a prototype.</v>
       </c>
-      <c r="O111" t="str">
-        <v/>
-      </c>
-      <c r="P111" t="str">
-        <v/>
-      </c>
-      <c r="Q111" t="str">
-        <v/>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -5740,15 +5330,6 @@
       <c r="N112" t="str">
         <v>The i-JACK traces its lineage to the IT JACK, a legendary hand-carved wood plug created by Megabass founder, Yuki Ito. Building on this history, i-JACK overwhelms with a powerful, “screw drive” action, creating huge water-disturbance, a booming “knock,” and an intense flash to call predators from far and wide. An original Stingray Bill design and integrated Rudder Action Balancer System (R.A.B) deliver a twisting wake bait retrieve with a wide roll-axis, flashing the i-JACK’s exquisitely detailed sides with each turn. Further, the R.A.B. system, with its heavy metal ball and rudder-like metal plate on a free-swinging pivot pin, throws its considerable weight behind each turn to generate unprecedented rolling action and a surprisingly loud “knock” with each turn. The i-JACK’s outsized rolling screw-action and sound extend its effectiveness even into deeper waters, where its bold presence and lifelike detail will be sure to fool even the most discerning predators.</v>
       </c>
-      <c r="O112" t="str">
-        <v/>
-      </c>
-      <c r="P112" t="str">
-        <v/>
-      </c>
-      <c r="Q112" t="str">
-        <v/>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -5793,15 +5374,6 @@
       <c r="N113" t="str">
         <v>The BURNING SHAD is pushed into overdrive, maximizing the roll drive of the ORC’s compact body at all speeds. Marvelous super-fast rolling action like an engine at its limit is produced by the GYRO BALANCING LBO SYSTEM, which harnesses the essential principle of a self-righting doll to drive relentless action at all speeds. Previously, a fast retrieve was required to generate the rolling, flickering action of a lure like the ORC. However, by harnessing the GYRO system, the BURNING SHAD produces dynamic roll, displacement and flash at slower speeds where other lures may begin to falter. With rod tip low and a slow retrieve, the BURNING SHAD will crawl just beneath the surface, bulging water and inciting explosive chase bites. Speed up your retrieve and BURNING SHAD tracks true with ever-stronger flash and rolling water displacement. The GYRO system creates a hard, rhythmical “click” sound to appeal to inactive fish. Additionally, the BURNING SHAD exhibits dramatically improved avoidance ability due to its body shape and hook placement, allowing for close-cover cranking. * The photograph is a prototype.</v>
       </c>
-      <c r="O113" t="str">
-        <v/>
-      </c>
-      <c r="P113" t="str">
-        <v/>
-      </c>
-      <c r="Q113" t="str">
-        <v/>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -5846,15 +5418,6 @@
       <c r="N114" t="str">
         <v>i-LOUD showcases the same Rudder Action Balancer System (PAT.) of the i-JACK, housed in a new concept jointed wakebait/propbait designed by ITO ENGINEERING. The RAB System emits a resounding ‘knock’ as it throws its weight from side to side, giving off a strong sonic presence as it helps power the outsized action of i-LOUD’s jointed body. Rear prop adds another layer of lively sound, and leaves a bubble trace along the retrieve line. With a large profile, and even larger action and sound, i-LOUD represents an aggressive approach to activate the feeding modes of dormant monster bass, and trigger explosive bites. ※The photograph is a prototype.</v>
       </c>
-      <c r="O114" t="str">
-        <v/>
-      </c>
-      <c r="P114" t="str">
-        <v/>
-      </c>
-      <c r="Q114" t="str">
-        <v/>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -5899,15 +5462,6 @@
       <c r="N115" t="str">
         <v>PROP DARTER 80 (X-80 PD) is something like top-water version of TRICK DARTER. The prop which was invented (PAT.P) just for this bait, is truly unique not simply because it is asymmetric but because of its lively swimming sound and its ability to spit back. As for the body, the inside structure has been completely overhauled and redesigned for a new set of objectives. As a result it leans to left and right when retrieved. It looks like a snake's swimming track. PROP DARTER has a lip, which tries to dive. Yet it cannot dive. This struggle adds to PROP DARTER's unique bio-sound and the surface action you have never seen before.</v>
       </c>
-      <c r="O115" t="str">
-        <v/>
-      </c>
-      <c r="P115" t="str">
-        <v/>
-      </c>
-      <c r="Q115" t="str">
-        <v/>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -5952,15 +5506,6 @@
       <c r="N116" t="str">
         <v>From the creators of the VISION ONETEN, comes the ultimate winged bait. I-WING’s incredibly realistic body featuring super-lightweight duralumin wings is the result of hundreds of hours of hydrodynamic testing in tough fields. ･ During dead slow retrieves i-WING generates micro pitch waves, evoking a small school of fish that swarms to weakened bait. ･During high speed retrieves the body practically hovers over the water and demonstrates agile buzz-crawling despite its large size. The internal R.A.B. (Rudder Action Balancer System) activates in conjunction with the wings, generating turning actions, and allowing the jointed tail to gracefully tail walk and emit a delayed “knock” sound. It will stimulate and appeal to even far away targets. In conjunction with the wobblin’ roll action, the R.A.B. weight swings on a pivot from side to side like a pendulum. When the heavy weight hits the inside of each wall, a strong sound and shock wave is emitted, adding another layer of acoustic attraction. The uniquely layered waves emitted by the body movement, wings, jointed tail and R.A.B. pendulum balancer combine to intensely stimulate the feeding instinct of monsters. * The photograph is a prototype.</v>
       </c>
-      <c r="O116" t="str">
-        <v/>
-      </c>
-      <c r="P116" t="str">
-        <v/>
-      </c>
-      <c r="Q116" t="str">
-        <v/>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -6005,15 +5550,6 @@
       <c r="N117" t="str">
         <v>PROPDARTER106 is equipped with the nearly frictionless LBO II (PAT.) moving balancer system to achieve superior weight transfer and cast distance for a propeller-mounted lure. The LBO II’s ball-bearing shaft weight is synchronized to the roll axis of the lure’s action for enhanced output. The responsive and seamless roll action creates frequent enticing flutters, mimicking the rise and wake of baitfish. Depending on the retrieval speed, a variety of "3-way actions" are produced, showcasing an extraordinary feeding magic.</v>
       </c>
-      <c r="O117" t="str">
-        <v/>
-      </c>
-      <c r="P117" t="str">
-        <v/>
-      </c>
-      <c r="Q117" t="str">
-        <v/>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -6058,15 +5594,6 @@
       <c r="N118" t="str">
         <v>Following in the footsteps of the i-Wing, ITO Engineering, with Yuki Ito at the helm, has finally released the top-secret i-WING FRY, designed under a veil of secrecy to catch even the cleverest fish on the first bite. In shallow areas normally attacked with crankbaits or spinnerbaits, simply reeling in the i-WING FRY will bring your target to the surface, with a stunning power that explodes through the water. Once it was deemed impossible for a winged lure to have a moving balancer, because of how the crawling action works, but ITO has successfully developed a proprietary format, available for the first time in this lure. By analyzing the “power points” and “action points” generated by the Linear Bearing Oscillator (LBO) of the moving balancer system, as it responds to a variety of likely actions, Yuki Ito has designed a brand-new hydrodynamic body especially for the i-WING FRY, so as to synchronize the movements of the central axis of the LBO and the rolling axis of the lure. The innovative design, which increases buoyancy in a manner reminiscent of a hovercraft, enters the lineage of unique simulated fish like the POP-X, brought to you exclusively by Megabass. In concert with the neodymium magnet, the shaft balancer of the LBO moves reflexively as the lure changes position, creating (1) “instant action,” (2) “optimal form after splashdown, to rapidly correct the LBO,” and (3) “instant magnetic anchoring.” In other words, the lure starts working the second it hits water, doing things no winged lure has done before, and exhibiting a stunning directability so that your target bites on the spot. The i-WING FRY responds instantly, even to the slightest control of the line slack. Always in motion, it draws the target in. Defying preconceptions of winged lures, and dismissing headwinds as irrelevant, the long-distance castability maximizes and amplifies productive areas like no lure of its class. On top of that, the tuned hydrodynamic body is equally in control on extremely slow retrieves and on faster retrieves liable to come tearing through the surface, demonstrating incredible stability. This is a lure that keeps on swimming, adapting to whitecaps and all manner of rough surface conditions. Simply reeling in the lure will catch plenty of fish, but shaking introduces wobble action and subtle undulation. Little twitches will produce the side-to side rotation or splash action seen with pencil bait.  If you're looking for a winged lure that has the finesse and impact on bite chance of worm lures, look no further than the i-WING FRY. * The photograph is a prototype.</v>
       </c>
-      <c r="O118" t="str">
-        <v/>
-      </c>
-      <c r="P118" t="str">
-        <v/>
-      </c>
-      <c r="Q118" t="str">
-        <v/>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -6111,15 +5638,6 @@
       <c r="N119" t="str">
         <v>Introducing the TRIPLE FRY, a new addition to the popular i-WING series that has taken bass fields across the world by storm. The tougher the conditions, the more TRIPLE FRY will showcase its mystical fish-catching performance. The super thin pair of baitfish wings possess a unique flexibility, making lifelike delicate and seductive waves with dead slow retrieves. The rolling dance of the main body combines with the jointed float tail and wings to create the illusion of panicked baitfish struggling at the surface in an enticing bait ball. The slower you reel it in, this unprecedented panic bait will trigger an increasingly powerful chain reaction of explosions on the water’s surface.</v>
       </c>
-      <c r="O119" t="str">
-        <v/>
-      </c>
-      <c r="P119" t="str">
-        <v/>
-      </c>
-      <c r="Q119" t="str">
-        <v/>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -6164,15 +5682,6 @@
       <c r="N120" t="str">
         <v>この動きに抗えるヌシは、いるでしょうか？　ガバリンは、従来フロッグの単調な誘いを完全に見切ったモンスターを相手に徹底テストして開発。独自のボディデザインにより、フローティングカバーのほんのわずか隙間、数十センチのオープンポケットでも、ガバリンはラインスラック・ワークやロッドワークに即応し、ピンポイントの鋭角なクイックターンやハイピッチ・ドッグウォークを披露。ガバリンのワイドな口角による絶妙な水噛みが水面を騒めかせ、重々しいサウンドとバブルを伴うダイブ＆スプラッシュを発生。 ３シーズンに及んだテストでは、叩き抜かれたフローティングカバーのポンド群から、ヌシレベルのビッグフィッシュたちをバイトさせる度、アップデートを重ねてきました。 多彩なロッドワークで挑むテクニカルなトップウォータープラッガーに向けて贈る、新感覚のアクティブアクションフロッグ。ガバリンならば、ヌシは呑み込みます。</v>
       </c>
-      <c r="O120" t="str">
-        <v/>
-      </c>
-      <c r="P120" t="str">
-        <v/>
-      </c>
-      <c r="Q120" t="str">
-        <v/>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -6217,15 +5726,6 @@
       <c r="N121" t="str">
         <v>The BIG GABOT is a larger, heavy-duty model of the PONY GABOT developed based on the strong requests of the US pro staff. While preserving the responsive CATAMARAN MOUTH of the PONY GABOT which allows for splash-walking action, the BIG GABOT features upgrades to various parts. In order to push the center of gravity farther back compared to the original GABOT, the skirt has been positioned away from the body. A new hook groove has been added to the connection point of the hook and body to limit unwanted hook slide. With the increase in size, the internal structure has also been redesigned and reinforced for durability. The BIG GABOT’s hook is custom-built for the new frog, increasing hook-penetration and reducing lost fish throughout the fight. With increased total weight, easy casting with thick PE line is possible. The larger body also allows for more powerful water displacement in heavy matted cover, dramatically increasing the appeal of the BIG GABOT in the eyes of big bass. The BIG GABOT has a striking presence that surpasses the original, stimulating the fighting instinct of big bass. * The photograph is a prototype.</v>
       </c>
-      <c r="O121" t="str">
-        <v/>
-      </c>
-      <c r="P121" t="str">
-        <v/>
-      </c>
-      <c r="Q121" t="str">
-        <v/>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -6270,15 +5770,6 @@
       <c r="N122" t="str">
         <v>“KING OF JERKBAIT”として世界で活躍するビジョン・ワンテンシリーズ。他のジャークベイトではオーバーダイブしがちだった水面直下のシャローレンジを完全攻略する、競技専用スペシャルモデルが、ONETEN-SRとONETEN-SSRです。 ［最大潜行深度1.0ｍ]を徹底的にキープする[SR]は、超広域のシャローエリアから、従来ジャークベイトの展開レンジに反応しなかったバスのストライクチャンスを大幅に拡大。 さらなる表層レンジを展開する、［最大先行深度0.7m以浅］の徹底キープを実現したONETEN-SSRは、これまでソフトジャークベイトやトップウォーターベイトに頼らざるを得なかった、ボトムにウィードやストラクチャーが存在する広大なスーパーシャローエリアをジャークベイティングによるホットスポットに変えてしまいます。 SRとSSRは、リールハンドルのノブに指をかけた瞬間から、着水と同時にアクションが即立ち上がり、着水地点のバイトも即時誘発。オリジナル・ワンテンよりも左右へのダート距離を拡大化し、ロッドアクションのワンストロークで移動可能な水中のダート距離は、ワンテン随一のものとなっています。 ロッドを立てて操作する、ラインスラックの瞬時の緩急によるショートストローク・トウィッチでは、水面へと踊りながら上昇する「ライズアップ軌道」をイレギュラーに披露。腹部をひるがえす「ロール・フラッタリング」、「フラッタリング＆ダート」など、多彩なアクロバティック・アクションを頻発させます。 SR、SSR共に、特殊フッ素コーティングにより貫通力を極限まで高め、いかなる襲撃角度からのショートバイトやラフアタックでも即掛けする、メガバス独自の最新デザインによるNEWアウトバーブフックを搭載。ハイスコアゲームを追求するトーナメントプロフェッショナルに向けて製作する、純競技仕様のスペシャルファンクションモデルです。</v>
       </c>
-      <c r="O122" t="str">
-        <v/>
-      </c>
-      <c r="P122" t="str">
-        <v/>
-      </c>
-      <c r="Q122" t="str">
-        <v/>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -6323,15 +5814,6 @@
       <c r="N123" t="str">
         <v>この動きに抗えるヌシは、いるでしょうか？　ガバリンは、従来フロッグの単調な誘いを完全に見切ったモンスターを相手に徹底テストして開発。独自のボディデザインにより、フローティングカバーのほんのわずか隙間、数十センチのオープンポケットでも、ガバリンはラインスラック・ワークやロッドワークに即応し、ピンポイントの鋭角なクイックターンやハイピッチ・ドッグウォークを披露。ガバリンのワイドな口角による絶妙な水噛みが水面を騒めかせ、重々しいサウンドとバブルを伴うダイブ＆スプラッシュを発生。 ３シーズンに及んだテストでは、叩き抜かれたフローティングカバーのポンド群から、ヌシレベルのビッグフィッシュたちをバイトさせる度、アップデートを重ねてきました。 多彩なロッドワークで挑むテクニカルなトップウォータープラッガーに向けて贈る、新感覚のアクティブアクションフロッグ。ガバリンならば、ヌシは呑み込みます。</v>
       </c>
-      <c r="O123" t="str">
-        <v/>
-      </c>
-      <c r="P123" t="str">
-        <v/>
-      </c>
-      <c r="Q123" t="str">
-        <v/>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -6376,15 +5858,6 @@
       <c r="N124" t="str">
         <v>The BATRA-X is the second joint project between Monster Kiss, led by Takuya Kozuka, and Megabass. The BATRA-X features innovative design elements and customizable functions that set it apart from past hollow frogs. The small yet high volume bullet-style body realizes nimble table turn actions and long distance castability. The Megabass original soft cup can be attached to the front of the body for rapid fire splash-crawling action and noisy sounds with a straight retrieve, something not possible with past frogs. The BATRA-X features a rumble tail and tail hook at the end of the penetration-type wire swivel that attract fish with sounds and vibration. This world’s first transformation hollow-body surface plug allows you to change out components based on situation and preference. * The photograph is a prototype</v>
       </c>
-      <c r="O124" t="str">
-        <v/>
-      </c>
-      <c r="P124" t="str">
-        <v/>
-      </c>
-      <c r="Q124" t="str">
-        <v/>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -6429,15 +5902,6 @@
       <c r="N125" t="str">
         <v>１９９０年代、USAトッププロたちからの熱い要望を受け、伊東由樹が米国トーナメントフィールドに向けて製作した「アイティオー・シャイナー」こそが、実は、名作ワンテンの原型と言われています。その、極めてナチュラルな「餌ライクな動き」にエッジの立った「強波動」を融合させた、特異なハイアピール・ジャークベイトは、様々なレンジで広域を回遊するあらゆるバスを圧倒的に誘引。「活性を上げたいファーストコンタクトは、ITO-SHINNER」、「喰わせにゆくなら、ONETEN」。というのが、メガバスUSAチームのセオリーになっているほどです。 ITO-SHINNERのレスポンシブなハイピッチ・アクションは、激しい明滅効果と激しい振動で刺激をもたらし、圧倒的なフィーディングをメイク。広域エリアからグッドコンディションを手際よく探り当てるスピーディーなゲームマネジメントを展開します。 ファーストブレイクを回遊する個体を優位に直撃するITO-SHINNERの潜行深度は、1.8～2m。ITO-SHINNER[+1]は、2.6 ～2.8mレンジへのアジャスタビリティを高めています。稀代のイレギュラーダートと強波動でリアクションバイトを多発させる、ジャークマスター御用達の普遍的ミノーです。</v>
       </c>
-      <c r="O125" t="str">
-        <v/>
-      </c>
-      <c r="P125" t="str">
-        <v/>
-      </c>
-      <c r="Q125" t="str">
-        <v/>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -6482,15 +5946,6 @@
       <c r="N126" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
-      <c r="O126" t="str">
-        <v/>
-      </c>
-      <c r="P126" t="str">
-        <v/>
-      </c>
-      <c r="Q126" t="str">
-        <v/>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -6535,15 +5990,6 @@
       <c r="N127" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
-      <c r="O127" t="str">
-        <v/>
-      </c>
-      <c r="P127" t="str">
-        <v/>
-      </c>
-      <c r="Q127" t="str">
-        <v/>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -6588,15 +6034,6 @@
       <c r="N128" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
-      <c r="O128" t="str">
-        <v/>
-      </c>
-      <c r="P128" t="str">
-        <v/>
-      </c>
-      <c r="Q128" t="str">
-        <v/>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -6641,15 +6078,6 @@
       <c r="N129" t="str">
         <v>LATES is a real stick roller bait which furiously rolls directly under water, releasing a natural impact targeting the lower range. The flickering created by the furious roll is exactly like a school of bait fishes migrating. At situations where the water surface is disturbed by the wind, it will further release the flickering impact appealing to the targets at the lower range. It is an extreme surface minnow “floating up and capturing” the migrating monsters. The use is simple. All you need to do is to retrieve at the speed between slow and medium speed. Furthermore “rise up &amp; fall” created by decreasing the retrieve speed at times, and the “hovering” which keeps one certain range while rolling will trigger reaction bites. Slow retrieve while using high gear installed reel will help make these operations with ease. Furthermore at top water games, slapping action made by twitching is effective. The instant slide action while fluttering will imitate a real panic bait. Roller bait-LATES will awaken the fish eaters aware of the upper layer. Please check out the power of this special minnow deeply pursuing the surface minnow game.</v>
       </c>
-      <c r="O129" t="str">
-        <v/>
-      </c>
-      <c r="P129" t="str">
-        <v/>
-      </c>
-      <c r="Q129" t="str">
-        <v/>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -6694,15 +6122,6 @@
       <c r="N130" t="str">
         <v>The high impact jerkbait KANATA AYU was designed to target fish that are keyed in on larger bait. With a streamlined, slender body, KANATA keeps resistance to a minimum. This allows for a fast, action-packed retrieve that will not put undue stress on angler’s wrists and forearms, even with a Medium Heavy setup. Sharp rod work fuels energetic darting action. Straight retrieve shows off a high-pitch rolling action with flashing visual appeal. Aerodynamic form and custom-fitted Megabass original Tungsten Triple Oscillating moving balancer system(PAT.) powers effortlessly long casts, allowing KANATA to target those clever monster fish from long range. KANATA AYU brings a new size and sensation to the jerkbait game. ※The photograph is a prototype.</v>
       </c>
-      <c r="O130" t="str">
-        <v/>
-      </c>
-      <c r="P130" t="str">
-        <v/>
-      </c>
-      <c r="Q130" t="str">
-        <v/>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -6747,15 +6166,6 @@
       <c r="N131" t="str">
         <v>The high performance ITO-SHINER was developed for top anglers like Aaron Martens and Edwin Evers for top-level US tournaments. To commemorate the ITO-SHINER’s release in America, it will also undergo a limited release in Japan. The ultimate life-like movements and unprecedented stimulating waves generated by this highly appealing jerk bait have the overwhelming power to round up bass scattered across a wide area. Using its robust body height compared to that of a slim minnow, it shows dramatically increased flashing performance, in addition to a fluttering tail-motion that is an extremely alluring target. The settings of the ITO-SHINER help to realize high-speed fishing, and will excel as a search bait in high-pressure tournament situations. The swimming depth is set to 1.8~2.0 meters (~6ft.), perfectly targeting the sweet spot for bass. With its wide, side to side darting it triggers reaction bites with amazing consistency.</v>
       </c>
-      <c r="O131" t="str">
-        <v/>
-      </c>
-      <c r="P131" t="str">
-        <v/>
-      </c>
-      <c r="Q131" t="str">
-        <v/>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -6800,15 +6210,6 @@
       <c r="N132" t="str">
         <v>The ITO SHINER, which earned its reputation as a foundational jerkbait in the storied Megabass arsenal, is now available as a Super Shallow Runner (SSR) to attack the 0-0.5m range. ITO SHINER SSR is a super shallow minnow that generates a hard-rolling and flashing action to call to predators cruising the jungle of vegetation just beneath the surface. The diving depth of the SSR is 1-2ft depending upon line type and diameter, making it an extremely effective competition search bait in and around weed areas. The unique wide-bend bill helps generate larger and more dynamic water displacement, challenging the subtler action so often associated with shallow offerings. Primarily designed for a straight retrieve, the SSR also is capable of darting action with intermittent jerks, leaping forward and laterally with pronounced roll and flash. Finely tuned hydrodynamics and internal balancer enable the SSR to stick to a tight, shallow range, triggering strikes from the shadows. The triple tungsten moving balancer system delivers supercharged casts, even against strong winds gusting across the flats. The ITO SHINER SSR is a competition-spec offering designed to dominate the shallow range with overwhelming flash and appeal.</v>
       </c>
-      <c r="O132" t="str">
-        <v/>
-      </c>
-      <c r="P132" t="str">
-        <v/>
-      </c>
-      <c r="Q132" t="str">
-        <v/>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -6853,15 +6254,6 @@
       <c r="N133" t="str">
         <v>KANATA+1 (Plus One) is a roll diving model with a maximum diving depth of 3.2m, 1m deeper than the original KANATA’s diving depth. Like the original, despite its big size (160mm) and 1.1/8oz weight, the +1 has surprisingly light retrieve resistance, enabling high-tempo searches with F5 (Medium Heavy) class rods. The KANATA’s high pitch roll action produces an extremely natural and tight action that is not found in other large body jerkbaits, as well as a flickering effect that spreads over a wide expanse. The ITO Tungsten Triple Oscillating System (PAT.) built into the lure’s slim, flat-sided form allows for impressive cast distance, even in headwinds. The high-impact minnow KANATA+1 has an overwhelming presence combined with a natural swimming action, a contrast that stimulates the predatory instinct of target fish at greater depths and distances.</v>
       </c>
-      <c r="O133" t="str">
-        <v/>
-      </c>
-      <c r="P133" t="str">
-        <v/>
-      </c>
-      <c r="Q133" t="str">
-        <v/>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -6906,15 +6298,6 @@
       <c r="N134" t="str">
         <v>The long-awaited second installment of the IxI series has arrived: I×I FURIOUS. Imae and Ito once again inspired each other to new heights, creating a high-speed subsurface crank that replicates the hair-trigger bite reaction of forage fleeing at breakneck speeds. To deliver truly highspeed performance in the challenging shallow subsurface range, Yuki Ito developed a patented water-through mechanism that directs water flow through the lure’s body to stabilize depth range and action at the upper limit of retrieve speeds. FURIOUS's patented design channels water through a head intake into an inner chamber that discharges flow via two downward ducts hidden in the lure’s gills. As retrieve speeds increase, the rate of water flow and pressure both increase in tandem, adding dynamic stability to dominate a new super-shallow range. With high-speed retrieves, this ducted water system keeps FURIOUS locked in a specific depth range to challenge those predators who have long ruled the shallows. FURIOUS is equipped with a Micro LBO (PAT.) moving-balancer system, powering outsized cast distance and displaying the superb balance to deliver stunningly high-pitched action and strobing flash. The fact that a lure of such diminutive size can achieve such long-distance castability, stability at speed and breathtaking action is truly a FURIOUS achievement. IxI will bring the shallow high-speed cranking game to another dimension. ■MODEL 1.5 ・Versatile shallow runner with a maximum diving depth of 1.5m. ・High-pitch flash and rolling-drive action with otherworldly stability at high speeds. ・ Ultra-tight action doesn’t miss a beat, even with bottom contact. Swim through tight riprap with dexterity to take the fight to the shallow range.</v>
       </c>
-      <c r="O134" t="str">
-        <v/>
-      </c>
-      <c r="P134" t="str">
-        <v/>
-      </c>
-      <c r="Q134" t="str">
-        <v/>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -6959,15 +6342,6 @@
       <c r="N135" t="str">
         <v>The long-awaited second installment of the IxI series has arrived: I×I FURIOUS. Imae and Ito once again inspired each other to new heights, creating a high-speed subsurface crank that replicates the hair-trigger bite reaction of forage fleeing at breakneck speeds. To deliver truly highspeed performance in the challenging shallow subsurface range, Yuki Ito developed a patented water-through mechanism that directs water flow through the lure’s body to stabilize depth range and action at the upper limit of retrieve speeds. FURIOUS's patented design channels water through a head intake into an inner chamber that discharges flow via two downward ducts hidden in the lure’s gills. As retrieve speeds increase, the rate of water flow and pressure both increase in tandem, adding dynamic stability to dominate a new super-shallow range. With high-speed retrieves, this ducted water system keeps FURIOUS locked in a specific depth range to challenge those predators who have long ruled the shallows. FURIOUS is equipped with a Micro LBO (PAT.) moving-balancer system, powering outsized cast distance and displaying the superb balance to deliver stunningly high-pitched action and strobing flash. The fact that a lure of such diminutive size can achieve such long-distance castability, stability at speed and breathtaking action is truly a FURIOUS achievement. IxI will bring the shallow high-speed cranking game to another dimension. ■MODEL 0.5 ・Super shallow runner with a diving depth of up to 0.5m. ・High-pitch flash and tight roll action that generates outsized presence and overwhelming responsiveness. ・ Targets the ultra-shallow range with a wide carpet-bombing approach and powerful high-speed action.</v>
       </c>
-      <c r="O135" t="str">
-        <v/>
-      </c>
-      <c r="P135" t="str">
-        <v/>
-      </c>
-      <c r="Q135" t="str">
-        <v/>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -7012,15 +6386,6 @@
       <c r="N136" t="str">
         <v>This next-generation shad made bass pro Katsutaka Imae exclaim “we’ve got something amazing here!” The TYPE-3 features an ability to trace a depth of 3.0m, but it can also perform exceptionally up to the 1.2m range. The design minimizes snags in the shallows and makes repeated hard contact with structures possible. Yuki Ito’s shad engineering has realized Katsutaka Imae’s “forward falling theory” at an extremely high level with this ultimate versatile shad featuring dazzling ultra-high pitch roll action. * The photograph is a prototype.</v>
       </c>
-      <c r="O136" t="str">
-        <v/>
-      </c>
-      <c r="P136" t="str">
-        <v/>
-      </c>
-      <c r="Q136" t="str">
-        <v/>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -7065,15 +6430,6 @@
       <c r="N137" t="str">
         <v>The I x I SHAD secret weapon A high pitch, high stability shad that allows for fast searches of the 1m shallow range, reliably turning bites into results. The high pitch screw-roll action allows for clear bottom contact thanks to the forward falling posture. This drastically increases the bite chances when contacting structure and the bottom. You can see the performance of this next-generation shad with its ability to draw out tough, clever fish with its speedy flashing. * The photograph is a prototype.</v>
       </c>
-      <c r="O137" t="str">
-        <v/>
-      </c>
-      <c r="P137" t="str">
-        <v/>
-      </c>
-      <c r="Q137" t="str">
-        <v/>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -7118,15 +6474,6 @@
       <c r="N138" t="str">
         <v>The goal of Katsutaka Imae and Yuki Ito was to land targets from the 4m+ range with a mere 57mm long shad body. The mounting position of the instant shifting balancer system Micro LBO (PAT.) allows for a super forward leaning posture impossible with normal ball weights. Ito moved the balancer head towards the intersection of the lip and body using a shaft with super small diameter bearings that made the extreme forward mounting design possible. With field tests using 6lb fluorocarbon line this big-lipped small shad demonstrated extremely long flight distances and succeeded in generating an astonishing diving vector. The outstanding fusion of aerodynamics and hydrodynamics have given the IxI SHAD the extreme performance needed to strike at deep targets. It is the ultimate solution for compactness, realism and performance.</v>
       </c>
-      <c r="O138" t="str">
-        <v/>
-      </c>
-      <c r="P138" t="str">
-        <v/>
-      </c>
-      <c r="Q138" t="str">
-        <v/>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -7171,15 +6518,6 @@
       <c r="N139" t="str">
         <v>The LIVE-X, one of Megabass’ original injection-molded lures of the early 90’s, is now reborn with the latest technology and supercharged performance. It's not a shad. It's not a minnow. And of course, it's not a simple crank. The state-of-the-art hydrodynamics with built-in LBO II(PAT.) produces ultra-fast flickering and live action from dead slow to ultra-high speed retrieves without fail. It is a bait with an overwhelmingly lifelike performance, turning neutral fish into reactive feeders when it matters most. This is the impact of a "live bait". The aerodynamic form, which Yuki Ito derived from countless hours of aerodynamic testing, improves casting distance by more than 30% in headwinds when compared to lures of equal volume. LIVE-X has succeeded in increasing the performance of carpet bombing a wider and more diverse range than ever before. In shallow water 2m deep or less, where conventional diving cranks have a hard time, LIVE-X is extremely dexterous, avoiding getting stuck and continuing to lure tough fish. The ability to feed cruising fish at depths of 3.5m or more is unique to the LIVE-X, which has been further refined to outperform the original. Switch on the feeding instinct of neutral fish that have not responded even to the ONETEN jerkbait. The second phase of the LIVING LEGEND project was started to catch discerning fish that are turned off from the overly aggressive action of many conventional cranks. This time, those of you who missed out on the explosive fishing experience with the original LIVE-X 30 years ago will experience it anew. Discover the true meaning of "LIVE-X". The legend continues.</v>
       </c>
-      <c r="O139" t="str">
-        <v/>
-      </c>
-      <c r="P139" t="str">
-        <v/>
-      </c>
-      <c r="Q139" t="str">
-        <v/>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -7224,15 +6562,6 @@
       <c r="N140" t="str">
         <v>The X-NANAHAN is a fusion of the ideals of Shinji Sato, one of Japan's foremost lure anglers, and the engineering of Yuki Ito, creator of dominant jerkbaits like the VISION ONETEN. In order to pursue superior castability in a small jerkbait minnow profile, the X-NANAHAN’s body is carved from a high-volume block, which results in a visually tight silhouette with greater precision. Air resistance has been thoroughly reduced to achieve overwhelming long-distance castability that surpasses the standard distance of 70mm-class minnows. The unique shape of the minnow, guided by the latest in hydrodynamics, provides excellent swimming response and intuitive handling. X-NANAHAN’s subtle action and flash reproduce the minute waves and flickering appeal of baitfish in an extremely realistic manner. Further, when twitched, X-NANAHAN bursts to life with a dynamic jerking and darting action that sets it apart from the school. The X-NANAHAN is a next-generation finesse minnow that pursues the "ultimate" in responsiveness. * The photograph is a prototype.</v>
       </c>
-      <c r="O140" t="str">
-        <v/>
-      </c>
-      <c r="P140" t="str">
-        <v/>
-      </c>
-      <c r="Q140" t="str">
-        <v/>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -7277,15 +6606,6 @@
       <c r="N141" t="str">
         <v>The X-NANAHAN is a fusion of the ideals of Shinji Sato, one of Japan's foremost lure anglers, and the engineering of Yuki Ito, creator of dominant jerkbaits like the VISION ONETEN. In order to pursue superior castability in a small jerkbait minnow profile, the X-NANAHAN’s body is carved from a high-volume block, which results in a visually tight silhouette with greater precision. Air resistance has been thoroughly reduced to achieve overwhelming long-distance castability that surpasses the standard distance of 70mm-class minnows. The unique shape of the minnow, guided by the latest in hydrodynamics, provides excellent swimming response and intuitive handling. X-NANAHAN’s subtle action and flash reproduce the minute waves and flickering appeal of baitfish in an extremely realistic manner. Further, when twitched, X-NANAHAN bursts to life with a dynamic jerking and darting action that sets it apart from the school. The X-NANAHAN is a next-generation finesse minnow that pursues the "ultimate" in responsiveness. * The photograph is a prototype.</v>
       </c>
-      <c r="O141" t="str">
-        <v/>
-      </c>
-      <c r="P141" t="str">
-        <v/>
-      </c>
-      <c r="Q141" t="str">
-        <v/>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -7330,15 +6650,6 @@
       <c r="N142" t="str">
         <v>The super minnow X-NANAHAN, which has generated unquestionable results from waters throughout Japan since its release, is now available in a +2 model for even deeper ranges. The NANAHAN+2’s 75mm compact body can now easily reach a range of 3m, bringing its irresistible appeal right under the noses of big bass tucked away in the depths. The NANAHAN’s rare combination of high-pitch roll action and rod-twitch trick darting induce difficult bites in the most important moments. The thoroughly tested aerobill enables a rocket-like cast with a stable flying posture, maximizing diving depth and productive water. The NANAHAN series now covers all key depth ranges, bringing an invaluable set of tools to the demanding angler.</v>
       </c>
-      <c r="O142" t="str">
-        <v/>
-      </c>
-      <c r="P142" t="str">
-        <v/>
-      </c>
-      <c r="Q142" t="str">
-        <v/>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -7383,15 +6694,6 @@
       <c r="N143" t="str">
         <v>The VISION95 "Q-GO" is a 3.74in. long minnow meant for shallow water. The swimming action of this bait is controlled by a completely new balancer system called the SHAFT BALANCER SYSTEM(PAT.) Instead of a moving, round balancer, the one in the Q-GO is shaped and fixed at the lowest point along the body. The result is an astounding new type of rolling action. Since the shaft weight acts as kind of reverse pendulum (think of it upside-down), the whole body swings with the shaft as a pivot. Unlike a moving balancer, the shaft balancer does not require guiding structures, so it frees up the space inside the bait. This allows the Q-GO to have very high buoyancy along with highly responsive movement. That is why the Q-GO is at home with any retrieval speed. Slow or fast, the Q-GO will get you the responses you have been waiting for.</v>
       </c>
-      <c r="O143" t="str">
-        <v/>
-      </c>
-      <c r="P143" t="str">
-        <v/>
-      </c>
-      <c r="Q143" t="str">
-        <v/>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -7436,15 +6738,6 @@
       <c r="N144" t="str">
         <v>"The VISION ONETEN Jr. packs the tournament-winning characteristics of the immensely successful VISION ONETEN jerk bait into a 98mm (3.85in) frame, generating more action per inch than its larger sibling. The VISION ONETEN Jr. has been carefully benchmarked against the VISION ONETEN, and has been redesigned from the ground up to improve upon the dynamic actions of the original, and expand the range of the jerk bait line. The ONETEN’s unique action has been distilled into the diminutive frame of the ONETEN Jr. Not only does it exhibit wide, erratic darts, but also demonstrates high pitch rolling and flashing during slow retrieves and wobble and roll agitation during fast retrieves. Finally, the dual-tungsten weights of the Megabass Multi way Moving Balancer System (PAT.) allow for incredible flight distance despite the lure’s small size.</v>
       </c>
-      <c r="O144" t="str">
-        <v/>
-      </c>
-      <c r="P144" t="str">
-        <v/>
-      </c>
-      <c r="Q144" t="str">
-        <v/>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -7489,15 +6782,6 @@
       <c r="N145" t="str">
         <v>Based on the ONETEN+1, a diving jerkbait responsible for overwhelming results in top U.S. tournaments, the VISION ONETEN+1 Jr. is a compact and agile performer engineered to target the toughest midrange waters—especially when matching smaller bait really counts. Aligning the uniquely contoured diving bill along the central axis of the body channels water along sculpted body lines, powering outsize, erratic darting action. Proven ONETEN design fools wary predators and generates striking flash, reaping massive dividends in midrange waters. Aerodynamic diving bill drastically reduces unnecessary air resistance, while the energy produced by the linear dual-tungsten weights of the Moving Balancer System allow for incredible flight distance even in rough conditions. * The photograph is a prototype</v>
       </c>
-      <c r="O145" t="str">
-        <v/>
-      </c>
-      <c r="P145" t="str">
-        <v/>
-      </c>
-      <c r="Q145" t="str">
-        <v/>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -7542,15 +6826,6 @@
       <c r="N146" t="str">
         <v>The VISION ONETEN+2 Jr. brings bite-sized jerkbait appeal to new depths, matching the tournament-winning 9-10ft range of the full-sized ONETEN+1. With a sculpted bill set along the lure’s central axis, the +2 Jr. achieves the kind of dynamic, razor-sharp darting action that earns the VISION ONETEN series a place in every serious jerkbait angler’s arsenal. At target depth, the +2 Jr. displays remarkably wide and responsive darting action. Its contoured body throwing off intense flash before coming to rest with a delicate shimmying appeal, provoking compulsive bites from deep cruisers. With an aerodynamic form and dual-tungsten weight transfer system, the ONETEN+2 Jr. outcasts expectations, bringing hard-fought trophies within reach.</v>
       </c>
-      <c r="O146" t="str">
-        <v/>
-      </c>
-      <c r="P146" t="str">
-        <v/>
-      </c>
-      <c r="Q146" t="str">
-        <v/>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -7595,15 +6870,6 @@
       <c r="N147" t="str">
         <v>The VISION ONETEN series, renowned as the “KING OF JERKBAITS” worldwide, is now available in a shallow-running model. With a maximum diving depth of 1m (3.2ft) on 14lb fluorocarbon, the ONETEN SR moves into action with the first angler input, effectively triggering strikes before the cast rings settle. Compared to the original ONETEN, the SR maintains a shallower running depth while expanding the lateral range of its side-to-side darting action, generating more action per jerk than even the original ONETEN. By holding the rod upright, varying line slack and applying short-stroke twitches between 11 and 1 o’clock, the ONETEN SR produces acrobatic actions such as a “rise-up darting” toward the surface, high flash “roll fluttering,” and endless combinations of “fluttering and darting.” The ONETEN SR is equipped with custom Megabass out-barb hooks. Premium 1X wire enhanced with a fluorine coating for superior penetration, these hooks generate instant hookups in the toughest situations. Designed for competitive angling, this high-performance lure is built to maximize your angling potential.</v>
       </c>
-      <c r="O147" t="str">
-        <v/>
-      </c>
-      <c r="P147" t="str">
-        <v/>
-      </c>
-      <c r="Q147" t="str">
-        <v/>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -7648,15 +6914,6 @@
       <c r="N148" t="str">
         <v>Introduced in the fall of 2000, the VISION ONETEN immediately captured the imagination of American anglers, setting a new standard for jerk baits. Designed by Yuki Ito for anglers in the United States, the ONETEN has emerged as the "go-to" jerk bait amongst touring pros, continuing to produce key fish and big checks from the Club level to the Bassmaster Classic. The profile, one-of-a-kind darting action, tungsten Multi-Way Moving Balancer System(PAT.) and hand-painted color patterns all contribute to the incredible fish-catching ability of the VISION ONETEN. The internal balancer system not only fuels the ONETEN's unparalleled action and huge flashes, but also allows it to cast like a bullet, far outpacing conventional jerk baits. This deadly package is finished off with three Megabass original sticky-sharp KATSUAGE OUT-BARB treble hooks, designed to increase hook-setting percentages when power-bait fishing. Crafted to generate results with a steady retrieve, traditional "jerk, jerk, pause," or trolling, the ONETEN responds to rod actions with unparalleled, life-like action. The one and only: VISION ONETEN.</v>
       </c>
-      <c r="O148" t="str">
-        <v/>
-      </c>
-      <c r="P148" t="str">
-        <v/>
-      </c>
-      <c r="Q148" t="str">
-        <v/>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -7701,15 +6958,6 @@
       <c r="N149" t="str">
         <v>The VISION ONETEN +1 is a mid-range jerk bait designed to increase the depth of the original ONETEN by up to 3ft. The ONETEN+1's medium bill is crafted to eliminate the traditional issues of high water-resistance, fatigue, and dead-end darting action often associated with long-bill minnows, all while preserving the legendary action of the original ONETEN. By positioning the line-eye close to the body, water resistance is reduced in order to make it easier to work the ONETEN+1 compared to conventional long bills. In addition, this angler-friendly design also channels more water towards the lure's forehead and along the carefully sculpted body, allowing for irresistible darting action with the slightest input. The ONETEN+1 is finished off with a dual-tungsten Multi-Way Moving Balancer System(PAT.) designed to produce superior long-distance castability even in tough conditions. The VISION ONETEN+1 : The legend just got deeper.</v>
       </c>
-      <c r="O149" t="str">
-        <v/>
-      </c>
-      <c r="P149" t="str">
-        <v/>
-      </c>
-      <c r="Q149" t="str">
-        <v/>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -7754,15 +7002,6 @@
       <c r="N150" t="str">
         <v>The ONETEN MAGNUM builds upon the overwhelming success of the VISION ONETEN in major tournaments around the world, featuring a redesigned fixed-balancer system, and a larger profile. Unlike the decentralized balancer-systems of many large jerk baits, the ONETEN MAGNUM has a specially tuned internal fixed weight balancer plate that allows for responsive action and swimming stability. The ONETEN MAGNUM dives to a depth of 2 feet (60cm), and with a slow retrieve, gives off an alluring wobble identical to a schooling baitfish. With a fast retrieve, the MAGNUM performs high pitch rolling actions; when stopped, the MAGNUM gives off a subtle wobble and floats up head first, just like a baitfish trying to escape a predator. With a larger profile, the ONETEN MAGNUM offers up a larger meal that will be sure to trigger bites from even the most cautious monsters.</v>
       </c>
-      <c r="O150" t="str">
-        <v/>
-      </c>
-      <c r="P150" t="str">
-        <v/>
-      </c>
-      <c r="Q150" t="str">
-        <v/>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -7807,15 +7046,6 @@
       <c r="N151" t="str">
         <v>The ONETEN LBO, which features the second-generation LBO II (PAT.) moving balancer system, has dramatically increased castability against headwinds, making stable, long approaches possible even under blustery conditions. Additionally, the balancer system—powered by 88 ball-bearings—significantly reduces friction during weight transfer, thereby transferring greater energy to the lure’s tail for greater casting distance. By extending the 110mm body of the original to a long-tailed 115mm, the center of gravity is able to shift even farther to the rear when casting, improving accuracy. The LBO II (PAT.) brings with it a lowered center of gravity along with a synchronized point of leverage and point of action that make instant, responsive actions possible from the moment you put your hand on the reel handle. The bearing weight, which is secured in optimal “ready” position by a neodymium magnetic field, generates sharp and highly regulated jerking actions, and the entirely new dimension of sharp, high pitch rolling action brings a heightened prominence to the ONETEN’s flashing. This special ONETEN, filled with ITO Engineering’s cutting-edge technologies, redefines the preexisting concept of jerkbaits. * The photograph is a prototype.</v>
       </c>
-      <c r="O151" t="str">
-        <v/>
-      </c>
-      <c r="P151" t="str">
-        <v/>
-      </c>
-      <c r="Q151" t="str">
-        <v/>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -7860,15 +7090,6 @@
       <c r="N152" t="str">
         <v>The ONETEN MAX LBO is a large, highly responsive jerkbait powered by the revolutionary LBOII moving balancer system. Thanks to the combination of a highly refined hydrodynamic body and the LBO’s virtually frictionless weight-transfer system, the ONETEN MAX LBO is able to eliminate the sluggishness seen in large jerkbaits of the past. The astonishingly responsive action, a credit to the work of ITO engineering, truly make it worthy of the position atop the vaunted ONETEN jerkbait series. The new patented moving balancer system, LBOII, is designed with micro ball bearings arranged in an infinite-loop configuration to drastically reduce friction of traditional moving balancers. The LBOII weight is magnetically held to the front position, and when unleashed during casting the inertial impact generates a powerful propulsion vector, dramatically increasing casting performance, even against headwinds. From the moment you begin your retrieve, the ONETEN MAX LBO’s weight leaps to the front position with astonishing speed, providing full lure action for the entirety of your cast. The overwhelmingly fast startup performance and incredibly dynamic jerking performance are thanks to the ONETEN MAX LBO’s action and power being on the same linear axis. * The photograph is a prototype.</v>
       </c>
-      <c r="O152" t="str">
-        <v/>
-      </c>
-      <c r="P152" t="str">
-        <v/>
-      </c>
-      <c r="Q152" t="str">
-        <v/>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -7913,15 +7134,6 @@
       <c r="N153" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth. * The photograph is a prototype.</v>
       </c>
-      <c r="O153" t="str">
-        <v/>
-      </c>
-      <c r="P153" t="str">
-        <v/>
-      </c>
-      <c r="Q153" t="str">
-        <v/>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -7966,15 +7178,6 @@
       <c r="N154" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth.</v>
       </c>
-      <c r="O154" t="str">
-        <v/>
-      </c>
-      <c r="P154" t="str">
-        <v/>
-      </c>
-      <c r="Q154" t="str">
-        <v/>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -8019,15 +7222,6 @@
       <c r="N155" t="str">
         <v>ワンテンR「Hi-FLOAT」は、ウィードやグラスの繁茂する高水温期において、圧巻の威力を発揮するワンテンRのシークレット・チューンドモデル。いわゆるウキウキパターンを広めた第一人者、佐藤信治が満を持して送り出すスペシャルメソッド対応モデルです。ウィードやグラス上のオープン域で2ジャークして浮かす、というのが王道メソッド。応用として、ショアのブッシュやリーズ、レイダウンなどのカバー周りや、桟橋や岩場などのストラクチャー周りにタイトにキャストし、やはり2ジャークして浮かす、といった使用方法が効果的。ワンテンR「Hi-FLOAT」だけの爆発力は、正直、秘密にしておきたかったことですが、多くのアングラーの笑顔がみたいプロガイド、佐藤信治だからこそリリースできたモデルです。</v>
       </c>
-      <c r="O155" t="str">
-        <v/>
-      </c>
-      <c r="P155" t="str">
-        <v/>
-      </c>
-      <c r="Q155" t="str">
-        <v/>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -8072,15 +7266,6 @@
       <c r="N156" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth.</v>
       </c>
-      <c r="O156" t="str">
-        <v/>
-      </c>
-      <c r="P156" t="str">
-        <v/>
-      </c>
-      <c r="Q156" t="str">
-        <v/>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -8125,15 +7310,6 @@
       <c r="N157" t="str">
         <v>The ONETEN R+3 joins the ONETEN R series. Inheriting the concept behind the ONETEN R, the R’s depth has finally reached 4m! Just imagine… the performance of the ONETEN R at a depth of 4m. The ONETEN R’s realistic baitfish darting and irregular actions are being brought to a range previously only occupied by big cranks. What’s noteworthy is that while having the ability to dive to such depths, the R+3 maintains light pulling resistance and with jerking can perform sharp darting in the deep zone that can trigger reaction bites at will. Years of Megabass hydrodynamics research and the unique actions of the ONETEN will now take the deepest range by storm. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth. * The photograph is a prototype.</v>
       </c>
-      <c r="O157" t="str">
-        <v/>
-      </c>
-      <c r="P157" t="str">
-        <v/>
-      </c>
-      <c r="Q157" t="str">
-        <v/>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -8178,15 +7354,6 @@
       <c r="N158" t="str">
         <v>The VISION ONETEN R Hi-FLOAT series now features a deep-diving +3 model that takes high buoyancy to new depths. The VISION ONETEN R+3 Hi-FLOAT is a guide-tuned model of the ONETEN R that excels when water temperatures rise, and submerged vegetation nears its peak. Taking shape from the summer jerkbait technique of legendary guide, Shinji Sato, the Hi-FLOAT is built to target the submerged weed beds of Lake Biwa with a jerk-jerk-rise approach. Whether targeting vegetation where the Hi-FLOAT setting is necessary to escape entanglement, or more traditional structure, the highly buoyant design adds a dynamic rising trigger for aggressive warm water feeders. The VISION ONETEN R+3 Hi-FLOAT has remained a Shinji Sato guide secret until now; experience the power of explosive buoyancy.</v>
       </c>
-      <c r="O158" t="str">
-        <v/>
-      </c>
-      <c r="P158" t="str">
-        <v/>
-      </c>
-      <c r="Q158" t="str">
-        <v/>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -8231,15 +7398,6 @@
       <c r="N159" t="str">
         <v>The X-48 Acrobat packs a bold punch much larger than its small frame would suggest. Designed to lure big fish with its finesse approach, the Acrobat springs into action with a twitch of the rod, delivering big action to trigger reaction bites. Built for situations when visible fish don’t commit, the Acrobat gives off a hi-pitch wobble and roll with straight retrieve, triggering bites from stubborn fish with well-timed rod action. Active moving balancer system drives unparalleled casting distance for its size, and guides life-like swimming action. The new generation of finesse minnow has arrived, and it packs a punch. ※The photograph is a prototype.</v>
       </c>
-      <c r="O159" t="str">
-        <v/>
-      </c>
-      <c r="P159" t="str">
-        <v/>
-      </c>
-      <c r="Q159" t="str">
-        <v/>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -8284,15 +7442,6 @@
       <c r="N160" t="str">
         <v>To give more sharpness to its movements during trick actions, the X-70's moving balancer design has been tuned to respond extremely sensitively to rod input such as twitches and jerks. During jerks, the X-70's unique flat body creates dynamic flashing that is easily mistaken for the flashing of live bait. There are many minnows that are focused on darting action, but the X-70 is probably the only one focused on getting bites with its mesmerizing flashing during normal retrieves as well.</v>
       </c>
-      <c r="O160" t="str">
-        <v/>
-      </c>
-      <c r="P160" t="str">
-        <v/>
-      </c>
-      <c r="Q160" t="str">
-        <v/>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -8337,15 +7486,6 @@
       <c r="N161" t="str">
         <v>The X-52 Acrobat packs a bold punch much larger than its small frame would suggest. Designed to lure big fish with its finesse approach, the Acrobat springs into action with a twitch of the rod, delivering big action to trigger reaction bites. Built for situations when visible fish don’t commit, the Acrobat gives off a hi-pitch wobble and roll with straight retrieve, triggering bites from stubborn fish with well-timed rod action. Active moving balancer system drives unparalleled casting distance for its size, and guides life-like swimming action. The new generation of finesse minnow has arrived, and it packs a punch. ※The photograph is a prototype.</v>
       </c>
-      <c r="O161" t="str">
-        <v/>
-      </c>
-      <c r="P161" t="str">
-        <v/>
-      </c>
-      <c r="Q161" t="str">
-        <v/>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -8390,15 +7530,6 @@
       <c r="N162" t="str">
         <v>Live-X REVENGE looks a lot like LEVIATHAN, but that is where resemblance stops. Slightly more slender than LEVIATHAN,REVENGE`s actions are controlled by a completely new balancer system. REVENGE`s diving range is between 6 and 10 feet, the most frequently used range, and shallower than LEVIATHAN. In a way, REVENGE is an easier and handier bait to use than LEVIATHAN. Also, REVENGE comes with MEGABASS original GUANIUM finish.</v>
       </c>
-      <c r="O162" t="str">
-        <v/>
-      </c>
-      <c r="P162" t="str">
-        <v/>
-      </c>
-      <c r="Q162" t="str">
-        <v/>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -8443,15 +7574,6 @@
       <c r="N163" t="str">
         <v>熾烈なUSAトーナメントシーンで勝ち抜くためのブランドン・パラニュークの知見と、世界各地のタフフィールドで膨大な実績を積み重ねてきた伊東由樹のエンジニアリングが融合し、誕生したシステム・ディープクランクシリーズがiPXです。 iPX-12は12ft(3.6m)を、iPX-16は16ft(4.8m)をメインレンジとし、それぞれ最大深度は15ft(4.5m)、18ft（5.4m)に到達。 内蔵された前後の2レーン内を各々フリーに移動し、潜行に応じてボディバランスを自発的に保持しようと多様な前転倒立型の重心ベクトルを適宜生み出す「フォワードロール重心移動システム」(PAT.P)は、限界まで前方向移動するフォワードバランシングが急角潜行を生み出し、プロダクティブゾーンを拡大。 リップ上にデザインした多角形ホールは、あらゆるダイビングアングルから効率よく水圧を確実に掴み、「フォワードロール重心移動システム」(PAT.P)と相まって、揺るぎ無いアクションスタビリティを生み出し続けます。 エッジの効いたウルトラ・ハイピッチアクションと強波動、体高のあるボディが発する激しい明滅は、広範囲にアピールしランカーのバイトを果敢に誘発。 ボトムコンタクトにおいて障害物回避からの復元力に優れ、持続的にボトムタッチし続けるディギングアクションと、長時間のデッドスロー＆ボトムトレースを実現。ライブシューティング／FFS（フォワード・フェイシング・ソナー）のトーナメントシーンにおいて釣り勝つことができる、究極のディープ・サーチベイトです。</v>
       </c>
-      <c r="O163" t="str">
-        <v/>
-      </c>
-      <c r="P163" t="str">
-        <v/>
-      </c>
-      <c r="Q163" t="str">
-        <v/>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -8496,15 +7618,6 @@
       <c r="N164" t="str">
         <v>熾烈なUSAトーナメントシーンで勝ち抜くためのブランドン・パラニュークの知見と、世界各地のタフフィールドで膨大な実績を積み重ねてきた伊東由樹のエンジニアリングが融合し、誕生したシステム・ディープクランクシリーズがiPXです。 iPX-12は12ft(3.6m)を、iPX-16は16ft(4.8m)をメインレンジとし、それぞれ最大深度は15ft(4.5m)、18ft（5.4m)に到達。 内蔵された前後の2レーン内を各々フリーに移動し、潜行に応じてボディバランスを自発的に保持しようと多様な前転倒立型の重心ベクトルを適宜生み出す「フォワードロール重心移動システム」(PAT.P)は、限界まで前方向移動するフォワードバランシングが急角潜行を生み出し、プロダクティブゾーンを拡大。 リップ上にデザインした多角形ホールは、あらゆるダイビングアングルから効率よく水圧を確実に掴み、「フォワードロール重心移動システム」(PAT.P)と相まって、揺るぎ無いアクションスタビリティを生み出し続けます。 エッジの効いたウルトラ・ハイピッチアクションと強波動、体高のあるボディが発する激しい明滅は、広範囲にアピールしランカーのバイトを果敢に誘発。 ボトムコンタクトにおいて障害物回避からの復元力に優れ、持続的にボトムタッチし続けるディギングアクションと、長時間のデッドスロー＆ボトムトレースを実現。ライブシューティング／FFS（フォワード・フェイシング・ソナー）のトーナメントシーンにおいて釣り勝つことができる、究極のディープ・サーチベイトです。</v>
       </c>
-      <c r="O164" t="str">
-        <v/>
-      </c>
-      <c r="P164" t="str">
-        <v/>
-      </c>
-      <c r="Q164" t="str">
-        <v/>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -8549,15 +7662,6 @@
       <c r="N165" t="str">
         <v>A well-kept secret of the Megabass Pro Team, the TRICK DARTER features the same legendary MULTI-WAY MOVING BALANCER SYSTEM (PAT.) as the VISION ONETEN, and is designed to move with an insane darting action that surpasses that of even the VISION ONETEN. With the addition of a fixed balancer in front, a spoonbill lip, and our infamous tungsten balancer system, the TRICK DARTER will truly "flee" erratically with short snaps of the rod, and draw reaction strikes from the most timid fish in the lake. Unlike conventional minnow–shaped jerk baits, the X-80 looks more like a shad or a shiner. Since baitfish with wider bodies flash more noticeably and are heartier meals for predators, the X-80 will attract larger fish. Furthermore, the X-80 swims with a distinct rolling wobble, an action that helps put our baits a world apart from the rest.</v>
       </c>
-      <c r="O165" t="str">
-        <v/>
-      </c>
-      <c r="P165" t="str">
-        <v/>
-      </c>
-      <c r="Q165" t="str">
-        <v/>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -8602,15 +7706,6 @@
       <c r="N166" t="str">
         <v>X-80Jr.は、ストレートリトリーブでは、オリジナルX-80を彷彿とさせるダイナミックなウォブンロール＆脱軌跡アクションを発生。ジャークやトゥイッチを併用しなくても、単純なストップ＆ゴーだけで、手軽にイレギュラーアクションを生み出します。トゥイッチを加えれば、シャッドプラグに切迫する強烈なフラッシングとキレのいいヒラ打ち瞬間ダートを披露。逃げ惑う小魚を演出し、スレきったモンスターにスイッチを入れます。X-80Jr.は、2連の重心移動ウエイトを搭載。安定した飛行姿勢とロングキャスタビリティを発揮します。従来のスモールサイズミノーの概念を覆す新次元のライトプラッキングを実現します。</v>
       </c>
-      <c r="O166" t="str">
-        <v/>
-      </c>
-      <c r="P166" t="str">
-        <v/>
-      </c>
-      <c r="Q166" t="str">
-        <v/>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -8655,15 +7750,6 @@
       <c r="N167" t="str">
         <v>LEVIATHAN is the flagship of Live-X series. It dose everything MARGAY and SMOLT does, but only more dynamically. If you want jerking actions in the mid-deep, LEVIATHAN is what you are looking for. Meticulously　detailed, LEVIATHAN showcases Yuki Ito? talent as a hand carver. LEVIATHAN can be used as a regular jerkbait. However, we suggest that you spend enough time to get to know what this bait is capable of doing.</v>
       </c>
-      <c r="O167" t="str">
-        <v/>
-      </c>
-      <c r="P167" t="str">
-        <v/>
-      </c>
-      <c r="Q167" t="str">
-        <v/>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -8708,15 +7794,6 @@
       <c r="N168" t="str">
         <v>I X I BLOWLY, is the ultimate shallow assault crankbait and third creation from the I×I project born from the combined insight of Katsutaka Imae and Yuki Ito. Equipped with Ito’s signature hydrodynamic theory (PAT.P) deployed in the FURIOUS series, BLOWLY features a fat-bodied profile that stirs the super-shallow zone with an fever-pitch retrieve action. This is no ordinary crank—it’s a veritable shockwave generator, designed to rattle the instincts of bass lurking anywhere near the retrieve line, forcing reaction bites from even the most indifferent feeders. At any retrieve speed, the I×I BLOWLY delivers a high-frequency pitch that outdoes even classic balsa crankbaits. Its distinct performance stems from the fusion of two critical elements: • Expanded frontal surface area that enhances visual and vibrational presence • Patented water-through structural design that amplifies action and hydrodynamic control Though it runs in the super-shallow range, BLOWLY provokes aggressive chase bites from bass rising out of deeper zones or approaching from lateral angles in open water. The result is a nonstop, high-alert game, where strikes come from every direction—vertical or horizontal—without warning.</v>
       </c>
-      <c r="O168" t="str">
-        <v/>
-      </c>
-      <c r="P168" t="str">
-        <v/>
-      </c>
-      <c r="Q168" t="str">
-        <v/>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -8761,15 +7838,6 @@
       <c r="N169" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O169" t="str">
-        <v/>
-      </c>
-      <c r="P169" t="str">
-        <v/>
-      </c>
-      <c r="Q169" t="str">
-        <v/>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -8814,15 +7882,6 @@
       <c r="N170" t="str">
         <v>When first designing the original GRIFFON crankbait in the late 1990’s, Yuki Ito sought a functionally comfortable form with an outsized impact. The result was a compact crankbait that quickly built a storied legacy around the world. This winning formula has given rise to a constantly evolving character that is compact, pinball-shaped, and mischievously productive—enter the third-generation GRIFFON. Enhanced hydrodynamics and a re-tuned internal structure dial up the GRIFFON’s relentlessly dynamic pinball-deflection action, delivering a larger-than-life reaction bite when it matters most. Its ability to quickly recover from frantic deflections is faithfully inherited from its forefathers and further refined. In the waters that so often feature in challenging tournaments, the GRIFFON has confidently demonstrated its outsized fishing performance. The only thing that can surpass a GRIFFON is, indeed, a GRIFFON. Discover your outperformance today.</v>
       </c>
-      <c r="O170" t="str">
-        <v/>
-      </c>
-      <c r="P170" t="str">
-        <v/>
-      </c>
-      <c r="Q170" t="str">
-        <v/>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -8867,15 +7926,6 @@
       <c r="N171" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O171" t="str">
-        <v/>
-      </c>
-      <c r="P171" t="str">
-        <v/>
-      </c>
-      <c r="Q171" t="str">
-        <v/>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -8920,15 +7970,6 @@
       <c r="N172" t="str">
         <v>When first designing the original GRIFFON crankbait in the late 1990’s, Yuki Ito sought a functionally comfortable form with an outsized impact. The result was a compact crankbait that quickly built a storied legacy around the world. This winning formula has given rise to a constantly evolving character that is compact, pinball-shaped, and mischievously productive—enter the third-generation GRIFFON. Enhanced hydrodynamics and a re-tuned internal structure dial up the GRIFFON’s relentlessly dynamic pinball-deflection action, delivering a larger-than-life reaction bite when it matters most. Its ability to quickly recover from frantic deflections is faithfully inherited from its forefathers and further refined. In the waters that so often feature in challenging tournaments, the GRIFFON has confidently demonstrated its outsized fishing performance. The only thing that can surpass a GRIFFON is, indeed, a GRIFFON. Discover your outperformance today.</v>
       </c>
-      <c r="O172" t="str">
-        <v/>
-      </c>
-      <c r="P172" t="str">
-        <v/>
-      </c>
-      <c r="Q172" t="str">
-        <v/>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -8973,15 +8014,6 @@
       <c r="N173" t="str">
         <v>The DEEP-X 100, which has been the long-established benchmark for diving crankbaits, is finally being equipped with the LBO II (Linear Bearing Oscillator II). With its surprisingly compact body, the DEEP-X can instantly attack at its maximum diving depth and displays an astonishing ability for obstacle evasion. No matter the type of contact, the LBO II combines with the cutting-edge hydrodynamic body to consistently maintain action and control, responding directly to the angler’s retrieve to trigger bites. With the LBO II and its new hydrodynamic form, the DEEP-X achieves a lag-less initial swimming response that allows for intuitive cranking. From ponds, to rivers, to large lakes, this versatile crankbait can easily hammer out results in any field. * The photograph is a prototype.</v>
       </c>
-      <c r="O173" t="str">
-        <v/>
-      </c>
-      <c r="P173" t="str">
-        <v/>
-      </c>
-      <c r="Q173" t="str">
-        <v/>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -9026,15 +8058,6 @@
       <c r="N174" t="str">
         <v>The DEEP-X 200 is one of Yuki Ito’s favorite lures in his 30+ year career as a lure designer. The DEEP-X 200 exhibits multifaceted performance and versatility for underwater games in many fields, excelling as a crankbait, a flatside shad, at times a diving minnow, and at times a vibration bait that searches a dedicated range. The uniquely evolved form of this DEEP-X 200 features further refinements from the previous model. In addition to the high pitch vibrations, the angle of the head amplifies its sharp, rolling action. It emits intense high pitch flashing and impactful vibrations. The astonishing flight distance of the slim-bodied 200, made possible by the LBO II, defies expectation. The ultra-long-distance casting performance easily outpaces a typical crankbait, demonstrating the far-reaching explosive performance of this extraordinary crankbait. * The photograph is a prototype.</v>
       </c>
-      <c r="O174" t="str">
-        <v/>
-      </c>
-      <c r="P174" t="str">
-        <v/>
-      </c>
-      <c r="Q174" t="str">
-        <v/>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -9079,15 +8102,6 @@
       <c r="N175" t="str">
         <v>The DEEP-X300 is a long anticipated deep-diving crank bait that adds dimension to the DEEP-X series. With a diving depth of 5m (almost 17 feet) and a much larger body size than the 200 and the 100, the DEEP-X300 will let you invade the depths where lunker fish routinely hide. As with its other DEEP-X brothers, the 300 is equipped with the MULTI-WAY MOVING BALANCER SYSTEM(PAT.). That means the 300 will dive almost vertically in order to maximize effective cranking distance and will also respond to every little twitch or jerk you send to the bait. All of the DEEP-X series crank baits will allow for the conventional bottom-digging method for creating those strike-inducing irregular darting actions, but what makes the DEEP-X series so unique is their mid-water twitch/jerk action, which appeals to the fish at any depth. The 300's colors are uniquely developed for the lower light environment of deeper water.</v>
       </c>
-      <c r="O175" t="str">
-        <v/>
-      </c>
-      <c r="P175" t="str">
-        <v/>
-      </c>
-      <c r="Q175" t="str">
-        <v/>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -9132,15 +8146,6 @@
       <c r="N176" t="str">
         <v>The DEEP-SIX was designed by Yuki Ito to trigger bites at depths of over 6 meters (20ft.), a largely uncharted territory among diving cranks. This range is made possible by a unique, super thin lip that slices through currents, and maintains the ideal balance required for a steep dive angle. Furthermore, the DEEP-SIX incorporates the renowned MULTI-WAY MOVING BALANCER SYSTEM(PAT.) of the DEEP-X series. During casts, the main weight moves to the rear, positioning DEEP-SIX tail-first to maximize aerodynamics and casting distance. When diving, the weight moves to the front of the lure to increase DEEP-SIX’s dive angle, which means you get down to target depth much faster. When DEEP-SIX reaches its maximum diving depth and contacts bottom, underwater structure, or is twitched, the main balancer is released, causing the weight to slide and increase action. If DEEP-SIX levels out at its maximum depth without contacting bottom, the main weight is released from the front and moves to the middle position. This changes the lure’s action, creating a realistic flash and aggressive high pitch rolling and wobbling that ignites the instincts of monsters in the deep. Until now, the super deep range has remained a safe haven for lunkers. Now Megabass has created a lure to venture into the deep, and dominate the monsters’ sanctuary.</v>
       </c>
-      <c r="O176" t="str">
-        <v/>
-      </c>
-      <c r="P176" t="str">
-        <v/>
-      </c>
-      <c r="Q176" t="str">
-        <v/>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -9185,15 +8190,6 @@
       <c r="N177" t="str">
         <v>The world-renowned DEEP-X series sports such exceptional performance that it is almost unfair to use it. Among that DEEP-X series, the DEEP-X150 has a particularly excellent record. Its tight, super-natural wobbling not only creates outstanding water displacement, but emits lively flashing that triggers the feeding instincts of neutral fish cruising in the mid range. The DEEP-X series' acrobatic actions upon contact with structures remains intact with 150's smaller body size, which only serves to make those actions sharper and more amplified. By hitting the lure against underwater slopes and objects on the bottom you can get reaction bites from even spooked bass under high pressure conditions.</v>
       </c>
-      <c r="O177" t="str">
-        <v/>
-      </c>
-      <c r="P177" t="str">
-        <v/>
-      </c>
-      <c r="Q177" t="str">
-        <v/>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -9238,15 +8234,6 @@
       <c r="N178" t="str">
         <v>With its extraordinary roll-axis and unique action, the FLAPSLAP has earned a niche reputation for its intensely powerful flashing appeal. The specially designed shaft balancer, placed ultra-low along the bottom of the body and slightly offset from the roll axis of the action, powers a pendulum action that enhances and stabilizes the lure’s outsized roll-axis and flash. This results in water agitation comparable to that of much bigger-bodied crankbait, supercharging the FLAPSLAP’s results in challenging conditions. With nearly instantaneous startup action from the first handle turn, its unique high-pitch screw drive action emits a striking strobe flash, evoking a fleeing shad. This otherworldly flat-sided bait contributed significantly to Edwin Evers’ victory at the 2016 BASSMASTER Classic.</v>
       </c>
-      <c r="O178" t="str">
-        <v/>
-      </c>
-      <c r="P178" t="str">
-        <v/>
-      </c>
-      <c r="Q178" t="str">
-        <v/>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -9291,15 +8278,6 @@
       <c r="N179" t="str">
         <v>With its extraordinary roll-axis and unique action, the FLAPSLAP has earned a niche reputation for its intensely powerful flashing appeal. The specially designed shaft balancer, placed ultra-low along the bottom of the body and slightly offset from the roll axis of the action, powers a pendulum action that enhances and stabilizes the lure’s outsized roll-axis and flash. This results in water agitation comparable to that of much bigger-bodied crankbait, supercharging the FLAPSLAP’s results in challenging conditions. With nearly instantaneous startup action from the first handle turn, its unique high-pitch screw drive action emits a striking strobe flash, evoking a fleeing shad. This otherworldly flat-sided bait contributed significantly to Edwin Evers’ victory at the 2016 BASSMASTER Classic.</v>
       </c>
-      <c r="O179" t="str">
-        <v/>
-      </c>
-      <c r="P179" t="str">
-        <v/>
-      </c>
-      <c r="Q179" t="str">
-        <v/>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -9344,15 +8322,6 @@
       <c r="N180" t="str">
         <v>The FLAPSLAP has received acclaim around the world for its phenomenal action and life-like detail, proving an indispensable addition to crankbait and jerkbait arsenals alike. Now equipped with the next-generation LBO II (PAT.) moving balancer system, the FLAPSLAP LBO rockets into the future with unrivaled casting distance. The nearly frictionless ball-bearing design of the LBO II (PAT.) balancer system leaps instantly to the tail section to power exceptional casting distance, then shifts to its front, low center-of-gravity position to deliver the storied action for which the FLAPSLAP is already well-known. Now tuned to suspend, the FLAPSLAP LBO can be burned, twitched, and paused above submerged weed beds and other target-rich environments, showing off its beautiful profile and elegant finishes to elicit bites from even the most discerning targets. Exquisite design, hydrodynamic form and balancer system combine to deliver not only the tight-wobbling action anglers expect from flat-sided crankbaits, but a difficult-to-achieve, wide-rolling action that sends enticing flashes throughout the water column. Additionally, much like the original, the FLAPSLAP LBO can be twitched to perform erratic darting rolls that displace water and display huge flashes to call in targets from distance, and trigger reaction bites from followers. * The photograph is a prototype.</v>
       </c>
-      <c r="O180" t="str">
-        <v/>
-      </c>
-      <c r="P180" t="str">
-        <v/>
-      </c>
-      <c r="Q180" t="str">
-        <v/>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -9397,15 +8366,6 @@
       <c r="N181" t="str">
         <v>メガバスファクトリーの熟練クラフツマンがハンドメイドによって製作するZ-CRANK。天然素材によるバルキーなハイフロートボディーは、バイブレーションプラグのような強波動・ハイピッチ・グラインドウォブリングを生み出し、マッディーカバーに潜伏する魚にしっかりとその存在をアピール。独特なフォルムと高強度・高弾性薄型コフィンリップによってスナッグレス性能を高め、シャローエリアのカバーに対するスタックを軽減。ブッシーなシャローやリップラップ、スタンプなどのカバーエリア付近を、ハイフロートボディが巧みにかわし、果敢なクランキングを展開します。</v>
       </c>
-      <c r="O181" t="str">
-        <v/>
-      </c>
-      <c r="P181" t="str">
-        <v/>
-      </c>
-      <c r="Q181" t="str">
-        <v/>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -9450,15 +8410,6 @@
       <c r="N182" t="str">
         <v>メガバスファクトリーの熟練クラフツマンがハンドメイドによって製作するZ-CRANK。天然素材によるバルキーなハイフロートボディーは、バイブレーションプラグのような強波動・ハイピッチ・グラインドウォブリングを生み出し、マッディーカバーに潜伏する魚にしっかりとその存在をアピール。独特なフォルムと高強度・高弾性薄型コフィンリップによってスナッグレス性能を高め、シャローエリアのカバーに対するスタックを軽減。ブッシーなシャローやリップラップ、スタンプなどのカバーエリア付近を、ハイフロートボディが巧みにかわし、果敢なクランキングを展開します。</v>
       </c>
-      <c r="O182" t="str">
-        <v/>
-      </c>
-      <c r="P182" t="str">
-        <v/>
-      </c>
-      <c r="Q182" t="str">
-        <v/>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -9503,15 +8454,6 @@
       <c r="N183" t="str">
         <v>The Z-2’s high pitch action is well-suited for mid-range areas and wide-open shallows. It features a “hard contact bill” designed to give clear feedback to the angler as the Z-2 relentlessly engages structures. The Z-2’s immediate posture recovery after contact is superb and its ability to trace tightly along the bottom is exceptional in its class. Previously, this degree of contact performance required a body volume twice as large in order to harness the effects of buoyancy, but the Z-2 has realized astonishing structure and bottom tracing with an unbelievably small size. The Z-2 is the ultimate searching master that allows the angler to clearly visualize the mid-range through the Z-2’s incessant contact. * The photograph is a prototype.</v>
       </c>
-      <c r="O183" t="str">
-        <v/>
-      </c>
-      <c r="P183" t="str">
-        <v/>
-      </c>
-      <c r="Q183" t="str">
-        <v/>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -9556,15 +8498,6 @@
       <c r="N184" t="str">
         <v>The Z-1 delivers “bulldog contact,” hitting bottom structure with relentless aggression to trigger frenzied reaction bites. The Z-1’s hard-hitting style sets it apart from the GRIFFON series’ finesse escape action. In the bitter winter, early spring, and during turnover periods, the Z-1 displays amazing stability that allows it to continuously engage riprap and shallow contours. Furious deflections never compromise the Z-1’s high pitch action during these situations, stimulating tough fish until they are compelled to bite. This next generation shallow runner is perfectly suited for attacking cruising fish around backwater sand bars, riprap, and shallow structures. * The photograph is a prototype.</v>
       </c>
-      <c r="O184" t="str">
-        <v/>
-      </c>
-      <c r="P184" t="str">
-        <v/>
-      </c>
-      <c r="Q184" t="str">
-        <v/>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -9609,15 +8542,6 @@
       <c r="N185" t="str">
         <v>The SONICSIDE is a competition-ready flatside crankbait born of the exacting demands of our Pro Staff. Built for a tight, high-pitch action to dominate cold water situations, the SONICSIDE displays unrivaled casting distance and stability during fast retrieves. The lip is shaped from tough, 1mm thick circuit board material reinforced with a molded support, making it an eerily responsive and durable option when targeting riprap and hard structure. Additionally, internal weights are fixed for a silent approach, and placed for optimal action, castability and stability at high speeds. This heavy-duty crankbait is built to out-cast and out-work the competition, dominating key targets in tough waters with its natural, high-pitch approach. * The photograph is a prototype.</v>
       </c>
-      <c r="O185" t="str">
-        <v/>
-      </c>
-      <c r="P185" t="str">
-        <v/>
-      </c>
-      <c r="Q185" t="str">
-        <v/>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -9662,15 +8586,6 @@
       <c r="N186" t="str">
         <v>The Super Z, renowned for its outsized castability and compact performance, is now available in a deeper diving Z3 version. Built to easily dominate deep water from wild ponds to big lakes, the Z3 can easily reach a maximum depth of 4m (13ft) on 8lb Fluorocarbon line. Powered by Megabass’ patented LBO II moving balancer system for superior casting distance, the Z3's hydrodynamic design exhibits an enticing tight-pitch action throughout the retrieve, staying true amidst current and bottom contact alike. Designed for easy handling with medium-light to medium rods in the F3 to F4 class, the Z3 is a compact deep crank for the next generation of discerning anglers. * The photograph is a prototype</v>
       </c>
-      <c r="O186" t="str">
-        <v/>
-      </c>
-      <c r="P186" t="str">
-        <v/>
-      </c>
-      <c r="Q186" t="str">
-        <v/>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -9715,15 +8630,6 @@
       <c r="N187" t="str">
         <v>Honed and refined over two years, the S-CRANK is a square bill crankbait featuring a patented design that generates a hard-hitting wobble action along with an erratic hunting, wandering retrieve. S-CRANK’s unique slalom action works even at high-speeds, wandering laterally off-course but always hunting back to center. Not only does this allow more effective coverage of wider areas, but the erratic wandering action triggers reaction bites much like deflections, increasing productivity in open water. Tight, enticing wobble draws inactive predators, while the sudden wandering escape action triggers decisive reaction bites. Square bill design and high buoyancy combine to reduce hang-ups to allow precise targeting of structure. * The photograph is a prototype.</v>
       </c>
-      <c r="O187" t="str">
-        <v/>
-      </c>
-      <c r="P187" t="str">
-        <v/>
-      </c>
-      <c r="Q187" t="str">
-        <v/>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -9768,15 +8674,6 @@
       <c r="N188" t="str">
         <v>BIG-M2.0 explores the 6ft range, a key depth throughout Lake Biwa that is a staple of renowned anglers like Shinji Sato. The BIG-M2.0 specializes in drawing bites from feeders lurking below the 6ft mark, sparking wild chases through open water and shallow cover alike. With a low center-of-gravity design, the BIG-M2.0 harnesses max-rotation rolling action to throw intense flash farther and wider, giving enticing glimpses of its exquisite flat-sided form to predators in the deep. Casts are powered by a triple balancer system, enabling long-distance ballistic approaches in weather conditions that would otherwise overpower conventional flat-sided offerings. Further, due to careful hydrodynamic consideration, the BIG-M exhibits surprisingly low pulling-resistance for its size, reducing the fatigue so often associated with larger lures. This allows anglers to comfortably deploy big bait techniques to target wider areas and new classes of fish, delivering maximum distance and performance with minimal effort. * The photograph is a prototype.</v>
       </c>
-      <c r="O188" t="str">
-        <v/>
-      </c>
-      <c r="P188" t="str">
-        <v/>
-      </c>
-      <c r="Q188" t="str">
-        <v/>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -9821,15 +8718,6 @@
       <c r="N189" t="str">
         <v>MPW「ハダラトラップ」70は、NEWコンセプト・トリックベイト。デッドスローリトリーブ中にも激しい明滅を「ランダム」に発生させ、ハイピッチ・ロールドライブを基調としながらも、クレバーフィッシュに見切られない、左右への「千鳥ダート軌道」でスイミング。 そんな複合的なエスケープアクションをオートマティックに披露してくれるHADARA TRAPは、直線軌道にて一定のリズムでアピールするバイブレーションプラグやスピナーベイトが見切られる状況、タフ化したメジャーエリアなどで大変有効です。 2つの超高比重・大径タングステンバランサーによる「タンデム重心移動システム」を搭載し、タフ化した広域エリアを効率よく攻め抜く圧巻の飛距離を叩き出します。 伊東由樹のハイドロダイナミクス理論によってデザインされた独特なボディは、広大なシャローエリアでも、一定の浅層レンジをキープしながらトリッキーに泳ぎ続けられる、ロングラン攻略を実現。 さらに、ハダラトラップ70は、リフト＆フォールでも威力を発揮。リフト時には、「ヒラウチバイブ」を発生し、フォール時にはボディを細かく震わせて沈下する「シミーフォール」を披露。マルチに仕掛けられる、特別なトラップベイトです。</v>
       </c>
-      <c r="O189" t="str">
-        <v/>
-      </c>
-      <c r="P189" t="str">
-        <v/>
-      </c>
-      <c r="Q189" t="str">
-        <v/>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -9874,15 +8762,6 @@
       <c r="N190" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O190" t="str">
-        <v/>
-      </c>
-      <c r="P190" t="str">
-        <v/>
-      </c>
-      <c r="Q190" t="str">
-        <v/>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -9927,15 +8806,6 @@
       <c r="N191" t="str">
         <v>The BIG-M is the evolutionary result of many years of Megabass big crankbaits. It leaves behind the fat bodied and long billed design of past deep cranks, assuming a flat side design with a short lip and low center of gravity. It realizes sharp, rolling action that generates an overwhelming flashing impact. This design is meant to trace the productive zone at a range of 3.5m (11-12ft). It has incredible castability that allows it to slice through headwinds, combined with low-resistance retrieve which allows it to be used all day long with minimal fatigue. The BIG-M has the power to draw in big bass lurking in the depths, all contained within a package full of extraordinarily refined engineering. Developed under the guidance of Lake Biwa’s “manager,” Shinji Sato, Yuki Ito and the development team came together to produce this next generation big crank. This giant killer crank will dramatically increase contact rates with big bass. * The photograph is a prototype.</v>
       </c>
-      <c r="O191" t="str">
-        <v/>
-      </c>
-      <c r="P191" t="str">
-        <v/>
-      </c>
-      <c r="Q191" t="str">
-        <v/>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -9980,15 +8850,6 @@
       <c r="N192" t="str">
         <v>The PROJECT LEGEND LD series concept places current designs for custom-tuning at the hands of Yuki Ito. The first lure to receive this treatment is the Knuckle 60, which has been fine-tuned with a circuit-board lip to tackle the tough waters of Japan. The thin, durable lip activates the KNUCKLE LD, making the bait even more responsive in the water, exhibiting a heightened high-pitch wobble &amp; roll action. Additionally, the front hook is equipped with lightweight heavy-duty swivel to increase hook up ratio and virtually eliminate lost fish. Internal weight balancer is secured from multiple angles to achieve a truly silent approach. Specially-tuned to catch that key fish in the toughest conditions. * The photograph is a prototype.</v>
       </c>
-      <c r="O192" t="str">
-        <v/>
-      </c>
-      <c r="P192" t="str">
-        <v/>
-      </c>
-      <c r="Q192" t="str">
-        <v/>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -10033,15 +8894,6 @@
       <c r="N193" t="str">
         <v>バイブレーションX ウルトラは、伊東独自のハイドロダイナミクスによるボディフォーミングが普遍的釣果をもたらしてきました。 新たに開発したウェイトパッケージングによりいっそう強化された超高速・ハイピッチロールドライブは、シャープかつ鋭いエッジの振動を生み、独自のプロペラ形状のボディが整流する際生み出す圧倒的な水流撹拌力と相まって、未知のランカーにアピール。 ボディ表面に波打つトーン変化を積極的に生み出し、視覚効果も最大限に引き出します。 バイブレーションXの爆釣伝説は不滅です。</v>
       </c>
-      <c r="O193" t="str">
-        <v/>
-      </c>
-      <c r="P193" t="str">
-        <v/>
-      </c>
-      <c r="Q193" t="str">
-        <v/>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -10086,15 +8938,6 @@
       <c r="N194" t="str">
         <v>The DYNA RESPONSE is a new concept metal vibe developed by Shinji Sato. The super-thin 0.6mm stainless plate cuts through water and features a carefully sculped weight design that generates powerful vibrations and quick start-up action. The weight’s hydrodynamic design powers a sharp, high pitch action and kicks into gear instantaneously whether employing lift &amp; fall or more traditional retrieves. The placement of the rear treble and innovative tinsel-tail detail significantly reduce line tangle on slack line and at the end of long casts, in addition to providing an enticingly new flicker-flash to the DYNA RESPONSE’s vibrating action. With its outsized flash, high-pitch vibration, tangle-fighting tinsel and lightning-quick startup action, the DYNA RESPONSE elevates the traditional metal vibe to new heights.</v>
       </c>
-      <c r="O194" t="str">
-        <v/>
-      </c>
-      <c r="P194" t="str">
-        <v/>
-      </c>
-      <c r="Q194" t="str">
-        <v/>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -10139,15 +8982,6 @@
       <c r="N195" t="str">
         <v>バイブレーションX スマトラは、伊東独自のハイドロダイナミクスによるボディフォーミングが普遍的釣果をもたらしてきました。 新たに開発したウェイトパッケージングによりいっそう強化された超高速・ハイピッチロールドライブは、シャープかつ鋭いエッジの振動を生み、独自のプロペラ形状のボディが整流する際生み出す圧倒的な水流撹拌力と相まって、未知のランカーにアピール。 ボディ表面に波打つトーン変化を積極的に生み出し、視覚効果も最大限に引き出します。 バイブレーションXの爆釣伝説は不滅です。</v>
       </c>
-      <c r="O195" t="str">
-        <v/>
-      </c>
-      <c r="P195" t="str">
-        <v/>
-      </c>
-      <c r="Q195" t="str">
-        <v/>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -10192,15 +9026,6 @@
       <c r="N196" t="str">
         <v>※The photograph is a prototype.</v>
       </c>
-      <c r="O196" t="str">
-        <v/>
-      </c>
-      <c r="P196" t="str">
-        <v/>
-      </c>
-      <c r="Q196" t="str">
-        <v/>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -10245,15 +9070,6 @@
       <c r="N197" t="str">
         <v>The concept behind the VIBRATION-X DYNA is high power + compact body!! The DYNA combines a bite-sized silhouette with violent rolling, ultra high-pitch vibration, overwhelming flight distance, and exceptional structure evasion performance. The internal weights are positioned to give the lowest possible center of gravity, increasing stability. The nose cup catches water flow, dramatically increasing responsiveness during actions. The exceptional initial swimming performance at the start of retrieves helps to increase the productive zone of the lure, allowing it to cover a wide area despite its small size. The DYNA is a little giant whose oversize vibrations and high-speed flashing puts past small vibes to shame. DYNA triggers the fighting instincts of neutral fish, drawing forth a new level of reaction bite. ※The photograph is a prototype.</v>
       </c>
-      <c r="O197" t="str">
-        <v/>
-      </c>
-      <c r="P197" t="str">
-        <v/>
-      </c>
-      <c r="Q197" t="str">
-        <v/>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -10298,15 +9114,6 @@
       <c r="N198" t="str">
         <v>1. Stop to Entice (Stop&amp;Go / Stay＆Jerk) The VIBRATION-X VATALION dramatically changes the strategy for targeting suspended bass. Twitching the lure results in dynamic 240-degree+ turns and intense flashing from the jointed body. In muddy water, the appeal of its broad, flat side far exceeds thin bodied jerkbaits and draws out many bites. The intermediate settings, the small “chip bill” that allows it to keep a consistent depth in shallows, the nose position line eye, the jointed slant tail—all of these features actively draw out those slow, reluctant fish in the shallows with the perfect “stop” approach. Whether it’s using stop &amp; go tactics to help evade the numerous structures in shallow areas or using stay &amp; jerk tactics immediately below the surface in weeded areas, this lure will help you get those suspended fish that spinnerbait and crankbait can’t touch. Watch it stimulate their activity level and land bite after bite. 2. Straight Retrieves in Shallows (Hi-Pitch - Straight Retrieve) During straight retrieves, it displays lifelike shimmering action, and the body segments contact each other to produce a sound that draws predators. It effectively draws bites from the shallow and midrange, covering a wide area. * The photograph is a prototype.</v>
       </c>
-      <c r="O198" t="str">
-        <v/>
-      </c>
-      <c r="P198" t="str">
-        <v/>
-      </c>
-      <c r="Q198" t="str">
-        <v/>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -10351,15 +9158,6 @@
       <c r="N199" t="str">
         <v>LEVEL SWIMMERは、より遠くのエリア、より深くのレンジ攻略を可能としたヘヴィーシンキング・プロップベイト。ただ巻くだけでバイトを得られる効率的な釣獲パフォーマンスは、高い集魚効果を兼ね備えた喰わせのフィネスベイトです。 一口サイズの「低重心・ヘヴィウェイテッドボディ」は、圧倒的なロングキャスタビリティを実現。狙いのレンジに速やかに到達し、広域のターゲットにアピールするサーチベイトとして威力を発揮します。 ミディアム～ディープレンジに到る、あらゆる水深で発揮される「超長距離・I字系スイム」＋「波動」＋「マイクロシルエット」は、従来のスピナーベイトやクランクベイトを見切ったタフな魚をバイトに持ち込みます。</v>
       </c>
-      <c r="O199" t="str">
-        <v/>
-      </c>
-      <c r="P199" t="str">
-        <v/>
-      </c>
-      <c r="Q199" t="str">
-        <v/>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -10404,15 +9202,6 @@
       <c r="N200" t="str">
         <v>The i-SLIDE 265R is a magnum glide bait that further refines the monster bass pedigree of the 262T, exhibiting decisive glides and sinuous slides to tempt the next generation of trophy catches. Featuring a crisp, responsive S-swimming slalom as its base action, the i-SLIDE 265R demonstrates tenacious stability even in rivers and backwater current. With a twitch or varied retrieve speed, it seamlessly performs underwater dog-walks and continuous turns, responding expertly to angler input. And with a reinforced internal wire harness and heavy-duty swiveling hook hangars, the 265R is built to overwhelm even the most brutal fighters, ensuring that hard-won bites land where they belong. Thanks to the R “Revolution Model” series engineering, even rough rod work translates into sharp slalom actions and quick, responsive slides—making advanced techniques accessible to anglers of all skill levels. The i-SLIDE “R” series promises dramatic encounters that will shatter your personal best.</v>
       </c>
-      <c r="O200" t="str">
-        <v/>
-      </c>
-      <c r="P200" t="str">
-        <v/>
-      </c>
-      <c r="Q200" t="str">
-        <v/>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -10457,15 +9246,6 @@
       <c r="N201" t="str">
         <v>R is for Revolution. The i-SLIDE has evolved, bringing its confidence-inspiring glide to fresh heights. The i-SLIDE 187 R’s refined design puts the power of sharp S-motion action in the hands of all anglers, regardless of big bait experience. With a redesigned tail and retuned internal weighting, the new R delivers with greater consistence. With a straight retrieve, ¾ turns of the handle, or twitching rod work, the i-SLIDE performs with confident ease, delivering a sinuous “S” swimming action or a wide left/right glide. The 187 R offers a direct feel that allows the angler to clearly perceive the glide’s action even when out of sight, increasing the odds of continued success. The i-SLIDE 187 R delivers a confident glide, bringing the power of big baits to anglers in search of the next trophy catch. 【Floating Model】 The responsive sliding action and agile slalom movement, which instantly responds to retrieve movements, trigger active feeding. The 187R is easily tuned for a wide range of situations and suspend/sink rates by adjusting the hook and ring sizes and/or attaching weights. 【Intermediate Model】 The suspend setting makes it appealing to dormant monsters that typically remain undiscovered. This model can be used for dead-sticking to imitate baits drifting unprotected with no action, sliding slalom action in the mid-range, and other technical presentations depending on the situation, and target’s reaction.</v>
       </c>
-      <c r="O201" t="str">
-        <v/>
-      </c>
-      <c r="P201" t="str">
-        <v/>
-      </c>
-      <c r="Q201" t="str">
-        <v/>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -10510,15 +9290,6 @@
       <c r="N202" t="str">
         <v>The i-BRAKE’s unique brake fins bring hard stopping power to suppress the lure’s speed, adding a new bite trigger to swimbait games. As retrieve speed slows down, the soft tail pitches erratically, fluttering and dancing, while the brake fins push water. The lure's sudden stopping power delivers a writhing action, which in turn triggers more chases and bites. The i-BRAKE realistically mimics the defenseless and sudden start/stop movements of live bait. During retrieval, the combination of brake fins that create turbulent water displacement and a soft paddle-tail that produces a natural swim sends fine vibration throughout the body, attracting even the most cautious targets. The subtle attraction of the i-BRAKE proves its worth in challenging conditions such as the post-spawn period and autumn turnover, where conventional approaches often struggle. This unique stopping ability delivers overwhelming bites when other approaches fall silent.</v>
       </c>
-      <c r="O202" t="str">
-        <v/>
-      </c>
-      <c r="P202" t="str">
-        <v/>
-      </c>
-      <c r="Q202" t="str">
-        <v/>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -10563,15 +9334,6 @@
       <c r="N203" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O203" t="str">
-        <v/>
-      </c>
-      <c r="P203" t="str">
-        <v/>
-      </c>
-      <c r="Q203" t="str">
-        <v/>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -10616,15 +9378,6 @@
       <c r="N204" t="str">
         <v>SPINE-X is a segmented subsurface swimbait equipped with an innovative user-controlled wire-through titanium spinal system to deliver dynamic action. Megabass’ LIVE-WIRED SYSTEM(PAT.P) leverages the shape-memory properties of titanium wire to add layers of customizable control to SPINE-X’s swimming movement. Included with three titanium “spines,” anglers can add multiple wires at a time for tighter “s” swimming and a faster recovery rate between segmented joints. By changing the number of titanium wires, anglers can adjust the suppleness and tension of SPINE-X to perfectly match angler input and target preferences. This not only enables situation-specific tuning but adds a dynamic element of internal tension to the swimbait’s movement, contributing to its lifelike appeal. Developed to target those exceedingly discerning trophy predators, SPINE-X swims with sinuous flash and sends twitches and jerks shuddering from tip to tail with unsurpassed realism.</v>
       </c>
-      <c r="O204" t="str">
-        <v/>
-      </c>
-      <c r="P204" t="str">
-        <v/>
-      </c>
-      <c r="Q204" t="str">
-        <v/>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -10669,15 +9422,6 @@
       <c r="N205" t="str">
         <v>GORHAM is a jointed waking and subsurface bait with a mysterious presence that awakens distant neutral targets. GORHAM’s articulated body is equipped with two synchronized LBO II(PAT.) systems in each section. This patented moving balancer system significantly improves flight posture and cast distance, while providing optimal swimming balance for immediate action startup. As a result, GORHAM’s attack range is dramatically increased, bringing far-off targets within easy reach. A dynamic, ultra-wide rolling wake action calls targets to GORHAM from greater distances, inspiring frenzied surface attacks. The unique RAMBLE TAIL provides an erratic disturbance that triggers the instincts of hesitant surface feeders. GORHAM opens the door to new topwater potential, triggering bites from otherwise dormant targets. SLOW RETRIEVE With a slow retrieve, GORHAM’s natural tail swing paired with the movement of its jointed body create an ultra-realistic, sinuous flashing wake action on the surface. FAST RETRIEVE With a fast retrieve, GORHAM dives into the shallow subsurface range, moving with a large flashing and rolling action that generates bulging water displacement, triggering the active feeding instincts of targets who lurk in search of a fleeing meal. Work in a twitch to incite bites from targets hot on the trail.</v>
       </c>
-      <c r="O205" t="str">
-        <v/>
-      </c>
-      <c r="P205" t="str">
-        <v/>
-      </c>
-      <c r="Q205" t="str">
-        <v/>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -10722,15 +9466,6 @@
       <c r="N206" t="str">
         <v>SuWITCH is equipped with the patented transforming lip system pioneered in the XPOD. This revolutionary system allows the angler to change the angle of the lip with a firm “click” to instantly switch between different target ranges and action profiles. “Su” means four. SuWITCH, or "four witches," has a diversely destructive power that joins four seemingly magical powers into a single lure. It is a new generation of multi-purpose swimbait that can switch up its diving range and action to suit the situation.Equipped with the world's first "2-step variable bill" one-touch lip adjustment mechanism for swimbaits, SuWITCH switches seamlessly between "wake mode" and "dive mode" at the angler’s behest. In each mode, the lure can be retrieved with either a straight retrieve or with the additional dynamism of twitching and jerking rod work. Thus, a single lure can produce actions with four different appealing characteristics.</v>
       </c>
-      <c r="O206" t="str">
-        <v/>
-      </c>
-      <c r="P206" t="str">
-        <v/>
-      </c>
-      <c r="Q206" t="str">
-        <v/>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -10775,15 +9510,6 @@
       <c r="N207" t="str">
         <v>The secret behind GARUDA’s overwhelming ability to attract fish and elicit bites rests in its powerful movement, painstaking detail, and the quality of its sound. Double-jointed construction and careful design drive smooth, sinuous action punctuated by the enticing “knock” of GARUDA’s joints coming in contact. Spec’d as a floating lure, GARUDA is also designed to attach teardrop sinkers to the underside of the lip to fine-tune for virtually any depth range. For fishing that involves bottom contact, GARUDA can be “back hook tuned” by removing the trebles, and attaching a single hook to the top of the lure. The back of the lure, where the groove for hook shank is located, features a neodymium magnet MAGHOLD (PAT.) system to keep the top hook in place. The GARUDA’s overwhelming destructive power is perfect for top range dead sticking and waking, mid-range retrieves, bottom contact, and anything a monster hunter could possibly desire from a big bait. GARUDA is built to bring you results beyond your imagination. * BOMBADA SNAP OVO Size: No.3 Equipped standard * The photograph is a prototype.</v>
       </c>
-      <c r="O207" t="str">
-        <v/>
-      </c>
-      <c r="P207" t="str">
-        <v/>
-      </c>
-      <c r="Q207" t="str">
-        <v/>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -10828,15 +9554,6 @@
       <c r="N208" t="str">
         <v>ジャマイカボアは、全米で人気のOROCHI BUZZをベースに、トーナメントユースに特化したスペックでデザイン。広域エリアを効率よくサーチでき、遭遇するあらゆるカヴァーをものともせずに引き倒すことができ、込み合うカヴァーから果敢にビッグウエイトを引き抜いてランディングに持ち込める、競技スペックのヘビーデューティーバズベイトです。 広域に散るバスを的確に訴求するマンタプロップの卓越した集魚効果もトップカテゴリーのプロたちが絶賛。広域シャローでバスの有無を確認したいとき、ジャマイカボアがシークレットベイトとして使われる理由のひとつです。 トーナメントでサーチしたい多様なシャローのカヴァーエリアからハイスコアを叩きだすための革新的スペックが満載。「勝つ」ために使うバズベイトが、ジャマイカボアです。</v>
       </c>
-      <c r="O208" t="str">
-        <v/>
-      </c>
-      <c r="P208" t="str">
-        <v/>
-      </c>
-      <c r="Q208" t="str">
-        <v/>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -10881,15 +9598,6 @@
       <c r="N209" t="str">
         <v>ジャマイカボアは、全米で人気のOROCHI BUZZをベースに、トーナメントユースに特化したスペックでデザイン。広域エリアを効率よくサーチでき、遭遇するあらゆるカヴァーをものともせずに引き倒すことができ、込み合うカヴァーから果敢にビッグウエイトを引き抜いてランディングに持ち込める、競技スペックのヘビーデューティーバズベイトです。 広域に散るバスを的確に訴求するマンタプロップの卓越した集魚効果もトップカテゴリーのプロたちが絶賛。広域シャローでバスの有無を確認したいとき、ジャマイカボアがシークレットベイトとして使われる理由のひとつです。 トーナメントでサーチしたい多様なシャローのカヴァーエリアからハイスコアを叩きだすための革新的スペックが満載。「勝つ」ために使うバズベイトが、ジャマイカボアです。</v>
       </c>
-      <c r="O209" t="str">
-        <v/>
-      </c>
-      <c r="P209" t="str">
-        <v/>
-      </c>
-      <c r="Q209" t="str">
-        <v/>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -10934,15 +9642,6 @@
       <c r="N210" t="str">
         <v>マグドラフトフリースタイルにジャストフィットする専用ジグヘッド。マグドラフトの卓越した誘いのアクションを最適化させるバランスで設計されています。ラインアイ周りの容積を削ぎ落して底面を張り出すことによる徹底した低重心ヘッドは、極めて安定したスイミングアクションと驚異的な障害物回避性能を発揮。重量級ヘッドはオリジナル・マグドラフトよりもさらに深いレンジの攻略を可能とします。</v>
       </c>
-      <c r="O210" t="str">
-        <v/>
-      </c>
-      <c r="P210" t="str">
-        <v/>
-      </c>
-      <c r="Q210" t="str">
-        <v/>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -10987,15 +9686,6 @@
       <c r="N211" t="str">
         <v>Crafted for victory in the toughest fields, the SV-3 draws inspiration from the legendary V-3, which earned its place in history as one of the pioneering baitfish-head spinnerbaits. Our “Super” V-3 spinnerbait is the embodiment of design and angling expertise, developed for top-level pros competing in the most challenging tournaments. This most recent masterpiece comes fully loaded with a number of innovative specs to earn its place in angler arsenals for years to come.</v>
       </c>
-      <c r="O211" t="str">
-        <v/>
-      </c>
-      <c r="P211" t="str">
-        <v/>
-      </c>
-      <c r="Q211" t="str">
-        <v/>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -11040,15 +9730,6 @@
       <c r="N212" t="str">
         <v>MEGABASS of America Inc.とメガバスUSAプロチームが一推しする、「オカシラ・スクリューヘッド」が米トーナメントのタフな状況をことごとく打開しています。翼形状が左右非対称に設計されたITOプロップ（ITO-Engineering製）を搭載し、デッドスローリトリーブ時やフォール時にイレギュラーな微波動とフラッシングを発生。バイトチャンスを積極的に生み出します。 また、アゴ下のウォータースルーレーンが、プロペラのスムーズな回転と適切なスイム姿勢、レンジキープ力をサポート。中層にサスペンドするニュートラルフィッシュをフィーディングモードに変えてしまう、マジカルなジグヘッドです。</v>
       </c>
-      <c r="O212" t="str">
-        <v/>
-      </c>
-      <c r="P212" t="str">
-        <v/>
-      </c>
-      <c r="Q212" t="str">
-        <v/>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -11093,15 +9774,6 @@
       <c r="N213" t="str">
         <v>フィッシュヘッドジグの決定版、「オカシラヘッド」は、シェイキング時のアクション、フォール姿勢、スイム姿勢、トラブルの回避性、フックアップ率の向上を徹底追求したファンクショナルなベイトフェイス・ジグヘッド。 正面から見てデルタ形状のヘッドは、シェイキングではパタパタとハタめくヒラウチ効果を発揮。アゴ下に設けたウォータースルーレーンは優れた直進安定性とベイトフィッシュライクなスイム姿勢を生み出します。 また、エラ内部にオフセットされて深くソフトベイトが装着できるデザインによって、様々なソフトベイトをシームレスに装着できます。沈下時は、通常のジグヘッドとは異なり、「水平姿勢」を保持したスパイラルフォールを生み出します。装着するだけでソフトベイトの性能を一段と高められる、元祖フィッシュヘッドジグです。</v>
       </c>
-      <c r="O213" t="str">
-        <v/>
-      </c>
-      <c r="P213" t="str">
-        <v/>
-      </c>
-      <c r="Q213" t="str">
-        <v/>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -11146,15 +9818,6 @@
       <c r="N214" t="str">
         <v>「オカシラヘッドHG」は、3/8oz.以上の専用設計を行ったミディアム・ヘヴィウエイテッド・ジグヘッド。求められる操作性、姿勢安定性、レンジキープ性能、障害物回避性能、フッキング性能等を高次元にまとめ上げました。低重心設計によるデルタ形状ヘッドは安定したスイム姿勢を保ち、適切な重量バランスによって操作性とレンジキープ力を高めています。また、ロングノーズフェイスがスタックを回避し、横方向に張り出したヘッド後端が根掛かりを高確率で回避。また、エラ部分はソフトベイトの接触面を隠し、深くインサートさせるオフセット形状により、様々な先端形状のソフトベイトをシームレスに装着できます。 ソフトベイトの潜在能力を一段と引き出すための、メガバス独自の高機能ジグヘッドです。</v>
       </c>
-      <c r="O214" t="str">
-        <v/>
-      </c>
-      <c r="P214" t="str">
-        <v/>
-      </c>
-      <c r="Q214" t="str">
-        <v/>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -11199,15 +9862,6 @@
       <c r="N215" t="str">
         <v>The ROBIN BLADE is a bladed created with extreme usability in mind. It was designed with the goal of achieving high straight-running stability, as well as the range-keeping ability needed to continually  adjust to the feeding range of bass. Even when the tips of weeds cling to the lure, it still transmits the sharp, ultra high-pitch vibrations right to your fingertips with certainty. In order to combine these two features into a high-level lure, Megabass designed its own unique HEXA-V plate utilizing a vertical folding process. In addition, the original hook features double worm keepers that securely hold trailer worms, along with the overwhelming strength needed to combat the power of extreme monsters. From your initial approach to the heated fight itself, this lure will make your encounters with monster bass a sure thing.</v>
       </c>
-      <c r="O215" t="str">
-        <v/>
-      </c>
-      <c r="P215" t="str">
-        <v/>
-      </c>
-      <c r="Q215" t="str">
-        <v/>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -11252,15 +9906,6 @@
       <c r="N216" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O216" t="str">
-        <v/>
-      </c>
-      <c r="P216" t="str">
-        <v/>
-      </c>
-      <c r="Q216" t="str">
-        <v/>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -11305,15 +9950,6 @@
       <c r="N217" t="str">
         <v>The UOZE SWIMMER is a new surefire concept bait proposed by Megabass. The realistic head features a nose section narrowed down to the limit, allowing it excel at slipping through obstacles such as rocks, branches, and weeds. The protrusions around the gills allow it to generate an optimal amount of water stirring, which combined with the low center of gravity design provide for stable range keeping ability. the tight blade attached to the titanium shape memory wire make wide ranged appeals through flashing and vibrations possible in areas of low visibility such as weed jungles. The flexible titanium shape memory wire does not interfere with hooking bites, and by allowing the blade to make contact with the bottom and structures before the body of the lure, the lure is prevented from diving too deep into obstacles, making delicate tracing and retrieves possible. The UOZE SWIMMER is equipped with a custom long shank wide gap hook. This foolproof design pierces through the jaws of monsters with accuracy, reliably landing them.</v>
       </c>
-      <c r="O217" t="str">
-        <v/>
-      </c>
-      <c r="P217" t="str">
-        <v/>
-      </c>
-      <c r="Q217" t="str">
-        <v/>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -11358,15 +9994,6 @@
       <c r="N218" t="str">
         <v>「マキッパFFS」は、ブランドン・パラニュークをはじめ、メガバスUSAプロスタッフの熱烈な要望から生まれた、FFS（Forward Facing Sonar）専用の「勝つための」ブレードジグです。コンパクトでスリムなMAKIPPAボディに、定評あるメガバス独自のブレードフックシステム（PAT.P）を搭載。ターゲットに見切られずにブレードバイトを積極的に絡め獲る、競技志向のフィネス・ブレードジグです。 高比重ウエイト設計により、狙いのレンジへ素早く到達。軽いトゥイッチやシェイクなどの繊細な操作に即応し、ボディ＆ブレードが放つフラッシングは、ターゲットに対してひと口サイズながらも強烈な存在感を発揮。レンジキープリトリーブと意図的なラインシェイクを組み合わせることで、低活性時でもバイトを引き出します。 リトリーブスピードを上げれば、ブレードの高速回転が逃走するベイトを想起させる鮮烈な閃光と波動を発生。FFSでは、他のルアーでは口を使わなかったターゲットがMAKIPPA FFSにリアクションバイトしてしまう、一線を画した反応がご覧いただけます。</v>
       </c>
-      <c r="O218" t="str">
-        <v/>
-      </c>
-      <c r="P218" t="str">
-        <v/>
-      </c>
-      <c r="Q218" t="str">
-        <v/>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -11411,15 +10038,6 @@
       <c r="N219" t="str">
         <v>METAL-Xは、独自の非対称フォルムとウエイトバランスによる水平フォールが、ベイトライクなナチュラルシルエットとフォールスピードを最適化。あらゆるターゲットに見切られる事なく捕食本能に火を点けます。 ボディマテリアルは軽比重の特殊合金を採用し、絶妙なフォールスピードでリアクションバイトを誘発、高確率でフッキングへ持ち込みます。 ディープエリアや低水温期はもちろん、ハイプレッシャーなタフコンディションや、リアクションでしか口を使わない状況において、他のルアーとは一線を画した釣果をもたらすシークレット・ベイトです。</v>
       </c>
-      <c r="O219" t="str">
-        <v/>
-      </c>
-      <c r="P219" t="str">
-        <v/>
-      </c>
-      <c r="Q219" t="str">
-        <v/>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -11464,15 +10082,6 @@
       <c r="N220" t="str">
         <v>X-BLAZARは、佐藤信治が提唱する新機軸テールスピンジグ。 いかなる時も安定したスイムを生み出す特殊合金製の低重心ボディに加え、専用設計のSV-BLADEがエッジの立った鋭いバイブを発生させ、激しいストロボ明滅を広角に放ちます。 ブレードの回転角を変化させるセッティングが、メリハリの効いた明滅と、手元まで確実に伝達されるエッジの立ったバイブレーションを発揮。その際に生まれる強波動は、ディープフィッシュが抗えない驚異的な集魚力とフィーディングへの覚醒を生み出します。 また、メタルルアーで発生しがちなライン絡みのトラブルやフックトラブルを軽減化。ブレードバイトを確実にフッキングに持ち込むためのセッティングも追求しました。 お目当てのレンジに素早く到達し、レンジコントロール性能に優れたX-BLAZARは、ライブシューティングにおいても卓越したパフォーマンスを発揮します。</v>
       </c>
-      <c r="O220" t="str">
-        <v/>
-      </c>
-      <c r="P220" t="str">
-        <v/>
-      </c>
-      <c r="Q220" t="str">
-        <v/>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -11517,15 +10126,6 @@
       <c r="N221" t="str">
         <v>タフフィッシュを微塵も迷わせず、果敢にバイトを引き出すフィーディングマジックスイマー「マグドラフト」をウェイテッドフックやジグヘッドなどを用いて使えるフリースタイル・ボディフォームを実現したのが、マグドラフトフリースタイルです。全米のトーナメントを席捲し続けているオリジナル・マグドラフト同様の釣獲力はお墨付き。込み合うカヴァーエリアにストレスなく、果敢なアプローチが出来る頼れる存在です。</v>
       </c>
-      <c r="O221" t="str">
-        <v/>
-      </c>
-      <c r="P221" t="str">
-        <v/>
-      </c>
-      <c r="Q221" t="str">
-        <v/>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -11570,15 +10170,6 @@
       <c r="N222" t="str">
         <v>■ Designed to draw in predators with both slow and fast retrieves. ■ Megabass' exclusive MAGHOLD SYSTEM (PAT.P) and belly slit will secure hooks in place to minimize the visual presence of unnatural treble hooks.</v>
       </c>
-      <c r="O222" t="str">
-        <v/>
-      </c>
-      <c r="P222" t="str">
-        <v/>
-      </c>
-      <c r="Q222" t="str">
-        <v/>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -11623,15 +10214,6 @@
       <c r="N223" t="str">
         <v>MAGDRAFT ハスレイバーは、「つねに動いてしまう」多くの可動セクションを持つ新次元のスイミング・マニピュレーターです。3連ボディ＆極薄ジョイントによる独自のボディシェイプは、わずかな水流でヒラヒラと艶めかしく動くライブフィンと相まって、タダ巻きだけで生命感溢れるリアルな泳ぎを披露。しなやかなアクションは、疑似生命体とでも呼ぶべき、ナチュラルベイトそのものを演出。水面直下のロングストローク・ジャークでは、本物のパニックベイトが逃げ惑うような瞬間移動的なエスケープアクションを披露。ストレートリトリーブにチェイスしつつも喰わなかったターゲットに対し、ジャークで捕食本能にスイッチを入れ、一撃でバイトに持ち込みます。 ストッピングの瞬間に発生する絶妙な揺らめき、リトリーブスピードを上げるたび引き起こされるパニックエスケープなど、単純動作を加えるだけで喰わせてしまう驚異の被捕食率が、HASU RAVERの凄いところ。 MAGHOLD(PAT.P)システムにより、フックはボディに磁着され、フックの存在をカモフラージュ。タフなターゲットに対する違和感をなくし、フレキシブルでナチュラルなアクションを披露。リザーバーのハスパターンをはじめ、落ち鮎、ウグイなど大型のベイトパターンにアジャストするHASU RAVERは、従来スイムベイトの誘いを見切ったターゲットに異次元の釣獲力をいかんなく発揮します。</v>
       </c>
-      <c r="O223" t="str">
-        <v/>
-      </c>
-      <c r="P223" t="str">
-        <v/>
-      </c>
-      <c r="Q223" t="str">
-        <v/>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -11676,15 +10258,6 @@
       <c r="N224" t="str">
         <v>MAGDRAFT AYU TWITCHER is a shallow-swimming technical swimbait that adapts its action depending on retrieve speed and rod work. Megabass' proprietary MAGHOLD(PAT.P) system magnetizes the hook to the body, camouflaging its presence and reducing interference with the bait’s movement. The AYU TWITCHER's highly responsive design provides outstanding swimming performance in fields where currents interfere, such as rivers and backwaters. In slack-water games, it enables precise contact and actively triggers the reaction bite of clever fish.</v>
       </c>
-      <c r="O224" t="str">
-        <v/>
-      </c>
-      <c r="P224" t="str">
-        <v/>
-      </c>
-      <c r="Q224" t="str">
-        <v/>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -11729,15 +10302,6 @@
       <c r="N225" t="str">
         <v>MAGDRAFT AYU TWITCHER is a shallow-swimming technical swimbait that adapts its action depending on retrieve speed and rod work. Megabass' proprietary MAGHOLD(PAT.P) system magnetizes the hook to the body, camouflaging its presence and reducing interference with the bait’s movement. The AYU TWITCHER's highly responsive design provides outstanding swimming performance in fields where currents interfere, such as rivers and backwaters. In slack-water games, it enables precise contact and actively triggers the reaction bite of clever fish.</v>
       </c>
-      <c r="O225" t="str">
-        <v/>
-      </c>
-      <c r="P225" t="str">
-        <v/>
-      </c>
-      <c r="Q225" t="str">
-        <v/>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -11782,15 +10346,6 @@
       <c r="N226" t="str">
         <v>DARK SLEEPER was developed to target fish holding to bottom structure with overwhelming realism and paddle-tail action. With a top fin designed both to camouflage its hook, and gently deflect off of structure, DARK SLEEPER is able to hold tight to cover, and move through complex structure. Low center of gravity weight setting and bottom fins keep DARK SLEEPER upright as it moves through structure, for a naturally appealing approach.</v>
       </c>
-      <c r="O226" t="str">
-        <v/>
-      </c>
-      <c r="P226" t="str">
-        <v/>
-      </c>
-      <c r="Q226" t="str">
-        <v/>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -11835,15 +10390,6 @@
       <c r="N227" t="str">
         <v>When deploying gill and crucian carp patterns, there are situations where regular swimbaits and fast-moving lures are not enough to tempt discerning predators. In such situations, the SLEEPER GILL’s unrivaled realism and enticing slow-retrieve ability conjure key bites. Featuring an adaptation of the dorsal fin weed guard pioneered by the DARK SLEEPER, the SLEEPER GILL can be sent where others fear to swim. Its jungle-crawling ability enables precision targeting of intricate laydowns, cover areas, weeds, standing timber, bottom structure, and more. Designed with a concealed top hook to trick veteran targets, the body features a hollow zone that compresses with the bite for sure hooksets. Low center of gravity design and pectoral fin balancers contribute to bottom-contact swimming stability, allowing for stealthy approaches through key structure areas.</v>
       </c>
-      <c r="O227" t="str">
-        <v/>
-      </c>
-      <c r="P227" t="str">
-        <v/>
-      </c>
-      <c r="Q227" t="str">
-        <v/>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -11888,15 +10434,6 @@
       <c r="N228" t="str">
         <v>The long-awaited, bottom-scuttling stealth craw has arrived. SLEEPER CRAW harnesses the revolutionary performance of the SLEEPER series, bringing its hidden-hook design, enticing realism, and undeniable fish-catching ability to the staid category of conventional craw imitators. Unlike traditional offerings, the SLEEPER CRAW’s weight and hook are concealed within its body. This presents a stealthy package that lulls targets into natural, long-duration bites and reduces the chances of snagging, allowing anglers to move from dock skipping to laydowns to more traditional rockpiles with confidence. Constructed with a buoyant, highly durable material with a custom scent, the SLEEPER CRAW rests in the claws-up ready position and moves with uncanny realism. With an encased weight built to navigate treacherous rock formations without the unnatural sounds of lead or tungsten contact, the CRAW is perfectly suited to bottom-contact applications. Bring it to life with light line shake, a bottom-bumping drag, or vigorous hops; regardless of your technique, SLEEPER CRAW’s unique design will deliver fresh bites.</v>
       </c>
-      <c r="O228" t="str">
-        <v/>
-      </c>
-      <c r="P228" t="str">
-        <v/>
-      </c>
-      <c r="Q228" t="str">
-        <v/>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -11941,15 +10478,6 @@
       <c r="N229" t="str">
         <v>米エリートシリーズを果敢に戦い抜くプロフェッショナルバスアングラー、木村建太の知見を具現化する、勝つためのベイト。それは、快適なフィールで使うことができ、多様なシーンに高次元でフィットする優れたエルゴノミクスを有しています。 木村建太のYAGOTは、一見すると、まるでトンボのヤゴですが、その秘めたるパフォーマンスを解き放つ時、未知のバイトを多発させる稀代のクリーチャーとなるのです。 伊東由樹の流体デザイニングから造形される特異なボディフォーミングは、優れたキャスタビリティと遊泳姿勢をもたらす機能的なボディ体積をもたらし、生命感あふれる繊細かつ緻密なレッグバイブレーションを発生。高い機能性の追求から整合された殊勝なボディは、見る角度によってはバルキーであり、スリムでもある独特なフォルムです。 放つフィッシングパフォーマンスは、まさに未知との遭遇レベル。競技に勝つためのハイスコアのバイトを果敢に誘発する、魔訶不思議なベイトです。</v>
       </c>
-      <c r="O229" t="str">
-        <v/>
-      </c>
-      <c r="P229" t="str">
-        <v/>
-      </c>
-      <c r="Q229" t="str">
-        <v/>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -11994,15 +10522,6 @@
       <c r="N230" t="str">
         <v>ボトムの誘いにとどまらず、ジグストでも果敢にビッグバイトを連発させる驚異のリアクションマジック、SLAPHOGが覚醒。 米国B.A.S.S.ツアーを戦うチャレンジングなスペシャリスト、木村建太の熱い思いと知見、幾多のリアクションバイト伝説を築き上げたディープカップビーバーの開発者、伊東由樹のハイドロデザイニングが融合。圧倒的なリアクションバイトを引き出すSLAPHOGが生まれました。</v>
       </c>
-      <c r="O230" t="str">
-        <v/>
-      </c>
-      <c r="P230" t="str">
-        <v/>
-      </c>
-      <c r="Q230" t="str">
-        <v/>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -12047,15 +10566,6 @@
       <c r="N231" t="str">
         <v>The HAZE-ST is engineered to elevate strike responses from cruising, mid-column neutral fish—exhibiting refined action across the finesse spectrum from drop shots to mid-strolling. Designed for tournament pressure zones where career-defining bites must be coaxed from pinpoint areas, the HAZE-ST empowers anglers with the full spectrum of delicate, high-precision techniques. From a natural, near-motionless stick pose, it can erupt into vivid, pulsing vibrations and subtle micro-waves that elicit strikes from the most discerning predators. Its ultra-responsive behavior eliminates dead motion and delay, enabling instantaneous lifelike movement with even the lightest input. The HAZE-ST enhances the offensive power of finesse fishing, dramatically increasing bite chances from seasoned, pressure-weary lunkers that previously refused to react. HAZE-ST is born of Japan’s long history of finesse outperformance, delivering a purebred competition model built to win.</v>
       </c>
-      <c r="O231" t="str">
-        <v/>
-      </c>
-      <c r="P231" t="str">
-        <v/>
-      </c>
-      <c r="Q231" t="str">
-        <v/>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -12100,15 +10610,6 @@
       <c r="N232" t="str">
         <v>タイニーエクスレイヤーは、その可愛いサイズに似合わず、ニュートラルなビッグフィッシュにスイッチを入れてくれる、ファイナルシークレットです。また、ダウンショットリグでは、余計なアクションを与えず、ただスローにたぐり寄せてくるだけでオートマティックに魚を引き出す、究極のデッドスティッキングベイトとして活躍。ビッグベイトで叩きぬかれたメジャーなポンドでは、タイニーエクスレイヤーは、スプーキーなビッグフィッシュを最終的に引き出してしまう強さを持っています。</v>
       </c>
-      <c r="O232" t="str">
-        <v/>
-      </c>
-      <c r="P232" t="str">
-        <v/>
-      </c>
-      <c r="Q232" t="str">
-        <v/>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -12153,15 +10654,6 @@
       <c r="N233" t="str">
         <v>HAZEDONG's elegantly tapered tail moves with an enticing, undulating motion, making wary and sluggish fish bite. An excellent choice for a drop shot or Carolina Rig dragged along the bottom, where every little bump sends tremors down the length of the tail. HAZEDONG explodes into larger-than-life movement with rod work, putting on a mesmerizing, dynamic display at the end of your line. However, unlike many straight tail worms that are incapable of subtlety, HAZEDONG can also be brought to a deadly stillness by patient anglers lying in wait for discerning trophy-class targets.</v>
       </c>
-      <c r="O233" t="str">
-        <v/>
-      </c>
-      <c r="P233" t="str">
-        <v/>
-      </c>
-      <c r="Q233" t="str">
-        <v/>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -12206,15 +10698,6 @@
       <c r="N234" t="str">
         <v>The super-thin shad tail catches the water even during dead-slow retrieves and delicate shaking, triggering targets with its natural vibrations. The slits in the belly allow the body to compress when bitten, increasing hookup rates. Adding an offset hook helps as well. Featuring layered material of different densities, the HAZEDONG SHAD is able to maintain excellent stability even when used with no sinker rigs. In addition, this layering process allows for incredibly natural two-tone color patterns.</v>
       </c>
-      <c r="O234" t="str">
-        <v/>
-      </c>
-      <c r="P234" t="str">
-        <v/>
-      </c>
-      <c r="Q234" t="str">
-        <v/>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -12259,15 +10742,6 @@
       <c r="N235" t="str">
         <v>The SPARK SHAD is designed with a keel-like underside—similar to a boat’s hull—to deliver exceptional stability and range-keeping ability, even during long retrieves. Its slim tail construction kicks into gear from a crawling retrieve, emitting alluring, sinuous waves that provide subtle appeal to coax bites from cautious predators. The addition of pectoral fins and a flat back further enhances the lure’s action, harnessing a touch of roll to add dynamism to its swim without rotating out of the ideal zone of stability. The SPARK SHAD is made for highly pressured monsters—those wary targets that have seen it all and spook easily. Its ultra-refined action mimics the behavior of neutral, unsuspecting baitfish with stunning realism. By deliberately limiting body roll beyond a controlled axis, the lure keeps the hook point aligned, greatly improving the hookup ratio during chase-and-strike scenarios. When you need to tempt the wisest predators in their home waters, SPARK SHAD delivers unmatched subtle swimming appeal.</v>
       </c>
-      <c r="O235" t="str">
-        <v/>
-      </c>
-      <c r="P235" t="str">
-        <v/>
-      </c>
-      <c r="Q235" t="str">
-        <v/>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -12312,15 +10786,6 @@
       <c r="N236" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O236" t="str">
-        <v/>
-      </c>
-      <c r="P236" t="str">
-        <v/>
-      </c>
-      <c r="Q236" t="str">
-        <v/>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -12365,15 +10830,6 @@
       <c r="N237" t="str">
         <v>The BOTTLE SHRIMP is a hog-type worm which imitates freshwater prawns and crayfish, one of the main types of bait used around the world. When used for Texas rigs and jig trailers, the large power arms will push through the water, demanding the attention of target fish. With bottom contact, the inertia of the weighted arms will cause a shivering action to move from the tips of the power arms through the entire body, triggering bites. For no sinker rigs, nail rigs, and Carolina rigs, the power arm will swing left and right during the fall, creating a subtle waving motion. The slow and powerful wave motion created by the power arms and the quick, vivid trembling motion created by the legs will bring about a more complicated and realistic pulse from the whole body, captivating target fish.</v>
       </c>
-      <c r="O237" t="str">
-        <v/>
-      </c>
-      <c r="P237" t="str">
-        <v/>
-      </c>
-      <c r="Q237" t="str">
-        <v/>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -12418,15 +10874,6 @@
       <c r="N238" t="str">
         <v>SLING SHADは、ミノー形態のフラットサイドシルエットと微水流にも鋭敏に反応する繊細なフォークテールを併せ持つ、ソフトスティックベイト。 腹部に高比重マテリアルを配した二層比重構造により、オフセットフックによるノーシンカーリグでも安定したスイミングと適切なフォール姿勢を保持。トゥイッチやジャークでは、ソフトジャークベイトとして艶めかしい左右へのダートアクションでターゲットを狂わせます。 低重心効果をもたらす二層比重構造は、ジグヘッド装着時のミドストで連続的なヒラウチ・ロールアクションを創出。ロールアクションと連動してテール部に微細な振動をもたらし、よりいっそうアピールを高めます。ブレードジグやワイヤーベイトのトレーラーとしても優れたパフォーマンスを発揮します。</v>
       </c>
-      <c r="O238" t="str">
-        <v/>
-      </c>
-      <c r="P238" t="str">
-        <v/>
-      </c>
-      <c r="Q238" t="str">
-        <v/>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -12471,15 +10918,6 @@
       <c r="N239" t="str">
         <v>The TK TWISTER is a super multifunction worm capable of being used in any rig. With slight twitching, the tail wriggles from side to side as it performs a darting action. With no sinkers and Texas rigs, the delicate crustacean-like vibrations generated by the two tails and the unique presence that the body projects causes monsters to lock on. Quantity: TK TWISTER / 5 pieces , TK TWISTER Jr. / 8 pieces</v>
       </c>
-      <c r="O239" t="str">
-        <v/>
-      </c>
-      <c r="P239" t="str">
-        <v/>
-      </c>
-      <c r="Q239" t="str">
-        <v/>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -12524,15 +10962,6 @@
       <c r="N240" t="str">
         <v>MEGABASS &amp; ITO ENGINEERING / OUTBARB HOOKは、従来フックに用いる鋼材のおよそ1.3倍の引張強度を実現した特殊鋼材を使用。ITO ENGINEERINGによる特殊規格の細軸設計が、従来の同軸径ルアーフック(淡水用)の強度と貫通力を遥かに凌駕する圧倒的な釣獲パフォーマンスを発揮。 特殊フッ素コートにより貫通性能を極限まで高め、いかなる角度からのショートバイトやラフアタックも即掛けする、極のオリジナル・トリプルフックです。</v>
       </c>
-      <c r="O240" t="str">
-        <v/>
-      </c>
-      <c r="P240" t="str">
-        <v/>
-      </c>
-      <c r="Q240" t="str">
-        <v/>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -12577,15 +11006,6 @@
       <c r="N241" t="str">
         <v>メガバスルアーの性能を最大限に引き出す、純正のティンセルフック。 傷んだフックの交換用やフックチューンなどにご使用いただけます。 熟練の職人が一本一本丹精込めて仕上げます。</v>
       </c>
-      <c r="O241" t="str">
-        <v/>
-      </c>
-      <c r="P241" t="str">
-        <v/>
-      </c>
-      <c r="Q241" t="str">
-        <v/>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -12630,15 +11050,6 @@
       <c r="N242" t="str">
         <v>メガバスオリジナルロングフェザーフック。 ルアーアクションの安定性を向上させ、揺らめくフェザーがフックの存在感を希薄化し、スプーキーな魚をバイトに持ち込みます。</v>
       </c>
-      <c r="O242" t="str">
-        <v/>
-      </c>
-      <c r="P242" t="str">
-        <v/>
-      </c>
-      <c r="Q242" t="str">
-        <v/>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -12683,15 +11094,6 @@
       <c r="N243" t="str">
         <v>メガバスルアーの性能を最大限に引き出す、純正のティーザーフック。 傷んだフックの交換用や毛針チューンなどにご使用いただけます。 熟練の職人が一本一本丹精込めて仕上げます。</v>
       </c>
-      <c r="O243" t="str">
-        <v/>
-      </c>
-      <c r="P243" t="str">
-        <v/>
-      </c>
-      <c r="Q243" t="str">
-        <v/>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -12736,15 +11138,6 @@
       <c r="N244" t="str">
         <v>TREBLE HOOK OUTBARB</v>
       </c>
-      <c r="O244" t="str">
-        <v/>
-      </c>
-      <c r="P244" t="str">
-        <v/>
-      </c>
-      <c r="Q244" t="str">
-        <v/>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -12789,15 +11182,6 @@
       <c r="N245" t="str">
         <v>The BUDDHA HOOK was developed to handle those subtle bites often encountered in GREATHUNTING. Thin diameter wire drives razor-point home for sure and easy hooksets. Proprietary hook bend is designed to pin native Trout securely, while the light and supple hook design keeps damage to a minimum. * The photograph is a prototype.</v>
       </c>
-      <c r="O245" t="str">
-        <v/>
-      </c>
-      <c r="P245" t="str">
-        <v/>
-      </c>
-      <c r="Q245" t="str">
-        <v/>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -12842,15 +11226,6 @@
       <c r="N246" t="str">
         <v>Megabass original wing parts kit for the customization of the i-WING135. Entice those monsters with a customized i-WING! *i-WING135 is sold separately. * The photograph is a prototype.</v>
       </c>
-      <c r="O246" t="str">
-        <v/>
-      </c>
-      <c r="P246" t="str">
-        <v/>
-      </c>
-      <c r="Q246" t="str">
-        <v/>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -18002,7 +16377,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q363"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N363"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">

--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N363"/>
+  <dimension ref="A1:N396"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16371,9 +16371,1461 @@
         <v/>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>KL1000</v>
+      </c>
+      <c r="B364">
+        <v>35</v>
+      </c>
+      <c r="C364" t="str">
+        <v>スイングベイト2.8"</v>
+      </c>
+      <c r="D364" t="str">
+        <v>スイングベイト2.8"</v>
+      </c>
+      <c r="E364" t="str">
+        <v/>
+      </c>
+      <c r="F364" t="str">
+        <v/>
+      </c>
+      <c r="G364" t="str">
+        <v/>
+      </c>
+      <c r="H364" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I364" t="str">
+        <v/>
+      </c>
+      <c r="J364" t="str">
+        <v/>
+      </c>
+      <c r="K364" t="str">
+        <v/>
+      </c>
+      <c r="L364" t="str">
+        <v>2026-04-10T05:00:09.333Z</v>
+      </c>
+      <c r="M364" t="str">
+        <v>2026-04-10T05:00:09.333Z</v>
+      </c>
+      <c r="N364" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>KL1001</v>
+      </c>
+      <c r="B365">
+        <v>35</v>
+      </c>
+      <c r="C365" t="str">
+        <v>スイングインパクト</v>
+      </c>
+      <c r="D365" t="str">
+        <v>スイングインパクト</v>
+      </c>
+      <c r="E365" t="str">
+        <v/>
+      </c>
+      <c r="F365" t="str">
+        <v/>
+      </c>
+      <c r="G365" t="str">
+        <v/>
+      </c>
+      <c r="H365" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I365" t="str">
+        <v/>
+      </c>
+      <c r="J365" t="str">
+        <v/>
+      </c>
+      <c r="K365" t="str">
+        <v/>
+      </c>
+      <c r="L365" t="str">
+        <v>2026-04-10T05:00:16.169Z</v>
+      </c>
+      <c r="M365" t="str">
+        <v>2026-04-10T05:00:16.169Z</v>
+      </c>
+      <c r="N365" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>KL1002</v>
+      </c>
+      <c r="B366">
+        <v>35</v>
+      </c>
+      <c r="C366" t="str">
+        <v>スイングインパクトファット</v>
+      </c>
+      <c r="D366" t="str">
+        <v>スイングインパクトファット</v>
+      </c>
+      <c r="E366" t="str">
+        <v/>
+      </c>
+      <c r="F366" t="str">
+        <v/>
+      </c>
+      <c r="G366" t="str">
+        <v/>
+      </c>
+      <c r="H366" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I366" t="str">
+        <v/>
+      </c>
+      <c r="J366" t="str">
+        <v/>
+      </c>
+      <c r="K366" t="str">
+        <v/>
+      </c>
+      <c r="L366" t="str">
+        <v>2026-04-10T05:00:26.223Z</v>
+      </c>
+      <c r="M366" t="str">
+        <v>2026-04-10T05:00:26.223Z</v>
+      </c>
+      <c r="N366" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>KL1003</v>
+      </c>
+      <c r="B367">
+        <v>35</v>
+      </c>
+      <c r="C367" t="str">
+        <v>イージーシャイナー</v>
+      </c>
+      <c r="D367" t="str">
+        <v>イージーシャイナー</v>
+      </c>
+      <c r="E367" t="str">
+        <v/>
+      </c>
+      <c r="F367" t="str">
+        <v/>
+      </c>
+      <c r="G367" t="str">
+        <v/>
+      </c>
+      <c r="H367" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I367" t="str">
+        <v/>
+      </c>
+      <c r="J367" t="str">
+        <v/>
+      </c>
+      <c r="K367" t="str">
+        <v/>
+      </c>
+      <c r="L367" t="str">
+        <v>2026-04-10T05:00:31.150Z</v>
+      </c>
+      <c r="M367" t="str">
+        <v>2026-04-10T05:00:31.150Z</v>
+      </c>
+      <c r="N367" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>KL1004</v>
+      </c>
+      <c r="B368">
+        <v>35</v>
+      </c>
+      <c r="C368" t="str">
+        <v>グライドカマロン3.5"</v>
+      </c>
+      <c r="D368" t="str">
+        <v>グライドカマロン3.5"</v>
+      </c>
+      <c r="E368" t="str">
+        <v/>
+      </c>
+      <c r="F368" t="str">
+        <v/>
+      </c>
+      <c r="G368" t="str">
+        <v/>
+      </c>
+      <c r="H368" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I368" t="str">
+        <v/>
+      </c>
+      <c r="J368" t="str">
+        <v/>
+      </c>
+      <c r="K368" t="str">
+        <v/>
+      </c>
+      <c r="L368" t="str">
+        <v>2026-04-10T05:00:32.478Z</v>
+      </c>
+      <c r="M368" t="str">
+        <v>2026-04-10T05:00:32.478Z</v>
+      </c>
+      <c r="N368" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>KL1005</v>
+      </c>
+      <c r="B369">
+        <v>35</v>
+      </c>
+      <c r="C369" t="str">
+        <v>フラッパーグラブ4"</v>
+      </c>
+      <c r="D369" t="str">
+        <v>フラッパーグラブ4"</v>
+      </c>
+      <c r="E369" t="str">
+        <v/>
+      </c>
+      <c r="F369" t="str">
+        <v/>
+      </c>
+      <c r="G369" t="str">
+        <v/>
+      </c>
+      <c r="H369" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I369" t="str">
+        <v/>
+      </c>
+      <c r="J369" t="str">
+        <v/>
+      </c>
+      <c r="K369" t="str">
+        <v/>
+      </c>
+      <c r="L369" t="str">
+        <v>2026-04-10T05:00:33.726Z</v>
+      </c>
+      <c r="M369" t="str">
+        <v>2026-04-10T05:00:33.726Z</v>
+      </c>
+      <c r="N369" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>KL1006</v>
+      </c>
+      <c r="B370">
+        <v>35</v>
+      </c>
+      <c r="C370" t="str">
+        <v>ハイパースパイダー</v>
+      </c>
+      <c r="D370" t="str">
+        <v>ハイパースパイダー</v>
+      </c>
+      <c r="E370" t="str">
+        <v/>
+      </c>
+      <c r="F370" t="str">
+        <v/>
+      </c>
+      <c r="G370" t="str">
+        <v/>
+      </c>
+      <c r="H370" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I370" t="str">
+        <v/>
+      </c>
+      <c r="J370" t="str">
+        <v/>
+      </c>
+      <c r="K370" t="str">
+        <v/>
+      </c>
+      <c r="L370" t="str">
+        <v>2026-04-10T05:00:35.359Z</v>
+      </c>
+      <c r="M370" t="str">
+        <v>2026-04-10T05:00:35.359Z</v>
+      </c>
+      <c r="N370" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>KL1007</v>
+      </c>
+      <c r="B371">
+        <v>35</v>
+      </c>
+      <c r="C371" t="str">
+        <v>パドリンビーバー</v>
+      </c>
+      <c r="D371" t="str">
+        <v>パドリンビーバー</v>
+      </c>
+      <c r="E371" t="str">
+        <v/>
+      </c>
+      <c r="F371" t="str">
+        <v/>
+      </c>
+      <c r="G371" t="str">
+        <v/>
+      </c>
+      <c r="H371" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I371" t="str">
+        <v/>
+      </c>
+      <c r="J371" t="str">
+        <v/>
+      </c>
+      <c r="K371" t="str">
+        <v/>
+      </c>
+      <c r="L371" t="str">
+        <v>2026-04-10T05:00:37.011Z</v>
+      </c>
+      <c r="M371" t="str">
+        <v>2026-04-10T05:00:37.011Z</v>
+      </c>
+      <c r="N371" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>KL1008</v>
+      </c>
+      <c r="B372">
+        <v>35</v>
+      </c>
+      <c r="C372" t="str">
+        <v>ネコカマロン</v>
+      </c>
+      <c r="D372" t="str">
+        <v>ネコカマロン</v>
+      </c>
+      <c r="E372" t="str">
+        <v/>
+      </c>
+      <c r="F372" t="str">
+        <v/>
+      </c>
+      <c r="G372" t="str">
+        <v/>
+      </c>
+      <c r="H372" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I372" t="str">
+        <v/>
+      </c>
+      <c r="J372" t="str">
+        <v/>
+      </c>
+      <c r="K372" t="str">
+        <v/>
+      </c>
+      <c r="L372" t="str">
+        <v>2026-04-10T05:00:38.559Z</v>
+      </c>
+      <c r="M372" t="str">
+        <v>2026-04-10T05:00:38.559Z</v>
+      </c>
+      <c r="N372" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="B373">
+        <v>35</v>
+      </c>
+      <c r="C373" t="str">
+        <v>フレックスチャンク</v>
+      </c>
+      <c r="D373" t="str">
+        <v>フレックスチャンク</v>
+      </c>
+      <c r="E373" t="str">
+        <v/>
+      </c>
+      <c r="F373" t="str">
+        <v/>
+      </c>
+      <c r="G373" t="str">
+        <v/>
+      </c>
+      <c r="H373" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I373" t="str">
+        <v/>
+      </c>
+      <c r="J373" t="str">
+        <v/>
+      </c>
+      <c r="K373" t="str">
+        <v/>
+      </c>
+      <c r="L373" t="str">
+        <v>2026-04-10T05:00:40.270Z</v>
+      </c>
+      <c r="M373" t="str">
+        <v>2026-04-10T05:00:40.270Z</v>
+      </c>
+      <c r="N373" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="B374">
+        <v>35</v>
+      </c>
+      <c r="C374" t="str">
+        <v>Easy Shaker</v>
+      </c>
+      <c r="D374" t="str">
+        <v>Easy Shaker</v>
+      </c>
+      <c r="E374" t="str">
+        <v/>
+      </c>
+      <c r="F374" t="str">
+        <v/>
+      </c>
+      <c r="G374" t="str">
+        <v/>
+      </c>
+      <c r="H374" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I374" t="str">
+        <v/>
+      </c>
+      <c r="J374" t="str">
+        <v/>
+      </c>
+      <c r="K374" t="str">
+        <v/>
+      </c>
+      <c r="L374" t="str">
+        <v>2026-04-10T05:00:42.551Z</v>
+      </c>
+      <c r="M374" t="str">
+        <v>2026-04-10T05:00:42.551Z</v>
+      </c>
+      <c r="N374" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>KL1011</v>
+      </c>
+      <c r="B375">
+        <v>35</v>
+      </c>
+      <c r="C375" t="str">
+        <v>カスタムリーチ</v>
+      </c>
+      <c r="D375" t="str">
+        <v>カスタムリーチ</v>
+      </c>
+      <c r="E375" t="str">
+        <v/>
+      </c>
+      <c r="F375" t="str">
+        <v/>
+      </c>
+      <c r="G375" t="str">
+        <v/>
+      </c>
+      <c r="H375" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I375" t="str">
+        <v/>
+      </c>
+      <c r="J375" t="str">
+        <v/>
+      </c>
+      <c r="K375" t="str">
+        <v/>
+      </c>
+      <c r="L375" t="str">
+        <v>2026-04-10T05:00:45.695Z</v>
+      </c>
+      <c r="M375" t="str">
+        <v>2026-04-10T05:00:45.695Z</v>
+      </c>
+      <c r="N375" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>KL1012</v>
+      </c>
+      <c r="B376">
+        <v>35</v>
+      </c>
+      <c r="C376" t="str">
+        <v>ノイジーフラッパー</v>
+      </c>
+      <c r="D376" t="str">
+        <v>ノイジーフラッパー</v>
+      </c>
+      <c r="E376" t="str">
+        <v/>
+      </c>
+      <c r="F376" t="str">
+        <v/>
+      </c>
+      <c r="G376" t="str">
+        <v/>
+      </c>
+      <c r="H376" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I376" t="str">
+        <v/>
+      </c>
+      <c r="J376" t="str">
+        <v/>
+      </c>
+      <c r="K376" t="str">
+        <v/>
+      </c>
+      <c r="L376" t="str">
+        <v>2026-04-10T05:00:49.253Z</v>
+      </c>
+      <c r="M376" t="str">
+        <v>2026-04-10T05:00:49.253Z</v>
+      </c>
+      <c r="N376" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="B377">
+        <v>35</v>
+      </c>
+      <c r="C377" t="str">
+        <v>クレイジーフラッパー</v>
+      </c>
+      <c r="D377" t="str">
+        <v>クレイジーフラッパー</v>
+      </c>
+      <c r="E377" t="str">
+        <v/>
+      </c>
+      <c r="F377" t="str">
+        <v/>
+      </c>
+      <c r="G377" t="str">
+        <v/>
+      </c>
+      <c r="H377" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I377" t="str">
+        <v/>
+      </c>
+      <c r="J377" t="str">
+        <v/>
+      </c>
+      <c r="K377" t="str">
+        <v/>
+      </c>
+      <c r="L377" t="str">
+        <v>2026-04-10T05:00:52.359Z</v>
+      </c>
+      <c r="M377" t="str">
+        <v>2026-04-10T05:00:52.359Z</v>
+      </c>
+      <c r="N377" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="B378">
+        <v>35</v>
+      </c>
+      <c r="C378" t="str">
+        <v>セクシーインパクト</v>
+      </c>
+      <c r="D378" t="str">
+        <v>セクシーインパクト</v>
+      </c>
+      <c r="E378" t="str">
+        <v/>
+      </c>
+      <c r="F378" t="str">
+        <v/>
+      </c>
+      <c r="G378" t="str">
+        <v/>
+      </c>
+      <c r="H378" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I378" t="str">
+        <v/>
+      </c>
+      <c r="J378" t="str">
+        <v/>
+      </c>
+      <c r="K378" t="str">
+        <v/>
+      </c>
+      <c r="L378" t="str">
+        <v>2026-04-10T05:01:05.353Z</v>
+      </c>
+      <c r="M378" t="str">
+        <v>2026-04-10T05:01:05.353Z</v>
+      </c>
+      <c r="N378" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>KL1015</v>
+      </c>
+      <c r="B379">
+        <v>35</v>
+      </c>
+      <c r="C379" t="str">
+        <v>リトルスパイダー</v>
+      </c>
+      <c r="D379" t="str">
+        <v>リトルスパイダー</v>
+      </c>
+      <c r="E379" t="str">
+        <v/>
+      </c>
+      <c r="F379" t="str">
+        <v/>
+      </c>
+      <c r="G379" t="str">
+        <v/>
+      </c>
+      <c r="H379" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I379" t="str">
+        <v/>
+      </c>
+      <c r="J379" t="str">
+        <v/>
+      </c>
+      <c r="K379" t="str">
+        <v/>
+      </c>
+      <c r="L379" t="str">
+        <v>2026-04-10T05:01:10.963Z</v>
+      </c>
+      <c r="M379" t="str">
+        <v>2026-04-10T05:01:10.963Z</v>
+      </c>
+      <c r="N379" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="B380">
+        <v>35</v>
+      </c>
+      <c r="C380" t="str">
+        <v>シャッドインパクト</v>
+      </c>
+      <c r="D380" t="str">
+        <v>シャッドインパクト</v>
+      </c>
+      <c r="E380" t="str">
+        <v/>
+      </c>
+      <c r="F380" t="str">
+        <v/>
+      </c>
+      <c r="G380" t="str">
+        <v/>
+      </c>
+      <c r="H380" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I380" t="str">
+        <v/>
+      </c>
+      <c r="J380" t="str">
+        <v/>
+      </c>
+      <c r="K380" t="str">
+        <v/>
+      </c>
+      <c r="L380" t="str">
+        <v>2026-04-10T05:01:20.888Z</v>
+      </c>
+      <c r="M380" t="str">
+        <v>2026-04-10T05:01:20.888Z</v>
+      </c>
+      <c r="N380" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>KL1017</v>
+      </c>
+      <c r="B381">
+        <v>35</v>
+      </c>
+      <c r="C381" t="str">
+        <v>ソルティ・コアチューブ</v>
+      </c>
+      <c r="D381" t="str">
+        <v>ソルティ・コアチューブ</v>
+      </c>
+      <c r="E381" t="str">
+        <v/>
+      </c>
+      <c r="F381" t="str">
+        <v/>
+      </c>
+      <c r="G381" t="str">
+        <v/>
+      </c>
+      <c r="H381" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I381" t="str">
+        <v/>
+      </c>
+      <c r="J381" t="str">
+        <v/>
+      </c>
+      <c r="K381" t="str">
+        <v/>
+      </c>
+      <c r="L381" t="str">
+        <v>2026-04-10T05:01:24.581Z</v>
+      </c>
+      <c r="M381" t="str">
+        <v>2026-04-10T05:01:24.581Z</v>
+      </c>
+      <c r="N381" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="B382">
+        <v>35</v>
+      </c>
+      <c r="C382" t="str">
+        <v>マッドワグ</v>
+      </c>
+      <c r="D382" t="str">
+        <v>マッドワグ</v>
+      </c>
+      <c r="E382" t="str">
+        <v/>
+      </c>
+      <c r="F382" t="str">
+        <v/>
+      </c>
+      <c r="G382" t="str">
+        <v/>
+      </c>
+      <c r="H382" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I382" t="str">
+        <v/>
+      </c>
+      <c r="J382" t="str">
+        <v/>
+      </c>
+      <c r="K382" t="str">
+        <v/>
+      </c>
+      <c r="L382" t="str">
+        <v>2026-04-10T05:01:30.282Z</v>
+      </c>
+      <c r="M382" t="str">
+        <v>2026-04-10T05:01:30.282Z</v>
+      </c>
+      <c r="N382" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>KL1019</v>
+      </c>
+      <c r="B383">
+        <v>35</v>
+      </c>
+      <c r="C383" t="str">
+        <v>ライブインパクト</v>
+      </c>
+      <c r="D383" t="str">
+        <v>ライブインパクト</v>
+      </c>
+      <c r="E383" t="str">
+        <v/>
+      </c>
+      <c r="F383" t="str">
+        <v/>
+      </c>
+      <c r="G383" t="str">
+        <v/>
+      </c>
+      <c r="H383" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I383" t="str">
+        <v/>
+      </c>
+      <c r="J383" t="str">
+        <v/>
+      </c>
+      <c r="K383" t="str">
+        <v/>
+      </c>
+      <c r="L383" t="str">
+        <v>2026-04-10T05:01:35.219Z</v>
+      </c>
+      <c r="M383" t="str">
+        <v>2026-04-10T05:01:35.219Z</v>
+      </c>
+      <c r="N383" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>KL1020</v>
+      </c>
+      <c r="B384">
+        <v>35</v>
+      </c>
+      <c r="C384" t="str">
+        <v>TEEボーンバズベイト</v>
+      </c>
+      <c r="D384" t="str">
+        <v>TEEボーンバズベイト</v>
+      </c>
+      <c r="E384" t="str">
+        <v/>
+      </c>
+      <c r="F384" t="str">
+        <v/>
+      </c>
+      <c r="G384" t="str">
+        <v/>
+      </c>
+      <c r="H384" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I384" t="str">
+        <v/>
+      </c>
+      <c r="J384" t="str">
+        <v/>
+      </c>
+      <c r="K384" t="str">
+        <v/>
+      </c>
+      <c r="L384" t="str">
+        <v>2026-04-10T05:01:36.834Z</v>
+      </c>
+      <c r="M384" t="str">
+        <v>2026-04-10T05:01:36.834Z</v>
+      </c>
+      <c r="N384" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>KL1021</v>
+      </c>
+      <c r="B385">
+        <v>35</v>
+      </c>
+      <c r="C385" t="str">
+        <v>ベイビーTEE-BONE スピナーベイト</v>
+      </c>
+      <c r="D385" t="str">
+        <v>ベイビーTEE-BONE スピナーベイト</v>
+      </c>
+      <c r="E385" t="str">
+        <v/>
+      </c>
+      <c r="F385" t="str">
+        <v/>
+      </c>
+      <c r="G385" t="str">
+        <v/>
+      </c>
+      <c r="H385" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I385" t="str">
+        <v/>
+      </c>
+      <c r="J385" t="str">
+        <v/>
+      </c>
+      <c r="K385" t="str">
+        <v/>
+      </c>
+      <c r="L385" t="str">
+        <v>2026-04-10T05:01:39.158Z</v>
+      </c>
+      <c r="M385" t="str">
+        <v>2026-04-10T05:01:39.158Z</v>
+      </c>
+      <c r="N385" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>KL1022</v>
+      </c>
+      <c r="B386">
+        <v>35</v>
+      </c>
+      <c r="C386" t="str">
+        <v>TEE-BONE スピナーベイト</v>
+      </c>
+      <c r="D386" t="str">
+        <v>TEE-BONE スピナーベイト</v>
+      </c>
+      <c r="E386" t="str">
+        <v/>
+      </c>
+      <c r="F386" t="str">
+        <v/>
+      </c>
+      <c r="G386" t="str">
+        <v/>
+      </c>
+      <c r="H386" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I386" t="str">
+        <v/>
+      </c>
+      <c r="J386" t="str">
+        <v/>
+      </c>
+      <c r="K386" t="str">
+        <v/>
+      </c>
+      <c r="L386" t="str">
+        <v>2026-04-10T05:01:40.855Z</v>
+      </c>
+      <c r="M386" t="str">
+        <v>2026-04-10T05:01:40.855Z</v>
+      </c>
+      <c r="N386" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>KL1023</v>
+      </c>
+      <c r="B387">
+        <v>35</v>
+      </c>
+      <c r="C387" t="str">
+        <v>ランブレードジグ</v>
+      </c>
+      <c r="D387" t="str">
+        <v>ランブレードジグ</v>
+      </c>
+      <c r="E387" t="str">
+        <v/>
+      </c>
+      <c r="F387" t="str">
+        <v/>
+      </c>
+      <c r="G387" t="str">
+        <v/>
+      </c>
+      <c r="H387" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I387" t="str">
+        <v/>
+      </c>
+      <c r="J387" t="str">
+        <v/>
+      </c>
+      <c r="K387" t="str">
+        <v/>
+      </c>
+      <c r="L387" t="str">
+        <v>2026-04-10T05:01:42.781Z</v>
+      </c>
+      <c r="M387" t="str">
+        <v>2026-04-10T05:01:42.781Z</v>
+      </c>
+      <c r="N387" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>KL1024</v>
+      </c>
+      <c r="B388">
+        <v>35</v>
+      </c>
+      <c r="C388" t="str">
+        <v>キャスティングジグ</v>
+      </c>
+      <c r="D388" t="str">
+        <v>キャスティングジグ</v>
+      </c>
+      <c r="E388" t="str">
+        <v/>
+      </c>
+      <c r="F388" t="str">
+        <v/>
+      </c>
+      <c r="G388" t="str">
+        <v/>
+      </c>
+      <c r="H388" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I388" t="str">
+        <v/>
+      </c>
+      <c r="J388" t="str">
+        <v/>
+      </c>
+      <c r="K388" t="str">
+        <v/>
+      </c>
+      <c r="L388" t="str">
+        <v>2026-04-10T05:01:44.227Z</v>
+      </c>
+      <c r="M388" t="str">
+        <v>2026-04-10T05:01:44.227Z</v>
+      </c>
+      <c r="N388" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>KL1025</v>
+      </c>
+      <c r="B389">
+        <v>35</v>
+      </c>
+      <c r="C389" t="str">
+        <v>スイングスイマー</v>
+      </c>
+      <c r="D389" t="str">
+        <v>スイングスイマー</v>
+      </c>
+      <c r="E389" t="str">
+        <v/>
+      </c>
+      <c r="F389" t="str">
+        <v/>
+      </c>
+      <c r="G389" t="str">
+        <v/>
+      </c>
+      <c r="H389" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I389" t="str">
+        <v/>
+      </c>
+      <c r="J389" t="str">
+        <v/>
+      </c>
+      <c r="K389" t="str">
+        <v/>
+      </c>
+      <c r="L389" t="str">
+        <v>2026-04-10T05:01:45.770Z</v>
+      </c>
+      <c r="M389" t="str">
+        <v>2026-04-10T05:01:45.770Z</v>
+      </c>
+      <c r="N389" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>KL1026</v>
+      </c>
+      <c r="B390">
+        <v>35</v>
+      </c>
+      <c r="C390" t="str">
+        <v>クランキンフットボールジグ</v>
+      </c>
+      <c r="D390" t="str">
+        <v>クランキンフットボールジグ</v>
+      </c>
+      <c r="E390" t="str">
+        <v/>
+      </c>
+      <c r="F390" t="str">
+        <v/>
+      </c>
+      <c r="G390" t="str">
+        <v/>
+      </c>
+      <c r="H390" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I390" t="str">
+        <v/>
+      </c>
+      <c r="J390" t="str">
+        <v/>
+      </c>
+      <c r="K390" t="str">
+        <v/>
+      </c>
+      <c r="L390" t="str">
+        <v>2026-04-10T05:01:47.045Z</v>
+      </c>
+      <c r="M390" t="str">
+        <v>2026-04-10T05:01:47.045Z</v>
+      </c>
+      <c r="N390" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>KL1027</v>
+      </c>
+      <c r="B391">
+        <v>35</v>
+      </c>
+      <c r="C391" t="str">
+        <v>ラバージグ モデル Ⅰ Ver.2.0</v>
+      </c>
+      <c r="D391" t="str">
+        <v>ラバージグ モデル Ⅰ Ver.2.0</v>
+      </c>
+      <c r="E391" t="str">
+        <v/>
+      </c>
+      <c r="F391" t="str">
+        <v/>
+      </c>
+      <c r="G391" t="str">
+        <v/>
+      </c>
+      <c r="H391" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I391" t="str">
+        <v/>
+      </c>
+      <c r="J391" t="str">
+        <v/>
+      </c>
+      <c r="K391" t="str">
+        <v/>
+      </c>
+      <c r="L391" t="str">
+        <v>2026-04-10T05:01:48.745Z</v>
+      </c>
+      <c r="M391" t="str">
+        <v>2026-04-10T05:01:48.745Z</v>
+      </c>
+      <c r="N391" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>KL1028</v>
+      </c>
+      <c r="B392">
+        <v>35</v>
+      </c>
+      <c r="C392" t="str">
+        <v>ラバージグ モデル Ⅳ ヘビーデューティージグ</v>
+      </c>
+      <c r="D392" t="str">
+        <v>ラバージグ モデル Ⅳ ヘビーデューティージグ</v>
+      </c>
+      <c r="E392" t="str">
+        <v/>
+      </c>
+      <c r="F392" t="str">
+        <v/>
+      </c>
+      <c r="G392" t="str">
+        <v/>
+      </c>
+      <c r="H392" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I392" t="str">
+        <v/>
+      </c>
+      <c r="J392" t="str">
+        <v/>
+      </c>
+      <c r="K392" t="str">
+        <v/>
+      </c>
+      <c r="L392" t="str">
+        <v>2026-04-10T05:01:50.828Z</v>
+      </c>
+      <c r="M392" t="str">
+        <v>2026-04-10T05:01:50.828Z</v>
+      </c>
+      <c r="N392" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>KL1029</v>
+      </c>
+      <c r="B393">
+        <v>35</v>
+      </c>
+      <c r="C393" t="str">
+        <v>タングステンラバージグ モデル II Ver. 2.0</v>
+      </c>
+      <c r="D393" t="str">
+        <v>タングステンラバージグ モデル II Ver. 2.0</v>
+      </c>
+      <c r="E393" t="str">
+        <v/>
+      </c>
+      <c r="F393" t="str">
+        <v/>
+      </c>
+      <c r="G393" t="str">
+        <v/>
+      </c>
+      <c r="H393" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I393" t="str">
+        <v/>
+      </c>
+      <c r="J393" t="str">
+        <v/>
+      </c>
+      <c r="K393" t="str">
+        <v/>
+      </c>
+      <c r="L393" t="str">
+        <v>2026-04-10T05:01:52.477Z</v>
+      </c>
+      <c r="M393" t="str">
+        <v>2026-04-10T05:01:52.477Z</v>
+      </c>
+      <c r="N393" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>KL1030</v>
+      </c>
+      <c r="B394">
+        <v>35</v>
+      </c>
+      <c r="C394" t="str">
+        <v>モデルIII スイムジグ</v>
+      </c>
+      <c r="D394" t="str">
+        <v>モデルIII スイムジグ</v>
+      </c>
+      <c r="E394" t="str">
+        <v/>
+      </c>
+      <c r="F394" t="str">
+        <v/>
+      </c>
+      <c r="G394" t="str">
+        <v/>
+      </c>
+      <c r="H394" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I394" t="str">
+        <v/>
+      </c>
+      <c r="J394" t="str">
+        <v/>
+      </c>
+      <c r="K394" t="str">
+        <v/>
+      </c>
+      <c r="L394" t="str">
+        <v>2026-04-10T05:01:55.893Z</v>
+      </c>
+      <c r="M394" t="str">
+        <v>2026-04-10T05:01:55.893Z</v>
+      </c>
+      <c r="N394" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>KL1031</v>
+      </c>
+      <c r="B395">
+        <v>35</v>
+      </c>
+      <c r="C395" t="str">
+        <v>ガードスピンジグ</v>
+      </c>
+      <c r="D395" t="str">
+        <v>ガードスピンジグ</v>
+      </c>
+      <c r="E395" t="str">
+        <v/>
+      </c>
+      <c r="F395" t="str">
+        <v/>
+      </c>
+      <c r="G395" t="str">
+        <v/>
+      </c>
+      <c r="H395" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I395" t="str">
+        <v/>
+      </c>
+      <c r="J395" t="str">
+        <v/>
+      </c>
+      <c r="K395" t="str">
+        <v/>
+      </c>
+      <c r="L395" t="str">
+        <v>2026-04-10T05:01:57.179Z</v>
+      </c>
+      <c r="M395" t="str">
+        <v>2026-04-10T05:01:57.179Z</v>
+      </c>
+      <c r="N395" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>KL1032</v>
+      </c>
+      <c r="B396">
+        <v>35</v>
+      </c>
+      <c r="C396" t="str">
+        <v>モノスピンジグ</v>
+      </c>
+      <c r="D396" t="str">
+        <v>モノスピンジグ</v>
+      </c>
+      <c r="E396" t="str">
+        <v/>
+      </c>
+      <c r="F396" t="str">
+        <v/>
+      </c>
+      <c r="G396" t="str">
+        <v/>
+      </c>
+      <c r="H396" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I396" t="str">
+        <v/>
+      </c>
+      <c r="J396" t="str">
+        <v/>
+      </c>
+      <c r="K396" t="str">
+        <v/>
+      </c>
+      <c r="L396" t="str">
+        <v>2026-04-10T05:01:58.540Z</v>
+      </c>
+      <c r="M396" t="str">
+        <v>2026-04-10T05:01:58.540Z</v>
+      </c>
+      <c r="N396" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N363"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N396"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N396"/>
+  <dimension ref="A1:O396"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,6 +442,9 @@
       <c r="N1" t="str">
         <v>description</v>
       </c>
+      <c r="O1" t="str">
+        <v>official_link</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -16391,28 +16394,31 @@
         <v/>
       </c>
       <c r="G364" t="str">
-        <v/>
+        <v>swimbait</v>
       </c>
       <c r="H364" t="str">
         <v>soft</v>
       </c>
       <c r="I364" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J364" t="str">
-        <v/>
+        <v>wobble_roll</v>
       </c>
       <c r="K364" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202501241430404411.jpg</v>
       </c>
       <c r="L364" t="str">
-        <v>2026-04-10T05:00:09.333Z</v>
+        <v>2026-04-10T05:39:11.615Z</v>
       </c>
       <c r="M364" t="str">
-        <v>2026-04-10T05:00:09.333Z</v>
+        <v>2026-04-10T05:39:11.615Z</v>
       </c>
       <c r="N364" t="str">
-        <v/>
+        <v>スイムベイトの名作を、忠実に、完全復刻！ 野尻湖や桧原湖をはじめとするハイランドクリアレイクのシークレットとして噂がうわさを呼び、ローカルの猛者たちから一般アングラーへと徐々に浸透、やがて定番化したTEMPTブランドの『スイングベイト』。 惜しまれながらも廃盤となったこのスイムベイト（シャッドテールワーム）を、ケイテックが完全復刻いたしました。</v>
+      </c>
+      <c r="O364" t="str">
+        <v>https://keitech.co.jp/pages/613/</v>
       </c>
     </row>
     <row r="365">
@@ -16435,28 +16441,31 @@
         <v/>
       </c>
       <c r="G365" t="str">
-        <v/>
+        <v>swimbait</v>
       </c>
       <c r="H365" t="str">
         <v>soft</v>
       </c>
       <c r="I365" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J365" t="str">
-        <v/>
+        <v>wobble_roll</v>
       </c>
       <c r="K365" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191540483278.jpg</v>
       </c>
       <c r="L365" t="str">
-        <v>2026-04-10T05:00:16.169Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="M365" t="str">
-        <v>2026-04-10T05:00:16.169Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="N365" t="str">
-        <v/>
+        <v>キビキビと、そして大きくスイングするテールアクション。ボトムでのズル引きやカーブフォールによるスイミングで効果絶大です。水を良く掴み、水流負けしないテールデザインがミソ。ジグヘッドはもとより、テキサス、キャロライナ、ダウンショットリグ、そしてネコリグやジグトレーラー等、あらゆる使い方で効果を発揮します。あまりシェイク等の小技を入れずに、スローにシンプルに使うことをお勧めいたします。</v>
+      </c>
+      <c r="O365" t="str">
+        <v>https://keitech.co.jp/pages/39/</v>
       </c>
     </row>
     <row r="366">
@@ -16479,28 +16488,31 @@
         <v/>
       </c>
       <c r="G366" t="str">
-        <v/>
+        <v>swimbait</v>
       </c>
       <c r="H366" t="str">
         <v>soft</v>
       </c>
       <c r="I366" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J366" t="str">
-        <v/>
+        <v>wobble_roll</v>
       </c>
       <c r="K366" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191547352876.jpg</v>
       </c>
       <c r="L366" t="str">
-        <v>2026-04-10T05:00:26.223Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="M366" t="str">
-        <v>2026-04-10T05:00:26.223Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="N366" t="str">
-        <v/>
+        <v>ワイドなスイングアクション、最強の水噛み、絶妙なロール、群を抜く集魚力。ある時はアシを抜けるスピナーベイト、ある時はボトムをつつくクランクベイト、ある時はウィードに絡むテキサスリグワーム、ある時は優秀なジグトレーラー…。試行錯誤の末に行きついた究極の広域性能をありったけの技術でお届け致します。</v>
+      </c>
+      <c r="O366" t="str">
+        <v>https://keitech.co.jp/pages/57/</v>
       </c>
     </row>
     <row r="367">
@@ -16523,28 +16535,31 @@
         <v/>
       </c>
       <c r="G367" t="str">
-        <v/>
+        <v>swimbait</v>
       </c>
       <c r="H367" t="str">
         <v>soft</v>
       </c>
       <c r="I367" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J367" t="str">
-        <v/>
+        <v>wobble_roll</v>
       </c>
       <c r="K367" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191558078979.jpg</v>
       </c>
       <c r="L367" t="str">
-        <v>2026-04-10T05:00:31.150Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="M367" t="str">
-        <v>2026-04-10T05:00:31.150Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="N367" t="str">
-        <v/>
+        <v>機敏なテールアクション、完璧なバランス、そして絶妙なロール･･･。確かに、そしてイージーに釣果を伸ばすための特別なスペックです。ただ巻くだけで反応してしまう。そんな魚のいかに多いことか、をご自信でお確かめ下さい。イージーシャイナー、好評発売中。</v>
+      </c>
+      <c r="O367" t="str">
+        <v>https://keitech.co.jp/pages/232/</v>
       </c>
     </row>
     <row r="368">
@@ -16567,28 +16582,31 @@
         <v/>
       </c>
       <c r="G368" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H368" t="str">
         <v>soft</v>
       </c>
       <c r="I368" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J368" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K368" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202401161646502833.jpg</v>
       </c>
       <c r="L368" t="str">
-        <v>2026-04-10T05:00:32.478Z</v>
+        <v>2026-04-10T05:39:33.792Z</v>
       </c>
       <c r="M368" t="str">
-        <v>2026-04-10T05:00:32.478Z</v>
+        <v>2026-04-10T05:39:33.792Z</v>
       </c>
       <c r="N368" t="str">
-        <v/>
+        <v>これが、ケイテックのバックスライド“専用”ワームバックスライド仕様の高比重ワームが釣れる理由のひとつに、文字どおり後方へのスライドフォールが挙げられます。同じカバー攻略でも、それはジグやテキサスリグにはけっして真似のできない芸当。いや、数多あるなかで、アングラーから逆の方向へと慣性が働くルアー自体、たぐいまれ。だから『グライドカマロン』の開発は、“いかにバックスライドさせるか”に重きを置きました。魚にこたえを聞いた理想的なフォール姿勢とスライド幅は、ハサミやヒゲを含めたボディデザインとマテリアルのたまもの。もちろん、フォール後のボトムステイやロッドワークでアクションを与えた際の挙動、カバーの抜け方（抜きやすさ）、回収のしやすさも徹底的に検証しています。オープンウォーターのミドストやボトストなど、自由な発想で使い方の幅を拡げていくのは釣りの醍醐味ですが、まずはノーシンカーリグでの、バックスライドを活かしたシャローカバー攻略を強くおすすめいたします。</v>
+      </c>
+      <c r="O368" t="str">
+        <v>https://keitech.co.jp/pages/608/</v>
       </c>
     </row>
     <row r="369">
@@ -16611,28 +16629,31 @@
         <v/>
       </c>
       <c r="G369" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H369" t="str">
         <v>soft</v>
       </c>
       <c r="I369" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J369" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K369" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202401161654221750.jpg</v>
       </c>
       <c r="L369" t="str">
-        <v>2026-04-10T05:00:33.726Z</v>
+        <v>2026-04-10T05:39:35.679Z</v>
       </c>
       <c r="M369" t="str">
-        <v>2026-04-10T05:00:33.726Z</v>
+        <v>2026-04-10T05:39:35.679Z</v>
       </c>
       <c r="N369" t="str">
-        <v/>
+        <v>それまで、 障害物周りやボトムでのスローな誘いに限定されていたワームフィッシングに、表・中層で巻いて喰わせるという革命的ストラテジーの扉を開いたカーリーテールグラブ。バスアングラーが増加の一途をたどった90年代中盤、投げて巻くだけのシンプルな操作で魚を手にすることのできるこのルアーは、バス釣りそのものの門戸を広げる重要な役割を担っていました。 『フラッパーグラブ』はまさにこの“投げて巻く”というシンプルな使用法に重きを置いて開発。したがって適するリグはさまざまあれど、私たちがもっともおすすめしたいのはずばり、ノーシンカーリグでのグラビンバズです。水面を使い、食性だけでなくリアクション的要素でもバスを反応させる釣法はむしろいまの時勢に即しており、一連の動作をよどみなく続けるための理想を形にしています。 釣法が細分化され、高度な技術を要する場面も少なくない昨今にあって、シンプルに、投げて巻いて、巻いて投げて、ルアー釣りの醍醐味を味わうためのツール、それが『フラッパーグラブ』なのです。</v>
+      </c>
+      <c r="O369" t="str">
+        <v>https://keitech.co.jp/pages/599/</v>
       </c>
     </row>
     <row r="370">
@@ -16655,28 +16676,31 @@
         <v/>
       </c>
       <c r="G370" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H370" t="str">
         <v>soft</v>
       </c>
       <c r="I370" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J370" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K370" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191655435515.jpg</v>
       </c>
       <c r="L370" t="str">
-        <v>2026-04-10T05:00:35.359Z</v>
+        <v>2026-04-10T05:39:37.181Z</v>
       </c>
       <c r="M370" t="str">
-        <v>2026-04-10T05:00:35.359Z</v>
+        <v>2026-04-10T05:39:37.181Z</v>
       </c>
       <c r="N370" t="str">
-        <v/>
+        <v>まだシリコンスカート仕様の“スモラバ”が存在していなかったころに発売を開始、以来、釣れるワームとしての位置付けをゆるぎないものとしてきた『リトルスパイダー』。そのたしかなコンセプトを継承しつつ、個体数減少が叫ばれる昨今のフィールド事情に最適化したもうひとつのフィネススカーテッドベイトこそ『ハイパースパイダー』です。『リトルスパイダー』との最大の相違点は、アクション入力時の存在感にあります。水のつかみ方、押し方、逃がし方を徹底的に検証し、全パーツをイチから設計。フォール、スイミング、シェイク…リグに合わせたどんな誘い方でも各部がレスポンスよく強く作動し、そのサイズからは想像できない誘引力を発揮します。『リトルスパイダー』との併用で根こそぎ釣るもよし、一発狙いの切り札として起用するもよし、強さを備えたフィネスの新たなトビラを開いてください。</v>
+      </c>
+      <c r="O370" t="str">
+        <v>https://keitech.co.jp/pages/582/</v>
       </c>
     </row>
     <row r="371">
@@ -16699,28 +16723,31 @@
         <v/>
       </c>
       <c r="G371" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H371" t="str">
         <v>soft</v>
       </c>
       <c r="I371" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J371" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K371" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191701313136.jpg</v>
       </c>
       <c r="L371" t="str">
-        <v>2026-04-10T05:00:37.011Z</v>
+        <v>2026-04-10T05:39:39.295Z</v>
       </c>
       <c r="M371" t="str">
-        <v>2026-04-10T05:00:37.011Z</v>
+        <v>2026-04-10T05:39:39.295Z</v>
       </c>
       <c r="N371" t="str">
-        <v/>
+        <v>カバーゲームをアップデートする、 第三世代パドルテールグラブ『パドリンビーバー』。アプローチがスムーズに行なえること。しっかりとバスを誘えること。あらゆる障害物で使用できること。これらは、ともするとキャスト数が釣果に直結する現代のカバーフィッシングにおいて、とても大切な要素だと言えるでしょう。さらに効率を高めたい。そんなカバーフィッシャーマンの“釣欲”を満たすべく、熟慮と実践を繰り返して辿り着いた形状こそがパドルテールグラブでした。 『パドリンビーバー』。カバーゲームをアップデートするための、我々からの提案です。</v>
+      </c>
+      <c r="O371" t="str">
+        <v>https://keitech.co.jp/pages/581/</v>
       </c>
     </row>
     <row r="372">
@@ -16743,28 +16770,31 @@
         <v/>
       </c>
       <c r="G372" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H372" t="str">
         <v>soft</v>
       </c>
       <c r="I372" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J372" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K372" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/20250418163325698.jpg</v>
       </c>
       <c r="L372" t="str">
-        <v>2026-04-10T05:00:38.559Z</v>
+        <v>2026-04-10T05:39:40.991Z</v>
       </c>
       <c r="M372" t="str">
-        <v>2026-04-10T05:00:38.559Z</v>
+        <v>2026-04-10T05:39:40.991Z</v>
       </c>
       <c r="N372" t="str">
-        <v/>
+        <v>エビ食いバスを刺激する、エビ系クローラー。エビを捕食するバスを釣るために開発したエビ系クローラー『ネコカマロン』。特にネコリグでの使用において、入水姿勢、着底後の倒れ込み、シェイク時のボディ部横振りアクションなど、着水からピックアップまで、水中にいる間、常に“エビ食いバス”を刺激するよう各パーツをデザインしました。素材は硬すぎず、柔らかすぎずの中弾性材料に、エビの淡い存在感を再現するための適量な塩、そして釣れる匂いと評判の“天然イカフレーバー”を配合しました。</v>
+      </c>
+      <c r="O372" t="str">
+        <v>https://keitech.co.jp/pages/551/</v>
       </c>
     </row>
     <row r="373">
@@ -16787,28 +16817,31 @@
         <v/>
       </c>
       <c r="G373" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H373" t="str">
         <v>soft</v>
       </c>
       <c r="I373" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J373" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K373" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191729594683.jpg</v>
       </c>
       <c r="L373" t="str">
-        <v>2026-04-10T05:00:40.270Z</v>
+        <v>2026-04-10T05:39:42.698Z</v>
       </c>
       <c r="M373" t="str">
-        <v>2026-04-10T05:00:40.270Z</v>
+        <v>2026-04-10T05:39:42.698Z</v>
       </c>
       <c r="N373" t="str">
-        <v/>
+        <v>長年にわたり、ジグフィッシャーマンがこだわったジグ着底時の自発的アクションがあります。ジグ着底後“パッ”とスカートがフレアし、少し遅れて“テローン”とトレーラーが倒れこむ。テロテロ１軍ポークでのみ出し得たこの“余韻アクション”は今までに多くのバスを虜にしてきました。そのなまめかしい動きを再現すべく開発したプラスティックチャンクこそが“フレックスチャンク”です。肉厚な脚をフレキシブルにアクションさせる“マクラギ構造”。最適な材料の柔らかさ、塩含有量による最適な比重。バイトを強烈に誘発する“天然イカフレーバー”。そしてワーム素材ならではの自在なカラーリング。水押し系チャンクトレーラー、フレックスチャンクの完成です。</v>
+      </c>
+      <c r="O373" t="str">
+        <v>https://keitech.co.jp/pages/456/</v>
       </c>
     </row>
     <row r="374">
@@ -16831,28 +16864,31 @@
         <v/>
       </c>
       <c r="G374" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H374" t="str">
         <v>soft</v>
       </c>
       <c r="I374" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J374" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K374" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011701561170.jpg</v>
       </c>
       <c r="L374" t="str">
-        <v>2026-04-10T05:00:42.551Z</v>
+        <v>2026-04-10T05:39:45.196Z</v>
       </c>
       <c r="M374" t="str">
-        <v>2026-04-10T05:00:42.551Z</v>
+        <v>2026-04-10T05:39:45.196Z</v>
       </c>
       <c r="N374" t="str">
-        <v/>
+        <v>コアは細身ながらリングをまとうことで、シルエットにボリュームを持たせつつ生命体ならではの自然な動き＝“Ultimate Lifelike Action”を実現した『イージーシェイカー』。 リングボディ＋ノンソルティマテリアルの組み合わせにより、ジグヘッドリグのスイミング時、あるいはダウンショットリグでボトムから浮かせた状態で誘った時など、絶妙な姿勢に加えて、トリッキーなダートやもだえるような艶めかしいアクションがその名のとおり“イージー”に演出可能となっています。 近年はバスフィッシングのみならず、アジングやロックフィッシュゲームをはじめソルトウォーターの世界でもその効能が認められており、弊社ラインナップのなかにあって「釣れるルアーは魚種を選ばない」を地で行く製品のひとつ。 バスで言うところのウルトラフィネスからオーソドックスなライトリグ仕様まで、ラインナップを拡充してまいりました。フィールドコンディションや対象魚にあわせた、最適なサイズをお選びください。</v>
+      </c>
+      <c r="O374" t="str">
+        <v>https://keitech.co.jp/pages/549/</v>
       </c>
     </row>
     <row r="375">
@@ -16875,28 +16911,31 @@
         <v/>
       </c>
       <c r="G375" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H375" t="str">
         <v>soft</v>
       </c>
       <c r="I375" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J375" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K375" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191804546996.jpg</v>
       </c>
       <c r="L375" t="str">
-        <v>2026-04-10T05:00:45.695Z</v>
+        <v>2026-04-10T05:39:48.055Z</v>
       </c>
       <c r="M375" t="str">
-        <v>2026-04-10T05:00:45.695Z</v>
+        <v>2026-04-10T05:39:48.055Z</v>
       </c>
       <c r="N375" t="str">
-        <v/>
+        <v>チョン掛け専用ダウンショットワーム、究極の食わせ系として名を馳せたカスタムリーチ。私達は、10数年ぶりにこれを復活させることに致しました。とは言っても、当時のままの仕様でのリバイバルではありません。デザイン、製法、そしてパッケージングとそれぞれ意匠を凝らし再開発。今の私達をして、「最高の仕事」と言えるレベルにまで高めての復活です。</v>
+      </c>
+      <c r="O375" t="str">
+        <v>https://keitech.co.jp/pages/450/</v>
       </c>
     </row>
     <row r="376">
@@ -16919,28 +16958,31 @@
         <v/>
       </c>
       <c r="G376" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H376" t="str">
         <v>soft</v>
       </c>
       <c r="I376" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J376" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K376" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011702381439.jpg</v>
       </c>
       <c r="L376" t="str">
-        <v>2026-04-10T05:00:49.253Z</v>
+        <v>2026-04-10T05:39:51.253Z</v>
       </c>
       <c r="M376" t="str">
-        <v>2026-04-10T05:00:49.253Z</v>
+        <v>2026-04-10T05:39:51.253Z</v>
       </c>
       <c r="N376" t="str">
-        <v/>
+        <v>水面をキープしながらスロー＆ステディなリトリーブ。微かなスプラッシュと均質な引き波を水面に作り込む。ノイジーフラッパーの大いなるバス吸引力は、こうした静かな展開でこそ発揮されます。カバーにタイトに、ゆっくり滑らかに、期待を膨らませて･･･。魔性のバジングフロッグ、ノイジーフラッパー。</v>
+      </c>
+      <c r="O376" t="str">
+        <v>https://keitech.co.jp/pages/423/</v>
       </c>
     </row>
     <row r="377">
@@ -16963,28 +17005,31 @@
         <v/>
       </c>
       <c r="G377" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H377" t="str">
         <v>soft</v>
       </c>
       <c r="I377" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J377" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K377" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191814411193.jpg</v>
       </c>
       <c r="L377" t="str">
-        <v>2026-04-10T05:00:52.359Z</v>
+        <v>2026-04-10T05:39:55.263Z</v>
       </c>
       <c r="M377" t="str">
-        <v>2026-04-10T05:00:52.359Z</v>
+        <v>2026-04-10T05:39:55.263Z</v>
       </c>
       <c r="N377" t="str">
-        <v/>
+        <v>あまたあるザリガニワームの中で輝くような異彩を放つ。超アクション系クローワーム、クレイジーフラッパー!!</v>
+      </c>
+      <c r="O377" t="str">
+        <v>https://keitech.co.jp/pages/381/</v>
       </c>
     </row>
     <row r="378">
@@ -17007,28 +17052,31 @@
         <v/>
       </c>
       <c r="G378" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H378" t="str">
         <v>soft</v>
       </c>
       <c r="I378" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J378" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K378" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191820097952.jpg</v>
       </c>
       <c r="L378" t="str">
-        <v>2026-04-10T05:01:05.353Z</v>
+        <v>2026-04-10T05:40:06.614Z</v>
       </c>
       <c r="M378" t="str">
-        <v>2026-04-10T05:01:05.353Z</v>
+        <v>2026-04-10T05:40:06.614Z</v>
       </c>
       <c r="N378" t="str">
-        <v/>
+        <v>ライフライクな動きを追求したピンテール系ストレートワーム。ワームに与えられた全ての動きは、完成されたテーパーデザインにより横振りテールアクションに変換。本物のベイトフィッシュに見まごうばかりのリアルさです。ノーシンカーのただ巻きから、ジグヘッド、ダウンショット、果てはヘビーテキサスまであらゆるリグにフィット。2.8”〜5.8”すべてワームをクセから守る専用ブリスターケースにてお届けします。もちろん強力天然イカフレーバー配合。バイトを長く、そして深くします。</v>
+      </c>
+      <c r="O378" t="str">
+        <v>https://keitech.co.jp/pages/158/</v>
       </c>
     </row>
     <row r="379">
@@ -17051,28 +17099,31 @@
         <v/>
       </c>
       <c r="G379" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H379" t="str">
         <v>soft</v>
       </c>
       <c r="I379" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J379" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K379" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191828058722.jpg</v>
       </c>
       <c r="L379" t="str">
-        <v>2026-04-10T05:01:10.963Z</v>
+        <v>2026-04-10T05:40:13.153Z</v>
       </c>
       <c r="M379" t="str">
-        <v>2026-04-10T05:01:10.963Z</v>
+        <v>2026-04-10T05:40:13.153Z</v>
       </c>
       <c r="N379" t="str">
-        <v/>
+        <v>透明感のある繊細なスカート、そしてピリピリと俊敏に動くダブルテール。シリコンスカート製のスモールラバージグがまだ世に出回っていなかった時代に、林圭一が思い描き開発したフィネススカーテッドグラブです。 当時からジグヘッド、ダウンショット、キャロライナそしてスプリットショットとあらゆるフィネスリグに対応し、常にステディな釣果をマークしてきました。最近のものは、透明感をさらに高めたノンソルティのワーム素材を使用。また天然イカフレーバーを配合した匂いつきの現代仕様でお届けします。 リトルスパイダー。今なおケイテックが誇るフィネスベイトの決定版です。</v>
+      </c>
+      <c r="O379" t="str">
+        <v>https://keitech.co.jp/pages/455/</v>
       </c>
     </row>
     <row r="380">
@@ -17095,28 +17146,31 @@
         <v/>
       </c>
       <c r="G380" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H380" t="str">
         <v>soft</v>
       </c>
       <c r="I380" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J380" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K380" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/20221219183446307.jpg</v>
       </c>
       <c r="L380" t="str">
-        <v>2026-04-10T05:01:20.888Z</v>
+        <v>2026-04-10T05:40:20.195Z</v>
       </c>
       <c r="M380" t="str">
-        <v>2026-04-10T05:01:20.888Z</v>
+        <v>2026-04-10T05:40:20.195Z</v>
       </c>
       <c r="N380" t="str">
-        <v/>
+        <v>ジグヘッドやダウンショット。シェイクすることによりタイトでキレのあるローリングアクションを生み出します。 独自に開発した精密２色成型にこのアクションが相まって超リアルな小魚を表現します。バスはためらいもなく腹からスパッと吸い込んでしまう、そんな強い”食わせ力”を持ったアイテムです。</v>
+      </c>
+      <c r="O380" t="str">
+        <v>https://keitech.co.jp/pages/35/</v>
       </c>
     </row>
     <row r="381">
@@ -17139,28 +17193,31 @@
         <v/>
       </c>
       <c r="G381" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H381" t="str">
         <v>soft</v>
       </c>
       <c r="I381" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J381" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K381" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191843366790.jpg</v>
       </c>
       <c r="L381" t="str">
-        <v>2026-04-10T05:01:24.581Z</v>
+        <v>2026-04-10T05:40:24.698Z</v>
       </c>
       <c r="M381" t="str">
-        <v>2026-04-10T05:01:24.581Z</v>
+        <v>2026-04-10T05:40:24.698Z</v>
       </c>
       <c r="N381" t="str">
-        <v/>
+        <v>私共が手にした新技術、それは超高精度コアショット成型技術。この新たな技術領域で今までにない機能を持ったワームを作りたい、そんな思いを具現化したのがソルティ・コアチューブ。テキサスリグによるカバー撃ち、ノーシンカー・リバースセットによるバックスライディングと様々なカバーフィッシングに対応。使いやすさと着実な釣果を約束するワームの新ジャンルです。</v>
+      </c>
+      <c r="O381" t="str">
+        <v>https://keitech.co.jp/pages/293/</v>
       </c>
     </row>
     <row r="382">
@@ -17183,28 +17240,31 @@
         <v/>
       </c>
       <c r="G382" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H382" t="str">
         <v>soft</v>
       </c>
       <c r="I382" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J382" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K382" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/20221219174541338.jpg</v>
       </c>
       <c r="L382" t="str">
-        <v>2026-04-10T05:01:30.282Z</v>
+        <v>2026-04-10T05:40:28.288Z</v>
       </c>
       <c r="M382" t="str">
-        <v>2026-04-10T05:01:30.282Z</v>
+        <v>2026-04-10T05:40:28.288Z</v>
       </c>
       <c r="N382" t="str">
-        <v/>
+        <v>デザイン極めたロングカーリーテール。 ウィードエリアでテキサスリグをスイムさせる。琵琶湖に代表されるそんな釣りを視野に開発。ごくスローなリトリーブでも強くワイドに水を掻くよう、特別なテールをデザインしました。ボディ形状にもこだわり、ウィードに対する絶対的な“スナッグレス性能”を盛り込んでいます。マッドワグ。ウィードの隙間をなめらかにかいくぐり、絶え間なく発散される強烈な集魚力。テールとボディのバランスに配慮したうえで４つのサイズそれぞれをしっかりと試し、丹念に作り込んだスイミングテキサス（マキマキ）用ワームの決定版です。</v>
+      </c>
+      <c r="O382" t="str">
+        <v>https://keitech.co.jp/pages/276/</v>
       </c>
     </row>
     <row r="383">
@@ -17227,28 +17287,31 @@
         <v/>
       </c>
       <c r="G383" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H383" t="str">
         <v>soft</v>
       </c>
       <c r="I383" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J383" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K383" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191850068911.jpg</v>
       </c>
       <c r="L383" t="str">
-        <v>2026-04-10T05:01:35.219Z</v>
+        <v>2026-04-10T05:40:33.878Z</v>
       </c>
       <c r="M383" t="str">
-        <v>2026-04-10T05:01:35.219Z</v>
+        <v>2026-04-10T05:40:33.878Z</v>
       </c>
       <c r="N383" t="str">
-        <v/>
+        <v>しなやかさと、ぎこちなさが入り混じった本物の生命感。ライブインパクトはそんな温もりを封じ込めたケイテックの会心作。高い汎用性を誇り、どんなリグで 使っても命が宿ったかのようにアクションします。ジグヘッド、ダウンショット、テキサスリグ、ワッキー系リグ、ジグトレーラーとあらゆる用途に対応しま す。 ※ ジグヘッドがボトムで立つほどの高浮力材料を使用。フォールスピードを抑え、ボトムで立つ、あるいは水中で漂う。 ※ 浮力により、ボトムでの根掛かりが激減。 ※ 水噛みに優れたリングボディとナチュラルさを醸し出すフィンテール。※ 歴然とした食いの良さ、天然イカフレーバー配合。</v>
+      </c>
+      <c r="O383" t="str">
+        <v>https://keitech.co.jp/pages/18/</v>
       </c>
     </row>
     <row r="384">
@@ -17271,28 +17334,31 @@
         <v/>
       </c>
       <c r="G384" t="str">
-        <v/>
+        <v>spinnerbait</v>
       </c>
       <c r="H384" t="str">
         <v>wire</v>
       </c>
       <c r="I384" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J384" t="str">
-        <v/>
+        <v>spin_flash</v>
       </c>
       <c r="K384" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/20260128162612996.jpg</v>
       </c>
       <c r="L384" t="str">
-        <v>2026-04-10T05:01:36.834Z</v>
+        <v>2026-04-10T05:40:37.872Z</v>
       </c>
       <c r="M384" t="str">
-        <v>2026-04-10T05:01:36.834Z</v>
+        <v>2026-04-10T05:40:37.872Z</v>
       </c>
       <c r="N384" t="str">
-        <v/>
+        <v>同じワイヤーベイトでも、バズベイトがスピナーベイトと明らかに異なるのはトレースレンジが限定されていること。 投げて、水面を巻く。 この実に単純な作業が、バズベイトを扱うアングラーに与えられた仕事なのです。 もちろん、障害物との距離感等バスのポジションを想定したコース取りは重要だし、状況に応じたスピードコントロールも大切です。</v>
+      </c>
+      <c r="O384" t="str">
+        <v>https://keitech.co.jp/pages/660/</v>
       </c>
     </row>
     <row r="385">
@@ -17315,28 +17381,31 @@
         <v/>
       </c>
       <c r="G385" t="str">
-        <v/>
+        <v>spinnerbait</v>
       </c>
       <c r="H385" t="str">
         <v>wire</v>
       </c>
       <c r="I385" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J385" t="str">
-        <v/>
+        <v>spin_flash</v>
       </c>
       <c r="K385" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202501241436271305.jpg</v>
       </c>
       <c r="L385" t="str">
-        <v>2026-04-10T05:01:39.158Z</v>
+        <v>2026-04-10T05:40:41.227Z</v>
       </c>
       <c r="M385" t="str">
-        <v>2026-04-10T05:01:39.158Z</v>
+        <v>2026-04-10T05:40:41.227Z</v>
       </c>
       <c r="N385" t="str">
-        <v/>
+        <v>日本基準のザ・スピナーベイト『ベイビーTEE-BONEスピナーベイト』オリジナルのTEEボーンスピナーベイトは、奇をてらうことなく、サーチベイトに求められる基本性能「よく飛び、よく動き、よく掛かる」を重視してパーツを選び、デザインに落とし込んだ“ザ・スピナーベイト”。そのコンセプトはまったく変えず、構成要素それぞれの役割をしっかりと調整してコンパクトにまとめたのが『ベイビーTEEボーンスピナーベイト』です。ハイプレッシャーや過度のアピールを嫌う状況において“小さい”ことがバイトチャンス増につながるのは真理であり、その点において日本基準と言えるでしょう。</v>
+      </c>
+      <c r="O385" t="str">
+        <v>https://keitech.co.jp/pages/617/</v>
       </c>
     </row>
     <row r="386">
@@ -17359,28 +17428,31 @@
         <v/>
       </c>
       <c r="G386" t="str">
-        <v/>
+        <v>spinnerbait</v>
       </c>
       <c r="H386" t="str">
         <v>wire</v>
       </c>
       <c r="I386" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J386" t="str">
-        <v/>
+        <v>spin_flash</v>
       </c>
       <c r="K386" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202403141759512800.jpg</v>
       </c>
       <c r="L386" t="str">
-        <v>2026-04-10T05:01:40.855Z</v>
+        <v>2026-04-10T05:40:43.082Z</v>
       </c>
       <c r="M386" t="str">
-        <v>2026-04-10T05:01:40.855Z</v>
+        <v>2026-04-10T05:40:43.082Z</v>
       </c>
       <c r="N386" t="str">
-        <v/>
+        <v>基本性能を、丁寧に紡いだ “Theケイテックカスタム”。誕生してから１世紀が経つとも言われるトラディショナルバスルアー、スピナーベイト。このルアーの特筆すべき基本性能は、ずばり“ウィードレスなサーチベイト”であること。その基本性能にフォーカスをあて、開発いたしました。よく飛び、よく動き、よく掛かる、サーチベイトに重要なこの３つの基本性能を重視しデザイン、部材選定を行ないました。スタンダードスピナーベイトとして、KEITECHが自信をもってお勧めいたします。</v>
+      </c>
+      <c r="O386" t="str">
+        <v>https://keitech.co.jp/pages/554/</v>
       </c>
     </row>
     <row r="387">
@@ -17403,28 +17475,31 @@
         <v/>
       </c>
       <c r="G387" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H387" t="str">
         <v>jig</v>
       </c>
       <c r="I387" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J387" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K387" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202407031757493567.jpg</v>
       </c>
       <c r="L387" t="str">
-        <v>2026-04-10T05:01:42.781Z</v>
+        <v>2026-04-10T05:40:45.753Z</v>
       </c>
       <c r="M387" t="str">
-        <v>2026-04-10T05:01:42.781Z</v>
+        <v>2026-04-10T05:40:45.753Z</v>
       </c>
       <c r="N387" t="str">
-        <v/>
+        <v>ブレーデッドジグという難題へのこたえ『ランブレードジグ』開発の発端は、ケイテックU.S.A.からの提案でした。「スイングインパクトFATをはじめ、多くのアングラーがブレーデッドジグのトレーラーとしてうちのワームを使っている。だから、それに見合ったオリジナルを作ってくれないか？」。バスルアーのカテゴリーのひとつとして定着し、すでに20年。最後発である以上、独自の発想をデザインに落とし込まなければ意味がありません。何より、釣れる道具であることが大前提であるのは、ほかのルアーと同じ。着手から5年。これがブレーデッドジグという難題への、わたしたちのこたえなのです。</v>
+      </c>
+      <c r="O387" t="str">
+        <v>https://keitech.co.jp/pages/625/</v>
       </c>
     </row>
     <row r="388">
@@ -17447,28 +17522,31 @@
         <v/>
       </c>
       <c r="G388" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H388" t="str">
         <v>jig</v>
       </c>
       <c r="I388" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J388" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K388" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011732559977.jpg</v>
       </c>
       <c r="L388" t="str">
-        <v>2026-04-10T05:01:44.227Z</v>
+        <v>2026-04-10T05:40:47.419Z</v>
       </c>
       <c r="M388" t="str">
-        <v>2026-04-10T05:01:44.227Z</v>
+        <v>2026-04-10T05:40:47.419Z</v>
       </c>
       <c r="N388" t="str">
-        <v/>
+        <v>ザ・スタンダード！使う場所・状況を選ばないセミフルサイズジグ多くのアングラーに愛され続けてきたラバージグ・モデルⅠのヘッドデザインを踏襲し、使いやすさを追求しました。モデルⅠと同じ角度で設計した横向きアイ、最適な硬さ・本数・長さでそろえたブラシガードと相まって、障害物に対する適度な引っ掛かり感とその後の絶妙な抜け感はジグマンの要求を高い次元で満たし、ストレスのないカバー攻略を実現可能にします。</v>
+      </c>
+      <c r="O388" t="str">
+        <v>https://keitech.co.jp/pages/575/</v>
       </c>
     </row>
     <row r="389">
@@ -17491,28 +17569,31 @@
         <v/>
       </c>
       <c r="G389" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H389" t="str">
         <v>jig</v>
       </c>
       <c r="I389" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J389" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K389" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202601091020542528.jpg</v>
       </c>
       <c r="L389" t="str">
-        <v>2026-04-10T05:01:45.770Z</v>
+        <v>2026-04-10T05:40:50.108Z</v>
       </c>
       <c r="M389" t="str">
-        <v>2026-04-10T05:01:45.770Z</v>
+        <v>2026-04-10T05:40:50.108Z</v>
       </c>
       <c r="N389" t="str">
-        <v/>
+        <v>ラインアイがフックと異なる線径であることにお気づきでしょうか。実はコレ、ヘッドのノーズをよりシャープにしてベジテーションのすり抜け性能を向上させるため、フックとは異なるパーツで構成しているのです。また、アイはラインの結び目がヘッドとの付け根に偏らないよう、オーバル形にデザインしました。</v>
+      </c>
+      <c r="O389" t="str">
+        <v>https://keitech.co.jp/pages/655/</v>
       </c>
     </row>
     <row r="390">
@@ -17535,28 +17616,31 @@
         <v/>
       </c>
       <c r="G390" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H390" t="str">
         <v>jig</v>
       </c>
       <c r="I390" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J390" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K390" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011733324565.jpg</v>
       </c>
       <c r="L390" t="str">
-        <v>2026-04-10T05:01:47.045Z</v>
+        <v>2026-04-10T05:40:51.763Z</v>
       </c>
       <c r="M390" t="str">
-        <v>2026-04-10T05:01:47.045Z</v>
+        <v>2026-04-10T05:40:51.763Z</v>
       </c>
       <c r="N390" t="str">
-        <v/>
+        <v>ボトムノックで食わせる、NEWコンセプトラバージグスカートベイトを得意とするケイテックの新提案。フットボールジグとスイムジグの釣れる要素を抽出し、ハードボトムをスローに巻くだけで甲殻類など底生動物のライブリーなアクションを演出できます。使い方の基本は、ボトムを感じながらゆっくり巻くこと。同じクランキンでも、クランクベイトのボトムノックとは一線を画す、クランキンフットボールジグならではの無二のメソッドをお試しください。</v>
+      </c>
+      <c r="O390" t="str">
+        <v>https://keitech.co.jp/pages/576/</v>
       </c>
     </row>
     <row r="391">
@@ -17579,28 +17663,31 @@
         <v/>
       </c>
       <c r="G391" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H391" t="str">
         <v>jig</v>
       </c>
       <c r="I391" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J391" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K391" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202401161640403055.jpg</v>
       </c>
       <c r="L391" t="str">
-        <v>2026-04-10T05:01:48.745Z</v>
+        <v>2026-04-10T05:40:53.441Z</v>
       </c>
       <c r="M391" t="str">
-        <v>2026-04-10T05:01:48.745Z</v>
+        <v>2026-04-10T05:40:53.441Z</v>
       </c>
       <c r="N391" t="str">
-        <v/>
+        <v>ボリュームを抑えたコンパクトな仕様。すり抜け性とスナッグレス性を両立するブラシガードホールの構造。トレーラーとマッチするスカートカラーのバリエーション。フレアに優れたシリコンラバーの採用… いまでは当たり前となったジャパニーズジグのさまざまな工夫を、創業当初から独自の発想で盛り込み、必要に応じて都度マイナーチェンジを繰り返してまいりました。 『ModelⅠ』はいわば、ケイテックの理念『経験は、品質に。』を象徴する製品。 四半世紀にわたり愛され続けている理由がそこにあります。そして2023年春、ヘッドの仕様を見直した『モデル Ⅰ Ver.2.0』を、満を持してJIG MANの皆さまにお届けいたします。</v>
+      </c>
+      <c r="O391" t="str">
+        <v>https://keitech.co.jp/pages/602/</v>
       </c>
     </row>
     <row r="392">
@@ -17623,28 +17710,31 @@
         <v/>
       </c>
       <c r="G392" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H392" t="str">
         <v>jig</v>
       </c>
       <c r="I392" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J392" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K392" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202401161641262646.jpg</v>
       </c>
       <c r="L392" t="str">
-        <v>2026-04-10T05:01:50.828Z</v>
+        <v>2026-04-10T05:40:55.491Z</v>
       </c>
       <c r="M392" t="str">
-        <v>2026-04-10T05:01:50.828Z</v>
+        <v>2026-04-10T05:40:55.491Z</v>
       </c>
       <c r="N392" t="str">
-        <v/>
+        <v>カバージグの理想形である『ModelⅠ』のコンセプトやデザインをすべて継承し、このカテゴリーのルアーに本来備わっているビッグフィッシュへの対応力を強化しました。 ヘビーウェイト＆フルサイズでありながら、樹脂タングステンをヘッド素材に用いることで全体ボリュームを抑え高いすり抜け性を発揮。なおかつ、抵抗の大きいバルキートレーラーと組み合わせても力負けすることなく、ヘッドを支点とするメリハリの利いた操作を可能にしています。 つまり、シャローのみならずミドル～ディープボトムのヘビーカバーでもスカーテッドベイトならではの有機的存在感で誘えるわけです。 リーズ帯の奥の奥、折り重なった流木や浮葉植物のヘビーマット、崩落跡のディープウォーターカバーなど、複雑に入り組んだピンスポットさえ狙い撃つことができる、オールレンジ対応“食わせのビッグベイト”。 ボリュームのあるトレーラーと『モデルⅣ』のコンボをそんなイメージでお使いいただくと、ジグフィッシングの新たなトビラが開くはずです。</v>
+      </c>
+      <c r="O392" t="str">
+        <v>https://keitech.co.jp/pages/603/</v>
       </c>
     </row>
     <row r="393">
@@ -17667,28 +17757,31 @@
         <v/>
       </c>
       <c r="G393" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H393" t="str">
         <v>jig</v>
       </c>
       <c r="I393" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J393" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K393" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202501300927538741.jpg</v>
       </c>
       <c r="L393" t="str">
-        <v>2026-04-10T05:01:52.477Z</v>
+        <v>2026-04-10T05:40:57.481Z</v>
       </c>
       <c r="M393" t="str">
-        <v>2026-04-10T05:01:52.477Z</v>
+        <v>2026-04-10T05:40:57.481Z</v>
       </c>
       <c r="N393" t="str">
-        <v/>
+        <v>比重13、樹脂タングステンヘッドのフットボールラバージグ。着底姿勢にこだわりたいミドル～ディープレンジの釣りにうってつけです。 ヘッド素材はとても硬く、鉛製品に比べ感度が大幅にアップ。着底の瞬間やボトムの様子が一層明確に把握できます。繊細なガードは見た目以上の効果。臆することなく水中のストラクチャーを直撃できます。繊細でよくフレアーするオリジナルシリコンスカートSR-40。丁寧かつ熟練の手巻きです。</v>
+      </c>
+      <c r="O393" t="str">
+        <v>https://keitech.co.jp/pages/10/</v>
       </c>
     </row>
     <row r="394">
@@ -17711,28 +17804,31 @@
         <v/>
       </c>
       <c r="G394" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H394" t="str">
         <v>jig</v>
       </c>
       <c r="I394" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J394" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K394" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202209221617177492.jpg</v>
       </c>
       <c r="L394" t="str">
-        <v>2026-04-10T05:01:55.893Z</v>
+        <v>2026-04-10T05:41:00.188Z</v>
       </c>
       <c r="M394" t="str">
-        <v>2026-04-10T05:01:55.893Z</v>
+        <v>2026-04-10T05:41:00.188Z</v>
       </c>
       <c r="N394" t="str">
-        <v/>
+        <v>コンパクトな樹脂タングステン製バナナヘッド、特製スカートを巻いたスクリューパーツ、丈夫な特注フック。ありそうで無かった理想のバランスを手に入れるため、吟味され尽くしたカスタムパーツ達。水面直下や中層をリトリーブする、ボトムをウィードや岩に当てながら泳がせる。従来のラバージグとはまったく違う、新たな境地・機能を開発しました。トレーラーには、弊社『スイングインパクトFAT4.8”』を“強く強く”お勧めいたします。比類なきバランス、バルキーな存在感、強い波動、卓越したウィードレス／スリ抜け性能。ビッグフィッシュを仕留めるための数々の要諦が、この組み合わせには込められています。</v>
+      </c>
+      <c r="O394" t="str">
+        <v>https://keitech.co.jp/pages/206/</v>
       </c>
     </row>
     <row r="395">
@@ -17755,28 +17851,31 @@
         <v/>
       </c>
       <c r="G395" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H395" t="str">
         <v>jig</v>
       </c>
       <c r="I395" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J395" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K395" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011735477115.jpg</v>
       </c>
       <c r="L395" t="str">
-        <v>2026-04-10T05:01:57.179Z</v>
+        <v>2026-04-10T05:41:01.840Z</v>
       </c>
       <c r="M395" t="str">
-        <v>2026-04-10T05:01:57.179Z</v>
+        <v>2026-04-10T05:41:01.840Z</v>
       </c>
       <c r="N395" t="str">
-        <v/>
+        <v>比重13樹脂タングステンを用い、カチッとコンパクトに仕上げたガード付きスモールラバージグ。小さいのにしっかりしたガード力、そして軽いくせに目を見張るカバー突破力。繊細かつ大胆にスモールベイトでカバーを攻める、そんな昨今の釣りにマッチしたアイテムです。やや硬め、機敏にフレアーするSR-40シリコンスカートを丁寧に手巻きしています。-0-0-0-0-0-0</v>
+      </c>
+      <c r="O395" t="str">
+        <v>https://keitech.co.jp/pages/13/</v>
       </c>
     </row>
     <row r="396">
@@ -17799,33 +17898,36 @@
         <v/>
       </c>
       <c r="G396" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H396" t="str">
         <v>jig</v>
       </c>
       <c r="I396" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J396" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K396" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011736112779.jpg</v>
       </c>
       <c r="L396" t="str">
-        <v>2026-04-10T05:01:58.540Z</v>
+        <v>2026-04-10T05:41:03.332Z</v>
       </c>
       <c r="M396" t="str">
-        <v>2026-04-10T05:01:58.540Z</v>
+        <v>2026-04-10T05:41:03.332Z</v>
       </c>
       <c r="N396" t="str">
-        <v/>
+        <v>ラウンドヘッドに今どきのラバーカッティング。そして繊細・精密を極めた“モノ（1本）ガード”。パラアシ、岩、ロープ、ウィード等ほとんどの障害物を難なくクリア、そしてフッキングは超イージーなノーガード感覚に仕上げています。昨今のパワーフィネスを知り尽くした仕様です。デコイ・リマリック #3フック、1/32, 1/20, 1/16, 3/32oz。ヘッドはもちろん比重13、樹脂タングステン製。</v>
+      </c>
+      <c r="O396" t="str">
+        <v>https://keitech.co.jp/pages/14/</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N396"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O396"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -489,6 +489,9 @@
       <c r="N2" t="str">
         <v/>
       </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -533,6 +536,9 @@
       <c r="N3" t="str">
         <v/>
       </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -577,6 +583,9 @@
       <c r="N4" t="str">
         <v/>
       </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -621,6 +630,9 @@
       <c r="N5" t="str">
         <v/>
       </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -665,6 +677,9 @@
       <c r="N6" t="str">
         <v/>
       </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -709,6 +724,9 @@
       <c r="N7" t="str">
         <v/>
       </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -753,6 +771,9 @@
       <c r="N8" t="str">
         <v/>
       </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -797,6 +818,9 @@
       <c r="N9" t="str">
         <v/>
       </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -841,6 +865,9 @@
       <c r="N10" t="str">
         <v/>
       </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -885,6 +912,9 @@
       <c r="N11" t="str">
         <v/>
       </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -929,6 +959,9 @@
       <c r="N12" t="str">
         <v/>
       </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -973,6 +1006,9 @@
       <c r="N13" t="str">
         <v/>
       </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1017,6 +1053,9 @@
       <c r="N14" t="str">
         <v/>
       </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1061,6 +1100,9 @@
       <c r="N15" t="str">
         <v/>
       </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1105,6 +1147,9 @@
       <c r="N16" t="str">
         <v/>
       </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1149,6 +1194,9 @@
       <c r="N17" t="str">
         <v/>
       </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1193,6 +1241,9 @@
       <c r="N18" t="str">
         <v/>
       </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1237,6 +1288,9 @@
       <c r="N19" t="str">
         <v/>
       </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1281,6 +1335,9 @@
       <c r="N20" t="str">
         <v/>
       </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1325,6 +1382,9 @@
       <c r="N21" t="str">
         <v/>
       </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1369,6 +1429,9 @@
       <c r="N22" t="str">
         <v/>
       </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1413,6 +1476,9 @@
       <c r="N23" t="str">
         <v/>
       </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1457,6 +1523,9 @@
       <c r="N24" t="str">
         <v/>
       </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1501,6 +1570,9 @@
       <c r="N25" t="str">
         <v/>
       </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1545,6 +1617,9 @@
       <c r="N26" t="str">
         <v/>
       </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1589,6 +1664,9 @@
       <c r="N27" t="str">
         <v/>
       </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1633,6 +1711,9 @@
       <c r="N28" t="str">
         <v/>
       </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1677,6 +1758,9 @@
       <c r="N29" t="str">
         <v/>
       </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1721,6 +1805,9 @@
       <c r="N30" t="str">
         <v/>
       </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1765,6 +1852,9 @@
       <c r="N31" t="str">
         <v/>
       </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1809,6 +1899,9 @@
       <c r="N32" t="str">
         <v/>
       </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1853,6 +1946,9 @@
       <c r="N33" t="str">
         <v/>
       </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1897,6 +1993,9 @@
       <c r="N34" t="str">
         <v/>
       </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1941,6 +2040,9 @@
       <c r="N35" t="str">
         <v/>
       </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1985,6 +2087,9 @@
       <c r="N36" t="str">
         <v/>
       </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2029,6 +2134,9 @@
       <c r="N37" t="str">
         <v/>
       </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2073,6 +2181,9 @@
       <c r="N38" t="str">
         <v/>
       </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2117,6 +2228,9 @@
       <c r="N39" t="str">
         <v/>
       </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2161,6 +2275,9 @@
       <c r="N40" t="str">
         <v/>
       </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2205,6 +2322,9 @@
       <c r="N41" t="str">
         <v/>
       </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2249,6 +2369,9 @@
       <c r="N42" t="str">
         <v/>
       </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2293,6 +2416,9 @@
       <c r="N43" t="str">
         <v/>
       </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2337,6 +2463,9 @@
       <c r="N44" t="str">
         <v/>
       </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2381,6 +2510,9 @@
       <c r="N45" t="str">
         <v/>
       </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2425,6 +2557,9 @@
       <c r="N46" t="str">
         <v/>
       </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2469,6 +2604,9 @@
       <c r="N47" t="str">
         <v/>
       </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2513,6 +2651,9 @@
       <c r="N48" t="str">
         <v/>
       </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2557,6 +2698,9 @@
       <c r="N49" t="str">
         <v/>
       </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2601,6 +2745,9 @@
       <c r="N50" t="str">
         <v/>
       </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2645,6 +2792,9 @@
       <c r="N51" t="str">
         <v/>
       </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2689,6 +2839,9 @@
       <c r="N52" t="str">
         <v/>
       </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2733,6 +2886,9 @@
       <c r="N53" t="str">
         <v/>
       </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2777,6 +2933,9 @@
       <c r="N54" t="str">
         <v/>
       </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2821,6 +2980,9 @@
       <c r="N55" t="str">
         <v/>
       </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2865,6 +3027,9 @@
       <c r="N56" t="str">
         <v/>
       </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2909,6 +3074,9 @@
       <c r="N57" t="str">
         <v/>
       </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2953,6 +3121,9 @@
       <c r="N58" t="str">
         <v/>
       </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2997,6 +3168,9 @@
       <c r="N59" t="str">
         <v/>
       </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3041,6 +3215,9 @@
       <c r="N60" t="str">
         <v/>
       </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3085,6 +3262,9 @@
       <c r="N61" t="str">
         <v/>
       </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3129,6 +3309,9 @@
       <c r="N62" t="str">
         <v/>
       </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3173,6 +3356,9 @@
       <c r="N63" t="str">
         <v/>
       </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3217,6 +3403,9 @@
       <c r="N64" t="str">
         <v/>
       </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3261,6 +3450,9 @@
       <c r="N65" t="str">
         <v/>
       </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3305,6 +3497,9 @@
       <c r="N66" t="str">
         <v/>
       </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3349,6 +3544,9 @@
       <c r="N67" t="str">
         <v/>
       </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3393,6 +3591,9 @@
       <c r="N68" t="str">
         <v/>
       </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3437,6 +3638,9 @@
       <c r="N69" t="str">
         <v/>
       </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3481,6 +3685,9 @@
       <c r="N70" t="str">
         <v/>
       </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3525,6 +3732,9 @@
       <c r="N71" t="str">
         <v/>
       </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3569,6 +3779,9 @@
       <c r="N72" t="str">
         <v/>
       </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -3613,6 +3826,9 @@
       <c r="N73" t="str">
         <v/>
       </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -3657,6 +3873,9 @@
       <c r="N74" t="str">
         <v/>
       </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -3701,6 +3920,9 @@
       <c r="N75" t="str">
         <v/>
       </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -3745,6 +3967,9 @@
       <c r="N76" t="str">
         <v/>
       </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -3789,6 +4014,9 @@
       <c r="N77" t="str">
         <v/>
       </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -3833,6 +4061,9 @@
       <c r="N78" t="str">
         <v/>
       </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -3877,6 +4108,9 @@
       <c r="N79" t="str">
         <v>Featuring a patented Double Inertial Balancer System for head-turning action, the DIAMANTE SONIC SLIDE delivers a dramatic 180-degree walk and extended sliding action. Generating aggressive turbulence and a deep metal knock with each turn, SONIC SLIDE calls fish up from surprising depths to trigger surface-breaching strikes. With a deep-cut keel design to enhance responsiveness and an aerodynamically optimized body, SONIC SLIDE is built for long-distance deployment in rough and calm waters alike.</v>
       </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -3921,6 +4155,9 @@
       <c r="N80" t="str">
         <v>メガバス創世期に誕生し、数多の伝説を築き上げたDOG-Xシリーズ。メガバス創業者、伊東由樹が見出し、DOG-Xに宿した不変の原理とハイドロメカニクスを最大限に体現する、DOG-Xシリーズのグレートマザーが降臨。ブランドン・パラニュークと共に闘う米国フィールドから世界に解き放ち、DOGMAXがいよいよグローバルなフィールドでモンスターを制圧。 強大でトルクフルなターンインとテールアウトを生み出す、「重心分割式シーソーバランサーシステム（PAT.）」、超・長距離スライドを生み出す「タンデム慣性バランサーシステム（PAT.）」、徹底的に水を噛み込んで食らいつき、スタビリティを高めながらリアルなボイルサウンドを発生させる「ウォータースルー・ギル（PAT.）」、内部のボールウエイトがピンポイント接触する衝突によって引き起こす「衝撃波」と硬質な「ノッキングサウンド」が、深層のモンスターにも果敢にアピール。誰もが手軽に130mmのビッグボディを軽快に操作でき、メガバス・トップウォーターマジックの神髄に触れることができます。 あらゆるフィッシュイーターのMAXサイズをフィーディングモードに入れてバイトさせてしまう、ファンクショナルなペンシルベイトです。</v>
       </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -3965,6 +4202,9 @@
       <c r="N81" t="str">
         <v>Introduced in 1996,POPX continues to dominate the high-end top-water bait markets of both Japan and the United States. Equipped with MEGABASS original SIDE-STEPPING BALANCER(PAT),POPX walks a rolling dog-walk unlike any other poppers, and the WATER DUCTS(PAT)which imitate the bubbly water coming out of gills and help create a natural"bio-sound", not an ordinary popping sound. POPX also spits, not splashes, quite a distance. Currently 16 colors are available."GG"stands for GUANIUM GHOST, the most shad-like finish, "PM"PEARL MICA(including SG CRACKED finish)and "GP"GUANIUM PHANTOM(including GP CRACKED finish),a see through phantom finish.</v>
       </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4009,6 +4249,9 @@
       <c r="N82" t="str">
         <v>The unique cup shape of the BABY POPX creates an irresistible water-pushing action. Its design produces a lively and engaging splash sound, perfectly complemented by its ability to respond with agility to even the most delicate rod work. With a nuanced short slide and splashing dog walk action, this diminutive popper is designed to captivate even the most elusive game. Despite its ultra-compact body, the BABY POPX offers incredible long-distance casting ability, allowing anglers to cover a wide area with ease and precision. Its centrally placed line eye adds dimension to the traditional popping retrieve, enabling a nimble dog walk to add another layer of allure to its presentation. Further, the BABY POPX’s micro form enables a stealthy splashdown at the end of a long cast, staying under the radar of easily spooked monsters until its pinpoint agility and splashing siren-song call explosive bites from below.</v>
       </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4053,6 +4296,9 @@
       <c r="N83" t="str">
         <v>KARASHI iGは、ハイドロダイナミクスから生まれた独特なキールヘッド(D.PAT.P)により、優れた直進性能を発揮。リトリーブ速度のわずかな変化に対し、あたかも船の揺れ戻しを抑制するような、ボディの姿勢変化を的確に微調整して補正するアクションを発生。 ただゆっくりと引くだけで生まれる幻惑の引き波と、卓越したスタビリティ効果が、これまでのi字系を見切ったクレバーフィッシュを的確にバイトに持ち込みます。 テールにセットした独自のフレアファイバーはキールヘッドの直進性を促進。 二度喰い、三度喰いさえ多発するKARASHI iGは、シビアなフィールドで使ってこそ差がつく、タフフィッシュを獲るために特化したスペシャルスペックが満載。勝つために使う、コンペティティブなi字系です。</v>
       </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4097,6 +4343,9 @@
       <c r="N84" t="str">
         <v>KARASHI 80は、オリジナルのKARASHI同様に水面直下のドッグウォークアクションを手軽かつ、ダイナミックに展開。さながら「リップレス・ジャークベイト」ともいうべき水面下で展開する規則的なロングダート性能は、水面までターゲットが出切らないシビアな状況下で新次元の釣獲パフォーマンスを発揮。 伊東由樹のハイドロダイナミクス理論が生み出したファンクショナルなボディ形態は、左右への規則正しいドッグウォークのリズムが刻みやすい節度ある水噛み抵抗感をもたらし、ジャークやトゥイッチによる水面直下での左右への規則的なロングダートを実現。 まさに、リップレス・ジャークベイトと呼べるＮＥＷジャンルを創造し、稀代のバージンインパクトを発揮します。 水面に出切らないナーバスなターゲットに対して、ダートアクションを仕掛けて喰わせる一撃必釣のシークレットパフォーマンスは圧巻。ぜひ、マジカルな釣果をご体感ください。</v>
       </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4141,6 +4390,9 @@
       <c r="N85" t="str">
         <v>The KARASHI is the embodiment of next-generation Japanese finesse. This secret worming bait will change the face of 3-inch finesse soft bait fishing. The super-natural feel of this bite-sized lure entices even the spookiest fish to bite and hold impulsively. For targets that see your other lures but hesitate to bite, the KARASHI is your secret “one shot, one kill” bite-triggering weapon. 1. With twitching, the KARASHI exhibits agile dog-walking and darting action. 2. With slow retrieves, KARASHI performs an I-shaped action. The defenseless wobbling action evokes injured bait, triggering bites from opportunistic feeders. The extremely natural minute-vibrations trigger bites from clever fish. KARASHI generates overwhelming performance from the combination of its darting action and I-shaped action.</v>
       </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4185,6 +4437,9 @@
       <c r="N86" t="str">
         <v>DOG-X Jr. is not simply a downsized version of our original DOG-X. It is certainly a bit smaller than DOG-X as the name indicates, but it is equipped with a new lengthwise moving balancer as well as the now familiar SIDE-STEPPING MOVING BALANCER (PAT.) of the original DOG-X. This new balancer pushes the bait while walking, so that the roll-walk action of DOG-X Jr. is sharper and more dynamic for its size. The point is that smaller bait does not have to suffer from a smaller action. The action of DOG-X Jr. will remind you of the baitfish chased by a predator, frantically ripping and skipping the water surface. Also, you will find out that casting and retrieving DOG-X Jr. with F1 or F2 class Destroyer bait rods is extremely enjoyable due to their high compatibility. If you want to experience the fastest and the smoothest dog-walk action of your life, you must go for DOG-X Jr.</v>
       </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4229,6 +4484,9 @@
       <c r="N87" t="str">
         <v>KARASHI SPINNERは、通常のI字系ルアーによるアプローチでは今一つ反応が得られなかった完全ニュートラルなバスに高い効果を発揮するプロップベイト。長距離リトリーブにおける優れた直進安定性と正姿勢への素早い復帰は、独自のキールヘッドデザインによるもの。ウィードボトムの表層～中層、シャローやオーバーハング下などで水面直下をスローにただ引きするだけでOKです。 また、水面へと浮上させ、軽くジャーク＆リトリーブすれば、稚鮎などナチュラルベイトの繊細なボイルを演出。通常のバズベイトやスイッシャーではインパクトが強すぎる時、KARASHI SPINNERなら的確にバイトに持ち込みます。</v>
       </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4273,6 +4531,9 @@
       <c r="N88" t="str">
         <v>As with other Megabass baits, POPMAX demands a lot of explaining. The original mold was again carved out by Yuki Ito rather than relying on computer design programs. And the paint works and the overall quality is impeccable as expected of Megabass. Also, POPMAX features a unique water flow system which consists of six water intakes and a water chamber. Instead of the regular water-through system used for POPX, this system utilizes the water pressure change inside the water chamber, making it act like a lip. Furthermore, when paused, the water in the chamber goes out and lifts its head, ready for a splash with a light rod action. With a gentle rod tip action POPMAX will roll-walk dynamically grabbing the water with each rolling action.</v>
       </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4317,6 +4578,9 @@
       <c r="N89" t="str">
         <v>The DOG-X QUICK WALKER supercharges the original DOG-X's dog walking prowess with a redesigned body, improved balancer system, and one-knock sound. It greatly surpasses the expectations for standard-sized pencil baits with its dynamic water displacement, sharp table turns and its one-knock sound, stimulating cruising fish in the mid range. The casting distance has been improved upon as well, to allow for speedy coverage of wide areas. This DOG-X will set fire to dormant beasts, even more so than the original.</v>
       </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4361,6 +4625,9 @@
       <c r="N90" t="str">
         <v>DOG-X has come into the world during Megabass genesis and has continued to send out Megabass engineering to the world. Taking over its legends, finally in year 2010 Super Dog-X has awakened. “High speed-dog walk” and the responsive “Quick slide &amp; turn” is achieved. Overturning the common sense of low water resistant compact pencil baits, the high level operability will not let the others follow. “See-saw balancing system PAT.” updated from the engineering of the first model is added, and the new design “Water through-Gill PAT.” which increases its stability by biting the water is applied. The original balancing body D.PAT.P by the high mounted-line eye that behaves responsively has been applied to achieve a real game. Many of Yuki Ito’s lure technology and design logic is loaded. DOG-X that caught fishes that could not be caught has evolved into a new generation DOG-X challenging clever and tough monsters in the 21st century. Not only with slow taper-light action rod, it is also possible to make dog walk actions with medium heavy action rods. Please check out the overwhelming “easy control ability” at all sorts of fields.</v>
       </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4405,6 +4672,9 @@
       <c r="N91" t="str">
         <v>Don’t be fooled by its size—this DOG-X was built for GIANTS. Powered by a patented SIDE-STEPPING BALANCER, the GIANT DOG-X is engineered to elevate the walking game of novices and experts alike. Featuring a tungsten balancer that moves laterally from left-to-right, the system throws its weight behind each turn for a sharper walk and a unique roll that flashes the GIANT DOG-X’s exquisite detail to monsters below. This effortlessly crisp and dynamic roll-walking action draws vicious strikes in even the toughest slick-calm conditions, bringing explosive performance to angling arsenals around the world.</v>
       </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4449,6 +4719,9 @@
       <c r="N92" t="str">
         <v>アンスラックスは、ローラージャイロ・バランサーシステム（PAT.P）によって、シャフトバランサー上を転位するボールウエイトが甲高いクリックサウンドを発生させ、多彩なマルチアクションを演出するウェイクベイト。 スローリトリーブでは、水面でスーパーローリングアクションを生み出し、腹部のフィン（尻ビレ）が左右にテイリングして水流を掻き分け、独自の三角波でアピール。リトリーブ速度を上げると、水面直下10～20㎝程度をローリング・スイムするサブサーフェスシャッドとして活躍。また、ジャークによるスラッピングでは、水面でスプラッシュやバブルを発生させるボイルベイトを演出。ストップ＆ゴーでは、ダイブ後にフラッタリングやライズアップするパニックベイトを再現。 多彩なアクションとダイナミックなパフォーマンスがもたらすアンスラックス独自の釣獲力を是非フィールドでご体感ください。</v>
       </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4493,6 +4766,9 @@
       <c r="N93" t="str">
         <v>The MEGADOG-X is a supercharged walking bait built to drive trophy　freshwater targets into a reactive frenzy. Clocking in at a hefty 180mm (7in), the MEGADOG-X powers a strategic topwater approach whenever big fish are keyed in on big meals. With a simple reel/stop retrieve, the MEGADOG-X will slide with surprising ease. With more vigorous rod work, the lure will explode into a fury of action, setting off an aggressive splash-walking chain reaction that calls to the largest predators in the area. Incorporating decades of dog-walking refinement, the MEGADOG-X makes big bait topwater angling even more accessible and explosive. * The photograph is a prototype</v>
       </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4537,6 +4813,9 @@
       <c r="N94" t="str">
         <v>アンスラックスは、ローラージャイロ・バランサーシステム（PAT.P）によって、シャフトバランサー上を転位するボールウエイトが甲高いクリックサウンドを発生させ、多彩なマルチアクションを演出するウェイクベイト。 スローリトリーブでは、水面でスーパーローリングアクションを生み出し、腹部のフィン（尻ビレ）が左右にテイリングして水流を掻き分け、独自の三角波でアピール。リトリーブ速度を上げると、水面直下10～20㎝程度をローリング・スイムするサブサーフェスシャッドとして活躍。また、ジャークによるスラッピングでは、水面でスプラッシュやバブルを発生させるボイルベイトを演出。ストップ＆ゴーでは、ダイブ後にフラッタリングやライズアップするパニックベイトを再現。 多彩なアクションとダイナミックなパフォーマンスがもたらすアンスラックス独自の釣獲力を是非フィールドでご体感ください。</v>
       </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4581,6 +4860,9 @@
       <c r="N95" t="str">
         <v>伊東由樹がプライベートゲーム用に手作りしていたランカーキラー・スイッシャーがエクスプローズ。 独特なひねり形状のプロペラには、独自のギアホール加工が施されており、スクラッチサウンドを発生。超低重心マウントしたフラットバランサーによって、激しいロッドワークによるジャークでもボディを回転させることなく、きっちりとラフウォーターに喰らいつく卓越したスタビリティを発揮。水面を激しく割るラフバイトにおいても確実なフックセットを実現します。 スローリトリーブによるタダ巻きでは、時折、ゆらりとウォブリング。凪の水面ではデッドリーベイトを効果的に演出します。 他のスイッシャーとは明らかに違う、一目瞭然のスペックを内包するプロップベイトのスペシャルエディションです。</v>
       </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4625,6 +4907,9 @@
       <c r="N96" t="str">
         <v>The XPOD is the world's first transformation-plug. The COMMAND BILL(PAT.), which has seven distinct settings, is adjustable according to angler preference and specific conditions. Each rugged setting alters the pressure and volume in the WATER INTAKE(PAT.), changing the lure's displacement, weight ratio, and body balance. By altering the properties of rod actino and lip setting, it can be adjusted for use in various situations. The XPOD is a multi-performance lure, allowing anglers to tap into its many abilities and applications. It can transform into 4 modes for top water: a roll-walking pencil bait, a dog-walking popper for targeting specific areas, a sliding pencil popper for targeting wide areas, and a splash head to lure in prey through sound and splashing. For the sub-surface it has 2 modes: a diving pencil and a diving popper. In addition, it has a special trick-darting dive mode using random trajectories and rolling action, allowing it to be used for slow retrieves as a diving swim-bait.</v>
       </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4669,6 +4954,9 @@
       <c r="N97" t="str">
         <v>The XPOD symbolizes the new era of Megabass top water baits. Loved across the world, it is now available in a smaller profile, retaining its captivating appearance and its situation-specific adaptability. Its realistic form will entice the most cunning of prey. While the profile may be small, it packs the same powerful punch as the original, and is ready to decisively bring down its targets.</v>
       </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -4713,6 +5001,9 @@
       <c r="N98" t="str">
         <v>Carefully honed for explosive walking action, DOG-X DIAMANTE cuts through water with unparalleled responsiveness. Featuring a Deep Cut Keel design to sharpen action and angler control, DIAMANTE walks with a lively commotion in calm and rough conditions alike. Designed to excel even at high speeds, DIAMANTE is ideally suited to rapid deployment, searching wide areas quickly and effectively. Rattle-tuned to the exacting specifications of veteran pros, DIAMANTE generates an enticing surface commotion, drawing strikes from afar.</v>
       </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4757,6 +5048,9 @@
       <c r="N99" t="str">
         <v>MPWは、POPXとは異なるパフォーマンスを発揮する、「テーブルターンを高速化してなお、ネチることができる」異次元のクイックレスポンス・ポッパーを創生。 メガバスのカタログモデルには存在しない、POPXとBabyPOPXの「中間サイズ」は、極みのフィネスポッパーゲームをさらにコンプリート。 アナザーPOPXの魔力は、スレきったメジャーレイクのクレバーフィッシュを相手にお確かめください。</v>
       </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -4801,6 +5095,9 @@
       <c r="N100" t="str">
         <v>MEGADOGは、メガバスが誇る稀代の名作DOG-Xのポテンシャルを、異次元のレベルまで高めた対ビッグフィッシュ用のスペシャルウェポンです。200mmを超える大型のベイトを水面に追い込み捕食するモンスターフィッシュのみをターゲットとし、既成概念を破壊する強烈なインパクトとアピール力を発揮したメガサイズペンシルベイトです。</v>
       </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -4845,6 +5142,9 @@
       <c r="N101" t="str">
         <v>KIRINJIの生みの親、伊東由樹は、水面直下にウィードが迫る広域エリアにて、KIRINJIを表層でただゆっくりと引くだけで、スピナーベイトに連日叩かれてきたスプーキーなバスを驚異的に釣っています。KIRINJIが水面でもたらす独特なハイピッチ・ロール・スクリューは、タフなバスにとても効果的です。同エリアから連続して何度もチェイスしてくる様は、KIRINJIが発生させる絶妙なライブ波動によるものでしょう。 MPWでは、フレッシュウォーターによりアジャストする特別なKIRINJIを製作。鋭いポッピングやスプラッシュが出しやすい比重へとチューンし、あの独特なライブ波動に加わるスパイシーなインパクトがシャローに散発するランカーをより広域から惹き寄せます。</v>
       </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -4889,6 +5189,9 @@
       <c r="N102" t="str">
         <v>Orca はイージーなロッドワークによって、アングラーの意図を超えた「変幻アクション」を誰もが自然に生み出すことができる、数奇なプロップフォーム（プロペラの捻り形態）ベイトです。計算された捻りボディが水を的確に絡め取り、水流の巻き込みと剥離を適宜に発生させることで、アングラーが意図しないアクションを自然に生み出します。Orca には使い込むほどにハマってしまう、こだわりのトップウォータープラッガーを虜にする特別な魔力が潜んでいます。</v>
       </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -4933,6 +5236,9 @@
       <c r="N103" t="str">
         <v>伊東由樹がプライベートゲーム用に手作りしていたランカーキラー・スイッシャーがエクスプローズ。 独特なひねり形状のプロペラには、独自のギアホール加工が施されており、スクラッチサウンドを発生。超低重心マウントしたフラットバランサーによって、激しいロッドワークによるジャークでもボディを回転させることなく、きっちりとラフウォーターに喰らいつく卓越したスタビリティを発揮。水面を激しく割るラフバイトにおいても確実なフックセットを実現します。 スローリトリーブによるタダ巻きでは、時折、ゆらりとウォブリング。凪の水面ではデッドリーベイトを効果的に演出します。 他のスイッシャーとは明らかに違う、一目瞭然のスペックを内包するプロップベイトのスペシャルエディションです。</v>
       </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -4977,6 +5283,9 @@
       <c r="N104" t="str">
         <v>プロップフォーム(プロペラ形態)ボディが生み出す、独自のインパクト。 ボディがスパイラル形状を持つプロペラデザイン。ボディ自体がプロペラ・・・これがアイティオー流のスイッシャーです。 SCREAM-X 3/4oz.はロッドティップを水面近くに下げてジャークすると即座にダート。強めの連続トゥイッチを入れると、左右へと激しくボディを反転させながらドッグウォーク＆テーブルターン。しかもその激しいドッグウォークの最中には、ジュオッ！っと、激しいスクリーミングサウンドを伴います。この動きが、大型ベイトの激しいハタキ行動を連想させるかもしれません。 操作のキモは、ロッドティップを水面近くに下げること。SCREAM-Xは、ルアーとアングラーの距離が近いときにロッドティップを上げてリトリーブするとプロペラが回転しないようにセッティングされています。バランスウエイトをボディ後部にインサートし、フロントを浮かせているからです。 従来のスイッシャーは、スポットでバスがバイトしなかったとき、回収中もプロペラが激しく回転して水面を騒々しく滑走するため、エリア全体に不要な警戒心を与えていました。SCREAM-Xは、狙うべきスポットだけでペラが回転し、軽妙な首振りターンと激しいインパクトを放つ独特なセッティングを施しています。</v>
       </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5021,6 +5330,9 @@
       <c r="N105" t="str">
         <v>BEETLE-X enchants bug-eating monster bass with its enticing action and siren call. Featuring AIR wings crafted with a material selected both for low elasticity and specific gravity, BEETLE-X HOVER CRAWL is able to perform a high-pitched crawling action that practically dances across the surface, even in rough conditions. Carefully tuned sound profile features a precise mix of steel and glass rattles, for a multilayered sound that consistently draws targets from afar. Finished with unprecedented detail, the HOVER CRAWL shines with alluring realism. ※The photograph is a prototype.</v>
       </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -5065,6 +5377,9 @@
       <c r="N106" t="str">
         <v>プロップフォーム(プロペラ形態)ボディが生み出す、独自のインパクト。 ボディがスパイラル形状を持つプロペラデザイン。ボディ自体がプロペラ・・・これがアイティオー流のスイッシャーです。 SCREAM-X Jr. 1/2oz.は、プロップフォーム（プロペラ形態）をベイトライクなスリムなボディ形態にデザイン。水面に食らいつくスタビリティを極限まで高め、あえて直進性能に特化してセットアップ。小型スイッシャーながら、タイトなプロペラボディが常時、水流をに瞬時に絡め取り、装着した前後のWプロップが激しく高回転。水面でスクリームサウンドを放ち、激しいフィーディング＆ボイルをイミテートします。</v>
       </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5109,6 +5424,9 @@
       <c r="N107" t="str">
         <v>Nano SIGLETT, the featherweight bug-pattern dynamo made for instantaneous inhalation, is the result of ITO Engineering's ultra-precision NanoCraft Technology. This unrelenting attention to minutiae gives shape to exquisite hydrodynamics that enable an extremely consistent and appealing action that often escapes conventional tiny lures. At a few hairs over 2cm, the Nano SIGLETT crawls with a high-pitch action that few bass will be able to ignore. This is finesse bug-pattern angling at its finest.</v>
       </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5153,6 +5471,9 @@
       <c r="N108" t="str">
         <v>TINY SIGLETT is a micro bug bait that imitates the struggling movements of cicada and similar winged insects on the water surface. Steady retrieve creates a paddling walking-motion, with each wing dipping into the water as it turns, walks, and splashes on the surface. Shake the line to imitate the fluttering death throes of a struggling insect, and fool even the most cunning of predators. Decreased buoyancy helps fish take down TINY SIGLETT for higher hook up ratios. ※The photograph is a prototype.</v>
       </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -5197,6 +5518,9 @@
       <c r="N109" t="str">
         <v>Siglett is a winged bug-bait modeled after a Japanese cicada. Its tungsten alloy balancer inside its chamber is sound-tuned to mimic the Higurashi cicada of Japan. Also, it looks just like one, complete with a pair of translucent wings made of semi-hard plastic which not only slide up &amp; down, but also act as large lips for jittering bug action.</v>
       </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -5241,6 +5565,9 @@
       <c r="N110" t="str">
         <v>Siglett is a winged bug-bait modeled after a Japanese cicada. Its tungsten alloy balancer inside its chamber is sound-tuned to mimic the Higurashi cicada of Japan. Also, it looks just like one, complete with a pair of translucent wings made of semi-hard plastic which not only slide up &amp; down, but also act as large lips for jittering bug action. Since line eye is located at its tail, Siglett casts with the least air resistance, insuring surprisingly good casting distance and accuracy as a winged bug bait. When retrieved, Siglett’s wings naturally ‘open up’ and each ‘wing lip’ starts to crawl alternately as it jitters along. Fast to slow-steady retrieve in open areas and stop &amp; go twitching action under overhangs are the most effective application. Enjoy a relaxing top-water fishing day with Siglett.</v>
       </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5285,6 +5612,9 @@
       <c r="N111" t="str">
         <v>As the name OVER REV indicates, the limiter-breaking high-speed rotations of the ORC are next-level. Introducing a flat side shallow crank that has succeeded in dramatically increasing roll speed!  The ORC’s super high-speed rolling is thanks to the newly developed GYRO BALANCING LBO mechanism that generates a high-speed wobbling roll like that of a roly-poly toy. This eliminates the need for the high-speed retrieves seen in previous flat sides which were needed to generate flashing. The ORC emits intense flashing and screw waves even during slow retrieves. It’s able to maintain a position directly under the surface for long periods of time, creating many opportunities to trigger bites. The ORC significantly raises the potential for contact with fish in shallow areas. If you retrieve it very slowly, it can perform as a topwater crank. In that situation, the GYRO BALANCER rhythmically strikes the body emitting a hard attack sound below the surface garnering attention from target fish. The ORC is a true shallow game revolutionary that features heightened shallow cover evasion performance and the ability to effectively draw out bites even when maintaining distance from cover. * The photograph is a prototype.</v>
       </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -5329,6 +5659,9 @@
       <c r="N112" t="str">
         <v>The i-JACK traces its lineage to the IT JACK, a legendary hand-carved wood plug created by Megabass founder, Yuki Ito. Building on this history, i-JACK overwhelms with a powerful, “screw drive” action, creating huge water-disturbance, a booming “knock,” and an intense flash to call predators from far and wide. An original Stingray Bill design and integrated Rudder Action Balancer System (R.A.B) deliver a twisting wake bait retrieve with a wide roll-axis, flashing the i-JACK’s exquisitely detailed sides with each turn. Further, the R.A.B. system, with its heavy metal ball and rudder-like metal plate on a free-swinging pivot pin, throws its considerable weight behind each turn to generate unprecedented rolling action and a surprisingly loud “knock” with each turn. The i-JACK’s outsized rolling screw-action and sound extend its effectiveness even into deeper waters, where its bold presence and lifelike detail will be sure to fool even the most discerning predators.</v>
       </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -5373,6 +5706,9 @@
       <c r="N113" t="str">
         <v>The BURNING SHAD is pushed into overdrive, maximizing the roll drive of the ORC’s compact body at all speeds. Marvelous super-fast rolling action like an engine at its limit is produced by the GYRO BALANCING LBO SYSTEM, which harnesses the essential principle of a self-righting doll to drive relentless action at all speeds. Previously, a fast retrieve was required to generate the rolling, flickering action of a lure like the ORC. However, by harnessing the GYRO system, the BURNING SHAD produces dynamic roll, displacement and flash at slower speeds where other lures may begin to falter. With rod tip low and a slow retrieve, the BURNING SHAD will crawl just beneath the surface, bulging water and inciting explosive chase bites. Speed up your retrieve and BURNING SHAD tracks true with ever-stronger flash and rolling water displacement. The GYRO system creates a hard, rhythmical “click” sound to appeal to inactive fish. Additionally, the BURNING SHAD exhibits dramatically improved avoidance ability due to its body shape and hook placement, allowing for close-cover cranking. * The photograph is a prototype.</v>
       </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -5417,6 +5753,9 @@
       <c r="N114" t="str">
         <v>i-LOUD showcases the same Rudder Action Balancer System (PAT.) of the i-JACK, housed in a new concept jointed wakebait/propbait designed by ITO ENGINEERING. The RAB System emits a resounding ‘knock’ as it throws its weight from side to side, giving off a strong sonic presence as it helps power the outsized action of i-LOUD’s jointed body. Rear prop adds another layer of lively sound, and leaves a bubble trace along the retrieve line. With a large profile, and even larger action and sound, i-LOUD represents an aggressive approach to activate the feeding modes of dormant monster bass, and trigger explosive bites. ※The photograph is a prototype.</v>
       </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -5461,6 +5800,9 @@
       <c r="N115" t="str">
         <v>PROP DARTER 80 (X-80 PD) is something like top-water version of TRICK DARTER. The prop which was invented (PAT.P) just for this bait, is truly unique not simply because it is asymmetric but because of its lively swimming sound and its ability to spit back. As for the body, the inside structure has been completely overhauled and redesigned for a new set of objectives. As a result it leans to left and right when retrieved. It looks like a snake's swimming track. PROP DARTER has a lip, which tries to dive. Yet it cannot dive. This struggle adds to PROP DARTER's unique bio-sound and the surface action you have never seen before.</v>
       </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -5505,6 +5847,9 @@
       <c r="N116" t="str">
         <v>From the creators of the VISION ONETEN, comes the ultimate winged bait. I-WING’s incredibly realistic body featuring super-lightweight duralumin wings is the result of hundreds of hours of hydrodynamic testing in tough fields. ･ During dead slow retrieves i-WING generates micro pitch waves, evoking a small school of fish that swarms to weakened bait. ･During high speed retrieves the body practically hovers over the water and demonstrates agile buzz-crawling despite its large size. The internal R.A.B. (Rudder Action Balancer System) activates in conjunction with the wings, generating turning actions, and allowing the jointed tail to gracefully tail walk and emit a delayed “knock” sound. It will stimulate and appeal to even far away targets. In conjunction with the wobblin’ roll action, the R.A.B. weight swings on a pivot from side to side like a pendulum. When the heavy weight hits the inside of each wall, a strong sound and shock wave is emitted, adding another layer of acoustic attraction. The uniquely layered waves emitted by the body movement, wings, jointed tail and R.A.B. pendulum balancer combine to intensely stimulate the feeding instinct of monsters. * The photograph is a prototype.</v>
       </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -5549,6 +5894,9 @@
       <c r="N117" t="str">
         <v>PROPDARTER106 is equipped with the nearly frictionless LBO II (PAT.) moving balancer system to achieve superior weight transfer and cast distance for a propeller-mounted lure. The LBO II’s ball-bearing shaft weight is synchronized to the roll axis of the lure’s action for enhanced output. The responsive and seamless roll action creates frequent enticing flutters, mimicking the rise and wake of baitfish. Depending on the retrieval speed, a variety of "3-way actions" are produced, showcasing an extraordinary feeding magic.</v>
       </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -5593,6 +5941,9 @@
       <c r="N118" t="str">
         <v>Following in the footsteps of the i-Wing, ITO Engineering, with Yuki Ito at the helm, has finally released the top-secret i-WING FRY, designed under a veil of secrecy to catch even the cleverest fish on the first bite. In shallow areas normally attacked with crankbaits or spinnerbaits, simply reeling in the i-WING FRY will bring your target to the surface, with a stunning power that explodes through the water. Once it was deemed impossible for a winged lure to have a moving balancer, because of how the crawling action works, but ITO has successfully developed a proprietary format, available for the first time in this lure. By analyzing the “power points” and “action points” generated by the Linear Bearing Oscillator (LBO) of the moving balancer system, as it responds to a variety of likely actions, Yuki Ito has designed a brand-new hydrodynamic body especially for the i-WING FRY, so as to synchronize the movements of the central axis of the LBO and the rolling axis of the lure. The innovative design, which increases buoyancy in a manner reminiscent of a hovercraft, enters the lineage of unique simulated fish like the POP-X, brought to you exclusively by Megabass. In concert with the neodymium magnet, the shaft balancer of the LBO moves reflexively as the lure changes position, creating (1) “instant action,” (2) “optimal form after splashdown, to rapidly correct the LBO,” and (3) “instant magnetic anchoring.” In other words, the lure starts working the second it hits water, doing things no winged lure has done before, and exhibiting a stunning directability so that your target bites on the spot. The i-WING FRY responds instantly, even to the slightest control of the line slack. Always in motion, it draws the target in. Defying preconceptions of winged lures, and dismissing headwinds as irrelevant, the long-distance castability maximizes and amplifies productive areas like no lure of its class. On top of that, the tuned hydrodynamic body is equally in control on extremely slow retrieves and on faster retrieves liable to come tearing through the surface, demonstrating incredible stability. This is a lure that keeps on swimming, adapting to whitecaps and all manner of rough surface conditions. Simply reeling in the lure will catch plenty of fish, but shaking introduces wobble action and subtle undulation. Little twitches will produce the side-to side rotation or splash action seen with pencil bait.  If you're looking for a winged lure that has the finesse and impact on bite chance of worm lures, look no further than the i-WING FRY. * The photograph is a prototype.</v>
       </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -5637,6 +5988,9 @@
       <c r="N119" t="str">
         <v>Introducing the TRIPLE FRY, a new addition to the popular i-WING series that has taken bass fields across the world by storm. The tougher the conditions, the more TRIPLE FRY will showcase its mystical fish-catching performance. The super thin pair of baitfish wings possess a unique flexibility, making lifelike delicate and seductive waves with dead slow retrieves. The rolling dance of the main body combines with the jointed float tail and wings to create the illusion of panicked baitfish struggling at the surface in an enticing bait ball. The slower you reel it in, this unprecedented panic bait will trigger an increasingly powerful chain reaction of explosions on the water’s surface.</v>
       </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -5681,6 +6035,9 @@
       <c r="N120" t="str">
         <v>この動きに抗えるヌシは、いるでしょうか？　ガバリンは、従来フロッグの単調な誘いを完全に見切ったモンスターを相手に徹底テストして開発。独自のボディデザインにより、フローティングカバーのほんのわずか隙間、数十センチのオープンポケットでも、ガバリンはラインスラック・ワークやロッドワークに即応し、ピンポイントの鋭角なクイックターンやハイピッチ・ドッグウォークを披露。ガバリンのワイドな口角による絶妙な水噛みが水面を騒めかせ、重々しいサウンドとバブルを伴うダイブ＆スプラッシュを発生。 ３シーズンに及んだテストでは、叩き抜かれたフローティングカバーのポンド群から、ヌシレベルのビッグフィッシュたちをバイトさせる度、アップデートを重ねてきました。 多彩なロッドワークで挑むテクニカルなトップウォータープラッガーに向けて贈る、新感覚のアクティブアクションフロッグ。ガバリンならば、ヌシは呑み込みます。</v>
       </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -5725,6 +6082,9 @@
       <c r="N121" t="str">
         <v>The BIG GABOT is a larger, heavy-duty model of the PONY GABOT developed based on the strong requests of the US pro staff. While preserving the responsive CATAMARAN MOUTH of the PONY GABOT which allows for splash-walking action, the BIG GABOT features upgrades to various parts. In order to push the center of gravity farther back compared to the original GABOT, the skirt has been positioned away from the body. A new hook groove has been added to the connection point of the hook and body to limit unwanted hook slide. With the increase in size, the internal structure has also been redesigned and reinforced for durability. The BIG GABOT’s hook is custom-built for the new frog, increasing hook-penetration and reducing lost fish throughout the fight. With increased total weight, easy casting with thick PE line is possible. The larger body also allows for more powerful water displacement in heavy matted cover, dramatically increasing the appeal of the BIG GABOT in the eyes of big bass. The BIG GABOT has a striking presence that surpasses the original, stimulating the fighting instinct of big bass. * The photograph is a prototype.</v>
       </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -5769,6 +6129,9 @@
       <c r="N122" t="str">
         <v>“KING OF JERKBAIT”として世界で活躍するビジョン・ワンテンシリーズ。他のジャークベイトではオーバーダイブしがちだった水面直下のシャローレンジを完全攻略する、競技専用スペシャルモデルが、ONETEN-SRとONETEN-SSRです。 ［最大潜行深度1.0ｍ]を徹底的にキープする[SR]は、超広域のシャローエリアから、従来ジャークベイトの展開レンジに反応しなかったバスのストライクチャンスを大幅に拡大。 さらなる表層レンジを展開する、［最大先行深度0.7m以浅］の徹底キープを実現したONETEN-SSRは、これまでソフトジャークベイトやトップウォーターベイトに頼らざるを得なかった、ボトムにウィードやストラクチャーが存在する広大なスーパーシャローエリアをジャークベイティングによるホットスポットに変えてしまいます。 SRとSSRは、リールハンドルのノブに指をかけた瞬間から、着水と同時にアクションが即立ち上がり、着水地点のバイトも即時誘発。オリジナル・ワンテンよりも左右へのダート距離を拡大化し、ロッドアクションのワンストロークで移動可能な水中のダート距離は、ワンテン随一のものとなっています。 ロッドを立てて操作する、ラインスラックの瞬時の緩急によるショートストローク・トウィッチでは、水面へと踊りながら上昇する「ライズアップ軌道」をイレギュラーに披露。腹部をひるがえす「ロール・フラッタリング」、「フラッタリング＆ダート」など、多彩なアクロバティック・アクションを頻発させます。 SR、SSR共に、特殊フッ素コーティングにより貫通力を極限まで高め、いかなる襲撃角度からのショートバイトやラフアタックでも即掛けする、メガバス独自の最新デザインによるNEWアウトバーブフックを搭載。ハイスコアゲームを追求するトーナメントプロフェッショナルに向けて製作する、純競技仕様のスペシャルファンクションモデルです。</v>
       </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -5813,6 +6176,9 @@
       <c r="N123" t="str">
         <v>この動きに抗えるヌシは、いるでしょうか？　ガバリンは、従来フロッグの単調な誘いを完全に見切ったモンスターを相手に徹底テストして開発。独自のボディデザインにより、フローティングカバーのほんのわずか隙間、数十センチのオープンポケットでも、ガバリンはラインスラック・ワークやロッドワークに即応し、ピンポイントの鋭角なクイックターンやハイピッチ・ドッグウォークを披露。ガバリンのワイドな口角による絶妙な水噛みが水面を騒めかせ、重々しいサウンドとバブルを伴うダイブ＆スプラッシュを発生。 ３シーズンに及んだテストでは、叩き抜かれたフローティングカバーのポンド群から、ヌシレベルのビッグフィッシュたちをバイトさせる度、アップデートを重ねてきました。 多彩なロッドワークで挑むテクニカルなトップウォータープラッガーに向けて贈る、新感覚のアクティブアクションフロッグ。ガバリンならば、ヌシは呑み込みます。</v>
       </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -5857,6 +6223,9 @@
       <c r="N124" t="str">
         <v>The BATRA-X is the second joint project between Monster Kiss, led by Takuya Kozuka, and Megabass. The BATRA-X features innovative design elements and customizable functions that set it apart from past hollow frogs. The small yet high volume bullet-style body realizes nimble table turn actions and long distance castability. The Megabass original soft cup can be attached to the front of the body for rapid fire splash-crawling action and noisy sounds with a straight retrieve, something not possible with past frogs. The BATRA-X features a rumble tail and tail hook at the end of the penetration-type wire swivel that attract fish with sounds and vibration. This world’s first transformation hollow-body surface plug allows you to change out components based on situation and preference. * The photograph is a prototype</v>
       </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -5901,6 +6270,9 @@
       <c r="N125" t="str">
         <v>１９９０年代、USAトッププロたちからの熱い要望を受け、伊東由樹が米国トーナメントフィールドに向けて製作した「アイティオー・シャイナー」こそが、実は、名作ワンテンの原型と言われています。その、極めてナチュラルな「餌ライクな動き」にエッジの立った「強波動」を融合させた、特異なハイアピール・ジャークベイトは、様々なレンジで広域を回遊するあらゆるバスを圧倒的に誘引。「活性を上げたいファーストコンタクトは、ITO-SHINNER」、「喰わせにゆくなら、ONETEN」。というのが、メガバスUSAチームのセオリーになっているほどです。 ITO-SHINNERのレスポンシブなハイピッチ・アクションは、激しい明滅効果と激しい振動で刺激をもたらし、圧倒的なフィーディングをメイク。広域エリアからグッドコンディションを手際よく探り当てるスピーディーなゲームマネジメントを展開します。 ファーストブレイクを回遊する個体を優位に直撃するITO-SHINNERの潜行深度は、1.8～2m。ITO-SHINNER[+1]は、2.6 ～2.8mレンジへのアジャスタビリティを高めています。稀代のイレギュラーダートと強波動でリアクションバイトを多発させる、ジャークマスター御用達の普遍的ミノーです。</v>
       </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -5945,6 +6317,9 @@
       <c r="N126" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -5989,6 +6364,9 @@
       <c r="N127" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -6033,6 +6411,9 @@
       <c r="N128" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -6077,6 +6458,9 @@
       <c r="N129" t="str">
         <v>LATES is a real stick roller bait which furiously rolls directly under water, releasing a natural impact targeting the lower range. The flickering created by the furious roll is exactly like a school of bait fishes migrating. At situations where the water surface is disturbed by the wind, it will further release the flickering impact appealing to the targets at the lower range. It is an extreme surface minnow “floating up and capturing” the migrating monsters. The use is simple. All you need to do is to retrieve at the speed between slow and medium speed. Furthermore “rise up &amp; fall” created by decreasing the retrieve speed at times, and the “hovering” which keeps one certain range while rolling will trigger reaction bites. Slow retrieve while using high gear installed reel will help make these operations with ease. Furthermore at top water games, slapping action made by twitching is effective. The instant slide action while fluttering will imitate a real panic bait. Roller bait-LATES will awaken the fish eaters aware of the upper layer. Please check out the power of this special minnow deeply pursuing the surface minnow game.</v>
       </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -6121,6 +6505,9 @@
       <c r="N130" t="str">
         <v>The high impact jerkbait KANATA AYU was designed to target fish that are keyed in on larger bait. With a streamlined, slender body, KANATA keeps resistance to a minimum. This allows for a fast, action-packed retrieve that will not put undue stress on angler’s wrists and forearms, even with a Medium Heavy setup. Sharp rod work fuels energetic darting action. Straight retrieve shows off a high-pitch rolling action with flashing visual appeal. Aerodynamic form and custom-fitted Megabass original Tungsten Triple Oscillating moving balancer system(PAT.) powers effortlessly long casts, allowing KANATA to target those clever monster fish from long range. KANATA AYU brings a new size and sensation to the jerkbait game. ※The photograph is a prototype.</v>
       </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -6165,6 +6552,9 @@
       <c r="N131" t="str">
         <v>The high performance ITO-SHINER was developed for top anglers like Aaron Martens and Edwin Evers for top-level US tournaments. To commemorate the ITO-SHINER’s release in America, it will also undergo a limited release in Japan. The ultimate life-like movements and unprecedented stimulating waves generated by this highly appealing jerk bait have the overwhelming power to round up bass scattered across a wide area. Using its robust body height compared to that of a slim minnow, it shows dramatically increased flashing performance, in addition to a fluttering tail-motion that is an extremely alluring target. The settings of the ITO-SHINER help to realize high-speed fishing, and will excel as a search bait in high-pressure tournament situations. The swimming depth is set to 1.8~2.0 meters (~6ft.), perfectly targeting the sweet spot for bass. With its wide, side to side darting it triggers reaction bites with amazing consistency.</v>
       </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -6209,6 +6599,9 @@
       <c r="N132" t="str">
         <v>The ITO SHINER, which earned its reputation as a foundational jerkbait in the storied Megabass arsenal, is now available as a Super Shallow Runner (SSR) to attack the 0-0.5m range. ITO SHINER SSR is a super shallow minnow that generates a hard-rolling and flashing action to call to predators cruising the jungle of vegetation just beneath the surface. The diving depth of the SSR is 1-2ft depending upon line type and diameter, making it an extremely effective competition search bait in and around weed areas. The unique wide-bend bill helps generate larger and more dynamic water displacement, challenging the subtler action so often associated with shallow offerings. Primarily designed for a straight retrieve, the SSR also is capable of darting action with intermittent jerks, leaping forward and laterally with pronounced roll and flash. Finely tuned hydrodynamics and internal balancer enable the SSR to stick to a tight, shallow range, triggering strikes from the shadows. The triple tungsten moving balancer system delivers supercharged casts, even against strong winds gusting across the flats. The ITO SHINER SSR is a competition-spec offering designed to dominate the shallow range with overwhelming flash and appeal.</v>
       </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -6253,6 +6646,9 @@
       <c r="N133" t="str">
         <v>KANATA+1 (Plus One) is a roll diving model with a maximum diving depth of 3.2m, 1m deeper than the original KANATA’s diving depth. Like the original, despite its big size (160mm) and 1.1/8oz weight, the +1 has surprisingly light retrieve resistance, enabling high-tempo searches with F5 (Medium Heavy) class rods. The KANATA’s high pitch roll action produces an extremely natural and tight action that is not found in other large body jerkbaits, as well as a flickering effect that spreads over a wide expanse. The ITO Tungsten Triple Oscillating System (PAT.) built into the lure’s slim, flat-sided form allows for impressive cast distance, even in headwinds. The high-impact minnow KANATA+1 has an overwhelming presence combined with a natural swimming action, a contrast that stimulates the predatory instinct of target fish at greater depths and distances.</v>
       </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -6297,6 +6693,9 @@
       <c r="N134" t="str">
         <v>The long-awaited second installment of the IxI series has arrived: I×I FURIOUS. Imae and Ito once again inspired each other to new heights, creating a high-speed subsurface crank that replicates the hair-trigger bite reaction of forage fleeing at breakneck speeds. To deliver truly highspeed performance in the challenging shallow subsurface range, Yuki Ito developed a patented water-through mechanism that directs water flow through the lure’s body to stabilize depth range and action at the upper limit of retrieve speeds. FURIOUS's patented design channels water through a head intake into an inner chamber that discharges flow via two downward ducts hidden in the lure’s gills. As retrieve speeds increase, the rate of water flow and pressure both increase in tandem, adding dynamic stability to dominate a new super-shallow range. With high-speed retrieves, this ducted water system keeps FURIOUS locked in a specific depth range to challenge those predators who have long ruled the shallows. FURIOUS is equipped with a Micro LBO (PAT.) moving-balancer system, powering outsized cast distance and displaying the superb balance to deliver stunningly high-pitched action and strobing flash. The fact that a lure of such diminutive size can achieve such long-distance castability, stability at speed and breathtaking action is truly a FURIOUS achievement. IxI will bring the shallow high-speed cranking game to another dimension. ■MODEL 1.5 ・Versatile shallow runner with a maximum diving depth of 1.5m. ・High-pitch flash and rolling-drive action with otherworldly stability at high speeds. ・ Ultra-tight action doesn’t miss a beat, even with bottom contact. Swim through tight riprap with dexterity to take the fight to the shallow range.</v>
       </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -6341,6 +6740,9 @@
       <c r="N135" t="str">
         <v>The long-awaited second installment of the IxI series has arrived: I×I FURIOUS. Imae and Ito once again inspired each other to new heights, creating a high-speed subsurface crank that replicates the hair-trigger bite reaction of forage fleeing at breakneck speeds. To deliver truly highspeed performance in the challenging shallow subsurface range, Yuki Ito developed a patented water-through mechanism that directs water flow through the lure’s body to stabilize depth range and action at the upper limit of retrieve speeds. FURIOUS's patented design channels water through a head intake into an inner chamber that discharges flow via two downward ducts hidden in the lure’s gills. As retrieve speeds increase, the rate of water flow and pressure both increase in tandem, adding dynamic stability to dominate a new super-shallow range. With high-speed retrieves, this ducted water system keeps FURIOUS locked in a specific depth range to challenge those predators who have long ruled the shallows. FURIOUS is equipped with a Micro LBO (PAT.) moving-balancer system, powering outsized cast distance and displaying the superb balance to deliver stunningly high-pitched action and strobing flash. The fact that a lure of such diminutive size can achieve such long-distance castability, stability at speed and breathtaking action is truly a FURIOUS achievement. IxI will bring the shallow high-speed cranking game to another dimension. ■MODEL 0.5 ・Super shallow runner with a diving depth of up to 0.5m. ・High-pitch flash and tight roll action that generates outsized presence and overwhelming responsiveness. ・ Targets the ultra-shallow range with a wide carpet-bombing approach and powerful high-speed action.</v>
       </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -6385,6 +6787,9 @@
       <c r="N136" t="str">
         <v>This next-generation shad made bass pro Katsutaka Imae exclaim “we’ve got something amazing here!” The TYPE-3 features an ability to trace a depth of 3.0m, but it can also perform exceptionally up to the 1.2m range. The design minimizes snags in the shallows and makes repeated hard contact with structures possible. Yuki Ito’s shad engineering has realized Katsutaka Imae’s “forward falling theory” at an extremely high level with this ultimate versatile shad featuring dazzling ultra-high pitch roll action. * The photograph is a prototype.</v>
       </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -6429,6 +6834,9 @@
       <c r="N137" t="str">
         <v>The I x I SHAD secret weapon A high pitch, high stability shad that allows for fast searches of the 1m shallow range, reliably turning bites into results. The high pitch screw-roll action allows for clear bottom contact thanks to the forward falling posture. This drastically increases the bite chances when contacting structure and the bottom. You can see the performance of this next-generation shad with its ability to draw out tough, clever fish with its speedy flashing. * The photograph is a prototype.</v>
       </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -6473,6 +6881,9 @@
       <c r="N138" t="str">
         <v>The goal of Katsutaka Imae and Yuki Ito was to land targets from the 4m+ range with a mere 57mm long shad body. The mounting position of the instant shifting balancer system Micro LBO (PAT.) allows for a super forward leaning posture impossible with normal ball weights. Ito moved the balancer head towards the intersection of the lip and body using a shaft with super small diameter bearings that made the extreme forward mounting design possible. With field tests using 6lb fluorocarbon line this big-lipped small shad demonstrated extremely long flight distances and succeeded in generating an astonishing diving vector. The outstanding fusion of aerodynamics and hydrodynamics have given the IxI SHAD the extreme performance needed to strike at deep targets. It is the ultimate solution for compactness, realism and performance.</v>
       </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -6517,6 +6928,9 @@
       <c r="N139" t="str">
         <v>The LIVE-X, one of Megabass’ original injection-molded lures of the early 90’s, is now reborn with the latest technology and supercharged performance. It's not a shad. It's not a minnow. And of course, it's not a simple crank. The state-of-the-art hydrodynamics with built-in LBO II(PAT.) produces ultra-fast flickering and live action from dead slow to ultra-high speed retrieves without fail. It is a bait with an overwhelmingly lifelike performance, turning neutral fish into reactive feeders when it matters most. This is the impact of a "live bait". The aerodynamic form, which Yuki Ito derived from countless hours of aerodynamic testing, improves casting distance by more than 30% in headwinds when compared to lures of equal volume. LIVE-X has succeeded in increasing the performance of carpet bombing a wider and more diverse range than ever before. In shallow water 2m deep or less, where conventional diving cranks have a hard time, LIVE-X is extremely dexterous, avoiding getting stuck and continuing to lure tough fish. The ability to feed cruising fish at depths of 3.5m or more is unique to the LIVE-X, which has been further refined to outperform the original. Switch on the feeding instinct of neutral fish that have not responded even to the ONETEN jerkbait. The second phase of the LIVING LEGEND project was started to catch discerning fish that are turned off from the overly aggressive action of many conventional cranks. This time, those of you who missed out on the explosive fishing experience with the original LIVE-X 30 years ago will experience it anew. Discover the true meaning of "LIVE-X". The legend continues.</v>
       </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -6561,6 +6975,9 @@
       <c r="N140" t="str">
         <v>The X-NANAHAN is a fusion of the ideals of Shinji Sato, one of Japan's foremost lure anglers, and the engineering of Yuki Ito, creator of dominant jerkbaits like the VISION ONETEN. In order to pursue superior castability in a small jerkbait minnow profile, the X-NANAHAN’s body is carved from a high-volume block, which results in a visually tight silhouette with greater precision. Air resistance has been thoroughly reduced to achieve overwhelming long-distance castability that surpasses the standard distance of 70mm-class minnows. The unique shape of the minnow, guided by the latest in hydrodynamics, provides excellent swimming response and intuitive handling. X-NANAHAN’s subtle action and flash reproduce the minute waves and flickering appeal of baitfish in an extremely realistic manner. Further, when twitched, X-NANAHAN bursts to life with a dynamic jerking and darting action that sets it apart from the school. The X-NANAHAN is a next-generation finesse minnow that pursues the "ultimate" in responsiveness. * The photograph is a prototype.</v>
       </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -6605,6 +7022,9 @@
       <c r="N141" t="str">
         <v>The X-NANAHAN is a fusion of the ideals of Shinji Sato, one of Japan's foremost lure anglers, and the engineering of Yuki Ito, creator of dominant jerkbaits like the VISION ONETEN. In order to pursue superior castability in a small jerkbait minnow profile, the X-NANAHAN’s body is carved from a high-volume block, which results in a visually tight silhouette with greater precision. Air resistance has been thoroughly reduced to achieve overwhelming long-distance castability that surpasses the standard distance of 70mm-class minnows. The unique shape of the minnow, guided by the latest in hydrodynamics, provides excellent swimming response and intuitive handling. X-NANAHAN’s subtle action and flash reproduce the minute waves and flickering appeal of baitfish in an extremely realistic manner. Further, when twitched, X-NANAHAN bursts to life with a dynamic jerking and darting action that sets it apart from the school. The X-NANAHAN is a next-generation finesse minnow that pursues the "ultimate" in responsiveness. * The photograph is a prototype.</v>
       </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -6649,6 +7069,9 @@
       <c r="N142" t="str">
         <v>The super minnow X-NANAHAN, which has generated unquestionable results from waters throughout Japan since its release, is now available in a +2 model for even deeper ranges. The NANAHAN+2’s 75mm compact body can now easily reach a range of 3m, bringing its irresistible appeal right under the noses of big bass tucked away in the depths. The NANAHAN’s rare combination of high-pitch roll action and rod-twitch trick darting induce difficult bites in the most important moments. The thoroughly tested aerobill enables a rocket-like cast with a stable flying posture, maximizing diving depth and productive water. The NANAHAN series now covers all key depth ranges, bringing an invaluable set of tools to the demanding angler.</v>
       </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -6693,6 +7116,9 @@
       <c r="N143" t="str">
         <v>The VISION95 "Q-GO" is a 3.74in. long minnow meant for shallow water. The swimming action of this bait is controlled by a completely new balancer system called the SHAFT BALANCER SYSTEM(PAT.) Instead of a moving, round balancer, the one in the Q-GO is shaped and fixed at the lowest point along the body. The result is an astounding new type of rolling action. Since the shaft weight acts as kind of reverse pendulum (think of it upside-down), the whole body swings with the shaft as a pivot. Unlike a moving balancer, the shaft balancer does not require guiding structures, so it frees up the space inside the bait. This allows the Q-GO to have very high buoyancy along with highly responsive movement. That is why the Q-GO is at home with any retrieval speed. Slow or fast, the Q-GO will get you the responses you have been waiting for.</v>
       </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -6737,6 +7163,9 @@
       <c r="N144" t="str">
         <v>"The VISION ONETEN Jr. packs the tournament-winning characteristics of the immensely successful VISION ONETEN jerk bait into a 98mm (3.85in) frame, generating more action per inch than its larger sibling. The VISION ONETEN Jr. has been carefully benchmarked against the VISION ONETEN, and has been redesigned from the ground up to improve upon the dynamic actions of the original, and expand the range of the jerk bait line. The ONETEN’s unique action has been distilled into the diminutive frame of the ONETEN Jr. Not only does it exhibit wide, erratic darts, but also demonstrates high pitch rolling and flashing during slow retrieves and wobble and roll agitation during fast retrieves. Finally, the dual-tungsten weights of the Megabass Multi way Moving Balancer System (PAT.) allow for incredible flight distance despite the lure’s small size.</v>
       </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -6781,6 +7210,9 @@
       <c r="N145" t="str">
         <v>Based on the ONETEN+1, a diving jerkbait responsible for overwhelming results in top U.S. tournaments, the VISION ONETEN+1 Jr. is a compact and agile performer engineered to target the toughest midrange waters—especially when matching smaller bait really counts. Aligning the uniquely contoured diving bill along the central axis of the body channels water along sculpted body lines, powering outsize, erratic darting action. Proven ONETEN design fools wary predators and generates striking flash, reaping massive dividends in midrange waters. Aerodynamic diving bill drastically reduces unnecessary air resistance, while the energy produced by the linear dual-tungsten weights of the Moving Balancer System allow for incredible flight distance even in rough conditions. * The photograph is a prototype</v>
       </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -6825,6 +7257,9 @@
       <c r="N146" t="str">
         <v>The VISION ONETEN+2 Jr. brings bite-sized jerkbait appeal to new depths, matching the tournament-winning 9-10ft range of the full-sized ONETEN+1. With a sculpted bill set along the lure’s central axis, the +2 Jr. achieves the kind of dynamic, razor-sharp darting action that earns the VISION ONETEN series a place in every serious jerkbait angler’s arsenal. At target depth, the +2 Jr. displays remarkably wide and responsive darting action. Its contoured body throwing off intense flash before coming to rest with a delicate shimmying appeal, provoking compulsive bites from deep cruisers. With an aerodynamic form and dual-tungsten weight transfer system, the ONETEN+2 Jr. outcasts expectations, bringing hard-fought trophies within reach.</v>
       </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -6869,6 +7304,9 @@
       <c r="N147" t="str">
         <v>The VISION ONETEN series, renowned as the “KING OF JERKBAITS” worldwide, is now available in a shallow-running model. With a maximum diving depth of 1m (3.2ft) on 14lb fluorocarbon, the ONETEN SR moves into action with the first angler input, effectively triggering strikes before the cast rings settle. Compared to the original ONETEN, the SR maintains a shallower running depth while expanding the lateral range of its side-to-side darting action, generating more action per jerk than even the original ONETEN. By holding the rod upright, varying line slack and applying short-stroke twitches between 11 and 1 o’clock, the ONETEN SR produces acrobatic actions such as a “rise-up darting” toward the surface, high flash “roll fluttering,” and endless combinations of “fluttering and darting.” The ONETEN SR is equipped with custom Megabass out-barb hooks. Premium 1X wire enhanced with a fluorine coating for superior penetration, these hooks generate instant hookups in the toughest situations. Designed for competitive angling, this high-performance lure is built to maximize your angling potential.</v>
       </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -6913,6 +7351,9 @@
       <c r="N148" t="str">
         <v>Introduced in the fall of 2000, the VISION ONETEN immediately captured the imagination of American anglers, setting a new standard for jerk baits. Designed by Yuki Ito for anglers in the United States, the ONETEN has emerged as the "go-to" jerk bait amongst touring pros, continuing to produce key fish and big checks from the Club level to the Bassmaster Classic. The profile, one-of-a-kind darting action, tungsten Multi-Way Moving Balancer System(PAT.) and hand-painted color patterns all contribute to the incredible fish-catching ability of the VISION ONETEN. The internal balancer system not only fuels the ONETEN's unparalleled action and huge flashes, but also allows it to cast like a bullet, far outpacing conventional jerk baits. This deadly package is finished off with three Megabass original sticky-sharp KATSUAGE OUT-BARB treble hooks, designed to increase hook-setting percentages when power-bait fishing. Crafted to generate results with a steady retrieve, traditional "jerk, jerk, pause," or trolling, the ONETEN responds to rod actions with unparalleled, life-like action. The one and only: VISION ONETEN.</v>
       </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -6957,6 +7398,9 @@
       <c r="N149" t="str">
         <v>The VISION ONETEN +1 is a mid-range jerk bait designed to increase the depth of the original ONETEN by up to 3ft. The ONETEN+1's medium bill is crafted to eliminate the traditional issues of high water-resistance, fatigue, and dead-end darting action often associated with long-bill minnows, all while preserving the legendary action of the original ONETEN. By positioning the line-eye close to the body, water resistance is reduced in order to make it easier to work the ONETEN+1 compared to conventional long bills. In addition, this angler-friendly design also channels more water towards the lure's forehead and along the carefully sculpted body, allowing for irresistible darting action with the slightest input. The ONETEN+1 is finished off with a dual-tungsten Multi-Way Moving Balancer System(PAT.) designed to produce superior long-distance castability even in tough conditions. The VISION ONETEN+1 : The legend just got deeper.</v>
       </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -7001,6 +7445,9 @@
       <c r="N150" t="str">
         <v>The ONETEN MAGNUM builds upon the overwhelming success of the VISION ONETEN in major tournaments around the world, featuring a redesigned fixed-balancer system, and a larger profile. Unlike the decentralized balancer-systems of many large jerk baits, the ONETEN MAGNUM has a specially tuned internal fixed weight balancer plate that allows for responsive action and swimming stability. The ONETEN MAGNUM dives to a depth of 2 feet (60cm), and with a slow retrieve, gives off an alluring wobble identical to a schooling baitfish. With a fast retrieve, the MAGNUM performs high pitch rolling actions; when stopped, the MAGNUM gives off a subtle wobble and floats up head first, just like a baitfish trying to escape a predator. With a larger profile, the ONETEN MAGNUM offers up a larger meal that will be sure to trigger bites from even the most cautious monsters.</v>
       </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -7045,6 +7492,9 @@
       <c r="N151" t="str">
         <v>The ONETEN LBO, which features the second-generation LBO II (PAT.) moving balancer system, has dramatically increased castability against headwinds, making stable, long approaches possible even under blustery conditions. Additionally, the balancer system—powered by 88 ball-bearings—significantly reduces friction during weight transfer, thereby transferring greater energy to the lure’s tail for greater casting distance. By extending the 110mm body of the original to a long-tailed 115mm, the center of gravity is able to shift even farther to the rear when casting, improving accuracy. The LBO II (PAT.) brings with it a lowered center of gravity along with a synchronized point of leverage and point of action that make instant, responsive actions possible from the moment you put your hand on the reel handle. The bearing weight, which is secured in optimal “ready” position by a neodymium magnetic field, generates sharp and highly regulated jerking actions, and the entirely new dimension of sharp, high pitch rolling action brings a heightened prominence to the ONETEN’s flashing. This special ONETEN, filled with ITO Engineering’s cutting-edge technologies, redefines the preexisting concept of jerkbaits. * The photograph is a prototype.</v>
       </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -7089,6 +7539,9 @@
       <c r="N152" t="str">
         <v>The ONETEN MAX LBO is a large, highly responsive jerkbait powered by the revolutionary LBOII moving balancer system. Thanks to the combination of a highly refined hydrodynamic body and the LBO’s virtually frictionless weight-transfer system, the ONETEN MAX LBO is able to eliminate the sluggishness seen in large jerkbaits of the past. The astonishingly responsive action, a credit to the work of ITO engineering, truly make it worthy of the position atop the vaunted ONETEN jerkbait series. The new patented moving balancer system, LBOII, is designed with micro ball bearings arranged in an infinite-loop configuration to drastically reduce friction of traditional moving balancers. The LBOII weight is magnetically held to the front position, and when unleashed during casting the inertial impact generates a powerful propulsion vector, dramatically increasing casting performance, even against headwinds. From the moment you begin your retrieve, the ONETEN MAX LBO’s weight leaps to the front position with astonishing speed, providing full lure action for the entirety of your cast. The overwhelmingly fast startup performance and incredibly dynamic jerking performance are thanks to the ONETEN MAX LBO’s action and power being on the same linear axis. * The photograph is a prototype.</v>
       </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -7133,6 +7586,9 @@
       <c r="N153" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth. * The photograph is a prototype.</v>
       </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -7177,6 +7633,9 @@
       <c r="N154" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth.</v>
       </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -7221,6 +7680,9 @@
       <c r="N155" t="str">
         <v>ワンテンR「Hi-FLOAT」は、ウィードやグラスの繁茂する高水温期において、圧巻の威力を発揮するワンテンRのシークレット・チューンドモデル。いわゆるウキウキパターンを広めた第一人者、佐藤信治が満を持して送り出すスペシャルメソッド対応モデルです。ウィードやグラス上のオープン域で2ジャークして浮かす、というのが王道メソッド。応用として、ショアのブッシュやリーズ、レイダウンなどのカバー周りや、桟橋や岩場などのストラクチャー周りにタイトにキャストし、やはり2ジャークして浮かす、といった使用方法が効果的。ワンテンR「Hi-FLOAT」だけの爆発力は、正直、秘密にしておきたかったことですが、多くのアングラーの笑顔がみたいプロガイド、佐藤信治だからこそリリースできたモデルです。</v>
       </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -7265,6 +7727,9 @@
       <c r="N156" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth.</v>
       </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -7309,6 +7774,9 @@
       <c r="N157" t="str">
         <v>The ONETEN R+3 joins the ONETEN R series. Inheriting the concept behind the ONETEN R, the R’s depth has finally reached 4m! Just imagine… the performance of the ONETEN R at a depth of 4m. The ONETEN R’s realistic baitfish darting and irregular actions are being brought to a range previously only occupied by big cranks. What’s noteworthy is that while having the ability to dive to such depths, the R+3 maintains light pulling resistance and with jerking can perform sharp darting in the deep zone that can trigger reaction bites at will. Years of Megabass hydrodynamics research and the unique actions of the ONETEN will now take the deepest range by storm. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth. * The photograph is a prototype.</v>
       </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -7353,6 +7821,9 @@
       <c r="N158" t="str">
         <v>The VISION ONETEN R Hi-FLOAT series now features a deep-diving +3 model that takes high buoyancy to new depths. The VISION ONETEN R+3 Hi-FLOAT is a guide-tuned model of the ONETEN R that excels when water temperatures rise, and submerged vegetation nears its peak. Taking shape from the summer jerkbait technique of legendary guide, Shinji Sato, the Hi-FLOAT is built to target the submerged weed beds of Lake Biwa with a jerk-jerk-rise approach. Whether targeting vegetation where the Hi-FLOAT setting is necessary to escape entanglement, or more traditional structure, the highly buoyant design adds a dynamic rising trigger for aggressive warm water feeders. The VISION ONETEN R+3 Hi-FLOAT has remained a Shinji Sato guide secret until now; experience the power of explosive buoyancy.</v>
       </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -7397,6 +7868,9 @@
       <c r="N159" t="str">
         <v>The X-48 Acrobat packs a bold punch much larger than its small frame would suggest. Designed to lure big fish with its finesse approach, the Acrobat springs into action with a twitch of the rod, delivering big action to trigger reaction bites. Built for situations when visible fish don’t commit, the Acrobat gives off a hi-pitch wobble and roll with straight retrieve, triggering bites from stubborn fish with well-timed rod action. Active moving balancer system drives unparalleled casting distance for its size, and guides life-like swimming action. The new generation of finesse minnow has arrived, and it packs a punch. ※The photograph is a prototype.</v>
       </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -7441,6 +7915,9 @@
       <c r="N160" t="str">
         <v>To give more sharpness to its movements during trick actions, the X-70's moving balancer design has been tuned to respond extremely sensitively to rod input such as twitches and jerks. During jerks, the X-70's unique flat body creates dynamic flashing that is easily mistaken for the flashing of live bait. There are many minnows that are focused on darting action, but the X-70 is probably the only one focused on getting bites with its mesmerizing flashing during normal retrieves as well.</v>
       </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -7485,6 +7962,9 @@
       <c r="N161" t="str">
         <v>The X-52 Acrobat packs a bold punch much larger than its small frame would suggest. Designed to lure big fish with its finesse approach, the Acrobat springs into action with a twitch of the rod, delivering big action to trigger reaction bites. Built for situations when visible fish don’t commit, the Acrobat gives off a hi-pitch wobble and roll with straight retrieve, triggering bites from stubborn fish with well-timed rod action. Active moving balancer system drives unparalleled casting distance for its size, and guides life-like swimming action. The new generation of finesse minnow has arrived, and it packs a punch. ※The photograph is a prototype.</v>
       </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -7529,6 +8009,9 @@
       <c r="N162" t="str">
         <v>Live-X REVENGE looks a lot like LEVIATHAN, but that is where resemblance stops. Slightly more slender than LEVIATHAN,REVENGE`s actions are controlled by a completely new balancer system. REVENGE`s diving range is between 6 and 10 feet, the most frequently used range, and shallower than LEVIATHAN. In a way, REVENGE is an easier and handier bait to use than LEVIATHAN. Also, REVENGE comes with MEGABASS original GUANIUM finish.</v>
       </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -7573,6 +8056,9 @@
       <c r="N163" t="str">
         <v>熾烈なUSAトーナメントシーンで勝ち抜くためのブランドン・パラニュークの知見と、世界各地のタフフィールドで膨大な実績を積み重ねてきた伊東由樹のエンジニアリングが融合し、誕生したシステム・ディープクランクシリーズがiPXです。 iPX-12は12ft(3.6m)を、iPX-16は16ft(4.8m)をメインレンジとし、それぞれ最大深度は15ft(4.5m)、18ft（5.4m)に到達。 内蔵された前後の2レーン内を各々フリーに移動し、潜行に応じてボディバランスを自発的に保持しようと多様な前転倒立型の重心ベクトルを適宜生み出す「フォワードロール重心移動システム」(PAT.P)は、限界まで前方向移動するフォワードバランシングが急角潜行を生み出し、プロダクティブゾーンを拡大。 リップ上にデザインした多角形ホールは、あらゆるダイビングアングルから効率よく水圧を確実に掴み、「フォワードロール重心移動システム」(PAT.P)と相まって、揺るぎ無いアクションスタビリティを生み出し続けます。 エッジの効いたウルトラ・ハイピッチアクションと強波動、体高のあるボディが発する激しい明滅は、広範囲にアピールしランカーのバイトを果敢に誘発。 ボトムコンタクトにおいて障害物回避からの復元力に優れ、持続的にボトムタッチし続けるディギングアクションと、長時間のデッドスロー＆ボトムトレースを実現。ライブシューティング／FFS（フォワード・フェイシング・ソナー）のトーナメントシーンにおいて釣り勝つことができる、究極のディープ・サーチベイトです。</v>
       </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -7617,6 +8103,9 @@
       <c r="N164" t="str">
         <v>熾烈なUSAトーナメントシーンで勝ち抜くためのブランドン・パラニュークの知見と、世界各地のタフフィールドで膨大な実績を積み重ねてきた伊東由樹のエンジニアリングが融合し、誕生したシステム・ディープクランクシリーズがiPXです。 iPX-12は12ft(3.6m)を、iPX-16は16ft(4.8m)をメインレンジとし、それぞれ最大深度は15ft(4.5m)、18ft（5.4m)に到達。 内蔵された前後の2レーン内を各々フリーに移動し、潜行に応じてボディバランスを自発的に保持しようと多様な前転倒立型の重心ベクトルを適宜生み出す「フォワードロール重心移動システム」(PAT.P)は、限界まで前方向移動するフォワードバランシングが急角潜行を生み出し、プロダクティブゾーンを拡大。 リップ上にデザインした多角形ホールは、あらゆるダイビングアングルから効率よく水圧を確実に掴み、「フォワードロール重心移動システム」(PAT.P)と相まって、揺るぎ無いアクションスタビリティを生み出し続けます。 エッジの効いたウルトラ・ハイピッチアクションと強波動、体高のあるボディが発する激しい明滅は、広範囲にアピールしランカーのバイトを果敢に誘発。 ボトムコンタクトにおいて障害物回避からの復元力に優れ、持続的にボトムタッチし続けるディギングアクションと、長時間のデッドスロー＆ボトムトレースを実現。ライブシューティング／FFS（フォワード・フェイシング・ソナー）のトーナメントシーンにおいて釣り勝つことができる、究極のディープ・サーチベイトです。</v>
       </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -7661,6 +8150,9 @@
       <c r="N165" t="str">
         <v>A well-kept secret of the Megabass Pro Team, the TRICK DARTER features the same legendary MULTI-WAY MOVING BALANCER SYSTEM (PAT.) as the VISION ONETEN, and is designed to move with an insane darting action that surpasses that of even the VISION ONETEN. With the addition of a fixed balancer in front, a spoonbill lip, and our infamous tungsten balancer system, the TRICK DARTER will truly "flee" erratically with short snaps of the rod, and draw reaction strikes from the most timid fish in the lake. Unlike conventional minnow–shaped jerk baits, the X-80 looks more like a shad or a shiner. Since baitfish with wider bodies flash more noticeably and are heartier meals for predators, the X-80 will attract larger fish. Furthermore, the X-80 swims with a distinct rolling wobble, an action that helps put our baits a world apart from the rest.</v>
       </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -7705,6 +8197,9 @@
       <c r="N166" t="str">
         <v>X-80Jr.は、ストレートリトリーブでは、オリジナルX-80を彷彿とさせるダイナミックなウォブンロール＆脱軌跡アクションを発生。ジャークやトゥイッチを併用しなくても、単純なストップ＆ゴーだけで、手軽にイレギュラーアクションを生み出します。トゥイッチを加えれば、シャッドプラグに切迫する強烈なフラッシングとキレのいいヒラ打ち瞬間ダートを披露。逃げ惑う小魚を演出し、スレきったモンスターにスイッチを入れます。X-80Jr.は、2連の重心移動ウエイトを搭載。安定した飛行姿勢とロングキャスタビリティを発揮します。従来のスモールサイズミノーの概念を覆す新次元のライトプラッキングを実現します。</v>
       </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -7749,6 +8244,9 @@
       <c r="N167" t="str">
         <v>LEVIATHAN is the flagship of Live-X series. It dose everything MARGAY and SMOLT does, but only more dynamically. If you want jerking actions in the mid-deep, LEVIATHAN is what you are looking for. Meticulously　detailed, LEVIATHAN showcases Yuki Ito? talent as a hand carver. LEVIATHAN can be used as a regular jerkbait. However, we suggest that you spend enough time to get to know what this bait is capable of doing.</v>
       </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -7793,6 +8291,9 @@
       <c r="N168" t="str">
         <v>I X I BLOWLY, is the ultimate shallow assault crankbait and third creation from the I×I project born from the combined insight of Katsutaka Imae and Yuki Ito. Equipped with Ito’s signature hydrodynamic theory (PAT.P) deployed in the FURIOUS series, BLOWLY features a fat-bodied profile that stirs the super-shallow zone with an fever-pitch retrieve action. This is no ordinary crank—it’s a veritable shockwave generator, designed to rattle the instincts of bass lurking anywhere near the retrieve line, forcing reaction bites from even the most indifferent feeders. At any retrieve speed, the I×I BLOWLY delivers a high-frequency pitch that outdoes even classic balsa crankbaits. Its distinct performance stems from the fusion of two critical elements: • Expanded frontal surface area that enhances visual and vibrational presence • Patented water-through structural design that amplifies action and hydrodynamic control Though it runs in the super-shallow range, BLOWLY provokes aggressive chase bites from bass rising out of deeper zones or approaching from lateral angles in open water. The result is a nonstop, high-alert game, where strikes come from every direction—vertical or horizontal—without warning.</v>
       </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -7837,6 +8338,9 @@
       <c r="N169" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -7881,6 +8385,9 @@
       <c r="N170" t="str">
         <v>When first designing the original GRIFFON crankbait in the late 1990’s, Yuki Ito sought a functionally comfortable form with an outsized impact. The result was a compact crankbait that quickly built a storied legacy around the world. This winning formula has given rise to a constantly evolving character that is compact, pinball-shaped, and mischievously productive—enter the third-generation GRIFFON. Enhanced hydrodynamics and a re-tuned internal structure dial up the GRIFFON’s relentlessly dynamic pinball-deflection action, delivering a larger-than-life reaction bite when it matters most. Its ability to quickly recover from frantic deflections is faithfully inherited from its forefathers and further refined. In the waters that so often feature in challenging tournaments, the GRIFFON has confidently demonstrated its outsized fishing performance. The only thing that can surpass a GRIFFON is, indeed, a GRIFFON. Discover your outperformance today.</v>
       </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -7925,6 +8432,9 @@
       <c r="N171" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -7969,6 +8479,9 @@
       <c r="N172" t="str">
         <v>When first designing the original GRIFFON crankbait in the late 1990’s, Yuki Ito sought a functionally comfortable form with an outsized impact. The result was a compact crankbait that quickly built a storied legacy around the world. This winning formula has given rise to a constantly evolving character that is compact, pinball-shaped, and mischievously productive—enter the third-generation GRIFFON. Enhanced hydrodynamics and a re-tuned internal structure dial up the GRIFFON’s relentlessly dynamic pinball-deflection action, delivering a larger-than-life reaction bite when it matters most. Its ability to quickly recover from frantic deflections is faithfully inherited from its forefathers and further refined. In the waters that so often feature in challenging tournaments, the GRIFFON has confidently demonstrated its outsized fishing performance. The only thing that can surpass a GRIFFON is, indeed, a GRIFFON. Discover your outperformance today.</v>
       </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -8013,6 +8526,9 @@
       <c r="N173" t="str">
         <v>The DEEP-X 100, which has been the long-established benchmark for diving crankbaits, is finally being equipped with the LBO II (Linear Bearing Oscillator II). With its surprisingly compact body, the DEEP-X can instantly attack at its maximum diving depth and displays an astonishing ability for obstacle evasion. No matter the type of contact, the LBO II combines with the cutting-edge hydrodynamic body to consistently maintain action and control, responding directly to the angler’s retrieve to trigger bites. With the LBO II and its new hydrodynamic form, the DEEP-X achieves a lag-less initial swimming response that allows for intuitive cranking. From ponds, to rivers, to large lakes, this versatile crankbait can easily hammer out results in any field. * The photograph is a prototype.</v>
       </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -8057,6 +8573,9 @@
       <c r="N174" t="str">
         <v>The DEEP-X 200 is one of Yuki Ito’s favorite lures in his 30+ year career as a lure designer. The DEEP-X 200 exhibits multifaceted performance and versatility for underwater games in many fields, excelling as a crankbait, a flatside shad, at times a diving minnow, and at times a vibration bait that searches a dedicated range. The uniquely evolved form of this DEEP-X 200 features further refinements from the previous model. In addition to the high pitch vibrations, the angle of the head amplifies its sharp, rolling action. It emits intense high pitch flashing and impactful vibrations. The astonishing flight distance of the slim-bodied 200, made possible by the LBO II, defies expectation. The ultra-long-distance casting performance easily outpaces a typical crankbait, demonstrating the far-reaching explosive performance of this extraordinary crankbait. * The photograph is a prototype.</v>
       </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -8101,6 +8620,9 @@
       <c r="N175" t="str">
         <v>The DEEP-X300 is a long anticipated deep-diving crank bait that adds dimension to the DEEP-X series. With a diving depth of 5m (almost 17 feet) and a much larger body size than the 200 and the 100, the DEEP-X300 will let you invade the depths where lunker fish routinely hide. As with its other DEEP-X brothers, the 300 is equipped with the MULTI-WAY MOVING BALANCER SYSTEM(PAT.). That means the 300 will dive almost vertically in order to maximize effective cranking distance and will also respond to every little twitch or jerk you send to the bait. All of the DEEP-X series crank baits will allow for the conventional bottom-digging method for creating those strike-inducing irregular darting actions, but what makes the DEEP-X series so unique is their mid-water twitch/jerk action, which appeals to the fish at any depth. The 300's colors are uniquely developed for the lower light environment of deeper water.</v>
       </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -8145,6 +8667,9 @@
       <c r="N176" t="str">
         <v>The DEEP-SIX was designed by Yuki Ito to trigger bites at depths of over 6 meters (20ft.), a largely uncharted territory among diving cranks. This range is made possible by a unique, super thin lip that slices through currents, and maintains the ideal balance required for a steep dive angle. Furthermore, the DEEP-SIX incorporates the renowned MULTI-WAY MOVING BALANCER SYSTEM(PAT.) of the DEEP-X series. During casts, the main weight moves to the rear, positioning DEEP-SIX tail-first to maximize aerodynamics and casting distance. When diving, the weight moves to the front of the lure to increase DEEP-SIX’s dive angle, which means you get down to target depth much faster. When DEEP-SIX reaches its maximum diving depth and contacts bottom, underwater structure, or is twitched, the main balancer is released, causing the weight to slide and increase action. If DEEP-SIX levels out at its maximum depth without contacting bottom, the main weight is released from the front and moves to the middle position. This changes the lure’s action, creating a realistic flash and aggressive high pitch rolling and wobbling that ignites the instincts of monsters in the deep. Until now, the super deep range has remained a safe haven for lunkers. Now Megabass has created a lure to venture into the deep, and dominate the monsters’ sanctuary.</v>
       </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -8189,6 +8714,9 @@
       <c r="N177" t="str">
         <v>The world-renowned DEEP-X series sports such exceptional performance that it is almost unfair to use it. Among that DEEP-X series, the DEEP-X150 has a particularly excellent record. Its tight, super-natural wobbling not only creates outstanding water displacement, but emits lively flashing that triggers the feeding instincts of neutral fish cruising in the mid range. The DEEP-X series' acrobatic actions upon contact with structures remains intact with 150's smaller body size, which only serves to make those actions sharper and more amplified. By hitting the lure against underwater slopes and objects on the bottom you can get reaction bites from even spooked bass under high pressure conditions.</v>
       </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -8233,6 +8761,9 @@
       <c r="N178" t="str">
         <v>With its extraordinary roll-axis and unique action, the FLAPSLAP has earned a niche reputation for its intensely powerful flashing appeal. The specially designed shaft balancer, placed ultra-low along the bottom of the body and slightly offset from the roll axis of the action, powers a pendulum action that enhances and stabilizes the lure’s outsized roll-axis and flash. This results in water agitation comparable to that of much bigger-bodied crankbait, supercharging the FLAPSLAP’s results in challenging conditions. With nearly instantaneous startup action from the first handle turn, its unique high-pitch screw drive action emits a striking strobe flash, evoking a fleeing shad. This otherworldly flat-sided bait contributed significantly to Edwin Evers’ victory at the 2016 BASSMASTER Classic.</v>
       </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -8277,6 +8808,9 @@
       <c r="N179" t="str">
         <v>With its extraordinary roll-axis and unique action, the FLAPSLAP has earned a niche reputation for its intensely powerful flashing appeal. The specially designed shaft balancer, placed ultra-low along the bottom of the body and slightly offset from the roll axis of the action, powers a pendulum action that enhances and stabilizes the lure’s outsized roll-axis and flash. This results in water agitation comparable to that of much bigger-bodied crankbait, supercharging the FLAPSLAP’s results in challenging conditions. With nearly instantaneous startup action from the first handle turn, its unique high-pitch screw drive action emits a striking strobe flash, evoking a fleeing shad. This otherworldly flat-sided bait contributed significantly to Edwin Evers’ victory at the 2016 BASSMASTER Classic.</v>
       </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -8321,6 +8855,9 @@
       <c r="N180" t="str">
         <v>The FLAPSLAP has received acclaim around the world for its phenomenal action and life-like detail, proving an indispensable addition to crankbait and jerkbait arsenals alike. Now equipped with the next-generation LBO II (PAT.) moving balancer system, the FLAPSLAP LBO rockets into the future with unrivaled casting distance. The nearly frictionless ball-bearing design of the LBO II (PAT.) balancer system leaps instantly to the tail section to power exceptional casting distance, then shifts to its front, low center-of-gravity position to deliver the storied action for which the FLAPSLAP is already well-known. Now tuned to suspend, the FLAPSLAP LBO can be burned, twitched, and paused above submerged weed beds and other target-rich environments, showing off its beautiful profile and elegant finishes to elicit bites from even the most discerning targets. Exquisite design, hydrodynamic form and balancer system combine to deliver not only the tight-wobbling action anglers expect from flat-sided crankbaits, but a difficult-to-achieve, wide-rolling action that sends enticing flashes throughout the water column. Additionally, much like the original, the FLAPSLAP LBO can be twitched to perform erratic darting rolls that displace water and display huge flashes to call in targets from distance, and trigger reaction bites from followers. * The photograph is a prototype.</v>
       </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -8365,6 +8902,9 @@
       <c r="N181" t="str">
         <v>メガバスファクトリーの熟練クラフツマンがハンドメイドによって製作するZ-CRANK。天然素材によるバルキーなハイフロートボディーは、バイブレーションプラグのような強波動・ハイピッチ・グラインドウォブリングを生み出し、マッディーカバーに潜伏する魚にしっかりとその存在をアピール。独特なフォルムと高強度・高弾性薄型コフィンリップによってスナッグレス性能を高め、シャローエリアのカバーに対するスタックを軽減。ブッシーなシャローやリップラップ、スタンプなどのカバーエリア付近を、ハイフロートボディが巧みにかわし、果敢なクランキングを展開します。</v>
       </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -8409,6 +8949,9 @@
       <c r="N182" t="str">
         <v>メガバスファクトリーの熟練クラフツマンがハンドメイドによって製作するZ-CRANK。天然素材によるバルキーなハイフロートボディーは、バイブレーションプラグのような強波動・ハイピッチ・グラインドウォブリングを生み出し、マッディーカバーに潜伏する魚にしっかりとその存在をアピール。独特なフォルムと高強度・高弾性薄型コフィンリップによってスナッグレス性能を高め、シャローエリアのカバーに対するスタックを軽減。ブッシーなシャローやリップラップ、スタンプなどのカバーエリア付近を、ハイフロートボディが巧みにかわし、果敢なクランキングを展開します。</v>
       </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -8453,6 +8996,9 @@
       <c r="N183" t="str">
         <v>The Z-2’s high pitch action is well-suited for mid-range areas and wide-open shallows. It features a “hard contact bill” designed to give clear feedback to the angler as the Z-2 relentlessly engages structures. The Z-2’s immediate posture recovery after contact is superb and its ability to trace tightly along the bottom is exceptional in its class. Previously, this degree of contact performance required a body volume twice as large in order to harness the effects of buoyancy, but the Z-2 has realized astonishing structure and bottom tracing with an unbelievably small size. The Z-2 is the ultimate searching master that allows the angler to clearly visualize the mid-range through the Z-2’s incessant contact. * The photograph is a prototype.</v>
       </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -8497,6 +9043,9 @@
       <c r="N184" t="str">
         <v>The Z-1 delivers “bulldog contact,” hitting bottom structure with relentless aggression to trigger frenzied reaction bites. The Z-1’s hard-hitting style sets it apart from the GRIFFON series’ finesse escape action. In the bitter winter, early spring, and during turnover periods, the Z-1 displays amazing stability that allows it to continuously engage riprap and shallow contours. Furious deflections never compromise the Z-1’s high pitch action during these situations, stimulating tough fish until they are compelled to bite. This next generation shallow runner is perfectly suited for attacking cruising fish around backwater sand bars, riprap, and shallow structures. * The photograph is a prototype.</v>
       </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -8541,6 +9090,9 @@
       <c r="N185" t="str">
         <v>The SONICSIDE is a competition-ready flatside crankbait born of the exacting demands of our Pro Staff. Built for a tight, high-pitch action to dominate cold water situations, the SONICSIDE displays unrivaled casting distance and stability during fast retrieves. The lip is shaped from tough, 1mm thick circuit board material reinforced with a molded support, making it an eerily responsive and durable option when targeting riprap and hard structure. Additionally, internal weights are fixed for a silent approach, and placed for optimal action, castability and stability at high speeds. This heavy-duty crankbait is built to out-cast and out-work the competition, dominating key targets in tough waters with its natural, high-pitch approach. * The photograph is a prototype.</v>
       </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -8585,6 +9137,9 @@
       <c r="N186" t="str">
         <v>The Super Z, renowned for its outsized castability and compact performance, is now available in a deeper diving Z3 version. Built to easily dominate deep water from wild ponds to big lakes, the Z3 can easily reach a maximum depth of 4m (13ft) on 8lb Fluorocarbon line. Powered by Megabass’ patented LBO II moving balancer system for superior casting distance, the Z3's hydrodynamic design exhibits an enticing tight-pitch action throughout the retrieve, staying true amidst current and bottom contact alike. Designed for easy handling with medium-light to medium rods in the F3 to F4 class, the Z3 is a compact deep crank for the next generation of discerning anglers. * The photograph is a prototype</v>
       </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -8629,6 +9184,9 @@
       <c r="N187" t="str">
         <v>Honed and refined over two years, the S-CRANK is a square bill crankbait featuring a patented design that generates a hard-hitting wobble action along with an erratic hunting, wandering retrieve. S-CRANK’s unique slalom action works even at high-speeds, wandering laterally off-course but always hunting back to center. Not only does this allow more effective coverage of wider areas, but the erratic wandering action triggers reaction bites much like deflections, increasing productivity in open water. Tight, enticing wobble draws inactive predators, while the sudden wandering escape action triggers decisive reaction bites. Square bill design and high buoyancy combine to reduce hang-ups to allow precise targeting of structure. * The photograph is a prototype.</v>
       </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -8673,6 +9231,9 @@
       <c r="N188" t="str">
         <v>BIG-M2.0 explores the 6ft range, a key depth throughout Lake Biwa that is a staple of renowned anglers like Shinji Sato. The BIG-M2.0 specializes in drawing bites from feeders lurking below the 6ft mark, sparking wild chases through open water and shallow cover alike. With a low center-of-gravity design, the BIG-M2.0 harnesses max-rotation rolling action to throw intense flash farther and wider, giving enticing glimpses of its exquisite flat-sided form to predators in the deep. Casts are powered by a triple balancer system, enabling long-distance ballistic approaches in weather conditions that would otherwise overpower conventional flat-sided offerings. Further, due to careful hydrodynamic consideration, the BIG-M exhibits surprisingly low pulling-resistance for its size, reducing the fatigue so often associated with larger lures. This allows anglers to comfortably deploy big bait techniques to target wider areas and new classes of fish, delivering maximum distance and performance with minimal effort. * The photograph is a prototype.</v>
       </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -8717,6 +9278,9 @@
       <c r="N189" t="str">
         <v>MPW「ハダラトラップ」70は、NEWコンセプト・トリックベイト。デッドスローリトリーブ中にも激しい明滅を「ランダム」に発生させ、ハイピッチ・ロールドライブを基調としながらも、クレバーフィッシュに見切られない、左右への「千鳥ダート軌道」でスイミング。 そんな複合的なエスケープアクションをオートマティックに披露してくれるHADARA TRAPは、直線軌道にて一定のリズムでアピールするバイブレーションプラグやスピナーベイトが見切られる状況、タフ化したメジャーエリアなどで大変有効です。 2つの超高比重・大径タングステンバランサーによる「タンデム重心移動システム」を搭載し、タフ化した広域エリアを効率よく攻め抜く圧巻の飛距離を叩き出します。 伊東由樹のハイドロダイナミクス理論によってデザインされた独特なボディは、広大なシャローエリアでも、一定の浅層レンジをキープしながらトリッキーに泳ぎ続けられる、ロングラン攻略を実現。 さらに、ハダラトラップ70は、リフト＆フォールでも威力を発揮。リフト時には、「ヒラウチバイブ」を発生し、フォール時にはボディを細かく震わせて沈下する「シミーフォール」を披露。マルチに仕掛けられる、特別なトラップベイトです。</v>
       </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -8761,6 +9325,9 @@
       <c r="N190" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -8805,6 +9372,9 @@
       <c r="N191" t="str">
         <v>The BIG-M is the evolutionary result of many years of Megabass big crankbaits. It leaves behind the fat bodied and long billed design of past deep cranks, assuming a flat side design with a short lip and low center of gravity. It realizes sharp, rolling action that generates an overwhelming flashing impact. This design is meant to trace the productive zone at a range of 3.5m (11-12ft). It has incredible castability that allows it to slice through headwinds, combined with low-resistance retrieve which allows it to be used all day long with minimal fatigue. The BIG-M has the power to draw in big bass lurking in the depths, all contained within a package full of extraordinarily refined engineering. Developed under the guidance of Lake Biwa’s “manager,” Shinji Sato, Yuki Ito and the development team came together to produce this next generation big crank. This giant killer crank will dramatically increase contact rates with big bass. * The photograph is a prototype.</v>
       </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -8849,6 +9419,9 @@
       <c r="N192" t="str">
         <v>The PROJECT LEGEND LD series concept places current designs for custom-tuning at the hands of Yuki Ito. The first lure to receive this treatment is the Knuckle 60, which has been fine-tuned with a circuit-board lip to tackle the tough waters of Japan. The thin, durable lip activates the KNUCKLE LD, making the bait even more responsive in the water, exhibiting a heightened high-pitch wobble &amp; roll action. Additionally, the front hook is equipped with lightweight heavy-duty swivel to increase hook up ratio and virtually eliminate lost fish. Internal weight balancer is secured from multiple angles to achieve a truly silent approach. Specially-tuned to catch that key fish in the toughest conditions. * The photograph is a prototype.</v>
       </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -8893,6 +9466,9 @@
       <c r="N193" t="str">
         <v>バイブレーションX ウルトラは、伊東独自のハイドロダイナミクスによるボディフォーミングが普遍的釣果をもたらしてきました。 新たに開発したウェイトパッケージングによりいっそう強化された超高速・ハイピッチロールドライブは、シャープかつ鋭いエッジの振動を生み、独自のプロペラ形状のボディが整流する際生み出す圧倒的な水流撹拌力と相まって、未知のランカーにアピール。 ボディ表面に波打つトーン変化を積極的に生み出し、視覚効果も最大限に引き出します。 バイブレーションXの爆釣伝説は不滅です。</v>
       </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -8937,6 +9513,9 @@
       <c r="N194" t="str">
         <v>The DYNA RESPONSE is a new concept metal vibe developed by Shinji Sato. The super-thin 0.6mm stainless plate cuts through water and features a carefully sculped weight design that generates powerful vibrations and quick start-up action. The weight’s hydrodynamic design powers a sharp, high pitch action and kicks into gear instantaneously whether employing lift &amp; fall or more traditional retrieves. The placement of the rear treble and innovative tinsel-tail detail significantly reduce line tangle on slack line and at the end of long casts, in addition to providing an enticingly new flicker-flash to the DYNA RESPONSE’s vibrating action. With its outsized flash, high-pitch vibration, tangle-fighting tinsel and lightning-quick startup action, the DYNA RESPONSE elevates the traditional metal vibe to new heights.</v>
       </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -8981,6 +9560,9 @@
       <c r="N195" t="str">
         <v>バイブレーションX スマトラは、伊東独自のハイドロダイナミクスによるボディフォーミングが普遍的釣果をもたらしてきました。 新たに開発したウェイトパッケージングによりいっそう強化された超高速・ハイピッチロールドライブは、シャープかつ鋭いエッジの振動を生み、独自のプロペラ形状のボディが整流する際生み出す圧倒的な水流撹拌力と相まって、未知のランカーにアピール。 ボディ表面に波打つトーン変化を積極的に生み出し、視覚効果も最大限に引き出します。 バイブレーションXの爆釣伝説は不滅です。</v>
       </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -9025,6 +9607,9 @@
       <c r="N196" t="str">
         <v>※The photograph is a prototype.</v>
       </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -9069,6 +9654,9 @@
       <c r="N197" t="str">
         <v>The concept behind the VIBRATION-X DYNA is high power + compact body!! The DYNA combines a bite-sized silhouette with violent rolling, ultra high-pitch vibration, overwhelming flight distance, and exceptional structure evasion performance. The internal weights are positioned to give the lowest possible center of gravity, increasing stability. The nose cup catches water flow, dramatically increasing responsiveness during actions. The exceptional initial swimming performance at the start of retrieves helps to increase the productive zone of the lure, allowing it to cover a wide area despite its small size. The DYNA is a little giant whose oversize vibrations and high-speed flashing puts past small vibes to shame. DYNA triggers the fighting instincts of neutral fish, drawing forth a new level of reaction bite. ※The photograph is a prototype.</v>
       </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -9113,6 +9701,9 @@
       <c r="N198" t="str">
         <v>1. Stop to Entice (Stop&amp;Go / Stay＆Jerk) The VIBRATION-X VATALION dramatically changes the strategy for targeting suspended bass. Twitching the lure results in dynamic 240-degree+ turns and intense flashing from the jointed body. In muddy water, the appeal of its broad, flat side far exceeds thin bodied jerkbaits and draws out many bites. The intermediate settings, the small “chip bill” that allows it to keep a consistent depth in shallows, the nose position line eye, the jointed slant tail—all of these features actively draw out those slow, reluctant fish in the shallows with the perfect “stop” approach. Whether it’s using stop &amp; go tactics to help evade the numerous structures in shallow areas or using stay &amp; jerk tactics immediately below the surface in weeded areas, this lure will help you get those suspended fish that spinnerbait and crankbait can’t touch. Watch it stimulate their activity level and land bite after bite. 2. Straight Retrieves in Shallows (Hi-Pitch - Straight Retrieve) During straight retrieves, it displays lifelike shimmering action, and the body segments contact each other to produce a sound that draws predators. It effectively draws bites from the shallow and midrange, covering a wide area. * The photograph is a prototype.</v>
       </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -9157,6 +9748,9 @@
       <c r="N199" t="str">
         <v>LEVEL SWIMMERは、より遠くのエリア、より深くのレンジ攻略を可能としたヘヴィーシンキング・プロップベイト。ただ巻くだけでバイトを得られる効率的な釣獲パフォーマンスは、高い集魚効果を兼ね備えた喰わせのフィネスベイトです。 一口サイズの「低重心・ヘヴィウェイテッドボディ」は、圧倒的なロングキャスタビリティを実現。狙いのレンジに速やかに到達し、広域のターゲットにアピールするサーチベイトとして威力を発揮します。 ミディアム～ディープレンジに到る、あらゆる水深で発揮される「超長距離・I字系スイム」＋「波動」＋「マイクロシルエット」は、従来のスピナーベイトやクランクベイトを見切ったタフな魚をバイトに持ち込みます。</v>
       </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -9201,6 +9795,9 @@
       <c r="N200" t="str">
         <v>The i-SLIDE 265R is a magnum glide bait that further refines the monster bass pedigree of the 262T, exhibiting decisive glides and sinuous slides to tempt the next generation of trophy catches. Featuring a crisp, responsive S-swimming slalom as its base action, the i-SLIDE 265R demonstrates tenacious stability even in rivers and backwater current. With a twitch or varied retrieve speed, it seamlessly performs underwater dog-walks and continuous turns, responding expertly to angler input. And with a reinforced internal wire harness and heavy-duty swiveling hook hangars, the 265R is built to overwhelm even the most brutal fighters, ensuring that hard-won bites land where they belong. Thanks to the R “Revolution Model” series engineering, even rough rod work translates into sharp slalom actions and quick, responsive slides—making advanced techniques accessible to anglers of all skill levels. The i-SLIDE “R” series promises dramatic encounters that will shatter your personal best.</v>
       </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -9245,6 +9842,9 @@
       <c r="N201" t="str">
         <v>R is for Revolution. The i-SLIDE has evolved, bringing its confidence-inspiring glide to fresh heights. The i-SLIDE 187 R’s refined design puts the power of sharp S-motion action in the hands of all anglers, regardless of big bait experience. With a redesigned tail and retuned internal weighting, the new R delivers with greater consistence. With a straight retrieve, ¾ turns of the handle, or twitching rod work, the i-SLIDE performs with confident ease, delivering a sinuous “S” swimming action or a wide left/right glide. The 187 R offers a direct feel that allows the angler to clearly perceive the glide’s action even when out of sight, increasing the odds of continued success. The i-SLIDE 187 R delivers a confident glide, bringing the power of big baits to anglers in search of the next trophy catch. 【Floating Model】 The responsive sliding action and agile slalom movement, which instantly responds to retrieve movements, trigger active feeding. The 187R is easily tuned for a wide range of situations and suspend/sink rates by adjusting the hook and ring sizes and/or attaching weights. 【Intermediate Model】 The suspend setting makes it appealing to dormant monsters that typically remain undiscovered. This model can be used for dead-sticking to imitate baits drifting unprotected with no action, sliding slalom action in the mid-range, and other technical presentations depending on the situation, and target’s reaction.</v>
       </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -9289,6 +9889,9 @@
       <c r="N202" t="str">
         <v>The i-BRAKE’s unique brake fins bring hard stopping power to suppress the lure’s speed, adding a new bite trigger to swimbait games. As retrieve speed slows down, the soft tail pitches erratically, fluttering and dancing, while the brake fins push water. The lure's sudden stopping power delivers a writhing action, which in turn triggers more chases and bites. The i-BRAKE realistically mimics the defenseless and sudden start/stop movements of live bait. During retrieval, the combination of brake fins that create turbulent water displacement and a soft paddle-tail that produces a natural swim sends fine vibration throughout the body, attracting even the most cautious targets. The subtle attraction of the i-BRAKE proves its worth in challenging conditions such as the post-spawn period and autumn turnover, where conventional approaches often struggle. This unique stopping ability delivers overwhelming bites when other approaches fall silent.</v>
       </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -9333,6 +9936,9 @@
       <c r="N203" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -9377,6 +9983,9 @@
       <c r="N204" t="str">
         <v>SPINE-X is a segmented subsurface swimbait equipped with an innovative user-controlled wire-through titanium spinal system to deliver dynamic action. Megabass’ LIVE-WIRED SYSTEM(PAT.P) leverages the shape-memory properties of titanium wire to add layers of customizable control to SPINE-X’s swimming movement. Included with three titanium “spines,” anglers can add multiple wires at a time for tighter “s” swimming and a faster recovery rate between segmented joints. By changing the number of titanium wires, anglers can adjust the suppleness and tension of SPINE-X to perfectly match angler input and target preferences. This not only enables situation-specific tuning but adds a dynamic element of internal tension to the swimbait’s movement, contributing to its lifelike appeal. Developed to target those exceedingly discerning trophy predators, SPINE-X swims with sinuous flash and sends twitches and jerks shuddering from tip to tail with unsurpassed realism.</v>
       </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -9421,6 +10030,9 @@
       <c r="N205" t="str">
         <v>GORHAM is a jointed waking and subsurface bait with a mysterious presence that awakens distant neutral targets. GORHAM’s articulated body is equipped with two synchronized LBO II(PAT.) systems in each section. This patented moving balancer system significantly improves flight posture and cast distance, while providing optimal swimming balance for immediate action startup. As a result, GORHAM’s attack range is dramatically increased, bringing far-off targets within easy reach. A dynamic, ultra-wide rolling wake action calls targets to GORHAM from greater distances, inspiring frenzied surface attacks. The unique RAMBLE TAIL provides an erratic disturbance that triggers the instincts of hesitant surface feeders. GORHAM opens the door to new topwater potential, triggering bites from otherwise dormant targets. SLOW RETRIEVE With a slow retrieve, GORHAM’s natural tail swing paired with the movement of its jointed body create an ultra-realistic, sinuous flashing wake action on the surface. FAST RETRIEVE With a fast retrieve, GORHAM dives into the shallow subsurface range, moving with a large flashing and rolling action that generates bulging water displacement, triggering the active feeding instincts of targets who lurk in search of a fleeing meal. Work in a twitch to incite bites from targets hot on the trail.</v>
       </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -9465,6 +10077,9 @@
       <c r="N206" t="str">
         <v>SuWITCH is equipped with the patented transforming lip system pioneered in the XPOD. This revolutionary system allows the angler to change the angle of the lip with a firm “click” to instantly switch between different target ranges and action profiles. “Su” means four. SuWITCH, or "four witches," has a diversely destructive power that joins four seemingly magical powers into a single lure. It is a new generation of multi-purpose swimbait that can switch up its diving range and action to suit the situation.Equipped with the world's first "2-step variable bill" one-touch lip adjustment mechanism for swimbaits, SuWITCH switches seamlessly between "wake mode" and "dive mode" at the angler’s behest. In each mode, the lure can be retrieved with either a straight retrieve or with the additional dynamism of twitching and jerking rod work. Thus, a single lure can produce actions with four different appealing characteristics.</v>
       </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -9509,6 +10124,9 @@
       <c r="N207" t="str">
         <v>The secret behind GARUDA’s overwhelming ability to attract fish and elicit bites rests in its powerful movement, painstaking detail, and the quality of its sound. Double-jointed construction and careful design drive smooth, sinuous action punctuated by the enticing “knock” of GARUDA’s joints coming in contact. Spec’d as a floating lure, GARUDA is also designed to attach teardrop sinkers to the underside of the lip to fine-tune for virtually any depth range. For fishing that involves bottom contact, GARUDA can be “back hook tuned” by removing the trebles, and attaching a single hook to the top of the lure. The back of the lure, where the groove for hook shank is located, features a neodymium magnet MAGHOLD (PAT.) system to keep the top hook in place. The GARUDA’s overwhelming destructive power is perfect for top range dead sticking and waking, mid-range retrieves, bottom contact, and anything a monster hunter could possibly desire from a big bait. GARUDA is built to bring you results beyond your imagination. * BOMBADA SNAP OVO Size: No.3 Equipped standard * The photograph is a prototype.</v>
       </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -9553,6 +10171,9 @@
       <c r="N208" t="str">
         <v>ジャマイカボアは、全米で人気のOROCHI BUZZをベースに、トーナメントユースに特化したスペックでデザイン。広域エリアを効率よくサーチでき、遭遇するあらゆるカヴァーをものともせずに引き倒すことができ、込み合うカヴァーから果敢にビッグウエイトを引き抜いてランディングに持ち込める、競技スペックのヘビーデューティーバズベイトです。 広域に散るバスを的確に訴求するマンタプロップの卓越した集魚効果もトップカテゴリーのプロたちが絶賛。広域シャローでバスの有無を確認したいとき、ジャマイカボアがシークレットベイトとして使われる理由のひとつです。 トーナメントでサーチしたい多様なシャローのカヴァーエリアからハイスコアを叩きだすための革新的スペックが満載。「勝つ」ために使うバズベイトが、ジャマイカボアです。</v>
       </c>
+      <c r="O208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -9597,6 +10218,9 @@
       <c r="N209" t="str">
         <v>ジャマイカボアは、全米で人気のOROCHI BUZZをベースに、トーナメントユースに特化したスペックでデザイン。広域エリアを効率よくサーチでき、遭遇するあらゆるカヴァーをものともせずに引き倒すことができ、込み合うカヴァーから果敢にビッグウエイトを引き抜いてランディングに持ち込める、競技スペックのヘビーデューティーバズベイトです。 広域に散るバスを的確に訴求するマンタプロップの卓越した集魚効果もトップカテゴリーのプロたちが絶賛。広域シャローでバスの有無を確認したいとき、ジャマイカボアがシークレットベイトとして使われる理由のひとつです。 トーナメントでサーチしたい多様なシャローのカヴァーエリアからハイスコアを叩きだすための革新的スペックが満載。「勝つ」ために使うバズベイトが、ジャマイカボアです。</v>
       </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -9641,6 +10265,9 @@
       <c r="N210" t="str">
         <v>マグドラフトフリースタイルにジャストフィットする専用ジグヘッド。マグドラフトの卓越した誘いのアクションを最適化させるバランスで設計されています。ラインアイ周りの容積を削ぎ落して底面を張り出すことによる徹底した低重心ヘッドは、極めて安定したスイミングアクションと驚異的な障害物回避性能を発揮。重量級ヘッドはオリジナル・マグドラフトよりもさらに深いレンジの攻略を可能とします。</v>
       </c>
+      <c r="O210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -9685,6 +10312,9 @@
       <c r="N211" t="str">
         <v>Crafted for victory in the toughest fields, the SV-3 draws inspiration from the legendary V-3, which earned its place in history as one of the pioneering baitfish-head spinnerbaits. Our “Super” V-3 spinnerbait is the embodiment of design and angling expertise, developed for top-level pros competing in the most challenging tournaments. This most recent masterpiece comes fully loaded with a number of innovative specs to earn its place in angler arsenals for years to come.</v>
       </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -9729,6 +10359,9 @@
       <c r="N212" t="str">
         <v>MEGABASS of America Inc.とメガバスUSAプロチームが一推しする、「オカシラ・スクリューヘッド」が米トーナメントのタフな状況をことごとく打開しています。翼形状が左右非対称に設計されたITOプロップ（ITO-Engineering製）を搭載し、デッドスローリトリーブ時やフォール時にイレギュラーな微波動とフラッシングを発生。バイトチャンスを積極的に生み出します。 また、アゴ下のウォータースルーレーンが、プロペラのスムーズな回転と適切なスイム姿勢、レンジキープ力をサポート。中層にサスペンドするニュートラルフィッシュをフィーディングモードに変えてしまう、マジカルなジグヘッドです。</v>
       </c>
+      <c r="O212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -9773,6 +10406,9 @@
       <c r="N213" t="str">
         <v>フィッシュヘッドジグの決定版、「オカシラヘッド」は、シェイキング時のアクション、フォール姿勢、スイム姿勢、トラブルの回避性、フックアップ率の向上を徹底追求したファンクショナルなベイトフェイス・ジグヘッド。 正面から見てデルタ形状のヘッドは、シェイキングではパタパタとハタめくヒラウチ効果を発揮。アゴ下に設けたウォータースルーレーンは優れた直進安定性とベイトフィッシュライクなスイム姿勢を生み出します。 また、エラ内部にオフセットされて深くソフトベイトが装着できるデザインによって、様々なソフトベイトをシームレスに装着できます。沈下時は、通常のジグヘッドとは異なり、「水平姿勢」を保持したスパイラルフォールを生み出します。装着するだけでソフトベイトの性能を一段と高められる、元祖フィッシュヘッドジグです。</v>
       </c>
+      <c r="O213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -9817,6 +10453,9 @@
       <c r="N214" t="str">
         <v>「オカシラヘッドHG」は、3/8oz.以上の専用設計を行ったミディアム・ヘヴィウエイテッド・ジグヘッド。求められる操作性、姿勢安定性、レンジキープ性能、障害物回避性能、フッキング性能等を高次元にまとめ上げました。低重心設計によるデルタ形状ヘッドは安定したスイム姿勢を保ち、適切な重量バランスによって操作性とレンジキープ力を高めています。また、ロングノーズフェイスがスタックを回避し、横方向に張り出したヘッド後端が根掛かりを高確率で回避。また、エラ部分はソフトベイトの接触面を隠し、深くインサートさせるオフセット形状により、様々な先端形状のソフトベイトをシームレスに装着できます。 ソフトベイトの潜在能力を一段と引き出すための、メガバス独自の高機能ジグヘッドです。</v>
       </c>
+      <c r="O214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -9861,6 +10500,9 @@
       <c r="N215" t="str">
         <v>The ROBIN BLADE is a bladed created with extreme usability in mind. It was designed with the goal of achieving high straight-running stability, as well as the range-keeping ability needed to continually  adjust to the feeding range of bass. Even when the tips of weeds cling to the lure, it still transmits the sharp, ultra high-pitch vibrations right to your fingertips with certainty. In order to combine these two features into a high-level lure, Megabass designed its own unique HEXA-V plate utilizing a vertical folding process. In addition, the original hook features double worm keepers that securely hold trailer worms, along with the overwhelming strength needed to combat the power of extreme monsters. From your initial approach to the heated fight itself, this lure will make your encounters with monster bass a sure thing.</v>
       </c>
+      <c r="O215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -9905,6 +10547,9 @@
       <c r="N216" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
+      <c r="O216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -9949,6 +10594,9 @@
       <c r="N217" t="str">
         <v>The UOZE SWIMMER is a new surefire concept bait proposed by Megabass. The realistic head features a nose section narrowed down to the limit, allowing it excel at slipping through obstacles such as rocks, branches, and weeds. The protrusions around the gills allow it to generate an optimal amount of water stirring, which combined with the low center of gravity design provide for stable range keeping ability. the tight blade attached to the titanium shape memory wire make wide ranged appeals through flashing and vibrations possible in areas of low visibility such as weed jungles. The flexible titanium shape memory wire does not interfere with hooking bites, and by allowing the blade to make contact with the bottom and structures before the body of the lure, the lure is prevented from diving too deep into obstacles, making delicate tracing and retrieves possible. The UOZE SWIMMER is equipped with a custom long shank wide gap hook. This foolproof design pierces through the jaws of monsters with accuracy, reliably landing them.</v>
       </c>
+      <c r="O217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -9993,6 +10641,9 @@
       <c r="N218" t="str">
         <v>「マキッパFFS」は、ブランドン・パラニュークをはじめ、メガバスUSAプロスタッフの熱烈な要望から生まれた、FFS（Forward Facing Sonar）専用の「勝つための」ブレードジグです。コンパクトでスリムなMAKIPPAボディに、定評あるメガバス独自のブレードフックシステム（PAT.P）を搭載。ターゲットに見切られずにブレードバイトを積極的に絡め獲る、競技志向のフィネス・ブレードジグです。 高比重ウエイト設計により、狙いのレンジへ素早く到達。軽いトゥイッチやシェイクなどの繊細な操作に即応し、ボディ＆ブレードが放つフラッシングは、ターゲットに対してひと口サイズながらも強烈な存在感を発揮。レンジキープリトリーブと意図的なラインシェイクを組み合わせることで、低活性時でもバイトを引き出します。 リトリーブスピードを上げれば、ブレードの高速回転が逃走するベイトを想起させる鮮烈な閃光と波動を発生。FFSでは、他のルアーでは口を使わなかったターゲットがMAKIPPA FFSにリアクションバイトしてしまう、一線を画した反応がご覧いただけます。</v>
       </c>
+      <c r="O218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -10037,6 +10688,9 @@
       <c r="N219" t="str">
         <v>METAL-Xは、独自の非対称フォルムとウエイトバランスによる水平フォールが、ベイトライクなナチュラルシルエットとフォールスピードを最適化。あらゆるターゲットに見切られる事なく捕食本能に火を点けます。 ボディマテリアルは軽比重の特殊合金を採用し、絶妙なフォールスピードでリアクションバイトを誘発、高確率でフッキングへ持ち込みます。 ディープエリアや低水温期はもちろん、ハイプレッシャーなタフコンディションや、リアクションでしか口を使わない状況において、他のルアーとは一線を画した釣果をもたらすシークレット・ベイトです。</v>
       </c>
+      <c r="O219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -10081,6 +10735,9 @@
       <c r="N220" t="str">
         <v>X-BLAZARは、佐藤信治が提唱する新機軸テールスピンジグ。 いかなる時も安定したスイムを生み出す特殊合金製の低重心ボディに加え、専用設計のSV-BLADEがエッジの立った鋭いバイブを発生させ、激しいストロボ明滅を広角に放ちます。 ブレードの回転角を変化させるセッティングが、メリハリの効いた明滅と、手元まで確実に伝達されるエッジの立ったバイブレーションを発揮。その際に生まれる強波動は、ディープフィッシュが抗えない驚異的な集魚力とフィーディングへの覚醒を生み出します。 また、メタルルアーで発生しがちなライン絡みのトラブルやフックトラブルを軽減化。ブレードバイトを確実にフッキングに持ち込むためのセッティングも追求しました。 お目当てのレンジに素早く到達し、レンジコントロール性能に優れたX-BLAZARは、ライブシューティングにおいても卓越したパフォーマンスを発揮します。</v>
       </c>
+      <c r="O220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -10125,6 +10782,9 @@
       <c r="N221" t="str">
         <v>タフフィッシュを微塵も迷わせず、果敢にバイトを引き出すフィーディングマジックスイマー「マグドラフト」をウェイテッドフックやジグヘッドなどを用いて使えるフリースタイル・ボディフォームを実現したのが、マグドラフトフリースタイルです。全米のトーナメントを席捲し続けているオリジナル・マグドラフト同様の釣獲力はお墨付き。込み合うカヴァーエリアにストレスなく、果敢なアプローチが出来る頼れる存在です。</v>
       </c>
+      <c r="O221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -10169,6 +10829,9 @@
       <c r="N222" t="str">
         <v>■ Designed to draw in predators with both slow and fast retrieves. ■ Megabass' exclusive MAGHOLD SYSTEM (PAT.P) and belly slit will secure hooks in place to minimize the visual presence of unnatural treble hooks.</v>
       </c>
+      <c r="O222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -10213,6 +10876,9 @@
       <c r="N223" t="str">
         <v>MAGDRAFT ハスレイバーは、「つねに動いてしまう」多くの可動セクションを持つ新次元のスイミング・マニピュレーターです。3連ボディ＆極薄ジョイントによる独自のボディシェイプは、わずかな水流でヒラヒラと艶めかしく動くライブフィンと相まって、タダ巻きだけで生命感溢れるリアルな泳ぎを披露。しなやかなアクションは、疑似生命体とでも呼ぶべき、ナチュラルベイトそのものを演出。水面直下のロングストローク・ジャークでは、本物のパニックベイトが逃げ惑うような瞬間移動的なエスケープアクションを披露。ストレートリトリーブにチェイスしつつも喰わなかったターゲットに対し、ジャークで捕食本能にスイッチを入れ、一撃でバイトに持ち込みます。 ストッピングの瞬間に発生する絶妙な揺らめき、リトリーブスピードを上げるたび引き起こされるパニックエスケープなど、単純動作を加えるだけで喰わせてしまう驚異の被捕食率が、HASU RAVERの凄いところ。 MAGHOLD(PAT.P)システムにより、フックはボディに磁着され、フックの存在をカモフラージュ。タフなターゲットに対する違和感をなくし、フレキシブルでナチュラルなアクションを披露。リザーバーのハスパターンをはじめ、落ち鮎、ウグイなど大型のベイトパターンにアジャストするHASU RAVERは、従来スイムベイトの誘いを見切ったターゲットに異次元の釣獲力をいかんなく発揮します。</v>
       </c>
+      <c r="O223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -10257,6 +10923,9 @@
       <c r="N224" t="str">
         <v>MAGDRAFT AYU TWITCHER is a shallow-swimming technical swimbait that adapts its action depending on retrieve speed and rod work. Megabass' proprietary MAGHOLD(PAT.P) system magnetizes the hook to the body, camouflaging its presence and reducing interference with the bait’s movement. The AYU TWITCHER's highly responsive design provides outstanding swimming performance in fields where currents interfere, such as rivers and backwaters. In slack-water games, it enables precise contact and actively triggers the reaction bite of clever fish.</v>
       </c>
+      <c r="O224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -10301,6 +10970,9 @@
       <c r="N225" t="str">
         <v>MAGDRAFT AYU TWITCHER is a shallow-swimming technical swimbait that adapts its action depending on retrieve speed and rod work. Megabass' proprietary MAGHOLD(PAT.P) system magnetizes the hook to the body, camouflaging its presence and reducing interference with the bait’s movement. The AYU TWITCHER's highly responsive design provides outstanding swimming performance in fields where currents interfere, such as rivers and backwaters. In slack-water games, it enables precise contact and actively triggers the reaction bite of clever fish.</v>
       </c>
+      <c r="O225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -10345,6 +11017,9 @@
       <c r="N226" t="str">
         <v>DARK SLEEPER was developed to target fish holding to bottom structure with overwhelming realism and paddle-tail action. With a top fin designed both to camouflage its hook, and gently deflect off of structure, DARK SLEEPER is able to hold tight to cover, and move through complex structure. Low center of gravity weight setting and bottom fins keep DARK SLEEPER upright as it moves through structure, for a naturally appealing approach.</v>
       </c>
+      <c r="O226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -10389,6 +11064,9 @@
       <c r="N227" t="str">
         <v>When deploying gill and crucian carp patterns, there are situations where regular swimbaits and fast-moving lures are not enough to tempt discerning predators. In such situations, the SLEEPER GILL’s unrivaled realism and enticing slow-retrieve ability conjure key bites. Featuring an adaptation of the dorsal fin weed guard pioneered by the DARK SLEEPER, the SLEEPER GILL can be sent where others fear to swim. Its jungle-crawling ability enables precision targeting of intricate laydowns, cover areas, weeds, standing timber, bottom structure, and more. Designed with a concealed top hook to trick veteran targets, the body features a hollow zone that compresses with the bite for sure hooksets. Low center of gravity design and pectoral fin balancers contribute to bottom-contact swimming stability, allowing for stealthy approaches through key structure areas.</v>
       </c>
+      <c r="O227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -10433,6 +11111,9 @@
       <c r="N228" t="str">
         <v>The long-awaited, bottom-scuttling stealth craw has arrived. SLEEPER CRAW harnesses the revolutionary performance of the SLEEPER series, bringing its hidden-hook design, enticing realism, and undeniable fish-catching ability to the staid category of conventional craw imitators. Unlike traditional offerings, the SLEEPER CRAW’s weight and hook are concealed within its body. This presents a stealthy package that lulls targets into natural, long-duration bites and reduces the chances of snagging, allowing anglers to move from dock skipping to laydowns to more traditional rockpiles with confidence. Constructed with a buoyant, highly durable material with a custom scent, the SLEEPER CRAW rests in the claws-up ready position and moves with uncanny realism. With an encased weight built to navigate treacherous rock formations without the unnatural sounds of lead or tungsten contact, the CRAW is perfectly suited to bottom-contact applications. Bring it to life with light line shake, a bottom-bumping drag, or vigorous hops; regardless of your technique, SLEEPER CRAW’s unique design will deliver fresh bites.</v>
       </c>
+      <c r="O228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -10477,6 +11158,9 @@
       <c r="N229" t="str">
         <v>米エリートシリーズを果敢に戦い抜くプロフェッショナルバスアングラー、木村建太の知見を具現化する、勝つためのベイト。それは、快適なフィールで使うことができ、多様なシーンに高次元でフィットする優れたエルゴノミクスを有しています。 木村建太のYAGOTは、一見すると、まるでトンボのヤゴですが、その秘めたるパフォーマンスを解き放つ時、未知のバイトを多発させる稀代のクリーチャーとなるのです。 伊東由樹の流体デザイニングから造形される特異なボディフォーミングは、優れたキャスタビリティと遊泳姿勢をもたらす機能的なボディ体積をもたらし、生命感あふれる繊細かつ緻密なレッグバイブレーションを発生。高い機能性の追求から整合された殊勝なボディは、見る角度によってはバルキーであり、スリムでもある独特なフォルムです。 放つフィッシングパフォーマンスは、まさに未知との遭遇レベル。競技に勝つためのハイスコアのバイトを果敢に誘発する、魔訶不思議なベイトです。</v>
       </c>
+      <c r="O229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -10521,6 +11205,9 @@
       <c r="N230" t="str">
         <v>ボトムの誘いにとどまらず、ジグストでも果敢にビッグバイトを連発させる驚異のリアクションマジック、SLAPHOGが覚醒。 米国B.A.S.S.ツアーを戦うチャレンジングなスペシャリスト、木村建太の熱い思いと知見、幾多のリアクションバイト伝説を築き上げたディープカップビーバーの開発者、伊東由樹のハイドロデザイニングが融合。圧倒的なリアクションバイトを引き出すSLAPHOGが生まれました。</v>
       </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -10565,6 +11252,9 @@
       <c r="N231" t="str">
         <v>The HAZE-ST is engineered to elevate strike responses from cruising, mid-column neutral fish—exhibiting refined action across the finesse spectrum from drop shots to mid-strolling. Designed for tournament pressure zones where career-defining bites must be coaxed from pinpoint areas, the HAZE-ST empowers anglers with the full spectrum of delicate, high-precision techniques. From a natural, near-motionless stick pose, it can erupt into vivid, pulsing vibrations and subtle micro-waves that elicit strikes from the most discerning predators. Its ultra-responsive behavior eliminates dead motion and delay, enabling instantaneous lifelike movement with even the lightest input. The HAZE-ST enhances the offensive power of finesse fishing, dramatically increasing bite chances from seasoned, pressure-weary lunkers that previously refused to react. HAZE-ST is born of Japan’s long history of finesse outperformance, delivering a purebred competition model built to win.</v>
       </c>
+      <c r="O231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -10609,6 +11299,9 @@
       <c r="N232" t="str">
         <v>タイニーエクスレイヤーは、その可愛いサイズに似合わず、ニュートラルなビッグフィッシュにスイッチを入れてくれる、ファイナルシークレットです。また、ダウンショットリグでは、余計なアクションを与えず、ただスローにたぐり寄せてくるだけでオートマティックに魚を引き出す、究極のデッドスティッキングベイトとして活躍。ビッグベイトで叩きぬかれたメジャーなポンドでは、タイニーエクスレイヤーは、スプーキーなビッグフィッシュを最終的に引き出してしまう強さを持っています。</v>
       </c>
+      <c r="O232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -10653,6 +11346,9 @@
       <c r="N233" t="str">
         <v>HAZEDONG's elegantly tapered tail moves with an enticing, undulating motion, making wary and sluggish fish bite. An excellent choice for a drop shot or Carolina Rig dragged along the bottom, where every little bump sends tremors down the length of the tail. HAZEDONG explodes into larger-than-life movement with rod work, putting on a mesmerizing, dynamic display at the end of your line. However, unlike many straight tail worms that are incapable of subtlety, HAZEDONG can also be brought to a deadly stillness by patient anglers lying in wait for discerning trophy-class targets.</v>
       </c>
+      <c r="O233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -10697,6 +11393,9 @@
       <c r="N234" t="str">
         <v>The super-thin shad tail catches the water even during dead-slow retrieves and delicate shaking, triggering targets with its natural vibrations. The slits in the belly allow the body to compress when bitten, increasing hookup rates. Adding an offset hook helps as well. Featuring layered material of different densities, the HAZEDONG SHAD is able to maintain excellent stability even when used with no sinker rigs. In addition, this layering process allows for incredibly natural two-tone color patterns.</v>
       </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -10741,6 +11440,9 @@
       <c r="N235" t="str">
         <v>The SPARK SHAD is designed with a keel-like underside—similar to a boat’s hull—to deliver exceptional stability and range-keeping ability, even during long retrieves. Its slim tail construction kicks into gear from a crawling retrieve, emitting alluring, sinuous waves that provide subtle appeal to coax bites from cautious predators. The addition of pectoral fins and a flat back further enhances the lure’s action, harnessing a touch of roll to add dynamism to its swim without rotating out of the ideal zone of stability. The SPARK SHAD is made for highly pressured monsters—those wary targets that have seen it all and spook easily. Its ultra-refined action mimics the behavior of neutral, unsuspecting baitfish with stunning realism. By deliberately limiting body roll beyond a controlled axis, the lure keeps the hook point aligned, greatly improving the hookup ratio during chase-and-strike scenarios. When you need to tempt the wisest predators in their home waters, SPARK SHAD delivers unmatched subtle swimming appeal.</v>
       </c>
+      <c r="O235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -10785,6 +11487,9 @@
       <c r="N236" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
+      <c r="O236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -10829,6 +11534,9 @@
       <c r="N237" t="str">
         <v>The BOTTLE SHRIMP is a hog-type worm which imitates freshwater prawns and crayfish, one of the main types of bait used around the world. When used for Texas rigs and jig trailers, the large power arms will push through the water, demanding the attention of target fish. With bottom contact, the inertia of the weighted arms will cause a shivering action to move from the tips of the power arms through the entire body, triggering bites. For no sinker rigs, nail rigs, and Carolina rigs, the power arm will swing left and right during the fall, creating a subtle waving motion. The slow and powerful wave motion created by the power arms and the quick, vivid trembling motion created by the legs will bring about a more complicated and realistic pulse from the whole body, captivating target fish.</v>
       </c>
+      <c r="O237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -10873,6 +11581,9 @@
       <c r="N238" t="str">
         <v>SLING SHADは、ミノー形態のフラットサイドシルエットと微水流にも鋭敏に反応する繊細なフォークテールを併せ持つ、ソフトスティックベイト。 腹部に高比重マテリアルを配した二層比重構造により、オフセットフックによるノーシンカーリグでも安定したスイミングと適切なフォール姿勢を保持。トゥイッチやジャークでは、ソフトジャークベイトとして艶めかしい左右へのダートアクションでターゲットを狂わせます。 低重心効果をもたらす二層比重構造は、ジグヘッド装着時のミドストで連続的なヒラウチ・ロールアクションを創出。ロールアクションと連動してテール部に微細な振動をもたらし、よりいっそうアピールを高めます。ブレードジグやワイヤーベイトのトレーラーとしても優れたパフォーマンスを発揮します。</v>
       </c>
+      <c r="O238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -10917,6 +11628,9 @@
       <c r="N239" t="str">
         <v>The TK TWISTER is a super multifunction worm capable of being used in any rig. With slight twitching, the tail wriggles from side to side as it performs a darting action. With no sinkers and Texas rigs, the delicate crustacean-like vibrations generated by the two tails and the unique presence that the body projects causes monsters to lock on. Quantity: TK TWISTER / 5 pieces , TK TWISTER Jr. / 8 pieces</v>
       </c>
+      <c r="O239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -10961,6 +11675,9 @@
       <c r="N240" t="str">
         <v>MEGABASS &amp; ITO ENGINEERING / OUTBARB HOOKは、従来フックに用いる鋼材のおよそ1.3倍の引張強度を実現した特殊鋼材を使用。ITO ENGINEERINGによる特殊規格の細軸設計が、従来の同軸径ルアーフック(淡水用)の強度と貫通力を遥かに凌駕する圧倒的な釣獲パフォーマンスを発揮。 特殊フッ素コートにより貫通性能を極限まで高め、いかなる角度からのショートバイトやラフアタックも即掛けする、極のオリジナル・トリプルフックです。</v>
       </c>
+      <c r="O240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -11005,6 +11722,9 @@
       <c r="N241" t="str">
         <v>メガバスルアーの性能を最大限に引き出す、純正のティンセルフック。 傷んだフックの交換用やフックチューンなどにご使用いただけます。 熟練の職人が一本一本丹精込めて仕上げます。</v>
       </c>
+      <c r="O241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -11049,6 +11769,9 @@
       <c r="N242" t="str">
         <v>メガバスオリジナルロングフェザーフック。 ルアーアクションの安定性を向上させ、揺らめくフェザーがフックの存在感を希薄化し、スプーキーな魚をバイトに持ち込みます。</v>
       </c>
+      <c r="O242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -11093,6 +11816,9 @@
       <c r="N243" t="str">
         <v>メガバスルアーの性能を最大限に引き出す、純正のティーザーフック。 傷んだフックの交換用や毛針チューンなどにご使用いただけます。 熟練の職人が一本一本丹精込めて仕上げます。</v>
       </c>
+      <c r="O243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -11137,6 +11863,9 @@
       <c r="N244" t="str">
         <v>TREBLE HOOK OUTBARB</v>
       </c>
+      <c r="O244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -11181,6 +11910,9 @@
       <c r="N245" t="str">
         <v>The BUDDHA HOOK was developed to handle those subtle bites often encountered in GREATHUNTING. Thin diameter wire drives razor-point home for sure and easy hooksets. Proprietary hook bend is designed to pin native Trout securely, while the light and supple hook design keeps damage to a minimum. * The photograph is a prototype.</v>
       </c>
+      <c r="O245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -11225,6 +11957,9 @@
       <c r="N246" t="str">
         <v>Megabass original wing parts kit for the customization of the i-WING135. Entice those monsters with a customized i-WING! *i-WING135 is sold separately. * The photograph is a prototype.</v>
       </c>
+      <c r="O246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -11269,6 +12004,9 @@
       <c r="N247" t="str">
         <v/>
       </c>
+      <c r="O247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -11313,6 +12051,9 @@
       <c r="N248" t="str">
         <v/>
       </c>
+      <c r="O248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -11357,6 +12098,9 @@
       <c r="N249" t="str">
         <v/>
       </c>
+      <c r="O249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -11401,6 +12145,9 @@
       <c r="N250" t="str">
         <v/>
       </c>
+      <c r="O250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -11445,6 +12192,9 @@
       <c r="N251" t="str">
         <v/>
       </c>
+      <c r="O251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -11489,6 +12239,9 @@
       <c r="N252" t="str">
         <v/>
       </c>
+      <c r="O252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -11533,6 +12286,9 @@
       <c r="N253" t="str">
         <v/>
       </c>
+      <c r="O253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -11577,6 +12333,9 @@
       <c r="N254" t="str">
         <v/>
       </c>
+      <c r="O254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -11621,6 +12380,9 @@
       <c r="N255" t="str">
         <v/>
       </c>
+      <c r="O255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -11665,6 +12427,9 @@
       <c r="N256" t="str">
         <v/>
       </c>
+      <c r="O256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -11709,6 +12474,9 @@
       <c r="N257" t="str">
         <v/>
       </c>
+      <c r="O257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -11753,6 +12521,9 @@
       <c r="N258" t="str">
         <v/>
       </c>
+      <c r="O258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -11797,6 +12568,9 @@
       <c r="N259" t="str">
         <v/>
       </c>
+      <c r="O259" t="str">
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -11841,6 +12615,9 @@
       <c r="N260" t="str">
         <v/>
       </c>
+      <c r="O260" t="str">
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -11885,6 +12662,9 @@
       <c r="N261" t="str">
         <v/>
       </c>
+      <c r="O261" t="str">
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -11929,6 +12709,9 @@
       <c r="N262" t="str">
         <v/>
       </c>
+      <c r="O262" t="str">
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -11973,6 +12756,9 @@
       <c r="N263" t="str">
         <v/>
       </c>
+      <c r="O263" t="str">
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -12017,6 +12803,9 @@
       <c r="N264" t="str">
         <v/>
       </c>
+      <c r="O264" t="str">
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -12061,6 +12850,9 @@
       <c r="N265" t="str">
         <v/>
       </c>
+      <c r="O265" t="str">
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -12105,6 +12897,9 @@
       <c r="N266" t="str">
         <v/>
       </c>
+      <c r="O266" t="str">
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -12149,6 +12944,9 @@
       <c r="N267" t="str">
         <v/>
       </c>
+      <c r="O267" t="str">
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -12193,6 +12991,9 @@
       <c r="N268" t="str">
         <v/>
       </c>
+      <c r="O268" t="str">
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -12237,6 +13038,9 @@
       <c r="N269" t="str">
         <v/>
       </c>
+      <c r="O269" t="str">
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -12281,6 +13085,9 @@
       <c r="N270" t="str">
         <v/>
       </c>
+      <c r="O270" t="str">
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -12325,6 +13132,9 @@
       <c r="N271" t="str">
         <v/>
       </c>
+      <c r="O271" t="str">
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -12369,6 +13179,9 @@
       <c r="N272" t="str">
         <v/>
       </c>
+      <c r="O272" t="str">
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -12413,6 +13226,9 @@
       <c r="N273" t="str">
         <v/>
       </c>
+      <c r="O273" t="str">
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -12457,6 +13273,9 @@
       <c r="N274" t="str">
         <v/>
       </c>
+      <c r="O274" t="str">
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -12501,6 +13320,9 @@
       <c r="N275" t="str">
         <v/>
       </c>
+      <c r="O275" t="str">
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -12545,6 +13367,9 @@
       <c r="N276" t="str">
         <v/>
       </c>
+      <c r="O276" t="str">
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -12589,6 +13414,9 @@
       <c r="N277" t="str">
         <v/>
       </c>
+      <c r="O277" t="str">
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -12633,6 +13461,9 @@
       <c r="N278" t="str">
         <v/>
       </c>
+      <c r="O278" t="str">
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -12677,6 +13508,9 @@
       <c r="N279" t="str">
         <v/>
       </c>
+      <c r="O279" t="str">
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -12721,6 +13555,9 @@
       <c r="N280" t="str">
         <v/>
       </c>
+      <c r="O280" t="str">
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -12765,6 +13602,9 @@
       <c r="N281" t="str">
         <v/>
       </c>
+      <c r="O281" t="str">
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -12809,6 +13649,9 @@
       <c r="N282" t="str">
         <v/>
       </c>
+      <c r="O282" t="str">
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -12853,6 +13696,9 @@
       <c r="N283" t="str">
         <v/>
       </c>
+      <c r="O283" t="str">
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -12897,6 +13743,9 @@
       <c r="N284" t="str">
         <v/>
       </c>
+      <c r="O284" t="str">
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -12941,6 +13790,9 @@
       <c r="N285" t="str">
         <v/>
       </c>
+      <c r="O285" t="str">
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -12985,6 +13837,9 @@
       <c r="N286" t="str">
         <v/>
       </c>
+      <c r="O286" t="str">
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -13029,6 +13884,9 @@
       <c r="N287" t="str">
         <v/>
       </c>
+      <c r="O287" t="str">
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -13073,6 +13931,9 @@
       <c r="N288" t="str">
         <v/>
       </c>
+      <c r="O288" t="str">
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -13117,6 +13978,9 @@
       <c r="N289" t="str">
         <v/>
       </c>
+      <c r="O289" t="str">
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -13161,6 +14025,9 @@
       <c r="N290" t="str">
         <v/>
       </c>
+      <c r="O290" t="str">
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -13205,6 +14072,9 @@
       <c r="N291" t="str">
         <v/>
       </c>
+      <c r="O291" t="str">
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -13249,6 +14119,9 @@
       <c r="N292" t="str">
         <v/>
       </c>
+      <c r="O292" t="str">
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -13293,6 +14166,9 @@
       <c r="N293" t="str">
         <v/>
       </c>
+      <c r="O293" t="str">
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -13337,6 +14213,9 @@
       <c r="N294" t="str">
         <v/>
       </c>
+      <c r="O294" t="str">
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -13381,6 +14260,9 @@
       <c r="N295" t="str">
         <v/>
       </c>
+      <c r="O295" t="str">
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -13425,6 +14307,9 @@
       <c r="N296" t="str">
         <v/>
       </c>
+      <c r="O296" t="str">
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -13469,6 +14354,9 @@
       <c r="N297" t="str">
         <v/>
       </c>
+      <c r="O297" t="str">
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -13513,6 +14401,9 @@
       <c r="N298" t="str">
         <v/>
       </c>
+      <c r="O298" t="str">
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -13557,6 +14448,9 @@
       <c r="N299" t="str">
         <v/>
       </c>
+      <c r="O299" t="str">
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -13601,6 +14495,9 @@
       <c r="N300" t="str">
         <v/>
       </c>
+      <c r="O300" t="str">
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -13645,6 +14542,9 @@
       <c r="N301" t="str">
         <v/>
       </c>
+      <c r="O301" t="str">
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -13689,6 +14589,9 @@
       <c r="N302" t="str">
         <v/>
       </c>
+      <c r="O302" t="str">
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -13733,6 +14636,9 @@
       <c r="N303" t="str">
         <v/>
       </c>
+      <c r="O303" t="str">
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -13777,6 +14683,9 @@
       <c r="N304" t="str">
         <v/>
       </c>
+      <c r="O304" t="str">
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -13821,6 +14730,9 @@
       <c r="N305" t="str">
         <v/>
       </c>
+      <c r="O305" t="str">
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -13865,6 +14777,9 @@
       <c r="N306" t="str">
         <v/>
       </c>
+      <c r="O306" t="str">
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -13909,6 +14824,9 @@
       <c r="N307" t="str">
         <v/>
       </c>
+      <c r="O307" t="str">
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -13953,6 +14871,9 @@
       <c r="N308" t="str">
         <v/>
       </c>
+      <c r="O308" t="str">
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -13997,6 +14918,9 @@
       <c r="N309" t="str">
         <v/>
       </c>
+      <c r="O309" t="str">
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -14041,6 +14965,9 @@
       <c r="N310" t="str">
         <v/>
       </c>
+      <c r="O310" t="str">
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -14085,6 +15012,9 @@
       <c r="N311" t="str">
         <v/>
       </c>
+      <c r="O311" t="str">
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -14129,6 +15059,9 @@
       <c r="N312" t="str">
         <v/>
       </c>
+      <c r="O312" t="str">
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -14173,6 +15106,9 @@
       <c r="N313" t="str">
         <v/>
       </c>
+      <c r="O313" t="str">
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -14217,6 +15153,9 @@
       <c r="N314" t="str">
         <v/>
       </c>
+      <c r="O314" t="str">
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -14261,6 +15200,9 @@
       <c r="N315" t="str">
         <v/>
       </c>
+      <c r="O315" t="str">
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -14305,6 +15247,9 @@
       <c r="N316" t="str">
         <v/>
       </c>
+      <c r="O316" t="str">
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -14349,6 +15294,9 @@
       <c r="N317" t="str">
         <v/>
       </c>
+      <c r="O317" t="str">
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -14393,6 +15341,9 @@
       <c r="N318" t="str">
         <v/>
       </c>
+      <c r="O318" t="str">
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -14437,6 +15388,9 @@
       <c r="N319" t="str">
         <v/>
       </c>
+      <c r="O319" t="str">
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -14481,6 +15435,9 @@
       <c r="N320" t="str">
         <v/>
       </c>
+      <c r="O320" t="str">
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -14525,6 +15482,9 @@
       <c r="N321" t="str">
         <v/>
       </c>
+      <c r="O321" t="str">
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -14569,6 +15529,9 @@
       <c r="N322" t="str">
         <v/>
       </c>
+      <c r="O322" t="str">
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -14613,6 +15576,9 @@
       <c r="N323" t="str">
         <v/>
       </c>
+      <c r="O323" t="str">
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -14657,6 +15623,9 @@
       <c r="N324" t="str">
         <v/>
       </c>
+      <c r="O324" t="str">
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -14701,6 +15670,9 @@
       <c r="N325" t="str">
         <v/>
       </c>
+      <c r="O325" t="str">
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -14745,6 +15717,9 @@
       <c r="N326" t="str">
         <v/>
       </c>
+      <c r="O326" t="str">
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -14789,6 +15764,9 @@
       <c r="N327" t="str">
         <v/>
       </c>
+      <c r="O327" t="str">
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -14833,6 +15811,9 @@
       <c r="N328" t="str">
         <v/>
       </c>
+      <c r="O328" t="str">
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -14877,6 +15858,9 @@
       <c r="N329" t="str">
         <v/>
       </c>
+      <c r="O329" t="str">
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -14921,6 +15905,9 @@
       <c r="N330" t="str">
         <v/>
       </c>
+      <c r="O330" t="str">
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -14965,6 +15952,9 @@
       <c r="N331" t="str">
         <v/>
       </c>
+      <c r="O331" t="str">
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -15009,6 +15999,9 @@
       <c r="N332" t="str">
         <v/>
       </c>
+      <c r="O332" t="str">
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -15053,6 +16046,9 @@
       <c r="N333" t="str">
         <v/>
       </c>
+      <c r="O333" t="str">
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -15097,6 +16093,9 @@
       <c r="N334" t="str">
         <v/>
       </c>
+      <c r="O334" t="str">
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -15141,6 +16140,9 @@
       <c r="N335" t="str">
         <v/>
       </c>
+      <c r="O335" t="str">
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -15185,6 +16187,9 @@
       <c r="N336" t="str">
         <v/>
       </c>
+      <c r="O336" t="str">
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -15229,6 +16234,9 @@
       <c r="N337" t="str">
         <v/>
       </c>
+      <c r="O337" t="str">
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -15273,6 +16281,9 @@
       <c r="N338" t="str">
         <v/>
       </c>
+      <c r="O338" t="str">
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -15317,6 +16328,9 @@
       <c r="N339" t="str">
         <v/>
       </c>
+      <c r="O339" t="str">
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -15361,6 +16375,9 @@
       <c r="N340" t="str">
         <v/>
       </c>
+      <c r="O340" t="str">
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -15405,6 +16422,9 @@
       <c r="N341" t="str">
         <v/>
       </c>
+      <c r="O341" t="str">
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -15449,6 +16469,9 @@
       <c r="N342" t="str">
         <v/>
       </c>
+      <c r="O342" t="str">
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -15493,6 +16516,9 @@
       <c r="N343" t="str">
         <v/>
       </c>
+      <c r="O343" t="str">
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -15537,6 +16563,9 @@
       <c r="N344" t="str">
         <v/>
       </c>
+      <c r="O344" t="str">
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -15581,6 +16610,9 @@
       <c r="N345" t="str">
         <v/>
       </c>
+      <c r="O345" t="str">
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -15625,6 +16657,9 @@
       <c r="N346" t="str">
         <v/>
       </c>
+      <c r="O346" t="str">
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -15669,6 +16704,9 @@
       <c r="N347" t="str">
         <v/>
       </c>
+      <c r="O347" t="str">
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -15713,6 +16751,9 @@
       <c r="N348" t="str">
         <v/>
       </c>
+      <c r="O348" t="str">
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -15757,6 +16798,9 @@
       <c r="N349" t="str">
         <v/>
       </c>
+      <c r="O349" t="str">
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -15801,6 +16845,9 @@
       <c r="N350" t="str">
         <v/>
       </c>
+      <c r="O350" t="str">
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -15845,6 +16892,9 @@
       <c r="N351" t="str">
         <v/>
       </c>
+      <c r="O351" t="str">
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -15889,6 +16939,9 @@
       <c r="N352" t="str">
         <v/>
       </c>
+      <c r="O352" t="str">
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -15933,6 +16986,9 @@
       <c r="N353" t="str">
         <v/>
       </c>
+      <c r="O353" t="str">
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -15977,6 +17033,9 @@
       <c r="N354" t="str">
         <v/>
       </c>
+      <c r="O354" t="str">
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -16021,6 +17080,9 @@
       <c r="N355" t="str">
         <v/>
       </c>
+      <c r="O355" t="str">
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -16065,6 +17127,9 @@
       <c r="N356" t="str">
         <v/>
       </c>
+      <c r="O356" t="str">
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -16109,6 +17174,9 @@
       <c r="N357" t="str">
         <v/>
       </c>
+      <c r="O357" t="str">
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -16153,6 +17221,9 @@
       <c r="N358" t="str">
         <v/>
       </c>
+      <c r="O358" t="str">
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -16197,6 +17268,9 @@
       <c r="N359" t="str">
         <v/>
       </c>
+      <c r="O359" t="str">
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -16241,6 +17315,9 @@
       <c r="N360" t="str">
         <v/>
       </c>
+      <c r="O360" t="str">
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -16285,6 +17362,9 @@
       <c r="N361" t="str">
         <v/>
       </c>
+      <c r="O361" t="str">
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -16329,6 +17409,9 @@
       <c r="N362" t="str">
         <v/>
       </c>
+      <c r="O362" t="str">
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -16371,6 +17454,9 @@
         <v/>
       </c>
       <c r="N363" t="str">
+        <v/>
+      </c>
+      <c r="O363" t="str">
         <v/>
       </c>
     </row>

--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O396"/>
+  <dimension ref="A1:P442"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,6 +445,9 @@
       <c r="O1" t="str">
         <v>official_link</v>
       </c>
+      <c r="P1" t="str">
+        <v>Description</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -492,6 +495,9 @@
       <c r="O2" t="str">
         <v/>
       </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -539,6 +545,9 @@
       <c r="O3" t="str">
         <v/>
       </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -586,6 +595,9 @@
       <c r="O4" t="str">
         <v/>
       </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -633,6 +645,9 @@
       <c r="O5" t="str">
         <v/>
       </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -680,6 +695,9 @@
       <c r="O6" t="str">
         <v/>
       </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -727,6 +745,9 @@
       <c r="O7" t="str">
         <v/>
       </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -774,6 +795,9 @@
       <c r="O8" t="str">
         <v/>
       </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -821,6 +845,9 @@
       <c r="O9" t="str">
         <v/>
       </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -868,6 +895,9 @@
       <c r="O10" t="str">
         <v/>
       </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -915,6 +945,9 @@
       <c r="O11" t="str">
         <v/>
       </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -962,6 +995,9 @@
       <c r="O12" t="str">
         <v/>
       </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1009,6 +1045,9 @@
       <c r="O13" t="str">
         <v/>
       </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1056,6 +1095,9 @@
       <c r="O14" t="str">
         <v/>
       </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1103,6 +1145,9 @@
       <c r="O15" t="str">
         <v/>
       </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1150,6 +1195,9 @@
       <c r="O16" t="str">
         <v/>
       </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1197,6 +1245,9 @@
       <c r="O17" t="str">
         <v/>
       </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1244,6 +1295,9 @@
       <c r="O18" t="str">
         <v/>
       </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1291,6 +1345,9 @@
       <c r="O19" t="str">
         <v/>
       </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1338,6 +1395,9 @@
       <c r="O20" t="str">
         <v/>
       </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1385,6 +1445,9 @@
       <c r="O21" t="str">
         <v/>
       </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1432,6 +1495,9 @@
       <c r="O22" t="str">
         <v/>
       </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1479,6 +1545,9 @@
       <c r="O23" t="str">
         <v/>
       </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1526,6 +1595,9 @@
       <c r="O24" t="str">
         <v/>
       </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1573,6 +1645,9 @@
       <c r="O25" t="str">
         <v/>
       </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1620,6 +1695,9 @@
       <c r="O26" t="str">
         <v/>
       </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1667,6 +1745,9 @@
       <c r="O27" t="str">
         <v/>
       </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1714,6 +1795,9 @@
       <c r="O28" t="str">
         <v/>
       </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1761,6 +1845,9 @@
       <c r="O29" t="str">
         <v/>
       </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1808,6 +1895,9 @@
       <c r="O30" t="str">
         <v/>
       </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1855,6 +1945,9 @@
       <c r="O31" t="str">
         <v/>
       </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1902,6 +1995,9 @@
       <c r="O32" t="str">
         <v/>
       </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1949,6 +2045,9 @@
       <c r="O33" t="str">
         <v/>
       </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1996,6 +2095,9 @@
       <c r="O34" t="str">
         <v/>
       </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -2043,6 +2145,9 @@
       <c r="O35" t="str">
         <v/>
       </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -2090,6 +2195,9 @@
       <c r="O36" t="str">
         <v/>
       </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2137,6 +2245,9 @@
       <c r="O37" t="str">
         <v/>
       </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2184,6 +2295,9 @@
       <c r="O38" t="str">
         <v/>
       </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2231,6 +2345,9 @@
       <c r="O39" t="str">
         <v/>
       </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2278,6 +2395,9 @@
       <c r="O40" t="str">
         <v/>
       </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2325,6 +2445,9 @@
       <c r="O41" t="str">
         <v/>
       </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2372,6 +2495,9 @@
       <c r="O42" t="str">
         <v/>
       </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2419,6 +2545,9 @@
       <c r="O43" t="str">
         <v/>
       </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2466,6 +2595,9 @@
       <c r="O44" t="str">
         <v/>
       </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2513,6 +2645,9 @@
       <c r="O45" t="str">
         <v/>
       </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2560,6 +2695,9 @@
       <c r="O46" t="str">
         <v/>
       </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2607,6 +2745,9 @@
       <c r="O47" t="str">
         <v/>
       </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2654,6 +2795,9 @@
       <c r="O48" t="str">
         <v/>
       </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2701,6 +2845,9 @@
       <c r="O49" t="str">
         <v/>
       </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2748,6 +2895,9 @@
       <c r="O50" t="str">
         <v/>
       </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2795,6 +2945,9 @@
       <c r="O51" t="str">
         <v/>
       </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2842,6 +2995,9 @@
       <c r="O52" t="str">
         <v/>
       </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2889,6 +3045,9 @@
       <c r="O53" t="str">
         <v/>
       </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2936,6 +3095,9 @@
       <c r="O54" t="str">
         <v/>
       </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2983,6 +3145,9 @@
       <c r="O55" t="str">
         <v/>
       </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3030,6 +3195,9 @@
       <c r="O56" t="str">
         <v/>
       </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3077,6 +3245,9 @@
       <c r="O57" t="str">
         <v/>
       </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3124,6 +3295,9 @@
       <c r="O58" t="str">
         <v/>
       </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3171,6 +3345,9 @@
       <c r="O59" t="str">
         <v/>
       </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3218,6 +3395,9 @@
       <c r="O60" t="str">
         <v/>
       </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3265,6 +3445,9 @@
       <c r="O61" t="str">
         <v/>
       </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3312,6 +3495,9 @@
       <c r="O62" t="str">
         <v/>
       </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3359,6 +3545,9 @@
       <c r="O63" t="str">
         <v/>
       </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3406,6 +3595,9 @@
       <c r="O64" t="str">
         <v/>
       </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3453,6 +3645,9 @@
       <c r="O65" t="str">
         <v/>
       </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3500,6 +3695,9 @@
       <c r="O66" t="str">
         <v/>
       </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3547,6 +3745,9 @@
       <c r="O67" t="str">
         <v/>
       </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3594,6 +3795,9 @@
       <c r="O68" t="str">
         <v/>
       </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3641,6 +3845,9 @@
       <c r="O69" t="str">
         <v/>
       </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3688,6 +3895,9 @@
       <c r="O70" t="str">
         <v/>
       </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3735,6 +3945,9 @@
       <c r="O71" t="str">
         <v/>
       </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3782,6 +3995,9 @@
       <c r="O72" t="str">
         <v/>
       </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -3829,6 +4045,9 @@
       <c r="O73" t="str">
         <v/>
       </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -3876,6 +4095,9 @@
       <c r="O74" t="str">
         <v/>
       </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -3923,6 +4145,9 @@
       <c r="O75" t="str">
         <v/>
       </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -3970,6 +4195,9 @@
       <c r="O76" t="str">
         <v/>
       </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4017,6 +4245,9 @@
       <c r="O77" t="str">
         <v/>
       </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4064,6 +4295,9 @@
       <c r="O78" t="str">
         <v/>
       </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4111,6 +4345,9 @@
       <c r="O79" t="str">
         <v/>
       </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4158,6 +4395,9 @@
       <c r="O80" t="str">
         <v/>
       </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4205,6 +4445,9 @@
       <c r="O81" t="str">
         <v/>
       </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4252,6 +4495,9 @@
       <c r="O82" t="str">
         <v/>
       </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4299,6 +4545,9 @@
       <c r="O83" t="str">
         <v/>
       </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4346,6 +4595,9 @@
       <c r="O84" t="str">
         <v/>
       </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4393,6 +4645,9 @@
       <c r="O85" t="str">
         <v/>
       </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4440,6 +4695,9 @@
       <c r="O86" t="str">
         <v/>
       </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4487,6 +4745,9 @@
       <c r="O87" t="str">
         <v/>
       </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4534,6 +4795,9 @@
       <c r="O88" t="str">
         <v/>
       </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4581,6 +4845,9 @@
       <c r="O89" t="str">
         <v/>
       </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4628,6 +4895,9 @@
       <c r="O90" t="str">
         <v/>
       </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4675,6 +4945,9 @@
       <c r="O91" t="str">
         <v/>
       </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4722,6 +4995,9 @@
       <c r="O92" t="str">
         <v/>
       </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4769,6 +5045,9 @@
       <c r="O93" t="str">
         <v/>
       </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4816,6 +5095,9 @@
       <c r="O94" t="str">
         <v/>
       </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4863,6 +5145,9 @@
       <c r="O95" t="str">
         <v/>
       </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4910,6 +5195,9 @@
       <c r="O96" t="str">
         <v/>
       </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4957,6 +5245,9 @@
       <c r="O97" t="str">
         <v/>
       </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -5004,6 +5295,9 @@
       <c r="O98" t="str">
         <v/>
       </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -5051,6 +5345,9 @@
       <c r="O99" t="str">
         <v/>
       </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -5098,6 +5395,9 @@
       <c r="O100" t="str">
         <v/>
       </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -5145,6 +5445,9 @@
       <c r="O101" t="str">
         <v/>
       </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -5192,6 +5495,9 @@
       <c r="O102" t="str">
         <v/>
       </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5239,6 +5545,9 @@
       <c r="O103" t="str">
         <v/>
       </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5286,6 +5595,9 @@
       <c r="O104" t="str">
         <v/>
       </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5333,6 +5645,9 @@
       <c r="O105" t="str">
         <v/>
       </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -5380,6 +5695,9 @@
       <c r="O106" t="str">
         <v/>
       </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5427,6 +5745,9 @@
       <c r="O107" t="str">
         <v/>
       </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5474,6 +5795,9 @@
       <c r="O108" t="str">
         <v/>
       </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -5521,6 +5845,9 @@
       <c r="O109" t="str">
         <v/>
       </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -5568,6 +5895,9 @@
       <c r="O110" t="str">
         <v/>
       </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5615,6 +5945,9 @@
       <c r="O111" t="str">
         <v/>
       </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -5662,6 +5995,9 @@
       <c r="O112" t="str">
         <v/>
       </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -5709,6 +6045,9 @@
       <c r="O113" t="str">
         <v/>
       </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -5756,6 +6095,9 @@
       <c r="O114" t="str">
         <v/>
       </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -5803,6 +6145,9 @@
       <c r="O115" t="str">
         <v/>
       </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -5850,6 +6195,9 @@
       <c r="O116" t="str">
         <v/>
       </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -5897,6 +6245,9 @@
       <c r="O117" t="str">
         <v/>
       </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -5944,6 +6295,9 @@
       <c r="O118" t="str">
         <v/>
       </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -5991,6 +6345,9 @@
       <c r="O119" t="str">
         <v/>
       </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -6038,6 +6395,9 @@
       <c r="O120" t="str">
         <v/>
       </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -6085,6 +6445,9 @@
       <c r="O121" t="str">
         <v/>
       </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -6132,6 +6495,9 @@
       <c r="O122" t="str">
         <v/>
       </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -6179,6 +6545,9 @@
       <c r="O123" t="str">
         <v/>
       </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -6226,6 +6595,9 @@
       <c r="O124" t="str">
         <v/>
       </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -6273,6 +6645,9 @@
       <c r="O125" t="str">
         <v/>
       </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -6320,6 +6695,9 @@
       <c r="O126" t="str">
         <v/>
       </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -6367,6 +6745,9 @@
       <c r="O127" t="str">
         <v/>
       </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -6414,6 +6795,9 @@
       <c r="O128" t="str">
         <v/>
       </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -6461,6 +6845,9 @@
       <c r="O129" t="str">
         <v/>
       </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -6508,6 +6895,9 @@
       <c r="O130" t="str">
         <v/>
       </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -6555,6 +6945,9 @@
       <c r="O131" t="str">
         <v/>
       </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -6602,6 +6995,9 @@
       <c r="O132" t="str">
         <v/>
       </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -6649,6 +7045,9 @@
       <c r="O133" t="str">
         <v/>
       </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -6696,6 +7095,9 @@
       <c r="O134" t="str">
         <v/>
       </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -6743,6 +7145,9 @@
       <c r="O135" t="str">
         <v/>
       </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -6790,6 +7195,9 @@
       <c r="O136" t="str">
         <v/>
       </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -6837,6 +7245,9 @@
       <c r="O137" t="str">
         <v/>
       </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -6884,6 +7295,9 @@
       <c r="O138" t="str">
         <v/>
       </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -6931,6 +7345,9 @@
       <c r="O139" t="str">
         <v/>
       </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -6978,6 +7395,9 @@
       <c r="O140" t="str">
         <v/>
       </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -7025,6 +7445,9 @@
       <c r="O141" t="str">
         <v/>
       </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -7072,6 +7495,9 @@
       <c r="O142" t="str">
         <v/>
       </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -7119,6 +7545,9 @@
       <c r="O143" t="str">
         <v/>
       </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -7166,6 +7595,9 @@
       <c r="O144" t="str">
         <v/>
       </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -7213,6 +7645,9 @@
       <c r="O145" t="str">
         <v/>
       </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -7260,6 +7695,9 @@
       <c r="O146" t="str">
         <v/>
       </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -7307,6 +7745,9 @@
       <c r="O147" t="str">
         <v/>
       </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -7354,6 +7795,9 @@
       <c r="O148" t="str">
         <v/>
       </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -7401,6 +7845,9 @@
       <c r="O149" t="str">
         <v/>
       </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -7448,6 +7895,9 @@
       <c r="O150" t="str">
         <v/>
       </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -7495,6 +7945,9 @@
       <c r="O151" t="str">
         <v/>
       </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -7542,6 +7995,9 @@
       <c r="O152" t="str">
         <v/>
       </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -7589,6 +8045,9 @@
       <c r="O153" t="str">
         <v/>
       </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -7636,6 +8095,9 @@
       <c r="O154" t="str">
         <v/>
       </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -7683,6 +8145,9 @@
       <c r="O155" t="str">
         <v/>
       </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -7730,6 +8195,9 @@
       <c r="O156" t="str">
         <v/>
       </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -7777,6 +8245,9 @@
       <c r="O157" t="str">
         <v/>
       </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -7824,6 +8295,9 @@
       <c r="O158" t="str">
         <v/>
       </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -7871,6 +8345,9 @@
       <c r="O159" t="str">
         <v/>
       </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -7918,6 +8395,9 @@
       <c r="O160" t="str">
         <v/>
       </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -7965,6 +8445,9 @@
       <c r="O161" t="str">
         <v/>
       </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -8012,6 +8495,9 @@
       <c r="O162" t="str">
         <v/>
       </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -8059,6 +8545,9 @@
       <c r="O163" t="str">
         <v/>
       </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -8106,6 +8595,9 @@
       <c r="O164" t="str">
         <v/>
       </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -8153,6 +8645,9 @@
       <c r="O165" t="str">
         <v/>
       </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -8200,6 +8695,9 @@
       <c r="O166" t="str">
         <v/>
       </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -8247,6 +8745,9 @@
       <c r="O167" t="str">
         <v/>
       </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -8294,6 +8795,9 @@
       <c r="O168" t="str">
         <v/>
       </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -8341,6 +8845,9 @@
       <c r="O169" t="str">
         <v/>
       </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -8388,6 +8895,9 @@
       <c r="O170" t="str">
         <v/>
       </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -8435,6 +8945,9 @@
       <c r="O171" t="str">
         <v/>
       </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -8482,6 +8995,9 @@
       <c r="O172" t="str">
         <v/>
       </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -8529,6 +9045,9 @@
       <c r="O173" t="str">
         <v/>
       </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -8576,6 +9095,9 @@
       <c r="O174" t="str">
         <v/>
       </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -8623,6 +9145,9 @@
       <c r="O175" t="str">
         <v/>
       </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -8670,6 +9195,9 @@
       <c r="O176" t="str">
         <v/>
       </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -8717,6 +9245,9 @@
       <c r="O177" t="str">
         <v/>
       </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -8764,6 +9295,9 @@
       <c r="O178" t="str">
         <v/>
       </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -8811,6 +9345,9 @@
       <c r="O179" t="str">
         <v/>
       </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -8858,6 +9395,9 @@
       <c r="O180" t="str">
         <v/>
       </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -8905,6 +9445,9 @@
       <c r="O181" t="str">
         <v/>
       </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -8952,6 +9495,9 @@
       <c r="O182" t="str">
         <v/>
       </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -8999,6 +9545,9 @@
       <c r="O183" t="str">
         <v/>
       </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -9046,6 +9595,9 @@
       <c r="O184" t="str">
         <v/>
       </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -9093,6 +9645,9 @@
       <c r="O185" t="str">
         <v/>
       </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -9140,6 +9695,9 @@
       <c r="O186" t="str">
         <v/>
       </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -9187,6 +9745,9 @@
       <c r="O187" t="str">
         <v/>
       </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -9234,6 +9795,9 @@
       <c r="O188" t="str">
         <v/>
       </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -9281,6 +9845,9 @@
       <c r="O189" t="str">
         <v/>
       </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -9328,6 +9895,9 @@
       <c r="O190" t="str">
         <v/>
       </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -9375,6 +9945,9 @@
       <c r="O191" t="str">
         <v/>
       </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -9422,6 +9995,9 @@
       <c r="O192" t="str">
         <v/>
       </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -9469,6 +10045,9 @@
       <c r="O193" t="str">
         <v/>
       </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -9516,6 +10095,9 @@
       <c r="O194" t="str">
         <v/>
       </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -9563,6 +10145,9 @@
       <c r="O195" t="str">
         <v/>
       </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -9610,6 +10195,9 @@
       <c r="O196" t="str">
         <v/>
       </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -9657,6 +10245,9 @@
       <c r="O197" t="str">
         <v/>
       </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -9704,6 +10295,9 @@
       <c r="O198" t="str">
         <v/>
       </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -9751,6 +10345,9 @@
       <c r="O199" t="str">
         <v/>
       </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -9798,6 +10395,9 @@
       <c r="O200" t="str">
         <v/>
       </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -9845,6 +10445,9 @@
       <c r="O201" t="str">
         <v/>
       </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -9892,6 +10495,9 @@
       <c r="O202" t="str">
         <v/>
       </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -9939,6 +10545,9 @@
       <c r="O203" t="str">
         <v/>
       </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -9986,6 +10595,9 @@
       <c r="O204" t="str">
         <v/>
       </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -10033,6 +10645,9 @@
       <c r="O205" t="str">
         <v/>
       </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -10080,6 +10695,9 @@
       <c r="O206" t="str">
         <v/>
       </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -10127,6 +10745,9 @@
       <c r="O207" t="str">
         <v/>
       </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -10174,6 +10795,9 @@
       <c r="O208" t="str">
         <v/>
       </c>
+      <c r="P208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -10221,6 +10845,9 @@
       <c r="O209" t="str">
         <v/>
       </c>
+      <c r="P209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -10268,6 +10895,9 @@
       <c r="O210" t="str">
         <v/>
       </c>
+      <c r="P210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -10315,6 +10945,9 @@
       <c r="O211" t="str">
         <v/>
       </c>
+      <c r="P211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -10362,6 +10995,9 @@
       <c r="O212" t="str">
         <v/>
       </c>
+      <c r="P212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -10409,6 +11045,9 @@
       <c r="O213" t="str">
         <v/>
       </c>
+      <c r="P213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -10456,6 +11095,9 @@
       <c r="O214" t="str">
         <v/>
       </c>
+      <c r="P214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -10503,6 +11145,9 @@
       <c r="O215" t="str">
         <v/>
       </c>
+      <c r="P215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -10550,6 +11195,9 @@
       <c r="O216" t="str">
         <v/>
       </c>
+      <c r="P216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -10597,6 +11245,9 @@
       <c r="O217" t="str">
         <v/>
       </c>
+      <c r="P217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -10644,6 +11295,9 @@
       <c r="O218" t="str">
         <v/>
       </c>
+      <c r="P218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -10691,6 +11345,9 @@
       <c r="O219" t="str">
         <v/>
       </c>
+      <c r="P219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -10738,6 +11395,9 @@
       <c r="O220" t="str">
         <v/>
       </c>
+      <c r="P220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -10785,6 +11445,9 @@
       <c r="O221" t="str">
         <v/>
       </c>
+      <c r="P221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -10832,6 +11495,9 @@
       <c r="O222" t="str">
         <v/>
       </c>
+      <c r="P222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -10879,6 +11545,9 @@
       <c r="O223" t="str">
         <v/>
       </c>
+      <c r="P223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -10926,6 +11595,9 @@
       <c r="O224" t="str">
         <v/>
       </c>
+      <c r="P224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -10973,6 +11645,9 @@
       <c r="O225" t="str">
         <v/>
       </c>
+      <c r="P225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -11020,6 +11695,9 @@
       <c r="O226" t="str">
         <v/>
       </c>
+      <c r="P226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -11067,6 +11745,9 @@
       <c r="O227" t="str">
         <v/>
       </c>
+      <c r="P227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -11114,6 +11795,9 @@
       <c r="O228" t="str">
         <v/>
       </c>
+      <c r="P228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -11161,6 +11845,9 @@
       <c r="O229" t="str">
         <v/>
       </c>
+      <c r="P229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -11208,6 +11895,9 @@
       <c r="O230" t="str">
         <v/>
       </c>
+      <c r="P230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -11255,6 +11945,9 @@
       <c r="O231" t="str">
         <v/>
       </c>
+      <c r="P231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -11302,6 +11995,9 @@
       <c r="O232" t="str">
         <v/>
       </c>
+      <c r="P232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -11349,6 +12045,9 @@
       <c r="O233" t="str">
         <v/>
       </c>
+      <c r="P233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -11396,6 +12095,9 @@
       <c r="O234" t="str">
         <v/>
       </c>
+      <c r="P234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -11443,6 +12145,9 @@
       <c r="O235" t="str">
         <v/>
       </c>
+      <c r="P235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -11490,6 +12195,9 @@
       <c r="O236" t="str">
         <v/>
       </c>
+      <c r="P236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -11537,6 +12245,9 @@
       <c r="O237" t="str">
         <v/>
       </c>
+      <c r="P237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -11584,6 +12295,9 @@
       <c r="O238" t="str">
         <v/>
       </c>
+      <c r="P238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -11631,6 +12345,9 @@
       <c r="O239" t="str">
         <v/>
       </c>
+      <c r="P239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -11678,6 +12395,9 @@
       <c r="O240" t="str">
         <v/>
       </c>
+      <c r="P240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -11725,6 +12445,9 @@
       <c r="O241" t="str">
         <v/>
       </c>
+      <c r="P241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -11772,6 +12495,9 @@
       <c r="O242" t="str">
         <v/>
       </c>
+      <c r="P242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -11819,6 +12545,9 @@
       <c r="O243" t="str">
         <v/>
       </c>
+      <c r="P243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -11866,6 +12595,9 @@
       <c r="O244" t="str">
         <v/>
       </c>
+      <c r="P244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -11913,6 +12645,9 @@
       <c r="O245" t="str">
         <v/>
       </c>
+      <c r="P245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -11960,6 +12695,9 @@
       <c r="O246" t="str">
         <v/>
       </c>
+      <c r="P246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -12007,6 +12745,9 @@
       <c r="O247" t="str">
         <v/>
       </c>
+      <c r="P247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -12054,6 +12795,9 @@
       <c r="O248" t="str">
         <v/>
       </c>
+      <c r="P248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -12101,6 +12845,9 @@
       <c r="O249" t="str">
         <v/>
       </c>
+      <c r="P249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -12148,6 +12895,9 @@
       <c r="O250" t="str">
         <v/>
       </c>
+      <c r="P250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -12195,6 +12945,9 @@
       <c r="O251" t="str">
         <v/>
       </c>
+      <c r="P251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -12242,6 +12995,9 @@
       <c r="O252" t="str">
         <v/>
       </c>
+      <c r="P252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -12289,6 +13045,9 @@
       <c r="O253" t="str">
         <v/>
       </c>
+      <c r="P253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -12336,6 +13095,9 @@
       <c r="O254" t="str">
         <v/>
       </c>
+      <c r="P254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -12383,6 +13145,9 @@
       <c r="O255" t="str">
         <v/>
       </c>
+      <c r="P255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -12430,6 +13195,9 @@
       <c r="O256" t="str">
         <v/>
       </c>
+      <c r="P256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -12477,6 +13245,9 @@
       <c r="O257" t="str">
         <v/>
       </c>
+      <c r="P257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -12524,6 +13295,9 @@
       <c r="O258" t="str">
         <v/>
       </c>
+      <c r="P258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -12571,6 +13345,9 @@
       <c r="O259" t="str">
         <v/>
       </c>
+      <c r="P259" t="str">
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -12618,6 +13395,9 @@
       <c r="O260" t="str">
         <v/>
       </c>
+      <c r="P260" t="str">
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -12665,6 +13445,9 @@
       <c r="O261" t="str">
         <v/>
       </c>
+      <c r="P261" t="str">
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -12712,6 +13495,9 @@
       <c r="O262" t="str">
         <v/>
       </c>
+      <c r="P262" t="str">
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -12759,6 +13545,9 @@
       <c r="O263" t="str">
         <v/>
       </c>
+      <c r="P263" t="str">
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -12806,6 +13595,9 @@
       <c r="O264" t="str">
         <v/>
       </c>
+      <c r="P264" t="str">
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -12853,6 +13645,9 @@
       <c r="O265" t="str">
         <v/>
       </c>
+      <c r="P265" t="str">
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -12900,6 +13695,9 @@
       <c r="O266" t="str">
         <v/>
       </c>
+      <c r="P266" t="str">
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -12947,6 +13745,9 @@
       <c r="O267" t="str">
         <v/>
       </c>
+      <c r="P267" t="str">
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -12994,6 +13795,9 @@
       <c r="O268" t="str">
         <v/>
       </c>
+      <c r="P268" t="str">
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -13041,6 +13845,9 @@
       <c r="O269" t="str">
         <v/>
       </c>
+      <c r="P269" t="str">
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -13088,6 +13895,9 @@
       <c r="O270" t="str">
         <v/>
       </c>
+      <c r="P270" t="str">
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -13135,6 +13945,9 @@
       <c r="O271" t="str">
         <v/>
       </c>
+      <c r="P271" t="str">
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -13182,6 +13995,9 @@
       <c r="O272" t="str">
         <v/>
       </c>
+      <c r="P272" t="str">
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -13229,6 +14045,9 @@
       <c r="O273" t="str">
         <v/>
       </c>
+      <c r="P273" t="str">
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -13276,6 +14095,9 @@
       <c r="O274" t="str">
         <v/>
       </c>
+      <c r="P274" t="str">
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -13323,6 +14145,9 @@
       <c r="O275" t="str">
         <v/>
       </c>
+      <c r="P275" t="str">
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -13370,6 +14195,9 @@
       <c r="O276" t="str">
         <v/>
       </c>
+      <c r="P276" t="str">
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -13417,6 +14245,9 @@
       <c r="O277" t="str">
         <v/>
       </c>
+      <c r="P277" t="str">
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -13464,6 +14295,9 @@
       <c r="O278" t="str">
         <v/>
       </c>
+      <c r="P278" t="str">
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -13511,6 +14345,9 @@
       <c r="O279" t="str">
         <v/>
       </c>
+      <c r="P279" t="str">
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -13558,6 +14395,9 @@
       <c r="O280" t="str">
         <v/>
       </c>
+      <c r="P280" t="str">
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -13605,6 +14445,9 @@
       <c r="O281" t="str">
         <v/>
       </c>
+      <c r="P281" t="str">
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -13652,6 +14495,9 @@
       <c r="O282" t="str">
         <v/>
       </c>
+      <c r="P282" t="str">
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -13699,6 +14545,9 @@
       <c r="O283" t="str">
         <v/>
       </c>
+      <c r="P283" t="str">
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -13746,6 +14595,9 @@
       <c r="O284" t="str">
         <v/>
       </c>
+      <c r="P284" t="str">
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -13793,6 +14645,9 @@
       <c r="O285" t="str">
         <v/>
       </c>
+      <c r="P285" t="str">
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -13840,6 +14695,9 @@
       <c r="O286" t="str">
         <v/>
       </c>
+      <c r="P286" t="str">
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -13887,6 +14745,9 @@
       <c r="O287" t="str">
         <v/>
       </c>
+      <c r="P287" t="str">
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -13934,6 +14795,9 @@
       <c r="O288" t="str">
         <v/>
       </c>
+      <c r="P288" t="str">
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -13981,6 +14845,9 @@
       <c r="O289" t="str">
         <v/>
       </c>
+      <c r="P289" t="str">
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -14028,6 +14895,9 @@
       <c r="O290" t="str">
         <v/>
       </c>
+      <c r="P290" t="str">
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -14075,6 +14945,9 @@
       <c r="O291" t="str">
         <v/>
       </c>
+      <c r="P291" t="str">
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -14122,6 +14995,9 @@
       <c r="O292" t="str">
         <v/>
       </c>
+      <c r="P292" t="str">
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -14169,6 +15045,9 @@
       <c r="O293" t="str">
         <v/>
       </c>
+      <c r="P293" t="str">
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -14216,6 +15095,9 @@
       <c r="O294" t="str">
         <v/>
       </c>
+      <c r="P294" t="str">
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -14263,6 +15145,9 @@
       <c r="O295" t="str">
         <v/>
       </c>
+      <c r="P295" t="str">
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -14310,6 +15195,9 @@
       <c r="O296" t="str">
         <v/>
       </c>
+      <c r="P296" t="str">
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -14357,6 +15245,9 @@
       <c r="O297" t="str">
         <v/>
       </c>
+      <c r="P297" t="str">
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -14404,6 +15295,9 @@
       <c r="O298" t="str">
         <v/>
       </c>
+      <c r="P298" t="str">
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -14451,6 +15345,9 @@
       <c r="O299" t="str">
         <v/>
       </c>
+      <c r="P299" t="str">
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -14498,6 +15395,9 @@
       <c r="O300" t="str">
         <v/>
       </c>
+      <c r="P300" t="str">
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -14545,6 +15445,9 @@
       <c r="O301" t="str">
         <v/>
       </c>
+      <c r="P301" t="str">
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -14592,6 +15495,9 @@
       <c r="O302" t="str">
         <v/>
       </c>
+      <c r="P302" t="str">
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -14639,6 +15545,9 @@
       <c r="O303" t="str">
         <v/>
       </c>
+      <c r="P303" t="str">
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -14686,6 +15595,9 @@
       <c r="O304" t="str">
         <v/>
       </c>
+      <c r="P304" t="str">
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -14733,6 +15645,9 @@
       <c r="O305" t="str">
         <v/>
       </c>
+      <c r="P305" t="str">
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -14780,6 +15695,9 @@
       <c r="O306" t="str">
         <v/>
       </c>
+      <c r="P306" t="str">
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -14827,6 +15745,9 @@
       <c r="O307" t="str">
         <v/>
       </c>
+      <c r="P307" t="str">
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -14874,6 +15795,9 @@
       <c r="O308" t="str">
         <v/>
       </c>
+      <c r="P308" t="str">
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -14921,6 +15845,9 @@
       <c r="O309" t="str">
         <v/>
       </c>
+      <c r="P309" t="str">
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -14968,6 +15895,9 @@
       <c r="O310" t="str">
         <v/>
       </c>
+      <c r="P310" t="str">
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -15015,6 +15945,9 @@
       <c r="O311" t="str">
         <v/>
       </c>
+      <c r="P311" t="str">
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -15062,6 +15995,9 @@
       <c r="O312" t="str">
         <v/>
       </c>
+      <c r="P312" t="str">
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -15109,6 +16045,9 @@
       <c r="O313" t="str">
         <v/>
       </c>
+      <c r="P313" t="str">
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -15156,6 +16095,9 @@
       <c r="O314" t="str">
         <v/>
       </c>
+      <c r="P314" t="str">
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -15203,6 +16145,9 @@
       <c r="O315" t="str">
         <v/>
       </c>
+      <c r="P315" t="str">
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -15250,6 +16195,9 @@
       <c r="O316" t="str">
         <v/>
       </c>
+      <c r="P316" t="str">
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -15297,6 +16245,9 @@
       <c r="O317" t="str">
         <v/>
       </c>
+      <c r="P317" t="str">
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -15344,6 +16295,9 @@
       <c r="O318" t="str">
         <v/>
       </c>
+      <c r="P318" t="str">
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -15391,6 +16345,9 @@
       <c r="O319" t="str">
         <v/>
       </c>
+      <c r="P319" t="str">
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -15438,6 +16395,9 @@
       <c r="O320" t="str">
         <v/>
       </c>
+      <c r="P320" t="str">
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -15485,6 +16445,9 @@
       <c r="O321" t="str">
         <v/>
       </c>
+      <c r="P321" t="str">
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -15532,6 +16495,9 @@
       <c r="O322" t="str">
         <v/>
       </c>
+      <c r="P322" t="str">
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -15579,6 +16545,9 @@
       <c r="O323" t="str">
         <v/>
       </c>
+      <c r="P323" t="str">
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -15626,6 +16595,9 @@
       <c r="O324" t="str">
         <v/>
       </c>
+      <c r="P324" t="str">
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -15673,6 +16645,9 @@
       <c r="O325" t="str">
         <v/>
       </c>
+      <c r="P325" t="str">
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -15720,6 +16695,9 @@
       <c r="O326" t="str">
         <v/>
       </c>
+      <c r="P326" t="str">
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -15767,6 +16745,9 @@
       <c r="O327" t="str">
         <v/>
       </c>
+      <c r="P327" t="str">
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -15814,6 +16795,9 @@
       <c r="O328" t="str">
         <v/>
       </c>
+      <c r="P328" t="str">
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -15861,6 +16845,9 @@
       <c r="O329" t="str">
         <v/>
       </c>
+      <c r="P329" t="str">
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -15908,6 +16895,9 @@
       <c r="O330" t="str">
         <v/>
       </c>
+      <c r="P330" t="str">
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -15955,6 +16945,9 @@
       <c r="O331" t="str">
         <v/>
       </c>
+      <c r="P331" t="str">
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -16002,6 +16995,9 @@
       <c r="O332" t="str">
         <v/>
       </c>
+      <c r="P332" t="str">
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -16049,6 +17045,9 @@
       <c r="O333" t="str">
         <v/>
       </c>
+      <c r="P333" t="str">
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -16096,6 +17095,9 @@
       <c r="O334" t="str">
         <v/>
       </c>
+      <c r="P334" t="str">
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -16143,6 +17145,9 @@
       <c r="O335" t="str">
         <v/>
       </c>
+      <c r="P335" t="str">
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -16190,6 +17195,9 @@
       <c r="O336" t="str">
         <v/>
       </c>
+      <c r="P336" t="str">
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -16237,6 +17245,9 @@
       <c r="O337" t="str">
         <v/>
       </c>
+      <c r="P337" t="str">
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -16284,6 +17295,9 @@
       <c r="O338" t="str">
         <v/>
       </c>
+      <c r="P338" t="str">
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -16331,6 +17345,9 @@
       <c r="O339" t="str">
         <v/>
       </c>
+      <c r="P339" t="str">
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -16378,6 +17395,9 @@
       <c r="O340" t="str">
         <v/>
       </c>
+      <c r="P340" t="str">
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -16425,6 +17445,9 @@
       <c r="O341" t="str">
         <v/>
       </c>
+      <c r="P341" t="str">
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -16472,6 +17495,9 @@
       <c r="O342" t="str">
         <v/>
       </c>
+      <c r="P342" t="str">
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -16519,6 +17545,9 @@
       <c r="O343" t="str">
         <v/>
       </c>
+      <c r="P343" t="str">
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -16566,6 +17595,9 @@
       <c r="O344" t="str">
         <v/>
       </c>
+      <c r="P344" t="str">
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -16613,6 +17645,9 @@
       <c r="O345" t="str">
         <v/>
       </c>
+      <c r="P345" t="str">
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -16660,6 +17695,9 @@
       <c r="O346" t="str">
         <v/>
       </c>
+      <c r="P346" t="str">
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -16707,6 +17745,9 @@
       <c r="O347" t="str">
         <v/>
       </c>
+      <c r="P347" t="str">
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -16754,6 +17795,9 @@
       <c r="O348" t="str">
         <v/>
       </c>
+      <c r="P348" t="str">
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -16801,6 +17845,9 @@
       <c r="O349" t="str">
         <v/>
       </c>
+      <c r="P349" t="str">
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -16848,6 +17895,9 @@
       <c r="O350" t="str">
         <v/>
       </c>
+      <c r="P350" t="str">
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -16895,6 +17945,9 @@
       <c r="O351" t="str">
         <v/>
       </c>
+      <c r="P351" t="str">
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -16942,6 +17995,9 @@
       <c r="O352" t="str">
         <v/>
       </c>
+      <c r="P352" t="str">
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -16989,6 +18045,9 @@
       <c r="O353" t="str">
         <v/>
       </c>
+      <c r="P353" t="str">
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -17036,6 +18095,9 @@
       <c r="O354" t="str">
         <v/>
       </c>
+      <c r="P354" t="str">
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -17083,6 +18145,9 @@
       <c r="O355" t="str">
         <v/>
       </c>
+      <c r="P355" t="str">
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -17130,6 +18195,9 @@
       <c r="O356" t="str">
         <v/>
       </c>
+      <c r="P356" t="str">
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -17177,6 +18245,9 @@
       <c r="O357" t="str">
         <v/>
       </c>
+      <c r="P357" t="str">
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -17224,6 +18295,9 @@
       <c r="O358" t="str">
         <v/>
       </c>
+      <c r="P358" t="str">
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -17271,6 +18345,9 @@
       <c r="O359" t="str">
         <v/>
       </c>
+      <c r="P359" t="str">
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -17318,6 +18395,9 @@
       <c r="O360" t="str">
         <v/>
       </c>
+      <c r="P360" t="str">
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -17365,6 +18445,9 @@
       <c r="O361" t="str">
         <v/>
       </c>
+      <c r="P361" t="str">
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -17412,6 +18495,9 @@
       <c r="O362" t="str">
         <v/>
       </c>
+      <c r="P362" t="str">
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -17459,6 +18545,9 @@
       <c r="O363" t="str">
         <v/>
       </c>
+      <c r="P363" t="str">
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -17506,6 +18595,9 @@
       <c r="O364" t="str">
         <v>https://keitech.co.jp/pages/613/</v>
       </c>
+      <c r="P364" t="str">
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -17553,6 +18645,9 @@
       <c r="O365" t="str">
         <v>https://keitech.co.jp/pages/39/</v>
       </c>
+      <c r="P365" t="str">
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -17600,6 +18695,9 @@
       <c r="O366" t="str">
         <v>https://keitech.co.jp/pages/57/</v>
       </c>
+      <c r="P366" t="str">
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -17647,6 +18745,9 @@
       <c r="O367" t="str">
         <v>https://keitech.co.jp/pages/232/</v>
       </c>
+      <c r="P367" t="str">
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -17694,6 +18795,9 @@
       <c r="O368" t="str">
         <v>https://keitech.co.jp/pages/608/</v>
       </c>
+      <c r="P368" t="str">
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -17741,6 +18845,9 @@
       <c r="O369" t="str">
         <v>https://keitech.co.jp/pages/599/</v>
       </c>
+      <c r="P369" t="str">
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -17788,6 +18895,9 @@
       <c r="O370" t="str">
         <v>https://keitech.co.jp/pages/582/</v>
       </c>
+      <c r="P370" t="str">
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -17835,6 +18945,9 @@
       <c r="O371" t="str">
         <v>https://keitech.co.jp/pages/581/</v>
       </c>
+      <c r="P371" t="str">
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -17882,6 +18995,9 @@
       <c r="O372" t="str">
         <v>https://keitech.co.jp/pages/551/</v>
       </c>
+      <c r="P372" t="str">
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -17929,6 +19045,9 @@
       <c r="O373" t="str">
         <v>https://keitech.co.jp/pages/456/</v>
       </c>
+      <c r="P373" t="str">
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -17976,6 +19095,9 @@
       <c r="O374" t="str">
         <v>https://keitech.co.jp/pages/549/</v>
       </c>
+      <c r="P374" t="str">
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -18023,6 +19145,9 @@
       <c r="O375" t="str">
         <v>https://keitech.co.jp/pages/450/</v>
       </c>
+      <c r="P375" t="str">
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -18070,6 +19195,9 @@
       <c r="O376" t="str">
         <v>https://keitech.co.jp/pages/423/</v>
       </c>
+      <c r="P376" t="str">
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -18117,6 +19245,9 @@
       <c r="O377" t="str">
         <v>https://keitech.co.jp/pages/381/</v>
       </c>
+      <c r="P377" t="str">
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -18164,6 +19295,9 @@
       <c r="O378" t="str">
         <v>https://keitech.co.jp/pages/158/</v>
       </c>
+      <c r="P378" t="str">
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -18211,6 +19345,9 @@
       <c r="O379" t="str">
         <v>https://keitech.co.jp/pages/455/</v>
       </c>
+      <c r="P379" t="str">
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -18258,6 +19395,9 @@
       <c r="O380" t="str">
         <v>https://keitech.co.jp/pages/35/</v>
       </c>
+      <c r="P380" t="str">
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -18305,6 +19445,9 @@
       <c r="O381" t="str">
         <v>https://keitech.co.jp/pages/293/</v>
       </c>
+      <c r="P381" t="str">
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -18352,6 +19495,9 @@
       <c r="O382" t="str">
         <v>https://keitech.co.jp/pages/276/</v>
       </c>
+      <c r="P382" t="str">
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -18399,6 +19545,9 @@
       <c r="O383" t="str">
         <v>https://keitech.co.jp/pages/18/</v>
       </c>
+      <c r="P383" t="str">
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -18446,6 +19595,9 @@
       <c r="O384" t="str">
         <v>https://keitech.co.jp/pages/660/</v>
       </c>
+      <c r="P384" t="str">
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -18493,6 +19645,9 @@
       <c r="O385" t="str">
         <v>https://keitech.co.jp/pages/617/</v>
       </c>
+      <c r="P385" t="str">
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -18540,6 +19695,9 @@
       <c r="O386" t="str">
         <v>https://keitech.co.jp/pages/554/</v>
       </c>
+      <c r="P386" t="str">
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -18587,6 +19745,9 @@
       <c r="O387" t="str">
         <v>https://keitech.co.jp/pages/625/</v>
       </c>
+      <c r="P387" t="str">
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -18634,6 +19795,9 @@
       <c r="O388" t="str">
         <v>https://keitech.co.jp/pages/575/</v>
       </c>
+      <c r="P388" t="str">
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -18681,6 +19845,9 @@
       <c r="O389" t="str">
         <v>https://keitech.co.jp/pages/655/</v>
       </c>
+      <c r="P389" t="str">
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -18728,6 +19895,9 @@
       <c r="O390" t="str">
         <v>https://keitech.co.jp/pages/576/</v>
       </c>
+      <c r="P390" t="str">
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
@@ -18775,6 +19945,9 @@
       <c r="O391" t="str">
         <v>https://keitech.co.jp/pages/602/</v>
       </c>
+      <c r="P391" t="str">
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -18822,6 +19995,9 @@
       <c r="O392" t="str">
         <v>https://keitech.co.jp/pages/603/</v>
       </c>
+      <c r="P392" t="str">
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -18869,6 +20045,9 @@
       <c r="O393" t="str">
         <v>https://keitech.co.jp/pages/10/</v>
       </c>
+      <c r="P393" t="str">
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -18916,6 +20095,9 @@
       <c r="O394" t="str">
         <v>https://keitech.co.jp/pages/206/</v>
       </c>
+      <c r="P394" t="str">
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -18963,6 +20145,9 @@
       <c r="O395" t="str">
         <v>https://keitech.co.jp/pages/13/</v>
       </c>
+      <c r="P395" t="str">
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -19010,10 +20195,2313 @@
       <c r="O396" t="str">
         <v>https://keitech.co.jp/pages/14/</v>
       </c>
+      <c r="P396" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>YAM001</v>
+      </c>
+      <c r="B397">
+        <v>112</v>
+      </c>
+      <c r="C397" t="str">
+        <v>Fuzzy Senko</v>
+      </c>
+      <c r="D397" t="str">
+        <v>Fuzzy Senko</v>
+      </c>
+      <c r="E397" t="str">
+        <v/>
+      </c>
+      <c r="F397" t="str">
+        <v/>
+      </c>
+      <c r="G397" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H397" t="str">
+        <v/>
+      </c>
+      <c r="I397" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J397" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K397" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_senko.jpg</v>
+      </c>
+      <c r="L397" t="str">
+        <v>2026-04-10T10:18:14.137Z</v>
+      </c>
+      <c r="M397" t="str">
+        <v>2026-04-10T10:18:14.137Z</v>
+      </c>
+      <c r="N397" t="str">
+        <v/>
+      </c>
+      <c r="O397" t="str">
+        <v/>
+      </c>
+      <c r="P397" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>YAM002</v>
+      </c>
+      <c r="B398">
+        <v>112</v>
+      </c>
+      <c r="C398" t="str">
+        <v>Fuzzy Nuki</v>
+      </c>
+      <c r="D398" t="str">
+        <v>Fuzzy Nuki</v>
+      </c>
+      <c r="E398" t="str">
+        <v/>
+      </c>
+      <c r="F398" t="str">
+        <v/>
+      </c>
+      <c r="G398" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H398" t="str">
+        <v/>
+      </c>
+      <c r="I398" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J398" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K398" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_nuki.jpg</v>
+      </c>
+      <c r="L398" t="str">
+        <v>2026-04-10T10:18:16.243Z</v>
+      </c>
+      <c r="M398" t="str">
+        <v>2026-04-10T10:18:16.243Z</v>
+      </c>
+      <c r="N398" t="str">
+        <v/>
+      </c>
+      <c r="O398" t="str">
+        <v/>
+      </c>
+      <c r="P398" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>YAM003</v>
+      </c>
+      <c r="B399">
+        <v>112</v>
+      </c>
+      <c r="C399" t="str">
+        <v>Fuzzy Nut 6pk</v>
+      </c>
+      <c r="D399" t="str">
+        <v>Fuzzy Nut 6pk</v>
+      </c>
+      <c r="E399" t="str">
+        <v/>
+      </c>
+      <c r="F399" t="str">
+        <v/>
+      </c>
+      <c r="G399" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H399" t="str">
+        <v/>
+      </c>
+      <c r="I399" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J399" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K399" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_nut_6pk.jpg</v>
+      </c>
+      <c r="L399" t="str">
+        <v>2026-04-10T10:18:18.376Z</v>
+      </c>
+      <c r="M399" t="str">
+        <v>2026-04-10T10:18:18.376Z</v>
+      </c>
+      <c r="N399" t="str">
+        <v/>
+      </c>
+      <c r="O399" t="str">
+        <v/>
+      </c>
+      <c r="P399" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>YAM004</v>
+      </c>
+      <c r="B400">
+        <v>112</v>
+      </c>
+      <c r="C400" t="str">
+        <v>Uni</v>
+      </c>
+      <c r="D400" t="str">
+        <v>Uni</v>
+      </c>
+      <c r="E400" t="str">
+        <v/>
+      </c>
+      <c r="F400" t="str">
+        <v/>
+      </c>
+      <c r="G400" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H400" t="str">
+        <v/>
+      </c>
+      <c r="I400" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J400" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K400" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_uni.jpg</v>
+      </c>
+      <c r="L400" t="str">
+        <v>2026-04-10T10:18:20.464Z</v>
+      </c>
+      <c r="M400" t="str">
+        <v>2026-04-10T10:18:20.464Z</v>
+      </c>
+      <c r="N400" t="str">
+        <v/>
+      </c>
+      <c r="O400" t="str">
+        <v/>
+      </c>
+      <c r="P400" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>YAM005</v>
+      </c>
+      <c r="B401">
+        <v>112</v>
+      </c>
+      <c r="C401" t="str">
+        <v>Ultimate Senko Kit – 100pc Assortment</v>
+      </c>
+      <c r="D401" t="str">
+        <v>Ultimate Senko Kit – 100pc Assortment</v>
+      </c>
+      <c r="E401" t="str">
+        <v/>
+      </c>
+      <c r="F401" t="str">
+        <v/>
+      </c>
+      <c r="G401" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H401" t="str">
+        <v/>
+      </c>
+      <c r="I401" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J401" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K401" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_ultimate_senko_kit___100pc_assortment.jpg</v>
+      </c>
+      <c r="L401" t="str">
+        <v>2026-04-10T10:18:23.621Z</v>
+      </c>
+      <c r="M401" t="str">
+        <v>2026-04-10T10:18:23.621Z</v>
+      </c>
+      <c r="N401" t="str">
+        <v/>
+      </c>
+      <c r="O401" t="str">
+        <v/>
+      </c>
+      <c r="P401" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>YAM006</v>
+      </c>
+      <c r="B402">
+        <v>112</v>
+      </c>
+      <c r="C402" t="str">
+        <v>Senko Kit – 160pc Assortment</v>
+      </c>
+      <c r="D402" t="str">
+        <v>Senko Kit – 160pc Assortment</v>
+      </c>
+      <c r="E402" t="str">
+        <v/>
+      </c>
+      <c r="F402" t="str">
+        <v/>
+      </c>
+      <c r="G402" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H402" t="str">
+        <v/>
+      </c>
+      <c r="I402" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J402" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K402" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_kit___160pc_assortment.jpg</v>
+      </c>
+      <c r="L402" t="str">
+        <v>2026-04-10T10:18:25.835Z</v>
+      </c>
+      <c r="M402" t="str">
+        <v>2026-04-10T10:18:25.835Z</v>
+      </c>
+      <c r="N402" t="str">
+        <v/>
+      </c>
+      <c r="O402" t="str">
+        <v/>
+      </c>
+      <c r="P402" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>YAM007</v>
+      </c>
+      <c r="B403">
+        <v>112</v>
+      </c>
+      <c r="C403" t="str">
+        <v>5″ Senko Baitfish Bundle – 50pc Assortment</v>
+      </c>
+      <c r="D403" t="str">
+        <v>5″ Senko Baitfish Bundle – 50pc Assortment</v>
+      </c>
+      <c r="E403" t="str">
+        <v/>
+      </c>
+      <c r="F403" t="str">
+        <v/>
+      </c>
+      <c r="G403" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H403" t="str">
+        <v/>
+      </c>
+      <c r="I403" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J403" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K403" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_baitfish_bundle___50pc_assortment.jpg</v>
+      </c>
+      <c r="L403" t="str">
+        <v>2026-04-10T10:18:27.985Z</v>
+      </c>
+      <c r="M403" t="str">
+        <v>2026-04-10T10:18:27.985Z</v>
+      </c>
+      <c r="N403" t="str">
+        <v/>
+      </c>
+      <c r="O403" t="str">
+        <v/>
+      </c>
+      <c r="P403" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>YAM008</v>
+      </c>
+      <c r="B404">
+        <v>112</v>
+      </c>
+      <c r="C404" t="str">
+        <v>5″ Senko Green Pumpkin Bundle – 50pc Assortment</v>
+      </c>
+      <c r="D404" t="str">
+        <v>5″ Senko Green Pumpkin Bundle – 50pc Assortment</v>
+      </c>
+      <c r="E404" t="str">
+        <v/>
+      </c>
+      <c r="F404" t="str">
+        <v/>
+      </c>
+      <c r="G404" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H404" t="str">
+        <v/>
+      </c>
+      <c r="I404" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J404" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K404" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_green_pumpkin_bundle___50pc_assortment.jpg</v>
+      </c>
+      <c r="L404" t="str">
+        <v>2026-04-10T10:18:30.130Z</v>
+      </c>
+      <c r="M404" t="str">
+        <v>2026-04-10T10:18:30.130Z</v>
+      </c>
+      <c r="N404" t="str">
+        <v/>
+      </c>
+      <c r="O404" t="str">
+        <v/>
+      </c>
+      <c r="P404" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>YAM009</v>
+      </c>
+      <c r="B405">
+        <v>112</v>
+      </c>
+      <c r="C405" t="str">
+        <v>Senko Bundle – 90pc Assortment</v>
+      </c>
+      <c r="D405" t="str">
+        <v>Senko Bundle – 90pc Assortment</v>
+      </c>
+      <c r="E405" t="str">
+        <v/>
+      </c>
+      <c r="F405" t="str">
+        <v/>
+      </c>
+      <c r="G405" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H405" t="str">
+        <v/>
+      </c>
+      <c r="I405" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J405" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K405" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_bundle___90pc_assortment.jpg</v>
+      </c>
+      <c r="L405" t="str">
+        <v>2026-04-10T10:18:33.272Z</v>
+      </c>
+      <c r="M405" t="str">
+        <v>2026-04-10T10:18:33.272Z</v>
+      </c>
+      <c r="N405" t="str">
+        <v/>
+      </c>
+      <c r="O405" t="str">
+        <v/>
+      </c>
+      <c r="P405" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>YAM010</v>
+      </c>
+      <c r="B406">
+        <v>112</v>
+      </c>
+      <c r="C406" t="str">
+        <v>Fat Senko 10pk</v>
+      </c>
+      <c r="D406" t="str">
+        <v>Fat Senko 10pk</v>
+      </c>
+      <c r="E406" t="str">
+        <v/>
+      </c>
+      <c r="F406" t="str">
+        <v/>
+      </c>
+      <c r="G406" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H406" t="str">
+        <v/>
+      </c>
+      <c r="I406" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J406" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K406" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fat_senko_10pk.jpg</v>
+      </c>
+      <c r="L406" t="str">
+        <v>2026-04-10T10:18:35.432Z</v>
+      </c>
+      <c r="M406" t="str">
+        <v>2026-04-10T10:18:35.432Z</v>
+      </c>
+      <c r="N406" t="str">
+        <v/>
+      </c>
+      <c r="O406" t="str">
+        <v/>
+      </c>
+      <c r="P406" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>YAM011</v>
+      </c>
+      <c r="B407">
+        <v>112</v>
+      </c>
+      <c r="C407" t="str">
+        <v>Swimming Senko</v>
+      </c>
+      <c r="D407" t="str">
+        <v>Swimming Senko</v>
+      </c>
+      <c r="E407" t="str">
+        <v/>
+      </c>
+      <c r="F407" t="str">
+        <v/>
+      </c>
+      <c r="G407" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H407" t="str">
+        <v/>
+      </c>
+      <c r="I407" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J407" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K407" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_swimming_senko.jpg</v>
+      </c>
+      <c r="L407" t="str">
+        <v>2026-04-10T10:18:36.702Z</v>
+      </c>
+      <c r="M407" t="str">
+        <v>2026-04-10T10:18:36.702Z</v>
+      </c>
+      <c r="N407" t="str">
+        <v/>
+      </c>
+      <c r="O407" t="str">
+        <v/>
+      </c>
+      <c r="P407" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>YAM012</v>
+      </c>
+      <c r="B408">
+        <v>112</v>
+      </c>
+      <c r="C408" t="str">
+        <v>Senko Bulk Packs</v>
+      </c>
+      <c r="D408" t="str">
+        <v>Senko Bulk Packs</v>
+      </c>
+      <c r="E408" t="str">
+        <v/>
+      </c>
+      <c r="F408" t="str">
+        <v/>
+      </c>
+      <c r="G408" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H408" t="str">
+        <v/>
+      </c>
+      <c r="I408" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J408" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K408" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_bulk_packs.jpg</v>
+      </c>
+      <c r="L408" t="str">
+        <v>2026-04-10T10:18:38.783Z</v>
+      </c>
+      <c r="M408" t="str">
+        <v>2026-04-10T10:18:38.783Z</v>
+      </c>
+      <c r="N408" t="str">
+        <v/>
+      </c>
+      <c r="O408" t="str">
+        <v/>
+      </c>
+      <c r="P408" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>YAM013</v>
+      </c>
+      <c r="B409">
+        <v>112</v>
+      </c>
+      <c r="C409" t="str">
+        <v>Megastrike Fish Attractant</v>
+      </c>
+      <c r="D409" t="str">
+        <v>Megastrike Fish Attractant</v>
+      </c>
+      <c r="E409" t="str">
+        <v/>
+      </c>
+      <c r="F409" t="str">
+        <v/>
+      </c>
+      <c r="G409" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H409" t="str">
+        <v/>
+      </c>
+      <c r="I409" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J409" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K409" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_megastrike_fish_attractant.jpg</v>
+      </c>
+      <c r="L409" t="str">
+        <v>2026-04-10T10:18:40.908Z</v>
+      </c>
+      <c r="M409" t="str">
+        <v>2026-04-10T10:18:40.908Z</v>
+      </c>
+      <c r="N409" t="str">
+        <v/>
+      </c>
+      <c r="O409" t="str">
+        <v/>
+      </c>
+      <c r="P409" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>YAM014</v>
+      </c>
+      <c r="B410">
+        <v>112</v>
+      </c>
+      <c r="C410" t="str">
+        <v>7″ Speed Senko 7pk</v>
+      </c>
+      <c r="D410" t="str">
+        <v>7″ Speed Senko 7pk</v>
+      </c>
+      <c r="E410" t="str">
+        <v/>
+      </c>
+      <c r="F410" t="str">
+        <v/>
+      </c>
+      <c r="G410" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H410" t="str">
+        <v/>
+      </c>
+      <c r="I410" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J410" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K410" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_7__speed_senko_7pk.jpg</v>
+      </c>
+      <c r="L410" t="str">
+        <v>2026-04-10T10:18:43.146Z</v>
+      </c>
+      <c r="M410" t="str">
+        <v>2026-04-10T10:18:43.146Z</v>
+      </c>
+      <c r="N410" t="str">
+        <v/>
+      </c>
+      <c r="O410" t="str">
+        <v/>
+      </c>
+      <c r="P410" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>YAM015</v>
+      </c>
+      <c r="B411">
+        <v>112</v>
+      </c>
+      <c r="C411" t="str">
+        <v>3″ Ned Senko 10pk</v>
+      </c>
+      <c r="D411" t="str">
+        <v>3″ Ned Senko 10pk</v>
+      </c>
+      <c r="E411" t="str">
+        <v/>
+      </c>
+      <c r="F411" t="str">
+        <v/>
+      </c>
+      <c r="G411" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H411" t="str">
+        <v/>
+      </c>
+      <c r="I411" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J411" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K411" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3__ned_senko_10pk.jpg</v>
+      </c>
+      <c r="L411" t="str">
+        <v>2026-04-10T10:18:45.238Z</v>
+      </c>
+      <c r="M411" t="str">
+        <v>2026-04-10T10:18:45.238Z</v>
+      </c>
+      <c r="N411" t="str">
+        <v/>
+      </c>
+      <c r="O411" t="str">
+        <v/>
+      </c>
+      <c r="P411" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>YAM016</v>
+      </c>
+      <c r="B412">
+        <v>112</v>
+      </c>
+      <c r="C412" t="str">
+        <v>3″ Slim Senko 10pk</v>
+      </c>
+      <c r="D412" t="str">
+        <v>3″ Slim Senko 10pk</v>
+      </c>
+      <c r="E412" t="str">
+        <v/>
+      </c>
+      <c r="F412" t="str">
+        <v/>
+      </c>
+      <c r="G412" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H412" t="str">
+        <v/>
+      </c>
+      <c r="I412" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J412" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K412" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3__slim_senko_10pk.jpg</v>
+      </c>
+      <c r="L412" t="str">
+        <v>2026-04-10T10:18:47.330Z</v>
+      </c>
+      <c r="M412" t="str">
+        <v>2026-04-10T10:18:47.330Z</v>
+      </c>
+      <c r="N412" t="str">
+        <v/>
+      </c>
+      <c r="O412" t="str">
+        <v/>
+      </c>
+      <c r="P412" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>YAM017</v>
+      </c>
+      <c r="B413">
+        <v>112</v>
+      </c>
+      <c r="C413" t="str">
+        <v>5″ Pro Senko 10pk</v>
+      </c>
+      <c r="D413" t="str">
+        <v>5″ Pro Senko 10pk</v>
+      </c>
+      <c r="E413" t="str">
+        <v/>
+      </c>
+      <c r="F413" t="str">
+        <v/>
+      </c>
+      <c r="G413" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H413" t="str">
+        <v/>
+      </c>
+      <c r="I413" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J413" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K413" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__pro_senko_10pk.jpg</v>
+      </c>
+      <c r="L413" t="str">
+        <v>2026-04-10T10:18:49.421Z</v>
+      </c>
+      <c r="M413" t="str">
+        <v>2026-04-10T10:18:49.421Z</v>
+      </c>
+      <c r="N413" t="str">
+        <v/>
+      </c>
+      <c r="O413" t="str">
+        <v/>
+      </c>
+      <c r="P413" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>YAM018</v>
+      </c>
+      <c r="B414">
+        <v>112</v>
+      </c>
+      <c r="C414" t="str">
+        <v>5″ Thin Senko 10pk</v>
+      </c>
+      <c r="D414" t="str">
+        <v>5″ Thin Senko 10pk</v>
+      </c>
+      <c r="E414" t="str">
+        <v/>
+      </c>
+      <c r="F414" t="str">
+        <v/>
+      </c>
+      <c r="G414" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H414" t="str">
+        <v/>
+      </c>
+      <c r="I414" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J414" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K414" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__thin_senko_10pk.jpg</v>
+      </c>
+      <c r="L414" t="str">
+        <v>2026-04-10T10:18:51.127Z</v>
+      </c>
+      <c r="M414" t="str">
+        <v>2026-04-10T10:18:51.127Z</v>
+      </c>
+      <c r="N414" t="str">
+        <v/>
+      </c>
+      <c r="O414" t="str">
+        <v/>
+      </c>
+      <c r="P414" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>YAM019</v>
+      </c>
+      <c r="B415">
+        <v>112</v>
+      </c>
+      <c r="C415" t="str">
+        <v>7″ Senko 5pk</v>
+      </c>
+      <c r="D415" t="str">
+        <v>7″ Senko 5pk</v>
+      </c>
+      <c r="E415" t="str">
+        <v/>
+      </c>
+      <c r="F415" t="str">
+        <v/>
+      </c>
+      <c r="G415" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H415" t="str">
+        <v/>
+      </c>
+      <c r="I415" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J415" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K415" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_7__senko_5pk.jpg</v>
+      </c>
+      <c r="L415" t="str">
+        <v>2026-04-10T10:18:53.263Z</v>
+      </c>
+      <c r="M415" t="str">
+        <v>2026-04-10T10:18:53.263Z</v>
+      </c>
+      <c r="N415" t="str">
+        <v/>
+      </c>
+      <c r="O415" t="str">
+        <v/>
+      </c>
+      <c r="P415" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>YAM020</v>
+      </c>
+      <c r="B416">
+        <v>112</v>
+      </c>
+      <c r="C416" t="str">
+        <v>6″ Senko 5pk</v>
+      </c>
+      <c r="D416" t="str">
+        <v>6″ Senko 5pk</v>
+      </c>
+      <c r="E416" t="str">
+        <v/>
+      </c>
+      <c r="F416" t="str">
+        <v/>
+      </c>
+      <c r="G416" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H416" t="str">
+        <v/>
+      </c>
+      <c r="I416" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J416" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K416" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_6__senko_5pk.jpg</v>
+      </c>
+      <c r="L416" t="str">
+        <v>2026-04-10T10:18:55.387Z</v>
+      </c>
+      <c r="M416" t="str">
+        <v>2026-04-10T10:18:55.387Z</v>
+      </c>
+      <c r="N416" t="str">
+        <v/>
+      </c>
+      <c r="O416" t="str">
+        <v/>
+      </c>
+      <c r="P416" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>YAM021</v>
+      </c>
+      <c r="B417">
+        <v>112</v>
+      </c>
+      <c r="C417" t="str">
+        <v>4″ Senko 10pk</v>
+      </c>
+      <c r="D417" t="str">
+        <v>4″ Senko 10pk</v>
+      </c>
+      <c r="E417" t="str">
+        <v/>
+      </c>
+      <c r="F417" t="str">
+        <v/>
+      </c>
+      <c r="G417" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H417" t="str">
+        <v/>
+      </c>
+      <c r="I417" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J417" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K417" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__senko_10pk.jpg</v>
+      </c>
+      <c r="L417" t="str">
+        <v>2026-04-10T10:18:57.476Z</v>
+      </c>
+      <c r="M417" t="str">
+        <v>2026-04-10T10:18:57.476Z</v>
+      </c>
+      <c r="N417" t="str">
+        <v/>
+      </c>
+      <c r="O417" t="str">
+        <v/>
+      </c>
+      <c r="P417" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>YAM022</v>
+      </c>
+      <c r="B418">
+        <v>112</v>
+      </c>
+      <c r="C418" t="str">
+        <v>5″ Senko 10pk</v>
+      </c>
+      <c r="D418" t="str">
+        <v>5″ Senko 10pk</v>
+      </c>
+      <c r="E418" t="str">
+        <v/>
+      </c>
+      <c r="F418" t="str">
+        <v/>
+      </c>
+      <c r="G418" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H418" t="str">
+        <v/>
+      </c>
+      <c r="I418" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J418" t="str">
+        <v>wacky</v>
+      </c>
+      <c r="K418" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_10pk.jpg</v>
+      </c>
+      <c r="L418" t="str">
+        <v>2026-04-10T10:18:59.215Z</v>
+      </c>
+      <c r="M418" t="str">
+        <v>2026-04-10T10:18:59.215Z</v>
+      </c>
+      <c r="N418" t="str">
+        <v/>
+      </c>
+      <c r="O418" t="str">
+        <v/>
+      </c>
+      <c r="P418" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>YAM023</v>
+      </c>
+      <c r="B419">
+        <v>112</v>
+      </c>
+      <c r="C419" t="str">
+        <v>Fat Shad Shape Worm 8pk</v>
+      </c>
+      <c r="D419" t="str">
+        <v>Fat Shad Shape Worm 8pk</v>
+      </c>
+      <c r="E419" t="str">
+        <v/>
+      </c>
+      <c r="F419" t="str">
+        <v/>
+      </c>
+      <c r="G419" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H419" t="str">
+        <v/>
+      </c>
+      <c r="I419" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J419" t="str">
+        <v>crawling</v>
+      </c>
+      <c r="K419" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fat_shad_shape_worm_8pk.jpg</v>
+      </c>
+      <c r="L419" t="str">
+        <v>2026-04-10T10:19:00.636Z</v>
+      </c>
+      <c r="M419" t="str">
+        <v>2026-04-10T10:19:00.636Z</v>
+      </c>
+      <c r="N419" t="str">
+        <v/>
+      </c>
+      <c r="O419" t="str">
+        <v/>
+      </c>
+      <c r="P419" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>YAM024</v>
+      </c>
+      <c r="B420">
+        <v>112</v>
+      </c>
+      <c r="C420" t="str">
+        <v>Shad Shape Worm 10pk</v>
+      </c>
+      <c r="D420" t="str">
+        <v>Shad Shape Worm 10pk</v>
+      </c>
+      <c r="E420" t="str">
+        <v/>
+      </c>
+      <c r="F420" t="str">
+        <v/>
+      </c>
+      <c r="G420" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H420" t="str">
+        <v/>
+      </c>
+      <c r="I420" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J420" t="str">
+        <v>crawling</v>
+      </c>
+      <c r="K420" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_worm_10pk.jpg</v>
+      </c>
+      <c r="L420" t="str">
+        <v>2026-04-10T10:19:02.734Z</v>
+      </c>
+      <c r="M420" t="str">
+        <v>2026-04-10T10:19:02.734Z</v>
+      </c>
+      <c r="N420" t="str">
+        <v/>
+      </c>
+      <c r="O420" t="str">
+        <v/>
+      </c>
+      <c r="P420" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>YAM025</v>
+      </c>
+      <c r="B421">
+        <v>112</v>
+      </c>
+      <c r="C421" t="str">
+        <v>Kut Tail Worm</v>
+      </c>
+      <c r="D421" t="str">
+        <v>Kut Tail Worm</v>
+      </c>
+      <c r="E421" t="str">
+        <v/>
+      </c>
+      <c r="F421" t="str">
+        <v/>
+      </c>
+      <c r="G421" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H421" t="str">
+        <v/>
+      </c>
+      <c r="I421" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J421" t="str">
+        <v>crawling</v>
+      </c>
+      <c r="K421" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_kut_tail_worm.jpg</v>
+      </c>
+      <c r="L421" t="str">
+        <v>2026-04-10T10:19:04.912Z</v>
+      </c>
+      <c r="M421" t="str">
+        <v>2026-04-10T10:19:04.912Z</v>
+      </c>
+      <c r="N421" t="str">
+        <v/>
+      </c>
+      <c r="O421" t="str">
+        <v/>
+      </c>
+      <c r="P421" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>YAM026</v>
+      </c>
+      <c r="B422">
+        <v>112</v>
+      </c>
+      <c r="C422" t="str">
+        <v>6.5″ Sensei Worm 10pk</v>
+      </c>
+      <c r="D422" t="str">
+        <v>6.5″ Sensei Worm 10pk</v>
+      </c>
+      <c r="E422" t="str">
+        <v/>
+      </c>
+      <c r="F422" t="str">
+        <v/>
+      </c>
+      <c r="G422" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H422" t="str">
+        <v/>
+      </c>
+      <c r="I422" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J422" t="str">
+        <v>crawling</v>
+      </c>
+      <c r="K422" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_6_5__sensei_worm_10pk.jpg</v>
+      </c>
+      <c r="L422" t="str">
+        <v>2026-04-10T10:19:07.068Z</v>
+      </c>
+      <c r="M422" t="str">
+        <v>2026-04-10T10:19:07.068Z</v>
+      </c>
+      <c r="N422" t="str">
+        <v/>
+      </c>
+      <c r="O422" t="str">
+        <v/>
+      </c>
+      <c r="P422" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>YAM027</v>
+      </c>
+      <c r="B423">
+        <v>112</v>
+      </c>
+      <c r="C423" t="str">
+        <v>Oki Worm 6pk</v>
+      </c>
+      <c r="D423" t="str">
+        <v>Oki Worm 6pk</v>
+      </c>
+      <c r="E423" t="str">
+        <v/>
+      </c>
+      <c r="F423" t="str">
+        <v/>
+      </c>
+      <c r="G423" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H423" t="str">
+        <v/>
+      </c>
+      <c r="I423" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J423" t="str">
+        <v>crawling</v>
+      </c>
+      <c r="K423" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_oki_worm_6pk.jpg</v>
+      </c>
+      <c r="L423" t="str">
+        <v>2026-04-10T10:19:10.212Z</v>
+      </c>
+      <c r="M423" t="str">
+        <v>2026-04-10T10:19:10.212Z</v>
+      </c>
+      <c r="N423" t="str">
+        <v/>
+      </c>
+      <c r="O423" t="str">
+        <v/>
+      </c>
+      <c r="P423" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>YAM028</v>
+      </c>
+      <c r="B424">
+        <v>112</v>
+      </c>
+      <c r="C424" t="str">
+        <v>Ichi Worm 6pk</v>
+      </c>
+      <c r="D424" t="str">
+        <v>Ichi Worm 6pk</v>
+      </c>
+      <c r="E424" t="str">
+        <v/>
+      </c>
+      <c r="F424" t="str">
+        <v/>
+      </c>
+      <c r="G424" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H424" t="str">
+        <v/>
+      </c>
+      <c r="I424" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J424" t="str">
+        <v>crawling</v>
+      </c>
+      <c r="K424" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_ichi_worm_6pk.jpg</v>
+      </c>
+      <c r="L424" t="str">
+        <v>2026-04-10T10:19:12.347Z</v>
+      </c>
+      <c r="M424" t="str">
+        <v>2026-04-10T10:19:12.347Z</v>
+      </c>
+      <c r="N424" t="str">
+        <v/>
+      </c>
+      <c r="O424" t="str">
+        <v/>
+      </c>
+      <c r="P424" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>YAM029</v>
+      </c>
+      <c r="B425">
+        <v>112</v>
+      </c>
+      <c r="C425" t="str">
+        <v>Slinko Floater</v>
+      </c>
+      <c r="D425" t="str">
+        <v>Slinko Floater</v>
+      </c>
+      <c r="E425" t="str">
+        <v/>
+      </c>
+      <c r="F425" t="str">
+        <v/>
+      </c>
+      <c r="G425" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H425" t="str">
+        <v/>
+      </c>
+      <c r="I425" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J425" t="str">
+        <v>crawling</v>
+      </c>
+      <c r="K425" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_slinko_floater.jpg</v>
+      </c>
+      <c r="L425" t="str">
+        <v>2026-04-10T10:19:15.237Z</v>
+      </c>
+      <c r="M425" t="str">
+        <v>2026-04-10T10:19:15.237Z</v>
+      </c>
+      <c r="N425" t="str">
+        <v/>
+      </c>
+      <c r="O425" t="str">
+        <v/>
+      </c>
+      <c r="P425" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>YAM030</v>
+      </c>
+      <c r="B426">
+        <v>112</v>
+      </c>
+      <c r="C426" t="str">
+        <v>5″ Shad Shape Floater 8pk</v>
+      </c>
+      <c r="D426" t="str">
+        <v>5″ Shad Shape Floater 8pk</v>
+      </c>
+      <c r="E426" t="str">
+        <v/>
+      </c>
+      <c r="F426" t="str">
+        <v/>
+      </c>
+      <c r="G426" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H426" t="str">
+        <v/>
+      </c>
+      <c r="I426" t="str">
+        <v>bottom</v>
+      </c>
+      <c r="J426" t="str">
+        <v>crawling</v>
+      </c>
+      <c r="K426" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__shad_shape_floater_8pk.jpg</v>
+      </c>
+      <c r="L426" t="str">
+        <v>2026-04-10T10:19:17.364Z</v>
+      </c>
+      <c r="M426" t="str">
+        <v>2026-04-10T10:19:17.364Z</v>
+      </c>
+      <c r="N426" t="str">
+        <v/>
+      </c>
+      <c r="O426" t="str">
+        <v/>
+      </c>
+      <c r="P426" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>YAM031</v>
+      </c>
+      <c r="B427">
+        <v>112</v>
+      </c>
+      <c r="C427" t="str">
+        <v>3.5″ Shinobi Grub 8pk</v>
+      </c>
+      <c r="D427" t="str">
+        <v>3.5″ Shinobi Grub 8pk</v>
+      </c>
+      <c r="E427" t="str">
+        <v/>
+      </c>
+      <c r="F427" t="str">
+        <v/>
+      </c>
+      <c r="G427" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H427" t="str">
+        <v/>
+      </c>
+      <c r="I427" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J427" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K427" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_5__shinobi_grub_8pk.jpg</v>
+      </c>
+      <c r="L427" t="str">
+        <v>2026-04-10T10:19:20.468Z</v>
+      </c>
+      <c r="M427" t="str">
+        <v>2026-04-10T10:19:20.468Z</v>
+      </c>
+      <c r="N427" t="str">
+        <v/>
+      </c>
+      <c r="O427" t="str">
+        <v/>
+      </c>
+      <c r="P427" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>YAM032</v>
+      </c>
+      <c r="B428">
+        <v>112</v>
+      </c>
+      <c r="C428" t="str">
+        <v>Hula Grub Bundle – 50pc Assortment</v>
+      </c>
+      <c r="D428" t="str">
+        <v>Hula Grub Bundle – 50pc Assortment</v>
+      </c>
+      <c r="E428" t="str">
+        <v/>
+      </c>
+      <c r="F428" t="str">
+        <v/>
+      </c>
+      <c r="G428" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H428" t="str">
+        <v/>
+      </c>
+      <c r="I428" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J428" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K428" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hula_grub_bundle___50pc_assortment.jpg</v>
+      </c>
+      <c r="L428" t="str">
+        <v>2026-04-10T10:19:23.545Z</v>
+      </c>
+      <c r="M428" t="str">
+        <v>2026-04-10T10:19:23.545Z</v>
+      </c>
+      <c r="N428" t="str">
+        <v/>
+      </c>
+      <c r="O428" t="str">
+        <v/>
+      </c>
+      <c r="P428" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>YAM033</v>
+      </c>
+      <c r="B429">
+        <v>112</v>
+      </c>
+      <c r="C429" t="str">
+        <v>Yamatanuki</v>
+      </c>
+      <c r="D429" t="str">
+        <v>Yamatanuki</v>
+      </c>
+      <c r="E429" t="str">
+        <v/>
+      </c>
+      <c r="F429" t="str">
+        <v/>
+      </c>
+      <c r="G429" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H429" t="str">
+        <v/>
+      </c>
+      <c r="I429" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J429" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K429" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yamatanuki.jpg</v>
+      </c>
+      <c r="L429" t="str">
+        <v>2026-04-10T10:19:26.555Z</v>
+      </c>
+      <c r="M429" t="str">
+        <v>2026-04-10T10:19:26.555Z</v>
+      </c>
+      <c r="N429" t="str">
+        <v/>
+      </c>
+      <c r="O429" t="str">
+        <v/>
+      </c>
+      <c r="P429" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>YAM034</v>
+      </c>
+      <c r="B430">
+        <v>112</v>
+      </c>
+      <c r="C430" t="str">
+        <v>Double Tail Hula Grub 10pk</v>
+      </c>
+      <c r="D430" t="str">
+        <v>Double Tail Hula Grub 10pk</v>
+      </c>
+      <c r="E430" t="str">
+        <v/>
+      </c>
+      <c r="F430" t="str">
+        <v/>
+      </c>
+      <c r="G430" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H430" t="str">
+        <v/>
+      </c>
+      <c r="I430" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J430" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K430" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_double_tail_hula_grub_10pk.jpg</v>
+      </c>
+      <c r="L430" t="str">
+        <v>2026-04-10T10:19:28.669Z</v>
+      </c>
+      <c r="M430" t="str">
+        <v>2026-04-10T10:19:28.669Z</v>
+      </c>
+      <c r="N430" t="str">
+        <v/>
+      </c>
+      <c r="O430" t="str">
+        <v/>
+      </c>
+      <c r="P430" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>YAM035</v>
+      </c>
+      <c r="B431">
+        <v>112</v>
+      </c>
+      <c r="C431" t="str">
+        <v>Double Tail Grub 20pk</v>
+      </c>
+      <c r="D431" t="str">
+        <v>Double Tail Grub 20pk</v>
+      </c>
+      <c r="E431" t="str">
+        <v/>
+      </c>
+      <c r="F431" t="str">
+        <v/>
+      </c>
+      <c r="G431" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H431" t="str">
+        <v/>
+      </c>
+      <c r="I431" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J431" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K431" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_double_tail_grub_20pk.jpg</v>
+      </c>
+      <c r="L431" t="str">
+        <v>2026-04-10T10:19:30.873Z</v>
+      </c>
+      <c r="M431" t="str">
+        <v>2026-04-10T10:19:30.873Z</v>
+      </c>
+      <c r="N431" t="str">
+        <v/>
+      </c>
+      <c r="O431" t="str">
+        <v/>
+      </c>
+      <c r="P431" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>YAM036</v>
+      </c>
+      <c r="B432">
+        <v>112</v>
+      </c>
+      <c r="C432" t="str">
+        <v>Single Tail Grub 20pk</v>
+      </c>
+      <c r="D432" t="str">
+        <v>Single Tail Grub 20pk</v>
+      </c>
+      <c r="E432" t="str">
+        <v/>
+      </c>
+      <c r="F432" t="str">
+        <v/>
+      </c>
+      <c r="G432" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H432" t="str">
+        <v/>
+      </c>
+      <c r="I432" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J432" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K432" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_single_tail_grub_20pk.jpg</v>
+      </c>
+      <c r="L432" t="str">
+        <v>2026-04-10T10:19:32.965Z</v>
+      </c>
+      <c r="M432" t="str">
+        <v>2026-04-10T10:19:32.965Z</v>
+      </c>
+      <c r="N432" t="str">
+        <v/>
+      </c>
+      <c r="O432" t="str">
+        <v/>
+      </c>
+      <c r="P432" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>YAM037</v>
+      </c>
+      <c r="B433">
+        <v>112</v>
+      </c>
+      <c r="C433" t="str">
+        <v>Shibo Swimmer</v>
+      </c>
+      <c r="D433" t="str">
+        <v>Shibo Swimmer</v>
+      </c>
+      <c r="E433" t="str">
+        <v/>
+      </c>
+      <c r="F433" t="str">
+        <v/>
+      </c>
+      <c r="G433" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H433" t="str">
+        <v/>
+      </c>
+      <c r="I433" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J433" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K433" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shibo_swimmer.jpg</v>
+      </c>
+      <c r="L433" t="str">
+        <v>2026-04-10T10:19:37.985Z</v>
+      </c>
+      <c r="M433" t="str">
+        <v>2026-04-10T10:19:37.985Z</v>
+      </c>
+      <c r="N433" t="str">
+        <v/>
+      </c>
+      <c r="O433" t="str">
+        <v/>
+      </c>
+      <c r="P433" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>YAM038</v>
+      </c>
+      <c r="B434">
+        <v>112</v>
+      </c>
+      <c r="C434" t="str">
+        <v>Hinge Minnow</v>
+      </c>
+      <c r="D434" t="str">
+        <v>Hinge Minnow</v>
+      </c>
+      <c r="E434" t="str">
+        <v/>
+      </c>
+      <c r="F434" t="str">
+        <v/>
+      </c>
+      <c r="G434" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H434" t="str">
+        <v/>
+      </c>
+      <c r="I434" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J434" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K434" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hinge_minnow.jpg</v>
+      </c>
+      <c r="L434" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="M434" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="N434" t="str">
+        <v/>
+      </c>
+      <c r="O434" t="str">
+        <v/>
+      </c>
+      <c r="P434" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>YAM039</v>
+      </c>
+      <c r="B435">
+        <v>112</v>
+      </c>
+      <c r="C435" t="str">
+        <v>Zako Swimbait Kit – 84pc Assortment</v>
+      </c>
+      <c r="D435" t="str">
+        <v>Zako Swimbait Kit – 84pc Assortment</v>
+      </c>
+      <c r="E435" t="str">
+        <v/>
+      </c>
+      <c r="F435" t="str">
+        <v/>
+      </c>
+      <c r="G435" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H435" t="str">
+        <v/>
+      </c>
+      <c r="I435" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J435" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K435" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait_kit___84pc_assortment.jpg</v>
+      </c>
+      <c r="L435" t="str">
+        <v>2026-04-10T10:19:41.850Z</v>
+      </c>
+      <c r="M435" t="str">
+        <v>2026-04-10T10:19:41.850Z</v>
+      </c>
+      <c r="N435" t="str">
+        <v/>
+      </c>
+      <c r="O435" t="str">
+        <v/>
+      </c>
+      <c r="P435" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>YAM040</v>
+      </c>
+      <c r="B436">
+        <v>112</v>
+      </c>
+      <c r="C436" t="str">
+        <v>Zako Slim 6pk</v>
+      </c>
+      <c r="D436" t="str">
+        <v>Zako Slim 6pk</v>
+      </c>
+      <c r="E436" t="str">
+        <v/>
+      </c>
+      <c r="F436" t="str">
+        <v/>
+      </c>
+      <c r="G436" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H436" t="str">
+        <v/>
+      </c>
+      <c r="I436" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J436" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K436" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_slim_6pk.jpg</v>
+      </c>
+      <c r="L436" t="str">
+        <v>2026-04-10T10:19:43.096Z</v>
+      </c>
+      <c r="M436" t="str">
+        <v>2026-04-10T10:19:43.096Z</v>
+      </c>
+      <c r="N436" t="str">
+        <v/>
+      </c>
+      <c r="O436" t="str">
+        <v/>
+      </c>
+      <c r="P436" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>YAM041</v>
+      </c>
+      <c r="B437">
+        <v>112</v>
+      </c>
+      <c r="C437" t="str">
+        <v>Scope Shad</v>
+      </c>
+      <c r="D437" t="str">
+        <v>Scope Shad</v>
+      </c>
+      <c r="E437" t="str">
+        <v/>
+      </c>
+      <c r="F437" t="str">
+        <v/>
+      </c>
+      <c r="G437" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H437" t="str">
+        <v/>
+      </c>
+      <c r="I437" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J437" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K437" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_scope_shad.jpg</v>
+      </c>
+      <c r="L437" t="str">
+        <v>2026-04-10T10:19:45.246Z</v>
+      </c>
+      <c r="M437" t="str">
+        <v>2026-04-10T10:19:45.246Z</v>
+      </c>
+      <c r="N437" t="str">
+        <v/>
+      </c>
+      <c r="O437" t="str">
+        <v/>
+      </c>
+      <c r="P437" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>YAM042</v>
+      </c>
+      <c r="B438">
+        <v>112</v>
+      </c>
+      <c r="C438" t="str">
+        <v>Shad Shape Swimmer 8pk</v>
+      </c>
+      <c r="D438" t="str">
+        <v>Shad Shape Swimmer 8pk</v>
+      </c>
+      <c r="E438" t="str">
+        <v/>
+      </c>
+      <c r="F438" t="str">
+        <v/>
+      </c>
+      <c r="G438" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H438" t="str">
+        <v/>
+      </c>
+      <c r="I438" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J438" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K438" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_swimmer_8pk.jpg</v>
+      </c>
+      <c r="L438" t="str">
+        <v>2026-04-10T10:19:48.508Z</v>
+      </c>
+      <c r="M438" t="str">
+        <v>2026-04-10T10:19:48.508Z</v>
+      </c>
+      <c r="N438" t="str">
+        <v/>
+      </c>
+      <c r="O438" t="str">
+        <v/>
+      </c>
+      <c r="P438" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>YAM043</v>
+      </c>
+      <c r="B439">
+        <v>112</v>
+      </c>
+      <c r="C439" t="str">
+        <v>Zako Swimbait</v>
+      </c>
+      <c r="D439" t="str">
+        <v>Zako Swimbait</v>
+      </c>
+      <c r="E439" t="str">
+        <v/>
+      </c>
+      <c r="F439" t="str">
+        <v/>
+      </c>
+      <c r="G439" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H439" t="str">
+        <v/>
+      </c>
+      <c r="I439" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J439" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K439" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait.jpg</v>
+      </c>
+      <c r="L439" t="str">
+        <v>2026-04-10T10:19:50.589Z</v>
+      </c>
+      <c r="M439" t="str">
+        <v>2026-04-10T10:19:50.589Z</v>
+      </c>
+      <c r="N439" t="str">
+        <v/>
+      </c>
+      <c r="O439" t="str">
+        <v/>
+      </c>
+      <c r="P439" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>YAM044</v>
+      </c>
+      <c r="B440">
+        <v>112</v>
+      </c>
+      <c r="C440" t="str">
+        <v>4″ Zako Swimbait Bulk Packs</v>
+      </c>
+      <c r="D440" t="str">
+        <v>4″ Zako Swimbait Bulk Packs</v>
+      </c>
+      <c r="E440" t="str">
+        <v/>
+      </c>
+      <c r="F440" t="str">
+        <v/>
+      </c>
+      <c r="G440" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H440" t="str">
+        <v/>
+      </c>
+      <c r="I440" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J440" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K440" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__zako_swimbait_bulk_packs.jpg</v>
+      </c>
+      <c r="L440" t="str">
+        <v>2026-04-10T10:19:52.662Z</v>
+      </c>
+      <c r="M440" t="str">
+        <v>2026-04-10T10:19:52.662Z</v>
+      </c>
+      <c r="N440" t="str">
+        <v/>
+      </c>
+      <c r="O440" t="str">
+        <v/>
+      </c>
+      <c r="P440" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>YAM045</v>
+      </c>
+      <c r="B441">
+        <v>112</v>
+      </c>
+      <c r="C441" t="str">
+        <v>4″ Paddle Tail Zako 5pk</v>
+      </c>
+      <c r="D441" t="str">
+        <v>4″ Paddle Tail Zako 5pk</v>
+      </c>
+      <c r="E441" t="str">
+        <v/>
+      </c>
+      <c r="F441" t="str">
+        <v/>
+      </c>
+      <c r="G441" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H441" t="str">
+        <v/>
+      </c>
+      <c r="I441" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J441" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K441" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__paddle_tail_zako_5pk.jpg</v>
+      </c>
+      <c r="L441" t="str">
+        <v>2026-04-10T10:19:55.958Z</v>
+      </c>
+      <c r="M441" t="str">
+        <v>2026-04-10T10:19:55.958Z</v>
+      </c>
+      <c r="N441" t="str">
+        <v/>
+      </c>
+      <c r="O441" t="str">
+        <v/>
+      </c>
+      <c r="P441" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>YAM046</v>
+      </c>
+      <c r="B442">
+        <v>112</v>
+      </c>
+      <c r="C442" t="str">
+        <v>5″ D-Shad 7pk</v>
+      </c>
+      <c r="D442" t="str">
+        <v>5″ D-Shad 7pk</v>
+      </c>
+      <c r="E442" t="str">
+        <v/>
+      </c>
+      <c r="F442" t="str">
+        <v/>
+      </c>
+      <c r="G442" t="str">
+        <v>softbait</v>
+      </c>
+      <c r="H442" t="str">
+        <v/>
+      </c>
+      <c r="I442" t="str">
+        <v>subsurface</v>
+      </c>
+      <c r="J442" t="str">
+        <v>swimming</v>
+      </c>
+      <c r="K442" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__d_shad_7pk.jpg</v>
+      </c>
+      <c r="L442" t="str">
+        <v>2026-04-10T10:19:57.724Z</v>
+      </c>
+      <c r="M442" t="str">
+        <v>2026-04-10T10:19:57.724Z</v>
+      </c>
+      <c r="N442" t="str">
+        <v/>
+      </c>
+      <c r="O442" t="str">
+        <v/>
+      </c>
+      <c r="P442" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O396"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P442"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P442"/>
+  <dimension ref="A1:P453"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -20204,7 +20204,7 @@
         <v>YAM001</v>
       </c>
       <c r="B397">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C397" t="str">
         <v>Fuzzy Senko</v>
@@ -20219,34 +20219,28 @@
         <v/>
       </c>
       <c r="G397" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H397" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I397" t="str">
-        <v>subsurface</v>
+        <v>Variable</v>
       </c>
       <c r="J397" t="str">
-        <v>swimming</v>
+        <v>worm</v>
       </c>
       <c r="K397" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_senko.jpg</v>
       </c>
       <c r="L397" t="str">
-        <v>2026-04-10T10:18:14.137Z</v>
+        <v>2026-04-10T10:42:44.627Z</v>
       </c>
       <c r="M397" t="str">
-        <v>2026-04-10T10:18:14.137Z</v>
+        <v>2026-04-10T10:42:44.627Z</v>
       </c>
       <c r="N397" t="str">
-        <v/>
-      </c>
-      <c r="O397" t="str">
-        <v/>
-      </c>
-      <c r="P397" t="str">
-        <v/>
+        <v>It’s the gold standard by which all stick baits are judged, but fuzzy. The Fuzzy Senko from Yamamoto Baits is exactly what it sounds like. The legendary Senko is now outfitted with threaded fine skirt material to create a new profile and tantalizing secondary action. The Fuzzy Senko is available in both 4" and 5" sizes, coming 5 and 4 per pack respectively, and can be found in 8 proven colors.</v>
       </c>
     </row>
     <row r="398">
@@ -20254,7 +20248,7 @@
         <v>YAM002</v>
       </c>
       <c r="B398">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C398" t="str">
         <v>Fuzzy Nuki</v>
@@ -20269,34 +20263,28 @@
         <v/>
       </c>
       <c r="G398" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H398" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I398" t="str">
-        <v>subsurface</v>
+        <v>Variable</v>
       </c>
       <c r="J398" t="str">
-        <v>swimming</v>
+        <v>worm</v>
       </c>
       <c r="K398" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_nuki.jpg</v>
       </c>
       <c r="L398" t="str">
-        <v>2026-04-10T10:18:16.243Z</v>
+        <v>2026-04-10T10:42:45.804Z</v>
       </c>
       <c r="M398" t="str">
-        <v>2026-04-10T10:18:16.243Z</v>
+        <v>2026-04-10T10:42:45.804Z</v>
       </c>
       <c r="N398" t="str">
-        <v/>
-      </c>
-      <c r="O398" t="str">
-        <v/>
-      </c>
-      <c r="P398" t="str">
-        <v/>
+        <v>The Yamatanuki just got fuzzy. The ultimate “heavy plastic” bait has joined the fuzzy bait family, now threaded with strands of fine skirt material to create a totally new profile and action. Just as much as it catches your eye, it also catches fish. Available in 8 Yamamoto colors, the Fuzzy Nuki is available in both 2.5" and 3.5" sizes. Pack Size: 2.5" - 5/pack 3.5" - 4/pack</v>
       </c>
     </row>
     <row r="399">
@@ -20304,7 +20292,7 @@
         <v>YAM003</v>
       </c>
       <c r="B399">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C399" t="str">
         <v>Fuzzy Nut 6pk</v>
@@ -20319,34 +20307,28 @@
         <v/>
       </c>
       <c r="G399" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H399" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I399" t="str">
-        <v>subsurface</v>
+        <v>Variable</v>
       </c>
       <c r="J399" t="str">
-        <v>swimming</v>
+        <v>worm</v>
       </c>
       <c r="K399" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_nut_6pk.jpg</v>
       </c>
       <c r="L399" t="str">
-        <v>2026-04-10T10:18:18.376Z</v>
+        <v>2026-04-10T10:42:58.235Z</v>
       </c>
       <c r="M399" t="str">
-        <v>2026-04-10T10:18:18.376Z</v>
+        <v>2026-04-10T10:42:58.235Z</v>
       </c>
       <c r="N399" t="str">
-        <v/>
-      </c>
-      <c r="O399" t="str">
-        <v/>
-      </c>
-      <c r="P399" t="str">
-        <v/>
+        <v>The Yamamoto Fuzzy Nut appears odd at first glance, but once you see it in the water and see how the fish react to it, you’ll look at it in an all-new light. The 1.5" Fuzzy Nut lives up to its name thanks to its threaded skirt material providing a very subtle secondary action. It is the perfect length to completely conceal a nail weight, while the heavyweight Yamamoto salted formula allows for the perfect fall rate. Especially killer on smallmouth and spotted bass, the Fuzzy Nut comes 6 per pack in 10 irresistible Yamamoto colors.</v>
       </c>
     </row>
     <row r="400">
@@ -20354,7 +20336,7 @@
         <v>YAM004</v>
       </c>
       <c r="B400">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C400" t="str">
         <v>Uni</v>
@@ -20369,34 +20351,28 @@
         <v/>
       </c>
       <c r="G400" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H400" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I400" t="str">
-        <v>subsurface</v>
+        <v>Variable</v>
       </c>
       <c r="J400" t="str">
-        <v>swimming</v>
+        <v>worm</v>
       </c>
       <c r="K400" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_uni.jpg</v>
       </c>
       <c r="L400" t="str">
-        <v>2026-04-10T10:18:20.464Z</v>
+        <v>2026-04-10T10:42:59.418Z</v>
       </c>
       <c r="M400" t="str">
-        <v>2026-04-10T10:18:20.464Z</v>
+        <v>2026-04-10T10:42:59.418Z</v>
       </c>
       <c r="N400" t="str">
-        <v/>
-      </c>
-      <c r="O400" t="str">
-        <v/>
-      </c>
-      <c r="P400" t="str">
-        <v/>
+        <v>The Yamamoto Uni is designed to be irresistible to bass. A TPE urchin-style bait, the Uni features bulbed appendages that catch water and shimmy with each twitch of the rod tip, falling with a very lifelike quiver. The custom Yamamoto TPE formula allows for a flexible yet durable bait that delivers the perfect buoyancy and action, while holding up fish after fish. If you're looking for a profile and action that fish have absolutely never seen before the Uni is your ticket to triggering more bites. 1 per pack.</v>
       </c>
     </row>
     <row r="401">
@@ -20404,7 +20380,7 @@
         <v>YAM005</v>
       </c>
       <c r="B401">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C401" t="str">
         <v>Ultimate Senko Kit – 100pc Assortment</v>
@@ -20419,34 +20395,28 @@
         <v/>
       </c>
       <c r="G401" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H401" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I401" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J401" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K401" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_ultimate_senko_kit___100pc_assortment.jpg</v>
       </c>
       <c r="L401" t="str">
-        <v>2026-04-10T10:18:23.621Z</v>
+        <v>2026-04-10T10:43:01.210Z</v>
       </c>
       <c r="M401" t="str">
-        <v>2026-04-10T10:18:23.621Z</v>
+        <v>2026-04-10T10:43:01.210Z</v>
       </c>
       <c r="N401" t="str">
-        <v/>
-      </c>
-      <c r="O401" t="str">
-        <v/>
-      </c>
-      <c r="P401" t="str">
-        <v/>
+        <v>The Ultimate Senko Kit is loaded with every size of the original Senko, the 4",5", 6" and the 7". Get a Senko for every situation. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 305 - Baby Bass 10/pc 306 - Natural Shad 10/pc 194 - Watermelon With Large Black 10/pc 912 - Green Pumpkin/Watermelon 10/pc 021 - Black With Large Blue 10/pc 363 - Green Pumpkin Blue 10/pc 963 - Gooseberry Laminate 5/pc 208 - Watermelon With Black &amp; Red Flake 5/pc 318 - Green Pumpkin With Large Red 5/pc 301 - Green Pumpkin With Large Green And Large Purple 5/pc 330 - Green Pumpkin With Purple and Small Copper 5/pc 925 - Green Pumpkin With Small Red / 042J Laminate 5/pc 297 - Green Pumpkin With Large Black</v>
       </c>
     </row>
     <row r="402">
@@ -20454,7 +20424,7 @@
         <v>YAM006</v>
       </c>
       <c r="B402">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C402" t="str">
         <v>Senko Kit – 160pc Assortment</v>
@@ -20469,34 +20439,28 @@
         <v/>
       </c>
       <c r="G402" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H402" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I402" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J402" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K402" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_kit___160pc_assortment.jpg</v>
       </c>
       <c r="L402" t="str">
-        <v>2026-04-10T10:18:25.835Z</v>
+        <v>2026-04-10T10:43:02.450Z</v>
       </c>
       <c r="M402" t="str">
-        <v>2026-04-10T10:18:25.835Z</v>
+        <v>2026-04-10T10:43:02.450Z</v>
       </c>
       <c r="N402" t="str">
-        <v/>
-      </c>
-      <c r="O402" t="str">
-        <v/>
-      </c>
-      <c r="P402" t="str">
-        <v/>
+        <v>The 5" Senko Kit is the big brother of our Senko Bundle. This Senko Kit comes loaded with 16 different bags of 5" Senkos, giving you a color for whatever conditions you find yourself in. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 213 - June Bug - Purple With Emerald Flake 10/pc 363 - Green Pumpkin Blue 10/pc 020 - Black 10/pc 355 - Green Pumpkin Magic 10/pc 297 - Green Pumpkin Pepper 10/pc 912 - Green Pumpkin/Watermelon 10/pc 305 - Baby Bass 10/pc 918 - Peanut Butter And Jelly 017/213 Laminate 10/pc 337 - Watermelon With Red 10/pc 963 - Gooseberry Laminate 10/pc 904 - Blue And Black Laminate 10/pc 952 - Bama Bug 10/pc 964 - Watermelon Slice Laminate 10/pc 356 - Plum Apple 10/pc 547 - 297/192 Tip 10/pc 306 - Natural Shad</v>
       </c>
     </row>
     <row r="403">
@@ -20504,7 +20468,7 @@
         <v>YAM007</v>
       </c>
       <c r="B403">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C403" t="str">
         <v>5″ Senko Baitfish Bundle – 50pc Assortment</v>
@@ -20519,34 +20483,28 @@
         <v/>
       </c>
       <c r="G403" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H403" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I403" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J403" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K403" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_baitfish_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L403" t="str">
-        <v>2026-04-10T10:18:27.985Z</v>
+        <v>2026-04-10T10:43:03.622Z</v>
       </c>
       <c r="M403" t="str">
-        <v>2026-04-10T10:18:27.985Z</v>
+        <v>2026-04-10T10:43:03.622Z</v>
       </c>
       <c r="N403" t="str">
-        <v/>
-      </c>
-      <c r="O403" t="str">
-        <v/>
-      </c>
-      <c r="P403" t="str">
-        <v/>
+        <v>Packed with 50 of the legendary 5” Senkos, this bundle is all about matching local forage. Each color is hand-picked to mimic common baitfish, giving you an edge when targeting bass that are keyed in on local forage. A go-to for pros and weekend anglers alike, the Senko’s unmatched action and versatility make it the top soft plastic in the game. Grab the Baitfish Bundle and be ready for any bass bite that comes your way. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 5" Senko, 305 - Baby Bass 10/pc 5" Senko, 967 - Goby 10/pc 5" Senko, 306 - Natural Shad 10/pc 5" Senko, 968 - Perch 10/pc 5" Senko, 9008 - Green Gizzard</v>
       </c>
     </row>
     <row r="404">
@@ -20554,7 +20512,7 @@
         <v>YAM008</v>
       </c>
       <c r="B404">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C404" t="str">
         <v>5″ Senko Green Pumpkin Bundle – 50pc Assortment</v>
@@ -20569,34 +20527,28 @@
         <v/>
       </c>
       <c r="G404" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H404" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I404" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J404" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K404" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_green_pumpkin_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L404" t="str">
-        <v>2026-04-10T10:18:30.130Z</v>
+        <v>2026-04-10T10:43:04.872Z</v>
       </c>
       <c r="M404" t="str">
-        <v>2026-04-10T10:18:30.130Z</v>
+        <v>2026-04-10T10:43:04.872Z</v>
       </c>
       <c r="N404" t="str">
-        <v/>
-      </c>
-      <c r="O404" t="str">
-        <v/>
-      </c>
-      <c r="P404" t="str">
-        <v/>
+        <v>This bundle includes 50 of the legendary 5” Senkos in five proven Green Pumpkin variations—one of the most reliable and versatile color groups in bass fishing. Known for their natural appeal, Green Pumpkin tones effectively mimic a wide range of baitfish and forage, making them a must-have in any tackle box. Trusted by pros and weekend anglers alike, the Senko delivers unmatched action and consistent results. Load up with the Pumpkin Bundle and stay ready for any bass bite, anytime. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 5" Senko, 297 - Green Pumpkin with Black Flake 10/pc 5" Senko, 912 - Green Pumpkin with Watermelon 10/pc 5" Senko, 301 - #297 NF/LG Green Pumpkin 10/pc 5" Senko, 355 - Green Pumpkin Magic 10/pc 5" Senko, 925 - Green Pumpkin with red Flake/042J</v>
       </c>
     </row>
     <row r="405">
@@ -20604,7 +20556,7 @@
         <v>YAM009</v>
       </c>
       <c r="B405">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C405" t="str">
         <v>Senko Bundle – 90pc Assortment</v>
@@ -20619,34 +20571,28 @@
         <v/>
       </c>
       <c r="G405" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H405" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I405" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J405" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K405" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_bundle___90pc_assortment.jpg</v>
       </c>
       <c r="L405" t="str">
-        <v>2026-04-10T10:18:33.272Z</v>
+        <v>2026-04-10T10:43:06.043Z</v>
       </c>
       <c r="M405" t="str">
-        <v>2026-04-10T10:18:33.272Z</v>
+        <v>2026-04-10T10:43:06.043Z</v>
       </c>
       <c r="N405" t="str">
-        <v/>
-      </c>
-      <c r="O405" t="str">
-        <v/>
-      </c>
-      <c r="P405" t="str">
-        <v/>
+        <v>The original soft stick bait just got better. Stock up on Senkos from some classic colors to some new ones you may not have tried yet. This 90pc assortment will not dissappoint. *Kits are subject to change based on availability refer to chart below for the most up to date offering 1/bag 5" SENKO / 10 PACK / WATERMELON W/ CREAM LAMINATE 1/bag 5" SENKO / 10 PACK / WATERMELON W/ RED FLAKE 1/bag 5" SENKO / 10 PACK / BLACK W/ LARGE BLUE FLAKE 1/bag 5" SENKO / 10 PACK / GREEN PUMPKIN MAGIC 1/bag 5" SENKO / 10 PACK / B-BUG GRINDER 1/bag 5" SENKO / 10 PACK / BAMA BUG 1/bag 5" SENKO / 10 PACK / PRO BLUE 1/bag 5" SENKO / 10 PACK / GREEN PUMPKIN BLACK FLAKE 1/bag 5" SENKO / 10 PACK / JUNE BUG PURPLE W/ EMERALD FLAKE</v>
       </c>
     </row>
     <row r="406">
@@ -20654,7 +20600,7 @@
         <v>YAM010</v>
       </c>
       <c r="B406">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C406" t="str">
         <v>Fat Senko 10pk</v>
@@ -20669,34 +20615,28 @@
         <v/>
       </c>
       <c r="G406" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H406" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I406" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J406" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K406" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fat_senko_10pk.jpg</v>
       </c>
       <c r="L406" t="str">
-        <v>2026-04-10T10:18:35.432Z</v>
+        <v>2026-04-10T10:43:07.273Z</v>
       </c>
       <c r="M406" t="str">
-        <v>2026-04-10T10:18:35.432Z</v>
+        <v>2026-04-10T10:43:07.273Z</v>
       </c>
       <c r="N406" t="str">
-        <v/>
-      </c>
-      <c r="O406" t="str">
-        <v/>
-      </c>
-      <c r="P406" t="str">
-        <v/>
+        <v>Rounding out Yamamoto’s extensive line-up of soft plastics, the Yamamoto Fat Senko provides an incredibly versatile, slightly chunkier profile that will have your livewell overflowing. Similar to the traditional Senko, the Yamamoto Fat Senko features a plumped-up stickbait construction that imparts time-tested, subtle Senko action. Incredibly effective weightless, on a shakey head, neko rig, and much more, the Yamamoto Fat Senko delivers a slightly different look that can be the key to unlocking the bite. More thickness also means increased angler visibility on sonar screens with forward-facing sonar techniques, the Fat Senko also improves success when fishing in windy conditions compared to the original due to its increased weight. Available in Yamamoto’s proven Senko color schemes, the Yamamoto Fat Senko continues to deliver the same bass-catching performance that anglers trust with additional features to help you catch more fish. 10 per pack</v>
       </c>
     </row>
     <row r="407">
@@ -20704,7 +20644,7 @@
         <v>YAM011</v>
       </c>
       <c r="B407">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C407" t="str">
         <v>Swimming Senko</v>
@@ -20719,34 +20659,28 @@
         <v/>
       </c>
       <c r="G407" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H407" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I407" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J407" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K407" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_swimming_senko.jpg</v>
       </c>
       <c r="L407" t="str">
-        <v>2026-04-10T10:18:36.702Z</v>
+        <v>2026-04-10T10:43:08.495Z</v>
       </c>
       <c r="M407" t="str">
-        <v>2026-04-10T10:18:36.702Z</v>
+        <v>2026-04-10T10:43:08.495Z</v>
       </c>
       <c r="N407" t="str">
-        <v/>
-      </c>
-      <c r="O407" t="str">
-        <v/>
-      </c>
-      <c r="P407" t="str">
-        <v/>
+        <v>A twist on a classic - the Swimming Senko is everything that's great about the legendary Senko, but with a little extra magic. Thanks to the tail, the Swimming Senko presents a hard-to-resist horizontal action that's more than enough to tempt a lunker to bite. The Swimming Senko marries the natural profile and subtleness of the Senko with the vibration and movement of a paddletail swimbait. The result is the perfect amount of subtle shimmy, and the perfect amount of kick. Available in 4 sizes ranging from 3.5" to 5.5" long, the Swimming Senko is a favorite of anglers everywhere. 3.5"- 7 Pack 4"- 10 Pack 5"- 10 Pack 5.5"- 7 Pack</v>
       </c>
     </row>
     <row r="408">
@@ -20754,7 +20688,7 @@
         <v>YAM012</v>
       </c>
       <c r="B408">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C408" t="str">
         <v>Senko Bulk Packs</v>
@@ -20769,34 +20703,28 @@
         <v/>
       </c>
       <c r="G408" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H408" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I408" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J408" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K408" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_bulk_packs.jpg</v>
       </c>
       <c r="L408" t="str">
-        <v>2026-04-10T10:18:38.783Z</v>
+        <v>2026-04-10T10:43:09.676Z</v>
       </c>
       <c r="M408" t="str">
-        <v>2026-04-10T10:18:38.783Z</v>
+        <v>2026-04-10T10:43:09.676Z</v>
       </c>
       <c r="N408" t="str">
-        <v/>
-      </c>
-      <c r="O408" t="str">
-        <v/>
-      </c>
-      <c r="P408" t="str">
-        <v/>
+        <v>The 5" Senko and 4" Senko are staples in the fishing world, and it's now available in our most popular colors in bulk packs of 50 or 100! The original soft-plastic stickbait is the #1 choice of anglers everywhere. "Iconic" is an understatement - the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
       </c>
     </row>
     <row r="409">
@@ -20804,7 +20732,7 @@
         <v>YAM013</v>
       </c>
       <c r="B409">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C409" t="str">
         <v>Megastrike Fish Attractant</v>
@@ -20819,34 +20747,28 @@
         <v/>
       </c>
       <c r="G409" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H409" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I409" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J409" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K409" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_megastrike_fish_attractant.jpg</v>
       </c>
       <c r="L409" t="str">
-        <v>2026-04-10T10:18:40.908Z</v>
+        <v>2026-04-10T10:43:10.851Z</v>
       </c>
       <c r="M409" t="str">
-        <v>2026-04-10T10:18:40.908Z</v>
+        <v>2026-04-10T10:43:10.851Z</v>
       </c>
       <c r="N409" t="str">
-        <v/>
-      </c>
-      <c r="O409" t="str">
-        <v/>
-      </c>
-      <c r="P409" t="str">
-        <v/>
+        <v>The MegaStrike Fish Attractant is comprised of the proper balance of Amino Acids and Proteins to make the fish strike, hold onto, and consume the product Extra long-lasting gel No mess tube Tube Size: 1 oz</v>
       </c>
     </row>
     <row r="410">
@@ -20854,7 +20776,7 @@
         <v>YAM014</v>
       </c>
       <c r="B410">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C410" t="str">
         <v>7″ Speed Senko 7pk</v>
@@ -20869,34 +20791,28 @@
         <v/>
       </c>
       <c r="G410" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H410" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I410" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J410" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K410" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_7__speed_senko_7pk.jpg</v>
       </c>
       <c r="L410" t="str">
-        <v>2026-04-10T10:18:43.146Z</v>
+        <v>2026-04-10T10:43:12.066Z</v>
       </c>
       <c r="M410" t="str">
-        <v>2026-04-10T10:18:43.146Z</v>
+        <v>2026-04-10T10:43:12.066Z</v>
       </c>
       <c r="N410" t="str">
-        <v/>
-      </c>
-      <c r="O410" t="str">
-        <v/>
-      </c>
-      <c r="P410" t="str">
-        <v/>
+        <v>The Speed Senko is sure to be your new favorite worm for covering water. Designed at the request of our pro’s, the Speed Senko is the ultimate worm for fishing grass and brush. Its thumping tail feels like a Colorado coming through the water and makes it easy for bass to zero in on it in grass, laydowns, brushpiles or any other cover. Try Texas rigging it with a light weight and swimming it over grass.. Or Texas rigged with a lift and drop retrieve in and around cover. This is one the fish will find, so you better find you some too! 7 per pack</v>
       </c>
     </row>
     <row r="411">
@@ -20904,7 +20820,7 @@
         <v>YAM015</v>
       </c>
       <c r="B411">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C411" t="str">
         <v>3″ Ned Senko 10pk</v>
@@ -20919,34 +20835,28 @@
         <v/>
       </c>
       <c r="G411" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H411" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I411" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J411" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K411" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3__ned_senko_10pk.jpg</v>
       </c>
       <c r="L411" t="str">
-        <v>2026-04-10T10:18:45.238Z</v>
+        <v>2026-04-10T10:43:13.291Z</v>
       </c>
       <c r="M411" t="str">
-        <v>2026-04-10T10:18:45.238Z</v>
+        <v>2026-04-10T10:43:13.291Z</v>
       </c>
       <c r="N411" t="str">
-        <v/>
-      </c>
-      <c r="O411" t="str">
-        <v/>
-      </c>
-      <c r="P411" t="str">
-        <v/>
+        <v>The exact same shape as the 3” fat Senko but built utilizing our “Mega Floater Formula” to make this bait stand up on a Ned head. The size is perfect. The shape is perfect and now the formula is perfect for Ned rigging. While the Original Senko formula is hands down the best for a lot of applications, it isn’t for Ned rigging. We designed this bait to have the same feel and texture of the time-tested Senko, but it floats making it stand up and be more visible when dancing around the bottom of your favorite fishing hole. The Yamamoto Ned Senko is available in 21 different fish catching colors. 10 Per Pack</v>
       </c>
     </row>
     <row r="412">
@@ -20954,7 +20864,7 @@
         <v>YAM016</v>
       </c>
       <c r="B412">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C412" t="str">
         <v>3″ Slim Senko 10pk</v>
@@ -20969,34 +20879,28 @@
         <v/>
       </c>
       <c r="G412" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H412" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I412" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J412" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K412" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3__slim_senko_10pk.jpg</v>
       </c>
       <c r="L412" t="str">
-        <v>2026-04-10T10:18:47.330Z</v>
+        <v>2026-04-10T10:43:14.466Z</v>
       </c>
       <c r="M412" t="str">
-        <v>2026-04-10T10:18:47.330Z</v>
+        <v>2026-04-10T10:43:14.466Z</v>
       </c>
       <c r="N412" t="str">
-        <v/>
-      </c>
-      <c r="O412" t="str">
-        <v/>
-      </c>
-      <c r="P412" t="str">
-        <v/>
+        <v>The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko. 10 per pack</v>
       </c>
     </row>
     <row r="413">
@@ -21004,7 +20908,7 @@
         <v>YAM017</v>
       </c>
       <c r="B413">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C413" t="str">
         <v>5″ Pro Senko 10pk</v>
@@ -21019,34 +20923,28 @@
         <v/>
       </c>
       <c r="G413" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H413" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I413" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J413" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K413" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__pro_senko_10pk.jpg</v>
       </c>
       <c r="L413" t="str">
-        <v>2026-04-10T10:18:49.421Z</v>
+        <v>2026-04-10T10:43:15.636Z</v>
       </c>
       <c r="M413" t="str">
-        <v>2026-04-10T10:18:49.421Z</v>
+        <v>2026-04-10T10:43:15.636Z</v>
       </c>
       <c r="N413" t="str">
-        <v/>
-      </c>
-      <c r="O413" t="str">
-        <v/>
-      </c>
-      <c r="P413" t="str">
-        <v/>
+        <v>The Yamamoto 5” Pro Senko Soft Bait tweaks the design of the world-famous Senko worm to provide anglers with a new way to fish this popular lure. The thinner construction and tapered tail give it a unique shaky worm action, while the redesigned head makes it easier to rig on shaky jigs or with a screw-in bullet sinker. Its versatility offers a great way to draw out the bigger fish from deeper water.</v>
       </c>
     </row>
     <row r="414">
@@ -21054,7 +20952,7 @@
         <v>YAM018</v>
       </c>
       <c r="B414">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C414" t="str">
         <v>5″ Thin Senko 10pk</v>
@@ -21069,34 +20967,28 @@
         <v/>
       </c>
       <c r="G414" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H414" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I414" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J414" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K414" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__thin_senko_10pk.jpg</v>
       </c>
       <c r="L414" t="str">
-        <v>2026-04-10T10:18:51.127Z</v>
+        <v>2026-04-10T10:43:16.934Z</v>
       </c>
       <c r="M414" t="str">
-        <v>2026-04-10T10:18:51.127Z</v>
+        <v>2026-04-10T10:43:16.934Z</v>
       </c>
       <c r="N414" t="str">
-        <v/>
-      </c>
-      <c r="O414" t="str">
-        <v/>
-      </c>
-      <c r="P414" t="str">
-        <v/>
+        <v>Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
       </c>
     </row>
     <row r="415">
@@ -21104,7 +20996,7 @@
         <v>YAM019</v>
       </c>
       <c r="B415">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C415" t="str">
         <v>7″ Senko 5pk</v>
@@ -21119,34 +21011,28 @@
         <v/>
       </c>
       <c r="G415" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H415" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I415" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J415" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K415" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_7__senko_5pk.jpg</v>
       </c>
       <c r="L415" t="str">
-        <v>2026-04-10T10:18:53.263Z</v>
+        <v>2026-04-10T10:43:18.214Z</v>
       </c>
       <c r="M415" t="str">
-        <v>2026-04-10T10:18:53.263Z</v>
+        <v>2026-04-10T10:43:18.214Z</v>
       </c>
       <c r="N415" t="str">
-        <v/>
-      </c>
-      <c r="O415" t="str">
-        <v/>
-      </c>
-      <c r="P415" t="str">
-        <v/>
+        <v>The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
       </c>
     </row>
     <row r="416">
@@ -21154,7 +21040,7 @@
         <v>YAM020</v>
       </c>
       <c r="B416">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C416" t="str">
         <v>6″ Senko 5pk</v>
@@ -21169,34 +21055,28 @@
         <v/>
       </c>
       <c r="G416" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H416" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I416" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J416" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K416" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_6__senko_5pk.jpg</v>
       </c>
       <c r="L416" t="str">
-        <v>2026-04-10T10:18:55.387Z</v>
+        <v>2026-04-10T10:43:19.631Z</v>
       </c>
       <c r="M416" t="str">
-        <v>2026-04-10T10:18:55.387Z</v>
+        <v>2026-04-10T10:43:19.631Z</v>
       </c>
       <c r="N416" t="str">
-        <v/>
-      </c>
-      <c r="O416" t="str">
-        <v/>
-      </c>
-      <c r="P416" t="str">
-        <v/>
+        <v>New 2025 Colors: 9025 - Sungill, 424 - Redbug, 425 - OG Junebug, &amp; 991 - 021/297 Green Pumpkin/Black Blue Laminate The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
       </c>
     </row>
     <row r="417">
@@ -21204,7 +21084,7 @@
         <v>YAM021</v>
       </c>
       <c r="B417">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C417" t="str">
         <v>4″ Senko 10pk</v>
@@ -21219,34 +21099,28 @@
         <v/>
       </c>
       <c r="G417" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H417" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I417" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J417" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K417" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__senko_10pk.jpg</v>
       </c>
       <c r="L417" t="str">
-        <v>2026-04-10T10:18:57.476Z</v>
+        <v>2026-04-10T10:43:21.844Z</v>
       </c>
       <c r="M417" t="str">
-        <v>2026-04-10T10:18:57.476Z</v>
+        <v>2026-04-10T10:43:21.844Z</v>
       </c>
       <c r="N417" t="str">
-        <v/>
-      </c>
-      <c r="O417" t="str">
-        <v/>
-      </c>
-      <c r="P417" t="str">
-        <v/>
+        <v>New 2025 Colors: 433 - Glowstick, 9025 - Sungill, 424 - Redbug, 425 - OG Junebug, &amp; 991 - 021/297 Green Pumpkin/Black Blue Laminate. The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
       </c>
     </row>
     <row r="418">
@@ -21254,7 +21128,7 @@
         <v>YAM022</v>
       </c>
       <c r="B418">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C418" t="str">
         <v>5″ Senko 10pk</v>
@@ -21269,34 +21143,28 @@
         <v/>
       </c>
       <c r="G418" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H418" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I418" t="str">
-        <v>bottom</v>
+        <v>Variable</v>
       </c>
       <c r="J418" t="str">
-        <v>wacky</v>
+        <v>worm</v>
       </c>
       <c r="K418" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_10pk.jpg</v>
       </c>
       <c r="L418" t="str">
-        <v>2026-04-10T10:18:59.215Z</v>
+        <v>2026-04-10T10:43:23.253Z</v>
       </c>
       <c r="M418" t="str">
-        <v>2026-04-10T10:18:59.215Z</v>
+        <v>2026-04-10T10:43:23.253Z</v>
       </c>
       <c r="N418" t="str">
-        <v/>
-      </c>
-      <c r="O418" t="str">
-        <v/>
-      </c>
-      <c r="P418" t="str">
-        <v/>
+        <v>New 2025 Colors: 433 - Glowstick, 9025 - Sungill, 424 - Redbug, 425 - OG Junebug, &amp; 991 - 021/297 Green Pumpkin/Black Blue Laminate The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko. 10 per pack</v>
       </c>
     </row>
     <row r="419">
@@ -21304,7 +21172,7 @@
         <v>YAM023</v>
       </c>
       <c r="B419">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C419" t="str">
         <v>Fat Shad Shape Worm 8pk</v>
@@ -21319,34 +21187,28 @@
         <v/>
       </c>
       <c r="G419" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H419" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I419" t="str">
-        <v>bottom</v>
+        <v>Bottom</v>
       </c>
       <c r="J419" t="str">
-        <v>crawling</v>
+        <v>worm</v>
       </c>
       <c r="K419" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fat_shad_shape_worm_8pk.jpg</v>
       </c>
       <c r="L419" t="str">
-        <v>2026-04-10T10:19:00.636Z</v>
+        <v>2026-04-10T10:43:24.763Z</v>
       </c>
       <c r="M419" t="str">
-        <v>2026-04-10T10:19:00.636Z</v>
+        <v>2026-04-10T10:43:24.763Z</v>
       </c>
       <c r="N419" t="str">
-        <v/>
-      </c>
-      <c r="O419" t="str">
-        <v/>
-      </c>
-      <c r="P419" t="str">
-        <v/>
+        <v>The new 4" Fat Shad Shape Worm is a larger offering of a Yamamoto staple. Still featuring the same proven Shad Shape Worm design, the 4" version provides a fatter body construction that makes it perfect for drop shotting, on a jighead or as a scrounger trailer. Its profile and action make it more visible for more bites. Coming 8 per pack, the 4" Fat Shad Shape Worm is available in 12 awesome Yamamoto colors.</v>
       </c>
     </row>
     <row r="420">
@@ -21354,7 +21216,7 @@
         <v>YAM024</v>
       </c>
       <c r="B420">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C420" t="str">
         <v>Shad Shape Worm 10pk</v>
@@ -21369,34 +21231,28 @@
         <v/>
       </c>
       <c r="G420" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H420" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I420" t="str">
-        <v>bottom</v>
+        <v>Bottom</v>
       </c>
       <c r="J420" t="str">
-        <v>crawling</v>
+        <v>worm</v>
       </c>
       <c r="K420" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_worm_10pk.jpg</v>
       </c>
       <c r="L420" t="str">
-        <v>2026-04-10T10:19:02.734Z</v>
+        <v>2026-04-10T10:43:26.035Z</v>
       </c>
       <c r="M420" t="str">
-        <v>2026-04-10T10:19:02.734Z</v>
+        <v>2026-04-10T10:43:26.035Z</v>
       </c>
       <c r="N420" t="str">
-        <v/>
-      </c>
-      <c r="O420" t="str">
-        <v/>
-      </c>
-      <c r="P420" t="str">
-        <v/>
+        <v>New 2025 Color: 3.75" | 433 - Glowstick The Yamamoto Shad Shape Worm gives anglers yet another reason to fish Yamamoto Baits. Combining the elements of a ribbed Senko and a tiny shad-like bait, these finesse worms are an ideal choice for drop shotting and darter heading, as well as, a range of other applications. Popular in Japan prior to their release in North America, the Yamamoto Shad Shape Worms offer a killer bait fish presentation that won't overpower the situation if the fish get finicky. The Shad Shapped worm comes in a 3" and 3.75" model and 10 per bag.</v>
       </c>
     </row>
     <row r="421">
@@ -21404,7 +21260,7 @@
         <v>YAM025</v>
       </c>
       <c r="B421">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C421" t="str">
         <v>Kut Tail Worm</v>
@@ -21419,34 +21275,28 @@
         <v/>
       </c>
       <c r="G421" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H421" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I421" t="str">
-        <v>bottom</v>
+        <v>Bottom</v>
       </c>
       <c r="J421" t="str">
-        <v>crawling</v>
+        <v>worm</v>
       </c>
       <c r="K421" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_kut_tail_worm.jpg</v>
       </c>
       <c r="L421" t="str">
-        <v>2026-04-10T10:19:04.912Z</v>
+        <v>2026-04-10T10:43:27.289Z</v>
       </c>
       <c r="M421" t="str">
-        <v>2026-04-10T10:19:04.912Z</v>
+        <v>2026-04-10T10:43:27.289Z</v>
       </c>
       <c r="N421" t="str">
-        <v/>
-      </c>
-      <c r="O421" t="str">
-        <v/>
-      </c>
-      <c r="P421" t="str">
-        <v/>
+        <v>The Kut Tail Worm is a great plastic to rig if you want to simplify finesse fishing. Its unique tail provides a subtle action that pairs well with the slender design. This combination is incredibly hard for even the most finnicky of fish to resist. Available in a wide range of sizes ranging from 4" all the way to 7.75", the Kut Tail is an excellent choice for drop-shotting or any other finesse style. Pack Size: 4" - 20pk 5" - 10pk 7.75" - 5pk</v>
       </c>
     </row>
     <row r="422">
@@ -21454,7 +21304,7 @@
         <v>YAM026</v>
       </c>
       <c r="B422">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C422" t="str">
         <v>6.5″ Sensei Worm 10pk</v>
@@ -21469,34 +21319,28 @@
         <v/>
       </c>
       <c r="G422" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H422" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I422" t="str">
-        <v>bottom</v>
+        <v>Bottom</v>
       </c>
       <c r="J422" t="str">
-        <v>crawling</v>
+        <v>worm</v>
       </c>
       <c r="K422" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_6_5__sensei_worm_10pk.jpg</v>
       </c>
       <c r="L422" t="str">
-        <v>2026-04-10T10:19:07.068Z</v>
+        <v>2026-04-10T10:43:28.557Z</v>
       </c>
       <c r="M422" t="str">
-        <v>2026-04-10T10:19:07.068Z</v>
+        <v>2026-04-10T10:43:28.557Z</v>
       </c>
       <c r="N422" t="str">
-        <v/>
-      </c>
-      <c r="O422" t="str">
-        <v/>
-      </c>
-      <c r="P422" t="str">
-        <v/>
+        <v>From the creators of the most successful soft plastic worm of all time comes the ultimate bait for finesse fishing applications. The all-new Sensei worm from Yamamoto Baits is a straight tail finesse worm measuring 6.5” in length. The Sensei worm features a custom-tailored soft plastic formula that leaves the worm neutrally buoyant in the water. This allows for an incredibly lifelike presentation when rigged on a drop shot, a neko rig, or your preferred rigging method of choice. The balance between the head of the worm and the subtle bulb of the tail allows the Sensei worm to have a wide, but slow shimmy when rigged weightless on a wacky rig. Whether you choose to fish it weightless in the shallows or on a shaky head out deep the Sensei worm is sure to be any anglers preferred tool when looking to outwit wily bass. Available in 12 fish catching colors. 10 Per pack</v>
       </c>
     </row>
     <row r="423">
@@ -21504,7 +21348,7 @@
         <v>YAM027</v>
       </c>
       <c r="B423">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C423" t="str">
         <v>Oki Worm 6pk</v>
@@ -21519,34 +21363,28 @@
         <v/>
       </c>
       <c r="G423" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H423" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I423" t="str">
-        <v>bottom</v>
+        <v>Bottom</v>
       </c>
       <c r="J423" t="str">
-        <v>crawling</v>
+        <v>worm</v>
       </c>
       <c r="K423" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_oki_worm_6pk.jpg</v>
       </c>
       <c r="L423" t="str">
-        <v>2026-04-10T10:19:10.212Z</v>
+        <v>2026-04-10T10:43:29.786Z</v>
       </c>
       <c r="M423" t="str">
-        <v>2026-04-10T10:19:10.212Z</v>
+        <v>2026-04-10T10:43:29.786Z</v>
       </c>
       <c r="N423" t="str">
-        <v/>
-      </c>
-      <c r="O423" t="str">
-        <v/>
-      </c>
-      <c r="P423" t="str">
-        <v/>
+        <v>New 2025 Colors: 425 - OG Junebug &amp; 424 - Redbug Due to the overwhelming requests from our professional anglers as well as our dedicated Yamamoto customers, we are very excited to introduce the brand-new Oki worm. “Oki” means long sword in Japanese, and that is exactly what this worm will remind you of – a long weapon used to put more bass in your boat. The 10” Oki is a straight-tail worm that is formulated using our popular Mega Floater Formula, which ensures that the Oki will float vertically and be more visible as well as have more action when presented on a standup jig head. 6 Per Pack</v>
       </c>
     </row>
     <row r="424">
@@ -21554,7 +21392,7 @@
         <v>YAM028</v>
       </c>
       <c r="B424">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C424" t="str">
         <v>Ichi Worm 6pk</v>
@@ -21569,34 +21407,28 @@
         <v/>
       </c>
       <c r="G424" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H424" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I424" t="str">
-        <v>bottom</v>
+        <v>Bottom</v>
       </c>
       <c r="J424" t="str">
-        <v>crawling</v>
+        <v>worm</v>
       </c>
       <c r="K424" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_ichi_worm_6pk.jpg</v>
       </c>
       <c r="L424" t="str">
-        <v>2026-04-10T10:19:12.347Z</v>
+        <v>2026-04-10T10:43:31.016Z</v>
       </c>
       <c r="M424" t="str">
-        <v>2026-04-10T10:19:12.347Z</v>
+        <v>2026-04-10T10:43:31.016Z</v>
       </c>
       <c r="N424" t="str">
-        <v/>
-      </c>
-      <c r="O424" t="str">
-        <v/>
-      </c>
-      <c r="P424" t="str">
-        <v/>
+        <v>New 2025 Colors: 424 - Redbug &amp; 425 - OG Junebug As with most things, all big worms are not created equally. Oftentimes, the details hidden in the design and formula are the true difference maker. In the case of the all-new Ichi Worm, the design paired with the formula sets this big worm apart from its competitors. By utilizing the ribbed body much akin to our popular Slinko, the Ichi Worm offers a bulky profile that displaces water and releases bubbles. Despite the bulk, this design doesn’t hinder hookups as it allows for maximum hook penetration. The combination of the ribbon tail, bulky ringed body, &amp; our Mega Floater Formula ensures that the Ichi stands up and moves with ease, even with the slowest movement or lightest weights. Available in 16 colors, the 10” Ichi worm has incredible action and appeals to the quality of bass that you tell stories about for years to come. 6 Per pack</v>
       </c>
     </row>
     <row r="425">
@@ -21604,7 +21436,7 @@
         <v>YAM029</v>
       </c>
       <c r="B425">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C425" t="str">
         <v>Slinko Floater</v>
@@ -21619,34 +21451,28 @@
         <v/>
       </c>
       <c r="G425" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H425" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I425" t="str">
-        <v>bottom</v>
+        <v>Bottom</v>
       </c>
       <c r="J425" t="str">
-        <v>crawling</v>
+        <v>worm</v>
       </c>
       <c r="K425" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_slinko_floater.jpg</v>
       </c>
       <c r="L425" t="str">
-        <v>2026-04-10T10:19:15.237Z</v>
+        <v>2026-04-10T10:43:33.489Z</v>
       </c>
       <c r="M425" t="str">
-        <v>2026-04-10T10:19:15.237Z</v>
+        <v>2026-04-10T10:43:33.489Z</v>
       </c>
       <c r="N425" t="str">
-        <v/>
-      </c>
-      <c r="O425" t="str">
-        <v/>
-      </c>
-      <c r="P425" t="str">
-        <v/>
+        <v>The 3.25" Slinko from Yamamoto is a bite-sized version of the original 5.5" Slinko. Built using the same Mega Floater Formula that makes its bigger predecessor so unique, the 3.25" Slinko produces in multiples applications, ranging from Ned rigs to Carolina rigs. The 3.25" Slinko is available in 10 winning colors and comes 8 per pack. The 5.5” Slinko is unlike anything in our product line. First, the ribbed shape body allows for bulk while maintaining the classic Senko profile. The ribs not only make for great hooksets, they put off bubbles to give a more lifelike presentation. The most important aspect of the Slinko is its construction from our new Mega Floater Formula. It stands up on a jighead, dances vertically on Neko rig, and floats on a Carolina Rig. Although new, it has the unmatched action that you would expect to get only from Yamamoto Baits! 7 Pack</v>
       </c>
     </row>
     <row r="426">
@@ -21654,7 +21480,7 @@
         <v>YAM030</v>
       </c>
       <c r="B426">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C426" t="str">
         <v>5″ Shad Shape Floater 8pk</v>
@@ -21669,34 +21495,28 @@
         <v/>
       </c>
       <c r="G426" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H426" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I426" t="str">
-        <v>bottom</v>
+        <v>Bottom</v>
       </c>
       <c r="J426" t="str">
-        <v>crawling</v>
+        <v>worm</v>
       </c>
       <c r="K426" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__shad_shape_floater_8pk.jpg</v>
       </c>
       <c r="L426" t="str">
-        <v>2026-04-10T10:19:17.364Z</v>
+        <v>2026-04-10T10:43:34.738Z</v>
       </c>
       <c r="M426" t="str">
-        <v>2026-04-10T10:19:17.364Z</v>
+        <v>2026-04-10T10:43:34.738Z</v>
       </c>
       <c r="N426" t="str">
-        <v/>
-      </c>
-      <c r="O426" t="str">
-        <v/>
-      </c>
-      <c r="P426" t="str">
-        <v/>
+        <v>Utilizing the shape of the Shad Shape Worm, but pairing with our new “Mega Floater Formula”, we are really excited about the new 5” Shad Shape Worm! This new version floats, which makes it absolute MONEY on a drop shot when you want a bigger profile bait. It is also incredible on a scrounger head! The profile and action make it an awesome baitfish imitator that will fool fish no matter how clear the water or how you rig it.. Largemouth, Smallmouth and Spots will all be suckers for the 5” Shad Shape floater! 8 Per Bag</v>
       </c>
     </row>
     <row r="427">
@@ -21704,7 +21524,7 @@
         <v>YAM031</v>
       </c>
       <c r="B427">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C427" t="str">
         <v>3.5″ Shinobi Grub 8pk</v>
@@ -21719,34 +21539,28 @@
         <v/>
       </c>
       <c r="G427" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H427" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I427" t="str">
-        <v>subsurface</v>
+        <v>Subsurface (0–0.5m)</v>
       </c>
       <c r="J427" t="str">
-        <v>swimming</v>
+        <v>wobble_roll</v>
       </c>
       <c r="K427" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_5__shinobi_grub_8pk.jpg</v>
       </c>
       <c r="L427" t="str">
-        <v>2026-04-10T10:19:20.468Z</v>
+        <v>2026-04-10T10:43:36.238Z</v>
       </c>
       <c r="M427" t="str">
-        <v>2026-04-10T10:19:20.468Z</v>
+        <v>2026-04-10T10:43:36.238Z</v>
       </c>
       <c r="N427" t="str">
-        <v/>
-      </c>
-      <c r="O427" t="str">
-        <v/>
-      </c>
-      <c r="P427" t="str">
-        <v/>
+        <v>The new Yamamoto Shinobi Grub is an all-around tool for serious anglers. The 3.5" double tail kicking grub catches fish on a variety of different rigs. The Shinobi can be used as a trailer on a jig, chatterbait, buzzbait, or spinnerbait. It is also deadly rigged independently such as on a Texas rig, jig head, swing head or Carolina Rig. Available in 8 proven Yamamoto colors, the Shinobi comes 8 per pack. The only wrong way to fish it is not to fish it.</v>
       </c>
     </row>
     <row r="428">
@@ -21754,7 +21568,7 @@
         <v>YAM032</v>
       </c>
       <c r="B428">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C428" t="str">
         <v>Hula Grub Bundle – 50pc Assortment</v>
@@ -21769,34 +21583,28 @@
         <v/>
       </c>
       <c r="G428" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H428" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I428" t="str">
-        <v>subsurface</v>
+        <v>Subsurface (0–0.5m)</v>
       </c>
       <c r="J428" t="str">
-        <v>swimming</v>
+        <v>wobble_roll</v>
       </c>
       <c r="K428" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hula_grub_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L428" t="str">
-        <v>2026-04-10T10:19:23.545Z</v>
+        <v>2026-04-10T10:43:37.464Z</v>
       </c>
       <c r="M428" t="str">
-        <v>2026-04-10T10:19:23.545Z</v>
+        <v>2026-04-10T10:43:37.464Z</v>
       </c>
       <c r="N428" t="str">
-        <v/>
-      </c>
-      <c r="O428" t="str">
-        <v/>
-      </c>
-      <c r="P428" t="str">
-        <v/>
+        <v>Packed with five bags of 5” Double Tail Hula Grubs, this grab bag delivers the ultimate in offshore soft plastic versatility. A go-to bait for decades, the Hula Grub is known for its unique design that hugs the bottom while producing irresistible action. Whether you’re fishing ledges, points, or rock piles, this bundle gives you 50 chances to hook into something big. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 5" Double Tail Hula Grub - 021 Black with Large Blue Flake 10/pc 5" Double Tail Hula Grub - 297 Green Pumpkin with Large Black Flake 10/pc 5" Double Tail Hula Grub - 9003 Fire Craw 10/pc 5" Double Tail Hula Grub - 301 Green Pumpkin with Large Green &amp; Purple Flake 10/pc 5" Double Tail Hula Grub - 208 Watermelon with Black &amp; Red Flake</v>
       </c>
     </row>
     <row r="429">
@@ -21804,7 +21612,7 @@
         <v>YAM033</v>
       </c>
       <c r="B429">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C429" t="str">
         <v>Yamatanuki</v>
@@ -21819,34 +21627,28 @@
         <v/>
       </c>
       <c r="G429" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H429" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I429" t="str">
-        <v>subsurface</v>
+        <v>Subsurface (0–0.5m)</v>
       </c>
       <c r="J429" t="str">
-        <v>swimming</v>
+        <v>wobble_roll</v>
       </c>
       <c r="K429" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yamatanuki.jpg</v>
       </c>
       <c r="L429" t="str">
-        <v>2026-04-10T10:19:26.555Z</v>
+        <v>2026-04-10T10:43:38.701Z</v>
       </c>
       <c r="M429" t="str">
-        <v>2026-04-10T10:19:26.555Z</v>
+        <v>2026-04-10T10:43:38.701Z</v>
       </c>
       <c r="N429" t="str">
-        <v/>
-      </c>
-      <c r="O429" t="str">
-        <v/>
-      </c>
-      <c r="P429" t="str">
-        <v/>
+        <v>New 2025 Color: 2.5" | 433 - Glowstick The Yamatanuki, a popular Japanese Yamamoto bait now available in the US, revolutionized the "heavy" soft plastic lure trend. The Yamatanuki features a custom formula for weightless fishing, offering excellent casting distance and fast fall. Perfect for flipping, casting, and dragging, it's also effective with forward-facing sonar. Available in 8 pro-chosen colors, it’s a versatile addition to any angler's toolkit. Offered in 3 sizes: 4.25" (6 pack), 3.5" (8 pack), and 2.5" (10 pack).</v>
       </c>
     </row>
     <row r="430">
@@ -21854,7 +21656,7 @@
         <v>YAM034</v>
       </c>
       <c r="B430">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C430" t="str">
         <v>Double Tail Hula Grub 10pk</v>
@@ -21869,34 +21671,28 @@
         <v/>
       </c>
       <c r="G430" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H430" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I430" t="str">
-        <v>subsurface</v>
+        <v>Subsurface (0–0.5m)</v>
       </c>
       <c r="J430" t="str">
-        <v>swimming</v>
+        <v>wobble_roll</v>
       </c>
       <c r="K430" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_double_tail_hula_grub_10pk.jpg</v>
       </c>
       <c r="L430" t="str">
-        <v>2026-04-10T10:19:28.669Z</v>
+        <v>2026-04-10T10:43:39.969Z</v>
       </c>
       <c r="M430" t="str">
-        <v>2026-04-10T10:19:28.669Z</v>
+        <v>2026-04-10T10:43:39.969Z</v>
       </c>
       <c r="N430" t="str">
-        <v/>
-      </c>
-      <c r="O430" t="str">
-        <v/>
-      </c>
-      <c r="P430" t="str">
-        <v/>
+        <v>It is impossible to talk about Yamamoto baits without talking about the Hula Grub. The bait that started it all for us. The Hula Grub is a golden standard for offshore fishing with a soft plastic bait. Thanks to its unique shape, this plastic stays on the bottom while providing a ton of action. Available in 2.5", 4", and 5" offerings and comes 10 per pack the Hula Grub is a timeless classic that will always have a place in an experienced angler's tacklebox.</v>
       </c>
     </row>
     <row r="431">
@@ -21904,7 +21700,7 @@
         <v>YAM035</v>
       </c>
       <c r="B431">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C431" t="str">
         <v>Double Tail Grub 20pk</v>
@@ -21919,34 +21715,28 @@
         <v/>
       </c>
       <c r="G431" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H431" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I431" t="str">
-        <v>subsurface</v>
+        <v>Subsurface (0–0.5m)</v>
       </c>
       <c r="J431" t="str">
-        <v>swimming</v>
+        <v>wobble_roll</v>
       </c>
       <c r="K431" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_double_tail_grub_20pk.jpg</v>
       </c>
       <c r="L431" t="str">
-        <v>2026-04-10T10:19:30.873Z</v>
+        <v>2026-04-10T10:43:41.219Z</v>
       </c>
       <c r="M431" t="str">
-        <v>2026-04-10T10:19:30.873Z</v>
+        <v>2026-04-10T10:43:41.219Z</v>
       </c>
       <c r="N431" t="str">
-        <v/>
-      </c>
-      <c r="O431" t="str">
-        <v/>
-      </c>
-      <c r="P431" t="str">
-        <v/>
+        <v>The Double Tail Grub knows how to make a splash. Available in both 4" and 5" and come 20 per pack, the Double Tail Grub offers a simple, timeless profile that that bass seem to lock in on. The Double Tail Grub excels as a jig trailer where it's shape and size appeal to crawfish eaters.</v>
       </c>
     </row>
     <row r="432">
@@ -21954,7 +21744,7 @@
         <v>YAM036</v>
       </c>
       <c r="B432">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C432" t="str">
         <v>Single Tail Grub 20pk</v>
@@ -21969,34 +21759,28 @@
         <v/>
       </c>
       <c r="G432" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H432" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I432" t="str">
-        <v>subsurface</v>
+        <v>Subsurface (0–0.5m)</v>
       </c>
       <c r="J432" t="str">
-        <v>swimming</v>
+        <v>wobble_roll</v>
       </c>
       <c r="K432" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_single_tail_grub_20pk.jpg</v>
       </c>
       <c r="L432" t="str">
-        <v>2026-04-10T10:19:32.965Z</v>
+        <v>2026-04-10T10:43:42.456Z</v>
       </c>
       <c r="M432" t="str">
-        <v>2026-04-10T10:19:32.965Z</v>
+        <v>2026-04-10T10:43:42.456Z</v>
       </c>
       <c r="N432" t="str">
-        <v/>
-      </c>
-      <c r="O432" t="str">
-        <v/>
-      </c>
-      <c r="P432" t="str">
-        <v/>
+        <v>The Single Tail Grub is a Yamamoto staple. Available in 4" and 5", the Single Tail Grub covers the gamut of potential applications. Whether you fish it alone or as a trailer, this plastic has a proven record of success. Smaller sizes provide the subtleness that finnicky fish desire, while the larger sizes can really beef up a presentation when the time is right. A versatile angler is a good angler, and nothing is more versatile than the Single Tail Grub. 20 Per Pack</v>
       </c>
     </row>
     <row r="433">
@@ -22004,13 +21788,13 @@
         <v>YAM037</v>
       </c>
       <c r="B433">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C433" t="str">
-        <v>Shibo Swimmer</v>
+        <v>Yama Bug 6pk</v>
       </c>
       <c r="D433" t="str">
-        <v>Shibo Swimmer</v>
+        <v>Yama Bug 6pk</v>
       </c>
       <c r="E433" t="str">
         <v/>
@@ -22019,34 +21803,28 @@
         <v/>
       </c>
       <c r="G433" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H433" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I433" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J433" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K433" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shibo_swimmer.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yama_bug_6pk.jpg</v>
       </c>
       <c r="L433" t="str">
-        <v>2026-04-10T10:19:37.985Z</v>
+        <v>2026-04-10T10:43:46.069Z</v>
       </c>
       <c r="M433" t="str">
-        <v>2026-04-10T10:19:37.985Z</v>
+        <v>2026-04-10T10:43:46.069Z</v>
       </c>
       <c r="N433" t="str">
-        <v/>
-      </c>
-      <c r="O433" t="str">
-        <v/>
-      </c>
-      <c r="P433" t="str">
-        <v/>
+        <v>The Yama Bug from Yamamoto was built due to demand from our pros and incorporates their input into what would make the ultimate creature bait. The Yama Bug is perfect for flipping and pitching, but it can get the job done as a jig trailer and in other scenarios as well. The Yama Bug’s reverse facing legs provide a quivering action that drives bass crazy, and its custom Yamamoto plastic formula provides the rest of the magic. Coming 6 per clamshell pack, the Yama Bug is available in 10 fish-catching colors.</v>
       </c>
     </row>
     <row r="434">
@@ -22054,13 +21832,13 @@
         <v>YAM038</v>
       </c>
       <c r="B434">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C434" t="str">
-        <v>Hinge Minnow</v>
+        <v>Yamacraw</v>
       </c>
       <c r="D434" t="str">
-        <v>Hinge Minnow</v>
+        <v>Yamacraw</v>
       </c>
       <c r="E434" t="str">
         <v/>
@@ -22069,34 +21847,28 @@
         <v/>
       </c>
       <c r="G434" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H434" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I434" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J434" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K434" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hinge_minnow.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yamacraw.jpg</v>
       </c>
       <c r="L434" t="str">
-        <v>2026-04-10T10:19:39.734Z</v>
+        <v>2026-04-10T10:43:49.506Z</v>
       </c>
       <c r="M434" t="str">
-        <v>2026-04-10T10:19:39.734Z</v>
+        <v>2026-04-10T10:43:49.506Z</v>
       </c>
       <c r="N434" t="str">
-        <v/>
-      </c>
-      <c r="O434" t="str">
-        <v/>
-      </c>
-      <c r="P434" t="str">
-        <v/>
+        <v>Released in December 2022, the Yama Craw quickly became a favorite for its incredible action and Mega Floater Formula. This bait maintains the perfect balance of body thickness to prevent splitting on jig keepers, while still accommodating a Texas rig and larger hooks. The action is unmatched for its size, and the Yamamoto quality remains top-notch. Available in 19 colors, the 3" Yama Craw comes in 8 packs and the 4" comes in 6 packs.</v>
       </c>
     </row>
     <row r="435">
@@ -22104,13 +21876,13 @@
         <v>YAM039</v>
       </c>
       <c r="B435">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C435" t="str">
-        <v>Zako Swimbait Kit – 84pc Assortment</v>
+        <v>Flappin’ Hog</v>
       </c>
       <c r="D435" t="str">
-        <v>Zako Swimbait Kit – 84pc Assortment</v>
+        <v>Flappin’ Hog</v>
       </c>
       <c r="E435" t="str">
         <v/>
@@ -22119,34 +21891,28 @@
         <v/>
       </c>
       <c r="G435" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H435" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I435" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J435" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K435" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait_kit___84pc_assortment.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_flappin__hog.jpg</v>
       </c>
       <c r="L435" t="str">
-        <v>2026-04-10T10:19:41.850Z</v>
+        <v>2026-04-10T10:43:51.759Z</v>
       </c>
       <c r="M435" t="str">
-        <v>2026-04-10T10:19:41.850Z</v>
+        <v>2026-04-10T10:43:51.759Z</v>
       </c>
       <c r="N435" t="str">
-        <v/>
-      </c>
-      <c r="O435" t="str">
-        <v/>
-      </c>
-      <c r="P435" t="str">
-        <v/>
+        <v>New 2025 Color: 991 - 021/297 Green Pumpkin/Black Blue Laminate The Flappin' Hog was built for pigs. As versatile as a bait can be, the Flappin Hog is a like a Swiss Army knife in your tackle box. Texas Rig it. Carolina Rig it. Use it as a jig trailer. No matter how you rig it, the bulky body and 3 different types of appendages will put off vibes that bass can't resist. Available in both a 3.75" size as well as 4.5", the Flappin' Hog will bring home the bacon. 3.75" - 7 Per pack 4.5" - 5 Per pack</v>
       </c>
     </row>
     <row r="436">
@@ -22154,13 +21920,13 @@
         <v>YAM040</v>
       </c>
       <c r="B436">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C436" t="str">
-        <v>Zako Slim 6pk</v>
+        <v>Sanshouo 6pk</v>
       </c>
       <c r="D436" t="str">
-        <v>Zako Slim 6pk</v>
+        <v>Sanshouo 6pk</v>
       </c>
       <c r="E436" t="str">
         <v/>
@@ -22169,34 +21935,28 @@
         <v/>
       </c>
       <c r="G436" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H436" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I436" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J436" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K436" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_slim_6pk.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_sanshouo_6pk.jpg</v>
       </c>
       <c r="L436" t="str">
-        <v>2026-04-10T10:19:43.096Z</v>
+        <v>2026-04-10T10:43:53.894Z</v>
       </c>
       <c r="M436" t="str">
-        <v>2026-04-10T10:19:43.096Z</v>
+        <v>2026-04-10T10:43:53.894Z</v>
       </c>
       <c r="N436" t="str">
-        <v/>
-      </c>
-      <c r="O436" t="str">
-        <v/>
-      </c>
-      <c r="P436" t="str">
-        <v/>
+        <v>Due to popular demand from anglers across the country, the Sanshouo is back and ready to be rigged on your favorite texas rig, jig or carolina rig. Fashioned to resemble a waterdog, sculpin, goby, or a bluegill, the Sanshouo has a distinct profile that fish don’t see all of the time. Its unique shape allows it to work equally whether you are on Lake Erie fishing for trophy smallmouth, at Okeechobee punching heavy mats, or sight fishing and flipping in California. The Sanshouo’s wide, flat tail allows it to glide back-and-forth with each twitch of the rod tip, creating a bait that triggers strikes whether fished deep or shallow. If you are looking for a go-to creature bait that fish have rarely seen, be sure to grab a bag of Sanshouos while they last! 6 Per pack</v>
       </c>
     </row>
     <row r="437">
@@ -22204,13 +21964,13 @@
         <v>YAM041</v>
       </c>
       <c r="B437">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C437" t="str">
-        <v>Scope Shad</v>
+        <v>2.5″ Covert Craw Floater 10pk</v>
       </c>
       <c r="D437" t="str">
-        <v>Scope Shad</v>
+        <v>2.5″ Covert Craw Floater 10pk</v>
       </c>
       <c r="E437" t="str">
         <v/>
@@ -22219,34 +21979,28 @@
         <v/>
       </c>
       <c r="G437" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H437" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I437" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J437" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K437" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_scope_shad.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_2_5__covert_craw_floater_10pk.jpg</v>
       </c>
       <c r="L437" t="str">
-        <v>2026-04-10T10:19:45.246Z</v>
+        <v>2026-04-10T10:43:56.086Z</v>
       </c>
       <c r="M437" t="str">
-        <v>2026-04-10T10:19:45.246Z</v>
+        <v>2026-04-10T10:43:56.086Z</v>
       </c>
       <c r="N437" t="str">
-        <v/>
-      </c>
-      <c r="O437" t="str">
-        <v/>
-      </c>
-      <c r="P437" t="str">
-        <v/>
+        <v>The Yamamoto Covert Craw is just as sneaky as it sounds. Based on a popular Japanese design, the 2.5'' Covert Craw can be used on a Ned rig or as a jig trailer. Its Mega Floater Formula gives it both versatility and appeal, the buoyant claws are complimented by 6 lifelike legs. Available in 8 proven colors and 10 per pack, the Covert Craw is sure to be your new favorite finesse craw offering.</v>
       </c>
     </row>
     <row r="438">
@@ -22254,13 +22008,13 @@
         <v>YAM042</v>
       </c>
       <c r="B438">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C438" t="str">
-        <v>Shad Shape Swimmer 8pk</v>
+        <v>3.5″ Nuki Bug 6pk</v>
       </c>
       <c r="D438" t="str">
-        <v>Shad Shape Swimmer 8pk</v>
+        <v>3.5″ Nuki Bug 6pk</v>
       </c>
       <c r="E438" t="str">
         <v/>
@@ -22269,34 +22023,28 @@
         <v/>
       </c>
       <c r="G438" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H438" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I438" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J438" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K438" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_swimmer_8pk.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_5__nuki_bug_6pk.jpg</v>
       </c>
       <c r="L438" t="str">
-        <v>2026-04-10T10:19:48.508Z</v>
+        <v>2026-04-10T10:43:57.923Z</v>
       </c>
       <c r="M438" t="str">
-        <v>2026-04-10T10:19:48.508Z</v>
+        <v>2026-04-10T10:43:57.923Z</v>
       </c>
       <c r="N438" t="str">
-        <v/>
-      </c>
-      <c r="O438" t="str">
-        <v/>
-      </c>
-      <c r="P438" t="str">
-        <v/>
+        <v>The Yamatanuki just got a little bugged out. Yamamoto’s Nuki Bug is everything anglers love about the Yamatanuki, but with the addition of 2 flanged claws and 6 legs. The 3.5’’ Nuki Bug falls like the original but has a subtle swimming action, even when rigged weightless on an EWG Hook. Available in 8 gorgeous colors with 6 per pack.</v>
       </c>
     </row>
     <row r="439">
@@ -22304,13 +22052,13 @@
         <v>YAM043</v>
       </c>
       <c r="B439">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C439" t="str">
-        <v>Zako Swimbait</v>
+        <v>3.75″ Cowboy 7pk</v>
       </c>
       <c r="D439" t="str">
-        <v>Zako Swimbait</v>
+        <v>3.75″ Cowboy 7pk</v>
       </c>
       <c r="E439" t="str">
         <v/>
@@ -22319,34 +22067,28 @@
         <v/>
       </c>
       <c r="G439" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H439" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I439" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J439" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K439" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_75__cowboy_7pk.jpg</v>
       </c>
       <c r="L439" t="str">
-        <v>2026-04-10T10:19:50.589Z</v>
+        <v>2026-04-10T10:44:01.827Z</v>
       </c>
       <c r="M439" t="str">
-        <v>2026-04-10T10:19:50.589Z</v>
+        <v>2026-04-10T10:44:01.827Z</v>
       </c>
       <c r="N439" t="str">
-        <v/>
-      </c>
-      <c r="O439" t="str">
-        <v/>
-      </c>
-      <c r="P439" t="str">
-        <v/>
+        <v>This Cowboy is well-armed. This creature bait pairs the bulky body of the 4.5” Flappin’ Hawg and the swimming tail kick of the iconic DT Grub to create a well-rounded plastic that shines in any scenario. If you need to be shallow, the Cowboy excels as a stand-alone Texas Rig as well as on the back of a jig. Conversely, the Cowboy will do just as much damage out away from the bank as part of a Carolina Rig or on a wobble-head jig. Bulky and loud, the Cowboy is ready for a showdown with big bass! 7 Per Pack</v>
       </c>
     </row>
     <row r="440">
@@ -22354,13 +22096,13 @@
         <v>YAM044</v>
       </c>
       <c r="B440">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C440" t="str">
-        <v>4″ Zako Swimbait Bulk Packs</v>
+        <v>PsychoDad 5pk</v>
       </c>
       <c r="D440" t="str">
-        <v>4″ Zako Swimbait Bulk Packs</v>
+        <v>PsychoDad 5pk</v>
       </c>
       <c r="E440" t="str">
         <v/>
@@ -22369,34 +22111,28 @@
         <v/>
       </c>
       <c r="G440" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H440" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I440" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J440" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K440" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__zako_swimbait_bulk_packs.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_psychodad_5pk.jpg</v>
       </c>
       <c r="L440" t="str">
-        <v>2026-04-10T10:19:52.662Z</v>
+        <v>2026-04-10T10:44:04.914Z</v>
       </c>
       <c r="M440" t="str">
-        <v>2026-04-10T10:19:52.662Z</v>
+        <v>2026-04-10T10:44:04.914Z</v>
       </c>
       <c r="N440" t="str">
-        <v/>
-      </c>
-      <c r="O440" t="str">
-        <v/>
-      </c>
-      <c r="P440" t="str">
-        <v/>
+        <v>Things get crazy when the Psycho Dad comes out. Featuring a built-in rattle chamber and large claws that act like swimbait tails, the Psycho Dad is the center of attention anytime it finds water. This 3.75” crawfish imitator was built for punching through cover, but it can do a whole lot more. Try it out on a Carolina Rig, standup head, or a jig trailer – you won’t be disappointed! 5 Per Pack</v>
       </c>
     </row>
     <row r="441">
@@ -22404,13 +22140,13 @@
         <v>YAM045</v>
       </c>
       <c r="B441">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C441" t="str">
-        <v>4″ Paddle Tail Zako 5pk</v>
+        <v>4″ Kreature 7pk</v>
       </c>
       <c r="D441" t="str">
-        <v>4″ Paddle Tail Zako 5pk</v>
+        <v>4″ Kreature 7pk</v>
       </c>
       <c r="E441" t="str">
         <v/>
@@ -22419,34 +22155,28 @@
         <v/>
       </c>
       <c r="G441" t="str">
-        <v>softbait</v>
+        <v>weightless_soft_bait</v>
       </c>
       <c r="H441" t="str">
-        <v/>
+        <v>soft</v>
       </c>
       <c r="I441" t="str">
-        <v>subsurface</v>
+        <v>Bottom</v>
       </c>
       <c r="J441" t="str">
-        <v>swimming</v>
+        <v>crawl_creature</v>
       </c>
       <c r="K441" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__paddle_tail_zako_5pk.jpg</v>
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__kreature_7pk.jpg</v>
       </c>
       <c r="L441" t="str">
-        <v>2026-04-10T10:19:55.958Z</v>
+        <v>2026-04-10T10:44:07.309Z</v>
       </c>
       <c r="M441" t="str">
-        <v>2026-04-10T10:19:55.958Z</v>
+        <v>2026-04-10T10:44:07.309Z</v>
       </c>
       <c r="N441" t="str">
-        <v/>
-      </c>
-      <c r="O441" t="str">
-        <v/>
-      </c>
-      <c r="P441" t="str">
-        <v/>
+        <v>The Kreature is sure to cause a stir. Featuring swimming “wings” and a free-flowing skirt of tentacles, the Kreature is impossible to ignore. 4” in size but much larger in attitude, the Kreature produces results as both a trailer and a standalone plastic. Try it on a Texas Rig in cover, or back off the bank and put it on a Carolina Rig. Either way, the fish are going to find it. 7 Per Pack</v>
       </c>
     </row>
     <row r="442">
@@ -22454,54 +22184,532 @@
         <v>YAM046</v>
       </c>
       <c r="B442">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="C442" t="str">
+        <v>3.75″ Fat Baby Craw 7pk</v>
+      </c>
+      <c r="D442" t="str">
+        <v>3.75″ Fat Baby Craw 7pk</v>
+      </c>
+      <c r="E442" t="str">
+        <v/>
+      </c>
+      <c r="F442" t="str">
+        <v/>
+      </c>
+      <c r="G442" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H442" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I442" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J442" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K442" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_75__fat_baby_craw_7pk.jpg</v>
+      </c>
+      <c r="L442" t="str">
+        <v>2026-04-10T10:44:09.439Z</v>
+      </c>
+      <c r="M442" t="str">
+        <v>2026-04-10T10:44:09.439Z</v>
+      </c>
+      <c r="N442" t="str">
+        <v>The Fat Baby Craw is a phenomenal finesse trailer. Its round design keeps it from sticking to cover while the bulk of the plastic ensures that it stays on the hook regardless of what it encounters. This 3.75” trailer has a nice, subtle movement that comes in handy in finesse applications. The Baby Craw is a slightly slimmed-down version of the Fat Baby Craw. 3.75”. It is a more-finesse style trailer for clearer water, smaller jigs, lighter line applications and wary bass. Both craw trailers are very lifelike in size and shape. 7 Per Pack</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>YAM047</v>
+      </c>
+      <c r="B443">
+        <v>21</v>
+      </c>
+      <c r="C443" t="str">
+        <v>4″ Fat Ika 10pk</v>
+      </c>
+      <c r="D443" t="str">
+        <v>4″ Fat Ika 10pk</v>
+      </c>
+      <c r="E443" t="str">
+        <v/>
+      </c>
+      <c r="F443" t="str">
+        <v/>
+      </c>
+      <c r="G443" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H443" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I443" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J443" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K443" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__fat_ika_10pk.jpg</v>
+      </c>
+      <c r="L443" t="str">
+        <v>2026-04-10T10:44:11.576Z</v>
+      </c>
+      <c r="M443" t="str">
+        <v>2026-04-10T10:44:11.576Z</v>
+      </c>
+      <c r="N443" t="str">
+        <v>Don’t let looks deceive you – the Ika isn’t your run-of-the-mill tube bait. Featuring a grub-style body and a tube-style skirt, the Ika can offer tons of rigging possibilities to fit any scenario. Pitch or flip a Fat Ika and experience bite-getting power that they harness. The 4.5” version shines in finesse situations, thanks to its subtle motion. Regardless of size or application, the common theme is that an Ika gets bit! 10 Per Pack</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>YAM048</v>
+      </c>
+      <c r="B444">
+        <v>21</v>
+      </c>
+      <c r="C444" t="str">
+        <v>Shibo Swimmer</v>
+      </c>
+      <c r="D444" t="str">
+        <v>Shibo Swimmer</v>
+      </c>
+      <c r="E444" t="str">
+        <v/>
+      </c>
+      <c r="F444" t="str">
+        <v/>
+      </c>
+      <c r="G444" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H444" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I444" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J444" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K444" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shibo_swimmer.jpg</v>
+      </c>
+      <c r="L444" t="str">
+        <v>2026-04-10T10:44:12.978Z</v>
+      </c>
+      <c r="M444" t="str">
+        <v>2026-04-10T10:44:12.978Z</v>
+      </c>
+      <c r="N444" t="str">
+        <v>The Yamamoto Shibo Swimmer was built to outperform traditional paddle tail swimbaits, delivering a harder thump and more water displacement for its size than any bait in its class. The custom Yamamoto soft plastic formula provides the ideal combination of a powerful tail kick, natural swimming action, and pronounced head wobble that bass can feel from a distance. The Shibo Swimmer truly separates itself with its versatility, consistently producing across a wide range of conditions. In colder water or during post-front conditions, it maintains a strong swimming action even on a slow, steady retrieve—when many swimbaits go dead. At moderate to fast retrieve speeds, its pronounced vibration makes it deadly in more stained water or when looking to trigger a reaction strike. Whether rigged on the back of a bladed jig, an Alabama rig, or a traditional ballhead jighead, the Shibo Swimmer comes alive, loading the rod tip with a deep, heavy thump that feels more like a hard bait than a soft plastic. If you’re looking for a swimbait that moves more than most, look no further than the Yamamoto Shibo Swimmer. 2.7”-8 pk | 3.2”-7pk | 3.7”-6pk</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>YAM049</v>
+      </c>
+      <c r="B445">
+        <v>21</v>
+      </c>
+      <c r="C445" t="str">
+        <v>Hinge Minnow</v>
+      </c>
+      <c r="D445" t="str">
+        <v>Hinge Minnow</v>
+      </c>
+      <c r="E445" t="str">
+        <v/>
+      </c>
+      <c r="F445" t="str">
+        <v/>
+      </c>
+      <c r="G445" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H445" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I445" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J445" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K445" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hinge_minnow.jpg</v>
+      </c>
+      <c r="L445" t="str">
+        <v>2026-04-10T10:44:14.192Z</v>
+      </c>
+      <c r="M445" t="str">
+        <v>2026-04-10T10:44:14.192Z</v>
+      </c>
+      <c r="N445" t="str">
+        <v>The Yamamoto Hinge Minnow is exactly what you expect from the most premium soft bait brand on earth. THE ultimate rolling minnow. A jointed, or “hinged” tail section allows the Hinge Minnow to roll, even on a straight retrieve which makes it easy for beginners and adds a constant fleeing action any time the bait is moving. Flanges run the length of the shoulders of the Hinge Minnow help slow the bait down, while its laminated top and bottom sections with independent weighting creates the perfect rate of roll. Available in 3.5", 5", 6" and even 7" sizes, the Hinge Minnow is a must-have in your arsenal and can be found in 10 winning Yamamoto colors. Keep rolling. 3.5" - 7pk 5" - 6pk 6" - 5pk 7" - 4pk</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>YAM050</v>
+      </c>
+      <c r="B446">
+        <v>21</v>
+      </c>
+      <c r="C446" t="str">
+        <v>Zako Swimbait Kit – 84pc Assortment</v>
+      </c>
+      <c r="D446" t="str">
+        <v>Zako Swimbait Kit – 84pc Assortment</v>
+      </c>
+      <c r="E446" t="str">
+        <v/>
+      </c>
+      <c r="F446" t="str">
+        <v/>
+      </c>
+      <c r="G446" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H446" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I446" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J446" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K446" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait_kit___84pc_assortment.jpg</v>
+      </c>
+      <c r="L446" t="str">
+        <v>2026-04-10T10:44:15.403Z</v>
+      </c>
+      <c r="M446" t="str">
+        <v>2026-04-10T10:44:15.403Z</v>
+      </c>
+      <c r="N446" t="str">
+        <v>The Zako Swimbait shines as a vibrating jig trailer but is a deadly combo on any bait that you want to swim. We have compiled some of the top color options in the 3" and 4" and married them together to create this kit. The Zako Swimbait kit comes loaded with 84 zako swimbaits and picked to ensure that you have a Zako for any condition you find in front of you. *items are subject to change based on availability, check graph below for the most up to date product mix 6/pc Zako Swimbait 4" - Black with Blue Flake YAM-134-06-021 6/pc Zako Swimbait 4" - Cream White YAM-134-06-036 6/pc Zako Swimbait 4" - Fading Watermelon with Large Black Flake YAM-134-06-194J 6/pc Zako Swimbait 4" - Tilapia Magic YAM-134-06-414 6/pc Zako Swimbait 4" - Blue Craw YAM-134-06-700 6/pc Zako Swimbait 4" - Green Gizzard YAM-134-06-9008 8/pc Zako Swimbait 3" - Rainbow Shad YAM-134JR-08-992 8/pc Zako Swimbait 3" - Black With Blue Flake YAM-134JR-08-021 8/pc Zako Swimbait 3" - Watermelon with Copper/Orange with Red Laminate YAM-134JR-08-956 8/pc Zako Swimbait 3" - Disco Green YAM-134JR-08-375 8/pc Zako Swimbait 3" - Sexy Shad YAM-134JR-08-9005 8/pc Zako Swimbait 3" - Pro Blue YAM-134JR-08-9004</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>YAM051</v>
+      </c>
+      <c r="B447">
+        <v>21</v>
+      </c>
+      <c r="C447" t="str">
+        <v>Zako Slim 6pk</v>
+      </c>
+      <c r="D447" t="str">
+        <v>Zako Slim 6pk</v>
+      </c>
+      <c r="E447" t="str">
+        <v/>
+      </c>
+      <c r="F447" t="str">
+        <v/>
+      </c>
+      <c r="G447" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H447" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I447" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J447" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K447" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_slim_6pk.jpg</v>
+      </c>
+      <c r="L447" t="str">
+        <v>2026-04-10T10:44:16.609Z</v>
+      </c>
+      <c r="M447" t="str">
+        <v>2026-04-10T10:44:16.609Z</v>
+      </c>
+      <c r="N447" t="str">
+        <v>The 3.5” Zako Slim from Yamamoto Baits is the perfect companion for smaller chatterbaits. Designed by Brett Hite, this updated version of the original Zako features a more sleek, compact profile that delivers a subtle presentation without sacrificing action. The tapered body and responsive tail create a lifelike movement that perfectly mirrors the action of any bladed jig, drawing in bass with an irresistible side to side quiver. Ideal for finesse fishing or when a smaller profile is needed, the Zako Slim gives you the versatility and performance to tackle tough conditions and bring in more bites. 6 Pack</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>YAM052</v>
+      </c>
+      <c r="B448">
+        <v>21</v>
+      </c>
+      <c r="C448" t="str">
+        <v>Scope Shad</v>
+      </c>
+      <c r="D448" t="str">
+        <v>Scope Shad</v>
+      </c>
+      <c r="E448" t="str">
+        <v/>
+      </c>
+      <c r="F448" t="str">
+        <v/>
+      </c>
+      <c r="G448" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H448" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I448" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J448" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K448" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_scope_shad.jpg</v>
+      </c>
+      <c r="L448" t="str">
+        <v>2026-04-10T10:44:17.821Z</v>
+      </c>
+      <c r="M448" t="str">
+        <v>2026-04-10T10:44:17.821Z</v>
+      </c>
+      <c r="N448" t="str">
+        <v>Building off the success of last year’s Scope Shad, Yamamoto has added both a 3.5’ and 4’’ offering for anglers wanting to upsize. Made from Yamamoto’s Mega Floater Formula, the Scope Shad is a forward-facing sonar weapon that can deliver in other finesse applications as well such as a trailer and on a dropshot. Available in 12 existing colors, as well as 5 brand new Stealth Series colors, the 3.5’’ and 4’’ offerings are proof that you can never have too much of a good thing. The 3" version is 10 per pack, 3.5’’ version is 8 per pack and the 4’’ version is 6 per pack.</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>YAM053</v>
+      </c>
+      <c r="B449">
+        <v>21</v>
+      </c>
+      <c r="C449" t="str">
+        <v>Shad Shape Swimmer 8pk</v>
+      </c>
+      <c r="D449" t="str">
+        <v>Shad Shape Swimmer 8pk</v>
+      </c>
+      <c r="E449" t="str">
+        <v/>
+      </c>
+      <c r="F449" t="str">
+        <v/>
+      </c>
+      <c r="G449" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H449" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I449" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J449" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K449" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_swimmer_8pk.jpg</v>
+      </c>
+      <c r="L449" t="str">
+        <v>2026-04-10T10:44:20.265Z</v>
+      </c>
+      <c r="M449" t="str">
+        <v>2026-04-10T10:44:20.265Z</v>
+      </c>
+      <c r="N449" t="str">
+        <v>Finesse is the name of the game in swimbaits right now, and the Shad Shape Swimmer provides the perfect action and profile that anglers (and fish) are craving. Available in 3 sizes (3.2'', 3.7'', 4.2'') and 17 colors, 5 of which are brand new Stealth Series colors, the Shad Shape Swimmer is a must-have for any serious swimbait fisherman. High quality materials and incredible color options, both of which Yamamoto is known for, team up with an awesome design to offer you a swim bait that produces as well as it looks. 8 Pack</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>YAM054</v>
+      </c>
+      <c r="B450">
+        <v>21</v>
+      </c>
+      <c r="C450" t="str">
+        <v>Zako Swimbait</v>
+      </c>
+      <c r="D450" t="str">
+        <v>Zako Swimbait</v>
+      </c>
+      <c r="E450" t="str">
+        <v/>
+      </c>
+      <c r="F450" t="str">
+        <v/>
+      </c>
+      <c r="G450" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H450" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I450" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J450" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K450" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait.jpg</v>
+      </c>
+      <c r="L450" t="str">
+        <v>2026-04-10T10:44:21.490Z</v>
+      </c>
+      <c r="M450" t="str">
+        <v>2026-04-10T10:44:21.490Z</v>
+      </c>
+      <c r="N450" t="str">
+        <v>New 2025 Color: 4" | 9025 - Sungill The Zako Swimbait is the number 1 vibrating jig trailer on the market for good reason. Measuring in at 3 inches and 4 inches long, the Zako's segmented design and natural profile makes it the perfect match for your favorite vibrating jig. But don't limit it to just that application, it can be used a spinnerbait trailer and many other ways as well. Tie one on and find out for yourself. 3"- 8 Pack 4"- 6 Pack</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>YAM055</v>
+      </c>
+      <c r="B451">
+        <v>21</v>
+      </c>
+      <c r="C451" t="str">
+        <v>4″ Zako Swimbait Bulk Packs</v>
+      </c>
+      <c r="D451" t="str">
+        <v>4″ Zako Swimbait Bulk Packs</v>
+      </c>
+      <c r="E451" t="str">
+        <v/>
+      </c>
+      <c r="F451" t="str">
+        <v/>
+      </c>
+      <c r="G451" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H451" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I451" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J451" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K451" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__zako_swimbait_bulk_packs.jpg</v>
+      </c>
+      <c r="L451" t="str">
+        <v>2026-04-10T10:44:22.697Z</v>
+      </c>
+      <c r="M451" t="str">
+        <v>2026-04-10T10:44:22.697Z</v>
+      </c>
+      <c r="N451" t="str">
+        <v>The Zako Swimbait is the number 1 vibrating jig trailer on the market for good reason. Measuring in at 4 inches long, the Zako’s segmented design and natural profile makes it the perfect match for your favorite vibrating jig. But don’t limit it to just that application, it can be used a spinnerbait trailer and many other ways as well. Tie one on and find out for yourself. Available in 50 or 100 packs.</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>YAM056</v>
+      </c>
+      <c r="B452">
+        <v>21</v>
+      </c>
+      <c r="C452" t="str">
+        <v>4″ Paddle Tail Zako 5pk</v>
+      </c>
+      <c r="D452" t="str">
+        <v>4″ Paddle Tail Zako 5pk</v>
+      </c>
+      <c r="E452" t="str">
+        <v/>
+      </c>
+      <c r="F452" t="str">
+        <v/>
+      </c>
+      <c r="G452" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H452" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I452" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J452" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K452" t="str">
+        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__paddle_tail_zako_5pk.jpg</v>
+      </c>
+      <c r="L452" t="str">
+        <v>2026-04-10T10:44:25.094Z</v>
+      </c>
+      <c r="M452" t="str">
+        <v>2026-04-10T10:44:25.094Z</v>
+      </c>
+      <c r="N452" t="str">
+        <v>The Paddle Tail Zako is everything you know and love about the Zako swimbait, but with a little more action! Featuring the same durable body as the traditional Zako, the Paddle Tail Zako implements a rectangular tail to give it that hard-kicking swimming motion anglers desire. The Paddle Tail Zako shines brightest on the back of a swim jig, but it can be used as a trailer for anything an angler may desire. 5 per Pack</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>YAM057</v>
+      </c>
+      <c r="B453">
+        <v>21</v>
+      </c>
+      <c r="C453" t="str">
         <v>5″ D-Shad 7pk</v>
       </c>
-      <c r="D442" t="str">
+      <c r="D453" t="str">
         <v>5″ D-Shad 7pk</v>
       </c>
-      <c r="E442" t="str">
-        <v/>
-      </c>
-      <c r="F442" t="str">
-        <v/>
-      </c>
-      <c r="G442" t="str">
-        <v>softbait</v>
-      </c>
-      <c r="H442" t="str">
-        <v/>
-      </c>
-      <c r="I442" t="str">
-        <v>subsurface</v>
-      </c>
-      <c r="J442" t="str">
-        <v>swimming</v>
-      </c>
-      <c r="K442" t="str">
+      <c r="E453" t="str">
+        <v/>
+      </c>
+      <c r="F453" t="str">
+        <v/>
+      </c>
+      <c r="G453" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H453" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I453" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J453" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K453" t="str">
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__d_shad_7pk.jpg</v>
       </c>
-      <c r="L442" t="str">
-        <v>2026-04-10T10:19:57.724Z</v>
-      </c>
-      <c r="M442" t="str">
-        <v>2026-04-10T10:19:57.724Z</v>
-      </c>
-      <c r="N442" t="str">
-        <v/>
-      </c>
-      <c r="O442" t="str">
-        <v/>
-      </c>
-      <c r="P442" t="str">
-        <v/>
+      <c r="L453" t="str">
+        <v>2026-04-10T10:44:26.290Z</v>
+      </c>
+      <c r="M453" t="str">
+        <v>2026-04-10T10:44:26.290Z</v>
+      </c>
+      <c r="N453" t="str">
+        <v>New 2025 Color: 433 - Glowstick The D-Shad is a new twist on an old classic. Heavier than a traditional soft-body jerk bait, the D-Shad allows for aggressive action, while allowing you to fish it more effectively all-throughout the water column. This comes in handy when fish want fast retrieval. When paused, the D-Shad will sink much like a Senko. The D-Shad's heavier tail provides a shimmy that drives fish mad. 7 Per Pack</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P442"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P453"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P453"/>
+  <dimension ref="A1:O453"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,9 +445,6 @@
       <c r="O1" t="str">
         <v>official_link</v>
       </c>
-      <c r="P1" t="str">
-        <v>Description</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -492,12 +489,6 @@
       <c r="N2" t="str">
         <v/>
       </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -542,12 +533,6 @@
       <c r="N3" t="str">
         <v/>
       </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -592,12 +577,6 @@
       <c r="N4" t="str">
         <v/>
       </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -642,12 +621,6 @@
       <c r="N5" t="str">
         <v/>
       </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -692,12 +665,6 @@
       <c r="N6" t="str">
         <v/>
       </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -742,12 +709,6 @@
       <c r="N7" t="str">
         <v/>
       </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -792,12 +753,6 @@
       <c r="N8" t="str">
         <v/>
       </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -842,12 +797,6 @@
       <c r="N9" t="str">
         <v/>
       </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -892,12 +841,6 @@
       <c r="N10" t="str">
         <v/>
       </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -942,12 +885,6 @@
       <c r="N11" t="str">
         <v/>
       </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -992,12 +929,6 @@
       <c r="N12" t="str">
         <v/>
       </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1042,12 +973,6 @@
       <c r="N13" t="str">
         <v/>
       </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1092,12 +1017,6 @@
       <c r="N14" t="str">
         <v/>
       </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1142,12 +1061,6 @@
       <c r="N15" t="str">
         <v/>
       </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1192,12 +1105,6 @@
       <c r="N16" t="str">
         <v/>
       </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1242,12 +1149,6 @@
       <c r="N17" t="str">
         <v/>
       </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1292,12 +1193,6 @@
       <c r="N18" t="str">
         <v/>
       </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1342,12 +1237,6 @@
       <c r="N19" t="str">
         <v/>
       </c>
-      <c r="O19" t="str">
-        <v/>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1392,12 +1281,6 @@
       <c r="N20" t="str">
         <v/>
       </c>
-      <c r="O20" t="str">
-        <v/>
-      </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1442,12 +1325,6 @@
       <c r="N21" t="str">
         <v/>
       </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1492,12 +1369,6 @@
       <c r="N22" t="str">
         <v/>
       </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1542,12 +1413,6 @@
       <c r="N23" t="str">
         <v/>
       </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1592,12 +1457,6 @@
       <c r="N24" t="str">
         <v/>
       </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1642,12 +1501,6 @@
       <c r="N25" t="str">
         <v/>
       </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1692,12 +1545,6 @@
       <c r="N26" t="str">
         <v/>
       </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1742,12 +1589,6 @@
       <c r="N27" t="str">
         <v/>
       </c>
-      <c r="O27" t="str">
-        <v/>
-      </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1792,12 +1633,6 @@
       <c r="N28" t="str">
         <v/>
       </c>
-      <c r="O28" t="str">
-        <v/>
-      </c>
-      <c r="P28" t="str">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1842,12 +1677,6 @@
       <c r="N29" t="str">
         <v/>
       </c>
-      <c r="O29" t="str">
-        <v/>
-      </c>
-      <c r="P29" t="str">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1892,12 +1721,6 @@
       <c r="N30" t="str">
         <v/>
       </c>
-      <c r="O30" t="str">
-        <v/>
-      </c>
-      <c r="P30" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1942,12 +1765,6 @@
       <c r="N31" t="str">
         <v/>
       </c>
-      <c r="O31" t="str">
-        <v/>
-      </c>
-      <c r="P31" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1992,12 +1809,6 @@
       <c r="N32" t="str">
         <v/>
       </c>
-      <c r="O32" t="str">
-        <v/>
-      </c>
-      <c r="P32" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -2042,12 +1853,6 @@
       <c r="N33" t="str">
         <v/>
       </c>
-      <c r="O33" t="str">
-        <v/>
-      </c>
-      <c r="P33" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -2092,12 +1897,6 @@
       <c r="N34" t="str">
         <v/>
       </c>
-      <c r="O34" t="str">
-        <v/>
-      </c>
-      <c r="P34" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -2142,12 +1941,6 @@
       <c r="N35" t="str">
         <v/>
       </c>
-      <c r="O35" t="str">
-        <v/>
-      </c>
-      <c r="P35" t="str">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -2192,12 +1985,6 @@
       <c r="N36" t="str">
         <v/>
       </c>
-      <c r="O36" t="str">
-        <v/>
-      </c>
-      <c r="P36" t="str">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2242,12 +2029,6 @@
       <c r="N37" t="str">
         <v/>
       </c>
-      <c r="O37" t="str">
-        <v/>
-      </c>
-      <c r="P37" t="str">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2292,12 +2073,6 @@
       <c r="N38" t="str">
         <v/>
       </c>
-      <c r="O38" t="str">
-        <v/>
-      </c>
-      <c r="P38" t="str">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2342,12 +2117,6 @@
       <c r="N39" t="str">
         <v/>
       </c>
-      <c r="O39" t="str">
-        <v/>
-      </c>
-      <c r="P39" t="str">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2392,12 +2161,6 @@
       <c r="N40" t="str">
         <v/>
       </c>
-      <c r="O40" t="str">
-        <v/>
-      </c>
-      <c r="P40" t="str">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2442,12 +2205,6 @@
       <c r="N41" t="str">
         <v/>
       </c>
-      <c r="O41" t="str">
-        <v/>
-      </c>
-      <c r="P41" t="str">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2492,12 +2249,6 @@
       <c r="N42" t="str">
         <v/>
       </c>
-      <c r="O42" t="str">
-        <v/>
-      </c>
-      <c r="P42" t="str">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2542,12 +2293,6 @@
       <c r="N43" t="str">
         <v/>
       </c>
-      <c r="O43" t="str">
-        <v/>
-      </c>
-      <c r="P43" t="str">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2592,12 +2337,6 @@
       <c r="N44" t="str">
         <v/>
       </c>
-      <c r="O44" t="str">
-        <v/>
-      </c>
-      <c r="P44" t="str">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2642,12 +2381,6 @@
       <c r="N45" t="str">
         <v/>
       </c>
-      <c r="O45" t="str">
-        <v/>
-      </c>
-      <c r="P45" t="str">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2692,12 +2425,6 @@
       <c r="N46" t="str">
         <v/>
       </c>
-      <c r="O46" t="str">
-        <v/>
-      </c>
-      <c r="P46" t="str">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2742,12 +2469,6 @@
       <c r="N47" t="str">
         <v/>
       </c>
-      <c r="O47" t="str">
-        <v/>
-      </c>
-      <c r="P47" t="str">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2792,12 +2513,6 @@
       <c r="N48" t="str">
         <v/>
       </c>
-      <c r="O48" t="str">
-        <v/>
-      </c>
-      <c r="P48" t="str">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2842,12 +2557,6 @@
       <c r="N49" t="str">
         <v/>
       </c>
-      <c r="O49" t="str">
-        <v/>
-      </c>
-      <c r="P49" t="str">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2892,12 +2601,6 @@
       <c r="N50" t="str">
         <v/>
       </c>
-      <c r="O50" t="str">
-        <v/>
-      </c>
-      <c r="P50" t="str">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2942,12 +2645,6 @@
       <c r="N51" t="str">
         <v/>
       </c>
-      <c r="O51" t="str">
-        <v/>
-      </c>
-      <c r="P51" t="str">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2992,12 +2689,6 @@
       <c r="N52" t="str">
         <v/>
       </c>
-      <c r="O52" t="str">
-        <v/>
-      </c>
-      <c r="P52" t="str">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -3042,12 +2733,6 @@
       <c r="N53" t="str">
         <v/>
       </c>
-      <c r="O53" t="str">
-        <v/>
-      </c>
-      <c r="P53" t="str">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3092,12 +2777,6 @@
       <c r="N54" t="str">
         <v/>
       </c>
-      <c r="O54" t="str">
-        <v/>
-      </c>
-      <c r="P54" t="str">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3142,12 +2821,6 @@
       <c r="N55" t="str">
         <v/>
       </c>
-      <c r="O55" t="str">
-        <v/>
-      </c>
-      <c r="P55" t="str">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3192,12 +2865,6 @@
       <c r="N56" t="str">
         <v/>
       </c>
-      <c r="O56" t="str">
-        <v/>
-      </c>
-      <c r="P56" t="str">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3242,12 +2909,6 @@
       <c r="N57" t="str">
         <v/>
       </c>
-      <c r="O57" t="str">
-        <v/>
-      </c>
-      <c r="P57" t="str">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3292,12 +2953,6 @@
       <c r="N58" t="str">
         <v/>
       </c>
-      <c r="O58" t="str">
-        <v/>
-      </c>
-      <c r="P58" t="str">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3342,12 +2997,6 @@
       <c r="N59" t="str">
         <v/>
       </c>
-      <c r="O59" t="str">
-        <v/>
-      </c>
-      <c r="P59" t="str">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3392,12 +3041,6 @@
       <c r="N60" t="str">
         <v/>
       </c>
-      <c r="O60" t="str">
-        <v/>
-      </c>
-      <c r="P60" t="str">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3442,12 +3085,6 @@
       <c r="N61" t="str">
         <v/>
       </c>
-      <c r="O61" t="str">
-        <v/>
-      </c>
-      <c r="P61" t="str">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3492,12 +3129,6 @@
       <c r="N62" t="str">
         <v/>
       </c>
-      <c r="O62" t="str">
-        <v/>
-      </c>
-      <c r="P62" t="str">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3542,12 +3173,6 @@
       <c r="N63" t="str">
         <v/>
       </c>
-      <c r="O63" t="str">
-        <v/>
-      </c>
-      <c r="P63" t="str">
-        <v/>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3592,12 +3217,6 @@
       <c r="N64" t="str">
         <v/>
       </c>
-      <c r="O64" t="str">
-        <v/>
-      </c>
-      <c r="P64" t="str">
-        <v/>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3642,12 +3261,6 @@
       <c r="N65" t="str">
         <v/>
       </c>
-      <c r="O65" t="str">
-        <v/>
-      </c>
-      <c r="P65" t="str">
-        <v/>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3692,12 +3305,6 @@
       <c r="N66" t="str">
         <v/>
       </c>
-      <c r="O66" t="str">
-        <v/>
-      </c>
-      <c r="P66" t="str">
-        <v/>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3742,12 +3349,6 @@
       <c r="N67" t="str">
         <v/>
       </c>
-      <c r="O67" t="str">
-        <v/>
-      </c>
-      <c r="P67" t="str">
-        <v/>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3792,12 +3393,6 @@
       <c r="N68" t="str">
         <v/>
       </c>
-      <c r="O68" t="str">
-        <v/>
-      </c>
-      <c r="P68" t="str">
-        <v/>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3842,12 +3437,6 @@
       <c r="N69" t="str">
         <v/>
       </c>
-      <c r="O69" t="str">
-        <v/>
-      </c>
-      <c r="P69" t="str">
-        <v/>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3892,12 +3481,6 @@
       <c r="N70" t="str">
         <v/>
       </c>
-      <c r="O70" t="str">
-        <v/>
-      </c>
-      <c r="P70" t="str">
-        <v/>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3942,12 +3525,6 @@
       <c r="N71" t="str">
         <v/>
       </c>
-      <c r="O71" t="str">
-        <v/>
-      </c>
-      <c r="P71" t="str">
-        <v/>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3992,12 +3569,6 @@
       <c r="N72" t="str">
         <v/>
       </c>
-      <c r="O72" t="str">
-        <v/>
-      </c>
-      <c r="P72" t="str">
-        <v/>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -4042,12 +3613,6 @@
       <c r="N73" t="str">
         <v/>
       </c>
-      <c r="O73" t="str">
-        <v/>
-      </c>
-      <c r="P73" t="str">
-        <v/>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -4092,12 +3657,6 @@
       <c r="N74" t="str">
         <v/>
       </c>
-      <c r="O74" t="str">
-        <v/>
-      </c>
-      <c r="P74" t="str">
-        <v/>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -4142,12 +3701,6 @@
       <c r="N75" t="str">
         <v/>
       </c>
-      <c r="O75" t="str">
-        <v/>
-      </c>
-      <c r="P75" t="str">
-        <v/>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -4192,12 +3745,6 @@
       <c r="N76" t="str">
         <v/>
       </c>
-      <c r="O76" t="str">
-        <v/>
-      </c>
-      <c r="P76" t="str">
-        <v/>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4242,12 +3789,6 @@
       <c r="N77" t="str">
         <v/>
       </c>
-      <c r="O77" t="str">
-        <v/>
-      </c>
-      <c r="P77" t="str">
-        <v/>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4292,12 +3833,6 @@
       <c r="N78" t="str">
         <v/>
       </c>
-      <c r="O78" t="str">
-        <v/>
-      </c>
-      <c r="P78" t="str">
-        <v/>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4342,12 +3877,6 @@
       <c r="N79" t="str">
         <v>Featuring a patented Double Inertial Balancer System for head-turning action, the DIAMANTE SONIC SLIDE delivers a dramatic 180-degree walk and extended sliding action. Generating aggressive turbulence and a deep metal knock with each turn, SONIC SLIDE calls fish up from surprising depths to trigger surface-breaching strikes. With a deep-cut keel design to enhance responsiveness and an aerodynamically optimized body, SONIC SLIDE is built for long-distance deployment in rough and calm waters alike.</v>
       </c>
-      <c r="O79" t="str">
-        <v/>
-      </c>
-      <c r="P79" t="str">
-        <v/>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4392,12 +3921,6 @@
       <c r="N80" t="str">
         <v>メガバス創世期に誕生し、数多の伝説を築き上げたDOG-Xシリーズ。メガバス創業者、伊東由樹が見出し、DOG-Xに宿した不変の原理とハイドロメカニクスを最大限に体現する、DOG-Xシリーズのグレートマザーが降臨。ブランドン・パラニュークと共に闘う米国フィールドから世界に解き放ち、DOGMAXがいよいよグローバルなフィールドでモンスターを制圧。 強大でトルクフルなターンインとテールアウトを生み出す、「重心分割式シーソーバランサーシステム（PAT.）」、超・長距離スライドを生み出す「タンデム慣性バランサーシステム（PAT.）」、徹底的に水を噛み込んで食らいつき、スタビリティを高めながらリアルなボイルサウンドを発生させる「ウォータースルー・ギル（PAT.）」、内部のボールウエイトがピンポイント接触する衝突によって引き起こす「衝撃波」と硬質な「ノッキングサウンド」が、深層のモンスターにも果敢にアピール。誰もが手軽に130mmのビッグボディを軽快に操作でき、メガバス・トップウォーターマジックの神髄に触れることができます。 あらゆるフィッシュイーターのMAXサイズをフィーディングモードに入れてバイトさせてしまう、ファンクショナルなペンシルベイトです。</v>
       </c>
-      <c r="O80" t="str">
-        <v/>
-      </c>
-      <c r="P80" t="str">
-        <v/>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4442,12 +3965,6 @@
       <c r="N81" t="str">
         <v>Introduced in 1996,POPX continues to dominate the high-end top-water bait markets of both Japan and the United States. Equipped with MEGABASS original SIDE-STEPPING BALANCER(PAT),POPX walks a rolling dog-walk unlike any other poppers, and the WATER DUCTS(PAT)which imitate the bubbly water coming out of gills and help create a natural"bio-sound", not an ordinary popping sound. POPX also spits, not splashes, quite a distance. Currently 16 colors are available."GG"stands for GUANIUM GHOST, the most shad-like finish, "PM"PEARL MICA(including SG CRACKED finish)and "GP"GUANIUM PHANTOM(including GP CRACKED finish),a see through phantom finish.</v>
       </c>
-      <c r="O81" t="str">
-        <v/>
-      </c>
-      <c r="P81" t="str">
-        <v/>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4492,12 +4009,6 @@
       <c r="N82" t="str">
         <v>The unique cup shape of the BABY POPX creates an irresistible water-pushing action. Its design produces a lively and engaging splash sound, perfectly complemented by its ability to respond with agility to even the most delicate rod work. With a nuanced short slide and splashing dog walk action, this diminutive popper is designed to captivate even the most elusive game. Despite its ultra-compact body, the BABY POPX offers incredible long-distance casting ability, allowing anglers to cover a wide area with ease and precision. Its centrally placed line eye adds dimension to the traditional popping retrieve, enabling a nimble dog walk to add another layer of allure to its presentation. Further, the BABY POPX’s micro form enables a stealthy splashdown at the end of a long cast, staying under the radar of easily spooked monsters until its pinpoint agility and splashing siren-song call explosive bites from below.</v>
       </c>
-      <c r="O82" t="str">
-        <v/>
-      </c>
-      <c r="P82" t="str">
-        <v/>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4542,12 +4053,6 @@
       <c r="N83" t="str">
         <v>KARASHI iGは、ハイドロダイナミクスから生まれた独特なキールヘッド(D.PAT.P)により、優れた直進性能を発揮。リトリーブ速度のわずかな変化に対し、あたかも船の揺れ戻しを抑制するような、ボディの姿勢変化を的確に微調整して補正するアクションを発生。 ただゆっくりと引くだけで生まれる幻惑の引き波と、卓越したスタビリティ効果が、これまでのi字系を見切ったクレバーフィッシュを的確にバイトに持ち込みます。 テールにセットした独自のフレアファイバーはキールヘッドの直進性を促進。 二度喰い、三度喰いさえ多発するKARASHI iGは、シビアなフィールドで使ってこそ差がつく、タフフィッシュを獲るために特化したスペシャルスペックが満載。勝つために使う、コンペティティブなi字系です。</v>
       </c>
-      <c r="O83" t="str">
-        <v/>
-      </c>
-      <c r="P83" t="str">
-        <v/>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4592,12 +4097,6 @@
       <c r="N84" t="str">
         <v>KARASHI 80は、オリジナルのKARASHI同様に水面直下のドッグウォークアクションを手軽かつ、ダイナミックに展開。さながら「リップレス・ジャークベイト」ともいうべき水面下で展開する規則的なロングダート性能は、水面までターゲットが出切らないシビアな状況下で新次元の釣獲パフォーマンスを発揮。 伊東由樹のハイドロダイナミクス理論が生み出したファンクショナルなボディ形態は、左右への規則正しいドッグウォークのリズムが刻みやすい節度ある水噛み抵抗感をもたらし、ジャークやトゥイッチによる水面直下での左右への規則的なロングダートを実現。 まさに、リップレス・ジャークベイトと呼べるＮＥＷジャンルを創造し、稀代のバージンインパクトを発揮します。 水面に出切らないナーバスなターゲットに対して、ダートアクションを仕掛けて喰わせる一撃必釣のシークレットパフォーマンスは圧巻。ぜひ、マジカルな釣果をご体感ください。</v>
       </c>
-      <c r="O84" t="str">
-        <v/>
-      </c>
-      <c r="P84" t="str">
-        <v/>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4642,12 +4141,6 @@
       <c r="N85" t="str">
         <v>The KARASHI is the embodiment of next-generation Japanese finesse. This secret worming bait will change the face of 3-inch finesse soft bait fishing. The super-natural feel of this bite-sized lure entices even the spookiest fish to bite and hold impulsively. For targets that see your other lures but hesitate to bite, the KARASHI is your secret “one shot, one kill” bite-triggering weapon. 1. With twitching, the KARASHI exhibits agile dog-walking and darting action. 2. With slow retrieves, KARASHI performs an I-shaped action. The defenseless wobbling action evokes injured bait, triggering bites from opportunistic feeders. The extremely natural minute-vibrations trigger bites from clever fish. KARASHI generates overwhelming performance from the combination of its darting action and I-shaped action.</v>
       </c>
-      <c r="O85" t="str">
-        <v/>
-      </c>
-      <c r="P85" t="str">
-        <v/>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4692,12 +4185,6 @@
       <c r="N86" t="str">
         <v>DOG-X Jr. is not simply a downsized version of our original DOG-X. It is certainly a bit smaller than DOG-X as the name indicates, but it is equipped with a new lengthwise moving balancer as well as the now familiar SIDE-STEPPING MOVING BALANCER (PAT.) of the original DOG-X. This new balancer pushes the bait while walking, so that the roll-walk action of DOG-X Jr. is sharper and more dynamic for its size. The point is that smaller bait does not have to suffer from a smaller action. The action of DOG-X Jr. will remind you of the baitfish chased by a predator, frantically ripping and skipping the water surface. Also, you will find out that casting and retrieving DOG-X Jr. with F1 or F2 class Destroyer bait rods is extremely enjoyable due to their high compatibility. If you want to experience the fastest and the smoothest dog-walk action of your life, you must go for DOG-X Jr.</v>
       </c>
-      <c r="O86" t="str">
-        <v/>
-      </c>
-      <c r="P86" t="str">
-        <v/>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4742,12 +4229,6 @@
       <c r="N87" t="str">
         <v>KARASHI SPINNERは、通常のI字系ルアーによるアプローチでは今一つ反応が得られなかった完全ニュートラルなバスに高い効果を発揮するプロップベイト。長距離リトリーブにおける優れた直進安定性と正姿勢への素早い復帰は、独自のキールヘッドデザインによるもの。ウィードボトムの表層～中層、シャローやオーバーハング下などで水面直下をスローにただ引きするだけでOKです。 また、水面へと浮上させ、軽くジャーク＆リトリーブすれば、稚鮎などナチュラルベイトの繊細なボイルを演出。通常のバズベイトやスイッシャーではインパクトが強すぎる時、KARASHI SPINNERなら的確にバイトに持ち込みます。</v>
       </c>
-      <c r="O87" t="str">
-        <v/>
-      </c>
-      <c r="P87" t="str">
-        <v/>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4792,12 +4273,6 @@
       <c r="N88" t="str">
         <v>As with other Megabass baits, POPMAX demands a lot of explaining. The original mold was again carved out by Yuki Ito rather than relying on computer design programs. And the paint works and the overall quality is impeccable as expected of Megabass. Also, POPMAX features a unique water flow system which consists of six water intakes and a water chamber. Instead of the regular water-through system used for POPX, this system utilizes the water pressure change inside the water chamber, making it act like a lip. Furthermore, when paused, the water in the chamber goes out and lifts its head, ready for a splash with a light rod action. With a gentle rod tip action POPMAX will roll-walk dynamically grabbing the water with each rolling action.</v>
       </c>
-      <c r="O88" t="str">
-        <v/>
-      </c>
-      <c r="P88" t="str">
-        <v/>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4842,12 +4317,6 @@
       <c r="N89" t="str">
         <v>The DOG-X QUICK WALKER supercharges the original DOG-X's dog walking prowess with a redesigned body, improved balancer system, and one-knock sound. It greatly surpasses the expectations for standard-sized pencil baits with its dynamic water displacement, sharp table turns and its one-knock sound, stimulating cruising fish in the mid range. The casting distance has been improved upon as well, to allow for speedy coverage of wide areas. This DOG-X will set fire to dormant beasts, even more so than the original.</v>
       </c>
-      <c r="O89" t="str">
-        <v/>
-      </c>
-      <c r="P89" t="str">
-        <v/>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4892,12 +4361,6 @@
       <c r="N90" t="str">
         <v>DOG-X has come into the world during Megabass genesis and has continued to send out Megabass engineering to the world. Taking over its legends, finally in year 2010 Super Dog-X has awakened. “High speed-dog walk” and the responsive “Quick slide &amp; turn” is achieved. Overturning the common sense of low water resistant compact pencil baits, the high level operability will not let the others follow. “See-saw balancing system PAT.” updated from the engineering of the first model is added, and the new design “Water through-Gill PAT.” which increases its stability by biting the water is applied. The original balancing body D.PAT.P by the high mounted-line eye that behaves responsively has been applied to achieve a real game. Many of Yuki Ito’s lure technology and design logic is loaded. DOG-X that caught fishes that could not be caught has evolved into a new generation DOG-X challenging clever and tough monsters in the 21st century. Not only with slow taper-light action rod, it is also possible to make dog walk actions with medium heavy action rods. Please check out the overwhelming “easy control ability” at all sorts of fields.</v>
       </c>
-      <c r="O90" t="str">
-        <v/>
-      </c>
-      <c r="P90" t="str">
-        <v/>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4942,12 +4405,6 @@
       <c r="N91" t="str">
         <v>Don’t be fooled by its size—this DOG-X was built for GIANTS. Powered by a patented SIDE-STEPPING BALANCER, the GIANT DOG-X is engineered to elevate the walking game of novices and experts alike. Featuring a tungsten balancer that moves laterally from left-to-right, the system throws its weight behind each turn for a sharper walk and a unique roll that flashes the GIANT DOG-X’s exquisite detail to monsters below. This effortlessly crisp and dynamic roll-walking action draws vicious strikes in even the toughest slick-calm conditions, bringing explosive performance to angling arsenals around the world.</v>
       </c>
-      <c r="O91" t="str">
-        <v/>
-      </c>
-      <c r="P91" t="str">
-        <v/>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4992,12 +4449,6 @@
       <c r="N92" t="str">
         <v>アンスラックスは、ローラージャイロ・バランサーシステム（PAT.P）によって、シャフトバランサー上を転位するボールウエイトが甲高いクリックサウンドを発生させ、多彩なマルチアクションを演出するウェイクベイト。 スローリトリーブでは、水面でスーパーローリングアクションを生み出し、腹部のフィン（尻ビレ）が左右にテイリングして水流を掻き分け、独自の三角波でアピール。リトリーブ速度を上げると、水面直下10～20㎝程度をローリング・スイムするサブサーフェスシャッドとして活躍。また、ジャークによるスラッピングでは、水面でスプラッシュやバブルを発生させるボイルベイトを演出。ストップ＆ゴーでは、ダイブ後にフラッタリングやライズアップするパニックベイトを再現。 多彩なアクションとダイナミックなパフォーマンスがもたらすアンスラックス独自の釣獲力を是非フィールドでご体感ください。</v>
       </c>
-      <c r="O92" t="str">
-        <v/>
-      </c>
-      <c r="P92" t="str">
-        <v/>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -5042,12 +4493,6 @@
       <c r="N93" t="str">
         <v>The MEGADOG-X is a supercharged walking bait built to drive trophy　freshwater targets into a reactive frenzy. Clocking in at a hefty 180mm (7in), the MEGADOG-X powers a strategic topwater approach whenever big fish are keyed in on big meals. With a simple reel/stop retrieve, the MEGADOG-X will slide with surprising ease. With more vigorous rod work, the lure will explode into a fury of action, setting off an aggressive splash-walking chain reaction that calls to the largest predators in the area. Incorporating decades of dog-walking refinement, the MEGADOG-X makes big bait topwater angling even more accessible and explosive. * The photograph is a prototype</v>
       </c>
-      <c r="O93" t="str">
-        <v/>
-      </c>
-      <c r="P93" t="str">
-        <v/>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -5092,12 +4537,6 @@
       <c r="N94" t="str">
         <v>アンスラックスは、ローラージャイロ・バランサーシステム（PAT.P）によって、シャフトバランサー上を転位するボールウエイトが甲高いクリックサウンドを発生させ、多彩なマルチアクションを演出するウェイクベイト。 スローリトリーブでは、水面でスーパーローリングアクションを生み出し、腹部のフィン（尻ビレ）が左右にテイリングして水流を掻き分け、独自の三角波でアピール。リトリーブ速度を上げると、水面直下10～20㎝程度をローリング・スイムするサブサーフェスシャッドとして活躍。また、ジャークによるスラッピングでは、水面でスプラッシュやバブルを発生させるボイルベイトを演出。ストップ＆ゴーでは、ダイブ後にフラッタリングやライズアップするパニックベイトを再現。 多彩なアクションとダイナミックなパフォーマンスがもたらすアンスラックス独自の釣獲力を是非フィールドでご体感ください。</v>
       </c>
-      <c r="O94" t="str">
-        <v/>
-      </c>
-      <c r="P94" t="str">
-        <v/>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -5142,12 +4581,6 @@
       <c r="N95" t="str">
         <v>伊東由樹がプライベートゲーム用に手作りしていたランカーキラー・スイッシャーがエクスプローズ。 独特なひねり形状のプロペラには、独自のギアホール加工が施されており、スクラッチサウンドを発生。超低重心マウントしたフラットバランサーによって、激しいロッドワークによるジャークでもボディを回転させることなく、きっちりとラフウォーターに喰らいつく卓越したスタビリティを発揮。水面を激しく割るラフバイトにおいても確実なフックセットを実現します。 スローリトリーブによるタダ巻きでは、時折、ゆらりとウォブリング。凪の水面ではデッドリーベイトを効果的に演出します。 他のスイッシャーとは明らかに違う、一目瞭然のスペックを内包するプロップベイトのスペシャルエディションです。</v>
       </c>
-      <c r="O95" t="str">
-        <v/>
-      </c>
-      <c r="P95" t="str">
-        <v/>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -5192,12 +4625,6 @@
       <c r="N96" t="str">
         <v>The XPOD is the world's first transformation-plug. The COMMAND BILL(PAT.), which has seven distinct settings, is adjustable according to angler preference and specific conditions. Each rugged setting alters the pressure and volume in the WATER INTAKE(PAT.), changing the lure's displacement, weight ratio, and body balance. By altering the properties of rod actino and lip setting, it can be adjusted for use in various situations. The XPOD is a multi-performance lure, allowing anglers to tap into its many abilities and applications. It can transform into 4 modes for top water: a roll-walking pencil bait, a dog-walking popper for targeting specific areas, a sliding pencil popper for targeting wide areas, and a splash head to lure in prey through sound and splashing. For the sub-surface it has 2 modes: a diving pencil and a diving popper. In addition, it has a special trick-darting dive mode using random trajectories and rolling action, allowing it to be used for slow retrieves as a diving swim-bait.</v>
       </c>
-      <c r="O96" t="str">
-        <v/>
-      </c>
-      <c r="P96" t="str">
-        <v/>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -5242,12 +4669,6 @@
       <c r="N97" t="str">
         <v>The XPOD symbolizes the new era of Megabass top water baits. Loved across the world, it is now available in a smaller profile, retaining its captivating appearance and its situation-specific adaptability. Its realistic form will entice the most cunning of prey. While the profile may be small, it packs the same powerful punch as the original, and is ready to decisively bring down its targets.</v>
       </c>
-      <c r="O97" t="str">
-        <v/>
-      </c>
-      <c r="P97" t="str">
-        <v/>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -5292,12 +4713,6 @@
       <c r="N98" t="str">
         <v>Carefully honed for explosive walking action, DOG-X DIAMANTE cuts through water with unparalleled responsiveness. Featuring a Deep Cut Keel design to sharpen action and angler control, DIAMANTE walks with a lively commotion in calm and rough conditions alike. Designed to excel even at high speeds, DIAMANTE is ideally suited to rapid deployment, searching wide areas quickly and effectively. Rattle-tuned to the exacting specifications of veteran pros, DIAMANTE generates an enticing surface commotion, drawing strikes from afar.</v>
       </c>
-      <c r="O98" t="str">
-        <v/>
-      </c>
-      <c r="P98" t="str">
-        <v/>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -5342,12 +4757,6 @@
       <c r="N99" t="str">
         <v>MPWは、POPXとは異なるパフォーマンスを発揮する、「テーブルターンを高速化してなお、ネチることができる」異次元のクイックレスポンス・ポッパーを創生。 メガバスのカタログモデルには存在しない、POPXとBabyPOPXの「中間サイズ」は、極みのフィネスポッパーゲームをさらにコンプリート。 アナザーPOPXの魔力は、スレきったメジャーレイクのクレバーフィッシュを相手にお確かめください。</v>
       </c>
-      <c r="O99" t="str">
-        <v/>
-      </c>
-      <c r="P99" t="str">
-        <v/>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -5392,12 +4801,6 @@
       <c r="N100" t="str">
         <v>MEGADOGは、メガバスが誇る稀代の名作DOG-Xのポテンシャルを、異次元のレベルまで高めた対ビッグフィッシュ用のスペシャルウェポンです。200mmを超える大型のベイトを水面に追い込み捕食するモンスターフィッシュのみをターゲットとし、既成概念を破壊する強烈なインパクトとアピール力を発揮したメガサイズペンシルベイトです。</v>
       </c>
-      <c r="O100" t="str">
-        <v/>
-      </c>
-      <c r="P100" t="str">
-        <v/>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -5442,12 +4845,6 @@
       <c r="N101" t="str">
         <v>KIRINJIの生みの親、伊東由樹は、水面直下にウィードが迫る広域エリアにて、KIRINJIを表層でただゆっくりと引くだけで、スピナーベイトに連日叩かれてきたスプーキーなバスを驚異的に釣っています。KIRINJIが水面でもたらす独特なハイピッチ・ロール・スクリューは、タフなバスにとても効果的です。同エリアから連続して何度もチェイスしてくる様は、KIRINJIが発生させる絶妙なライブ波動によるものでしょう。 MPWでは、フレッシュウォーターによりアジャストする特別なKIRINJIを製作。鋭いポッピングやスプラッシュが出しやすい比重へとチューンし、あの独特なライブ波動に加わるスパイシーなインパクトがシャローに散発するランカーをより広域から惹き寄せます。</v>
       </c>
-      <c r="O101" t="str">
-        <v/>
-      </c>
-      <c r="P101" t="str">
-        <v/>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -5492,12 +4889,6 @@
       <c r="N102" t="str">
         <v>Orca はイージーなロッドワークによって、アングラーの意図を超えた「変幻アクション」を誰もが自然に生み出すことができる、数奇なプロップフォーム（プロペラの捻り形態）ベイトです。計算された捻りボディが水を的確に絡め取り、水流の巻き込みと剥離を適宜に発生させることで、アングラーが意図しないアクションを自然に生み出します。Orca には使い込むほどにハマってしまう、こだわりのトップウォータープラッガーを虜にする特別な魔力が潜んでいます。</v>
       </c>
-      <c r="O102" t="str">
-        <v/>
-      </c>
-      <c r="P102" t="str">
-        <v/>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5542,12 +4933,6 @@
       <c r="N103" t="str">
         <v>伊東由樹がプライベートゲーム用に手作りしていたランカーキラー・スイッシャーがエクスプローズ。 独特なひねり形状のプロペラには、独自のギアホール加工が施されており、スクラッチサウンドを発生。超低重心マウントしたフラットバランサーによって、激しいロッドワークによるジャークでもボディを回転させることなく、きっちりとラフウォーターに喰らいつく卓越したスタビリティを発揮。水面を激しく割るラフバイトにおいても確実なフックセットを実現します。 スローリトリーブによるタダ巻きでは、時折、ゆらりとウォブリング。凪の水面ではデッドリーベイトを効果的に演出します。 他のスイッシャーとは明らかに違う、一目瞭然のスペックを内包するプロップベイトのスペシャルエディションです。</v>
       </c>
-      <c r="O103" t="str">
-        <v/>
-      </c>
-      <c r="P103" t="str">
-        <v/>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5592,12 +4977,6 @@
       <c r="N104" t="str">
         <v>プロップフォーム(プロペラ形態)ボディが生み出す、独自のインパクト。 ボディがスパイラル形状を持つプロペラデザイン。ボディ自体がプロペラ・・・これがアイティオー流のスイッシャーです。 SCREAM-X 3/4oz.はロッドティップを水面近くに下げてジャークすると即座にダート。強めの連続トゥイッチを入れると、左右へと激しくボディを反転させながらドッグウォーク＆テーブルターン。しかもその激しいドッグウォークの最中には、ジュオッ！っと、激しいスクリーミングサウンドを伴います。この動きが、大型ベイトの激しいハタキ行動を連想させるかもしれません。 操作のキモは、ロッドティップを水面近くに下げること。SCREAM-Xは、ルアーとアングラーの距離が近いときにロッドティップを上げてリトリーブするとプロペラが回転しないようにセッティングされています。バランスウエイトをボディ後部にインサートし、フロントを浮かせているからです。 従来のスイッシャーは、スポットでバスがバイトしなかったとき、回収中もプロペラが激しく回転して水面を騒々しく滑走するため、エリア全体に不要な警戒心を与えていました。SCREAM-Xは、狙うべきスポットだけでペラが回転し、軽妙な首振りターンと激しいインパクトを放つ独特なセッティングを施しています。</v>
       </c>
-      <c r="O104" t="str">
-        <v/>
-      </c>
-      <c r="P104" t="str">
-        <v/>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5642,12 +5021,6 @@
       <c r="N105" t="str">
         <v>BEETLE-X enchants bug-eating monster bass with its enticing action and siren call. Featuring AIR wings crafted with a material selected both for low elasticity and specific gravity, BEETLE-X HOVER CRAWL is able to perform a high-pitched crawling action that practically dances across the surface, even in rough conditions. Carefully tuned sound profile features a precise mix of steel and glass rattles, for a multilayered sound that consistently draws targets from afar. Finished with unprecedented detail, the HOVER CRAWL shines with alluring realism. ※The photograph is a prototype.</v>
       </c>
-      <c r="O105" t="str">
-        <v/>
-      </c>
-      <c r="P105" t="str">
-        <v/>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -5692,12 +5065,6 @@
       <c r="N106" t="str">
         <v>プロップフォーム(プロペラ形態)ボディが生み出す、独自のインパクト。 ボディがスパイラル形状を持つプロペラデザイン。ボディ自体がプロペラ・・・これがアイティオー流のスイッシャーです。 SCREAM-X Jr. 1/2oz.は、プロップフォーム（プロペラ形態）をベイトライクなスリムなボディ形態にデザイン。水面に食らいつくスタビリティを極限まで高め、あえて直進性能に特化してセットアップ。小型スイッシャーながら、タイトなプロペラボディが常時、水流をに瞬時に絡め取り、装着した前後のWプロップが激しく高回転。水面でスクリームサウンドを放ち、激しいフィーディング＆ボイルをイミテートします。</v>
       </c>
-      <c r="O106" t="str">
-        <v/>
-      </c>
-      <c r="P106" t="str">
-        <v/>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5742,12 +5109,6 @@
       <c r="N107" t="str">
         <v>Nano SIGLETT, the featherweight bug-pattern dynamo made for instantaneous inhalation, is the result of ITO Engineering's ultra-precision NanoCraft Technology. This unrelenting attention to minutiae gives shape to exquisite hydrodynamics that enable an extremely consistent and appealing action that often escapes conventional tiny lures. At a few hairs over 2cm, the Nano SIGLETT crawls with a high-pitch action that few bass will be able to ignore. This is finesse bug-pattern angling at its finest.</v>
       </c>
-      <c r="O107" t="str">
-        <v/>
-      </c>
-      <c r="P107" t="str">
-        <v/>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5792,12 +5153,6 @@
       <c r="N108" t="str">
         <v>TINY SIGLETT is a micro bug bait that imitates the struggling movements of cicada and similar winged insects on the water surface. Steady retrieve creates a paddling walking-motion, with each wing dipping into the water as it turns, walks, and splashes on the surface. Shake the line to imitate the fluttering death throes of a struggling insect, and fool even the most cunning of predators. Decreased buoyancy helps fish take down TINY SIGLETT for higher hook up ratios. ※The photograph is a prototype.</v>
       </c>
-      <c r="O108" t="str">
-        <v/>
-      </c>
-      <c r="P108" t="str">
-        <v/>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -5842,12 +5197,6 @@
       <c r="N109" t="str">
         <v>Siglett is a winged bug-bait modeled after a Japanese cicada. Its tungsten alloy balancer inside its chamber is sound-tuned to mimic the Higurashi cicada of Japan. Also, it looks just like one, complete with a pair of translucent wings made of semi-hard plastic which not only slide up &amp; down, but also act as large lips for jittering bug action.</v>
       </c>
-      <c r="O109" t="str">
-        <v/>
-      </c>
-      <c r="P109" t="str">
-        <v/>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -5892,12 +5241,6 @@
       <c r="N110" t="str">
         <v>Siglett is a winged bug-bait modeled after a Japanese cicada. Its tungsten alloy balancer inside its chamber is sound-tuned to mimic the Higurashi cicada of Japan. Also, it looks just like one, complete with a pair of translucent wings made of semi-hard plastic which not only slide up &amp; down, but also act as large lips for jittering bug action. Since line eye is located at its tail, Siglett casts with the least air resistance, insuring surprisingly good casting distance and accuracy as a winged bug bait. When retrieved, Siglett’s wings naturally ‘open up’ and each ‘wing lip’ starts to crawl alternately as it jitters along. Fast to slow-steady retrieve in open areas and stop &amp; go twitching action under overhangs are the most effective application. Enjoy a relaxing top-water fishing day with Siglett.</v>
       </c>
-      <c r="O110" t="str">
-        <v/>
-      </c>
-      <c r="P110" t="str">
-        <v/>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5942,12 +5285,6 @@
       <c r="N111" t="str">
         <v>As the name OVER REV indicates, the limiter-breaking high-speed rotations of the ORC are next-level. Introducing a flat side shallow crank that has succeeded in dramatically increasing roll speed!  The ORC’s super high-speed rolling is thanks to the newly developed GYRO BALANCING LBO mechanism that generates a high-speed wobbling roll like that of a roly-poly toy. This eliminates the need for the high-speed retrieves seen in previous flat sides which were needed to generate flashing. The ORC emits intense flashing and screw waves even during slow retrieves. It’s able to maintain a position directly under the surface for long periods of time, creating many opportunities to trigger bites. The ORC significantly raises the potential for contact with fish in shallow areas. If you retrieve it very slowly, it can perform as a topwater crank. In that situation, the GYRO BALANCER rhythmically strikes the body emitting a hard attack sound below the surface garnering attention from target fish. The ORC is a true shallow game revolutionary that features heightened shallow cover evasion performance and the ability to effectively draw out bites even when maintaining distance from cover. * The photograph is a prototype.</v>
       </c>
-      <c r="O111" t="str">
-        <v/>
-      </c>
-      <c r="P111" t="str">
-        <v/>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -5992,12 +5329,6 @@
       <c r="N112" t="str">
         <v>The i-JACK traces its lineage to the IT JACK, a legendary hand-carved wood plug created by Megabass founder, Yuki Ito. Building on this history, i-JACK overwhelms with a powerful, “screw drive” action, creating huge water-disturbance, a booming “knock,” and an intense flash to call predators from far and wide. An original Stingray Bill design and integrated Rudder Action Balancer System (R.A.B) deliver a twisting wake bait retrieve with a wide roll-axis, flashing the i-JACK’s exquisitely detailed sides with each turn. Further, the R.A.B. system, with its heavy metal ball and rudder-like metal plate on a free-swinging pivot pin, throws its considerable weight behind each turn to generate unprecedented rolling action and a surprisingly loud “knock” with each turn. The i-JACK’s outsized rolling screw-action and sound extend its effectiveness even into deeper waters, where its bold presence and lifelike detail will be sure to fool even the most discerning predators.</v>
       </c>
-      <c r="O112" t="str">
-        <v/>
-      </c>
-      <c r="P112" t="str">
-        <v/>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -6042,12 +5373,6 @@
       <c r="N113" t="str">
         <v>The BURNING SHAD is pushed into overdrive, maximizing the roll drive of the ORC’s compact body at all speeds. Marvelous super-fast rolling action like an engine at its limit is produced by the GYRO BALANCING LBO SYSTEM, which harnesses the essential principle of a self-righting doll to drive relentless action at all speeds. Previously, a fast retrieve was required to generate the rolling, flickering action of a lure like the ORC. However, by harnessing the GYRO system, the BURNING SHAD produces dynamic roll, displacement and flash at slower speeds where other lures may begin to falter. With rod tip low and a slow retrieve, the BURNING SHAD will crawl just beneath the surface, bulging water and inciting explosive chase bites. Speed up your retrieve and BURNING SHAD tracks true with ever-stronger flash and rolling water displacement. The GYRO system creates a hard, rhythmical “click” sound to appeal to inactive fish. Additionally, the BURNING SHAD exhibits dramatically improved avoidance ability due to its body shape and hook placement, allowing for close-cover cranking. * The photograph is a prototype.</v>
       </c>
-      <c r="O113" t="str">
-        <v/>
-      </c>
-      <c r="P113" t="str">
-        <v/>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -6092,12 +5417,6 @@
       <c r="N114" t="str">
         <v>i-LOUD showcases the same Rudder Action Balancer System (PAT.) of the i-JACK, housed in a new concept jointed wakebait/propbait designed by ITO ENGINEERING. The RAB System emits a resounding ‘knock’ as it throws its weight from side to side, giving off a strong sonic presence as it helps power the outsized action of i-LOUD’s jointed body. Rear prop adds another layer of lively sound, and leaves a bubble trace along the retrieve line. With a large profile, and even larger action and sound, i-LOUD represents an aggressive approach to activate the feeding modes of dormant monster bass, and trigger explosive bites. ※The photograph is a prototype.</v>
       </c>
-      <c r="O114" t="str">
-        <v/>
-      </c>
-      <c r="P114" t="str">
-        <v/>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -6142,12 +5461,6 @@
       <c r="N115" t="str">
         <v>PROP DARTER 80 (X-80 PD) is something like top-water version of TRICK DARTER. The prop which was invented (PAT.P) just for this bait, is truly unique not simply because it is asymmetric but because of its lively swimming sound and its ability to spit back. As for the body, the inside structure has been completely overhauled and redesigned for a new set of objectives. As a result it leans to left and right when retrieved. It looks like a snake's swimming track. PROP DARTER has a lip, which tries to dive. Yet it cannot dive. This struggle adds to PROP DARTER's unique bio-sound and the surface action you have never seen before.</v>
       </c>
-      <c r="O115" t="str">
-        <v/>
-      </c>
-      <c r="P115" t="str">
-        <v/>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -6192,12 +5505,6 @@
       <c r="N116" t="str">
         <v>From the creators of the VISION ONETEN, comes the ultimate winged bait. I-WING’s incredibly realistic body featuring super-lightweight duralumin wings is the result of hundreds of hours of hydrodynamic testing in tough fields. ･ During dead slow retrieves i-WING generates micro pitch waves, evoking a small school of fish that swarms to weakened bait. ･During high speed retrieves the body practically hovers over the water and demonstrates agile buzz-crawling despite its large size. The internal R.A.B. (Rudder Action Balancer System) activates in conjunction with the wings, generating turning actions, and allowing the jointed tail to gracefully tail walk and emit a delayed “knock” sound. It will stimulate and appeal to even far away targets. In conjunction with the wobblin’ roll action, the R.A.B. weight swings on a pivot from side to side like a pendulum. When the heavy weight hits the inside of each wall, a strong sound and shock wave is emitted, adding another layer of acoustic attraction. The uniquely layered waves emitted by the body movement, wings, jointed tail and R.A.B. pendulum balancer combine to intensely stimulate the feeding instinct of monsters. * The photograph is a prototype.</v>
       </c>
-      <c r="O116" t="str">
-        <v/>
-      </c>
-      <c r="P116" t="str">
-        <v/>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -6242,12 +5549,6 @@
       <c r="N117" t="str">
         <v>PROPDARTER106 is equipped with the nearly frictionless LBO II (PAT.) moving balancer system to achieve superior weight transfer and cast distance for a propeller-mounted lure. The LBO II’s ball-bearing shaft weight is synchronized to the roll axis of the lure’s action for enhanced output. The responsive and seamless roll action creates frequent enticing flutters, mimicking the rise and wake of baitfish. Depending on the retrieval speed, a variety of "3-way actions" are produced, showcasing an extraordinary feeding magic.</v>
       </c>
-      <c r="O117" t="str">
-        <v/>
-      </c>
-      <c r="P117" t="str">
-        <v/>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -6292,12 +5593,6 @@
       <c r="N118" t="str">
         <v>Following in the footsteps of the i-Wing, ITO Engineering, with Yuki Ito at the helm, has finally released the top-secret i-WING FRY, designed under a veil of secrecy to catch even the cleverest fish on the first bite. In shallow areas normally attacked with crankbaits or spinnerbaits, simply reeling in the i-WING FRY will bring your target to the surface, with a stunning power that explodes through the water. Once it was deemed impossible for a winged lure to have a moving balancer, because of how the crawling action works, but ITO has successfully developed a proprietary format, available for the first time in this lure. By analyzing the “power points” and “action points” generated by the Linear Bearing Oscillator (LBO) of the moving balancer system, as it responds to a variety of likely actions, Yuki Ito has designed a brand-new hydrodynamic body especially for the i-WING FRY, so as to synchronize the movements of the central axis of the LBO and the rolling axis of the lure. The innovative design, which increases buoyancy in a manner reminiscent of a hovercraft, enters the lineage of unique simulated fish like the POP-X, brought to you exclusively by Megabass. In concert with the neodymium magnet, the shaft balancer of the LBO moves reflexively as the lure changes position, creating (1) “instant action,” (2) “optimal form after splashdown, to rapidly correct the LBO,” and (3) “instant magnetic anchoring.” In other words, the lure starts working the second it hits water, doing things no winged lure has done before, and exhibiting a stunning directability so that your target bites on the spot. The i-WING FRY responds instantly, even to the slightest control of the line slack. Always in motion, it draws the target in. Defying preconceptions of winged lures, and dismissing headwinds as irrelevant, the long-distance castability maximizes and amplifies productive areas like no lure of its class. On top of that, the tuned hydrodynamic body is equally in control on extremely slow retrieves and on faster retrieves liable to come tearing through the surface, demonstrating incredible stability. This is a lure that keeps on swimming, adapting to whitecaps and all manner of rough surface conditions. Simply reeling in the lure will catch plenty of fish, but shaking introduces wobble action and subtle undulation. Little twitches will produce the side-to side rotation or splash action seen with pencil bait.  If you're looking for a winged lure that has the finesse and impact on bite chance of worm lures, look no further than the i-WING FRY. * The photograph is a prototype.</v>
       </c>
-      <c r="O118" t="str">
-        <v/>
-      </c>
-      <c r="P118" t="str">
-        <v/>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -6342,12 +5637,6 @@
       <c r="N119" t="str">
         <v>Introducing the TRIPLE FRY, a new addition to the popular i-WING series that has taken bass fields across the world by storm. The tougher the conditions, the more TRIPLE FRY will showcase its mystical fish-catching performance. The super thin pair of baitfish wings possess a unique flexibility, making lifelike delicate and seductive waves with dead slow retrieves. The rolling dance of the main body combines with the jointed float tail and wings to create the illusion of panicked baitfish struggling at the surface in an enticing bait ball. The slower you reel it in, this unprecedented panic bait will trigger an increasingly powerful chain reaction of explosions on the water’s surface.</v>
       </c>
-      <c r="O119" t="str">
-        <v/>
-      </c>
-      <c r="P119" t="str">
-        <v/>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -6392,12 +5681,6 @@
       <c r="N120" t="str">
         <v>この動きに抗えるヌシは、いるでしょうか？　ガバリンは、従来フロッグの単調な誘いを完全に見切ったモンスターを相手に徹底テストして開発。独自のボディデザインにより、フローティングカバーのほんのわずか隙間、数十センチのオープンポケットでも、ガバリンはラインスラック・ワークやロッドワークに即応し、ピンポイントの鋭角なクイックターンやハイピッチ・ドッグウォークを披露。ガバリンのワイドな口角による絶妙な水噛みが水面を騒めかせ、重々しいサウンドとバブルを伴うダイブ＆スプラッシュを発生。 ３シーズンに及んだテストでは、叩き抜かれたフローティングカバーのポンド群から、ヌシレベルのビッグフィッシュたちをバイトさせる度、アップデートを重ねてきました。 多彩なロッドワークで挑むテクニカルなトップウォータープラッガーに向けて贈る、新感覚のアクティブアクションフロッグ。ガバリンならば、ヌシは呑み込みます。</v>
       </c>
-      <c r="O120" t="str">
-        <v/>
-      </c>
-      <c r="P120" t="str">
-        <v/>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -6442,12 +5725,6 @@
       <c r="N121" t="str">
         <v>The BIG GABOT is a larger, heavy-duty model of the PONY GABOT developed based on the strong requests of the US pro staff. While preserving the responsive CATAMARAN MOUTH of the PONY GABOT which allows for splash-walking action, the BIG GABOT features upgrades to various parts. In order to push the center of gravity farther back compared to the original GABOT, the skirt has been positioned away from the body. A new hook groove has been added to the connection point of the hook and body to limit unwanted hook slide. With the increase in size, the internal structure has also been redesigned and reinforced for durability. The BIG GABOT’s hook is custom-built for the new frog, increasing hook-penetration and reducing lost fish throughout the fight. With increased total weight, easy casting with thick PE line is possible. The larger body also allows for more powerful water displacement in heavy matted cover, dramatically increasing the appeal of the BIG GABOT in the eyes of big bass. The BIG GABOT has a striking presence that surpasses the original, stimulating the fighting instinct of big bass. * The photograph is a prototype.</v>
       </c>
-      <c r="O121" t="str">
-        <v/>
-      </c>
-      <c r="P121" t="str">
-        <v/>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -6492,12 +5769,6 @@
       <c r="N122" t="str">
         <v>“KING OF JERKBAIT”として世界で活躍するビジョン・ワンテンシリーズ。他のジャークベイトではオーバーダイブしがちだった水面直下のシャローレンジを完全攻略する、競技専用スペシャルモデルが、ONETEN-SRとONETEN-SSRです。 ［最大潜行深度1.0ｍ]を徹底的にキープする[SR]は、超広域のシャローエリアから、従来ジャークベイトの展開レンジに反応しなかったバスのストライクチャンスを大幅に拡大。 さらなる表層レンジを展開する、［最大先行深度0.7m以浅］の徹底キープを実現したONETEN-SSRは、これまでソフトジャークベイトやトップウォーターベイトに頼らざるを得なかった、ボトムにウィードやストラクチャーが存在する広大なスーパーシャローエリアをジャークベイティングによるホットスポットに変えてしまいます。 SRとSSRは、リールハンドルのノブに指をかけた瞬間から、着水と同時にアクションが即立ち上がり、着水地点のバイトも即時誘発。オリジナル・ワンテンよりも左右へのダート距離を拡大化し、ロッドアクションのワンストロークで移動可能な水中のダート距離は、ワンテン随一のものとなっています。 ロッドを立てて操作する、ラインスラックの瞬時の緩急によるショートストローク・トウィッチでは、水面へと踊りながら上昇する「ライズアップ軌道」をイレギュラーに披露。腹部をひるがえす「ロール・フラッタリング」、「フラッタリング＆ダート」など、多彩なアクロバティック・アクションを頻発させます。 SR、SSR共に、特殊フッ素コーティングにより貫通力を極限まで高め、いかなる襲撃角度からのショートバイトやラフアタックでも即掛けする、メガバス独自の最新デザインによるNEWアウトバーブフックを搭載。ハイスコアゲームを追求するトーナメントプロフェッショナルに向けて製作する、純競技仕様のスペシャルファンクションモデルです。</v>
       </c>
-      <c r="O122" t="str">
-        <v/>
-      </c>
-      <c r="P122" t="str">
-        <v/>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -6542,12 +5813,6 @@
       <c r="N123" t="str">
         <v>この動きに抗えるヌシは、いるでしょうか？　ガバリンは、従来フロッグの単調な誘いを完全に見切ったモンスターを相手に徹底テストして開発。独自のボディデザインにより、フローティングカバーのほんのわずか隙間、数十センチのオープンポケットでも、ガバリンはラインスラック・ワークやロッドワークに即応し、ピンポイントの鋭角なクイックターンやハイピッチ・ドッグウォークを披露。ガバリンのワイドな口角による絶妙な水噛みが水面を騒めかせ、重々しいサウンドとバブルを伴うダイブ＆スプラッシュを発生。 ３シーズンに及んだテストでは、叩き抜かれたフローティングカバーのポンド群から、ヌシレベルのビッグフィッシュたちをバイトさせる度、アップデートを重ねてきました。 多彩なロッドワークで挑むテクニカルなトップウォータープラッガーに向けて贈る、新感覚のアクティブアクションフロッグ。ガバリンならば、ヌシは呑み込みます。</v>
       </c>
-      <c r="O123" t="str">
-        <v/>
-      </c>
-      <c r="P123" t="str">
-        <v/>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -6592,12 +5857,6 @@
       <c r="N124" t="str">
         <v>The BATRA-X is the second joint project between Monster Kiss, led by Takuya Kozuka, and Megabass. The BATRA-X features innovative design elements and customizable functions that set it apart from past hollow frogs. The small yet high volume bullet-style body realizes nimble table turn actions and long distance castability. The Megabass original soft cup can be attached to the front of the body for rapid fire splash-crawling action and noisy sounds with a straight retrieve, something not possible with past frogs. The BATRA-X features a rumble tail and tail hook at the end of the penetration-type wire swivel that attract fish with sounds and vibration. This world’s first transformation hollow-body surface plug allows you to change out components based on situation and preference. * The photograph is a prototype</v>
       </c>
-      <c r="O124" t="str">
-        <v/>
-      </c>
-      <c r="P124" t="str">
-        <v/>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -6642,12 +5901,6 @@
       <c r="N125" t="str">
         <v>１９９０年代、USAトッププロたちからの熱い要望を受け、伊東由樹が米国トーナメントフィールドに向けて製作した「アイティオー・シャイナー」こそが、実は、名作ワンテンの原型と言われています。その、極めてナチュラルな「餌ライクな動き」にエッジの立った「強波動」を融合させた、特異なハイアピール・ジャークベイトは、様々なレンジで広域を回遊するあらゆるバスを圧倒的に誘引。「活性を上げたいファーストコンタクトは、ITO-SHINNER」、「喰わせにゆくなら、ONETEN」。というのが、メガバスUSAチームのセオリーになっているほどです。 ITO-SHINNERのレスポンシブなハイピッチ・アクションは、激しい明滅効果と激しい振動で刺激をもたらし、圧倒的なフィーディングをメイク。広域エリアからグッドコンディションを手際よく探り当てるスピーディーなゲームマネジメントを展開します。 ファーストブレイクを回遊する個体を優位に直撃するITO-SHINNERの潜行深度は、1.8～2m。ITO-SHINNER[+1]は、2.6 ～2.8mレンジへのアジャスタビリティを高めています。稀代のイレギュラーダートと強波動でリアクションバイトを多発させる、ジャークマスター御用達の普遍的ミノーです。</v>
       </c>
-      <c r="O125" t="str">
-        <v/>
-      </c>
-      <c r="P125" t="str">
-        <v/>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -6692,12 +5945,6 @@
       <c r="N126" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
-      <c r="O126" t="str">
-        <v/>
-      </c>
-      <c r="P126" t="str">
-        <v/>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -6742,12 +5989,6 @@
       <c r="N127" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
-      <c r="O127" t="str">
-        <v/>
-      </c>
-      <c r="P127" t="str">
-        <v/>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -6792,12 +6033,6 @@
       <c r="N128" t="str">
         <v>The SHADING-X R is fueled by a patented balancer system that enables dizzyingly high-pitch action and improved cast performance, elevating the finesse shad to exquisite new heights. Reengineered to perform in Japan’s toughest conditions, the SHADING-X R series is built to deliver bites when bass are keyed on precise, high-pitch action. The main spherical weight of the TRIANGLE COUNTER BALANCING SYSTEM(PAT.) operates as a traditional moving balancer, increasing cast distance on bait finesse and spinning setups alike. The upper balancer truly comes alive when twitches cause it to shift along its lateral axis, adding unpredictable dynamism to the SHADING-X R’s action. With one fixed weight and two moving balancers, the lure’s center of gravity is dynamically triangulated in every configuration from cast to retrieve, powering the SHADING-X’s compelling performance. The thin, tapered body generates a high-pitched vibration that practically bursts at the seams, supercharging the kind of tight action that is often required in finesse situations. Upon retrieve, the balancers roll into the forward position for an optimal head-down posture, enabling a hair-trigger responsiveness that will even bring the SHADING-X R to life with ultra-slow pulls or extra-sensitive angler input. With a fast retrieve, the high-pitch vibration compels targets into decisive reaction bites. The engineering of the SHADING-X R series brings disparate parts together in perfect harmony, leveraging dynamic weight triangulation to deliver a new high-pitch predator for the toughest angling conditions.</v>
       </c>
-      <c r="O128" t="str">
-        <v/>
-      </c>
-      <c r="P128" t="str">
-        <v/>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -6842,12 +6077,6 @@
       <c r="N129" t="str">
         <v>LATES is a real stick roller bait which furiously rolls directly under water, releasing a natural impact targeting the lower range. The flickering created by the furious roll is exactly like a school of bait fishes migrating. At situations where the water surface is disturbed by the wind, it will further release the flickering impact appealing to the targets at the lower range. It is an extreme surface minnow “floating up and capturing” the migrating monsters. The use is simple. All you need to do is to retrieve at the speed between slow and medium speed. Furthermore “rise up &amp; fall” created by decreasing the retrieve speed at times, and the “hovering” which keeps one certain range while rolling will trigger reaction bites. Slow retrieve while using high gear installed reel will help make these operations with ease. Furthermore at top water games, slapping action made by twitching is effective. The instant slide action while fluttering will imitate a real panic bait. Roller bait-LATES will awaken the fish eaters aware of the upper layer. Please check out the power of this special minnow deeply pursuing the surface minnow game.</v>
       </c>
-      <c r="O129" t="str">
-        <v/>
-      </c>
-      <c r="P129" t="str">
-        <v/>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -6892,12 +6121,6 @@
       <c r="N130" t="str">
         <v>The high impact jerkbait KANATA AYU was designed to target fish that are keyed in on larger bait. With a streamlined, slender body, KANATA keeps resistance to a minimum. This allows for a fast, action-packed retrieve that will not put undue stress on angler’s wrists and forearms, even with a Medium Heavy setup. Sharp rod work fuels energetic darting action. Straight retrieve shows off a high-pitch rolling action with flashing visual appeal. Aerodynamic form and custom-fitted Megabass original Tungsten Triple Oscillating moving balancer system(PAT.) powers effortlessly long casts, allowing KANATA to target those clever monster fish from long range. KANATA AYU brings a new size and sensation to the jerkbait game. ※The photograph is a prototype.</v>
       </c>
-      <c r="O130" t="str">
-        <v/>
-      </c>
-      <c r="P130" t="str">
-        <v/>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -6942,12 +6165,6 @@
       <c r="N131" t="str">
         <v>The high performance ITO-SHINER was developed for top anglers like Aaron Martens and Edwin Evers for top-level US tournaments. To commemorate the ITO-SHINER’s release in America, it will also undergo a limited release in Japan. The ultimate life-like movements and unprecedented stimulating waves generated by this highly appealing jerk bait have the overwhelming power to round up bass scattered across a wide area. Using its robust body height compared to that of a slim minnow, it shows dramatically increased flashing performance, in addition to a fluttering tail-motion that is an extremely alluring target. The settings of the ITO-SHINER help to realize high-speed fishing, and will excel as a search bait in high-pressure tournament situations. The swimming depth is set to 1.8~2.0 meters (~6ft.), perfectly targeting the sweet spot for bass. With its wide, side to side darting it triggers reaction bites with amazing consistency.</v>
       </c>
-      <c r="O131" t="str">
-        <v/>
-      </c>
-      <c r="P131" t="str">
-        <v/>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -6992,12 +6209,6 @@
       <c r="N132" t="str">
         <v>The ITO SHINER, which earned its reputation as a foundational jerkbait in the storied Megabass arsenal, is now available as a Super Shallow Runner (SSR) to attack the 0-0.5m range. ITO SHINER SSR is a super shallow minnow that generates a hard-rolling and flashing action to call to predators cruising the jungle of vegetation just beneath the surface. The diving depth of the SSR is 1-2ft depending upon line type and diameter, making it an extremely effective competition search bait in and around weed areas. The unique wide-bend bill helps generate larger and more dynamic water displacement, challenging the subtler action so often associated with shallow offerings. Primarily designed for a straight retrieve, the SSR also is capable of darting action with intermittent jerks, leaping forward and laterally with pronounced roll and flash. Finely tuned hydrodynamics and internal balancer enable the SSR to stick to a tight, shallow range, triggering strikes from the shadows. The triple tungsten moving balancer system delivers supercharged casts, even against strong winds gusting across the flats. The ITO SHINER SSR is a competition-spec offering designed to dominate the shallow range with overwhelming flash and appeal.</v>
       </c>
-      <c r="O132" t="str">
-        <v/>
-      </c>
-      <c r="P132" t="str">
-        <v/>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -7042,12 +6253,6 @@
       <c r="N133" t="str">
         <v>KANATA+1 (Plus One) is a roll diving model with a maximum diving depth of 3.2m, 1m deeper than the original KANATA’s diving depth. Like the original, despite its big size (160mm) and 1.1/8oz weight, the +1 has surprisingly light retrieve resistance, enabling high-tempo searches with F5 (Medium Heavy) class rods. The KANATA’s high pitch roll action produces an extremely natural and tight action that is not found in other large body jerkbaits, as well as a flickering effect that spreads over a wide expanse. The ITO Tungsten Triple Oscillating System (PAT.) built into the lure’s slim, flat-sided form allows for impressive cast distance, even in headwinds. The high-impact minnow KANATA+1 has an overwhelming presence combined with a natural swimming action, a contrast that stimulates the predatory instinct of target fish at greater depths and distances.</v>
       </c>
-      <c r="O133" t="str">
-        <v/>
-      </c>
-      <c r="P133" t="str">
-        <v/>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -7092,12 +6297,6 @@
       <c r="N134" t="str">
         <v>The long-awaited second installment of the IxI series has arrived: I×I FURIOUS. Imae and Ito once again inspired each other to new heights, creating a high-speed subsurface crank that replicates the hair-trigger bite reaction of forage fleeing at breakneck speeds. To deliver truly highspeed performance in the challenging shallow subsurface range, Yuki Ito developed a patented water-through mechanism that directs water flow through the lure’s body to stabilize depth range and action at the upper limit of retrieve speeds. FURIOUS's patented design channels water through a head intake into an inner chamber that discharges flow via two downward ducts hidden in the lure’s gills. As retrieve speeds increase, the rate of water flow and pressure both increase in tandem, adding dynamic stability to dominate a new super-shallow range. With high-speed retrieves, this ducted water system keeps FURIOUS locked in a specific depth range to challenge those predators who have long ruled the shallows. FURIOUS is equipped with a Micro LBO (PAT.) moving-balancer system, powering outsized cast distance and displaying the superb balance to deliver stunningly high-pitched action and strobing flash. The fact that a lure of such diminutive size can achieve such long-distance castability, stability at speed and breathtaking action is truly a FURIOUS achievement. IxI will bring the shallow high-speed cranking game to another dimension. ■MODEL 1.5 ・Versatile shallow runner with a maximum diving depth of 1.5m. ・High-pitch flash and rolling-drive action with otherworldly stability at high speeds. ・ Ultra-tight action doesn’t miss a beat, even with bottom contact. Swim through tight riprap with dexterity to take the fight to the shallow range.</v>
       </c>
-      <c r="O134" t="str">
-        <v/>
-      </c>
-      <c r="P134" t="str">
-        <v/>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -7142,12 +6341,6 @@
       <c r="N135" t="str">
         <v>The long-awaited second installment of the IxI series has arrived: I×I FURIOUS. Imae and Ito once again inspired each other to new heights, creating a high-speed subsurface crank that replicates the hair-trigger bite reaction of forage fleeing at breakneck speeds. To deliver truly highspeed performance in the challenging shallow subsurface range, Yuki Ito developed a patented water-through mechanism that directs water flow through the lure’s body to stabilize depth range and action at the upper limit of retrieve speeds. FURIOUS's patented design channels water through a head intake into an inner chamber that discharges flow via two downward ducts hidden in the lure’s gills. As retrieve speeds increase, the rate of water flow and pressure both increase in tandem, adding dynamic stability to dominate a new super-shallow range. With high-speed retrieves, this ducted water system keeps FURIOUS locked in a specific depth range to challenge those predators who have long ruled the shallows. FURIOUS is equipped with a Micro LBO (PAT.) moving-balancer system, powering outsized cast distance and displaying the superb balance to deliver stunningly high-pitched action and strobing flash. The fact that a lure of such diminutive size can achieve such long-distance castability, stability at speed and breathtaking action is truly a FURIOUS achievement. IxI will bring the shallow high-speed cranking game to another dimension. ■MODEL 0.5 ・Super shallow runner with a diving depth of up to 0.5m. ・High-pitch flash and tight roll action that generates outsized presence and overwhelming responsiveness. ・ Targets the ultra-shallow range with a wide carpet-bombing approach and powerful high-speed action.</v>
       </c>
-      <c r="O135" t="str">
-        <v/>
-      </c>
-      <c r="P135" t="str">
-        <v/>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -7192,12 +6385,6 @@
       <c r="N136" t="str">
         <v>This next-generation shad made bass pro Katsutaka Imae exclaim “we’ve got something amazing here!” The TYPE-3 features an ability to trace a depth of 3.0m, but it can also perform exceptionally up to the 1.2m range. The design minimizes snags in the shallows and makes repeated hard contact with structures possible. Yuki Ito’s shad engineering has realized Katsutaka Imae’s “forward falling theory” at an extremely high level with this ultimate versatile shad featuring dazzling ultra-high pitch roll action. * The photograph is a prototype.</v>
       </c>
-      <c r="O136" t="str">
-        <v/>
-      </c>
-      <c r="P136" t="str">
-        <v/>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -7242,12 +6429,6 @@
       <c r="N137" t="str">
         <v>The I x I SHAD secret weapon A high pitch, high stability shad that allows for fast searches of the 1m shallow range, reliably turning bites into results. The high pitch screw-roll action allows for clear bottom contact thanks to the forward falling posture. This drastically increases the bite chances when contacting structure and the bottom. You can see the performance of this next-generation shad with its ability to draw out tough, clever fish with its speedy flashing. * The photograph is a prototype.</v>
       </c>
-      <c r="O137" t="str">
-        <v/>
-      </c>
-      <c r="P137" t="str">
-        <v/>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -7292,12 +6473,6 @@
       <c r="N138" t="str">
         <v>The goal of Katsutaka Imae and Yuki Ito was to land targets from the 4m+ range with a mere 57mm long shad body. The mounting position of the instant shifting balancer system Micro LBO (PAT.) allows for a super forward leaning posture impossible with normal ball weights. Ito moved the balancer head towards the intersection of the lip and body using a shaft with super small diameter bearings that made the extreme forward mounting design possible. With field tests using 6lb fluorocarbon line this big-lipped small shad demonstrated extremely long flight distances and succeeded in generating an astonishing diving vector. The outstanding fusion of aerodynamics and hydrodynamics have given the IxI SHAD the extreme performance needed to strike at deep targets. It is the ultimate solution for compactness, realism and performance.</v>
       </c>
-      <c r="O138" t="str">
-        <v/>
-      </c>
-      <c r="P138" t="str">
-        <v/>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -7342,12 +6517,6 @@
       <c r="N139" t="str">
         <v>The LIVE-X, one of Megabass’ original injection-molded lures of the early 90’s, is now reborn with the latest technology and supercharged performance. It's not a shad. It's not a minnow. And of course, it's not a simple crank. The state-of-the-art hydrodynamics with built-in LBO II(PAT.) produces ultra-fast flickering and live action from dead slow to ultra-high speed retrieves without fail. It is a bait with an overwhelmingly lifelike performance, turning neutral fish into reactive feeders when it matters most. This is the impact of a "live bait". The aerodynamic form, which Yuki Ito derived from countless hours of aerodynamic testing, improves casting distance by more than 30% in headwinds when compared to lures of equal volume. LIVE-X has succeeded in increasing the performance of carpet bombing a wider and more diverse range than ever before. In shallow water 2m deep or less, where conventional diving cranks have a hard time, LIVE-X is extremely dexterous, avoiding getting stuck and continuing to lure tough fish. The ability to feed cruising fish at depths of 3.5m or more is unique to the LIVE-X, which has been further refined to outperform the original. Switch on the feeding instinct of neutral fish that have not responded even to the ONETEN jerkbait. The second phase of the LIVING LEGEND project was started to catch discerning fish that are turned off from the overly aggressive action of many conventional cranks. This time, those of you who missed out on the explosive fishing experience with the original LIVE-X 30 years ago will experience it anew. Discover the true meaning of "LIVE-X". The legend continues.</v>
       </c>
-      <c r="O139" t="str">
-        <v/>
-      </c>
-      <c r="P139" t="str">
-        <v/>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -7392,12 +6561,6 @@
       <c r="N140" t="str">
         <v>The X-NANAHAN is a fusion of the ideals of Shinji Sato, one of Japan's foremost lure anglers, and the engineering of Yuki Ito, creator of dominant jerkbaits like the VISION ONETEN. In order to pursue superior castability in a small jerkbait minnow profile, the X-NANAHAN’s body is carved from a high-volume block, which results in a visually tight silhouette with greater precision. Air resistance has been thoroughly reduced to achieve overwhelming long-distance castability that surpasses the standard distance of 70mm-class minnows. The unique shape of the minnow, guided by the latest in hydrodynamics, provides excellent swimming response and intuitive handling. X-NANAHAN’s subtle action and flash reproduce the minute waves and flickering appeal of baitfish in an extremely realistic manner. Further, when twitched, X-NANAHAN bursts to life with a dynamic jerking and darting action that sets it apart from the school. The X-NANAHAN is a next-generation finesse minnow that pursues the "ultimate" in responsiveness. * The photograph is a prototype.</v>
       </c>
-      <c r="O140" t="str">
-        <v/>
-      </c>
-      <c r="P140" t="str">
-        <v/>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -7442,12 +6605,6 @@
       <c r="N141" t="str">
         <v>The X-NANAHAN is a fusion of the ideals of Shinji Sato, one of Japan's foremost lure anglers, and the engineering of Yuki Ito, creator of dominant jerkbaits like the VISION ONETEN. In order to pursue superior castability in a small jerkbait minnow profile, the X-NANAHAN’s body is carved from a high-volume block, which results in a visually tight silhouette with greater precision. Air resistance has been thoroughly reduced to achieve overwhelming long-distance castability that surpasses the standard distance of 70mm-class minnows. The unique shape of the minnow, guided by the latest in hydrodynamics, provides excellent swimming response and intuitive handling. X-NANAHAN’s subtle action and flash reproduce the minute waves and flickering appeal of baitfish in an extremely realistic manner. Further, when twitched, X-NANAHAN bursts to life with a dynamic jerking and darting action that sets it apart from the school. The X-NANAHAN is a next-generation finesse minnow that pursues the "ultimate" in responsiveness. * The photograph is a prototype.</v>
       </c>
-      <c r="O141" t="str">
-        <v/>
-      </c>
-      <c r="P141" t="str">
-        <v/>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -7492,12 +6649,6 @@
       <c r="N142" t="str">
         <v>The super minnow X-NANAHAN, which has generated unquestionable results from waters throughout Japan since its release, is now available in a +2 model for even deeper ranges. The NANAHAN+2’s 75mm compact body can now easily reach a range of 3m, bringing its irresistible appeal right under the noses of big bass tucked away in the depths. The NANAHAN’s rare combination of high-pitch roll action and rod-twitch trick darting induce difficult bites in the most important moments. The thoroughly tested aerobill enables a rocket-like cast with a stable flying posture, maximizing diving depth and productive water. The NANAHAN series now covers all key depth ranges, bringing an invaluable set of tools to the demanding angler.</v>
       </c>
-      <c r="O142" t="str">
-        <v/>
-      </c>
-      <c r="P142" t="str">
-        <v/>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -7542,12 +6693,6 @@
       <c r="N143" t="str">
         <v>The VISION95 "Q-GO" is a 3.74in. long minnow meant for shallow water. The swimming action of this bait is controlled by a completely new balancer system called the SHAFT BALANCER SYSTEM(PAT.) Instead of a moving, round balancer, the one in the Q-GO is shaped and fixed at the lowest point along the body. The result is an astounding new type of rolling action. Since the shaft weight acts as kind of reverse pendulum (think of it upside-down), the whole body swings with the shaft as a pivot. Unlike a moving balancer, the shaft balancer does not require guiding structures, so it frees up the space inside the bait. This allows the Q-GO to have very high buoyancy along with highly responsive movement. That is why the Q-GO is at home with any retrieval speed. Slow or fast, the Q-GO will get you the responses you have been waiting for.</v>
       </c>
-      <c r="O143" t="str">
-        <v/>
-      </c>
-      <c r="P143" t="str">
-        <v/>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -7592,12 +6737,6 @@
       <c r="N144" t="str">
         <v>"The VISION ONETEN Jr. packs the tournament-winning characteristics of the immensely successful VISION ONETEN jerk bait into a 98mm (3.85in) frame, generating more action per inch than its larger sibling. The VISION ONETEN Jr. has been carefully benchmarked against the VISION ONETEN, and has been redesigned from the ground up to improve upon the dynamic actions of the original, and expand the range of the jerk bait line. The ONETEN’s unique action has been distilled into the diminutive frame of the ONETEN Jr. Not only does it exhibit wide, erratic darts, but also demonstrates high pitch rolling and flashing during slow retrieves and wobble and roll agitation during fast retrieves. Finally, the dual-tungsten weights of the Megabass Multi way Moving Balancer System (PAT.) allow for incredible flight distance despite the lure’s small size.</v>
       </c>
-      <c r="O144" t="str">
-        <v/>
-      </c>
-      <c r="P144" t="str">
-        <v/>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -7642,12 +6781,6 @@
       <c r="N145" t="str">
         <v>Based on the ONETEN+1, a diving jerkbait responsible for overwhelming results in top U.S. tournaments, the VISION ONETEN+1 Jr. is a compact and agile performer engineered to target the toughest midrange waters—especially when matching smaller bait really counts. Aligning the uniquely contoured diving bill along the central axis of the body channels water along sculpted body lines, powering outsize, erratic darting action. Proven ONETEN design fools wary predators and generates striking flash, reaping massive dividends in midrange waters. Aerodynamic diving bill drastically reduces unnecessary air resistance, while the energy produced by the linear dual-tungsten weights of the Moving Balancer System allow for incredible flight distance even in rough conditions. * The photograph is a prototype</v>
       </c>
-      <c r="O145" t="str">
-        <v/>
-      </c>
-      <c r="P145" t="str">
-        <v/>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -7692,12 +6825,6 @@
       <c r="N146" t="str">
         <v>The VISION ONETEN+2 Jr. brings bite-sized jerkbait appeal to new depths, matching the tournament-winning 9-10ft range of the full-sized ONETEN+1. With a sculpted bill set along the lure’s central axis, the +2 Jr. achieves the kind of dynamic, razor-sharp darting action that earns the VISION ONETEN series a place in every serious jerkbait angler’s arsenal. At target depth, the +2 Jr. displays remarkably wide and responsive darting action. Its contoured body throwing off intense flash before coming to rest with a delicate shimmying appeal, provoking compulsive bites from deep cruisers. With an aerodynamic form and dual-tungsten weight transfer system, the ONETEN+2 Jr. outcasts expectations, bringing hard-fought trophies within reach.</v>
       </c>
-      <c r="O146" t="str">
-        <v/>
-      </c>
-      <c r="P146" t="str">
-        <v/>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -7742,12 +6869,6 @@
       <c r="N147" t="str">
         <v>The VISION ONETEN series, renowned as the “KING OF JERKBAITS” worldwide, is now available in a shallow-running model. With a maximum diving depth of 1m (3.2ft) on 14lb fluorocarbon, the ONETEN SR moves into action with the first angler input, effectively triggering strikes before the cast rings settle. Compared to the original ONETEN, the SR maintains a shallower running depth while expanding the lateral range of its side-to-side darting action, generating more action per jerk than even the original ONETEN. By holding the rod upright, varying line slack and applying short-stroke twitches between 11 and 1 o’clock, the ONETEN SR produces acrobatic actions such as a “rise-up darting” toward the surface, high flash “roll fluttering,” and endless combinations of “fluttering and darting.” The ONETEN SR is equipped with custom Megabass out-barb hooks. Premium 1X wire enhanced with a fluorine coating for superior penetration, these hooks generate instant hookups in the toughest situations. Designed for competitive angling, this high-performance lure is built to maximize your angling potential.</v>
       </c>
-      <c r="O147" t="str">
-        <v/>
-      </c>
-      <c r="P147" t="str">
-        <v/>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -7792,12 +6913,6 @@
       <c r="N148" t="str">
         <v>Introduced in the fall of 2000, the VISION ONETEN immediately captured the imagination of American anglers, setting a new standard for jerk baits. Designed by Yuki Ito for anglers in the United States, the ONETEN has emerged as the "go-to" jerk bait amongst touring pros, continuing to produce key fish and big checks from the Club level to the Bassmaster Classic. The profile, one-of-a-kind darting action, tungsten Multi-Way Moving Balancer System(PAT.) and hand-painted color patterns all contribute to the incredible fish-catching ability of the VISION ONETEN. The internal balancer system not only fuels the ONETEN's unparalleled action and huge flashes, but also allows it to cast like a bullet, far outpacing conventional jerk baits. This deadly package is finished off with three Megabass original sticky-sharp KATSUAGE OUT-BARB treble hooks, designed to increase hook-setting percentages when power-bait fishing. Crafted to generate results with a steady retrieve, traditional "jerk, jerk, pause," or trolling, the ONETEN responds to rod actions with unparalleled, life-like action. The one and only: VISION ONETEN.</v>
       </c>
-      <c r="O148" t="str">
-        <v/>
-      </c>
-      <c r="P148" t="str">
-        <v/>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -7842,12 +6957,6 @@
       <c r="N149" t="str">
         <v>The VISION ONETEN +1 is a mid-range jerk bait designed to increase the depth of the original ONETEN by up to 3ft. The ONETEN+1's medium bill is crafted to eliminate the traditional issues of high water-resistance, fatigue, and dead-end darting action often associated with long-bill minnows, all while preserving the legendary action of the original ONETEN. By positioning the line-eye close to the body, water resistance is reduced in order to make it easier to work the ONETEN+1 compared to conventional long bills. In addition, this angler-friendly design also channels more water towards the lure's forehead and along the carefully sculpted body, allowing for irresistible darting action with the slightest input. The ONETEN+1 is finished off with a dual-tungsten Multi-Way Moving Balancer System(PAT.) designed to produce superior long-distance castability even in tough conditions. The VISION ONETEN+1 : The legend just got deeper.</v>
       </c>
-      <c r="O149" t="str">
-        <v/>
-      </c>
-      <c r="P149" t="str">
-        <v/>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -7892,12 +7001,6 @@
       <c r="N150" t="str">
         <v>The ONETEN MAGNUM builds upon the overwhelming success of the VISION ONETEN in major tournaments around the world, featuring a redesigned fixed-balancer system, and a larger profile. Unlike the decentralized balancer-systems of many large jerk baits, the ONETEN MAGNUM has a specially tuned internal fixed weight balancer plate that allows for responsive action and swimming stability. The ONETEN MAGNUM dives to a depth of 2 feet (60cm), and with a slow retrieve, gives off an alluring wobble identical to a schooling baitfish. With a fast retrieve, the MAGNUM performs high pitch rolling actions; when stopped, the MAGNUM gives off a subtle wobble and floats up head first, just like a baitfish trying to escape a predator. With a larger profile, the ONETEN MAGNUM offers up a larger meal that will be sure to trigger bites from even the most cautious monsters.</v>
       </c>
-      <c r="O150" t="str">
-        <v/>
-      </c>
-      <c r="P150" t="str">
-        <v/>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -7942,12 +7045,6 @@
       <c r="N151" t="str">
         <v>The ONETEN LBO, which features the second-generation LBO II (PAT.) moving balancer system, has dramatically increased castability against headwinds, making stable, long approaches possible even under blustery conditions. Additionally, the balancer system—powered by 88 ball-bearings—significantly reduces friction during weight transfer, thereby transferring greater energy to the lure’s tail for greater casting distance. By extending the 110mm body of the original to a long-tailed 115mm, the center of gravity is able to shift even farther to the rear when casting, improving accuracy. The LBO II (PAT.) brings with it a lowered center of gravity along with a synchronized point of leverage and point of action that make instant, responsive actions possible from the moment you put your hand on the reel handle. The bearing weight, which is secured in optimal “ready” position by a neodymium magnetic field, generates sharp and highly regulated jerking actions, and the entirely new dimension of sharp, high pitch rolling action brings a heightened prominence to the ONETEN’s flashing. This special ONETEN, filled with ITO Engineering’s cutting-edge technologies, redefines the preexisting concept of jerkbaits. * The photograph is a prototype.</v>
       </c>
-      <c r="O151" t="str">
-        <v/>
-      </c>
-      <c r="P151" t="str">
-        <v/>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -7992,12 +7089,6 @@
       <c r="N152" t="str">
         <v>The ONETEN MAX LBO is a large, highly responsive jerkbait powered by the revolutionary LBOII moving balancer system. Thanks to the combination of a highly refined hydrodynamic body and the LBO’s virtually frictionless weight-transfer system, the ONETEN MAX LBO is able to eliminate the sluggishness seen in large jerkbaits of the past. The astonishingly responsive action, a credit to the work of ITO engineering, truly make it worthy of the position atop the vaunted ONETEN jerkbait series. The new patented moving balancer system, LBOII, is designed with micro ball bearings arranged in an infinite-loop configuration to drastically reduce friction of traditional moving balancers. The LBOII weight is magnetically held to the front position, and when unleashed during casting the inertial impact generates a powerful propulsion vector, dramatically increasing casting performance, even against headwinds. From the moment you begin your retrieve, the ONETEN MAX LBO’s weight leaps to the front position with astonishing speed, providing full lure action for the entirety of your cast. The overwhelmingly fast startup performance and incredibly dynamic jerking performance are thanks to the ONETEN MAX LBO’s action and power being on the same linear axis. * The photograph is a prototype.</v>
       </c>
-      <c r="O152" t="str">
-        <v/>
-      </c>
-      <c r="P152" t="str">
-        <v/>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -8042,12 +7133,6 @@
       <c r="N153" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth. * The photograph is a prototype.</v>
       </c>
-      <c r="O153" t="str">
-        <v/>
-      </c>
-      <c r="P153" t="str">
-        <v/>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -8092,12 +7177,6 @@
       <c r="N154" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth.</v>
       </c>
-      <c r="O154" t="str">
-        <v/>
-      </c>
-      <c r="P154" t="str">
-        <v/>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -8142,12 +7221,6 @@
       <c r="N155" t="str">
         <v>ワンテンR「Hi-FLOAT」は、ウィードやグラスの繁茂する高水温期において、圧巻の威力を発揮するワンテンRのシークレット・チューンドモデル。いわゆるウキウキパターンを広めた第一人者、佐藤信治が満を持して送り出すスペシャルメソッド対応モデルです。ウィードやグラス上のオープン域で2ジャークして浮かす、というのが王道メソッド。応用として、ショアのブッシュやリーズ、レイダウンなどのカバー周りや、桟橋や岩場などのストラクチャー周りにタイトにキャストし、やはり2ジャークして浮かす、といった使用方法が効果的。ワンテンR「Hi-FLOAT」だけの爆発力は、正直、秘密にしておきたかったことですが、多くのアングラーの笑顔がみたいプロガイド、佐藤信治だからこそリリースできたモデルです。</v>
       </c>
-      <c r="O155" t="str">
-        <v/>
-      </c>
-      <c r="P155" t="str">
-        <v/>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -8192,12 +7265,6 @@
       <c r="N156" t="str">
         <v>The ONETEN R was specially designed by Yuki Ito and renowned jerkbait angler Shinji Sato. The objective of the ONETEN R was to build upon the unique jerking action of the ONETEN, and fine-tune for domination on Lake Biwa in both straight retrieve and traditional jerkbait applications. During jerking and retrieves, it exhibits unique performance, honed over countless years of experience and prototypes. This full contact jerkbait “system” targets specific depths, and will reliably draw out reaction bites no matter the season. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth.</v>
       </c>
-      <c r="O156" t="str">
-        <v/>
-      </c>
-      <c r="P156" t="str">
-        <v/>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -8242,12 +7309,6 @@
       <c r="N157" t="str">
         <v>The ONETEN R+3 joins the ONETEN R series. Inheriting the concept behind the ONETEN R, the R’s depth has finally reached 4m! Just imagine… the performance of the ONETEN R at a depth of 4m. The ONETEN R’s realistic baitfish darting and irregular actions are being brought to a range previously only occupied by big cranks. What’s noteworthy is that while having the ability to dive to such depths, the R+3 maintains light pulling resistance and with jerking can perform sharp darting in the deep zone that can trigger reaction bites at will. Years of Megabass hydrodynamics research and the unique actions of the ONETEN will now take the deepest range by storm. &lt;ONETEN R - CONCEPT&gt; 1. ONETEN R retains the sharp, darting action of the original ONETEN, but during retrieves it’s designed to perform a refined, natural action that will get the attention of even the most cautious bass. 2. Moving balancer system now features one tungsten weight instead of two. By combining the weights into one main weight, it increases the casting power and flight distance due to its beautiful flight posture. 3. By switching between the ONETEN R, R+1, and R+2, you can adjust precisely to the appropriate swimming depth. * The photograph is a prototype.</v>
       </c>
-      <c r="O157" t="str">
-        <v/>
-      </c>
-      <c r="P157" t="str">
-        <v/>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -8292,12 +7353,6 @@
       <c r="N158" t="str">
         <v>The VISION ONETEN R Hi-FLOAT series now features a deep-diving +3 model that takes high buoyancy to new depths. The VISION ONETEN R+3 Hi-FLOAT is a guide-tuned model of the ONETEN R that excels when water temperatures rise, and submerged vegetation nears its peak. Taking shape from the summer jerkbait technique of legendary guide, Shinji Sato, the Hi-FLOAT is built to target the submerged weed beds of Lake Biwa with a jerk-jerk-rise approach. Whether targeting vegetation where the Hi-FLOAT setting is necessary to escape entanglement, or more traditional structure, the highly buoyant design adds a dynamic rising trigger for aggressive warm water feeders. The VISION ONETEN R+3 Hi-FLOAT has remained a Shinji Sato guide secret until now; experience the power of explosive buoyancy.</v>
       </c>
-      <c r="O158" t="str">
-        <v/>
-      </c>
-      <c r="P158" t="str">
-        <v/>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -8342,12 +7397,6 @@
       <c r="N159" t="str">
         <v>The X-48 Acrobat packs a bold punch much larger than its small frame would suggest. Designed to lure big fish with its finesse approach, the Acrobat springs into action with a twitch of the rod, delivering big action to trigger reaction bites. Built for situations when visible fish don’t commit, the Acrobat gives off a hi-pitch wobble and roll with straight retrieve, triggering bites from stubborn fish with well-timed rod action. Active moving balancer system drives unparalleled casting distance for its size, and guides life-like swimming action. The new generation of finesse minnow has arrived, and it packs a punch. ※The photograph is a prototype.</v>
       </c>
-      <c r="O159" t="str">
-        <v/>
-      </c>
-      <c r="P159" t="str">
-        <v/>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -8392,12 +7441,6 @@
       <c r="N160" t="str">
         <v>To give more sharpness to its movements during trick actions, the X-70's moving balancer design has been tuned to respond extremely sensitively to rod input such as twitches and jerks. During jerks, the X-70's unique flat body creates dynamic flashing that is easily mistaken for the flashing of live bait. There are many minnows that are focused on darting action, but the X-70 is probably the only one focused on getting bites with its mesmerizing flashing during normal retrieves as well.</v>
       </c>
-      <c r="O160" t="str">
-        <v/>
-      </c>
-      <c r="P160" t="str">
-        <v/>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -8442,12 +7485,6 @@
       <c r="N161" t="str">
         <v>The X-52 Acrobat packs a bold punch much larger than its small frame would suggest. Designed to lure big fish with its finesse approach, the Acrobat springs into action with a twitch of the rod, delivering big action to trigger reaction bites. Built for situations when visible fish don’t commit, the Acrobat gives off a hi-pitch wobble and roll with straight retrieve, triggering bites from stubborn fish with well-timed rod action. Active moving balancer system drives unparalleled casting distance for its size, and guides life-like swimming action. The new generation of finesse minnow has arrived, and it packs a punch. ※The photograph is a prototype.</v>
       </c>
-      <c r="O161" t="str">
-        <v/>
-      </c>
-      <c r="P161" t="str">
-        <v/>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -8492,12 +7529,6 @@
       <c r="N162" t="str">
         <v>Live-X REVENGE looks a lot like LEVIATHAN, but that is where resemblance stops. Slightly more slender than LEVIATHAN,REVENGE`s actions are controlled by a completely new balancer system. REVENGE`s diving range is between 6 and 10 feet, the most frequently used range, and shallower than LEVIATHAN. In a way, REVENGE is an easier and handier bait to use than LEVIATHAN. Also, REVENGE comes with MEGABASS original GUANIUM finish.</v>
       </c>
-      <c r="O162" t="str">
-        <v/>
-      </c>
-      <c r="P162" t="str">
-        <v/>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -8542,12 +7573,6 @@
       <c r="N163" t="str">
         <v>熾烈なUSAトーナメントシーンで勝ち抜くためのブランドン・パラニュークの知見と、世界各地のタフフィールドで膨大な実績を積み重ねてきた伊東由樹のエンジニアリングが融合し、誕生したシステム・ディープクランクシリーズがiPXです。 iPX-12は12ft(3.6m)を、iPX-16は16ft(4.8m)をメインレンジとし、それぞれ最大深度は15ft(4.5m)、18ft（5.4m)に到達。 内蔵された前後の2レーン内を各々フリーに移動し、潜行に応じてボディバランスを自発的に保持しようと多様な前転倒立型の重心ベクトルを適宜生み出す「フォワードロール重心移動システム」(PAT.P)は、限界まで前方向移動するフォワードバランシングが急角潜行を生み出し、プロダクティブゾーンを拡大。 リップ上にデザインした多角形ホールは、あらゆるダイビングアングルから効率よく水圧を確実に掴み、「フォワードロール重心移動システム」(PAT.P)と相まって、揺るぎ無いアクションスタビリティを生み出し続けます。 エッジの効いたウルトラ・ハイピッチアクションと強波動、体高のあるボディが発する激しい明滅は、広範囲にアピールしランカーのバイトを果敢に誘発。 ボトムコンタクトにおいて障害物回避からの復元力に優れ、持続的にボトムタッチし続けるディギングアクションと、長時間のデッドスロー＆ボトムトレースを実現。ライブシューティング／FFS（フォワード・フェイシング・ソナー）のトーナメントシーンにおいて釣り勝つことができる、究極のディープ・サーチベイトです。</v>
       </c>
-      <c r="O163" t="str">
-        <v/>
-      </c>
-      <c r="P163" t="str">
-        <v/>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -8592,12 +7617,6 @@
       <c r="N164" t="str">
         <v>熾烈なUSAトーナメントシーンで勝ち抜くためのブランドン・パラニュークの知見と、世界各地のタフフィールドで膨大な実績を積み重ねてきた伊東由樹のエンジニアリングが融合し、誕生したシステム・ディープクランクシリーズがiPXです。 iPX-12は12ft(3.6m)を、iPX-16は16ft(4.8m)をメインレンジとし、それぞれ最大深度は15ft(4.5m)、18ft（5.4m)に到達。 内蔵された前後の2レーン内を各々フリーに移動し、潜行に応じてボディバランスを自発的に保持しようと多様な前転倒立型の重心ベクトルを適宜生み出す「フォワードロール重心移動システム」(PAT.P)は、限界まで前方向移動するフォワードバランシングが急角潜行を生み出し、プロダクティブゾーンを拡大。 リップ上にデザインした多角形ホールは、あらゆるダイビングアングルから効率よく水圧を確実に掴み、「フォワードロール重心移動システム」(PAT.P)と相まって、揺るぎ無いアクションスタビリティを生み出し続けます。 エッジの効いたウルトラ・ハイピッチアクションと強波動、体高のあるボディが発する激しい明滅は、広範囲にアピールしランカーのバイトを果敢に誘発。 ボトムコンタクトにおいて障害物回避からの復元力に優れ、持続的にボトムタッチし続けるディギングアクションと、長時間のデッドスロー＆ボトムトレースを実現。ライブシューティング／FFS（フォワード・フェイシング・ソナー）のトーナメントシーンにおいて釣り勝つことができる、究極のディープ・サーチベイトです。</v>
       </c>
-      <c r="O164" t="str">
-        <v/>
-      </c>
-      <c r="P164" t="str">
-        <v/>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -8642,12 +7661,6 @@
       <c r="N165" t="str">
         <v>A well-kept secret of the Megabass Pro Team, the TRICK DARTER features the same legendary MULTI-WAY MOVING BALANCER SYSTEM (PAT.) as the VISION ONETEN, and is designed to move with an insane darting action that surpasses that of even the VISION ONETEN. With the addition of a fixed balancer in front, a spoonbill lip, and our infamous tungsten balancer system, the TRICK DARTER will truly "flee" erratically with short snaps of the rod, and draw reaction strikes from the most timid fish in the lake. Unlike conventional minnow–shaped jerk baits, the X-80 looks more like a shad or a shiner. Since baitfish with wider bodies flash more noticeably and are heartier meals for predators, the X-80 will attract larger fish. Furthermore, the X-80 swims with a distinct rolling wobble, an action that helps put our baits a world apart from the rest.</v>
       </c>
-      <c r="O165" t="str">
-        <v/>
-      </c>
-      <c r="P165" t="str">
-        <v/>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -8692,12 +7705,6 @@
       <c r="N166" t="str">
         <v>X-80Jr.は、ストレートリトリーブでは、オリジナルX-80を彷彿とさせるダイナミックなウォブンロール＆脱軌跡アクションを発生。ジャークやトゥイッチを併用しなくても、単純なストップ＆ゴーだけで、手軽にイレギュラーアクションを生み出します。トゥイッチを加えれば、シャッドプラグに切迫する強烈なフラッシングとキレのいいヒラ打ち瞬間ダートを披露。逃げ惑う小魚を演出し、スレきったモンスターにスイッチを入れます。X-80Jr.は、2連の重心移動ウエイトを搭載。安定した飛行姿勢とロングキャスタビリティを発揮します。従来のスモールサイズミノーの概念を覆す新次元のライトプラッキングを実現します。</v>
       </c>
-      <c r="O166" t="str">
-        <v/>
-      </c>
-      <c r="P166" t="str">
-        <v/>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -8742,12 +7749,6 @@
       <c r="N167" t="str">
         <v>LEVIATHAN is the flagship of Live-X series. It dose everything MARGAY and SMOLT does, but only more dynamically. If you want jerking actions in the mid-deep, LEVIATHAN is what you are looking for. Meticulously　detailed, LEVIATHAN showcases Yuki Ito? talent as a hand carver. LEVIATHAN can be used as a regular jerkbait. However, we suggest that you spend enough time to get to know what this bait is capable of doing.</v>
       </c>
-      <c r="O167" t="str">
-        <v/>
-      </c>
-      <c r="P167" t="str">
-        <v/>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -8792,12 +7793,6 @@
       <c r="N168" t="str">
         <v>I X I BLOWLY, is the ultimate shallow assault crankbait and third creation from the I×I project born from the combined insight of Katsutaka Imae and Yuki Ito. Equipped with Ito’s signature hydrodynamic theory (PAT.P) deployed in the FURIOUS series, BLOWLY features a fat-bodied profile that stirs the super-shallow zone with an fever-pitch retrieve action. This is no ordinary crank—it’s a veritable shockwave generator, designed to rattle the instincts of bass lurking anywhere near the retrieve line, forcing reaction bites from even the most indifferent feeders. At any retrieve speed, the I×I BLOWLY delivers a high-frequency pitch that outdoes even classic balsa crankbaits. Its distinct performance stems from the fusion of two critical elements: • Expanded frontal surface area that enhances visual and vibrational presence • Patented water-through structural design that amplifies action and hydrodynamic control Though it runs in the super-shallow range, BLOWLY provokes aggressive chase bites from bass rising out of deeper zones or approaching from lateral angles in open water. The result is a nonstop, high-alert game, where strikes come from every direction—vertical or horizontal—without warning.</v>
       </c>
-      <c r="O168" t="str">
-        <v/>
-      </c>
-      <c r="P168" t="str">
-        <v/>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -8842,12 +7837,6 @@
       <c r="N169" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O169" t="str">
-        <v/>
-      </c>
-      <c r="P169" t="str">
-        <v/>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -8892,12 +7881,6 @@
       <c r="N170" t="str">
         <v>When first designing the original GRIFFON crankbait in the late 1990’s, Yuki Ito sought a functionally comfortable form with an outsized impact. The result was a compact crankbait that quickly built a storied legacy around the world. This winning formula has given rise to a constantly evolving character that is compact, pinball-shaped, and mischievously productive—enter the third-generation GRIFFON. Enhanced hydrodynamics and a re-tuned internal structure dial up the GRIFFON’s relentlessly dynamic pinball-deflection action, delivering a larger-than-life reaction bite when it matters most. Its ability to quickly recover from frantic deflections is faithfully inherited from its forefathers and further refined. In the waters that so often feature in challenging tournaments, the GRIFFON has confidently demonstrated its outsized fishing performance. The only thing that can surpass a GRIFFON is, indeed, a GRIFFON. Discover your outperformance today.</v>
       </c>
-      <c r="O170" t="str">
-        <v/>
-      </c>
-      <c r="P170" t="str">
-        <v/>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -8942,12 +7925,6 @@
       <c r="N171" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O171" t="str">
-        <v/>
-      </c>
-      <c r="P171" t="str">
-        <v/>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -8992,12 +7969,6 @@
       <c r="N172" t="str">
         <v>When first designing the original GRIFFON crankbait in the late 1990’s, Yuki Ito sought a functionally comfortable form with an outsized impact. The result was a compact crankbait that quickly built a storied legacy around the world. This winning formula has given rise to a constantly evolving character that is compact, pinball-shaped, and mischievously productive—enter the third-generation GRIFFON. Enhanced hydrodynamics and a re-tuned internal structure dial up the GRIFFON’s relentlessly dynamic pinball-deflection action, delivering a larger-than-life reaction bite when it matters most. Its ability to quickly recover from frantic deflections is faithfully inherited from its forefathers and further refined. In the waters that so often feature in challenging tournaments, the GRIFFON has confidently demonstrated its outsized fishing performance. The only thing that can surpass a GRIFFON is, indeed, a GRIFFON. Discover your outperformance today.</v>
       </c>
-      <c r="O172" t="str">
-        <v/>
-      </c>
-      <c r="P172" t="str">
-        <v/>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -9042,12 +8013,6 @@
       <c r="N173" t="str">
         <v>The DEEP-X 100, which has been the long-established benchmark for diving crankbaits, is finally being equipped with the LBO II (Linear Bearing Oscillator II). With its surprisingly compact body, the DEEP-X can instantly attack at its maximum diving depth and displays an astonishing ability for obstacle evasion. No matter the type of contact, the LBO II combines with the cutting-edge hydrodynamic body to consistently maintain action and control, responding directly to the angler’s retrieve to trigger bites. With the LBO II and its new hydrodynamic form, the DEEP-X achieves a lag-less initial swimming response that allows for intuitive cranking. From ponds, to rivers, to large lakes, this versatile crankbait can easily hammer out results in any field. * The photograph is a prototype.</v>
       </c>
-      <c r="O173" t="str">
-        <v/>
-      </c>
-      <c r="P173" t="str">
-        <v/>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -9092,12 +8057,6 @@
       <c r="N174" t="str">
         <v>The DEEP-X 200 is one of Yuki Ito’s favorite lures in his 30+ year career as a lure designer. The DEEP-X 200 exhibits multifaceted performance and versatility for underwater games in many fields, excelling as a crankbait, a flatside shad, at times a diving minnow, and at times a vibration bait that searches a dedicated range. The uniquely evolved form of this DEEP-X 200 features further refinements from the previous model. In addition to the high pitch vibrations, the angle of the head amplifies its sharp, rolling action. It emits intense high pitch flashing and impactful vibrations. The astonishing flight distance of the slim-bodied 200, made possible by the LBO II, defies expectation. The ultra-long-distance casting performance easily outpaces a typical crankbait, demonstrating the far-reaching explosive performance of this extraordinary crankbait. * The photograph is a prototype.</v>
       </c>
-      <c r="O174" t="str">
-        <v/>
-      </c>
-      <c r="P174" t="str">
-        <v/>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -9142,12 +8101,6 @@
       <c r="N175" t="str">
         <v>The DEEP-X300 is a long anticipated deep-diving crank bait that adds dimension to the DEEP-X series. With a diving depth of 5m (almost 17 feet) and a much larger body size than the 200 and the 100, the DEEP-X300 will let you invade the depths where lunker fish routinely hide. As with its other DEEP-X brothers, the 300 is equipped with the MULTI-WAY MOVING BALANCER SYSTEM(PAT.). That means the 300 will dive almost vertically in order to maximize effective cranking distance and will also respond to every little twitch or jerk you send to the bait. All of the DEEP-X series crank baits will allow for the conventional bottom-digging method for creating those strike-inducing irregular darting actions, but what makes the DEEP-X series so unique is their mid-water twitch/jerk action, which appeals to the fish at any depth. The 300's colors are uniquely developed for the lower light environment of deeper water.</v>
       </c>
-      <c r="O175" t="str">
-        <v/>
-      </c>
-      <c r="P175" t="str">
-        <v/>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -9192,12 +8145,6 @@
       <c r="N176" t="str">
         <v>The DEEP-SIX was designed by Yuki Ito to trigger bites at depths of over 6 meters (20ft.), a largely uncharted territory among diving cranks. This range is made possible by a unique, super thin lip that slices through currents, and maintains the ideal balance required for a steep dive angle. Furthermore, the DEEP-SIX incorporates the renowned MULTI-WAY MOVING BALANCER SYSTEM(PAT.) of the DEEP-X series. During casts, the main weight moves to the rear, positioning DEEP-SIX tail-first to maximize aerodynamics and casting distance. When diving, the weight moves to the front of the lure to increase DEEP-SIX’s dive angle, which means you get down to target depth much faster. When DEEP-SIX reaches its maximum diving depth and contacts bottom, underwater structure, or is twitched, the main balancer is released, causing the weight to slide and increase action. If DEEP-SIX levels out at its maximum depth without contacting bottom, the main weight is released from the front and moves to the middle position. This changes the lure’s action, creating a realistic flash and aggressive high pitch rolling and wobbling that ignites the instincts of monsters in the deep. Until now, the super deep range has remained a safe haven for lunkers. Now Megabass has created a lure to venture into the deep, and dominate the monsters’ sanctuary.</v>
       </c>
-      <c r="O176" t="str">
-        <v/>
-      </c>
-      <c r="P176" t="str">
-        <v/>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -9242,12 +8189,6 @@
       <c r="N177" t="str">
         <v>The world-renowned DEEP-X series sports such exceptional performance that it is almost unfair to use it. Among that DEEP-X series, the DEEP-X150 has a particularly excellent record. Its tight, super-natural wobbling not only creates outstanding water displacement, but emits lively flashing that triggers the feeding instincts of neutral fish cruising in the mid range. The DEEP-X series' acrobatic actions upon contact with structures remains intact with 150's smaller body size, which only serves to make those actions sharper and more amplified. By hitting the lure against underwater slopes and objects on the bottom you can get reaction bites from even spooked bass under high pressure conditions.</v>
       </c>
-      <c r="O177" t="str">
-        <v/>
-      </c>
-      <c r="P177" t="str">
-        <v/>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -9292,12 +8233,6 @@
       <c r="N178" t="str">
         <v>With its extraordinary roll-axis and unique action, the FLAPSLAP has earned a niche reputation for its intensely powerful flashing appeal. The specially designed shaft balancer, placed ultra-low along the bottom of the body and slightly offset from the roll axis of the action, powers a pendulum action that enhances and stabilizes the lure’s outsized roll-axis and flash. This results in water agitation comparable to that of much bigger-bodied crankbait, supercharging the FLAPSLAP’s results in challenging conditions. With nearly instantaneous startup action from the first handle turn, its unique high-pitch screw drive action emits a striking strobe flash, evoking a fleeing shad. This otherworldly flat-sided bait contributed significantly to Edwin Evers’ victory at the 2016 BASSMASTER Classic.</v>
       </c>
-      <c r="O178" t="str">
-        <v/>
-      </c>
-      <c r="P178" t="str">
-        <v/>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -9342,12 +8277,6 @@
       <c r="N179" t="str">
         <v>With its extraordinary roll-axis and unique action, the FLAPSLAP has earned a niche reputation for its intensely powerful flashing appeal. The specially designed shaft balancer, placed ultra-low along the bottom of the body and slightly offset from the roll axis of the action, powers a pendulum action that enhances and stabilizes the lure’s outsized roll-axis and flash. This results in water agitation comparable to that of much bigger-bodied crankbait, supercharging the FLAPSLAP’s results in challenging conditions. With nearly instantaneous startup action from the first handle turn, its unique high-pitch screw drive action emits a striking strobe flash, evoking a fleeing shad. This otherworldly flat-sided bait contributed significantly to Edwin Evers’ victory at the 2016 BASSMASTER Classic.</v>
       </c>
-      <c r="O179" t="str">
-        <v/>
-      </c>
-      <c r="P179" t="str">
-        <v/>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -9392,12 +8321,6 @@
       <c r="N180" t="str">
         <v>The FLAPSLAP has received acclaim around the world for its phenomenal action and life-like detail, proving an indispensable addition to crankbait and jerkbait arsenals alike. Now equipped with the next-generation LBO II (PAT.) moving balancer system, the FLAPSLAP LBO rockets into the future with unrivaled casting distance. The nearly frictionless ball-bearing design of the LBO II (PAT.) balancer system leaps instantly to the tail section to power exceptional casting distance, then shifts to its front, low center-of-gravity position to deliver the storied action for which the FLAPSLAP is already well-known. Now tuned to suspend, the FLAPSLAP LBO can be burned, twitched, and paused above submerged weed beds and other target-rich environments, showing off its beautiful profile and elegant finishes to elicit bites from even the most discerning targets. Exquisite design, hydrodynamic form and balancer system combine to deliver not only the tight-wobbling action anglers expect from flat-sided crankbaits, but a difficult-to-achieve, wide-rolling action that sends enticing flashes throughout the water column. Additionally, much like the original, the FLAPSLAP LBO can be twitched to perform erratic darting rolls that displace water and display huge flashes to call in targets from distance, and trigger reaction bites from followers. * The photograph is a prototype.</v>
       </c>
-      <c r="O180" t="str">
-        <v/>
-      </c>
-      <c r="P180" t="str">
-        <v/>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -9442,12 +8365,6 @@
       <c r="N181" t="str">
         <v>メガバスファクトリーの熟練クラフツマンがハンドメイドによって製作するZ-CRANK。天然素材によるバルキーなハイフロートボディーは、バイブレーションプラグのような強波動・ハイピッチ・グラインドウォブリングを生み出し、マッディーカバーに潜伏する魚にしっかりとその存在をアピール。独特なフォルムと高強度・高弾性薄型コフィンリップによってスナッグレス性能を高め、シャローエリアのカバーに対するスタックを軽減。ブッシーなシャローやリップラップ、スタンプなどのカバーエリア付近を、ハイフロートボディが巧みにかわし、果敢なクランキングを展開します。</v>
       </c>
-      <c r="O181" t="str">
-        <v/>
-      </c>
-      <c r="P181" t="str">
-        <v/>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -9492,12 +8409,6 @@
       <c r="N182" t="str">
         <v>メガバスファクトリーの熟練クラフツマンがハンドメイドによって製作するZ-CRANK。天然素材によるバルキーなハイフロートボディーは、バイブレーションプラグのような強波動・ハイピッチ・グラインドウォブリングを生み出し、マッディーカバーに潜伏する魚にしっかりとその存在をアピール。独特なフォルムと高強度・高弾性薄型コフィンリップによってスナッグレス性能を高め、シャローエリアのカバーに対するスタックを軽減。ブッシーなシャローやリップラップ、スタンプなどのカバーエリア付近を、ハイフロートボディが巧みにかわし、果敢なクランキングを展開します。</v>
       </c>
-      <c r="O182" t="str">
-        <v/>
-      </c>
-      <c r="P182" t="str">
-        <v/>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -9542,12 +8453,6 @@
       <c r="N183" t="str">
         <v>The Z-2’s high pitch action is well-suited for mid-range areas and wide-open shallows. It features a “hard contact bill” designed to give clear feedback to the angler as the Z-2 relentlessly engages structures. The Z-2’s immediate posture recovery after contact is superb and its ability to trace tightly along the bottom is exceptional in its class. Previously, this degree of contact performance required a body volume twice as large in order to harness the effects of buoyancy, but the Z-2 has realized astonishing structure and bottom tracing with an unbelievably small size. The Z-2 is the ultimate searching master that allows the angler to clearly visualize the mid-range through the Z-2’s incessant contact. * The photograph is a prototype.</v>
       </c>
-      <c r="O183" t="str">
-        <v/>
-      </c>
-      <c r="P183" t="str">
-        <v/>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -9592,12 +8497,6 @@
       <c r="N184" t="str">
         <v>The Z-1 delivers “bulldog contact,” hitting bottom structure with relentless aggression to trigger frenzied reaction bites. The Z-1’s hard-hitting style sets it apart from the GRIFFON series’ finesse escape action. In the bitter winter, early spring, and during turnover periods, the Z-1 displays amazing stability that allows it to continuously engage riprap and shallow contours. Furious deflections never compromise the Z-1’s high pitch action during these situations, stimulating tough fish until they are compelled to bite. This next generation shallow runner is perfectly suited for attacking cruising fish around backwater sand bars, riprap, and shallow structures. * The photograph is a prototype.</v>
       </c>
-      <c r="O184" t="str">
-        <v/>
-      </c>
-      <c r="P184" t="str">
-        <v/>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -9642,12 +8541,6 @@
       <c r="N185" t="str">
         <v>The SONICSIDE is a competition-ready flatside crankbait born of the exacting demands of our Pro Staff. Built for a tight, high-pitch action to dominate cold water situations, the SONICSIDE displays unrivaled casting distance and stability during fast retrieves. The lip is shaped from tough, 1mm thick circuit board material reinforced with a molded support, making it an eerily responsive and durable option when targeting riprap and hard structure. Additionally, internal weights are fixed for a silent approach, and placed for optimal action, castability and stability at high speeds. This heavy-duty crankbait is built to out-cast and out-work the competition, dominating key targets in tough waters with its natural, high-pitch approach. * The photograph is a prototype.</v>
       </c>
-      <c r="O185" t="str">
-        <v/>
-      </c>
-      <c r="P185" t="str">
-        <v/>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -9692,12 +8585,6 @@
       <c r="N186" t="str">
         <v>The Super Z, renowned for its outsized castability and compact performance, is now available in a deeper diving Z3 version. Built to easily dominate deep water from wild ponds to big lakes, the Z3 can easily reach a maximum depth of 4m (13ft) on 8lb Fluorocarbon line. Powered by Megabass’ patented LBO II moving balancer system for superior casting distance, the Z3's hydrodynamic design exhibits an enticing tight-pitch action throughout the retrieve, staying true amidst current and bottom contact alike. Designed for easy handling with medium-light to medium rods in the F3 to F4 class, the Z3 is a compact deep crank for the next generation of discerning anglers. * The photograph is a prototype</v>
       </c>
-      <c r="O186" t="str">
-        <v/>
-      </c>
-      <c r="P186" t="str">
-        <v/>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -9742,12 +8629,6 @@
       <c r="N187" t="str">
         <v>Honed and refined over two years, the S-CRANK is a square bill crankbait featuring a patented design that generates a hard-hitting wobble action along with an erratic hunting, wandering retrieve. S-CRANK’s unique slalom action works even at high-speeds, wandering laterally off-course but always hunting back to center. Not only does this allow more effective coverage of wider areas, but the erratic wandering action triggers reaction bites much like deflections, increasing productivity in open water. Tight, enticing wobble draws inactive predators, while the sudden wandering escape action triggers decisive reaction bites. Square bill design and high buoyancy combine to reduce hang-ups to allow precise targeting of structure. * The photograph is a prototype.</v>
       </c>
-      <c r="O187" t="str">
-        <v/>
-      </c>
-      <c r="P187" t="str">
-        <v/>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -9792,12 +8673,6 @@
       <c r="N188" t="str">
         <v>BIG-M2.0 explores the 6ft range, a key depth throughout Lake Biwa that is a staple of renowned anglers like Shinji Sato. The BIG-M2.0 specializes in drawing bites from feeders lurking below the 6ft mark, sparking wild chases through open water and shallow cover alike. With a low center-of-gravity design, the BIG-M2.0 harnesses max-rotation rolling action to throw intense flash farther and wider, giving enticing glimpses of its exquisite flat-sided form to predators in the deep. Casts are powered by a triple balancer system, enabling long-distance ballistic approaches in weather conditions that would otherwise overpower conventional flat-sided offerings. Further, due to careful hydrodynamic consideration, the BIG-M exhibits surprisingly low pulling-resistance for its size, reducing the fatigue so often associated with larger lures. This allows anglers to comfortably deploy big bait techniques to target wider areas and new classes of fish, delivering maximum distance and performance with minimal effort. * The photograph is a prototype.</v>
       </c>
-      <c r="O188" t="str">
-        <v/>
-      </c>
-      <c r="P188" t="str">
-        <v/>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -9842,12 +8717,6 @@
       <c r="N189" t="str">
         <v>MPW「ハダラトラップ」70は、NEWコンセプト・トリックベイト。デッドスローリトリーブ中にも激しい明滅を「ランダム」に発生させ、ハイピッチ・ロールドライブを基調としながらも、クレバーフィッシュに見切られない、左右への「千鳥ダート軌道」でスイミング。 そんな複合的なエスケープアクションをオートマティックに披露してくれるHADARA TRAPは、直線軌道にて一定のリズムでアピールするバイブレーションプラグやスピナーベイトが見切られる状況、タフ化したメジャーエリアなどで大変有効です。 2つの超高比重・大径タングステンバランサーによる「タンデム重心移動システム」を搭載し、タフ化した広域エリアを効率よく攻め抜く圧巻の飛距離を叩き出します。 伊東由樹のハイドロダイナミクス理論によってデザインされた独特なボディは、広大なシャローエリアでも、一定の浅層レンジをキープしながらトリッキーに泳ぎ続けられる、ロングラン攻略を実現。 さらに、ハダラトラップ70は、リフト＆フォールでも威力を発揮。リフト時には、「ヒラウチバイブ」を発生し、フォール時にはボディを細かく震わせて沈下する「シミーフォール」を披露。マルチに仕掛けられる、特別なトラップベイトです。</v>
       </c>
-      <c r="O189" t="str">
-        <v/>
-      </c>
-      <c r="P189" t="str">
-        <v/>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -9892,12 +8761,6 @@
       <c r="N190" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O190" t="str">
-        <v/>
-      </c>
-      <c r="P190" t="str">
-        <v/>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -9942,12 +8805,6 @@
       <c r="N191" t="str">
         <v>The BIG-M is the evolutionary result of many years of Megabass big crankbaits. It leaves behind the fat bodied and long billed design of past deep cranks, assuming a flat side design with a short lip and low center of gravity. It realizes sharp, rolling action that generates an overwhelming flashing impact. This design is meant to trace the productive zone at a range of 3.5m (11-12ft). It has incredible castability that allows it to slice through headwinds, combined with low-resistance retrieve which allows it to be used all day long with minimal fatigue. The BIG-M has the power to draw in big bass lurking in the depths, all contained within a package full of extraordinarily refined engineering. Developed under the guidance of Lake Biwa’s “manager,” Shinji Sato, Yuki Ito and the development team came together to produce this next generation big crank. This giant killer crank will dramatically increase contact rates with big bass. * The photograph is a prototype.</v>
       </c>
-      <c r="O191" t="str">
-        <v/>
-      </c>
-      <c r="P191" t="str">
-        <v/>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -9992,12 +8849,6 @@
       <c r="N192" t="str">
         <v>The PROJECT LEGEND LD series concept places current designs for custom-tuning at the hands of Yuki Ito. The first lure to receive this treatment is the Knuckle 60, which has been fine-tuned with a circuit-board lip to tackle the tough waters of Japan. The thin, durable lip activates the KNUCKLE LD, making the bait even more responsive in the water, exhibiting a heightened high-pitch wobble &amp; roll action. Additionally, the front hook is equipped with lightweight heavy-duty swivel to increase hook up ratio and virtually eliminate lost fish. Internal weight balancer is secured from multiple angles to achieve a truly silent approach. Specially-tuned to catch that key fish in the toughest conditions. * The photograph is a prototype.</v>
       </c>
-      <c r="O192" t="str">
-        <v/>
-      </c>
-      <c r="P192" t="str">
-        <v/>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -10042,12 +8893,6 @@
       <c r="N193" t="str">
         <v>バイブレーションX ウルトラは、伊東独自のハイドロダイナミクスによるボディフォーミングが普遍的釣果をもたらしてきました。 新たに開発したウェイトパッケージングによりいっそう強化された超高速・ハイピッチロールドライブは、シャープかつ鋭いエッジの振動を生み、独自のプロペラ形状のボディが整流する際生み出す圧倒的な水流撹拌力と相まって、未知のランカーにアピール。 ボディ表面に波打つトーン変化を積極的に生み出し、視覚効果も最大限に引き出します。 バイブレーションXの爆釣伝説は不滅です。</v>
       </c>
-      <c r="O193" t="str">
-        <v/>
-      </c>
-      <c r="P193" t="str">
-        <v/>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -10092,12 +8937,6 @@
       <c r="N194" t="str">
         <v>The DYNA RESPONSE is a new concept metal vibe developed by Shinji Sato. The super-thin 0.6mm stainless plate cuts through water and features a carefully sculped weight design that generates powerful vibrations and quick start-up action. The weight’s hydrodynamic design powers a sharp, high pitch action and kicks into gear instantaneously whether employing lift &amp; fall or more traditional retrieves. The placement of the rear treble and innovative tinsel-tail detail significantly reduce line tangle on slack line and at the end of long casts, in addition to providing an enticingly new flicker-flash to the DYNA RESPONSE’s vibrating action. With its outsized flash, high-pitch vibration, tangle-fighting tinsel and lightning-quick startup action, the DYNA RESPONSE elevates the traditional metal vibe to new heights.</v>
       </c>
-      <c r="O194" t="str">
-        <v/>
-      </c>
-      <c r="P194" t="str">
-        <v/>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -10142,12 +8981,6 @@
       <c r="N195" t="str">
         <v>バイブレーションX スマトラは、伊東独自のハイドロダイナミクスによるボディフォーミングが普遍的釣果をもたらしてきました。 新たに開発したウェイトパッケージングによりいっそう強化された超高速・ハイピッチロールドライブは、シャープかつ鋭いエッジの振動を生み、独自のプロペラ形状のボディが整流する際生み出す圧倒的な水流撹拌力と相まって、未知のランカーにアピール。 ボディ表面に波打つトーン変化を積極的に生み出し、視覚効果も最大限に引き出します。 バイブレーションXの爆釣伝説は不滅です。</v>
       </c>
-      <c r="O195" t="str">
-        <v/>
-      </c>
-      <c r="P195" t="str">
-        <v/>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -10192,12 +9025,6 @@
       <c r="N196" t="str">
         <v>※The photograph is a prototype.</v>
       </c>
-      <c r="O196" t="str">
-        <v/>
-      </c>
-      <c r="P196" t="str">
-        <v/>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -10242,12 +9069,6 @@
       <c r="N197" t="str">
         <v>The concept behind the VIBRATION-X DYNA is high power + compact body!! The DYNA combines a bite-sized silhouette with violent rolling, ultra high-pitch vibration, overwhelming flight distance, and exceptional structure evasion performance. The internal weights are positioned to give the lowest possible center of gravity, increasing stability. The nose cup catches water flow, dramatically increasing responsiveness during actions. The exceptional initial swimming performance at the start of retrieves helps to increase the productive zone of the lure, allowing it to cover a wide area despite its small size. The DYNA is a little giant whose oversize vibrations and high-speed flashing puts past small vibes to shame. DYNA triggers the fighting instincts of neutral fish, drawing forth a new level of reaction bite. ※The photograph is a prototype.</v>
       </c>
-      <c r="O197" t="str">
-        <v/>
-      </c>
-      <c r="P197" t="str">
-        <v/>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -10292,12 +9113,6 @@
       <c r="N198" t="str">
         <v>1. Stop to Entice (Stop&amp;Go / Stay＆Jerk) The VIBRATION-X VATALION dramatically changes the strategy for targeting suspended bass. Twitching the lure results in dynamic 240-degree+ turns and intense flashing from the jointed body. In muddy water, the appeal of its broad, flat side far exceeds thin bodied jerkbaits and draws out many bites. The intermediate settings, the small “chip bill” that allows it to keep a consistent depth in shallows, the nose position line eye, the jointed slant tail—all of these features actively draw out those slow, reluctant fish in the shallows with the perfect “stop” approach. Whether it’s using stop &amp; go tactics to help evade the numerous structures in shallow areas or using stay &amp; jerk tactics immediately below the surface in weeded areas, this lure will help you get those suspended fish that spinnerbait and crankbait can’t touch. Watch it stimulate their activity level and land bite after bite. 2. Straight Retrieves in Shallows (Hi-Pitch - Straight Retrieve) During straight retrieves, it displays lifelike shimmering action, and the body segments contact each other to produce a sound that draws predators. It effectively draws bites from the shallow and midrange, covering a wide area. * The photograph is a prototype.</v>
       </c>
-      <c r="O198" t="str">
-        <v/>
-      </c>
-      <c r="P198" t="str">
-        <v/>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -10342,12 +9157,6 @@
       <c r="N199" t="str">
         <v>LEVEL SWIMMERは、より遠くのエリア、より深くのレンジ攻略を可能としたヘヴィーシンキング・プロップベイト。ただ巻くだけでバイトを得られる効率的な釣獲パフォーマンスは、高い集魚効果を兼ね備えた喰わせのフィネスベイトです。 一口サイズの「低重心・ヘヴィウェイテッドボディ」は、圧倒的なロングキャスタビリティを実現。狙いのレンジに速やかに到達し、広域のターゲットにアピールするサーチベイトとして威力を発揮します。 ミディアム～ディープレンジに到る、あらゆる水深で発揮される「超長距離・I字系スイム」＋「波動」＋「マイクロシルエット」は、従来のスピナーベイトやクランクベイトを見切ったタフな魚をバイトに持ち込みます。</v>
       </c>
-      <c r="O199" t="str">
-        <v/>
-      </c>
-      <c r="P199" t="str">
-        <v/>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -10392,12 +9201,6 @@
       <c r="N200" t="str">
         <v>The i-SLIDE 265R is a magnum glide bait that further refines the monster bass pedigree of the 262T, exhibiting decisive glides and sinuous slides to tempt the next generation of trophy catches. Featuring a crisp, responsive S-swimming slalom as its base action, the i-SLIDE 265R demonstrates tenacious stability even in rivers and backwater current. With a twitch or varied retrieve speed, it seamlessly performs underwater dog-walks and continuous turns, responding expertly to angler input. And with a reinforced internal wire harness and heavy-duty swiveling hook hangars, the 265R is built to overwhelm even the most brutal fighters, ensuring that hard-won bites land where they belong. Thanks to the R “Revolution Model” series engineering, even rough rod work translates into sharp slalom actions and quick, responsive slides—making advanced techniques accessible to anglers of all skill levels. The i-SLIDE “R” series promises dramatic encounters that will shatter your personal best.</v>
       </c>
-      <c r="O200" t="str">
-        <v/>
-      </c>
-      <c r="P200" t="str">
-        <v/>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -10442,12 +9245,6 @@
       <c r="N201" t="str">
         <v>R is for Revolution. The i-SLIDE has evolved, bringing its confidence-inspiring glide to fresh heights. The i-SLIDE 187 R’s refined design puts the power of sharp S-motion action in the hands of all anglers, regardless of big bait experience. With a redesigned tail and retuned internal weighting, the new R delivers with greater consistence. With a straight retrieve, ¾ turns of the handle, or twitching rod work, the i-SLIDE performs with confident ease, delivering a sinuous “S” swimming action or a wide left/right glide. The 187 R offers a direct feel that allows the angler to clearly perceive the glide’s action even when out of sight, increasing the odds of continued success. The i-SLIDE 187 R delivers a confident glide, bringing the power of big baits to anglers in search of the next trophy catch. 【Floating Model】 The responsive sliding action and agile slalom movement, which instantly responds to retrieve movements, trigger active feeding. The 187R is easily tuned for a wide range of situations and suspend/sink rates by adjusting the hook and ring sizes and/or attaching weights. 【Intermediate Model】 The suspend setting makes it appealing to dormant monsters that typically remain undiscovered. This model can be used for dead-sticking to imitate baits drifting unprotected with no action, sliding slalom action in the mid-range, and other technical presentations depending on the situation, and target’s reaction.</v>
       </c>
-      <c r="O201" t="str">
-        <v/>
-      </c>
-      <c r="P201" t="str">
-        <v/>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -10492,12 +9289,6 @@
       <c r="N202" t="str">
         <v>The i-BRAKE’s unique brake fins bring hard stopping power to suppress the lure’s speed, adding a new bite trigger to swimbait games. As retrieve speed slows down, the soft tail pitches erratically, fluttering and dancing, while the brake fins push water. The lure's sudden stopping power delivers a writhing action, which in turn triggers more chases and bites. The i-BRAKE realistically mimics the defenseless and sudden start/stop movements of live bait. During retrieval, the combination of brake fins that create turbulent water displacement and a soft paddle-tail that produces a natural swim sends fine vibration throughout the body, attracting even the most cautious targets. The subtle attraction of the i-BRAKE proves its worth in challenging conditions such as the post-spawn period and autumn turnover, where conventional approaches often struggle. This unique stopping ability delivers overwhelming bites when other approaches fall silent.</v>
       </c>
-      <c r="O202" t="str">
-        <v/>
-      </c>
-      <c r="P202" t="str">
-        <v/>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -10542,12 +9333,6 @@
       <c r="N203" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O203" t="str">
-        <v/>
-      </c>
-      <c r="P203" t="str">
-        <v/>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -10592,12 +9377,6 @@
       <c r="N204" t="str">
         <v>SPINE-X is a segmented subsurface swimbait equipped with an innovative user-controlled wire-through titanium spinal system to deliver dynamic action. Megabass’ LIVE-WIRED SYSTEM(PAT.P) leverages the shape-memory properties of titanium wire to add layers of customizable control to SPINE-X’s swimming movement. Included with three titanium “spines,” anglers can add multiple wires at a time for tighter “s” swimming and a faster recovery rate between segmented joints. By changing the number of titanium wires, anglers can adjust the suppleness and tension of SPINE-X to perfectly match angler input and target preferences. This not only enables situation-specific tuning but adds a dynamic element of internal tension to the swimbait’s movement, contributing to its lifelike appeal. Developed to target those exceedingly discerning trophy predators, SPINE-X swims with sinuous flash and sends twitches and jerks shuddering from tip to tail with unsurpassed realism.</v>
       </c>
-      <c r="O204" t="str">
-        <v/>
-      </c>
-      <c r="P204" t="str">
-        <v/>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -10642,12 +9421,6 @@
       <c r="N205" t="str">
         <v>GORHAM is a jointed waking and subsurface bait with a mysterious presence that awakens distant neutral targets. GORHAM’s articulated body is equipped with two synchronized LBO II(PAT.) systems in each section. This patented moving balancer system significantly improves flight posture and cast distance, while providing optimal swimming balance for immediate action startup. As a result, GORHAM’s attack range is dramatically increased, bringing far-off targets within easy reach. A dynamic, ultra-wide rolling wake action calls targets to GORHAM from greater distances, inspiring frenzied surface attacks. The unique RAMBLE TAIL provides an erratic disturbance that triggers the instincts of hesitant surface feeders. GORHAM opens the door to new topwater potential, triggering bites from otherwise dormant targets. SLOW RETRIEVE With a slow retrieve, GORHAM’s natural tail swing paired with the movement of its jointed body create an ultra-realistic, sinuous flashing wake action on the surface. FAST RETRIEVE With a fast retrieve, GORHAM dives into the shallow subsurface range, moving with a large flashing and rolling action that generates bulging water displacement, triggering the active feeding instincts of targets who lurk in search of a fleeing meal. Work in a twitch to incite bites from targets hot on the trail.</v>
       </c>
-      <c r="O205" t="str">
-        <v/>
-      </c>
-      <c r="P205" t="str">
-        <v/>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -10692,12 +9465,6 @@
       <c r="N206" t="str">
         <v>SuWITCH is equipped with the patented transforming lip system pioneered in the XPOD. This revolutionary system allows the angler to change the angle of the lip with a firm “click” to instantly switch between different target ranges and action profiles. “Su” means four. SuWITCH, or "four witches," has a diversely destructive power that joins four seemingly magical powers into a single lure. It is a new generation of multi-purpose swimbait that can switch up its diving range and action to suit the situation.Equipped with the world's first "2-step variable bill" one-touch lip adjustment mechanism for swimbaits, SuWITCH switches seamlessly between "wake mode" and "dive mode" at the angler’s behest. In each mode, the lure can be retrieved with either a straight retrieve or with the additional dynamism of twitching and jerking rod work. Thus, a single lure can produce actions with four different appealing characteristics.</v>
       </c>
-      <c r="O206" t="str">
-        <v/>
-      </c>
-      <c r="P206" t="str">
-        <v/>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -10742,12 +9509,6 @@
       <c r="N207" t="str">
         <v>The secret behind GARUDA’s overwhelming ability to attract fish and elicit bites rests in its powerful movement, painstaking detail, and the quality of its sound. Double-jointed construction and careful design drive smooth, sinuous action punctuated by the enticing “knock” of GARUDA’s joints coming in contact. Spec’d as a floating lure, GARUDA is also designed to attach teardrop sinkers to the underside of the lip to fine-tune for virtually any depth range. For fishing that involves bottom contact, GARUDA can be “back hook tuned” by removing the trebles, and attaching a single hook to the top of the lure. The back of the lure, where the groove for hook shank is located, features a neodymium magnet MAGHOLD (PAT.) system to keep the top hook in place. The GARUDA’s overwhelming destructive power is perfect for top range dead sticking and waking, mid-range retrieves, bottom contact, and anything a monster hunter could possibly desire from a big bait. GARUDA is built to bring you results beyond your imagination. * BOMBADA SNAP OVO Size: No.3 Equipped standard * The photograph is a prototype.</v>
       </c>
-      <c r="O207" t="str">
-        <v/>
-      </c>
-      <c r="P207" t="str">
-        <v/>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -10792,12 +9553,6 @@
       <c r="N208" t="str">
         <v>ジャマイカボアは、全米で人気のOROCHI BUZZをベースに、トーナメントユースに特化したスペックでデザイン。広域エリアを効率よくサーチでき、遭遇するあらゆるカヴァーをものともせずに引き倒すことができ、込み合うカヴァーから果敢にビッグウエイトを引き抜いてランディングに持ち込める、競技スペックのヘビーデューティーバズベイトです。 広域に散るバスを的確に訴求するマンタプロップの卓越した集魚効果もトップカテゴリーのプロたちが絶賛。広域シャローでバスの有無を確認したいとき、ジャマイカボアがシークレットベイトとして使われる理由のひとつです。 トーナメントでサーチしたい多様なシャローのカヴァーエリアからハイスコアを叩きだすための革新的スペックが満載。「勝つ」ために使うバズベイトが、ジャマイカボアです。</v>
       </c>
-      <c r="O208" t="str">
-        <v/>
-      </c>
-      <c r="P208" t="str">
-        <v/>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -10842,12 +9597,6 @@
       <c r="N209" t="str">
         <v>ジャマイカボアは、全米で人気のOROCHI BUZZをベースに、トーナメントユースに特化したスペックでデザイン。広域エリアを効率よくサーチでき、遭遇するあらゆるカヴァーをものともせずに引き倒すことができ、込み合うカヴァーから果敢にビッグウエイトを引き抜いてランディングに持ち込める、競技スペックのヘビーデューティーバズベイトです。 広域に散るバスを的確に訴求するマンタプロップの卓越した集魚効果もトップカテゴリーのプロたちが絶賛。広域シャローでバスの有無を確認したいとき、ジャマイカボアがシークレットベイトとして使われる理由のひとつです。 トーナメントでサーチしたい多様なシャローのカヴァーエリアからハイスコアを叩きだすための革新的スペックが満載。「勝つ」ために使うバズベイトが、ジャマイカボアです。</v>
       </c>
-      <c r="O209" t="str">
-        <v/>
-      </c>
-      <c r="P209" t="str">
-        <v/>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -10892,12 +9641,6 @@
       <c r="N210" t="str">
         <v>マグドラフトフリースタイルにジャストフィットする専用ジグヘッド。マグドラフトの卓越した誘いのアクションを最適化させるバランスで設計されています。ラインアイ周りの容積を削ぎ落して底面を張り出すことによる徹底した低重心ヘッドは、極めて安定したスイミングアクションと驚異的な障害物回避性能を発揮。重量級ヘッドはオリジナル・マグドラフトよりもさらに深いレンジの攻略を可能とします。</v>
       </c>
-      <c r="O210" t="str">
-        <v/>
-      </c>
-      <c r="P210" t="str">
-        <v/>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -10942,12 +9685,6 @@
       <c r="N211" t="str">
         <v>Crafted for victory in the toughest fields, the SV-3 draws inspiration from the legendary V-3, which earned its place in history as one of the pioneering baitfish-head spinnerbaits. Our “Super” V-3 spinnerbait is the embodiment of design and angling expertise, developed for top-level pros competing in the most challenging tournaments. This most recent masterpiece comes fully loaded with a number of innovative specs to earn its place in angler arsenals for years to come.</v>
       </c>
-      <c r="O211" t="str">
-        <v/>
-      </c>
-      <c r="P211" t="str">
-        <v/>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -10992,12 +9729,6 @@
       <c r="N212" t="str">
         <v>MEGABASS of America Inc.とメガバスUSAプロチームが一推しする、「オカシラ・スクリューヘッド」が米トーナメントのタフな状況をことごとく打開しています。翼形状が左右非対称に設計されたITOプロップ（ITO-Engineering製）を搭載し、デッドスローリトリーブ時やフォール時にイレギュラーな微波動とフラッシングを発生。バイトチャンスを積極的に生み出します。 また、アゴ下のウォータースルーレーンが、プロペラのスムーズな回転と適切なスイム姿勢、レンジキープ力をサポート。中層にサスペンドするニュートラルフィッシュをフィーディングモードに変えてしまう、マジカルなジグヘッドです。</v>
       </c>
-      <c r="O212" t="str">
-        <v/>
-      </c>
-      <c r="P212" t="str">
-        <v/>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -11042,12 +9773,6 @@
       <c r="N213" t="str">
         <v>フィッシュヘッドジグの決定版、「オカシラヘッド」は、シェイキング時のアクション、フォール姿勢、スイム姿勢、トラブルの回避性、フックアップ率の向上を徹底追求したファンクショナルなベイトフェイス・ジグヘッド。 正面から見てデルタ形状のヘッドは、シェイキングではパタパタとハタめくヒラウチ効果を発揮。アゴ下に設けたウォータースルーレーンは優れた直進安定性とベイトフィッシュライクなスイム姿勢を生み出します。 また、エラ内部にオフセットされて深くソフトベイトが装着できるデザインによって、様々なソフトベイトをシームレスに装着できます。沈下時は、通常のジグヘッドとは異なり、「水平姿勢」を保持したスパイラルフォールを生み出します。装着するだけでソフトベイトの性能を一段と高められる、元祖フィッシュヘッドジグです。</v>
       </c>
-      <c r="O213" t="str">
-        <v/>
-      </c>
-      <c r="P213" t="str">
-        <v/>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -11092,12 +9817,6 @@
       <c r="N214" t="str">
         <v>「オカシラヘッドHG」は、3/8oz.以上の専用設計を行ったミディアム・ヘヴィウエイテッド・ジグヘッド。求められる操作性、姿勢安定性、レンジキープ性能、障害物回避性能、フッキング性能等を高次元にまとめ上げました。低重心設計によるデルタ形状ヘッドは安定したスイム姿勢を保ち、適切な重量バランスによって操作性とレンジキープ力を高めています。また、ロングノーズフェイスがスタックを回避し、横方向に張り出したヘッド後端が根掛かりを高確率で回避。また、エラ部分はソフトベイトの接触面を隠し、深くインサートさせるオフセット形状により、様々な先端形状のソフトベイトをシームレスに装着できます。 ソフトベイトの潜在能力を一段と引き出すための、メガバス独自の高機能ジグヘッドです。</v>
       </c>
-      <c r="O214" t="str">
-        <v/>
-      </c>
-      <c r="P214" t="str">
-        <v/>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -11142,12 +9861,6 @@
       <c r="N215" t="str">
         <v>The ROBIN BLADE is a bladed created with extreme usability in mind. It was designed with the goal of achieving high straight-running stability, as well as the range-keeping ability needed to continually  adjust to the feeding range of bass. Even when the tips of weeds cling to the lure, it still transmits the sharp, ultra high-pitch vibrations right to your fingertips with certainty. In order to combine these two features into a high-level lure, Megabass designed its own unique HEXA-V plate utilizing a vertical folding process. In addition, the original hook features double worm keepers that securely hold trailer worms, along with the overwhelming strength needed to combat the power of extreme monsters. From your initial approach to the heated fight itself, this lure will make your encounters with monster bass a sure thing.</v>
       </c>
-      <c r="O215" t="str">
-        <v/>
-      </c>
-      <c r="P215" t="str">
-        <v/>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -11192,12 +9905,6 @@
       <c r="N216" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O216" t="str">
-        <v/>
-      </c>
-      <c r="P216" t="str">
-        <v/>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -11242,12 +9949,6 @@
       <c r="N217" t="str">
         <v>The UOZE SWIMMER is a new surefire concept bait proposed by Megabass. The realistic head features a nose section narrowed down to the limit, allowing it excel at slipping through obstacles such as rocks, branches, and weeds. The protrusions around the gills allow it to generate an optimal amount of water stirring, which combined with the low center of gravity design provide for stable range keeping ability. the tight blade attached to the titanium shape memory wire make wide ranged appeals through flashing and vibrations possible in areas of low visibility such as weed jungles. The flexible titanium shape memory wire does not interfere with hooking bites, and by allowing the blade to make contact with the bottom and structures before the body of the lure, the lure is prevented from diving too deep into obstacles, making delicate tracing and retrieves possible. The UOZE SWIMMER is equipped with a custom long shank wide gap hook. This foolproof design pierces through the jaws of monsters with accuracy, reliably landing them.</v>
       </c>
-      <c r="O217" t="str">
-        <v/>
-      </c>
-      <c r="P217" t="str">
-        <v/>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -11292,12 +9993,6 @@
       <c r="N218" t="str">
         <v>「マキッパFFS」は、ブランドン・パラニュークをはじめ、メガバスUSAプロスタッフの熱烈な要望から生まれた、FFS（Forward Facing Sonar）専用の「勝つための」ブレードジグです。コンパクトでスリムなMAKIPPAボディに、定評あるメガバス独自のブレードフックシステム（PAT.P）を搭載。ターゲットに見切られずにブレードバイトを積極的に絡め獲る、競技志向のフィネス・ブレードジグです。 高比重ウエイト設計により、狙いのレンジへ素早く到達。軽いトゥイッチやシェイクなどの繊細な操作に即応し、ボディ＆ブレードが放つフラッシングは、ターゲットに対してひと口サイズながらも強烈な存在感を発揮。レンジキープリトリーブと意図的なラインシェイクを組み合わせることで、低活性時でもバイトを引き出します。 リトリーブスピードを上げれば、ブレードの高速回転が逃走するベイトを想起させる鮮烈な閃光と波動を発生。FFSでは、他のルアーでは口を使わなかったターゲットがMAKIPPA FFSにリアクションバイトしてしまう、一線を画した反応がご覧いただけます。</v>
       </c>
-      <c r="O218" t="str">
-        <v/>
-      </c>
-      <c r="P218" t="str">
-        <v/>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -11342,12 +10037,6 @@
       <c r="N219" t="str">
         <v>METAL-Xは、独自の非対称フォルムとウエイトバランスによる水平フォールが、ベイトライクなナチュラルシルエットとフォールスピードを最適化。あらゆるターゲットに見切られる事なく捕食本能に火を点けます。 ボディマテリアルは軽比重の特殊合金を採用し、絶妙なフォールスピードでリアクションバイトを誘発、高確率でフッキングへ持ち込みます。 ディープエリアや低水温期はもちろん、ハイプレッシャーなタフコンディションや、リアクションでしか口を使わない状況において、他のルアーとは一線を画した釣果をもたらすシークレット・ベイトです。</v>
       </c>
-      <c r="O219" t="str">
-        <v/>
-      </c>
-      <c r="P219" t="str">
-        <v/>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -11392,12 +10081,6 @@
       <c r="N220" t="str">
         <v>X-BLAZARは、佐藤信治が提唱する新機軸テールスピンジグ。 いかなる時も安定したスイムを生み出す特殊合金製の低重心ボディに加え、専用設計のSV-BLADEがエッジの立った鋭いバイブを発生させ、激しいストロボ明滅を広角に放ちます。 ブレードの回転角を変化させるセッティングが、メリハリの効いた明滅と、手元まで確実に伝達されるエッジの立ったバイブレーションを発揮。その際に生まれる強波動は、ディープフィッシュが抗えない驚異的な集魚力とフィーディングへの覚醒を生み出します。 また、メタルルアーで発生しがちなライン絡みのトラブルやフックトラブルを軽減化。ブレードバイトを確実にフッキングに持ち込むためのセッティングも追求しました。 お目当てのレンジに素早く到達し、レンジコントロール性能に優れたX-BLAZARは、ライブシューティングにおいても卓越したパフォーマンスを発揮します。</v>
       </c>
-      <c r="O220" t="str">
-        <v/>
-      </c>
-      <c r="P220" t="str">
-        <v/>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -11442,12 +10125,6 @@
       <c r="N221" t="str">
         <v>タフフィッシュを微塵も迷わせず、果敢にバイトを引き出すフィーディングマジックスイマー「マグドラフト」をウェイテッドフックやジグヘッドなどを用いて使えるフリースタイル・ボディフォームを実現したのが、マグドラフトフリースタイルです。全米のトーナメントを席捲し続けているオリジナル・マグドラフト同様の釣獲力はお墨付き。込み合うカヴァーエリアにストレスなく、果敢なアプローチが出来る頼れる存在です。</v>
       </c>
-      <c r="O221" t="str">
-        <v/>
-      </c>
-      <c r="P221" t="str">
-        <v/>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -11492,12 +10169,6 @@
       <c r="N222" t="str">
         <v>■ Designed to draw in predators with both slow and fast retrieves. ■ Megabass' exclusive MAGHOLD SYSTEM (PAT.P) and belly slit will secure hooks in place to minimize the visual presence of unnatural treble hooks.</v>
       </c>
-      <c r="O222" t="str">
-        <v/>
-      </c>
-      <c r="P222" t="str">
-        <v/>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -11542,12 +10213,6 @@
       <c r="N223" t="str">
         <v>MAGDRAFT ハスレイバーは、「つねに動いてしまう」多くの可動セクションを持つ新次元のスイミング・マニピュレーターです。3連ボディ＆極薄ジョイントによる独自のボディシェイプは、わずかな水流でヒラヒラと艶めかしく動くライブフィンと相まって、タダ巻きだけで生命感溢れるリアルな泳ぎを披露。しなやかなアクションは、疑似生命体とでも呼ぶべき、ナチュラルベイトそのものを演出。水面直下のロングストローク・ジャークでは、本物のパニックベイトが逃げ惑うような瞬間移動的なエスケープアクションを披露。ストレートリトリーブにチェイスしつつも喰わなかったターゲットに対し、ジャークで捕食本能にスイッチを入れ、一撃でバイトに持ち込みます。 ストッピングの瞬間に発生する絶妙な揺らめき、リトリーブスピードを上げるたび引き起こされるパニックエスケープなど、単純動作を加えるだけで喰わせてしまう驚異の被捕食率が、HASU RAVERの凄いところ。 MAGHOLD(PAT.P)システムにより、フックはボディに磁着され、フックの存在をカモフラージュ。タフなターゲットに対する違和感をなくし、フレキシブルでナチュラルなアクションを披露。リザーバーのハスパターンをはじめ、落ち鮎、ウグイなど大型のベイトパターンにアジャストするHASU RAVERは、従来スイムベイトの誘いを見切ったターゲットに異次元の釣獲力をいかんなく発揮します。</v>
       </c>
-      <c r="O223" t="str">
-        <v/>
-      </c>
-      <c r="P223" t="str">
-        <v/>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -11592,12 +10257,6 @@
       <c r="N224" t="str">
         <v>MAGDRAFT AYU TWITCHER is a shallow-swimming technical swimbait that adapts its action depending on retrieve speed and rod work. Megabass' proprietary MAGHOLD(PAT.P) system magnetizes the hook to the body, camouflaging its presence and reducing interference with the bait’s movement. The AYU TWITCHER's highly responsive design provides outstanding swimming performance in fields where currents interfere, such as rivers and backwaters. In slack-water games, it enables precise contact and actively triggers the reaction bite of clever fish.</v>
       </c>
-      <c r="O224" t="str">
-        <v/>
-      </c>
-      <c r="P224" t="str">
-        <v/>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -11642,12 +10301,6 @@
       <c r="N225" t="str">
         <v>MAGDRAFT AYU TWITCHER is a shallow-swimming technical swimbait that adapts its action depending on retrieve speed and rod work. Megabass' proprietary MAGHOLD(PAT.P) system magnetizes the hook to the body, camouflaging its presence and reducing interference with the bait’s movement. The AYU TWITCHER's highly responsive design provides outstanding swimming performance in fields where currents interfere, such as rivers and backwaters. In slack-water games, it enables precise contact and actively triggers the reaction bite of clever fish.</v>
       </c>
-      <c r="O225" t="str">
-        <v/>
-      </c>
-      <c r="P225" t="str">
-        <v/>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -11692,12 +10345,6 @@
       <c r="N226" t="str">
         <v>DARK SLEEPER was developed to target fish holding to bottom structure with overwhelming realism and paddle-tail action. With a top fin designed both to camouflage its hook, and gently deflect off of structure, DARK SLEEPER is able to hold tight to cover, and move through complex structure. Low center of gravity weight setting and bottom fins keep DARK SLEEPER upright as it moves through structure, for a naturally appealing approach.</v>
       </c>
-      <c r="O226" t="str">
-        <v/>
-      </c>
-      <c r="P226" t="str">
-        <v/>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -11742,12 +10389,6 @@
       <c r="N227" t="str">
         <v>When deploying gill and crucian carp patterns, there are situations where regular swimbaits and fast-moving lures are not enough to tempt discerning predators. In such situations, the SLEEPER GILL’s unrivaled realism and enticing slow-retrieve ability conjure key bites. Featuring an adaptation of the dorsal fin weed guard pioneered by the DARK SLEEPER, the SLEEPER GILL can be sent where others fear to swim. Its jungle-crawling ability enables precision targeting of intricate laydowns, cover areas, weeds, standing timber, bottom structure, and more. Designed with a concealed top hook to trick veteran targets, the body features a hollow zone that compresses with the bite for sure hooksets. Low center of gravity design and pectoral fin balancers contribute to bottom-contact swimming stability, allowing for stealthy approaches through key structure areas.</v>
       </c>
-      <c r="O227" t="str">
-        <v/>
-      </c>
-      <c r="P227" t="str">
-        <v/>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -11792,12 +10433,6 @@
       <c r="N228" t="str">
         <v>The long-awaited, bottom-scuttling stealth craw has arrived. SLEEPER CRAW harnesses the revolutionary performance of the SLEEPER series, bringing its hidden-hook design, enticing realism, and undeniable fish-catching ability to the staid category of conventional craw imitators. Unlike traditional offerings, the SLEEPER CRAW’s weight and hook are concealed within its body. This presents a stealthy package that lulls targets into natural, long-duration bites and reduces the chances of snagging, allowing anglers to move from dock skipping to laydowns to more traditional rockpiles with confidence. Constructed with a buoyant, highly durable material with a custom scent, the SLEEPER CRAW rests in the claws-up ready position and moves with uncanny realism. With an encased weight built to navigate treacherous rock formations without the unnatural sounds of lead or tungsten contact, the CRAW is perfectly suited to bottom-contact applications. Bring it to life with light line shake, a bottom-bumping drag, or vigorous hops; regardless of your technique, SLEEPER CRAW’s unique design will deliver fresh bites.</v>
       </c>
-      <c r="O228" t="str">
-        <v/>
-      </c>
-      <c r="P228" t="str">
-        <v/>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -11842,12 +10477,6 @@
       <c r="N229" t="str">
         <v>米エリートシリーズを果敢に戦い抜くプロフェッショナルバスアングラー、木村建太の知見を具現化する、勝つためのベイト。それは、快適なフィールで使うことができ、多様なシーンに高次元でフィットする優れたエルゴノミクスを有しています。 木村建太のYAGOTは、一見すると、まるでトンボのヤゴですが、その秘めたるパフォーマンスを解き放つ時、未知のバイトを多発させる稀代のクリーチャーとなるのです。 伊東由樹の流体デザイニングから造形される特異なボディフォーミングは、優れたキャスタビリティと遊泳姿勢をもたらす機能的なボディ体積をもたらし、生命感あふれる繊細かつ緻密なレッグバイブレーションを発生。高い機能性の追求から整合された殊勝なボディは、見る角度によってはバルキーであり、スリムでもある独特なフォルムです。 放つフィッシングパフォーマンスは、まさに未知との遭遇レベル。競技に勝つためのハイスコアのバイトを果敢に誘発する、魔訶不思議なベイトです。</v>
       </c>
-      <c r="O229" t="str">
-        <v/>
-      </c>
-      <c r="P229" t="str">
-        <v/>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -11892,12 +10521,6 @@
       <c r="N230" t="str">
         <v>ボトムの誘いにとどまらず、ジグストでも果敢にビッグバイトを連発させる驚異のリアクションマジック、SLAPHOGが覚醒。 米国B.A.S.S.ツアーを戦うチャレンジングなスペシャリスト、木村建太の熱い思いと知見、幾多のリアクションバイト伝説を築き上げたディープカップビーバーの開発者、伊東由樹のハイドロデザイニングが融合。圧倒的なリアクションバイトを引き出すSLAPHOGが生まれました。</v>
       </c>
-      <c r="O230" t="str">
-        <v/>
-      </c>
-      <c r="P230" t="str">
-        <v/>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -11942,12 +10565,6 @@
       <c r="N231" t="str">
         <v>The HAZE-ST is engineered to elevate strike responses from cruising, mid-column neutral fish—exhibiting refined action across the finesse spectrum from drop shots to mid-strolling. Designed for tournament pressure zones where career-defining bites must be coaxed from pinpoint areas, the HAZE-ST empowers anglers with the full spectrum of delicate, high-precision techniques. From a natural, near-motionless stick pose, it can erupt into vivid, pulsing vibrations and subtle micro-waves that elicit strikes from the most discerning predators. Its ultra-responsive behavior eliminates dead motion and delay, enabling instantaneous lifelike movement with even the lightest input. The HAZE-ST enhances the offensive power of finesse fishing, dramatically increasing bite chances from seasoned, pressure-weary lunkers that previously refused to react. HAZE-ST is born of Japan’s long history of finesse outperformance, delivering a purebred competition model built to win.</v>
       </c>
-      <c r="O231" t="str">
-        <v/>
-      </c>
-      <c r="P231" t="str">
-        <v/>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -11992,12 +10609,6 @@
       <c r="N232" t="str">
         <v>タイニーエクスレイヤーは、その可愛いサイズに似合わず、ニュートラルなビッグフィッシュにスイッチを入れてくれる、ファイナルシークレットです。また、ダウンショットリグでは、余計なアクションを与えず、ただスローにたぐり寄せてくるだけでオートマティックに魚を引き出す、究極のデッドスティッキングベイトとして活躍。ビッグベイトで叩きぬかれたメジャーなポンドでは、タイニーエクスレイヤーは、スプーキーなビッグフィッシュを最終的に引き出してしまう強さを持っています。</v>
       </c>
-      <c r="O232" t="str">
-        <v/>
-      </c>
-      <c r="P232" t="str">
-        <v/>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -12042,12 +10653,6 @@
       <c r="N233" t="str">
         <v>HAZEDONG's elegantly tapered tail moves with an enticing, undulating motion, making wary and sluggish fish bite. An excellent choice for a drop shot or Carolina Rig dragged along the bottom, where every little bump sends tremors down the length of the tail. HAZEDONG explodes into larger-than-life movement with rod work, putting on a mesmerizing, dynamic display at the end of your line. However, unlike many straight tail worms that are incapable of subtlety, HAZEDONG can also be brought to a deadly stillness by patient anglers lying in wait for discerning trophy-class targets.</v>
       </c>
-      <c r="O233" t="str">
-        <v/>
-      </c>
-      <c r="P233" t="str">
-        <v/>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -12092,12 +10697,6 @@
       <c r="N234" t="str">
         <v>The super-thin shad tail catches the water even during dead-slow retrieves and delicate shaking, triggering targets with its natural vibrations. The slits in the belly allow the body to compress when bitten, increasing hookup rates. Adding an offset hook helps as well. Featuring layered material of different densities, the HAZEDONG SHAD is able to maintain excellent stability even when used with no sinker rigs. In addition, this layering process allows for incredibly natural two-tone color patterns.</v>
       </c>
-      <c r="O234" t="str">
-        <v/>
-      </c>
-      <c r="P234" t="str">
-        <v/>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -12142,12 +10741,6 @@
       <c r="N235" t="str">
         <v>The SPARK SHAD is designed with a keel-like underside—similar to a boat’s hull—to deliver exceptional stability and range-keeping ability, even during long retrieves. Its slim tail construction kicks into gear from a crawling retrieve, emitting alluring, sinuous waves that provide subtle appeal to coax bites from cautious predators. The addition of pectoral fins and a flat back further enhances the lure’s action, harnessing a touch of roll to add dynamism to its swim without rotating out of the ideal zone of stability. The SPARK SHAD is made for highly pressured monsters—those wary targets that have seen it all and spook easily. Its ultra-refined action mimics the behavior of neutral, unsuspecting baitfish with stunning realism. By deliberately limiting body roll beyond a controlled axis, the lure keeps the hook point aligned, greatly improving the hookup ratio during chase-and-strike scenarios. When you need to tempt the wisest predators in their home waters, SPARK SHAD delivers unmatched subtle swimming appeal.</v>
       </c>
-      <c r="O235" t="str">
-        <v/>
-      </c>
-      <c r="P235" t="str">
-        <v/>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -12192,12 +10785,6 @@
       <c r="N236" t="str">
         <v>* The photograph is a prototype.</v>
       </c>
-      <c r="O236" t="str">
-        <v/>
-      </c>
-      <c r="P236" t="str">
-        <v/>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -12242,12 +10829,6 @@
       <c r="N237" t="str">
         <v>The BOTTLE SHRIMP is a hog-type worm which imitates freshwater prawns and crayfish, one of the main types of bait used around the world. When used for Texas rigs and jig trailers, the large power arms will push through the water, demanding the attention of target fish. With bottom contact, the inertia of the weighted arms will cause a shivering action to move from the tips of the power arms through the entire body, triggering bites. For no sinker rigs, nail rigs, and Carolina rigs, the power arm will swing left and right during the fall, creating a subtle waving motion. The slow and powerful wave motion created by the power arms and the quick, vivid trembling motion created by the legs will bring about a more complicated and realistic pulse from the whole body, captivating target fish.</v>
       </c>
-      <c r="O237" t="str">
-        <v/>
-      </c>
-      <c r="P237" t="str">
-        <v/>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -12292,12 +10873,6 @@
       <c r="N238" t="str">
         <v>SLING SHADは、ミノー形態のフラットサイドシルエットと微水流にも鋭敏に反応する繊細なフォークテールを併せ持つ、ソフトスティックベイト。 腹部に高比重マテリアルを配した二層比重構造により、オフセットフックによるノーシンカーリグでも安定したスイミングと適切なフォール姿勢を保持。トゥイッチやジャークでは、ソフトジャークベイトとして艶めかしい左右へのダートアクションでターゲットを狂わせます。 低重心効果をもたらす二層比重構造は、ジグヘッド装着時のミドストで連続的なヒラウチ・ロールアクションを創出。ロールアクションと連動してテール部に微細な振動をもたらし、よりいっそうアピールを高めます。ブレードジグやワイヤーベイトのトレーラーとしても優れたパフォーマンスを発揮します。</v>
       </c>
-      <c r="O238" t="str">
-        <v/>
-      </c>
-      <c r="P238" t="str">
-        <v/>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -12342,12 +10917,6 @@
       <c r="N239" t="str">
         <v>The TK TWISTER is a super multifunction worm capable of being used in any rig. With slight twitching, the tail wriggles from side to side as it performs a darting action. With no sinkers and Texas rigs, the delicate crustacean-like vibrations generated by the two tails and the unique presence that the body projects causes monsters to lock on. Quantity: TK TWISTER / 5 pieces , TK TWISTER Jr. / 8 pieces</v>
       </c>
-      <c r="O239" t="str">
-        <v/>
-      </c>
-      <c r="P239" t="str">
-        <v/>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -12392,12 +10961,6 @@
       <c r="N240" t="str">
         <v>MEGABASS &amp; ITO ENGINEERING / OUTBARB HOOKは、従来フックに用いる鋼材のおよそ1.3倍の引張強度を実現した特殊鋼材を使用。ITO ENGINEERINGによる特殊規格の細軸設計が、従来の同軸径ルアーフック(淡水用)の強度と貫通力を遥かに凌駕する圧倒的な釣獲パフォーマンスを発揮。 特殊フッ素コートにより貫通性能を極限まで高め、いかなる角度からのショートバイトやラフアタックも即掛けする、極のオリジナル・トリプルフックです。</v>
       </c>
-      <c r="O240" t="str">
-        <v/>
-      </c>
-      <c r="P240" t="str">
-        <v/>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -12442,12 +11005,6 @@
       <c r="N241" t="str">
         <v>メガバスルアーの性能を最大限に引き出す、純正のティンセルフック。 傷んだフックの交換用やフックチューンなどにご使用いただけます。 熟練の職人が一本一本丹精込めて仕上げます。</v>
       </c>
-      <c r="O241" t="str">
-        <v/>
-      </c>
-      <c r="P241" t="str">
-        <v/>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -12492,12 +11049,6 @@
       <c r="N242" t="str">
         <v>メガバスオリジナルロングフェザーフック。 ルアーアクションの安定性を向上させ、揺らめくフェザーがフックの存在感を希薄化し、スプーキーな魚をバイトに持ち込みます。</v>
       </c>
-      <c r="O242" t="str">
-        <v/>
-      </c>
-      <c r="P242" t="str">
-        <v/>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -12542,12 +11093,6 @@
       <c r="N243" t="str">
         <v>メガバスルアーの性能を最大限に引き出す、純正のティーザーフック。 傷んだフックの交換用や毛針チューンなどにご使用いただけます。 熟練の職人が一本一本丹精込めて仕上げます。</v>
       </c>
-      <c r="O243" t="str">
-        <v/>
-      </c>
-      <c r="P243" t="str">
-        <v/>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -12592,12 +11137,6 @@
       <c r="N244" t="str">
         <v>TREBLE HOOK OUTBARB</v>
       </c>
-      <c r="O244" t="str">
-        <v/>
-      </c>
-      <c r="P244" t="str">
-        <v/>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -12642,12 +11181,6 @@
       <c r="N245" t="str">
         <v>The BUDDHA HOOK was developed to handle those subtle bites often encountered in GREATHUNTING. Thin diameter wire drives razor-point home for sure and easy hooksets. Proprietary hook bend is designed to pin native Trout securely, while the light and supple hook design keeps damage to a minimum. * The photograph is a prototype.</v>
       </c>
-      <c r="O245" t="str">
-        <v/>
-      </c>
-      <c r="P245" t="str">
-        <v/>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -12692,12 +11225,6 @@
       <c r="N246" t="str">
         <v>Megabass original wing parts kit for the customization of the i-WING135. Entice those monsters with a customized i-WING! *i-WING135 is sold separately. * The photograph is a prototype.</v>
       </c>
-      <c r="O246" t="str">
-        <v/>
-      </c>
-      <c r="P246" t="str">
-        <v/>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -12742,12 +11269,6 @@
       <c r="N247" t="str">
         <v/>
       </c>
-      <c r="O247" t="str">
-        <v/>
-      </c>
-      <c r="P247" t="str">
-        <v/>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -12792,12 +11313,6 @@
       <c r="N248" t="str">
         <v/>
       </c>
-      <c r="O248" t="str">
-        <v/>
-      </c>
-      <c r="P248" t="str">
-        <v/>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -12842,12 +11357,6 @@
       <c r="N249" t="str">
         <v/>
       </c>
-      <c r="O249" t="str">
-        <v/>
-      </c>
-      <c r="P249" t="str">
-        <v/>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -12892,12 +11401,6 @@
       <c r="N250" t="str">
         <v/>
       </c>
-      <c r="O250" t="str">
-        <v/>
-      </c>
-      <c r="P250" t="str">
-        <v/>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -12942,12 +11445,6 @@
       <c r="N251" t="str">
         <v/>
       </c>
-      <c r="O251" t="str">
-        <v/>
-      </c>
-      <c r="P251" t="str">
-        <v/>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -12992,12 +11489,6 @@
       <c r="N252" t="str">
         <v/>
       </c>
-      <c r="O252" t="str">
-        <v/>
-      </c>
-      <c r="P252" t="str">
-        <v/>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -13042,12 +11533,6 @@
       <c r="N253" t="str">
         <v/>
       </c>
-      <c r="O253" t="str">
-        <v/>
-      </c>
-      <c r="P253" t="str">
-        <v/>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -13092,12 +11577,6 @@
       <c r="N254" t="str">
         <v/>
       </c>
-      <c r="O254" t="str">
-        <v/>
-      </c>
-      <c r="P254" t="str">
-        <v/>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -13142,12 +11621,6 @@
       <c r="N255" t="str">
         <v/>
       </c>
-      <c r="O255" t="str">
-        <v/>
-      </c>
-      <c r="P255" t="str">
-        <v/>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -13192,12 +11665,6 @@
       <c r="N256" t="str">
         <v/>
       </c>
-      <c r="O256" t="str">
-        <v/>
-      </c>
-      <c r="P256" t="str">
-        <v/>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -13242,12 +11709,6 @@
       <c r="N257" t="str">
         <v/>
       </c>
-      <c r="O257" t="str">
-        <v/>
-      </c>
-      <c r="P257" t="str">
-        <v/>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -13292,12 +11753,6 @@
       <c r="N258" t="str">
         <v/>
       </c>
-      <c r="O258" t="str">
-        <v/>
-      </c>
-      <c r="P258" t="str">
-        <v/>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -13342,12 +11797,6 @@
       <c r="N259" t="str">
         <v/>
       </c>
-      <c r="O259" t="str">
-        <v/>
-      </c>
-      <c r="P259" t="str">
-        <v/>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -13392,12 +11841,6 @@
       <c r="N260" t="str">
         <v/>
       </c>
-      <c r="O260" t="str">
-        <v/>
-      </c>
-      <c r="P260" t="str">
-        <v/>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -13442,12 +11885,6 @@
       <c r="N261" t="str">
         <v/>
       </c>
-      <c r="O261" t="str">
-        <v/>
-      </c>
-      <c r="P261" t="str">
-        <v/>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -13492,12 +11929,6 @@
       <c r="N262" t="str">
         <v/>
       </c>
-      <c r="O262" t="str">
-        <v/>
-      </c>
-      <c r="P262" t="str">
-        <v/>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -13542,12 +11973,6 @@
       <c r="N263" t="str">
         <v/>
       </c>
-      <c r="O263" t="str">
-        <v/>
-      </c>
-      <c r="P263" t="str">
-        <v/>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -13592,12 +12017,6 @@
       <c r="N264" t="str">
         <v/>
       </c>
-      <c r="O264" t="str">
-        <v/>
-      </c>
-      <c r="P264" t="str">
-        <v/>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -13642,12 +12061,6 @@
       <c r="N265" t="str">
         <v/>
       </c>
-      <c r="O265" t="str">
-        <v/>
-      </c>
-      <c r="P265" t="str">
-        <v/>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -13692,12 +12105,6 @@
       <c r="N266" t="str">
         <v/>
       </c>
-      <c r="O266" t="str">
-        <v/>
-      </c>
-      <c r="P266" t="str">
-        <v/>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -13742,12 +12149,6 @@
       <c r="N267" t="str">
         <v/>
       </c>
-      <c r="O267" t="str">
-        <v/>
-      </c>
-      <c r="P267" t="str">
-        <v/>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -13792,12 +12193,6 @@
       <c r="N268" t="str">
         <v/>
       </c>
-      <c r="O268" t="str">
-        <v/>
-      </c>
-      <c r="P268" t="str">
-        <v/>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -13842,12 +12237,6 @@
       <c r="N269" t="str">
         <v/>
       </c>
-      <c r="O269" t="str">
-        <v/>
-      </c>
-      <c r="P269" t="str">
-        <v/>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -13892,12 +12281,6 @@
       <c r="N270" t="str">
         <v/>
       </c>
-      <c r="O270" t="str">
-        <v/>
-      </c>
-      <c r="P270" t="str">
-        <v/>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -13942,12 +12325,6 @@
       <c r="N271" t="str">
         <v/>
       </c>
-      <c r="O271" t="str">
-        <v/>
-      </c>
-      <c r="P271" t="str">
-        <v/>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -13992,12 +12369,6 @@
       <c r="N272" t="str">
         <v/>
       </c>
-      <c r="O272" t="str">
-        <v/>
-      </c>
-      <c r="P272" t="str">
-        <v/>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -14042,12 +12413,6 @@
       <c r="N273" t="str">
         <v/>
       </c>
-      <c r="O273" t="str">
-        <v/>
-      </c>
-      <c r="P273" t="str">
-        <v/>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -14092,12 +12457,6 @@
       <c r="N274" t="str">
         <v/>
       </c>
-      <c r="O274" t="str">
-        <v/>
-      </c>
-      <c r="P274" t="str">
-        <v/>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -14142,12 +12501,6 @@
       <c r="N275" t="str">
         <v/>
       </c>
-      <c r="O275" t="str">
-        <v/>
-      </c>
-      <c r="P275" t="str">
-        <v/>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -14192,12 +12545,6 @@
       <c r="N276" t="str">
         <v/>
       </c>
-      <c r="O276" t="str">
-        <v/>
-      </c>
-      <c r="P276" t="str">
-        <v/>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -14242,12 +12589,6 @@
       <c r="N277" t="str">
         <v/>
       </c>
-      <c r="O277" t="str">
-        <v/>
-      </c>
-      <c r="P277" t="str">
-        <v/>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -14292,12 +12633,6 @@
       <c r="N278" t="str">
         <v/>
       </c>
-      <c r="O278" t="str">
-        <v/>
-      </c>
-      <c r="P278" t="str">
-        <v/>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -14342,12 +12677,6 @@
       <c r="N279" t="str">
         <v/>
       </c>
-      <c r="O279" t="str">
-        <v/>
-      </c>
-      <c r="P279" t="str">
-        <v/>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -14392,12 +12721,6 @@
       <c r="N280" t="str">
         <v/>
       </c>
-      <c r="O280" t="str">
-        <v/>
-      </c>
-      <c r="P280" t="str">
-        <v/>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -14442,12 +12765,6 @@
       <c r="N281" t="str">
         <v/>
       </c>
-      <c r="O281" t="str">
-        <v/>
-      </c>
-      <c r="P281" t="str">
-        <v/>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -14492,12 +12809,6 @@
       <c r="N282" t="str">
         <v/>
       </c>
-      <c r="O282" t="str">
-        <v/>
-      </c>
-      <c r="P282" t="str">
-        <v/>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -14542,12 +12853,6 @@
       <c r="N283" t="str">
         <v/>
       </c>
-      <c r="O283" t="str">
-        <v/>
-      </c>
-      <c r="P283" t="str">
-        <v/>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -14592,12 +12897,6 @@
       <c r="N284" t="str">
         <v/>
       </c>
-      <c r="O284" t="str">
-        <v/>
-      </c>
-      <c r="P284" t="str">
-        <v/>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -14642,12 +12941,6 @@
       <c r="N285" t="str">
         <v/>
       </c>
-      <c r="O285" t="str">
-        <v/>
-      </c>
-      <c r="P285" t="str">
-        <v/>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -14692,12 +12985,6 @@
       <c r="N286" t="str">
         <v/>
       </c>
-      <c r="O286" t="str">
-        <v/>
-      </c>
-      <c r="P286" t="str">
-        <v/>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -14742,12 +13029,6 @@
       <c r="N287" t="str">
         <v/>
       </c>
-      <c r="O287" t="str">
-        <v/>
-      </c>
-      <c r="P287" t="str">
-        <v/>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -14792,12 +13073,6 @@
       <c r="N288" t="str">
         <v/>
       </c>
-      <c r="O288" t="str">
-        <v/>
-      </c>
-      <c r="P288" t="str">
-        <v/>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -14842,12 +13117,6 @@
       <c r="N289" t="str">
         <v/>
       </c>
-      <c r="O289" t="str">
-        <v/>
-      </c>
-      <c r="P289" t="str">
-        <v/>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -14892,12 +13161,6 @@
       <c r="N290" t="str">
         <v/>
       </c>
-      <c r="O290" t="str">
-        <v/>
-      </c>
-      <c r="P290" t="str">
-        <v/>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -14942,12 +13205,6 @@
       <c r="N291" t="str">
         <v/>
       </c>
-      <c r="O291" t="str">
-        <v/>
-      </c>
-      <c r="P291" t="str">
-        <v/>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -14992,12 +13249,6 @@
       <c r="N292" t="str">
         <v/>
       </c>
-      <c r="O292" t="str">
-        <v/>
-      </c>
-      <c r="P292" t="str">
-        <v/>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -15042,12 +13293,6 @@
       <c r="N293" t="str">
         <v/>
       </c>
-      <c r="O293" t="str">
-        <v/>
-      </c>
-      <c r="P293" t="str">
-        <v/>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -15092,12 +13337,6 @@
       <c r="N294" t="str">
         <v/>
       </c>
-      <c r="O294" t="str">
-        <v/>
-      </c>
-      <c r="P294" t="str">
-        <v/>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -15142,12 +13381,6 @@
       <c r="N295" t="str">
         <v/>
       </c>
-      <c r="O295" t="str">
-        <v/>
-      </c>
-      <c r="P295" t="str">
-        <v/>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -15192,12 +13425,6 @@
       <c r="N296" t="str">
         <v/>
       </c>
-      <c r="O296" t="str">
-        <v/>
-      </c>
-      <c r="P296" t="str">
-        <v/>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -15242,12 +13469,6 @@
       <c r="N297" t="str">
         <v/>
       </c>
-      <c r="O297" t="str">
-        <v/>
-      </c>
-      <c r="P297" t="str">
-        <v/>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -15292,12 +13513,6 @@
       <c r="N298" t="str">
         <v/>
       </c>
-      <c r="O298" t="str">
-        <v/>
-      </c>
-      <c r="P298" t="str">
-        <v/>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -15342,12 +13557,6 @@
       <c r="N299" t="str">
         <v/>
       </c>
-      <c r="O299" t="str">
-        <v/>
-      </c>
-      <c r="P299" t="str">
-        <v/>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -15392,12 +13601,6 @@
       <c r="N300" t="str">
         <v/>
       </c>
-      <c r="O300" t="str">
-        <v/>
-      </c>
-      <c r="P300" t="str">
-        <v/>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -15442,12 +13645,6 @@
       <c r="N301" t="str">
         <v/>
       </c>
-      <c r="O301" t="str">
-        <v/>
-      </c>
-      <c r="P301" t="str">
-        <v/>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -15492,12 +13689,6 @@
       <c r="N302" t="str">
         <v/>
       </c>
-      <c r="O302" t="str">
-        <v/>
-      </c>
-      <c r="P302" t="str">
-        <v/>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -15542,12 +13733,6 @@
       <c r="N303" t="str">
         <v/>
       </c>
-      <c r="O303" t="str">
-        <v/>
-      </c>
-      <c r="P303" t="str">
-        <v/>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -15592,12 +13777,6 @@
       <c r="N304" t="str">
         <v/>
       </c>
-      <c r="O304" t="str">
-        <v/>
-      </c>
-      <c r="P304" t="str">
-        <v/>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -15642,12 +13821,6 @@
       <c r="N305" t="str">
         <v/>
       </c>
-      <c r="O305" t="str">
-        <v/>
-      </c>
-      <c r="P305" t="str">
-        <v/>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -15692,12 +13865,6 @@
       <c r="N306" t="str">
         <v/>
       </c>
-      <c r="O306" t="str">
-        <v/>
-      </c>
-      <c r="P306" t="str">
-        <v/>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -15742,12 +13909,6 @@
       <c r="N307" t="str">
         <v/>
       </c>
-      <c r="O307" t="str">
-        <v/>
-      </c>
-      <c r="P307" t="str">
-        <v/>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -15792,12 +13953,6 @@
       <c r="N308" t="str">
         <v/>
       </c>
-      <c r="O308" t="str">
-        <v/>
-      </c>
-      <c r="P308" t="str">
-        <v/>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -15842,12 +13997,6 @@
       <c r="N309" t="str">
         <v/>
       </c>
-      <c r="O309" t="str">
-        <v/>
-      </c>
-      <c r="P309" t="str">
-        <v/>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -15892,12 +14041,6 @@
       <c r="N310" t="str">
         <v/>
       </c>
-      <c r="O310" t="str">
-        <v/>
-      </c>
-      <c r="P310" t="str">
-        <v/>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -15942,12 +14085,6 @@
       <c r="N311" t="str">
         <v/>
       </c>
-      <c r="O311" t="str">
-        <v/>
-      </c>
-      <c r="P311" t="str">
-        <v/>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -15992,12 +14129,6 @@
       <c r="N312" t="str">
         <v/>
       </c>
-      <c r="O312" t="str">
-        <v/>
-      </c>
-      <c r="P312" t="str">
-        <v/>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -16042,12 +14173,6 @@
       <c r="N313" t="str">
         <v/>
       </c>
-      <c r="O313" t="str">
-        <v/>
-      </c>
-      <c r="P313" t="str">
-        <v/>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -16092,12 +14217,6 @@
       <c r="N314" t="str">
         <v/>
       </c>
-      <c r="O314" t="str">
-        <v/>
-      </c>
-      <c r="P314" t="str">
-        <v/>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -16142,12 +14261,6 @@
       <c r="N315" t="str">
         <v/>
       </c>
-      <c r="O315" t="str">
-        <v/>
-      </c>
-      <c r="P315" t="str">
-        <v/>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -16192,12 +14305,6 @@
       <c r="N316" t="str">
         <v/>
       </c>
-      <c r="O316" t="str">
-        <v/>
-      </c>
-      <c r="P316" t="str">
-        <v/>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -16242,12 +14349,6 @@
       <c r="N317" t="str">
         <v/>
       </c>
-      <c r="O317" t="str">
-        <v/>
-      </c>
-      <c r="P317" t="str">
-        <v/>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -16292,12 +14393,6 @@
       <c r="N318" t="str">
         <v/>
       </c>
-      <c r="O318" t="str">
-        <v/>
-      </c>
-      <c r="P318" t="str">
-        <v/>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -16342,12 +14437,6 @@
       <c r="N319" t="str">
         <v/>
       </c>
-      <c r="O319" t="str">
-        <v/>
-      </c>
-      <c r="P319" t="str">
-        <v/>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -16392,12 +14481,6 @@
       <c r="N320" t="str">
         <v/>
       </c>
-      <c r="O320" t="str">
-        <v/>
-      </c>
-      <c r="P320" t="str">
-        <v/>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -16442,12 +14525,6 @@
       <c r="N321" t="str">
         <v/>
       </c>
-      <c r="O321" t="str">
-        <v/>
-      </c>
-      <c r="P321" t="str">
-        <v/>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -16492,12 +14569,6 @@
       <c r="N322" t="str">
         <v/>
       </c>
-      <c r="O322" t="str">
-        <v/>
-      </c>
-      <c r="P322" t="str">
-        <v/>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -16542,12 +14613,6 @@
       <c r="N323" t="str">
         <v/>
       </c>
-      <c r="O323" t="str">
-        <v/>
-      </c>
-      <c r="P323" t="str">
-        <v/>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -16592,12 +14657,6 @@
       <c r="N324" t="str">
         <v/>
       </c>
-      <c r="O324" t="str">
-        <v/>
-      </c>
-      <c r="P324" t="str">
-        <v/>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -16642,12 +14701,6 @@
       <c r="N325" t="str">
         <v/>
       </c>
-      <c r="O325" t="str">
-        <v/>
-      </c>
-      <c r="P325" t="str">
-        <v/>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -16692,12 +14745,6 @@
       <c r="N326" t="str">
         <v/>
       </c>
-      <c r="O326" t="str">
-        <v/>
-      </c>
-      <c r="P326" t="str">
-        <v/>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -16742,12 +14789,6 @@
       <c r="N327" t="str">
         <v/>
       </c>
-      <c r="O327" t="str">
-        <v/>
-      </c>
-      <c r="P327" t="str">
-        <v/>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -16792,12 +14833,6 @@
       <c r="N328" t="str">
         <v/>
       </c>
-      <c r="O328" t="str">
-        <v/>
-      </c>
-      <c r="P328" t="str">
-        <v/>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -16842,12 +14877,6 @@
       <c r="N329" t="str">
         <v/>
       </c>
-      <c r="O329" t="str">
-        <v/>
-      </c>
-      <c r="P329" t="str">
-        <v/>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -16892,12 +14921,6 @@
       <c r="N330" t="str">
         <v/>
       </c>
-      <c r="O330" t="str">
-        <v/>
-      </c>
-      <c r="P330" t="str">
-        <v/>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -16942,12 +14965,6 @@
       <c r="N331" t="str">
         <v/>
       </c>
-      <c r="O331" t="str">
-        <v/>
-      </c>
-      <c r="P331" t="str">
-        <v/>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -16992,12 +15009,6 @@
       <c r="N332" t="str">
         <v/>
       </c>
-      <c r="O332" t="str">
-        <v/>
-      </c>
-      <c r="P332" t="str">
-        <v/>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -17042,12 +15053,6 @@
       <c r="N333" t="str">
         <v/>
       </c>
-      <c r="O333" t="str">
-        <v/>
-      </c>
-      <c r="P333" t="str">
-        <v/>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -17092,12 +15097,6 @@
       <c r="N334" t="str">
         <v/>
       </c>
-      <c r="O334" t="str">
-        <v/>
-      </c>
-      <c r="P334" t="str">
-        <v/>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -17142,12 +15141,6 @@
       <c r="N335" t="str">
         <v/>
       </c>
-      <c r="O335" t="str">
-        <v/>
-      </c>
-      <c r="P335" t="str">
-        <v/>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -17192,12 +15185,6 @@
       <c r="N336" t="str">
         <v/>
       </c>
-      <c r="O336" t="str">
-        <v/>
-      </c>
-      <c r="P336" t="str">
-        <v/>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -17242,12 +15229,6 @@
       <c r="N337" t="str">
         <v/>
       </c>
-      <c r="O337" t="str">
-        <v/>
-      </c>
-      <c r="P337" t="str">
-        <v/>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -17292,12 +15273,6 @@
       <c r="N338" t="str">
         <v/>
       </c>
-      <c r="O338" t="str">
-        <v/>
-      </c>
-      <c r="P338" t="str">
-        <v/>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -17342,12 +15317,6 @@
       <c r="N339" t="str">
         <v/>
       </c>
-      <c r="O339" t="str">
-        <v/>
-      </c>
-      <c r="P339" t="str">
-        <v/>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -17392,12 +15361,6 @@
       <c r="N340" t="str">
         <v/>
       </c>
-      <c r="O340" t="str">
-        <v/>
-      </c>
-      <c r="P340" t="str">
-        <v/>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -17442,12 +15405,6 @@
       <c r="N341" t="str">
         <v/>
       </c>
-      <c r="O341" t="str">
-        <v/>
-      </c>
-      <c r="P341" t="str">
-        <v/>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -17492,12 +15449,6 @@
       <c r="N342" t="str">
         <v/>
       </c>
-      <c r="O342" t="str">
-        <v/>
-      </c>
-      <c r="P342" t="str">
-        <v/>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -17542,12 +15493,6 @@
       <c r="N343" t="str">
         <v/>
       </c>
-      <c r="O343" t="str">
-        <v/>
-      </c>
-      <c r="P343" t="str">
-        <v/>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -17592,12 +15537,6 @@
       <c r="N344" t="str">
         <v/>
       </c>
-      <c r="O344" t="str">
-        <v/>
-      </c>
-      <c r="P344" t="str">
-        <v/>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -17642,12 +15581,6 @@
       <c r="N345" t="str">
         <v/>
       </c>
-      <c r="O345" t="str">
-        <v/>
-      </c>
-      <c r="P345" t="str">
-        <v/>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -17692,12 +15625,6 @@
       <c r="N346" t="str">
         <v/>
       </c>
-      <c r="O346" t="str">
-        <v/>
-      </c>
-      <c r="P346" t="str">
-        <v/>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -17742,12 +15669,6 @@
       <c r="N347" t="str">
         <v/>
       </c>
-      <c r="O347" t="str">
-        <v/>
-      </c>
-      <c r="P347" t="str">
-        <v/>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -17792,12 +15713,6 @@
       <c r="N348" t="str">
         <v/>
       </c>
-      <c r="O348" t="str">
-        <v/>
-      </c>
-      <c r="P348" t="str">
-        <v/>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -17842,12 +15757,6 @@
       <c r="N349" t="str">
         <v/>
       </c>
-      <c r="O349" t="str">
-        <v/>
-      </c>
-      <c r="P349" t="str">
-        <v/>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -17892,12 +15801,6 @@
       <c r="N350" t="str">
         <v/>
       </c>
-      <c r="O350" t="str">
-        <v/>
-      </c>
-      <c r="P350" t="str">
-        <v/>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -17942,12 +15845,6 @@
       <c r="N351" t="str">
         <v/>
       </c>
-      <c r="O351" t="str">
-        <v/>
-      </c>
-      <c r="P351" t="str">
-        <v/>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -17992,12 +15889,6 @@
       <c r="N352" t="str">
         <v/>
       </c>
-      <c r="O352" t="str">
-        <v/>
-      </c>
-      <c r="P352" t="str">
-        <v/>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -18042,12 +15933,6 @@
       <c r="N353" t="str">
         <v/>
       </c>
-      <c r="O353" t="str">
-        <v/>
-      </c>
-      <c r="P353" t="str">
-        <v/>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -18092,12 +15977,6 @@
       <c r="N354" t="str">
         <v/>
       </c>
-      <c r="O354" t="str">
-        <v/>
-      </c>
-      <c r="P354" t="str">
-        <v/>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -18142,12 +16021,6 @@
       <c r="N355" t="str">
         <v/>
       </c>
-      <c r="O355" t="str">
-        <v/>
-      </c>
-      <c r="P355" t="str">
-        <v/>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -18192,12 +16065,6 @@
       <c r="N356" t="str">
         <v/>
       </c>
-      <c r="O356" t="str">
-        <v/>
-      </c>
-      <c r="P356" t="str">
-        <v/>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -18242,12 +16109,6 @@
       <c r="N357" t="str">
         <v/>
       </c>
-      <c r="O357" t="str">
-        <v/>
-      </c>
-      <c r="P357" t="str">
-        <v/>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -18292,12 +16153,6 @@
       <c r="N358" t="str">
         <v/>
       </c>
-      <c r="O358" t="str">
-        <v/>
-      </c>
-      <c r="P358" t="str">
-        <v/>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -18342,12 +16197,6 @@
       <c r="N359" t="str">
         <v/>
       </c>
-      <c r="O359" t="str">
-        <v/>
-      </c>
-      <c r="P359" t="str">
-        <v/>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -18392,12 +16241,6 @@
       <c r="N360" t="str">
         <v/>
       </c>
-      <c r="O360" t="str">
-        <v/>
-      </c>
-      <c r="P360" t="str">
-        <v/>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -18442,12 +16285,6 @@
       <c r="N361" t="str">
         <v/>
       </c>
-      <c r="O361" t="str">
-        <v/>
-      </c>
-      <c r="P361" t="str">
-        <v/>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -18492,12 +16329,6 @@
       <c r="N362" t="str">
         <v/>
       </c>
-      <c r="O362" t="str">
-        <v/>
-      </c>
-      <c r="P362" t="str">
-        <v/>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -18542,12 +16373,6 @@
       <c r="N363" t="str">
         <v/>
       </c>
-      <c r="O363" t="str">
-        <v/>
-      </c>
-      <c r="P363" t="str">
-        <v/>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -18595,9 +16420,6 @@
       <c r="O364" t="str">
         <v>https://keitech.co.jp/pages/613/</v>
       </c>
-      <c r="P364" t="str">
-        <v/>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -18645,9 +16467,6 @@
       <c r="O365" t="str">
         <v>https://keitech.co.jp/pages/39/</v>
       </c>
-      <c r="P365" t="str">
-        <v/>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -18695,9 +16514,6 @@
       <c r="O366" t="str">
         <v>https://keitech.co.jp/pages/57/</v>
       </c>
-      <c r="P366" t="str">
-        <v/>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -18745,9 +16561,6 @@
       <c r="O367" t="str">
         <v>https://keitech.co.jp/pages/232/</v>
       </c>
-      <c r="P367" t="str">
-        <v/>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -18795,9 +16608,6 @@
       <c r="O368" t="str">
         <v>https://keitech.co.jp/pages/608/</v>
       </c>
-      <c r="P368" t="str">
-        <v/>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -18845,9 +16655,6 @@
       <c r="O369" t="str">
         <v>https://keitech.co.jp/pages/599/</v>
       </c>
-      <c r="P369" t="str">
-        <v/>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -18895,9 +16702,6 @@
       <c r="O370" t="str">
         <v>https://keitech.co.jp/pages/582/</v>
       </c>
-      <c r="P370" t="str">
-        <v/>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -18945,9 +16749,6 @@
       <c r="O371" t="str">
         <v>https://keitech.co.jp/pages/581/</v>
       </c>
-      <c r="P371" t="str">
-        <v/>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -18995,9 +16796,6 @@
       <c r="O372" t="str">
         <v>https://keitech.co.jp/pages/551/</v>
       </c>
-      <c r="P372" t="str">
-        <v/>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -19045,9 +16843,6 @@
       <c r="O373" t="str">
         <v>https://keitech.co.jp/pages/456/</v>
       </c>
-      <c r="P373" t="str">
-        <v/>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -19095,9 +16890,6 @@
       <c r="O374" t="str">
         <v>https://keitech.co.jp/pages/549/</v>
       </c>
-      <c r="P374" t="str">
-        <v/>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -19145,9 +16937,6 @@
       <c r="O375" t="str">
         <v>https://keitech.co.jp/pages/450/</v>
       </c>
-      <c r="P375" t="str">
-        <v/>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -19195,9 +16984,6 @@
       <c r="O376" t="str">
         <v>https://keitech.co.jp/pages/423/</v>
       </c>
-      <c r="P376" t="str">
-        <v/>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -19245,9 +17031,6 @@
       <c r="O377" t="str">
         <v>https://keitech.co.jp/pages/381/</v>
       </c>
-      <c r="P377" t="str">
-        <v/>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -19295,9 +17078,6 @@
       <c r="O378" t="str">
         <v>https://keitech.co.jp/pages/158/</v>
       </c>
-      <c r="P378" t="str">
-        <v/>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -19345,9 +17125,6 @@
       <c r="O379" t="str">
         <v>https://keitech.co.jp/pages/455/</v>
       </c>
-      <c r="P379" t="str">
-        <v/>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -19395,9 +17172,6 @@
       <c r="O380" t="str">
         <v>https://keitech.co.jp/pages/35/</v>
       </c>
-      <c r="P380" t="str">
-        <v/>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -19445,9 +17219,6 @@
       <c r="O381" t="str">
         <v>https://keitech.co.jp/pages/293/</v>
       </c>
-      <c r="P381" t="str">
-        <v/>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -19495,9 +17266,6 @@
       <c r="O382" t="str">
         <v>https://keitech.co.jp/pages/276/</v>
       </c>
-      <c r="P382" t="str">
-        <v/>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -19545,9 +17313,6 @@
       <c r="O383" t="str">
         <v>https://keitech.co.jp/pages/18/</v>
       </c>
-      <c r="P383" t="str">
-        <v/>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -19595,9 +17360,6 @@
       <c r="O384" t="str">
         <v>https://keitech.co.jp/pages/660/</v>
       </c>
-      <c r="P384" t="str">
-        <v/>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -19645,9 +17407,6 @@
       <c r="O385" t="str">
         <v>https://keitech.co.jp/pages/617/</v>
       </c>
-      <c r="P385" t="str">
-        <v/>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -19695,9 +17454,6 @@
       <c r="O386" t="str">
         <v>https://keitech.co.jp/pages/554/</v>
       </c>
-      <c r="P386" t="str">
-        <v/>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -19745,9 +17501,6 @@
       <c r="O387" t="str">
         <v>https://keitech.co.jp/pages/625/</v>
       </c>
-      <c r="P387" t="str">
-        <v/>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -19795,9 +17548,6 @@
       <c r="O388" t="str">
         <v>https://keitech.co.jp/pages/575/</v>
       </c>
-      <c r="P388" t="str">
-        <v/>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -19845,9 +17595,6 @@
       <c r="O389" t="str">
         <v>https://keitech.co.jp/pages/655/</v>
       </c>
-      <c r="P389" t="str">
-        <v/>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -19895,9 +17642,6 @@
       <c r="O390" t="str">
         <v>https://keitech.co.jp/pages/576/</v>
       </c>
-      <c r="P390" t="str">
-        <v/>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
@@ -19945,9 +17689,6 @@
       <c r="O391" t="str">
         <v>https://keitech.co.jp/pages/602/</v>
       </c>
-      <c r="P391" t="str">
-        <v/>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -19995,9 +17736,6 @@
       <c r="O392" t="str">
         <v>https://keitech.co.jp/pages/603/</v>
       </c>
-      <c r="P392" t="str">
-        <v/>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -20045,9 +17783,6 @@
       <c r="O393" t="str">
         <v>https://keitech.co.jp/pages/10/</v>
       </c>
-      <c r="P393" t="str">
-        <v/>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -20095,9 +17830,6 @@
       <c r="O394" t="str">
         <v>https://keitech.co.jp/pages/206/</v>
       </c>
-      <c r="P394" t="str">
-        <v/>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -20145,9 +17877,6 @@
       <c r="O395" t="str">
         <v>https://keitech.co.jp/pages/13/</v>
       </c>
-      <c r="P395" t="str">
-        <v/>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -20195,9 +17924,6 @@
       <c r="O396" t="str">
         <v>https://keitech.co.jp/pages/14/</v>
       </c>
-      <c r="P396" t="str">
-        <v/>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
@@ -20234,10 +17960,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_senko.jpg</v>
       </c>
       <c r="L397" t="str">
-        <v>2026-04-10T10:42:44.627Z</v>
+        <v>2026-04-10T12:07:28.695Z</v>
       </c>
       <c r="M397" t="str">
-        <v>2026-04-10T10:42:44.627Z</v>
+        <v>2026-04-10T12:07:28.695Z</v>
       </c>
       <c r="N397" t="str">
         <v>It’s the gold standard by which all stick baits are judged, but fuzzy. The Fuzzy Senko from Yamamoto Baits is exactly what it sounds like. The legendary Senko is now outfitted with threaded fine skirt material to create a new profile and tantalizing secondary action. The Fuzzy Senko is available in both 4" and 5" sizes, coming 5 and 4 per pack respectively, and can be found in 8 proven colors.</v>
@@ -20278,10 +18004,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_nuki.jpg</v>
       </c>
       <c r="L398" t="str">
-        <v>2026-04-10T10:42:45.804Z</v>
+        <v>2026-04-10T12:07:30.291Z</v>
       </c>
       <c r="M398" t="str">
-        <v>2026-04-10T10:42:45.804Z</v>
+        <v>2026-04-10T12:07:30.291Z</v>
       </c>
       <c r="N398" t="str">
         <v>The Yamatanuki just got fuzzy. The ultimate “heavy plastic” bait has joined the fuzzy bait family, now threaded with strands of fine skirt material to create a totally new profile and action. Just as much as it catches your eye, it also catches fish. Available in 8 Yamamoto colors, the Fuzzy Nuki is available in both 2.5" and 3.5" sizes. Pack Size: 2.5" - 5/pack 3.5" - 4/pack</v>
@@ -20322,10 +18048,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_nut_6pk.jpg</v>
       </c>
       <c r="L399" t="str">
-        <v>2026-04-10T10:42:58.235Z</v>
+        <v>2026-04-10T12:07:31.877Z</v>
       </c>
       <c r="M399" t="str">
-        <v>2026-04-10T10:42:58.235Z</v>
+        <v>2026-04-10T12:07:31.877Z</v>
       </c>
       <c r="N399" t="str">
         <v>The Yamamoto Fuzzy Nut appears odd at first glance, but once you see it in the water and see how the fish react to it, you’ll look at it in an all-new light. The 1.5" Fuzzy Nut lives up to its name thanks to its threaded skirt material providing a very subtle secondary action. It is the perfect length to completely conceal a nail weight, while the heavyweight Yamamoto salted formula allows for the perfect fall rate. Especially killer on smallmouth and spotted bass, the Fuzzy Nut comes 6 per pack in 10 irresistible Yamamoto colors.</v>
@@ -20366,10 +18092,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_uni.jpg</v>
       </c>
       <c r="L400" t="str">
-        <v>2026-04-10T10:42:59.418Z</v>
+        <v>2026-04-10T12:07:33.479Z</v>
       </c>
       <c r="M400" t="str">
-        <v>2026-04-10T10:42:59.418Z</v>
+        <v>2026-04-10T12:07:33.479Z</v>
       </c>
       <c r="N400" t="str">
         <v>The Yamamoto Uni is designed to be irresistible to bass. A TPE urchin-style bait, the Uni features bulbed appendages that catch water and shimmy with each twitch of the rod tip, falling with a very lifelike quiver. The custom Yamamoto TPE formula allows for a flexible yet durable bait that delivers the perfect buoyancy and action, while holding up fish after fish. If you're looking for a profile and action that fish have absolutely never seen before the Uni is your ticket to triggering more bites. 1 per pack.</v>
@@ -20410,10 +18136,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_ultimate_senko_kit___100pc_assortment.jpg</v>
       </c>
       <c r="L401" t="str">
-        <v>2026-04-10T10:43:01.210Z</v>
+        <v>2026-04-10T12:07:35.206Z</v>
       </c>
       <c r="M401" t="str">
-        <v>2026-04-10T10:43:01.210Z</v>
+        <v>2026-04-10T12:07:35.206Z</v>
       </c>
       <c r="N401" t="str">
         <v>The Ultimate Senko Kit is loaded with every size of the original Senko, the 4",5", 6" and the 7". Get a Senko for every situation. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 305 - Baby Bass 10/pc 306 - Natural Shad 10/pc 194 - Watermelon With Large Black 10/pc 912 - Green Pumpkin/Watermelon 10/pc 021 - Black With Large Blue 10/pc 363 - Green Pumpkin Blue 10/pc 963 - Gooseberry Laminate 5/pc 208 - Watermelon With Black &amp; Red Flake 5/pc 318 - Green Pumpkin With Large Red 5/pc 301 - Green Pumpkin With Large Green And Large Purple 5/pc 330 - Green Pumpkin With Purple and Small Copper 5/pc 925 - Green Pumpkin With Small Red / 042J Laminate 5/pc 297 - Green Pumpkin With Large Black</v>
@@ -20454,10 +18180,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_kit___160pc_assortment.jpg</v>
       </c>
       <c r="L402" t="str">
-        <v>2026-04-10T10:43:02.450Z</v>
+        <v>2026-04-10T12:07:36.787Z</v>
       </c>
       <c r="M402" t="str">
-        <v>2026-04-10T10:43:02.450Z</v>
+        <v>2026-04-10T12:07:36.787Z</v>
       </c>
       <c r="N402" t="str">
         <v>The 5" Senko Kit is the big brother of our Senko Bundle. This Senko Kit comes loaded with 16 different bags of 5" Senkos, giving you a color for whatever conditions you find yourself in. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 213 - June Bug - Purple With Emerald Flake 10/pc 363 - Green Pumpkin Blue 10/pc 020 - Black 10/pc 355 - Green Pumpkin Magic 10/pc 297 - Green Pumpkin Pepper 10/pc 912 - Green Pumpkin/Watermelon 10/pc 305 - Baby Bass 10/pc 918 - Peanut Butter And Jelly 017/213 Laminate 10/pc 337 - Watermelon With Red 10/pc 963 - Gooseberry Laminate 10/pc 904 - Blue And Black Laminate 10/pc 952 - Bama Bug 10/pc 964 - Watermelon Slice Laminate 10/pc 356 - Plum Apple 10/pc 547 - 297/192 Tip 10/pc 306 - Natural Shad</v>
@@ -20498,10 +18224,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_baitfish_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L403" t="str">
-        <v>2026-04-10T10:43:03.622Z</v>
+        <v>2026-04-10T12:07:38.368Z</v>
       </c>
       <c r="M403" t="str">
-        <v>2026-04-10T10:43:03.622Z</v>
+        <v>2026-04-10T12:07:38.368Z</v>
       </c>
       <c r="N403" t="str">
         <v>Packed with 50 of the legendary 5” Senkos, this bundle is all about matching local forage. Each color is hand-picked to mimic common baitfish, giving you an edge when targeting bass that are keyed in on local forage. A go-to for pros and weekend anglers alike, the Senko’s unmatched action and versatility make it the top soft plastic in the game. Grab the Baitfish Bundle and be ready for any bass bite that comes your way. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 5" Senko, 305 - Baby Bass 10/pc 5" Senko, 967 - Goby 10/pc 5" Senko, 306 - Natural Shad 10/pc 5" Senko, 968 - Perch 10/pc 5" Senko, 9008 - Green Gizzard</v>
@@ -20542,10 +18268,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_green_pumpkin_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L404" t="str">
-        <v>2026-04-10T10:43:04.872Z</v>
+        <v>2026-04-10T12:07:39.977Z</v>
       </c>
       <c r="M404" t="str">
-        <v>2026-04-10T10:43:04.872Z</v>
+        <v>2026-04-10T12:07:39.977Z</v>
       </c>
       <c r="N404" t="str">
         <v>This bundle includes 50 of the legendary 5” Senkos in five proven Green Pumpkin variations—one of the most reliable and versatile color groups in bass fishing. Known for their natural appeal, Green Pumpkin tones effectively mimic a wide range of baitfish and forage, making them a must-have in any tackle box. Trusted by pros and weekend anglers alike, the Senko delivers unmatched action and consistent results. Load up with the Pumpkin Bundle and stay ready for any bass bite, anytime. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 5" Senko, 297 - Green Pumpkin with Black Flake 10/pc 5" Senko, 912 - Green Pumpkin with Watermelon 10/pc 5" Senko, 301 - #297 NF/LG Green Pumpkin 10/pc 5" Senko, 355 - Green Pumpkin Magic 10/pc 5" Senko, 925 - Green Pumpkin with red Flake/042J</v>
@@ -20586,10 +18312,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_bundle___90pc_assortment.jpg</v>
       </c>
       <c r="L405" t="str">
-        <v>2026-04-10T10:43:06.043Z</v>
+        <v>2026-04-10T12:07:41.570Z</v>
       </c>
       <c r="M405" t="str">
-        <v>2026-04-10T10:43:06.043Z</v>
+        <v>2026-04-10T12:07:41.570Z</v>
       </c>
       <c r="N405" t="str">
         <v>The original soft stick bait just got better. Stock up on Senkos from some classic colors to some new ones you may not have tried yet. This 90pc assortment will not dissappoint. *Kits are subject to change based on availability refer to chart below for the most up to date offering 1/bag 5" SENKO / 10 PACK / WATERMELON W/ CREAM LAMINATE 1/bag 5" SENKO / 10 PACK / WATERMELON W/ RED FLAKE 1/bag 5" SENKO / 10 PACK / BLACK W/ LARGE BLUE FLAKE 1/bag 5" SENKO / 10 PACK / GREEN PUMPKIN MAGIC 1/bag 5" SENKO / 10 PACK / B-BUG GRINDER 1/bag 5" SENKO / 10 PACK / BAMA BUG 1/bag 5" SENKO / 10 PACK / PRO BLUE 1/bag 5" SENKO / 10 PACK / GREEN PUMPKIN BLACK FLAKE 1/bag 5" SENKO / 10 PACK / JUNE BUG PURPLE W/ EMERALD FLAKE</v>
@@ -20630,10 +18356,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fat_senko_10pk.jpg</v>
       </c>
       <c r="L406" t="str">
-        <v>2026-04-10T10:43:07.273Z</v>
+        <v>2026-04-10T12:07:43.176Z</v>
       </c>
       <c r="M406" t="str">
-        <v>2026-04-10T10:43:07.273Z</v>
+        <v>2026-04-10T12:07:43.176Z</v>
       </c>
       <c r="N406" t="str">
         <v>Rounding out Yamamoto’s extensive line-up of soft plastics, the Yamamoto Fat Senko provides an incredibly versatile, slightly chunkier profile that will have your livewell overflowing. Similar to the traditional Senko, the Yamamoto Fat Senko features a plumped-up stickbait construction that imparts time-tested, subtle Senko action. Incredibly effective weightless, on a shakey head, neko rig, and much more, the Yamamoto Fat Senko delivers a slightly different look that can be the key to unlocking the bite. More thickness also means increased angler visibility on sonar screens with forward-facing sonar techniques, the Fat Senko also improves success when fishing in windy conditions compared to the original due to its increased weight. Available in Yamamoto’s proven Senko color schemes, the Yamamoto Fat Senko continues to deliver the same bass-catching performance that anglers trust with additional features to help you catch more fish. 10 per pack</v>
@@ -20674,10 +18400,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_swimming_senko.jpg</v>
       </c>
       <c r="L407" t="str">
-        <v>2026-04-10T10:43:08.495Z</v>
+        <v>2026-04-10T12:07:44.352Z</v>
       </c>
       <c r="M407" t="str">
-        <v>2026-04-10T10:43:08.495Z</v>
+        <v>2026-04-10T12:07:44.352Z</v>
       </c>
       <c r="N407" t="str">
         <v>A twist on a classic - the Swimming Senko is everything that's great about the legendary Senko, but with a little extra magic. Thanks to the tail, the Swimming Senko presents a hard-to-resist horizontal action that's more than enough to tempt a lunker to bite. The Swimming Senko marries the natural profile and subtleness of the Senko with the vibration and movement of a paddletail swimbait. The result is the perfect amount of subtle shimmy, and the perfect amount of kick. Available in 4 sizes ranging from 3.5" to 5.5" long, the Swimming Senko is a favorite of anglers everywhere. 3.5"- 7 Pack 4"- 10 Pack 5"- 10 Pack 5.5"- 7 Pack</v>
@@ -20718,10 +18444,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_bulk_packs.jpg</v>
       </c>
       <c r="L408" t="str">
-        <v>2026-04-10T10:43:09.676Z</v>
+        <v>2026-04-10T12:07:46.362Z</v>
       </c>
       <c r="M408" t="str">
-        <v>2026-04-10T10:43:09.676Z</v>
+        <v>2026-04-10T12:07:46.362Z</v>
       </c>
       <c r="N408" t="str">
         <v>The 5" Senko and 4" Senko are staples in the fishing world, and it's now available in our most popular colors in bulk packs of 50 or 100! The original soft-plastic stickbait is the #1 choice of anglers everywhere. "Iconic" is an understatement - the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
@@ -20762,10 +18488,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_megastrike_fish_attractant.jpg</v>
       </c>
       <c r="L409" t="str">
-        <v>2026-04-10T10:43:10.851Z</v>
+        <v>2026-04-10T12:07:47.963Z</v>
       </c>
       <c r="M409" t="str">
-        <v>2026-04-10T10:43:10.851Z</v>
+        <v>2026-04-10T12:07:47.963Z</v>
       </c>
       <c r="N409" t="str">
         <v>The MegaStrike Fish Attractant is comprised of the proper balance of Amino Acids and Proteins to make the fish strike, hold onto, and consume the product Extra long-lasting gel No mess tube Tube Size: 1 oz</v>
@@ -20806,10 +18532,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_7__speed_senko_7pk.jpg</v>
       </c>
       <c r="L410" t="str">
-        <v>2026-04-10T10:43:12.066Z</v>
+        <v>2026-04-10T12:07:49.627Z</v>
       </c>
       <c r="M410" t="str">
-        <v>2026-04-10T10:43:12.066Z</v>
+        <v>2026-04-10T12:07:49.627Z</v>
       </c>
       <c r="N410" t="str">
         <v>The Speed Senko is sure to be your new favorite worm for covering water. Designed at the request of our pro’s, the Speed Senko is the ultimate worm for fishing grass and brush. Its thumping tail feels like a Colorado coming through the water and makes it easy for bass to zero in on it in grass, laydowns, brushpiles or any other cover. Try Texas rigging it with a light weight and swimming it over grass.. Or Texas rigged with a lift and drop retrieve in and around cover. This is one the fish will find, so you better find you some too! 7 per pack</v>
@@ -20850,10 +18576,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3__ned_senko_10pk.jpg</v>
       </c>
       <c r="L411" t="str">
-        <v>2026-04-10T10:43:13.291Z</v>
+        <v>2026-04-10T12:07:51.218Z</v>
       </c>
       <c r="M411" t="str">
-        <v>2026-04-10T10:43:13.291Z</v>
+        <v>2026-04-10T12:07:51.218Z</v>
       </c>
       <c r="N411" t="str">
         <v>The exact same shape as the 3” fat Senko but built utilizing our “Mega Floater Formula” to make this bait stand up on a Ned head. The size is perfect. The shape is perfect and now the formula is perfect for Ned rigging. While the Original Senko formula is hands down the best for a lot of applications, it isn’t for Ned rigging. We designed this bait to have the same feel and texture of the time-tested Senko, but it floats making it stand up and be more visible when dancing around the bottom of your favorite fishing hole. The Yamamoto Ned Senko is available in 21 different fish catching colors. 10 Per Pack</v>
@@ -20894,10 +18620,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3__slim_senko_10pk.jpg</v>
       </c>
       <c r="L412" t="str">
-        <v>2026-04-10T10:43:14.466Z</v>
+        <v>2026-04-10T12:07:52.823Z</v>
       </c>
       <c r="M412" t="str">
-        <v>2026-04-10T10:43:14.466Z</v>
+        <v>2026-04-10T12:07:52.823Z</v>
       </c>
       <c r="N412" t="str">
         <v>The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko. 10 per pack</v>
@@ -20938,10 +18664,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__pro_senko_10pk.jpg</v>
       </c>
       <c r="L413" t="str">
-        <v>2026-04-10T10:43:15.636Z</v>
+        <v>2026-04-10T12:07:54.419Z</v>
       </c>
       <c r="M413" t="str">
-        <v>2026-04-10T10:43:15.636Z</v>
+        <v>2026-04-10T12:07:54.419Z</v>
       </c>
       <c r="N413" t="str">
         <v>The Yamamoto 5” Pro Senko Soft Bait tweaks the design of the world-famous Senko worm to provide anglers with a new way to fish this popular lure. The thinner construction and tapered tail give it a unique shaky worm action, while the redesigned head makes it easier to rig on shaky jigs or with a screw-in bullet sinker. Its versatility offers a great way to draw out the bigger fish from deeper water.</v>
@@ -20982,10 +18708,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__thin_senko_10pk.jpg</v>
       </c>
       <c r="L414" t="str">
-        <v>2026-04-10T10:43:16.934Z</v>
+        <v>2026-04-10T12:07:56.074Z</v>
       </c>
       <c r="M414" t="str">
-        <v>2026-04-10T10:43:16.934Z</v>
+        <v>2026-04-10T12:07:56.074Z</v>
       </c>
       <c r="N414" t="str">
         <v>Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
@@ -21026,10 +18752,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_7__senko_5pk.jpg</v>
       </c>
       <c r="L415" t="str">
-        <v>2026-04-10T10:43:18.214Z</v>
+        <v>2026-04-10T12:07:57.660Z</v>
       </c>
       <c r="M415" t="str">
-        <v>2026-04-10T10:43:18.214Z</v>
+        <v>2026-04-10T12:07:57.660Z</v>
       </c>
       <c r="N415" t="str">
         <v>The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
@@ -21070,10 +18796,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_6__senko_5pk.jpg</v>
       </c>
       <c r="L416" t="str">
-        <v>2026-04-10T10:43:19.631Z</v>
+        <v>2026-04-10T12:07:59.256Z</v>
       </c>
       <c r="M416" t="str">
-        <v>2026-04-10T10:43:19.631Z</v>
+        <v>2026-04-10T12:07:59.256Z</v>
       </c>
       <c r="N416" t="str">
         <v>New 2025 Colors: 9025 - Sungill, 424 - Redbug, 425 - OG Junebug, &amp; 991 - 021/297 Green Pumpkin/Black Blue Laminate The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
@@ -21114,10 +18840,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__senko_10pk.jpg</v>
       </c>
       <c r="L417" t="str">
-        <v>2026-04-10T10:43:21.844Z</v>
+        <v>2026-04-10T12:08:00.867Z</v>
       </c>
       <c r="M417" t="str">
-        <v>2026-04-10T10:43:21.844Z</v>
+        <v>2026-04-10T12:08:00.867Z</v>
       </c>
       <c r="N417" t="str">
         <v>New 2025 Colors: 433 - Glowstick, 9025 - Sungill, 424 - Redbug, 425 - OG Junebug, &amp; 991 - 021/297 Green Pumpkin/Black Blue Laminate. The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko.</v>
@@ -21158,10 +18884,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_10pk.jpg</v>
       </c>
       <c r="L418" t="str">
-        <v>2026-04-10T10:43:23.253Z</v>
+        <v>2026-04-10T12:08:02.489Z</v>
       </c>
       <c r="M418" t="str">
-        <v>2026-04-10T10:43:23.253Z</v>
+        <v>2026-04-10T12:08:02.489Z</v>
       </c>
       <c r="N418" t="str">
         <v>New 2025 Colors: 433 - Glowstick, 9025 - Sungill, 424 - Redbug, 425 - OG Junebug, &amp; 991 - 021/297 Green Pumpkin/Black Blue Laminate The Senko is a staple in the fishing world. The original soft-plastic stickbait comes in sizes ranging from 3 inches up to 7, and it has become the #1 choice of anglers everywhere. “Iconic” is an understatement – the Senko has spawned thousands of imposters, but nothing beats the original. Versatility is a key attribute of the Senko, allowing it to be fished in a multitude of ways that all end up putting more fish in the boat. The only wrong way to fish a Senko is to not fish with the original Senko. 10 per pack</v>
@@ -21202,10 +18928,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fat_shad_shape_worm_8pk.jpg</v>
       </c>
       <c r="L419" t="str">
-        <v>2026-04-10T10:43:24.763Z</v>
+        <v>2026-04-10T12:08:05.100Z</v>
       </c>
       <c r="M419" t="str">
-        <v>2026-04-10T10:43:24.763Z</v>
+        <v>2026-04-10T12:08:05.100Z</v>
       </c>
       <c r="N419" t="str">
         <v>The new 4" Fat Shad Shape Worm is a larger offering of a Yamamoto staple. Still featuring the same proven Shad Shape Worm design, the 4" version provides a fatter body construction that makes it perfect for drop shotting, on a jighead or as a scrounger trailer. Its profile and action make it more visible for more bites. Coming 8 per pack, the 4" Fat Shad Shape Worm is available in 12 awesome Yamamoto colors.</v>
@@ -21246,10 +18972,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_worm_10pk.jpg</v>
       </c>
       <c r="L420" t="str">
-        <v>2026-04-10T10:43:26.035Z</v>
+        <v>2026-04-10T12:08:06.723Z</v>
       </c>
       <c r="M420" t="str">
-        <v>2026-04-10T10:43:26.035Z</v>
+        <v>2026-04-10T12:08:06.723Z</v>
       </c>
       <c r="N420" t="str">
         <v>New 2025 Color: 3.75" | 433 - Glowstick The Yamamoto Shad Shape Worm gives anglers yet another reason to fish Yamamoto Baits. Combining the elements of a ribbed Senko and a tiny shad-like bait, these finesse worms are an ideal choice for drop shotting and darter heading, as well as, a range of other applications. Popular in Japan prior to their release in North America, the Yamamoto Shad Shape Worms offer a killer bait fish presentation that won't overpower the situation if the fish get finicky. The Shad Shapped worm comes in a 3" and 3.75" model and 10 per bag.</v>
@@ -21290,10 +19016,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_kut_tail_worm.jpg</v>
       </c>
       <c r="L421" t="str">
-        <v>2026-04-10T10:43:27.289Z</v>
+        <v>2026-04-10T12:08:08.358Z</v>
       </c>
       <c r="M421" t="str">
-        <v>2026-04-10T10:43:27.289Z</v>
+        <v>2026-04-10T12:08:08.358Z</v>
       </c>
       <c r="N421" t="str">
         <v>The Kut Tail Worm is a great plastic to rig if you want to simplify finesse fishing. Its unique tail provides a subtle action that pairs well with the slender design. This combination is incredibly hard for even the most finnicky of fish to resist. Available in a wide range of sizes ranging from 4" all the way to 7.75", the Kut Tail is an excellent choice for drop-shotting or any other finesse style. Pack Size: 4" - 20pk 5" - 10pk 7.75" - 5pk</v>
@@ -21334,10 +19060,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_6_5__sensei_worm_10pk.jpg</v>
       </c>
       <c r="L422" t="str">
-        <v>2026-04-10T10:43:28.557Z</v>
+        <v>2026-04-10T12:08:09.950Z</v>
       </c>
       <c r="M422" t="str">
-        <v>2026-04-10T10:43:28.557Z</v>
+        <v>2026-04-10T12:08:09.950Z</v>
       </c>
       <c r="N422" t="str">
         <v>From the creators of the most successful soft plastic worm of all time comes the ultimate bait for finesse fishing applications. The all-new Sensei worm from Yamamoto Baits is a straight tail finesse worm measuring 6.5” in length. The Sensei worm features a custom-tailored soft plastic formula that leaves the worm neutrally buoyant in the water. This allows for an incredibly lifelike presentation when rigged on a drop shot, a neko rig, or your preferred rigging method of choice. The balance between the head of the worm and the subtle bulb of the tail allows the Sensei worm to have a wide, but slow shimmy when rigged weightless on a wacky rig. Whether you choose to fish it weightless in the shallows or on a shaky head out deep the Sensei worm is sure to be any anglers preferred tool when looking to outwit wily bass. Available in 12 fish catching colors. 10 Per pack</v>
@@ -21378,10 +19104,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_oki_worm_6pk.jpg</v>
       </c>
       <c r="L423" t="str">
-        <v>2026-04-10T10:43:29.786Z</v>
+        <v>2026-04-10T12:08:11.764Z</v>
       </c>
       <c r="M423" t="str">
-        <v>2026-04-10T10:43:29.786Z</v>
+        <v>2026-04-10T12:08:11.764Z</v>
       </c>
       <c r="N423" t="str">
         <v>New 2025 Colors: 425 - OG Junebug &amp; 424 - Redbug Due to the overwhelming requests from our professional anglers as well as our dedicated Yamamoto customers, we are very excited to introduce the brand-new Oki worm. “Oki” means long sword in Japanese, and that is exactly what this worm will remind you of – a long weapon used to put more bass in your boat. The 10” Oki is a straight-tail worm that is formulated using our popular Mega Floater Formula, which ensures that the Oki will float vertically and be more visible as well as have more action when presented on a standup jig head. 6 Per Pack</v>
@@ -21422,10 +19148,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_ichi_worm_6pk.jpg</v>
       </c>
       <c r="L424" t="str">
-        <v>2026-04-10T10:43:31.016Z</v>
+        <v>2026-04-10T12:08:13.380Z</v>
       </c>
       <c r="M424" t="str">
-        <v>2026-04-10T10:43:31.016Z</v>
+        <v>2026-04-10T12:08:13.380Z</v>
       </c>
       <c r="N424" t="str">
         <v>New 2025 Colors: 424 - Redbug &amp; 425 - OG Junebug As with most things, all big worms are not created equally. Oftentimes, the details hidden in the design and formula are the true difference maker. In the case of the all-new Ichi Worm, the design paired with the formula sets this big worm apart from its competitors. By utilizing the ribbed body much akin to our popular Slinko, the Ichi Worm offers a bulky profile that displaces water and releases bubbles. Despite the bulk, this design doesn’t hinder hookups as it allows for maximum hook penetration. The combination of the ribbon tail, bulky ringed body, &amp; our Mega Floater Formula ensures that the Ichi stands up and moves with ease, even with the slowest movement or lightest weights. Available in 16 colors, the 10” Ichi worm has incredible action and appeals to the quality of bass that you tell stories about for years to come. 6 Per pack</v>
@@ -21466,10 +19192,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_slinko_floater.jpg</v>
       </c>
       <c r="L425" t="str">
-        <v>2026-04-10T10:43:33.489Z</v>
+        <v>2026-04-10T12:08:16.099Z</v>
       </c>
       <c r="M425" t="str">
-        <v>2026-04-10T10:43:33.489Z</v>
+        <v>2026-04-10T12:08:16.099Z</v>
       </c>
       <c r="N425" t="str">
         <v>The 3.25" Slinko from Yamamoto is a bite-sized version of the original 5.5" Slinko. Built using the same Mega Floater Formula that makes its bigger predecessor so unique, the 3.25" Slinko produces in multiples applications, ranging from Ned rigs to Carolina rigs. The 3.25" Slinko is available in 10 winning colors and comes 8 per pack. The 5.5” Slinko is unlike anything in our product line. First, the ribbed shape body allows for bulk while maintaining the classic Senko profile. The ribs not only make for great hooksets, they put off bubbles to give a more lifelike presentation. The most important aspect of the Slinko is its construction from our new Mega Floater Formula. It stands up on a jighead, dances vertically on Neko rig, and floats on a Carolina Rig. Although new, it has the unmatched action that you would expect to get only from Yamamoto Baits! 7 Pack</v>
@@ -21510,10 +19236,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__shad_shape_floater_8pk.jpg</v>
       </c>
       <c r="L426" t="str">
-        <v>2026-04-10T10:43:34.738Z</v>
+        <v>2026-04-10T12:08:17.693Z</v>
       </c>
       <c r="M426" t="str">
-        <v>2026-04-10T10:43:34.738Z</v>
+        <v>2026-04-10T12:08:17.693Z</v>
       </c>
       <c r="N426" t="str">
         <v>Utilizing the shape of the Shad Shape Worm, but pairing with our new “Mega Floater Formula”, we are really excited about the new 5” Shad Shape Worm! This new version floats, which makes it absolute MONEY on a drop shot when you want a bigger profile bait. It is also incredible on a scrounger head! The profile and action make it an awesome baitfish imitator that will fool fish no matter how clear the water or how you rig it.. Largemouth, Smallmouth and Spots will all be suckers for the 5” Shad Shape floater! 8 Per Bag</v>
@@ -21554,10 +19280,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_5__shinobi_grub_8pk.jpg</v>
       </c>
       <c r="L427" t="str">
-        <v>2026-04-10T10:43:36.238Z</v>
+        <v>2026-04-10T12:08:20.341Z</v>
       </c>
       <c r="M427" t="str">
-        <v>2026-04-10T10:43:36.238Z</v>
+        <v>2026-04-10T12:08:20.341Z</v>
       </c>
       <c r="N427" t="str">
         <v>The new Yamamoto Shinobi Grub is an all-around tool for serious anglers. The 3.5" double tail kicking grub catches fish on a variety of different rigs. The Shinobi can be used as a trailer on a jig, chatterbait, buzzbait, or spinnerbait. It is also deadly rigged independently such as on a Texas rig, jig head, swing head or Carolina Rig. Available in 8 proven Yamamoto colors, the Shinobi comes 8 per pack. The only wrong way to fish it is not to fish it.</v>
@@ -21598,10 +19324,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hula_grub_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L428" t="str">
-        <v>2026-04-10T10:43:37.464Z</v>
+        <v>2026-04-10T12:08:21.926Z</v>
       </c>
       <c r="M428" t="str">
-        <v>2026-04-10T10:43:37.464Z</v>
+        <v>2026-04-10T12:08:21.926Z</v>
       </c>
       <c r="N428" t="str">
         <v>Packed with five bags of 5” Double Tail Hula Grubs, this grab bag delivers the ultimate in offshore soft plastic versatility. A go-to bait for decades, the Hula Grub is known for its unique design that hugs the bottom while producing irresistible action. Whether you’re fishing ledges, points, or rock piles, this bundle gives you 50 chances to hook into something big. *Kits are subject to change based on availability refer to chart below for the most up to date offering 10/pc 5" Double Tail Hula Grub - 021 Black with Large Blue Flake 10/pc 5" Double Tail Hula Grub - 297 Green Pumpkin with Large Black Flake 10/pc 5" Double Tail Hula Grub - 9003 Fire Craw 10/pc 5" Double Tail Hula Grub - 301 Green Pumpkin with Large Green &amp; Purple Flake 10/pc 5" Double Tail Hula Grub - 208 Watermelon with Black &amp; Red Flake</v>
@@ -21642,10 +19368,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yamatanuki.jpg</v>
       </c>
       <c r="L429" t="str">
-        <v>2026-04-10T10:43:38.701Z</v>
+        <v>2026-04-10T12:08:23.545Z</v>
       </c>
       <c r="M429" t="str">
-        <v>2026-04-10T10:43:38.701Z</v>
+        <v>2026-04-10T12:08:23.545Z</v>
       </c>
       <c r="N429" t="str">
         <v>New 2025 Color: 2.5" | 433 - Glowstick The Yamatanuki, a popular Japanese Yamamoto bait now available in the US, revolutionized the "heavy" soft plastic lure trend. The Yamatanuki features a custom formula for weightless fishing, offering excellent casting distance and fast fall. Perfect for flipping, casting, and dragging, it's also effective with forward-facing sonar. Available in 8 pro-chosen colors, it’s a versatile addition to any angler's toolkit. Offered in 3 sizes: 4.25" (6 pack), 3.5" (8 pack), and 2.5" (10 pack).</v>
@@ -21686,10 +19412,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_double_tail_hula_grub_10pk.jpg</v>
       </c>
       <c r="L430" t="str">
-        <v>2026-04-10T10:43:39.969Z</v>
+        <v>2026-04-10T12:08:25.185Z</v>
       </c>
       <c r="M430" t="str">
-        <v>2026-04-10T10:43:39.969Z</v>
+        <v>2026-04-10T12:08:25.185Z</v>
       </c>
       <c r="N430" t="str">
         <v>It is impossible to talk about Yamamoto baits without talking about the Hula Grub. The bait that started it all for us. The Hula Grub is a golden standard for offshore fishing with a soft plastic bait. Thanks to its unique shape, this plastic stays on the bottom while providing a ton of action. Available in 2.5", 4", and 5" offerings and comes 10 per pack the Hula Grub is a timeless classic that will always have a place in an experienced angler's tacklebox.</v>
@@ -21730,10 +19456,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_double_tail_grub_20pk.jpg</v>
       </c>
       <c r="L431" t="str">
-        <v>2026-04-10T10:43:41.219Z</v>
+        <v>2026-04-10T12:08:26.800Z</v>
       </c>
       <c r="M431" t="str">
-        <v>2026-04-10T10:43:41.219Z</v>
+        <v>2026-04-10T12:08:26.800Z</v>
       </c>
       <c r="N431" t="str">
         <v>The Double Tail Grub knows how to make a splash. Available in both 4" and 5" and come 20 per pack, the Double Tail Grub offers a simple, timeless profile that that bass seem to lock in on. The Double Tail Grub excels as a jig trailer where it's shape and size appeal to crawfish eaters.</v>
@@ -21774,10 +19500,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_single_tail_grub_20pk.jpg</v>
       </c>
       <c r="L432" t="str">
-        <v>2026-04-10T10:43:42.456Z</v>
+        <v>2026-04-10T12:08:28.409Z</v>
       </c>
       <c r="M432" t="str">
-        <v>2026-04-10T10:43:42.456Z</v>
+        <v>2026-04-10T12:08:28.409Z</v>
       </c>
       <c r="N432" t="str">
         <v>The Single Tail Grub is a Yamamoto staple. Available in 4" and 5", the Single Tail Grub covers the gamut of potential applications. Whether you fish it alone or as a trailer, this plastic has a proven record of success. Smaller sizes provide the subtleness that finnicky fish desire, while the larger sizes can really beef up a presentation when the time is right. A versatile angler is a good angler, and nothing is more versatile than the Single Tail Grub. 20 Per Pack</v>
@@ -21818,10 +19544,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yama_bug_6pk.jpg</v>
       </c>
       <c r="L433" t="str">
-        <v>2026-04-10T10:43:46.069Z</v>
+        <v>2026-04-10T12:08:32.124Z</v>
       </c>
       <c r="M433" t="str">
-        <v>2026-04-10T10:43:46.069Z</v>
+        <v>2026-04-10T12:08:32.124Z</v>
       </c>
       <c r="N433" t="str">
         <v>The Yama Bug from Yamamoto was built due to demand from our pros and incorporates their input into what would make the ultimate creature bait. The Yama Bug is perfect for flipping and pitching, but it can get the job done as a jig trailer and in other scenarios as well. The Yama Bug’s reverse facing legs provide a quivering action that drives bass crazy, and its custom Yamamoto plastic formula provides the rest of the magic. Coming 6 per clamshell pack, the Yama Bug is available in 10 fish-catching colors.</v>
@@ -21862,10 +19588,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yamacraw.jpg</v>
       </c>
       <c r="L434" t="str">
-        <v>2026-04-10T10:43:49.506Z</v>
+        <v>2026-04-10T12:08:34.872Z</v>
       </c>
       <c r="M434" t="str">
-        <v>2026-04-10T10:43:49.506Z</v>
+        <v>2026-04-10T12:08:34.872Z</v>
       </c>
       <c r="N434" t="str">
         <v>Released in December 2022, the Yama Craw quickly became a favorite for its incredible action and Mega Floater Formula. This bait maintains the perfect balance of body thickness to prevent splitting on jig keepers, while still accommodating a Texas rig and larger hooks. The action is unmatched for its size, and the Yamamoto quality remains top-notch. Available in 19 colors, the 3" Yama Craw comes in 8 packs and the 4" comes in 6 packs.</v>
@@ -21906,10 +19632,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_flappin__hog.jpg</v>
       </c>
       <c r="L435" t="str">
-        <v>2026-04-10T10:43:51.759Z</v>
+        <v>2026-04-10T12:08:36.459Z</v>
       </c>
       <c r="M435" t="str">
-        <v>2026-04-10T10:43:51.759Z</v>
+        <v>2026-04-10T12:08:36.459Z</v>
       </c>
       <c r="N435" t="str">
         <v>New 2025 Color: 991 - 021/297 Green Pumpkin/Black Blue Laminate The Flappin' Hog was built for pigs. As versatile as a bait can be, the Flappin Hog is a like a Swiss Army knife in your tackle box. Texas Rig it. Carolina Rig it. Use it as a jig trailer. No matter how you rig it, the bulky body and 3 different types of appendages will put off vibes that bass can't resist. Available in both a 3.75" size as well as 4.5", the Flappin' Hog will bring home the bacon. 3.75" - 7 Per pack 4.5" - 5 Per pack</v>
@@ -21950,10 +19676,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_sanshouo_6pk.jpg</v>
       </c>
       <c r="L436" t="str">
-        <v>2026-04-10T10:43:53.894Z</v>
+        <v>2026-04-10T12:08:38.058Z</v>
       </c>
       <c r="M436" t="str">
-        <v>2026-04-10T10:43:53.894Z</v>
+        <v>2026-04-10T12:08:38.058Z</v>
       </c>
       <c r="N436" t="str">
         <v>Due to popular demand from anglers across the country, the Sanshouo is back and ready to be rigged on your favorite texas rig, jig or carolina rig. Fashioned to resemble a waterdog, sculpin, goby, or a bluegill, the Sanshouo has a distinct profile that fish don’t see all of the time. Its unique shape allows it to work equally whether you are on Lake Erie fishing for trophy smallmouth, at Okeechobee punching heavy mats, or sight fishing and flipping in California. The Sanshouo’s wide, flat tail allows it to glide back-and-forth with each twitch of the rod tip, creating a bait that triggers strikes whether fished deep or shallow. If you are looking for a go-to creature bait that fish have rarely seen, be sure to grab a bag of Sanshouos while they last! 6 Per pack</v>
@@ -21994,10 +19720,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_2_5__covert_craw_floater_10pk.jpg</v>
       </c>
       <c r="L437" t="str">
-        <v>2026-04-10T10:43:56.086Z</v>
+        <v>2026-04-10T12:08:39.675Z</v>
       </c>
       <c r="M437" t="str">
-        <v>2026-04-10T10:43:56.086Z</v>
+        <v>2026-04-10T12:08:39.675Z</v>
       </c>
       <c r="N437" t="str">
         <v>The Yamamoto Covert Craw is just as sneaky as it sounds. Based on a popular Japanese design, the 2.5'' Covert Craw can be used on a Ned rig or as a jig trailer. Its Mega Floater Formula gives it both versatility and appeal, the buoyant claws are complimented by 6 lifelike legs. Available in 8 proven colors and 10 per pack, the Covert Craw is sure to be your new favorite finesse craw offering.</v>
@@ -22038,10 +19764,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_5__nuki_bug_6pk.jpg</v>
       </c>
       <c r="L438" t="str">
-        <v>2026-04-10T10:43:57.923Z</v>
+        <v>2026-04-10T12:08:41.277Z</v>
       </c>
       <c r="M438" t="str">
-        <v>2026-04-10T10:43:57.923Z</v>
+        <v>2026-04-10T12:08:41.277Z</v>
       </c>
       <c r="N438" t="str">
         <v>The Yamatanuki just got a little bugged out. Yamamoto’s Nuki Bug is everything anglers love about the Yamatanuki, but with the addition of 2 flanged claws and 6 legs. The 3.5’’ Nuki Bug falls like the original but has a subtle swimming action, even when rigged weightless on an EWG Hook. Available in 8 gorgeous colors with 6 per pack.</v>
@@ -22082,10 +19808,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_75__cowboy_7pk.jpg</v>
       </c>
       <c r="L439" t="str">
-        <v>2026-04-10T10:44:01.827Z</v>
+        <v>2026-04-10T12:08:44.036Z</v>
       </c>
       <c r="M439" t="str">
-        <v>2026-04-10T10:44:01.827Z</v>
+        <v>2026-04-10T12:08:44.036Z</v>
       </c>
       <c r="N439" t="str">
         <v>This Cowboy is well-armed. This creature bait pairs the bulky body of the 4.5” Flappin’ Hawg and the swimming tail kick of the iconic DT Grub to create a well-rounded plastic that shines in any scenario. If you need to be shallow, the Cowboy excels as a stand-alone Texas Rig as well as on the back of a jig. Conversely, the Cowboy will do just as much damage out away from the bank as part of a Carolina Rig or on a wobble-head jig. Bulky and loud, the Cowboy is ready for a showdown with big bass! 7 Per Pack</v>
@@ -22126,10 +19852,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_psychodad_5pk.jpg</v>
       </c>
       <c r="L440" t="str">
-        <v>2026-04-10T10:44:04.914Z</v>
+        <v>2026-04-10T12:08:45.655Z</v>
       </c>
       <c r="M440" t="str">
-        <v>2026-04-10T10:44:04.914Z</v>
+        <v>2026-04-10T12:08:45.655Z</v>
       </c>
       <c r="N440" t="str">
         <v>Things get crazy when the Psycho Dad comes out. Featuring a built-in rattle chamber and large claws that act like swimbait tails, the Psycho Dad is the center of attention anytime it finds water. This 3.75” crawfish imitator was built for punching through cover, but it can do a whole lot more. Try it out on a Carolina Rig, standup head, or a jig trailer – you won’t be disappointed! 5 Per Pack</v>
@@ -22170,10 +19896,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__kreature_7pk.jpg</v>
       </c>
       <c r="L441" t="str">
-        <v>2026-04-10T10:44:07.309Z</v>
+        <v>2026-04-10T12:08:47.244Z</v>
       </c>
       <c r="M441" t="str">
-        <v>2026-04-10T10:44:07.309Z</v>
+        <v>2026-04-10T12:08:47.244Z</v>
       </c>
       <c r="N441" t="str">
         <v>The Kreature is sure to cause a stir. Featuring swimming “wings” and a free-flowing skirt of tentacles, the Kreature is impossible to ignore. 4” in size but much larger in attitude, the Kreature produces results as both a trailer and a standalone plastic. Try it on a Texas Rig in cover, or back off the bank and put it on a Carolina Rig. Either way, the fish are going to find it. 7 Per Pack</v>
@@ -22214,10 +19940,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_75__fat_baby_craw_7pk.jpg</v>
       </c>
       <c r="L442" t="str">
-        <v>2026-04-10T10:44:09.439Z</v>
+        <v>2026-04-10T12:08:48.829Z</v>
       </c>
       <c r="M442" t="str">
-        <v>2026-04-10T10:44:09.439Z</v>
+        <v>2026-04-10T12:08:48.829Z</v>
       </c>
       <c r="N442" t="str">
         <v>The Fat Baby Craw is a phenomenal finesse trailer. Its round design keeps it from sticking to cover while the bulk of the plastic ensures that it stays on the hook regardless of what it encounters. This 3.75” trailer has a nice, subtle movement that comes in handy in finesse applications. The Baby Craw is a slightly slimmed-down version of the Fat Baby Craw. 3.75”. It is a more-finesse style trailer for clearer water, smaller jigs, lighter line applications and wary bass. Both craw trailers are very lifelike in size and shape. 7 Per Pack</v>
@@ -22258,10 +19984,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__fat_ika_10pk.jpg</v>
       </c>
       <c r="L443" t="str">
-        <v>2026-04-10T10:44:11.576Z</v>
+        <v>2026-04-10T12:08:50.421Z</v>
       </c>
       <c r="M443" t="str">
-        <v>2026-04-10T10:44:11.576Z</v>
+        <v>2026-04-10T12:08:50.421Z</v>
       </c>
       <c r="N443" t="str">
         <v>Don’t let looks deceive you – the Ika isn’t your run-of-the-mill tube bait. Featuring a grub-style body and a tube-style skirt, the Ika can offer tons of rigging possibilities to fit any scenario. Pitch or flip a Fat Ika and experience bite-getting power that they harness. The 4.5” version shines in finesse situations, thanks to its subtle motion. Regardless of size or application, the common theme is that an Ika gets bit! 10 Per Pack</v>
@@ -22302,10 +20028,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shibo_swimmer.jpg</v>
       </c>
       <c r="L444" t="str">
-        <v>2026-04-10T10:44:12.978Z</v>
+        <v>2026-04-10T12:08:52.970Z</v>
       </c>
       <c r="M444" t="str">
-        <v>2026-04-10T10:44:12.978Z</v>
+        <v>2026-04-10T12:08:52.970Z</v>
       </c>
       <c r="N444" t="str">
         <v>The Yamamoto Shibo Swimmer was built to outperform traditional paddle tail swimbaits, delivering a harder thump and more water displacement for its size than any bait in its class. The custom Yamamoto soft plastic formula provides the ideal combination of a powerful tail kick, natural swimming action, and pronounced head wobble that bass can feel from a distance. The Shibo Swimmer truly separates itself with its versatility, consistently producing across a wide range of conditions. In colder water or during post-front conditions, it maintains a strong swimming action even on a slow, steady retrieve—when many swimbaits go dead. At moderate to fast retrieve speeds, its pronounced vibration makes it deadly in more stained water or when looking to trigger a reaction strike. Whether rigged on the back of a bladed jig, an Alabama rig, or a traditional ballhead jighead, the Shibo Swimmer comes alive, loading the rod tip with a deep, heavy thump that feels more like a hard bait than a soft plastic. If you’re looking for a swimbait that moves more than most, look no further than the Yamamoto Shibo Swimmer. 2.7”-8 pk | 3.2”-7pk | 3.7”-6pk</v>
@@ -22346,10 +20072,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hinge_minnow.jpg</v>
       </c>
       <c r="L445" t="str">
-        <v>2026-04-10T10:44:14.192Z</v>
+        <v>2026-04-10T12:08:54.558Z</v>
       </c>
       <c r="M445" t="str">
-        <v>2026-04-10T10:44:14.192Z</v>
+        <v>2026-04-10T12:08:54.558Z</v>
       </c>
       <c r="N445" t="str">
         <v>The Yamamoto Hinge Minnow is exactly what you expect from the most premium soft bait brand on earth. THE ultimate rolling minnow. A jointed, or “hinged” tail section allows the Hinge Minnow to roll, even on a straight retrieve which makes it easy for beginners and adds a constant fleeing action any time the bait is moving. Flanges run the length of the shoulders of the Hinge Minnow help slow the bait down, while its laminated top and bottom sections with independent weighting creates the perfect rate of roll. Available in 3.5", 5", 6" and even 7" sizes, the Hinge Minnow is a must-have in your arsenal and can be found in 10 winning Yamamoto colors. Keep rolling. 3.5" - 7pk 5" - 6pk 6" - 5pk 7" - 4pk</v>
@@ -22390,10 +20116,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait_kit___84pc_assortment.jpg</v>
       </c>
       <c r="L446" t="str">
-        <v>2026-04-10T10:44:15.403Z</v>
+        <v>2026-04-10T12:08:56.163Z</v>
       </c>
       <c r="M446" t="str">
-        <v>2026-04-10T10:44:15.403Z</v>
+        <v>2026-04-10T12:08:56.163Z</v>
       </c>
       <c r="N446" t="str">
         <v>The Zako Swimbait shines as a vibrating jig trailer but is a deadly combo on any bait that you want to swim. We have compiled some of the top color options in the 3" and 4" and married them together to create this kit. The Zako Swimbait kit comes loaded with 84 zako swimbaits and picked to ensure that you have a Zako for any condition you find in front of you. *items are subject to change based on availability, check graph below for the most up to date product mix 6/pc Zako Swimbait 4" - Black with Blue Flake YAM-134-06-021 6/pc Zako Swimbait 4" - Cream White YAM-134-06-036 6/pc Zako Swimbait 4" - Fading Watermelon with Large Black Flake YAM-134-06-194J 6/pc Zako Swimbait 4" - Tilapia Magic YAM-134-06-414 6/pc Zako Swimbait 4" - Blue Craw YAM-134-06-700 6/pc Zako Swimbait 4" - Green Gizzard YAM-134-06-9008 8/pc Zako Swimbait 3" - Rainbow Shad YAM-134JR-08-992 8/pc Zako Swimbait 3" - Black With Blue Flake YAM-134JR-08-021 8/pc Zako Swimbait 3" - Watermelon with Copper/Orange with Red Laminate YAM-134JR-08-956 8/pc Zako Swimbait 3" - Disco Green YAM-134JR-08-375 8/pc Zako Swimbait 3" - Sexy Shad YAM-134JR-08-9005 8/pc Zako Swimbait 3" - Pro Blue YAM-134JR-08-9004</v>
@@ -22434,10 +20160,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_slim_6pk.jpg</v>
       </c>
       <c r="L447" t="str">
-        <v>2026-04-10T10:44:16.609Z</v>
+        <v>2026-04-10T12:08:57.740Z</v>
       </c>
       <c r="M447" t="str">
-        <v>2026-04-10T10:44:16.609Z</v>
+        <v>2026-04-10T12:08:57.740Z</v>
       </c>
       <c r="N447" t="str">
         <v>The 3.5” Zako Slim from Yamamoto Baits is the perfect companion for smaller chatterbaits. Designed by Brett Hite, this updated version of the original Zako features a more sleek, compact profile that delivers a subtle presentation without sacrificing action. The tapered body and responsive tail create a lifelike movement that perfectly mirrors the action of any bladed jig, drawing in bass with an irresistible side to side quiver. Ideal for finesse fishing or when a smaller profile is needed, the Zako Slim gives you the versatility and performance to tackle tough conditions and bring in more bites. 6 Pack</v>
@@ -22478,10 +20204,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_scope_shad.jpg</v>
       </c>
       <c r="L448" t="str">
-        <v>2026-04-10T10:44:17.821Z</v>
+        <v>2026-04-10T12:08:59.341Z</v>
       </c>
       <c r="M448" t="str">
-        <v>2026-04-10T10:44:17.821Z</v>
+        <v>2026-04-10T12:08:59.341Z</v>
       </c>
       <c r="N448" t="str">
         <v>Building off the success of last year’s Scope Shad, Yamamoto has added both a 3.5’ and 4’’ offering for anglers wanting to upsize. Made from Yamamoto’s Mega Floater Formula, the Scope Shad is a forward-facing sonar weapon that can deliver in other finesse applications as well such as a trailer and on a dropshot. Available in 12 existing colors, as well as 5 brand new Stealth Series colors, the 3.5’’ and 4’’ offerings are proof that you can never have too much of a good thing. The 3" version is 10 per pack, 3.5’’ version is 8 per pack and the 4’’ version is 6 per pack.</v>
@@ -22522,10 +20248,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_swimmer_8pk.jpg</v>
       </c>
       <c r="L449" t="str">
-        <v>2026-04-10T10:44:20.265Z</v>
+        <v>2026-04-10T12:09:02.138Z</v>
       </c>
       <c r="M449" t="str">
-        <v>2026-04-10T10:44:20.265Z</v>
+        <v>2026-04-10T12:09:02.138Z</v>
       </c>
       <c r="N449" t="str">
         <v>Finesse is the name of the game in swimbaits right now, and the Shad Shape Swimmer provides the perfect action and profile that anglers (and fish) are craving. Available in 3 sizes (3.2'', 3.7'', 4.2'') and 17 colors, 5 of which are brand new Stealth Series colors, the Shad Shape Swimmer is a must-have for any serious swimbait fisherman. High quality materials and incredible color options, both of which Yamamoto is known for, team up with an awesome design to offer you a swim bait that produces as well as it looks. 8 Pack</v>
@@ -22566,10 +20292,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait.jpg</v>
       </c>
       <c r="L450" t="str">
-        <v>2026-04-10T10:44:21.490Z</v>
+        <v>2026-04-10T12:09:03.734Z</v>
       </c>
       <c r="M450" t="str">
-        <v>2026-04-10T10:44:21.490Z</v>
+        <v>2026-04-10T12:09:03.734Z</v>
       </c>
       <c r="N450" t="str">
         <v>New 2025 Color: 4" | 9025 - Sungill The Zako Swimbait is the number 1 vibrating jig trailer on the market for good reason. Measuring in at 3 inches and 4 inches long, the Zako's segmented design and natural profile makes it the perfect match for your favorite vibrating jig. But don't limit it to just that application, it can be used a spinnerbait trailer and many other ways as well. Tie one on and find out for yourself. 3"- 8 Pack 4"- 6 Pack</v>
@@ -22610,10 +20336,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__zako_swimbait_bulk_packs.jpg</v>
       </c>
       <c r="L451" t="str">
-        <v>2026-04-10T10:44:22.697Z</v>
+        <v>2026-04-10T12:09:04.892Z</v>
       </c>
       <c r="M451" t="str">
-        <v>2026-04-10T10:44:22.697Z</v>
+        <v>2026-04-10T12:09:04.892Z</v>
       </c>
       <c r="N451" t="str">
         <v>The Zako Swimbait is the number 1 vibrating jig trailer on the market for good reason. Measuring in at 4 inches long, the Zako’s segmented design and natural profile makes it the perfect match for your favorite vibrating jig. But don’t limit it to just that application, it can be used a spinnerbait trailer and many other ways as well. Tie one on and find out for yourself. Available in 50 or 100 packs.</v>
@@ -22654,10 +20380,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__paddle_tail_zako_5pk.jpg</v>
       </c>
       <c r="L452" t="str">
-        <v>2026-04-10T10:44:25.094Z</v>
+        <v>2026-04-10T12:09:07.644Z</v>
       </c>
       <c r="M452" t="str">
-        <v>2026-04-10T10:44:25.094Z</v>
+        <v>2026-04-10T12:09:07.644Z</v>
       </c>
       <c r="N452" t="str">
         <v>The Paddle Tail Zako is everything you know and love about the Zako swimbait, but with a little more action! Featuring the same durable body as the traditional Zako, the Paddle Tail Zako implements a rectangular tail to give it that hard-kicking swimming motion anglers desire. The Paddle Tail Zako shines brightest on the back of a swim jig, but it can be used as a trailer for anything an angler may desire. 5 per Pack</v>
@@ -22698,10 +20424,10 @@
         <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__d_shad_7pk.jpg</v>
       </c>
       <c r="L453" t="str">
-        <v>2026-04-10T10:44:26.290Z</v>
+        <v>2026-04-10T12:09:09.237Z</v>
       </c>
       <c r="M453" t="str">
-        <v>2026-04-10T10:44:26.290Z</v>
+        <v>2026-04-10T12:09:09.237Z</v>
       </c>
       <c r="N453" t="str">
         <v>New 2025 Color: 433 - Glowstick The D-Shad is a new twist on an old classic. Heavier than a traditional soft-body jerk bait, the D-Shad allows for aggressive action, while allowing you to fish it more effectively all-throughout the water column. This comes in handy when fish want fast retrieval. When paused, the D-Shad will sink much like a Senko. The D-Shad's heavier tail provides a shimmy that drives fish mad. 7 Per Pack</v>
@@ -22709,7 +20435,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P453"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O453"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -1046,7 +1046,7 @@
         <v>glide</v>
       </c>
       <c r="K14" t="str">
-        <v>images/shimano_lures/Bantam ARMAJOINT 190SF FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ARMAJOINT%20190SF%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1093,7 +1093,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K15" t="str">
-        <v>images/shimano_lures/FACER 85+SF_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/FACER%2085%2BSF_main.jpg</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1140,7 +1140,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K16" t="str">
-        <v>images/shimano_lures/MD ZUMVERNO 95SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/MD%20ZUMVERNO%2095SP_main.jpg</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1187,7 +1187,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K17" t="str">
-        <v>images/shimano_lures/LIGEN 66F WALKING SPEC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/LIGEN%2066F%20WALKING%20SPEC_main.jpg</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1234,7 +1234,7 @@
         <v>glide</v>
       </c>
       <c r="K18" t="str">
-        <v>images/shimano_lures/Bantam ARMAJOINT 280SF ARMABOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ARMAJOINT%20280SF%20ARMABOOST_main.jpg</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K19" t="str">
-        <v>images/shimano_lures/GRAVITATOR 220SF ARMABOOST_FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/GRAVITATOR%20220SF%20ARMABOOST_FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1328,7 +1328,7 @@
         <v>glide</v>
       </c>
       <c r="K20" t="str">
-        <v>images/shimano_lures/Bantam ARMAJOINT 190F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ARMAJOINT%20190F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1375,7 +1375,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K21" t="str">
-        <v>images/shimano_lures/Bantam BT BAIT 77F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20BT%20BAIT%2077F_main.jpg</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1422,7 +1422,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K22" t="str">
-        <v>images/shimano_lures/Bantam BT BAIT 99SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20BT%20BAIT%2099SS_main.jpg</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1469,7 +1469,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K23" t="str">
-        <v>images/shimano_lures/SCORPION WORLD JERK 110F_110S FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/SCORPION%20WORLD%20JERK%20110F_110S%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1516,7 +1516,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K24" t="str">
-        <v>images/shimano_lures/SCORPION WORLD JERK 115F_115S FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/SCORPION%20WORLD%20JERK%20115F_115S%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1563,7 +1563,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K25" t="str">
-        <v>images/shimano_lures/Bantam WORLD MINNOW 115SP FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20MINNOW%20115SP%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1610,7 +1610,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K26" t="str">
-        <v>images/shimano_lures/Bantam WORLD MINNOW 115F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20MINNOW%20115F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1657,7 +1657,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K27" t="str">
-        <v>images/shimano_lures/Bantam WORLD CRANK 73F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20CRANK%2073F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1704,7 +1704,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K28" t="str">
-        <v>images/shimano_lures/Bantam ZUMVERNO 95SP FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ZUMVERNO%2095SP%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1751,7 +1751,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K29" t="str">
-        <v>images/shimano_lures/Bantam WORLD POP 69F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20POP%2069F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1798,7 +1798,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K30" t="str">
-        <v>images/shimano_lures/SCORPION JERK 90S JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/SCORPION%20JERK%2090S%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K31" t="str">
-        <v>images/shimano_lures/Bantam WORLD RUSH 56F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20RUSH%2056F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1892,7 +1892,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K32" t="str">
-        <v>images/shimano_lures/Bantam UNDURATOR 88F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20UNDURATOR%2088F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1939,7 +1939,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K33" t="str">
-        <v>images/shimano_lures/Bantam OLIVA CRANK FLAT 65F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20OLIVA%20CRANK%20FLAT%2065F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1986,7 +1986,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K34" t="str">
-        <v>images/shimano_lures/Bantam ENBER 60SP FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ENBER%2060SP%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K35" t="str">
-        <v>images/shimano_lures/Bantam LIGEN 66F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20LIGEN%2066F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -2080,7 +2080,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K36" t="str">
-        <v>images/shimano_lures/Bantam MD ZUMVERNO 115SP_115SP FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20MD%20ZUMVERNO%20115SP_115SP%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -2127,7 +2127,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K37" t="str">
-        <v>images/shimano_lures/Bantam SWAGY MDW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20SWAGY%20MDW_main.jpg</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2174,7 +2174,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K38" t="str">
-        <v>images/shimano_lures/Bantam SWAGY TW_DW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20SWAGY%20TW_DW_main.jpg</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2221,7 +2221,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K39" t="str">
-        <v>images/shimano_lures/Bantam JIJIL 70_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20JIJIL%2070_main.jpg</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2268,7 +2268,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K40" t="str">
-        <v>images/shimano_lures/Bantam MACBETH 50 RATTLE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20MACBETH%2050%20RATTLE_main.jpg</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2315,7 +2315,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K41" t="str">
-        <v>images/shimano_lures/Bantam JIJIL PROP 67SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20JIJIL%20PROP%2067SS_main.jpg</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2362,7 +2362,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K42" t="str">
-        <v>images/shimano_lures/Bantam MACBETH SHALLOW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20MACBETH%20SHALLOW_main.jpg</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2409,7 +2409,7 @@
         <v>glide</v>
       </c>
       <c r="K43" t="str">
-        <v>images/shimano_lures/Bantam ARMAJOINT 190 CUSTOM PARTS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ARMAJOINT%20190%20CUSTOM%20PARTS_main.jpg</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2456,7 +2456,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K44" t="str">
-        <v>images/shimano_lures/Bantam BT BAIT 99 CUSTOM PARTS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20BT%20BAIT%2099%20CUSTOM%20PARTS_main.jpg</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2503,7 +2503,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K45" t="str">
-        <v>images/shimano_lures/Bantam BT BAIT 77 CUSTOM PARTS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20BT%20BAIT%2077%20CUSTOM%20PARTS_main.jpg</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2550,7 +2550,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K46" t="str">
-        <v>images/shimano_lures/CARDIFF REFRAIN 45XS BOTTOM SPEC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20REFRAIN%2045XS%20BOTTOM%20SPEC_main.jpg</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2597,7 +2597,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K47" t="str">
-        <v>images/shimano_lures/CARDIFF REFRAIN 50HS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20REFRAIN%2050HS_main.jpg</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2644,7 +2644,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K48" t="str">
-        <v>images/shimano_lures/CARDIFF WINDLIP 85S JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20WINDLIP%2085S%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2691,7 +2691,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K49" t="str">
-        <v>images/shimano_lures/CARDIFF FLUGEL 99F DR FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20FLUGEL%2099F%20DR%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2738,7 +2738,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K50" t="str">
-        <v>images/shimano_lures/CARDIFF WIND LIP 95S_105S JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20WIND%20LIP%2095S_105S%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2785,7 +2785,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K51" t="str">
-        <v>images/shimano_lures/CARDIFF WINDLIP STICK 90S JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20WINDLIP%20STICK%2090S%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2832,7 +2832,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K52" t="str">
-        <v>images/shimano_lures/CARDIFF REFRAIN 42S_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20REFRAIN%2042S_main.jpg</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2879,7 +2879,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K53" t="str">
-        <v>images/shimano_lures/CARDIFF ML BULLET 93F JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ML%20BULLET%2093F%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2926,7 +2926,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K54" t="str">
-        <v>images/shimano_lures/CARDIFF OOTORO 45F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20OOTORO%2045F_main.jpg</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2973,7 +2973,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K55" t="str">
-        <v>images/shimano_lures/CARDIFF DIVERISE 55F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20DIVERISE%2055F_main.jpg</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -3020,7 +3020,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K56" t="str">
-        <v>images/shimano_lures/CARDIFF SLASH RUSH 55SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLASH%20RUSH%2055SS_main.jpg</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K57" t="str">
-        <v>images/shimano_lures/CARDIFF FUWATORO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20FUWATORO%20TOP%2035F_main.jpg</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -3114,7 +3114,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K58" t="str">
-        <v>images/shimano_lures/CARDIFF FUWATORO TOP 35F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20FUWATORO%20TOP%2035F_main.jpg</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -3161,7 +3161,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K59" t="str">
-        <v>images/shimano_lures/CARDIFF SOKOTORO 30S_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SOKOTORO%2030S_main.jpg</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3208,7 +3208,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K60" t="str">
-        <v>images/shimano_lures/CARDIFF CHIBITORO 25F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20CHIBITORO%2025F_main.jpg</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3255,7 +3255,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K61" t="str">
-        <v>images/shimano_lures/CARDIFF CHIBITORO 25S_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20CHIBITORO%2025S_main.jpg</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3302,7 +3302,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K62" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER PREMIUM FINISH_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%20PREMIUM%20FINISH_main.jpg</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3349,7 +3349,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K63" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER PREMIUM FINISH_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%20PREMIUM%20FINISH_main.jpg</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3396,7 +3396,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K64" t="str">
-        <v>images/shimano_lures/CARDIFF SEARCH SWIMMER CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SEARCH%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3443,7 +3443,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K65" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER 5.0g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%205.0g_main.jpg</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3490,7 +3490,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K66" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER 5.0g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%205.0g_main.jpg</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3537,7 +3537,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K67" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3584,7 +3584,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K68" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K69" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER 0.9g~3.5g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%200.9g~3.5g_main.jpg</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3678,7 +3678,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K70" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER 1.5g~3.5g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%201.5g~3.5g_main.jpg</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3725,7 +3725,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K71" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER CE CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%20CE%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3772,7 +3772,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K72" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER CE CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%20CE%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3819,7 +3819,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K73" t="str">
-        <v>images/shimano_lures/CARDIFF ALUMI ROLL 2.8g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ALUMI%20ROLL%202.8g_main.jpg</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3866,7 +3866,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K74" t="str">
-        <v>images/shimano_lures/CARDIFF ALUMI SLIM 2.6g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ALUMI%20SLIM%202.6g_main.jpg</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -3913,7 +3913,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K75" t="str">
-        <v>images/shimano_lures/CARDIFF SEARCH SWIMMER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SEARCH%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -3960,7 +3960,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K76" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -4007,7 +4007,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K77" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER CE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%20CE%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L77" t="str">
         <v/>
@@ -4054,7 +4054,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K78" t="str">
-        <v>images/shimano_lures/CARDIFF WOBBLE SWIMMER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20WOBBLE%20SWIMMER_main.jpg</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -4101,7 +4101,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K79" t="str">
-        <v>images/megabass_lures/DOG-X DIAMANTE SONIC SLIDE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DOG-X%20DIAMANTE%20SONIC%20SLIDE_main.jpg</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -4148,7 +4148,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K80" t="str">
-        <v>images/megabass_lures/DOGMAX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DOGMAX_main.jpg</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -4195,7 +4195,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K81" t="str">
-        <v>images/megabass_lures/POPX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/POPX_main.jpg</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -4242,7 +4242,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K82" t="str">
-        <v>images/megabass_lures/BABY POPX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/BABY%20POPX_main.jpg</v>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -4289,7 +4289,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K83" t="str">
-        <v>images/megabass_lures/KARASHI iG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/KARASHI%20iG_main.jpg</v>
       </c>
       <c r="L83" t="str">
         <v/>
@@ -4336,7 +4336,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K84" t="str">
-        <v>images/megabass_lures/KARASHI 80_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/KARASHI%2080_main.png</v>
       </c>
       <c r="L84" t="str">
         <v/>
@@ -4383,7 +4383,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K85" t="str">
-        <v>images/megabass_lures/KARASHI_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/KARASHI_main.jpg</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -4430,7 +4430,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K86" t="str">
-        <v>images/megabass_lures/DOG-X Jr.COAYU_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DOG-X%20Jr.COAYU_main.jpg</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -4477,7 +4477,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K87" t="str">
-        <v>images/megabass_lures/KARASHI SPINNER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/KARASHI%20SPINNER_main.jpg</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -4524,7 +4524,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K88" t="str">
-        <v>images/megabass_lures/POPMAX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/POPMAX_main.jpg</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -4618,7 +4618,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K90" t="str">
-        <v>images/megabass_lures/DOG-X SPEED SLIDE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DOG-X%20SPEED%20SLIDE_main.jpg</v>
       </c>
       <c r="L90" t="str">
         <v/>
@@ -4665,7 +4665,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K91" t="str">
-        <v>images/megabass_lures/GIANT DOG-X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/GIANT%20DOG-X_main.jpg</v>
       </c>
       <c r="L91" t="str">
         <v/>
@@ -4712,7 +4712,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K92" t="str">
-        <v>images/megabass_lures/ANTHRAX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ANTHRAX_main.jpg</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -4759,7 +4759,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K93" t="str">
-        <v>images/megabass_lures/MEGADOG-X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MEGADOG-X_main.jpg</v>
       </c>
       <c r="L93" t="str">
         <v/>
@@ -4806,7 +4806,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K94" t="str">
-        <v>images/megabass_lures/ANTHRAX 100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ANTHRAX%20100_main.jpg</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -4900,7 +4900,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K96" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_xpod.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/XPOD%20Jr._main.jpg</v>
       </c>
       <c r="L96" t="str">
         <v/>
@@ -4947,7 +4947,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K97" t="str">
-        <v>images/megabass_lures/XPOD Jr._main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/XPOD%20Jr._main.jpg</v>
       </c>
       <c r="L97" t="str">
         <v/>
@@ -4994,7 +4994,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K98" t="str">
-        <v>images/megabass_lures/DOG-X DIAMANTE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DOG-X%20DIAMANTE%20SONIC%20SLIDE_main.jpg</v>
       </c>
       <c r="L98" t="str">
         <v/>
@@ -5088,7 +5088,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K100" t="str">
-        <v>images/megabass_lures/MPW MEGADOG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MPW%20MEGADOG_main.jpg</v>
       </c>
       <c r="L100" t="str">
         <v/>
@@ -5135,7 +5135,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K101" t="str">
-        <v>images/megabass_lures/MPW KIRINJI 90_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MPW%20KIRINJI%2090_main.jpg</v>
       </c>
       <c r="L101" t="str">
         <v/>
@@ -5182,7 +5182,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K102" t="str">
-        <v>images/megabass_lures/SCREAM-X Orca_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SCREAM-X%20Orca_main.jpg</v>
       </c>
       <c r="L102" t="str">
         <v/>
@@ -5229,7 +5229,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K103" t="str">
-        <v>images/megabass_lures/X-PLOSE SLOW SWIMMER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-PLOSE%20SLOW%20SWIMMER_main.jpg</v>
       </c>
       <c r="L103" t="str">
         <v/>
@@ -5276,7 +5276,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K104" t="str">
-        <v>images/megabass_lures/SCREAM-X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SCREAM-X_main.jpg</v>
       </c>
       <c r="L104" t="str">
         <v/>
@@ -5323,7 +5323,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K105" t="str">
-        <v>images/megabass_lures/BEETLE-X HOVER CRAWL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/BEETLE-X%20HOVER%20CRAWL_main.jpg</v>
       </c>
       <c r="L105" t="str">
         <v/>
@@ -5370,7 +5370,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K106" t="str">
-        <v>images/megabass_lures/SCREAM-X Jr._main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SCREAM-X%20Jr._main.jpg</v>
       </c>
       <c r="L106" t="str">
         <v/>
@@ -5417,7 +5417,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K107" t="str">
-        <v>images/megabass_lures/NANO SIGLETT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/NANO%20SIGLETT_main.jpg</v>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -5464,7 +5464,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K108" t="str">
-        <v>images/megabass_lures/TINY SIGLETT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/TINY%20SIGLETT_main.jpg</v>
       </c>
       <c r="L108" t="str">
         <v/>
@@ -5511,7 +5511,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K109" t="str">
-        <v>images/megabass_lures/GRAND SIGLETT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/GRAND%20SIGLETT_main.jpg</v>
       </c>
       <c r="L109" t="str">
         <v/>
@@ -5558,7 +5558,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K110" t="str">
-        <v>images/megabass_lures/SIGLETT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SIGLETT_main.jpg</v>
       </c>
       <c r="L110" t="str">
         <v/>
@@ -5605,7 +5605,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K111" t="str">
-        <v>images/megabass_lures/ORC(OVER REV CRANK)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ORC(OVER%20REV%20CRANK)_main.jpg</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -5652,7 +5652,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K112" t="str">
-        <v>images/megabass_lures/i-JACK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/i-JACK_main.jpg</v>
       </c>
       <c r="L112" t="str">
         <v/>
@@ -5699,7 +5699,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K113" t="str">
-        <v>images/megabass_lures/ORC BURNING SHAD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ORC%20BURNING%20SHAD_main.jpg</v>
       </c>
       <c r="L113" t="str">
         <v/>
@@ -5746,7 +5746,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K114" t="str">
-        <v>images/megabass_lures/PROP DARTER i-LOUD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/PROP%20DARTER%20i-LOUD_main.jpg</v>
       </c>
       <c r="L114" t="str">
         <v/>
@@ -5793,7 +5793,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K115" t="str">
-        <v>images/megabass_lures/PROPDARTER 80_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/PROPDARTER%2080_main.jpg</v>
       </c>
       <c r="L115" t="str">
         <v/>
@@ -5840,7 +5840,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K116" t="str">
-        <v>images/megabass_lures/i-WING 135_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/i-WING%20135%20SPARE%20PARTS%20KIT_main.jpg</v>
       </c>
       <c r="L116" t="str">
         <v/>
@@ -5887,7 +5887,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K117" t="str">
-        <v>images/megabass_lures/PROPDARTER 106_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/PROPDARTER%20106_main.jpg</v>
       </c>
       <c r="L117" t="str">
         <v/>
@@ -5934,7 +5934,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K118" t="str">
-        <v>images/megabass_lures/i-WING FRY_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/i-WING%20FRY_main.jpg</v>
       </c>
       <c r="L118" t="str">
         <v/>
@@ -5981,7 +5981,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K119" t="str">
-        <v>images/megabass_lures/i-WING TRIPLE FRY_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/i-WING%20TRIPLE%20FRY_main.jpg</v>
       </c>
       <c r="L119" t="str">
         <v/>
@@ -6028,7 +6028,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K120" t="str">
-        <v>images/megabass_lures/GABARIN Jr._main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/GABARIN%20Jr._main.jpg</v>
       </c>
       <c r="L120" t="str">
         <v/>
@@ -6075,7 +6075,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K121" t="str">
-        <v>images/megabass_lures/BIG GABOT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/BIG%20GABOT_main.jpg</v>
       </c>
       <c r="L121" t="str">
         <v/>
@@ -6122,7 +6122,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K122" t="str">
-        <v>images/megabass_lures/VISION ONETEN SSR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%20SSR_main.jpg</v>
       </c>
       <c r="L122" t="str">
         <v/>
@@ -6169,7 +6169,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K123" t="str">
-        <v>images/megabass_lures/GABARIN_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/GABARIN_main.jpg</v>
       </c>
       <c r="L123" t="str">
         <v/>
@@ -6216,7 +6216,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K124" t="str">
-        <v>images/megabass_lures/BATRA-X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/BATRA-X_main.jpg</v>
       </c>
       <c r="L124" t="str">
         <v/>
@@ -6263,7 +6263,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K125" t="str">
-        <v>images/megabass_lures/ITO SHINER +1_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ITO%20SHINER%20%2B1_main.jpg</v>
       </c>
       <c r="L125" t="str">
         <v/>
@@ -6310,7 +6310,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K126" t="str">
-        <v>images/megabass_lures/SHADING-X R 62_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SHADING-X%20R%2062_main.jpg</v>
       </c>
       <c r="L126" t="str">
         <v/>
@@ -6357,7 +6357,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K127" t="str">
-        <v>images/megabass_lures/SHADING-X R 55_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SHADING-X%20R%2055_main.jpg</v>
       </c>
       <c r="L127" t="str">
         <v/>
@@ -6404,7 +6404,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K128" t="str">
-        <v>images/megabass_lures/SHADING-X R 75_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SHADING-X%20R%2075_main.jpg</v>
       </c>
       <c r="L128" t="str">
         <v/>
@@ -6451,7 +6451,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K129" t="str">
-        <v>images/megabass_lures/LATES FeedingWoofer_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/LATES%20FeedingWoofer_main.jpg</v>
       </c>
       <c r="L129" t="str">
         <v/>
@@ -6498,7 +6498,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K130" t="str">
-        <v>images/megabass_lures/KANATA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/KANATA_main.jpg</v>
       </c>
       <c r="L130" t="str">
         <v/>
@@ -6545,7 +6545,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K131" t="str">
-        <v>images/megabass_lures/ITO SHINER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ITO%20SHINER%20%2B1_main.jpg</v>
       </c>
       <c r="L131" t="str">
         <v/>
@@ -6592,7 +6592,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K132" t="str">
-        <v>images/megabass_lures/ITO SHINER SSR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ITO%20SHINER%20SSR_main.jpg</v>
       </c>
       <c r="L132" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K133" t="str">
-        <v>images/megabass_lures/KANATA +1_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/KANATA%20%2B1_main.jpg</v>
       </c>
       <c r="L133" t="str">
         <v/>
@@ -6733,7 +6733,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K135" t="str">
-        <v>images/megabass_lures/IxI FURIOUS 0.5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/IxI%20FURIOUS%200.5_main.jpg</v>
       </c>
       <c r="L135" t="str">
         <v/>
@@ -6780,7 +6780,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K136" t="str">
-        <v>images/megabass_lures/I x I SHAD TYPE-3_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/I%20x%20I%20SHAD%20TYPE-3_main.jpg</v>
       </c>
       <c r="L136" t="str">
         <v/>
@@ -6827,7 +6827,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K137" t="str">
-        <v>images/megabass_lures/I x I SHAD TYPE-R_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/I%20x%20I%20SHAD%20TYPE-R_main.jpg</v>
       </c>
       <c r="L137" t="str">
         <v/>
@@ -6874,7 +6874,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K138" t="str">
-        <v>images/megabass_lures/IxI SHAD TX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/IxI%20SHAD%20TX_main.jpg</v>
       </c>
       <c r="L138" t="str">
         <v/>
@@ -6921,7 +6921,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K139" t="str">
-        <v>images/megabass_lures/LIVE-X MODEL1_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/LIVE-X%20MODEL1_main.jpg</v>
       </c>
       <c r="L139" t="str">
         <v/>
@@ -6968,7 +6968,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K140" t="str">
-        <v>images/megabass_lures/X-NANAHAN_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-NANAHAN_main.jpg</v>
       </c>
       <c r="L140" t="str">
         <v/>
@@ -7015,7 +7015,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K141" t="str">
-        <v>images/megabass_lures/X-NANAHAN+1_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-NANAHAN%2B1_main.jpg</v>
       </c>
       <c r="L141" t="str">
         <v/>
@@ -7062,7 +7062,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K142" t="str">
-        <v>images/megabass_lures/X-NANAHAN+2_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-NANAHAN%2B2_main.jpg</v>
       </c>
       <c r="L142" t="str">
         <v/>
@@ -7109,7 +7109,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K143" t="str">
-        <v>images/megabass_lures/VISION 95_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%2095_main.jpg</v>
       </c>
       <c r="L143" t="str">
         <v/>
@@ -7156,7 +7156,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K144" t="str">
-        <v>images/megabass_lures/VISION ONETEN Jr._main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%20Jr._main.jpg</v>
       </c>
       <c r="L144" t="str">
         <v/>
@@ -7203,7 +7203,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K145" t="str">
-        <v>images/megabass_lures/VISION ONETEN+1 Jr._main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%2B1%20Jr._main.jpg</v>
       </c>
       <c r="L145" t="str">
         <v/>
@@ -7250,7 +7250,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K146" t="str">
-        <v>images/megabass_lures/VISION ONETEN+2 Jr._main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%2B2%20Jr._main.jpg</v>
       </c>
       <c r="L146" t="str">
         <v/>
@@ -7297,7 +7297,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K147" t="str">
-        <v>images/megabass_lures/VISION ONETEN  SR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%20%20SR_main.jpg</v>
       </c>
       <c r="L147" t="str">
         <v/>
@@ -7344,7 +7344,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K148" t="str">
-        <v>images/megabass_lures/VISION ONETEN_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%20%20SR_main.jpg</v>
       </c>
       <c r="L148" t="str">
         <v/>
@@ -7391,7 +7391,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K149" t="str">
-        <v>images/megabass_lures/VISION ONETEN +1_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%20%2B1_main.jpg</v>
       </c>
       <c r="L149" t="str">
         <v/>
@@ -7438,7 +7438,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K150" t="str">
-        <v>images/megabass_lures/VISION ONETEN MAGNUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%20MAGNUM_main.jpg</v>
       </c>
       <c r="L150" t="str">
         <v/>
@@ -7485,7 +7485,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K151" t="str">
-        <v>images/megabass_lures/VISION ONETEN LBO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%20LBO_main.jpg</v>
       </c>
       <c r="L151" t="str">
         <v/>
@@ -7532,7 +7532,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K152" t="str">
-        <v>images/megabass_lures/VISION ONETEN MAX LBO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VISION%20ONETEN%20MAX%20LBO_main.jpg</v>
       </c>
       <c r="L152" t="str">
         <v/>
@@ -7579,7 +7579,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K153" t="str">
-        <v>images/megabass_lures/ONETEN R+2_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ONETEN%20R%2B2_main.jpg</v>
       </c>
       <c r="L153" t="str">
         <v/>
@@ -7626,7 +7626,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K154" t="str">
-        <v>images/megabass_lures/ONETEN R+1_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ONETEN%20R%2B1_main.jpg</v>
       </c>
       <c r="L154" t="str">
         <v/>
@@ -7673,7 +7673,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K155" t="str">
-        <v>images/megabass_lures/ONETEN R Hi-FLOAT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ONETEN%20R%20Hi-FLOAT_main.jpg</v>
       </c>
       <c r="L155" t="str">
         <v/>
@@ -7720,7 +7720,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K156" t="str">
-        <v>images/megabass_lures/ONETEN R_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ONETEN%20R%20Hi-FLOAT_main.jpg</v>
       </c>
       <c r="L156" t="str">
         <v/>
@@ -7767,7 +7767,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K157" t="str">
-        <v>images/megabass_lures/ONETEN R+3_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ONETEN%20R%2B3%20Hi-FLOAT_main.jpg</v>
       </c>
       <c r="L157" t="str">
         <v/>
@@ -7814,7 +7814,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K158" t="str">
-        <v>images/megabass_lures/ONETEN R+3 Hi-FLOAT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/ONETEN%20R%2B3%20Hi-FLOAT_main.jpg</v>
       </c>
       <c r="L158" t="str">
         <v/>
@@ -7861,7 +7861,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K159" t="str">
-        <v>images/megabass_lures/X-48 ACROBAT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-48%20ACROBAT_main.jpg</v>
       </c>
       <c r="L159" t="str">
         <v/>
@@ -7908,7 +7908,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K160" t="str">
-        <v>images/megabass_lures/X-70_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-70_main.jpg</v>
       </c>
       <c r="L160" t="str">
         <v/>
@@ -7955,7 +7955,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K161" t="str">
-        <v>images/megabass_lures/X-52 ACROBAT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-52%20ACROBAT_main.jpg</v>
       </c>
       <c r="L161" t="str">
         <v/>
@@ -8002,7 +8002,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K162" t="str">
-        <v>images/megabass_lures/LIVE-X REVENGE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/LIVE-X%20REVENGE_main.jpg</v>
       </c>
       <c r="L162" t="str">
         <v/>
@@ -8049,7 +8049,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K163" t="str">
-        <v>images/megabass_lures/iPX-12_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/iPX-12_main.jpg</v>
       </c>
       <c r="L163" t="str">
         <v/>
@@ -8096,7 +8096,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K164" t="str">
-        <v>images/megabass_lures/iPX-16_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/iPX-16_main.jpg</v>
       </c>
       <c r="L164" t="str">
         <v/>
@@ -8143,7 +8143,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K165" t="str">
-        <v>images/megabass_lures/X-80 TRICK DARTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-80%20TRICK%20DARTER_main.jpg</v>
       </c>
       <c r="L165" t="str">
         <v/>
@@ -8190,7 +8190,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K166" t="str">
-        <v>images/megabass_lures/X-80Jr._main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-80Jr._main.jpg</v>
       </c>
       <c r="L166" t="str">
         <v/>
@@ -8237,7 +8237,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K167" t="str">
-        <v>images/megabass_lures/LIVE-X  LEVIATHAN_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/LIVE-X%20%20LEVIATHAN_main.jpg</v>
       </c>
       <c r="L167" t="str">
         <v/>
@@ -8331,7 +8331,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K169" t="str">
-        <v>images/megabass_lures/GRIFFON Bait Finesse SR-X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/GRIFFON%20Bait%20Finesse%20SR-X_main.jpg</v>
       </c>
       <c r="L169" t="str">
         <v/>
@@ -8378,7 +8378,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K170" t="str">
-        <v>images/megabass_lures/MR-X GRIFFON_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MR-X%20GRIFFON_main.jpg</v>
       </c>
       <c r="L170" t="str">
         <v/>
@@ -8425,7 +8425,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K171" t="str">
-        <v>images/megabass_lures/GRIFFON Bait Finesse MR-X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/GRIFFON%20Bait%20Finesse%20MR-X_main.jpg</v>
       </c>
       <c r="L171" t="str">
         <v/>
@@ -8472,7 +8472,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K172" t="str">
-        <v>images/megabass_lures/SR-X GRIFFON_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SR-X%20GRIFFON_main.jpg</v>
       </c>
       <c r="L172" t="str">
         <v/>
@@ -8519,7 +8519,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K173" t="str">
-        <v>images/megabass_lures/DEEP-X100 LBO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DEEP-X100%20LBO_main.jpg</v>
       </c>
       <c r="L173" t="str">
         <v/>
@@ -8566,7 +8566,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K174" t="str">
-        <v>images/megabass_lures/DEEP-X200 LBO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DEEP-X200%20LBO_main.jpg</v>
       </c>
       <c r="L174" t="str">
         <v/>
@@ -8613,7 +8613,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K175" t="str">
-        <v>images/megabass_lures/DEEP-X300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DEEP-X300_main.jpg</v>
       </c>
       <c r="L175" t="str">
         <v/>
@@ -8660,7 +8660,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K176" t="str">
-        <v>images/megabass_lures/DEEP-SIX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DEEP-SIX_main.jpg</v>
       </c>
       <c r="L176" t="str">
         <v/>
@@ -8707,7 +8707,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K177" t="str">
-        <v>images/megabass_lures/DEEP-X150_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DEEP-X150_main.jpg</v>
       </c>
       <c r="L177" t="str">
         <v/>
@@ -8754,7 +8754,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K178" t="str">
-        <v>images/megabass_lures/FLAPSLAP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/FLAPSLAP_main.jpg</v>
       </c>
       <c r="L178" t="str">
         <v/>
@@ -8848,7 +8848,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K180" t="str">
-        <v>images/megabass_lures/FLAPSLAP LBO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/FLAPSLAP%20LBO_main.jpg</v>
       </c>
       <c r="L180" t="str">
         <v/>
@@ -8895,7 +8895,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K181" t="str">
-        <v>images/megabass_lures/Z-CRANK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/Z-CRANK_main.jpg</v>
       </c>
       <c r="L181" t="str">
         <v/>
@@ -8942,7 +8942,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K182" t="str">
-        <v>images/megabass_lures/Z-CRANK Jr._main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/Z-CRANK%20Jr._main.jpg</v>
       </c>
       <c r="L182" t="str">
         <v/>
@@ -8989,7 +8989,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K183" t="str">
-        <v>images/megabass_lures/SUPER-Z Z2_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SUPER-Z%20Z2_main.jpg</v>
       </c>
       <c r="L183" t="str">
         <v/>
@@ -9036,7 +9036,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K184" t="str">
-        <v>images/megabass_lures/SUPER-Z Z1_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SUPER-Z%20Z1_main.jpg</v>
       </c>
       <c r="L184" t="str">
         <v/>
@@ -9083,7 +9083,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K185" t="str">
-        <v>images/megabass_lures/SonicSide_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SonicSide_main.jpg</v>
       </c>
       <c r="L185" t="str">
         <v/>
@@ -9130,7 +9130,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K186" t="str">
-        <v>images/megabass_lures/SUPER-Z Z3_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SUPER-Z%20Z3_main.jpg</v>
       </c>
       <c r="L186" t="str">
         <v/>
@@ -9177,7 +9177,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K187" t="str">
-        <v>images/megabass_lures/S-CRANK 1.5 _ 1.2_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/S-CRANK%201.5%20_%201.2_main.jpg</v>
       </c>
       <c r="L187" t="str">
         <v/>
@@ -9224,7 +9224,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K188" t="str">
-        <v>images/megabass_lures/BIG-M 2.0_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/BIG-M%202.0_main.jpg</v>
       </c>
       <c r="L188" t="str">
         <v/>
@@ -9271,7 +9271,7 @@
         <v>tight_wobble</v>
       </c>
       <c r="K189" t="str">
-        <v>images/megabass_lures/MPW HADARATRAP 70_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MPW%20HADARATRAP%2070_main.jpg</v>
       </c>
       <c r="L189" t="str">
         <v/>
@@ -9318,7 +9318,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K190" t="str">
-        <v>images/megabass_lures/BIG-M 7.5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/BIG-M%207.5_main.jpg</v>
       </c>
       <c r="L190" t="str">
         <v/>
@@ -9365,7 +9365,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K191" t="str">
-        <v>images/megabass_lures/BIG-M 4.0_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/BIG-M%204.0_main.jpg</v>
       </c>
       <c r="L191" t="str">
         <v/>
@@ -9412,7 +9412,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K192" t="str">
-        <v>images/megabass_lures/The KNUCKLE LD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/The%20KNUCKLE%20LD_main.jpg</v>
       </c>
       <c r="L192" t="str">
         <v/>
@@ -9459,7 +9459,7 @@
         <v>vibration</v>
       </c>
       <c r="K193" t="str">
-        <v>images/megabass_lures/VIBRATION-X ULTRA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VIBRATION-X%20ULTRA_main.jpg</v>
       </c>
       <c r="L193" t="str">
         <v/>
@@ -9506,7 +9506,7 @@
         <v>vibration</v>
       </c>
       <c r="K194" t="str">
-        <v>images/megabass_lures/VIBRATION-X DYNA RESPONSE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VIBRATION-X%20DYNA%20RESPONSE_main.jpg</v>
       </c>
       <c r="L194" t="str">
         <v/>
@@ -9553,7 +9553,7 @@
         <v>vibration</v>
       </c>
       <c r="K195" t="str">
-        <v>images/megabass_lures/VIBRATION-X SMATRA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VIBRATION-X%20SMATRA_main.jpg</v>
       </c>
       <c r="L195" t="str">
         <v/>
@@ -9600,7 +9600,7 @@
         <v>vibration</v>
       </c>
       <c r="K196" t="str">
-        <v>images/megabass_lures/VIBRATION-X NANO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VIBRATION-X%20NANO_main.jpg</v>
       </c>
       <c r="L196" t="str">
         <v/>
@@ -9647,7 +9647,7 @@
         <v>vibration</v>
       </c>
       <c r="K197" t="str">
-        <v>images/megabass_lures/VIBRATION-X DYNA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VIBRATION-X%20DYNA%20RESPONSE_main.jpg</v>
       </c>
       <c r="L197" t="str">
         <v/>
@@ -9694,7 +9694,7 @@
         <v>vibration</v>
       </c>
       <c r="K198" t="str">
-        <v>images/megabass_lures/VIBRATION-X VATALION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VIBRATION-X%20VATALION_main.jpg</v>
       </c>
       <c r="L198" t="str">
         <v/>
@@ -9741,7 +9741,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K199" t="str">
-        <v>images/megabass_lures/LEVEL SWIMMER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/LEVEL%20SWIMMER_main.jpg</v>
       </c>
       <c r="L199" t="str">
         <v/>
@@ -9835,7 +9835,7 @@
         <v>glide</v>
       </c>
       <c r="K201" t="str">
-        <v>images/megabass_lures/i-SLIDE 187R_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/i-SLIDE%20187R_main.jpg</v>
       </c>
       <c r="L201" t="str">
         <v/>
@@ -9882,7 +9882,7 @@
         <v>glide</v>
       </c>
       <c r="K202" t="str">
-        <v>images/megabass_lures/i-BRAKE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/i-BRAKE_main.jpg</v>
       </c>
       <c r="L202" t="str">
         <v/>
@@ -9929,7 +9929,7 @@
         <v>glide</v>
       </c>
       <c r="K203" t="str">
-        <v>images/megabass_lures/VATALION190_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VATALION190_main.jpg</v>
       </c>
       <c r="L203" t="str">
         <v/>
@@ -9976,7 +9976,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K204" t="str">
-        <v>images/megabass_lures/SPINE-X 190F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SPINE-X%20190F_main.jpg</v>
       </c>
       <c r="L204" t="str">
         <v/>
@@ -10023,7 +10023,7 @@
         <v>glide</v>
       </c>
       <c r="K205" t="str">
-        <v>images/megabass_lures/GORHAM 147F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/GORHAM%20147F_main.jpg</v>
       </c>
       <c r="L205" t="str">
         <v/>
@@ -10070,7 +10070,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K206" t="str">
-        <v>images/megabass_lures/SuWITCH_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SuWITCH_main.jpg</v>
       </c>
       <c r="L206" t="str">
         <v/>
@@ -10117,7 +10117,7 @@
         <v>glide</v>
       </c>
       <c r="K207" t="str">
-        <v>images/megabass_lures/GARUDA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/GARUDA_main.jpg</v>
       </c>
       <c r="L207" t="str">
         <v/>
@@ -10164,7 +10164,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K208" t="str">
-        <v>images/megabass_lures/JAMAICA BOA Jr. SUPER METAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/JAMAICA%20BOA%20Jr.%20SUPER%20METAL_main.jpg</v>
       </c>
       <c r="L208" t="str">
         <v/>
@@ -10258,7 +10258,7 @@
         <v>variable</v>
       </c>
       <c r="K210" t="str">
-        <v>images/megabass_lures/MAGDRAFT HEAD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MAGDRAFT%20HEAD_main.jpg</v>
       </c>
       <c r="L210" t="str">
         <v/>
@@ -10305,7 +10305,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K211" t="str">
-        <v>images/megabass_lures/SV-3_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SV-3_main.jpg</v>
       </c>
       <c r="L211" t="str">
         <v/>
@@ -10352,7 +10352,7 @@
         <v>variable</v>
       </c>
       <c r="K212" t="str">
-        <v>images/megabass_lures/OKASHIRA SCREW HEAD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/OKASHIRA%20SCREW%20HEAD_main.jpg</v>
       </c>
       <c r="L212" t="str">
         <v/>
@@ -10399,7 +10399,7 @@
         <v>variable</v>
       </c>
       <c r="K213" t="str">
-        <v>images/megabass_lures/OKASHIRA HEAD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/OKASHIRA%20HEAD-HG%EF%BC%88Huge-Contact%EF%BC%89_main.jpg</v>
       </c>
       <c r="L213" t="str">
         <v/>
@@ -10446,7 +10446,7 @@
         <v>variable</v>
       </c>
       <c r="K214" t="str">
-        <v>images/megabass_lures/OKASHIRA HEAD-HG（Huge-Contact）_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/OKASHIRA%20HEAD-HG%EF%BC%88Huge-Contact%EF%BC%89_main.jpg</v>
       </c>
       <c r="L214" t="str">
         <v/>
@@ -10540,7 +10540,7 @@
         <v>glide</v>
       </c>
       <c r="K216" t="str">
-        <v>images/megabass_lures/VATALION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/VATALION_main.jpg</v>
       </c>
       <c r="L216" t="str">
         <v/>
@@ -10587,7 +10587,7 @@
         <v>variable</v>
       </c>
       <c r="K217" t="str">
-        <v>images/megabass_lures/UOZE SWIMMER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/UOZE%20SWIMMER_main.jpg</v>
       </c>
       <c r="L217" t="str">
         <v/>
@@ -10634,7 +10634,7 @@
         <v>variable</v>
       </c>
       <c r="K218" t="str">
-        <v>images/megabass_lures/MAKIPPA FFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MAKIPPA%20FFS_main.jpg</v>
       </c>
       <c r="L218" t="str">
         <v/>
@@ -10681,7 +10681,7 @@
         <v>variable</v>
       </c>
       <c r="K219" t="str">
-        <v>images/megabass_lures/METAL-X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/METAL-X_main.jpg</v>
       </c>
       <c r="L219" t="str">
         <v/>
@@ -10728,7 +10728,7 @@
         <v>variable</v>
       </c>
       <c r="K220" t="str">
-        <v>images/megabass_lures/X-BLAZAR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/X-BLAZAR_main.jpg</v>
       </c>
       <c r="L220" t="str">
         <v/>
@@ -10822,7 +10822,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K222" t="str">
-        <v>images/megabass_lures/MAGDRAFT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MAGDRAFT_main.jpg</v>
       </c>
       <c r="L222" t="str">
         <v/>
@@ -10869,7 +10869,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K223" t="str">
-        <v>images/megabass_lures/MAGDRAFT 鰣 HASU RAVER(S)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MAGDRAFT%20%E9%B0%A3%20HASU%20RAVER(S)_main.jpg</v>
       </c>
       <c r="L223" t="str">
         <v/>
@@ -10916,7 +10916,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K224" t="str">
-        <v>images/megabass_lures/MAGDRAFT 鮎 AYU TWITCHER(S)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MAGDRAFT%20%E9%AE%8E%20AYU%20TWITCHER(S)_main.jpg</v>
       </c>
       <c r="L224" t="str">
         <v/>
@@ -10963,7 +10963,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K225" t="str">
-        <v>images/megabass_lures/MAGDRAFT 鮎 AYU TWITCHER(SF)_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/MAGDRAFT%20%E9%AE%8E%20AYU%20TWITCHER(SF)_main.jpg</v>
       </c>
       <c r="L225" t="str">
         <v/>
@@ -11010,7 +11010,7 @@
         <v>variable</v>
       </c>
       <c r="K226" t="str">
-        <v>images/megabass_lures/DARK SLEEPER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/DARK%20SLEEPER_main.jpg</v>
       </c>
       <c r="L226" t="str">
         <v/>
@@ -11057,7 +11057,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K227" t="str">
-        <v>images/megabass_lures/SLEEPER GILL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SLEEPER%20GILL_main.jpg</v>
       </c>
       <c r="L227" t="str">
         <v/>
@@ -11104,7 +11104,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K228" t="str">
-        <v>images/megabass_lures/SLEEPER CRAW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SLEEPER%20CRAW_main.jpg</v>
       </c>
       <c r="L228" t="str">
         <v/>
@@ -11151,7 +11151,7 @@
         <v>variable</v>
       </c>
       <c r="K229" t="str">
-        <v>images/megabass_lures/YAGOT 3.5inch_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/YAGOT%203.5inch_main.jpg</v>
       </c>
       <c r="L229" t="str">
         <v/>
@@ -11198,7 +11198,7 @@
         <v>variable</v>
       </c>
       <c r="K230" t="str">
-        <v>images/megabass_lures/SLAPHOG 3.5inch_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SLAPHOG%203.5inch_main.jpg</v>
       </c>
       <c r="L230" t="str">
         <v/>
@@ -11245,7 +11245,7 @@
         <v>variable</v>
       </c>
       <c r="K231" t="str">
-        <v>images/megabass_lures/HAZE-ST 3.4inch_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/HAZE-ST%203.4inch_main.jpg</v>
       </c>
       <c r="L231" t="str">
         <v/>
@@ -11292,7 +11292,7 @@
         <v>variable</v>
       </c>
       <c r="K232" t="str">
-        <v>images/megabass_lures/TINY XLAYER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/TINY%20XLAYER_main.jpg</v>
       </c>
       <c r="L232" t="str">
         <v/>
@@ -11339,7 +11339,7 @@
         <v>variable</v>
       </c>
       <c r="K233" t="str">
-        <v>images/megabass_lures/HAZEDONG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/HAZEDONG_main.jpg</v>
       </c>
       <c r="L233" t="str">
         <v/>
@@ -11386,7 +11386,7 @@
         <v>variable</v>
       </c>
       <c r="K234" t="str">
-        <v>images/megabass_lures/HAZEDONG SHAD 3inch_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/HAZEDONG%20SHAD%203inch_main.jpg</v>
       </c>
       <c r="L234" t="str">
         <v/>
@@ -11433,7 +11433,7 @@
         <v>variable</v>
       </c>
       <c r="K235" t="str">
-        <v>images/megabass_lures/SPARK SHAD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SPARK%20SHAD_main.jpg</v>
       </c>
       <c r="L235" t="str">
         <v/>
@@ -11480,7 +11480,7 @@
         <v>variable</v>
       </c>
       <c r="K236" t="str">
-        <v>images/megabass_lures/TOURNAMENT CRAWLER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/TOURNAMENT%20CRAWLER_main.jpg</v>
       </c>
       <c r="L236" t="str">
         <v/>
@@ -11527,7 +11527,7 @@
         <v>variable</v>
       </c>
       <c r="K237" t="str">
-        <v>images/megabass_lures/BOTTLE SHRIMP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/BOTTLE%20SHRIMP_main.jpg</v>
       </c>
       <c r="L237" t="str">
         <v/>
@@ -11574,7 +11574,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K238" t="str">
-        <v>images/megabass_lures/SLING SHAD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SLING%20SHAD_main.jpg</v>
       </c>
       <c r="L238" t="str">
         <v/>
@@ -11621,7 +11621,7 @@
         <v>variable</v>
       </c>
       <c r="K239" t="str">
-        <v>images/megabass_lures/TK TWISTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/TK%20TWISTER_main.jpg</v>
       </c>
       <c r="L239" t="str">
         <v/>
@@ -11668,7 +11668,7 @@
         <v>variable</v>
       </c>
       <c r="K240" t="str">
-        <v>images/megabass_lures/OUTBARB HOOK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/OUTBARB%20HOOK_main.jpg</v>
       </c>
       <c r="L240" t="str">
         <v/>
@@ -11715,7 +11715,7 @@
         <v>variable</v>
       </c>
       <c r="K241" t="str">
-        <v>images/megabass_lures/TINSEL HOOK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/TINSEL%20HOOK_main.jpg</v>
       </c>
       <c r="L241" t="str">
         <v/>
@@ -11762,7 +11762,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K242" t="str">
-        <v>images/megabass_lures/SLOWL FEATHER HOOK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/SLOWL%20FEATHER%20HOOK_main.jpg</v>
       </c>
       <c r="L242" t="str">
         <v/>
@@ -11809,7 +11809,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K243" t="str">
-        <v>images/megabass_lures/TEASER HOOK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/TEASER%20HOOK_main.jpg</v>
       </c>
       <c r="L243" t="str">
         <v/>
@@ -11856,7 +11856,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K244" t="str">
-        <v>images/megabass_lures/KATSUAGE HOOK_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/KATSUAGE%20HOOK_main.jpg</v>
       </c>
       <c r="L244" t="str">
         <v/>
@@ -11903,7 +11903,7 @@
         <v>variable</v>
       </c>
       <c r="K245" t="str">
-        <v>images/megabass_lures/鬼手仏針_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/%E9%AC%BC%E6%89%8B%E4%BB%8F%E9%87%9D_main.jpg</v>
       </c>
       <c r="L245" t="str">
         <v/>
@@ -11950,7 +11950,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K246" t="str">
-        <v>images/megabass_lures/i-WING 135 SPARE PARTS KIT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_lures/i-WING%20135%20SPARE%20PARTS%20KIT_main.jpg</v>
       </c>
       <c r="L246" t="str">
         <v/>
@@ -11997,7 +11997,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K247" t="str">
-        <v>images/daiwa_lures/ハンクルミノー -スティーズカスタム-HMKL MINNOW - STEEZ CUSTOM -_HMKLMinnow-SteezCustom_AdelWakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%8F%E3%83%B3%E3%82%AF%E3%83%AB%E3%83%9F%E3%83%8E%E3%83%BC%20-%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0-HMKL%20MINNOW%20-%20STEEZ%20CUSTOM%20-_HMKLMinnow-SteezCustom_AdelWakasagi.jpg</v>
       </c>
       <c r="L247" t="str">
         <v/>
@@ -12044,7 +12044,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K248" t="str">
-        <v>images/daiwa_lures/スティーズクランポSTEEZ CRANPO_STEEZ_CRANPO_81F_KAERU_4550133580918.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AF%E3%83%A9%E3%83%B3%E3%83%9DSTEEZ%20CRANPO_STEEZ_CRANPO_81F_KAERU_4550133580918.jpg</v>
       </c>
       <c r="L248" t="str">
         <v/>
@@ -12138,7 +12138,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K250" t="str">
-        <v>images/daiwa_lures/スティーズプロップSTEEZ PROP_SteezProp_70F_Kurokin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%97%E3%83%AD%E3%83%83%E3%83%97STEEZ%20PROP_SteezProp_70F_Kurokin.jpg</v>
       </c>
       <c r="L250" t="str">
         <v/>
@@ -12185,7 +12185,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K251" t="str">
-        <v>images/daiwa_lures/スティーズ スプーンSTEEZ SPOON_SteezSpoon_Hasu.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%83%97%E3%83%BC%E3%83%B3STEEZ%20SPOON_SteezSpoon_Hasu.png</v>
       </c>
       <c r="L251" t="str">
         <v/>
@@ -12232,7 +12232,7 @@
         <v>glide</v>
       </c>
       <c r="K252" t="str">
-        <v>images/daiwa_lures/スティーズ アプナスジョイントSTEEZ APNAS JOINT_CHART_4550133464942.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%A2%E3%83%97%E3%83%8A%E3%82%B9%E3%82%B8%E3%83%A7%E3%82%A4%E3%83%B3%E3%83%88STEEZ%20APNAS%20JOINT_CHART_4550133464942.jpg</v>
       </c>
       <c r="L252" t="str">
         <v/>
@@ -12279,7 +12279,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K253" t="str">
-        <v>images/daiwa_lures/スティーズクランクSTEEZ CRANK_22STEEZ_CRANK_700_MATTE_HOLO_WAKASAGI_4550133507472.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AF%E3%83%A9%E3%83%B3%E3%82%AFSTEEZ%20CRANK_22STEEZ_CRANK_700_MATTE_HOLO_WAKASAGI_4550133507472.jpg</v>
       </c>
       <c r="L253" t="str">
         <v/>
@@ -12326,7 +12326,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K254" t="str">
-        <v>images/daiwa_lures/バンクフラッターBANK FLUTTER_BankFlutter_ChartBack_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%90%E3%83%B3%E3%82%AF%E3%83%95%E3%83%A9%E3%83%83%E3%82%BF%E3%83%BCBANK%20FLUTTER_BankFlutter_ChartBack_1.jpg</v>
       </c>
       <c r="L254" t="str">
         <v/>
@@ -12373,7 +12373,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K255" t="str">
-        <v>images/daiwa_lures/DジャークベイトD-JERKBAIT_D-JERKBAIT112F_SR-LI_LI_WAKASAGI_4550133665271.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/D%E3%82%B8%E3%83%A3%E3%83%BC%E3%82%AF%E3%83%99%E3%82%A4%E3%83%88D-JERKBAIT_D-JERKBAIT112F_SR-LI_LI_WAKASAGI_4550133665271.jpg</v>
       </c>
       <c r="L255" t="str">
         <v/>
@@ -12420,7 +12420,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K256" t="str">
-        <v>images/daiwa_lures/スティーズ ツインバズSTEEZ TWIN BUZZ_STEEZ_TWIN_BUZZ_1-4OZ_MATTE_BLACK_4550133583315.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%84%E3%82%A4%E3%83%B3%E3%83%90%E3%82%BASTEEZ%20TWIN%20BUZZ_STEEZ_TWIN_BUZZ_1-4OZ_MATTE_BLACK_4550133583315.jpg</v>
       </c>
       <c r="L256" t="str">
         <v/>
@@ -12467,7 +12467,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K257" t="str">
-        <v>images/daiwa_lures/スティーズ ダブルクラッチSTEEZ DOUBLE CLUTCH_SteezDoubleClutch_75SP_IPWakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81STEEZ%20DOUBLE%20CLUTCH_SteezDoubleClutch_75SP_IPWakasagi.jpg</v>
       </c>
       <c r="L257" t="str">
         <v/>
@@ -12514,7 +12514,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K258" t="str">
-        <v>images/daiwa_lures/ちびふく零  ふく零  だいふく零CHIBI FUKU ZERO  FUKU ZERO  DAIFUKU ZERO_FukuZero_ChartBackBN.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%A1%E3%81%B3%E3%81%B5%E3%81%8F%E9%9B%B6%20%20%E3%81%B5%E3%81%8F%E9%9B%B6%20%20%E3%81%A0%E3%81%84%E3%81%B5%E3%81%8F%E9%9B%B6CHIBI%20FUKU%20ZERO%20%20FUKU%20ZERO%20%20DAIFUKU%20ZERO_FukuZero_ChartBackBN.jpg</v>
       </c>
       <c r="L258" t="str">
         <v/>
@@ -12561,7 +12561,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K259" t="str">
-        <v>images/daiwa_lures/T.D.ハイパークランクT.D.HYPER CRANK_TD_HyperCrank_1064Ti_B-2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/T.D.%E3%83%8F%E3%82%A4%E3%83%91%E3%83%BC%E3%82%AF%E3%83%A9%E3%83%B3%E3%82%AFT.D.HYPER%20CRANK_TD_HyperCrank_1064Ti_B-2.jpg</v>
       </c>
       <c r="L259" t="str">
         <v/>
@@ -12608,7 +12608,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K260" t="str">
-        <v>images/daiwa_lures/スティーズバズベイトSTEEZ BUZZ BAIT_STEEZ_BUZZ_BAIT_1-2OZ_MATTE_BLACK_4550133578342.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%90%E3%82%BA%E3%83%99%E3%82%A4%E3%83%88STEEZ%20BUZZ%20BAIT_STEEZ_BUZZ_BAIT_1-2OZ_MATTE_BLACK_4550133578342.jpg</v>
       </c>
       <c r="L260" t="str">
         <v/>
@@ -12655,7 +12655,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K261" t="str">
-        <v>images/daiwa_lures/スティーズ ポッパーSTEEZ POPPER_STEEZ_POPPER_60F_RW_UMEKYO_ORANGE_4550133589317.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%9D%E3%83%83%E3%83%91%E3%83%BCSTEEZ%20POPPER_STEEZ_POPPER_60F_RW_UMEKYO_ORANGE_4550133589317.jpg</v>
       </c>
       <c r="L261" t="str">
         <v/>
@@ -12702,7 +12702,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K262" t="str">
-        <v>images/daiwa_lures/タイニースティーズクランクTINY STEEZ CRANK_TINY_STEEZ_CRANK_200_CITRUS_SHAD_4550133509193.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%BF%E3%82%A4%E3%83%8B%E3%83%BC%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AF%E3%83%A9%E3%83%B3%E3%82%AFTINY%20STEEZ%20CRANK_TINY_STEEZ_CRANK_200_CITRUS_SHAD_4550133509193.jpg</v>
       </c>
       <c r="L262" t="str">
         <v/>
@@ -12749,7 +12749,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K263" t="str">
-        <v>images/daiwa_lures/ドラウンシケーダ REV JrDROWN CICADA REV Jr_DROWN_CICADA_REV_CLEAR_BROWN_4550133081736.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%89%E3%83%A9%E3%82%A6%E3%83%B3%E3%82%B7%E3%82%B1%E3%83%BC%E3%83%80%20REV%20JrDROWN%20CICADA%20REV%20Jr_DROWN_CICADA_REV_CLEAR_BROWN_4550133081736.jpg</v>
       </c>
       <c r="L263" t="str">
         <v/>
@@ -12796,7 +12796,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K264" t="str">
-        <v>images/daiwa_lures/T.D.ミノーT.D. MINNOW_TDMinnow_95SP_GhostAyu.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/T.D.%E3%83%9F%E3%83%8E%E3%83%BCT.D.%20MINNOW_TDMinnow_95SP_GhostAyu.jpg</v>
       </c>
       <c r="L264" t="str">
         <v/>
@@ -12843,7 +12843,7 @@
         <v>variable</v>
       </c>
       <c r="K265" t="str">
-        <v>images/daiwa_lures/スティーズ シャッドSTEEZ SHAD_SteezShad_54SPMR_Wakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89STEEZ%20SHAD_SteezShad_54SPMR_Wakasagi.jpg</v>
       </c>
       <c r="L265" t="str">
         <v/>
@@ -12890,7 +12890,7 @@
         <v>variable</v>
       </c>
       <c r="K266" t="str">
-        <v>images/daiwa_lures/スティーズ サイレントシャッドSTEEZ SILENT SHAD_STEEZ_SILENT_SHAD_54SP_SR_AKABANE_SHAD_4550133404993.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B5%E3%82%A4%E3%83%AC%E3%83%B3%E3%83%88%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89STEEZ%C2%A0SILENT%C2%A0SHAD_STEEZ_SILENT_SHAD_54SP_SR_AKABANE_SHAD_4550133404993.jpg</v>
       </c>
       <c r="L266" t="str">
         <v/>
@@ -12937,7 +12937,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K267" t="str">
-        <v>images/daiwa_lures/スティーズスクエアSTEEZ SQUARE_25STEEZ_SQUARE_100_BLUE_BACK_CHART_4550133580994.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%B9%E3%82%AF%E3%82%A8%E3%82%A2STEEZ%20SQUARE_25STEEZ_SQUARE_100_BLUE_BACK_CHART_4550133580994.jpg</v>
       </c>
       <c r="L267" t="str">
         <v/>
@@ -12984,7 +12984,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K268" t="str">
-        <v>images/daiwa_lures/ドラウンドラゴンフライDROWN DRAGONFLY_DROWNDRAGONFLY_ONIYANMA_4550133472619.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%89%E3%83%A9%E3%82%A6%E3%83%B3%E3%83%89%E3%83%A9%E3%82%B4%E3%83%B3%E3%83%95%E3%83%A9%E3%82%A4DROWN%20DRAGONFLY_DROWNDRAGONFLY_ONIYANMA_4550133472619.jpg</v>
       </c>
       <c r="L268" t="str">
         <v/>
@@ -13078,7 +13078,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K270" t="str">
-        <v>images/daiwa_lures/ギルネードGILLNADO_Gillnado50S_SightKurokin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AE%E3%83%AB%E3%83%8D%E3%83%BC%E3%83%89GILLNADO_Gillnado50S_SightKurokin.jpg</v>
       </c>
       <c r="L270" t="str">
         <v/>
@@ -13125,7 +13125,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K271" t="str">
-        <v>images/daiwa_lures/ガストネードGUSTNADO_GUSTNADO55S_SIGHT_SHINER_4550133307324.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AC%E3%82%B9%E3%83%88%E3%83%8D%E3%83%BC%E3%83%89GUSTNADO_GUSTNADO55S_SIGHT_SHINER_4550133307324.jpg</v>
       </c>
       <c r="L271" t="str">
         <v/>
@@ -13172,7 +13172,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K272" t="str">
-        <v>images/daiwa_lures/スティーズ アスロックSTEEZ ASROC_SteezAsroc_SliverWhite.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%A2%E3%82%B9%E3%83%AD%E3%83%83%E3%82%AFSTEEZ%20ASROC_SteezAsroc_SliverWhite.jpg</v>
       </c>
       <c r="L272" t="str">
         <v/>
@@ -13219,7 +13219,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K273" t="str">
-        <v>images/daiwa_lures/スティーズ スピナーベイトSTEEZ SPINNER BAIT_STEEZ_SPINNER_BAIT_38OZ_TW_SILVER_WHITE.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%83%94%E3%83%8A%E3%83%BC%E3%83%99%E3%82%A4%E3%83%88STEEZ%20SPINNER%20BAIT_STEEZ_SPINNER_BAIT_38OZ_TW_SILVER_WHITE.jpg</v>
       </c>
       <c r="L273" t="str">
         <v/>
@@ -13266,7 +13266,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K274" t="str">
-        <v>images/daiwa_lures/ふく平FUKU HIRA_FUKU_HIRA_CITRUS_CHART_4550133559686.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%B5%E3%81%8F%E5%B9%B3FUKU%20HIRA_FUKU_HIRA_CITRUS_CHART_4550133559686.jpg</v>
       </c>
       <c r="L274" t="str">
         <v/>
@@ -13313,7 +13313,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K275" t="str">
-        <v>images/daiwa_lures/ふく弐FUKU 2_FUKU_2_CITRUS_CHART_4550133581090.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%B5%E3%81%8F%E5%BC%90FUKU%202_FUKU_2_CITRUS_CHART_4550133581090.jpg</v>
       </c>
       <c r="L275" t="str">
         <v/>
@@ -13360,7 +13360,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K276" t="str">
-        <v>images/daiwa_lures/スティーズイグラSTEEZ IGLA_STEEZ_IGLA_14OZ_TYPE_INDIANA_SILVER_WHITE_4550133566738.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%A4%E3%82%B0%E3%83%A9STEEZ%20IGLA_STEEZ_IGLA_14OZ_TYPE_INDIANA_SILVER_WHITE_4550133566738.jpg</v>
       </c>
       <c r="L276" t="str">
         <v/>
@@ -13407,7 +13407,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K277" t="str">
-        <v>images/daiwa_lures/スティーズ ペンシルSTEEZ PENCIL_SteezPencil_60F_Wakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%9A%E3%83%B3%E3%82%B7%E3%83%ABSTEEZ%20PENCIL_SteezPencil_60F_Wakasagi.jpg</v>
       </c>
       <c r="L277" t="str">
         <v/>
@@ -13454,7 +13454,7 @@
         <v>variable</v>
       </c>
       <c r="K278" t="str">
-        <v>images/daiwa_lures/ちびふくシャッド弐  ふくシャッド弐CHIBI FUKU SHAD 2  FUKU SHAD 2_FUKU_SHAD_2_CITRUS_CHART_4550133504716.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%A1%E3%81%B3%E3%81%B5%E3%81%8F%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89%E5%BC%90%20%20%E3%81%B5%E3%81%8F%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89%E5%BC%90CHIBI%20FUKU%20SHAD%202%20%20FUKU%20SHAD%202_FUKU_SHAD_2_CITRUS_CHART_4550133504716.jpg</v>
       </c>
       <c r="L278" t="str">
         <v/>
@@ -13501,7 +13501,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K279" t="str">
-        <v>images/daiwa_lures/スティーズ カバーチャターSTEEZ COVER CHATTER_25STEEZ_COVER_CHATTER_3-8_BLACK_4550133578205.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%AB%E3%83%90%E3%83%BC%E3%83%81%E3%83%A3%E3%82%BF%E3%83%BCSTEEZ%20COVER%20CHATTER_25STEEZ_COVER_CHATTER_3-8_BLACK_4550133578205.jpg</v>
       </c>
       <c r="L279" t="str">
         <v/>
@@ -13548,7 +13548,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K280" t="str">
-        <v>images/daiwa_lures/ふく壱  ちびふく壱FUKU ICHI  CHIBI FUKU ICHI_FukuIchi_Torafugu.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%B5%E3%81%8F%E5%A3%B1%20%20%E3%81%A1%E3%81%B3%E3%81%B5%E3%81%8F%E5%A3%B1FUKU%20ICHI%20%20CHIBI%20FUKU%20ICHI_FukuIchi_Torafugu.jpg</v>
       </c>
       <c r="L280" t="str">
         <v/>
@@ -13595,7 +13595,7 @@
         <v>vibration</v>
       </c>
       <c r="K281" t="str">
-        <v>images/daiwa_lures/スティーズメタルバイブスリムSTEEZ METAL VIB SLIM_STEEZ_METAL_VIB_SLIM_8G_ADEL_WAKASAGI_4550133447464.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%A1%E3%82%BF%E3%83%AB%E3%83%90%E3%82%A4%E3%83%96%E3%82%B9%E3%83%AA%E3%83%A0STEEZ%20METAL%20VIB%20SLIM_STEEZ_METAL_VIB_SLIM_8G_ADEL_WAKASAGI_4550133447464.jpg</v>
       </c>
       <c r="L281" t="str">
         <v/>
@@ -13689,7 +13689,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K283" t="str">
-        <v>images/daiwa_lures/カシューナッツCASHEW NUT_CASHEW_NUTS_KUROKIN_4550133567131.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AB%E3%82%B7%E3%83%A5%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84CASHEW%20NUT_CASHEW_NUTS_KUROKIN_4550133567131.jpg</v>
       </c>
       <c r="L283" t="str">
         <v/>
@@ -13736,7 +13736,7 @@
         <v>vibration</v>
       </c>
       <c r="K284" t="str">
-        <v>images/daiwa_lures/T.D.バイブレーションT.D.VIBRATION_TD_Vibration_74S_Wakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/T.D.%E3%83%90%E3%82%A4%E3%83%96%E3%83%AC%E3%83%BC%E3%82%B7%E3%83%A7%E3%83%B3T.D.VIBRATION_TD_Vibration_74S_Wakasagi.jpg</v>
       </c>
       <c r="L284" t="str">
         <v/>
@@ -13783,7 +13783,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K285" t="str">
-        <v>images/daiwa_lures/ラトリンチューブキックスRATTLIN' TUBE KICKS_4_SnowWhiteShrimp.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%A9%E3%83%88%E3%83%AA%E3%83%B3%E3%83%81%E3%83%A5%E3%83%BC%E3%83%96%E3%82%AD%E3%83%83%E3%82%AF%E3%82%B9RATTLIN'%20TUBE%20KICKS_4_SnowWhiteShrimp.jpg</v>
       </c>
       <c r="L285" t="str">
         <v/>
@@ -13830,7 +13830,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K286" t="str">
-        <v>images/daiwa_lures/ワイルドピーナッツ  タイニーワイルドピーナッツWILD PEANUT  TINY WILD PEANUT_WildPeanut_KinkirakinCraw.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%AF%E3%82%A4%E3%83%AB%E3%83%89%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84%20%20%E3%82%BF%E3%82%A4%E3%83%8B%E3%83%BC%E3%83%AF%E3%82%A4%E3%83%AB%E3%83%89%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84WILD%20PEANUT%20%20TINY%20WILD%20PEANUT_WildPeanut_KinkirakinCraw.jpg</v>
       </c>
       <c r="L286" t="str">
         <v/>
@@ -13877,7 +13877,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K287" t="str">
-        <v>images/daiwa_lures/アーモンドALMOND_ALMOND_KUROKIN_4550133566639.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%A2%E3%83%BC%E3%83%A2%E3%83%B3%E3%83%89ALMOND_ALMOND_KUROKIN_4550133566639.jpg</v>
       </c>
       <c r="L287" t="str">
         <v/>
@@ -13924,7 +13924,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K288" t="str">
-        <v>images/daiwa_lures/スティーズ ブラーモSTEEZ BRAMO_7_GREEN-PUMPKIN_4550133457630.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%96%E3%83%A9%E3%83%BC%E3%83%A2STEEZ%20BRAMO_7_GREEN-PUMPKIN_4550133457630.jpg</v>
       </c>
       <c r="L288" t="str">
         <v/>
@@ -13971,7 +13971,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K289" t="str">
-        <v>images/daiwa_lures/デカピーナッツ IIDEKA PEANUT II_DekaPeanutII_SSR_BlackChartBerry.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%87%E3%82%AB%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84%20IIDEKA%20PEANUT%20II_DekaPeanutII_SSR_BlackChartBerry.jpg</v>
       </c>
       <c r="L289" t="str">
         <v/>
@@ -14018,7 +14018,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K290" t="str">
-        <v>images/daiwa_lures/ピーナッツPEANUT_Peanut_SR_SexyShad.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84PEANUT_Peanut_SR_SexyShad.jpg</v>
       </c>
       <c r="L290" t="str">
         <v/>
@@ -14065,7 +14065,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K291" t="str">
-        <v>images/daiwa_lures/スティーズバンクハッカークローSTEEZ BANK HACKER CRAW_STEEZ_BANK_HACKER_CLAW_GREEN_PUMPKIN_4550133566899.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%90%E3%83%B3%E3%82%AF%E3%83%8F%E3%83%83%E3%82%AB%E3%83%BC%E3%82%AF%E3%83%AD%E3%83%BCSTEEZ%20BANK%20HACKER%20CRAW_STEEZ_BANK_HACKER_CLAW_GREEN_PUMPKIN_4550133566899.jpg</v>
       </c>
       <c r="L291" t="str">
         <v/>
@@ -14112,7 +14112,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K292" t="str">
-        <v>images/daiwa_lures/ムーブベイトMOVE BAIT_MoveBait_31_GreenPumpkin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%A0%E3%83%BC%E3%83%96%E3%83%99%E3%82%A4%E3%83%88MOVE%20BAIT_MoveBait_31_GreenPumpkin.jpg</v>
       </c>
       <c r="L292" t="str">
         <v/>
@@ -14159,7 +14159,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K293" t="str">
-        <v>images/daiwa_lures/タイニーピーナッツTINY PEANUT_TinyPeanuts_SR_KuroKin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%BF%E3%82%A4%E3%83%8B%E3%83%BC%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84TINY%20PEANUT_TinyPeanuts_SR_KuroKin.jpg</v>
       </c>
       <c r="L293" t="str">
         <v/>
@@ -14206,7 +14206,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K294" t="str">
-        <v>images/daiwa_lures/スティーズクローSTEEZ CRAW_1_GREEN_PUMPKIN_4550133464546.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AF%E3%83%AD%E3%83%BCSTEEZ%20CRAW_1_GREEN_PUMPKIN_4550133464546.jpg</v>
       </c>
       <c r="L294" t="str">
         <v/>
@@ -14253,7 +14253,7 @@
         <v>variable</v>
       </c>
       <c r="K295" t="str">
-        <v>images/daiwa_lures/ムーブホグMOVE HOG_3_GREEN_PUMPKIN_4550133566974.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%A0%E3%83%BC%E3%83%96%E3%83%9B%E3%82%B0MOVE%20HOG_3_GREEN_PUMPKIN_4550133566974.jpg</v>
       </c>
       <c r="L295" t="str">
         <v/>
@@ -14300,7 +14300,7 @@
         <v>glide</v>
       </c>
       <c r="K296" t="str">
-        <v>images/daiwa_lures/スティーズ アプナスバグSTEEZ APNAS BUG_STEEZ-APNAS-BUG-GREEN-PUMPKIN-BLUE-FLAKE_4550133465024.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%A2%E3%83%97%E3%83%8A%E3%82%B9%E3%83%90%E3%82%B0STEEZ%20APNAS%20BUG_STEEZ-APNAS-BUG-GREEN-PUMPKIN-BLUE-FLAKE_4550133465024.jpg</v>
       </c>
       <c r="L296" t="str">
         <v/>
@@ -14347,7 +14347,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K297" t="str">
-        <v>images/daiwa_lures/スティーズ ポップクラッカーSTEEZ POP CRACKER_1_NUDE_BROWN_4550133354410.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%9D%E3%83%83%E3%83%97%E3%82%AF%E3%83%A9%E3%83%83%E3%82%AB%E3%83%BCSTEEZ%20POP%20CRACKER_1_NUDE_BROWN_4550133354410.jpg</v>
       </c>
       <c r="L297" t="str">
         <v/>
@@ -14394,7 +14394,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K298" t="str">
-        <v>images/daiwa_lures/スティーズ スターリングフィッシュSTEEZ STIRRING FISH_3_BIWAKO_AYU_4550133399077.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%82%BF%E3%83%BC%E3%83%AA%E3%83%B3%E3%82%B0%E3%83%95%E3%82%A3%E3%83%83%E3%82%B7%E3%83%A5STEEZ%20STIRRING%20FISH_3_BIWAKO_AYU_4550133399077.jpg</v>
       </c>
       <c r="L298" t="str">
         <v/>
@@ -14441,7 +14441,7 @@
         <v>variable</v>
       </c>
       <c r="K299" t="str">
-        <v>images/daiwa_lures/シュリンピード／シュリンピードJr.SHRIMPEDE／SHRIMPEDE Jr._Shrimpede_GreenPumpkin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%A5%E3%83%AA%E3%83%B3%E3%83%94%E3%83%BC%E3%83%89%EF%BC%8F%E3%82%B7%E3%83%A5%E3%83%AA%E3%83%B3%E3%83%94%E3%83%BC%E3%83%89Jr.SHRIMPEDE%EF%BC%8FSHRIMPEDE%20Jr._Shrimpede_GreenPumpkin.jpg</v>
       </c>
       <c r="L299" t="str">
         <v/>
@@ -14488,7 +14488,7 @@
         <v>variable</v>
       </c>
       <c r="K300" t="str">
-        <v>images/daiwa_lures/キッケルカーリーKIKKER CURLY_melon_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AD%E3%83%83%E3%82%B1%E3%83%AB%E3%82%AB%E3%83%BC%E3%83%AA%E3%83%BCKIKKER%20CURLY_melon_1.jpg</v>
       </c>
       <c r="L300" t="str">
         <v/>
@@ -14535,7 +14535,7 @@
         <v>variable</v>
       </c>
       <c r="K301" t="str">
-        <v>images/daiwa_lures/スティーズネコストレートSTEEZ NEKO STRAIGHT_75_GREEN_PUMPKIN_BLUE_FLAKE_4550133564222.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%8D%E3%82%B3%E3%82%B9%E3%83%88%E3%83%AC%E3%83%BC%E3%83%88STEEZ%20NEKO%20STRAIGHT_75_GREEN_PUMPKIN_BLUE_FLAKE_4550133564222.jpg</v>
       </c>
       <c r="L301" t="str">
         <v/>
@@ -14582,7 +14582,7 @@
         <v>variable</v>
       </c>
       <c r="K302" t="str">
-        <v>images/daiwa_lures/スティーズ ホグSTEEZ HOG_SteezHog_GreenPumpkin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%9B%E3%82%B0STEEZ%20HOG_SteezHog_GreenPumpkin.jpg</v>
       </c>
       <c r="L302" t="str">
         <v/>
@@ -14629,7 +14629,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K303" t="str">
-        <v>images/daiwa_lures/スティーズ パワーフィネスジグSTEEZ POWERFINESSEJIG_5G_GREEN_PUMPKIM_BLUE_FLAKE_4550133464140.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%91%E3%83%AF%E3%83%BC%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%E3%82%B8%E3%82%B0STEEZ%20POWERFINESSEJIG_5G_GREEN_PUMPKIM_BLUE_FLAKE_4550133464140.jpg</v>
       </c>
       <c r="L303" t="str">
         <v/>
@@ -14676,7 +14676,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K304" t="str">
-        <v>images/daiwa_lures/スティーズ リアルスラッガーSTEEZ REAL SLUGGER_7-SILVER-WAKASAGI_4550133448171.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%AA%E3%82%A2%E3%83%AB%E3%82%B9%E3%83%A9%E3%83%83%E3%82%AC%E3%83%BCSTEEZ%20REAL%20SLUGGER_7-SILVER-WAKASAGI_4550133448171.jpg</v>
       </c>
       <c r="L304" t="str">
         <v/>
@@ -14723,7 +14723,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K305" t="str">
-        <v>images/daiwa_lures/スティーズ　ネコファットSTEEZ NEKO FAT_2_GREEN_PUMPKIN_4550133614842.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%80%80%E3%83%8D%E3%82%B3%E3%83%95%E3%82%A1%E3%83%83%E3%83%88STEEZ%20NEKO%20FAT_2_GREEN_PUMPKIN_4550133614842.jpg</v>
       </c>
       <c r="L305" t="str">
         <v/>
@@ -14770,7 +14770,7 @@
         <v>variable</v>
       </c>
       <c r="K306" t="str">
-        <v>images/daiwa_lures/スティーズ フィネスストレートSTEEZ FINESSE STRAIGHT_3_YAMA-P_EBIMISO_4550133559853.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%E3%82%B9%E3%83%88%E3%83%AC%E3%83%BC%E3%83%88STEEZ%20FINESSE%20STRAIGHT_3_YAMA-P_EBIMISO_4550133559853.jpg</v>
       </c>
       <c r="L306" t="str">
         <v/>
@@ -14817,7 +14817,7 @@
         <v>variable</v>
       </c>
       <c r="K307" t="str">
-        <v>images/daiwa_lures/スティーズネコストレートロングSTEEZ NEKO STRAIGHT LONG_STEEZ_NEKO_STRAIGHT_LONG_9_MIMIZU_4550133536052.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%8D%E3%82%B3%E3%82%B9%E3%83%88%E3%83%AC%E3%83%BC%E3%83%88%E3%83%AD%E3%83%B3%E3%82%B0STEEZ%20NEKO%20STRAIGHT%20LONG_STEEZ_NEKO_STRAIGHT_LONG_9_MIMIZU_4550133536052.jpg</v>
       </c>
       <c r="L307" t="str">
         <v/>
@@ -14864,7 +14864,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K308" t="str">
-        <v>images/daiwa_lures/スティーズ スターリングツインSTEEZ STIRRING TWIN_STEEZStirringTwin_GreenPumpkin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%82%BF%E3%83%BC%E3%83%AA%E3%83%B3%E3%82%B0%E3%83%84%E3%82%A4%E3%83%B3STEEZ%20STIRRING%20TWIN_STEEZStirringTwin_GreenPumpkin.jpg</v>
       </c>
       <c r="L308" t="str">
         <v/>
@@ -14911,7 +14911,7 @@
         <v>variable</v>
       </c>
       <c r="K309" t="str">
-        <v>images/daiwa_lures/スティーズ スターリングシャッドSTEEZ STIRRING SHAD_SteezStirringShad_28_MagicShad.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%82%BF%E3%83%BC%E3%83%AA%E3%83%B3%E3%82%B0%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89STEEZ%20STIRRING%20SHAD_SteezStirringShad_28_MagicShad.jpg</v>
       </c>
       <c r="L309" t="str">
         <v/>
@@ -14958,7 +14958,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K310" t="str">
-        <v>images/daiwa_lures/BHカバージグBH COVER JIG_BH_COVER_JIG_10G_BLACK_4550133506192.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%82%AB%E3%83%90%E3%83%BC%E3%82%B8%E3%82%B0BH%20COVER%20JIG_BH_COVER_JIG_10G_BLACK_4550133506192.jpg</v>
       </c>
       <c r="L310" t="str">
         <v/>
@@ -15005,7 +15005,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K311" t="str">
-        <v>images/daiwa_lures/BHマルチジグBH MULTI JIG_BH_MULTI_JIG_10G_BLACK_4550133505089.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%83%9E%E3%83%AB%E3%83%81%E3%82%B8%E3%82%B0BH%20MULTI%20JIG_BH_MULTI_JIG_10G_BLACK_4550133505089.jpg</v>
       </c>
       <c r="L311" t="str">
         <v/>
@@ -15052,7 +15052,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K312" t="str">
-        <v>images/daiwa_lures/スティーズ パワーフィネスジグ TYPEカバーSTEEZ POWERFINESSEJIG TYPECOVER_7G-GREEN-PUMPKIM-BULE-FLAKE_4550133464461.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%91%E3%83%AF%E3%83%BC%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%E3%82%B8%E3%82%B0%20TYPE%E3%82%AB%E3%83%90%E3%83%BCSTEEZ%20POWERFINESSEJIG%20TYPECOVER_7G-GREEN-PUMPKIM-BULE-FLAKE_4550133464461.jpg</v>
       </c>
       <c r="L312" t="str">
         <v/>
@@ -15099,7 +15099,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K313" t="str">
-        <v>images/daiwa_lures/BHジグスピナーBH JIG SPINNER_BH_JIG_SPINNER_7_WAKASAGI_4550133508424.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%82%B8%E3%82%B0%E3%82%B9%E3%83%94%E3%83%8A%E3%83%BCBH%20JIG%20SPINNER_BH_JIG_SPINNER_7_WAKASAGI_4550133508424.jpg</v>
       </c>
       <c r="L313" t="str">
         <v/>
@@ -15146,7 +15146,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K314" t="str">
-        <v>images/daiwa_lures/BHミニジグBH MINI JIG_2G_GREEN_PUMPKIN_4550133505812.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%83%9F%E3%83%8B%E3%82%B8%E3%82%B0BH%20MINI%20JIG_2G_GREEN_PUMPKIN_4550133505812.jpg</v>
       </c>
       <c r="L314" t="str">
         <v/>
@@ -15193,7 +15193,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K315" t="str">
-        <v>images/daiwa_lures/シルバークリークミノージョイントSILVER CREEK MINNOW JOINT_SILVER_CREEK_MINNOW_JOINT_50S_CHART_YAMAME_OB_4550133460609.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BC%E3%82%B8%E3%83%A7%E3%82%A4%E3%83%B3%E3%83%88SILVER%20CREEK%20MINNOW%20JOINT_SILVER_CREEK_MINNOW_JOINT_50S_CHART_YAMAME_OB_4550133460609.jpg</v>
       </c>
       <c r="L315" t="str">
         <v/>
@@ -15240,7 +15240,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K316" t="str">
-        <v>images/daiwa_lures/シルバークリークミノーSILVER CREEK MINNOW_SilverCreekMinnow_40S_Akakin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BCSILVER%20CREEK%20MINNOW_SilverCreekMinnow_40S_Akakin.jpg</v>
       </c>
       <c r="L316" t="str">
         <v/>
@@ -15287,7 +15287,7 @@
         <v>vibration</v>
       </c>
       <c r="K317" t="str">
-        <v>images/daiwa_lures/BHメタルバイブBH METAL VIB_BH_METAL_VIB_5G_WAKASAGI_4550133508790.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%83%A1%E3%82%BF%E3%83%AB%E3%83%90%E3%82%A4%E3%83%96BH%20METAL%20VIB_BH_METAL_VIB_5G_WAKASAGI_4550133508790.jpg</v>
       </c>
       <c r="L317" t="str">
         <v/>
@@ -15334,7 +15334,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K318" t="str">
-        <v>images/daiwa_lures/ダブルクラッチF1 C&amp;R カスタムDOUBLECLUTCH F1 C&amp;R CUSTOM_DOUBLECLUTCH45F1CRCUSTOMCHARTYAMAMEORANGEBELLY4550133564703.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81F1%20C%26R%20%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0DOUBLECLUTCH%20F1%20C%26R%20CUSTOM_DOUBLECLUTCH45F1CRCUSTOMCHARTYAMAMEORANGEBELLY4550133564703.jpg</v>
       </c>
       <c r="L318" t="str">
         <v/>
@@ -15381,7 +15381,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K319" t="str">
-        <v>images/daiwa_lures/シルバークリークミノーTGSILVER CREEK MINNOW TG_SILVER_CREEK_MINNOW_TG_50S-LI_LI_CHART_YAMAME_4550133687860.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BCTGSILVER%20CREEK%20MINNOW%20TG_SILVER_CREEK_MINNOW_TG_50S-LI_LI_CHART_YAMAME_4550133687860.jpg</v>
       </c>
       <c r="L319" t="str">
         <v/>
@@ -15428,7 +15428,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K320" t="str">
-        <v>images/daiwa_lures/シルバークリークミノーダートカスタムSILVER CREEK MINNOW DART CUSTOM_SilverCreekMinnowDartCustom_48S_Yamame.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BC%E3%83%80%E3%83%BC%E3%83%88%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0SILVER%20CREEK%20MINNOW%20DART%20CUSTOM_SilverCreekMinnowDartCustom_48S_Yamame.jpg</v>
       </c>
       <c r="L320" t="str">
         <v/>
@@ -15475,7 +15475,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K321" t="str">
-        <v>images/daiwa_lures/ワブクラ30DR  C&amp;R カスタムWABCRA30DR C&amp;R CUSTOM_WABCRA30DRCRCUSTOMCHARTYAMAMEORANGEBELLY4550133564765.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%AF%E3%83%96%E3%82%AF%E3%83%A930DR%20%20C%26R%20%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0WABCRA30DR%20C%26R%20CUSTOM_WABCRA30DRCRCUSTOMCHARTYAMAMEORANGEBELLY4550133564765.jpg</v>
       </c>
       <c r="L321" t="str">
         <v/>
@@ -15522,7 +15522,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K322" t="str">
-        <v>images/daiwa_lures/ドクターミノーIIジョイントDr.MINNOW II JOINT_DrMinnow2J_50S_Yamame.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9F%E3%83%8E%E3%83%BCII%E3%82%B8%E3%83%A7%E3%82%A4%E3%83%B3%E3%83%88Dr.MINNOW%20II%20JOINT_DrMinnow2J_50S_Yamame.jpg</v>
       </c>
       <c r="L322" t="str">
         <v/>
@@ -15569,7 +15569,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K323" t="str">
-        <v>images/daiwa_lures/シルバークリークミノーダイビングカスタムSILVER CREEK MINNOW DIVING CUSTOM_SilverCreekMinnowDivingCustom50FS_ChartYamameOB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BC%E3%83%80%E3%82%A4%E3%83%93%E3%83%B3%E3%82%B0%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0SILVER%20CREEK%20MINNOW%20DIVING%20CUSTOM_SilverCreekMinnowDivingCustom50FS_ChartYamameOB.jpg</v>
       </c>
       <c r="L323" t="str">
         <v/>
@@ -15616,7 +15616,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K324" t="str">
-        <v>images/daiwa_lures/シルバークリークミノースローフォールカスタムSILVER CREEK MINNOW SLOW FALL CUSTOM_SilverCreekMinnowFallCustom_40SS_ChartYamameOrangeBerry.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BC%E3%82%B9%E3%83%AD%E3%83%BC%E3%83%95%E3%82%A9%E3%83%BC%E3%83%AB%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0SILVER%20CREEK%20MINNOW%20SLOW%20FALL%20CUSTOM_SilverCreekMinnowFallCustom_40SS_ChartYamameOrangeBerry.jpg</v>
       </c>
       <c r="L324" t="str">
         <v/>
@@ -15663,7 +15663,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K325" t="str">
-        <v>images/daiwa_lures/DR.ミノー2DR. MINNOW Ⅱ_MINNOW2_Yamame.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/DR.%E3%83%9F%E3%83%8E%E3%83%BC2DR.%20MINNOW%20%E2%85%A1_MINNOW2_Yamame.jpg</v>
       </c>
       <c r="L325" t="str">
         <v/>
@@ -15710,7 +15710,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K326" t="str">
-        <v>images/daiwa_lures/チヌーク SCHINOOK S_ChinookS_DoPink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%81%E3%83%8C%E3%83%BC%E3%82%AF%20SCHINOOK%20S_ChinookS_DoPink.jpg</v>
       </c>
       <c r="L326" t="str">
         <v/>
@@ -15757,7 +15757,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K327" t="str">
-        <v>images/daiwa_lures/クルセイダー激アツCRUSADER GEKIATSU_CrusaderGekiAtsu_YamameOB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AF%E3%83%AB%E3%82%BB%E3%82%A4%E3%83%80%E3%83%BC%E6%BF%80%E3%82%A2%E3%83%84CRUSADER%20GEKIATSU_CrusaderGekiAtsu_YamameOB.jpg</v>
       </c>
       <c r="L327" t="str">
         <v/>
@@ -15804,7 +15804,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K328" t="str">
-        <v>images/daiwa_lures/Dr.ミノーII エリアチューンDr.MINNOW II AREA TUNE_DrMinnow2AreaTune_42HF_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/Dr.%E3%83%9F%E3%83%8E%E3%83%BCII%20%E3%82%A8%E3%83%AA%E3%82%A2%E3%83%81%E3%83%A5%E3%83%BC%E3%83%B3Dr.MINNOW%20II%20AREA%20TUNE_DrMinnow2AreaTune_42HF_Clear.jpg</v>
       </c>
       <c r="L328" t="str">
         <v/>
@@ -15851,7 +15851,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K329" t="str">
-        <v>images/daiwa_lures/クルセイダーCRUSADER_Crusader_13S_DoPink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AF%E3%83%AB%E3%82%BB%E3%82%A4%E3%83%80%E3%83%BCCRUSADER_Crusader_13S_DoPink.jpg</v>
       </c>
       <c r="L329" t="str">
         <v/>
@@ -15898,7 +15898,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K330" t="str">
-        <v>images/daiwa_lures/チヌーク激アツCHINOOK GEKIATSU_ChinookGekiatsu_4S_YamameOrangeBerry.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%81%E3%83%8C%E3%83%BC%E3%82%AF%E6%BF%80%E3%82%A2%E3%83%84CHINOOK%20GEKIATSU_ChinookGekiatsu_4S_YamameOrangeBerry.jpg</v>
       </c>
       <c r="L330" t="str">
         <v/>
@@ -15945,7 +15945,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K331" t="str">
-        <v>images/daiwa_lures/レーザーチヌークSLASER CHINOOK S_LazerChinookS_17S_YROrangeYamame.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%AC%E3%83%BC%E3%82%B6%E3%83%BC%E3%83%81%E3%83%8C%E3%83%BC%E3%82%AFSLASER%20CHINOOK%20S_LazerChinookS_17S_YROrangeYamame.jpg</v>
       </c>
       <c r="L331" t="str">
         <v/>
@@ -15992,7 +15992,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K332" t="str">
-        <v>images/daiwa_lures/ブレットンBRETTON_Bretton_No3_3g_G.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%96%E3%83%AC%E3%83%83%E3%83%88%E3%83%B3BRETTON_Bretton_No3_3g_G.jpg</v>
       </c>
       <c r="L332" t="str">
         <v/>
@@ -16039,7 +16039,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K333" t="str">
-        <v>images/daiwa_lures/SilverCreek スピナーSILVER CREEK SPINNER_SilverCreekSpinner_30_Mikan.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/SilverCreek%20%E3%82%B9%E3%83%94%E3%83%8A%E3%83%BCSILVER%20CREEK%20SPINNER_SilverCreekSpinner_30_Mikan.jpg</v>
       </c>
       <c r="L333" t="str">
         <v/>
@@ -16086,7 +16086,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K334" t="str">
-        <v>images/daiwa_lures/シルバークリーク スピナーSSSILVER CREEK SPINNER SS_5_CHART_YAMAME_ORANGE_BELLY_4550133494819.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20%E3%82%B9%E3%83%94%E3%83%8A%E3%83%BCSSSILVER%20CREEK%20SPINNER%20SS_5_CHART_YAMAME_ORANGE_BELLY_4550133494819.jpg</v>
       </c>
       <c r="L334" t="str">
         <v/>
@@ -16133,7 +16133,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K335" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 60F1 tuned by HMKLPRESSO DOUBLECLUTCH60F1 tuned by HMKL_PressoDoubleClutch60F1_ToppingFood.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2060F1%20tuned%20by%20HMKLPRESSO%20DOUBLECLUTCH60F1%20tuned%20by%20HMKL_PressoDoubleClutch60F1_ToppingFood.jpg</v>
       </c>
       <c r="L335" t="str">
         <v/>
@@ -16180,7 +16180,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K336" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 60SS tuned by HMKLPRESSO DOUBLE CLUTCH 60SS tuned by HMKL_PressoDoubleClutch60SSTunedByHMKL_WavePink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2060SS%20tuned%20by%20HMKLPRESSO%20DOUBLE%20CLUTCH%2060SS%20tuned%20by%20HMKL_PressoDoubleClutch60SSTunedByHMKL_WavePink.jpg</v>
       </c>
       <c r="L336" t="str">
         <v/>
@@ -16227,7 +16227,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K337" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 45S tuned by HMKLPRESSO DOUBLE CLUTCH 45S tuned by HMKL_PressoDoubleClutch45STunedHMKL_ToppingFood.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2045S%20tuned%20by%20HMKLPRESSO%20DOUBLE%20CLUTCH%2045S%20tuned%20by%20HMKL_PressoDoubleClutch45STunedHMKL_ToppingFood.jpg</v>
       </c>
       <c r="L337" t="str">
         <v/>
@@ -16274,7 +16274,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K338" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 60SHF tuned by HMKLPRESSO DOUBLECLUTCH 60SHF tuned by HMKL_Presso_DoubleClutch_60SHF_ToppingFood.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2060SHF%20tuned%20by%20HMKLPRESSO%20DOUBLECLUTCH%2060SHF%20tuned%20by%20HMKL_Presso_DoubleClutch_60SHF_ToppingFood.jpg</v>
       </c>
       <c r="L338" t="str">
         <v/>
@@ -16321,7 +16321,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K339" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 45F1 tuned by HMKLPRESSO DOUBLECLUTCH45F1 tuned by HMKL_DoubleClutch45F1_ToppingFood.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2045F1%20tuned%20by%20HMKLPRESSO%20DOUBLECLUTCH45F1%20tuned%20by%20HMKL_DoubleClutch45F1_ToppingFood.jpg</v>
       </c>
       <c r="L339" t="str">
         <v/>
@@ -16368,7 +16368,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K340" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 75SS tuned by HMKLPRESSO DOUBLE CLUTCH 75SS tuned by HMKL_PressoDoubleClutch75SSTunedByHMKL_WaveBlack.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2075SS%20tuned%20by%20HMKLPRESSO%20DOUBLE%20CLUTCH%2075SS%20tuned%20by%20HMKL_PressoDoubleClutch75SSTunedByHMKL_WaveBlack.jpg</v>
       </c>
       <c r="L340" t="str">
         <v/>
@@ -16415,7 +16415,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K341" t="str">
-        <v>images/daiwa_lures/プレッソ ワブクラJr.PRESSO WABCRA Jr.__25F_SR_GOMASHIO_GLOW_4550133555824.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AF%E3%83%96%E3%82%AF%E3%83%A9Jr.PRESSO%20WABCRA%20Jr.__25F_SR_GOMASHIO_GLOW_4550133555824.jpg</v>
       </c>
       <c r="L341" t="str">
         <v/>
@@ -16462,7 +16462,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K342" t="str">
-        <v>images/daiwa_lures/プレッソ ワブクラスリムPRESSO WABCRA SLIM_PRESSO_WABCRA_SLIM_39F_SR_CLEAR_4550133556012.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AF%E3%83%96%E3%82%AF%E3%83%A9%E3%82%B9%E3%83%AA%E3%83%A0PRESSO%20WABCRA%20SLIM_PRESSO_WABCRA_SLIM_39F_SR_CLEAR_4550133556012.jpg</v>
       </c>
       <c r="L342" t="str">
         <v/>
@@ -16509,7 +16509,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K343" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 48F tuned by HMKLPRESSO DOUBLECLUTCH 48F tuned by HMKL_PRESSO_DOUBLECLUTCH_48F_TOPPING_FOOD_4550133419829.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2048F%20tuned%20by%20HMKLPRESSO%20DOUBLECLUTCH%2048F%20tuned%20by%20HMKL_PRESSO_DOUBLECLUTCH_48F_TOPPING_FOOD_4550133419829.jpg</v>
       </c>
       <c r="L343" t="str">
         <v/>
@@ -16556,7 +16556,7 @@
         <v>variable</v>
       </c>
       <c r="K344" t="str">
-        <v>images/daiwa_lures/プレッソ メガポッピンバグPRESSO MEGA POPPIN'BUG_PRESSOMEGAPOPPINBUGSAKURAHIMEGROW4550133431647.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%A1%E3%82%AC%E3%83%9D%E3%83%83%E3%83%94%E3%83%B3%E3%83%90%E3%82%B0PRESSO%20MEGA%20POPPIN'BUG_PRESSOMEGAPOPPINBUGSAKURAHIMEGROW4550133431647.jpg</v>
       </c>
       <c r="L344" t="str">
         <v/>
@@ -16650,7 +16650,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K346" t="str">
-        <v>images/daiwa_lures/プレッソ ステップダートPRESSO STEP DART_PressoStepDart_ReactionGold.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%B9%E3%83%86%E3%83%83%E3%83%97%E3%83%80%E3%83%BC%E3%83%88PRESSO%20STEP%20DART_PressoStepDart_ReactionGold.jpg</v>
       </c>
       <c r="L346" t="str">
         <v/>
@@ -16697,7 +16697,7 @@
         <v>variable</v>
       </c>
       <c r="K347" t="str">
-        <v>images/daiwa_lures/プレッソ ポッピンバグ  ラトリンポッピンバグPRESSO POPPIN'BUG  RATLLIN'POPPIN'BUG_PressoPoppinBug_SukeSukeBrownPellet.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%9D%E3%83%83%E3%83%94%E3%83%B3%E3%83%90%E3%82%B0%20%20%E3%83%A9%E3%83%88%E3%83%AA%E3%83%B3%E3%83%9D%E3%83%83%E3%83%94%E3%83%B3%E3%83%90%E3%82%B0PRESSO%20POPPIN'BUG%20%20RATLLIN'POPPIN'BUG_PressoPoppinBug_SukeSukeBrownPellet.jpg</v>
       </c>
       <c r="L347" t="str">
         <v/>
@@ -16744,7 +16744,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K348" t="str">
-        <v>images/daiwa_lures/プレッソ リバクラPRESSO RIVECRA_PressoRivecra30S_GomashioGrow_2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AA%E3%83%90%E3%82%AF%E3%83%A9PRESSO%20RIVECRA_PressoRivecra30S_GomashioGrow_2.jpg</v>
       </c>
       <c r="L348" t="str">
         <v/>
@@ -16791,7 +16791,7 @@
         <v>variable</v>
       </c>
       <c r="K349" t="str">
-        <v>images/daiwa_lures/プレッソ ラトリンウェイクバグPRESSO RATLLIN'WAKE BUG_PRESSORATLLINWAKEBUG28HFCLEAR4550133656897.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%A9%E3%83%88%E3%83%AA%E3%83%B3%E3%82%A6%E3%82%A7%E3%82%A4%E3%82%AF%E3%83%90%E3%82%B0PRESSO%20RATLLIN'WAKE%20BUG_PRESSORATLLINWAKEBUG28HFCLEAR4550133656897.jpg</v>
       </c>
       <c r="L349" t="str">
         <v/>
@@ -16838,7 +16838,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K350" t="str">
-        <v>images/daiwa_lures/ドクターミノー ジョイント 5F プレッソチューンDR. MINNOW JOINT 5F PRESSO TUNE_DrMinnowJoint5FPressoTune_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9F%E3%83%8E%E3%83%BC%20%E3%82%B8%E3%83%A7%E3%82%A4%E3%83%B3%E3%83%88%205F%20%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%83%81%E3%83%A5%E3%83%BC%E3%83%B3DR.%20MINNOW%20JOINT%205F%20PRESSO%20TUNE_DrMinnowJoint5FPressoTune_Clear.jpg</v>
       </c>
       <c r="L350" t="str">
         <v/>
@@ -16885,7 +16885,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K351" t="str">
-        <v>images/daiwa_lures/プレッソ ワブクラPRESSO WABCRA_PressoWabcra_DR_GomashioGlow.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AF%E3%83%96%E3%82%AF%E3%83%A9PRESSO%20WABCRA_PressoWabcra_DR_GomashioGlow.jpg</v>
       </c>
       <c r="L351" t="str">
         <v/>
@@ -16932,7 +16932,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K352" t="str">
-        <v>images/daiwa_lures/鱒ノ芋虫MASUNO IMOMUSHI_MasunoImomushi_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E8%8A%8B%E8%99%ABMASUNO%20IMOMUSHI_MasunoImomushi_Clear.jpg</v>
       </c>
       <c r="L352" t="str">
         <v/>
@@ -16979,7 +16979,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K353" t="str">
-        <v>images/daiwa_lures/プレッソ ディーザPRESSO DEAZA_PressoDeaza25_LatteGreenGrow_left.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%87%E3%82%A3%E3%83%BC%E3%82%B6PRESSO%20DEAZA_PressoDeaza25_LatteGreenGrow_left.jpg</v>
       </c>
       <c r="L353" t="str">
         <v/>
@@ -17026,7 +17026,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K354" t="str">
-        <v>images/daiwa_lures/鱒ノ小魚MASUNO KOZAKAN_MasunoKozakana_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E5%B0%8F%E9%AD%9AMASUNO%20KOZAKAN_MasunoKozakana_Clear.jpg</v>
       </c>
       <c r="L354" t="str">
         <v/>
@@ -17073,7 +17073,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K355" t="str">
-        <v>images/daiwa_lures/鱒の小枝 スクリューMASU NO KOEDA SCREW_MASU_NO_KOEDA_SCREW_CLEAR_RED_4550133450167.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%81%AE%E5%B0%8F%E6%9E%9D%20%E3%82%B9%E3%82%AF%E3%83%AA%E3%83%A5%E3%83%BCMASU%20NO%20KOEDA%20SCREW_MASU_NO_KOEDA_SCREW_CLEAR_RED_4550133450167.jpg</v>
       </c>
       <c r="L355" t="str">
         <v/>
@@ -17120,7 +17120,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K356" t="str">
-        <v>images/daiwa_lures/鱒ノつぼみMASU NO TSUBOMI_MASU_NO_TSUBOMI_ANZU_4550133242960.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E3%81%A4%E3%81%BC%E3%81%BFMASU%20NO%20TSUBOMI_MASU_NO_TSUBOMI_ANZU_4550133242960.jpg</v>
       </c>
       <c r="L356" t="str">
         <v/>
@@ -17167,7 +17167,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K357" t="str">
-        <v>images/daiwa_lures/鱒ノ筒／鱒ノ筒Jr.MASU NO TSUTSU／MASU NO TSUTSU Jr._MASU_NO_TSUTSU_FLAMINGO_4550133454011.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E7%AD%92%EF%BC%8F%E9%B1%92%E3%83%8E%E7%AD%92Jr.MASU%20NO%20TSUTSU%EF%BC%8FMASU%20NO%20TSUTSU%20Jr._MASU_NO_TSUTSU_FLAMINGO_4550133454011.jpg</v>
       </c>
       <c r="L357" t="str">
         <v/>
@@ -17214,7 +17214,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K358" t="str">
-        <v>images/daiwa_lures/鱒ノ種MASUNOTANE_Masynotane_Shou10mm_Olive.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E7%A8%AEMASUNOTANE_Masynotane_Shou10mm_Olive.jpg</v>
       </c>
       <c r="L358" t="str">
         <v/>
@@ -17261,7 +17261,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K359" t="str">
-        <v>images/daiwa_lures/鱒もろこしMASUMOROKOSHI_MasuMorokoshi_SweetCorn.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%82%82%E3%82%8D%E3%81%93%E3%81%97MASUMOROKOSHI_MasuMorokoshi_SweetCorn.jpg</v>
       </c>
       <c r="L359" t="str">
         <v/>
@@ -17308,7 +17308,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K360" t="str">
-        <v>images/daiwa_lures/鱒ノ小枝／鱒ノ小枝Jr.MASUNOKOEDA／MASUNOKOEDA Jr._Masunokoeda_Mimizu.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E5%B0%8F%E6%9E%9D%EF%BC%8F%E9%B1%92%E3%83%8E%E5%B0%8F%E6%9E%9DJr.MASUNOKOEDA%EF%BC%8FMASUNOKOEDA%20Jr._Masunokoeda_Mimizu.jpg</v>
       </c>
       <c r="L360" t="str">
         <v/>
@@ -17355,7 +17355,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K361" t="str">
-        <v>images/daiwa_lures/プレッソ アトラPRESSO ATTRA_8_ORANGE_MANGO_4550133583018.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%A2%E3%83%88%E3%83%A9PRESSO%20ATTRA_8_ORANGE_MANGO_4550133583018.jpg</v>
       </c>
       <c r="L361" t="str">
         <v/>
@@ -17402,7 +17402,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K362" t="str">
-        <v>images/daiwa_lures/プレッソ イヴ激アツ 2.5PRESSO EVE GEKIATSU 2.5_PressoEveGekiatsu25_Karashi_front4550133114014.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%A4%E3%83%B4%E6%BF%80%E3%82%A2%E3%83%84%202.5PRESSO%20EVE%20GEKIATSU%202.5_PressoEveGekiatsu25_Karashi_front4550133114014.jpg</v>
       </c>
       <c r="L362" t="str">
         <v/>
@@ -17449,7 +17449,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K363" t="str">
-        <v>images/daiwa_lures/プレッソ ルミオンPRESSO LUMION_orengemango.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AB%E3%83%9F%E3%82%AA%E3%83%B3PRESSO%20LUMION_orengemango.jpg</v>
       </c>
       <c r="L363" t="str">
         <v/>
@@ -19047,7 +19047,7 @@
         <v>worm</v>
       </c>
       <c r="K397" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_senko.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_fuzzy_senko.jpg</v>
       </c>
       <c r="L397" t="str">
         <v>2026-04-10T12:07:28.695Z</v>
@@ -19094,7 +19094,7 @@
         <v>worm</v>
       </c>
       <c r="K398" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_nuki.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_fuzzy_nuki.jpg</v>
       </c>
       <c r="L398" t="str">
         <v>2026-04-10T12:07:30.291Z</v>
@@ -19141,7 +19141,7 @@
         <v>worm</v>
       </c>
       <c r="K399" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fuzzy_nut_6pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_fuzzy_nut_6pk.jpg</v>
       </c>
       <c r="L399" t="str">
         <v>2026-04-10T12:07:31.877Z</v>
@@ -19188,7 +19188,7 @@
         <v>worm</v>
       </c>
       <c r="K400" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_uni.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_uni.jpg</v>
       </c>
       <c r="L400" t="str">
         <v>2026-04-10T12:07:33.479Z</v>
@@ -19235,7 +19235,7 @@
         <v>worm</v>
       </c>
       <c r="K401" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_ultimate_senko_kit___100pc_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_ultimate_senko_kit___100pc_assortment.jpg</v>
       </c>
       <c r="L401" t="str">
         <v>2026-04-10T12:07:35.206Z</v>
@@ -19282,7 +19282,7 @@
         <v>worm</v>
       </c>
       <c r="K402" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_kit___160pc_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_senko_kit___160pc_assortment.jpg</v>
       </c>
       <c r="L402" t="str">
         <v>2026-04-10T12:07:36.787Z</v>
@@ -19329,7 +19329,7 @@
         <v>worm</v>
       </c>
       <c r="K403" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_baitfish_bundle___50pc_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_5__senko_baitfish_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L403" t="str">
         <v>2026-04-10T12:07:38.368Z</v>
@@ -19376,7 +19376,7 @@
         <v>worm</v>
       </c>
       <c r="K404" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_green_pumpkin_bundle___50pc_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_5__senko_green_pumpkin_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L404" t="str">
         <v>2026-04-10T12:07:39.977Z</v>
@@ -19423,7 +19423,7 @@
         <v>worm</v>
       </c>
       <c r="K405" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_bundle___90pc_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_senko_bundle___90pc_assortment.jpg</v>
       </c>
       <c r="L405" t="str">
         <v>2026-04-10T12:07:41.570Z</v>
@@ -19470,7 +19470,7 @@
         <v>worm</v>
       </c>
       <c r="K406" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fat_senko_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_fat_senko_10pk.jpg</v>
       </c>
       <c r="L406" t="str">
         <v>2026-04-10T12:07:43.176Z</v>
@@ -19517,7 +19517,7 @@
         <v>worm</v>
       </c>
       <c r="K407" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_swimming_senko.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_swimming_senko.jpg</v>
       </c>
       <c r="L407" t="str">
         <v>2026-04-10T12:07:44.352Z</v>
@@ -19564,7 +19564,7 @@
         <v>worm</v>
       </c>
       <c r="K408" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_senko_bulk_packs.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_senko_bulk_packs.jpg</v>
       </c>
       <c r="L408" t="str">
         <v>2026-04-10T12:07:46.362Z</v>
@@ -19611,7 +19611,7 @@
         <v>worm</v>
       </c>
       <c r="K409" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_megastrike_fish_attractant.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_megastrike_fish_attractant.jpg</v>
       </c>
       <c r="L409" t="str">
         <v>2026-04-10T12:07:47.963Z</v>
@@ -19658,7 +19658,7 @@
         <v>worm</v>
       </c>
       <c r="K410" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_7__speed_senko_7pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_7__speed_senko_7pk.jpg</v>
       </c>
       <c r="L410" t="str">
         <v>2026-04-10T12:07:49.627Z</v>
@@ -19705,7 +19705,7 @@
         <v>worm</v>
       </c>
       <c r="K411" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3__ned_senko_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_3__ned_senko_10pk.jpg</v>
       </c>
       <c r="L411" t="str">
         <v>2026-04-10T12:07:51.218Z</v>
@@ -19752,7 +19752,7 @@
         <v>worm</v>
       </c>
       <c r="K412" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3__slim_senko_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_3__slim_senko_10pk.jpg</v>
       </c>
       <c r="L412" t="str">
         <v>2026-04-10T12:07:52.823Z</v>
@@ -19799,7 +19799,7 @@
         <v>worm</v>
       </c>
       <c r="K413" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__pro_senko_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_5__pro_senko_10pk.jpg</v>
       </c>
       <c r="L413" t="str">
         <v>2026-04-10T12:07:54.419Z</v>
@@ -19846,7 +19846,7 @@
         <v>worm</v>
       </c>
       <c r="K414" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__thin_senko_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_5__thin_senko_10pk.jpg</v>
       </c>
       <c r="L414" t="str">
         <v>2026-04-10T12:07:56.074Z</v>
@@ -19893,7 +19893,7 @@
         <v>worm</v>
       </c>
       <c r="K415" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_7__senko_5pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_7__senko_5pk.jpg</v>
       </c>
       <c r="L415" t="str">
         <v>2026-04-10T12:07:57.660Z</v>
@@ -19940,7 +19940,7 @@
         <v>worm</v>
       </c>
       <c r="K416" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_6__senko_5pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_6__senko_5pk.jpg</v>
       </c>
       <c r="L416" t="str">
         <v>2026-04-10T12:07:59.256Z</v>
@@ -19987,7 +19987,7 @@
         <v>worm</v>
       </c>
       <c r="K417" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__senko_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_4__senko_10pk.jpg</v>
       </c>
       <c r="L417" t="str">
         <v>2026-04-10T12:08:00.867Z</v>
@@ -20034,7 +20034,7 @@
         <v>worm</v>
       </c>
       <c r="K418" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__senko_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_5__senko_10pk.jpg</v>
       </c>
       <c r="L418" t="str">
         <v>2026-04-10T12:08:02.489Z</v>
@@ -20081,7 +20081,7 @@
         <v>worm</v>
       </c>
       <c r="K419" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_fat_shad_shape_worm_8pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_fat_shad_shape_worm_8pk.jpg</v>
       </c>
       <c r="L419" t="str">
         <v>2026-04-10T12:08:05.100Z</v>
@@ -20128,7 +20128,7 @@
         <v>worm</v>
       </c>
       <c r="K420" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_worm_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_shad_shape_worm_10pk.jpg</v>
       </c>
       <c r="L420" t="str">
         <v>2026-04-10T12:08:06.723Z</v>
@@ -20175,7 +20175,7 @@
         <v>worm</v>
       </c>
       <c r="K421" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_kut_tail_worm.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_kut_tail_worm.jpg</v>
       </c>
       <c r="L421" t="str">
         <v>2026-04-10T12:08:08.358Z</v>
@@ -20222,7 +20222,7 @@
         <v>worm</v>
       </c>
       <c r="K422" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_6_5__sensei_worm_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_6_5__sensei_worm_10pk.jpg</v>
       </c>
       <c r="L422" t="str">
         <v>2026-04-10T12:08:09.950Z</v>
@@ -20269,7 +20269,7 @@
         <v>worm</v>
       </c>
       <c r="K423" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_oki_worm_6pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_oki_worm_6pk.jpg</v>
       </c>
       <c r="L423" t="str">
         <v>2026-04-10T12:08:11.764Z</v>
@@ -20316,7 +20316,7 @@
         <v>worm</v>
       </c>
       <c r="K424" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_ichi_worm_6pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_ichi_worm_6pk.jpg</v>
       </c>
       <c r="L424" t="str">
         <v>2026-04-10T12:08:13.380Z</v>
@@ -20363,7 +20363,7 @@
         <v>worm</v>
       </c>
       <c r="K425" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_slinko_floater.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_slinko_floater.jpg</v>
       </c>
       <c r="L425" t="str">
         <v>2026-04-10T12:08:16.099Z</v>
@@ -20410,7 +20410,7 @@
         <v>worm</v>
       </c>
       <c r="K426" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__shad_shape_floater_8pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_5__shad_shape_floater_8pk.jpg</v>
       </c>
       <c r="L426" t="str">
         <v>2026-04-10T12:08:17.693Z</v>
@@ -20457,7 +20457,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K427" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_5__shinobi_grub_8pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_3_5__shinobi_grub_8pk.jpg</v>
       </c>
       <c r="L427" t="str">
         <v>2026-04-10T12:08:20.341Z</v>
@@ -20504,7 +20504,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K428" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hula_grub_bundle___50pc_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_hula_grub_bundle___50pc_assortment.jpg</v>
       </c>
       <c r="L428" t="str">
         <v>2026-04-10T12:08:21.926Z</v>
@@ -20551,7 +20551,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K429" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yamatanuki.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_yamatanuki.jpg</v>
       </c>
       <c r="L429" t="str">
         <v>2026-04-10T12:08:23.545Z</v>
@@ -20598,7 +20598,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K430" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_double_tail_hula_grub_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_double_tail_hula_grub_10pk.jpg</v>
       </c>
       <c r="L430" t="str">
         <v>2026-04-10T12:08:25.185Z</v>
@@ -20645,7 +20645,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K431" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_double_tail_grub_20pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_double_tail_grub_20pk.jpg</v>
       </c>
       <c r="L431" t="str">
         <v>2026-04-10T12:08:26.800Z</v>
@@ -20692,7 +20692,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K432" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_single_tail_grub_20pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_single_tail_grub_20pk.jpg</v>
       </c>
       <c r="L432" t="str">
         <v>2026-04-10T12:08:28.409Z</v>
@@ -20739,7 +20739,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K433" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yama_bug_6pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_yama_bug_6pk.jpg</v>
       </c>
       <c r="L433" t="str">
         <v>2026-04-10T12:08:32.124Z</v>
@@ -20786,7 +20786,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K434" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_yamacraw.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_yamacraw.jpg</v>
       </c>
       <c r="L434" t="str">
         <v>2026-04-10T12:08:34.872Z</v>
@@ -20833,7 +20833,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K435" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_flappin__hog.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_flappin__hog.jpg</v>
       </c>
       <c r="L435" t="str">
         <v>2026-04-10T12:08:36.459Z</v>
@@ -20880,7 +20880,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K436" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_sanshouo_6pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_sanshouo_6pk.jpg</v>
       </c>
       <c r="L436" t="str">
         <v>2026-04-10T12:08:38.058Z</v>
@@ -20927,7 +20927,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K437" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_2_5__covert_craw_floater_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_2_5__covert_craw_floater_10pk.jpg</v>
       </c>
       <c r="L437" t="str">
         <v>2026-04-10T12:08:39.675Z</v>
@@ -20974,7 +20974,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K438" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_5__nuki_bug_6pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_3_5__nuki_bug_6pk.jpg</v>
       </c>
       <c r="L438" t="str">
         <v>2026-04-10T12:08:41.277Z</v>
@@ -21021,7 +21021,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K439" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_75__cowboy_7pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_3_75__cowboy_7pk.jpg</v>
       </c>
       <c r="L439" t="str">
         <v>2026-04-10T12:08:44.036Z</v>
@@ -21068,7 +21068,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K440" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_psychodad_5pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_psychodad_5pk.jpg</v>
       </c>
       <c r="L440" t="str">
         <v>2026-04-10T12:08:45.655Z</v>
@@ -21115,7 +21115,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K441" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__kreature_7pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_4__kreature_7pk.jpg</v>
       </c>
       <c r="L441" t="str">
         <v>2026-04-10T12:08:47.244Z</v>
@@ -21162,7 +21162,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K442" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_3_75__fat_baby_craw_7pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_3_75__fat_baby_craw_7pk.jpg</v>
       </c>
       <c r="L442" t="str">
         <v>2026-04-10T12:08:48.829Z</v>
@@ -21209,7 +21209,7 @@
         <v>crawl_creature</v>
       </c>
       <c r="K443" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__fat_ika_10pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_4__fat_ika_10pk.jpg</v>
       </c>
       <c r="L443" t="str">
         <v>2026-04-10T12:08:50.421Z</v>
@@ -21256,7 +21256,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K444" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shibo_swimmer.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_shibo_swimmer.jpg</v>
       </c>
       <c r="L444" t="str">
         <v>2026-04-10T12:08:52.970Z</v>
@@ -21303,7 +21303,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K445" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_hinge_minnow.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_hinge_minnow.jpg</v>
       </c>
       <c r="L445" t="str">
         <v>2026-04-10T12:08:54.558Z</v>
@@ -21350,7 +21350,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K446" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait_kit___84pc_assortment.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_zako_swimbait_kit___84pc_assortment.jpg</v>
       </c>
       <c r="L446" t="str">
         <v>2026-04-10T12:08:56.163Z</v>
@@ -21397,7 +21397,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K447" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_slim_6pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_zako_slim_6pk.jpg</v>
       </c>
       <c r="L447" t="str">
         <v>2026-04-10T12:08:57.740Z</v>
@@ -21444,7 +21444,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K448" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_scope_shad.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_scope_shad.jpg</v>
       </c>
       <c r="L448" t="str">
         <v>2026-04-10T12:08:59.341Z</v>
@@ -21491,7 +21491,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K449" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_shad_shape_swimmer_8pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_shad_shape_swimmer_8pk.jpg</v>
       </c>
       <c r="L449" t="str">
         <v>2026-04-10T12:09:02.138Z</v>
@@ -21538,7 +21538,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K450" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_zako_swimbait.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_zako_swimbait.jpg</v>
       </c>
       <c r="L450" t="str">
         <v>2026-04-10T12:09:03.734Z</v>
@@ -21585,7 +21585,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K451" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__zako_swimbait_bulk_packs.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_4__zako_swimbait_bulk_packs.jpg</v>
       </c>
       <c r="L451" t="str">
         <v>2026-04-10T12:09:04.892Z</v>
@@ -21632,7 +21632,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K452" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_4__paddle_tail_zako_5pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_4__paddle_tail_zako_5pk.jpg</v>
       </c>
       <c r="L452" t="str">
         <v>2026-04-10T12:09:07.644Z</v>
@@ -21679,7 +21679,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K453" t="str">
-        <v>pkgGear/images/lure/YAMAMOTO/yamamoto_5__d_shad_7pk.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/YAMAMOTO_lures/yamamoto_5__d_shad_7pk.jpg</v>
       </c>
       <c r="L453" t="str">
         <v>2026-04-10T12:09:09.237Z</v>

--- a/GearSage-client/rate/excel/lure.xlsx
+++ b/GearSage-client/rate/excel/lure.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -401,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O453"/>
+  <dimension ref="A1:O583"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -21694,9 +21690,6119 @@
         <v/>
       </c>
     </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>EL1000</v>
+      </c>
+      <c r="B454">
+        <v>15</v>
+      </c>
+      <c r="C454" t="str">
+        <v>コンバットラット</v>
+      </c>
+      <c r="D454" t="str">
+        <v/>
+      </c>
+      <c r="E454" t="str">
+        <v/>
+      </c>
+      <c r="F454" t="str">
+        <v/>
+      </c>
+      <c r="G454" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H454" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I454" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J454" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K454" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットラット.jpg</v>
+      </c>
+      <c r="L454" t="str">
+        <v/>
+      </c>
+      <c r="M454" t="str">
+        <v/>
+      </c>
+      <c r="N454" t="str">
+        <v>「トーナメントではできるだけ速く広くエリアをカバーしたい」が「ここぞというスポットではバスをじらすような使い方もしたい」というジャスティンのこだわり。 さらに、リトリーブだけでなくロッドアクションにも機敏に反応。トゥイッチングでのテーブルターンも華麗にこなす。 また、リトリーブスピードに応じて段階的にサウンドが変化。巻き速度の変化と音の変化の相乗効果でリアクションバイトを激しく誘発。 【EG公式 Instagram】 ・ コンバットラット・アクション動画→</v>
+      </c>
+      <c r="O454" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/CombatRat.html</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>EL1001</v>
+      </c>
+      <c r="B455">
+        <v>15</v>
+      </c>
+      <c r="C455" t="str">
+        <v>ティンバーフラッシュ</v>
+      </c>
+      <c r="D455" t="str">
+        <v/>
+      </c>
+      <c r="E455" t="str">
+        <v/>
+      </c>
+      <c r="F455" t="str">
+        <v/>
+      </c>
+      <c r="G455" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H455" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I455" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J455" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K455" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ティンバーフラッシュ.jpg</v>
+      </c>
+      <c r="L455" t="str">
+        <v/>
+      </c>
+      <c r="M455" t="str">
+        <v/>
+      </c>
+      <c r="N455" t="str">
+        <v>真のビッグベイター菊元俊文の入魂作。ウッド製ハンドクラフテッドビッグベイト“ティンバーフラッシュ”。水面でのスローリトリーブによる強烈な水押しとサウンド&amp;テールスプラッシュによる恐ろしいまでの集魚力。深いレンジの狡猾でレイジーなビッグバスにバイトさせる為、菊元はティンバーフラッシュには最大1.2ｍの潜行能力をプラスさせ、より幅広い対応力を高めた。そしてベイトフィッシュの輝きに最も近いといわれるアルミをリアルフィニッシュしたことで、視覚面でもストライク率を高めることに成功。感動を呼ぶビッグバイト。ビッグベイトの真髄“ティンバーフラッシュ”。</v>
+      </c>
+      <c r="O455" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Timberflash.html</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>EL1002</v>
+      </c>
+      <c r="B456">
+        <v>15</v>
+      </c>
+      <c r="C456" t="str">
+        <v>ブリムスライド</v>
+      </c>
+      <c r="D456" t="str">
+        <v/>
+      </c>
+      <c r="E456" t="str">
+        <v/>
+      </c>
+      <c r="F456" t="str">
+        <v/>
+      </c>
+      <c r="G456" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H456" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I456" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J456" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K456" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ブリムスライド.jpg</v>
+      </c>
+      <c r="L456" t="str">
+        <v/>
+      </c>
+      <c r="M456" t="str">
+        <v/>
+      </c>
+      <c r="N456" t="str">
+        <v>攻めが早い。エスケイプアクションでバイトトリガーをオンにする。 モンスターの本能を破壊する攻撃的リアクションビッグベイト。 リアリズム……見た目はもちろん、襲われるべきもののアクションにとことんこだわったブルーギル型フローティングビッグベイト、ブリムスライド。着水直後の電光石火のスピードバイトを始め、さらには、体高のあるフラットサイドボディと背ビレや尾ビレ等、各ヒレが大きく水を動かしビッグバスを探しながらも同時に仕留めてしまうといった、早い展開を得意とします。 ただ巻きでは、スピードを上げるとブルーギルやフナが逃げ惑う様をイミテート。そのハイピッチな水押しエスケイプアクションが追い喰いを誘発。「グリグリッ！」と一瞬リールを速巻きしたりロッドでジャークを入れると、切れ込むようなスライドダート＆ダイブアクションを演出。その後のライジングアクションで突き上げてひったくるようなバイトを誘発します。これらのアクションから生み出される強烈なストライクは、まさに襲われるべきものの証。 また、ジャーク時のフックへのライン絡みといった、この手のルアーにありがちなトラブルを極限まで排除した設計によって、絶好のストライクチャンスを逃さず攻撃的に仕掛けることができます。 3oz.クラスフローティングモデル。菊元俊文が求めた攻めが早いリアリズム。襲われるべきものとしてモンスターの本能を破壊する攻撃的リアクションビッグベイト、ブリムスライド。 ウエイトシールを貼ることで容易にサスペンド、スローシンキングチューン。低水温期やタフタイムのスローダウンを余儀なくされた展開においても、リアリズムがその威力を発揮します。 ▶ ブリムスライド実釣アクションムービー</v>
+      </c>
+      <c r="O456" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Breamslide.html</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>EL1003</v>
+      </c>
+      <c r="B457">
+        <v>15</v>
+      </c>
+      <c r="C457" t="str">
+        <v>ロイヤルフラッシュ</v>
+      </c>
+      <c r="D457" t="str">
+        <v/>
+      </c>
+      <c r="E457" t="str">
+        <v/>
+      </c>
+      <c r="F457" t="str">
+        <v/>
+      </c>
+      <c r="G457" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H457" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I457" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J457" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K457" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ロイヤルフラッシュ.jpg</v>
+      </c>
+      <c r="L457" t="str">
+        <v/>
+      </c>
+      <c r="M457" t="str">
+        <v/>
+      </c>
+      <c r="N457" t="str">
+        <v>多連系ビッグベイトの切り札、ロイヤルフラッシュ。 大振りな動き、強波動ハイサウンド＆ハイアピールなビッグベイトと大きく趣を異にする多連系ビッグベイト「ロイヤルフラッシュ」。 そのアクションは、基本的に頭を振らず、ロールを排除しただけでなくスロ−では極めてナチュラルにウネウネと泳ぎ、特にテール部の動きが強調されます。そして、段々とスピードアップするにつれ、よりタイトになり、従来のビッグベイトではあり得なかったハイピッチな振動が得られます。 そして、その動きはリアルベイトフィッシュそのもの。また、デッドスティック時における極めてナチュラルな動きは、スレたバス、深いレンジ、離れた場所からも、たまらなくバスをアトラクトします。 また、フラットサイド面を活かしたフラッシングは、リトリーブスピードを上げた時のエスケープアクションや、トゥイッチでのヒラ打ち時のバイトトリガーとなります。 追わせるだけでなく、突然「ドン！」と出る強烈なビッグバイト。従来のビッグベイトで獲れなかったバスを獲る。別流派。多連系ビッグベイトの切り札。ロイヤルフラッシュ。</v>
+      </c>
+      <c r="O457" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Royalflash.html</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>EL1004</v>
+      </c>
+      <c r="B458">
+        <v>15</v>
+      </c>
+      <c r="C458" t="str">
+        <v>ロイヤルフラッシュJr.</v>
+      </c>
+      <c r="D458" t="str">
+        <v/>
+      </c>
+      <c r="E458" t="str">
+        <v/>
+      </c>
+      <c r="F458" t="str">
+        <v/>
+      </c>
+      <c r="G458" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H458" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I458" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J458" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K458" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ロイヤルフラッシュjr.jpg</v>
+      </c>
+      <c r="L458" t="str">
+        <v/>
+      </c>
+      <c r="M458" t="str">
+        <v/>
+      </c>
+      <c r="N458" t="str">
+        <v>誰にでも使いやすい「釣れる」ビッグベイト。 “ロイヤルフラッシュJr．”はビッグベイト専用タックルを必要としない極めて攻撃範囲が広い多連系コンパクトビッグベイト。5連のオリジナルモデルをそのままスケールダウンさせるのではなく、あえて4連ボディに専用設計。コンパクトながら強烈なアピール力と、それでいてナチュラルさを併せ持つキラーアクションを身につけました。 ビッグレイクのみならず、河川、リザーバー、野池等あらゆるフィールドを手中に収めるコンパクトなビッグベイト。“ロイヤルフラッシュJr．”その「釣れる」という性能を実感してください。</v>
+      </c>
+      <c r="O458" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/RoyalflashJr.html</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>EL1005</v>
+      </c>
+      <c r="B459">
+        <v>15</v>
+      </c>
+      <c r="C459" t="str">
+        <v>エスドライブ</v>
+      </c>
+      <c r="D459" t="str">
+        <v/>
+      </c>
+      <c r="E459" t="str">
+        <v/>
+      </c>
+      <c r="F459" t="str">
+        <v/>
+      </c>
+      <c r="G459" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H459" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I459" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J459" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K459" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/エスドライブ.jpg</v>
+      </c>
+      <c r="L459" t="str">
+        <v/>
+      </c>
+      <c r="M459" t="str">
+        <v/>
+      </c>
+      <c r="N459" t="str">
+        <v>これが「S字系」。菊元が生み出したリップレスジョイントの切り札。 エスドライブを初めて投げた時、巻くだけで極めてナチュラルにS字を描くその泳ぎに貴方は感動せずにはいられないだろう。 ウォブリングでもローリングでもバイブレーションでもない「S字系」の動きと波動。菊元は言う「バスはエスドライブを完全にエサ（生命体）だと思っているみたいだ。」と。何故なら、これが、バスの射程圏を通れば、ほとんどのバスがチェイスもしくは何らかの反応をするからだ。 そして何より同じバスが2度、3度とミスバイトしても、まだバイトしてくるさまは、彼らプレデターの本能を強烈に刺激し、狂わせる何かがあるとしか思えないのである。まさしくこいつは生き物なのだ。 ［ 関連製品 ］ 小沼が求めたオチアユパターン攻略特化型モデル。 → エスドライブ（フローティングモデル）製品ページ</v>
+      </c>
+      <c r="O459" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Esdrive.html</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>EL1006</v>
+      </c>
+      <c r="B460">
+        <v>15</v>
+      </c>
+      <c r="C460" t="str">
+        <v>コンバットクランクTC-60</v>
+      </c>
+      <c r="D460" t="str">
+        <v/>
+      </c>
+      <c r="E460" t="str">
+        <v/>
+      </c>
+      <c r="F460" t="str">
+        <v/>
+      </c>
+      <c r="G460" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H460" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I460" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J460" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K460" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランクtc_60.jpg</v>
+      </c>
+      <c r="L460" t="str">
+        <v/>
+      </c>
+      <c r="M460" t="str">
+        <v/>
+      </c>
+      <c r="N460" t="str">
+        <v>ラウンドボディタイプとは全く違うフラットサイドならではの強烈なウォーターディスプレイスメントを水面から表層で発生させる今までに無い形状の水面波動系クランクベイト。 TC-60はフラットサイドとは言え、幅広でテールへ行くにつれ太くなるファットなデザインにより、優秀なキャスタビリティーとアキュラシー性の高さを実現。最大の特長としてボディ内部にブラス製のウエイトルームをもうけた。円筒形のこのウエイトルームの内部でメインウエイト兼ラトルとなるタングステンボールが左右にヒットすることで、今までに無い音色のカン高くてラウドなラトルサウンドが得られることとなった。 菊元のこだわりにより、超高速でも飛び出さないというメリットよりも、中低速リトリーブで最もバスを誘えるアクション設定に変更。これは彼の経験から、ゆっくり巻いた方が、バイトが多発したからにほかならない。ただし、これは少しテクニカルだが高速でルアーが限界スピードを超え水面から飛び出す寸前の状態を上手くコントロールしてやることで、他に類を見ないハイピッチハイトーンラトルサウンドと、「ゴボゴボゴボッ」という激しく泡をかむサウンドが絶妙なハーモニーを生み、バイトを誘発する。 スローリトリーブから徐々にスピードをあげるこのテクニックは時にデッドリーなメソッドとなるのである。また、トップ～表層系クランクの弱点であったフッキングの悪さも、フラットサイドデザインとビッグフック搭載により解消。トップウォータークランキングの新しい世界。</v>
+      </c>
+      <c r="O460" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/CombatCrankTc60.html</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>EL1007</v>
+      </c>
+      <c r="B461">
+        <v>15</v>
+      </c>
+      <c r="C461" t="str">
+        <v>ベルカント</v>
+      </c>
+      <c r="D461" t="str">
+        <v/>
+      </c>
+      <c r="E461" t="str">
+        <v/>
+      </c>
+      <c r="F461" t="str">
+        <v/>
+      </c>
+      <c r="G461" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H461" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I461" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J461" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K461" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ベルカント.jpg</v>
+      </c>
+      <c r="L461" t="str">
+        <v/>
+      </c>
+      <c r="M461" t="str">
+        <v/>
+      </c>
+      <c r="N461" t="str">
+        <v>（※）ある程度の高速リトリーブでハンティングモーションが発生、ものに当てることなく喰わせのキッカケをつくり出します。 ハンティングモーション＝極軽いチドリアクション。抵抗で一瞬軌道が逸れるが瞬時に立て直し泳ぎ出すような動き。 ▶ 菊元俊文が新型クランク「ベルカント」をナマ解説 「鮎の遡上ルートに横たわるティンバーをかすめるように巻いて……」</v>
+      </c>
+      <c r="O461" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Belcanto.html</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>EL1008</v>
+      </c>
+      <c r="B462">
+        <v>15</v>
+      </c>
+      <c r="C462" t="str">
+        <v>コンバットクランクシャローホグ</v>
+      </c>
+      <c r="D462" t="str">
+        <v/>
+      </c>
+      <c r="E462" t="str">
+        <v/>
+      </c>
+      <c r="F462" t="str">
+        <v/>
+      </c>
+      <c r="G462" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H462" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I462" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J462" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K462" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランクシャローホグ.jpg</v>
+      </c>
+      <c r="L462" t="str">
+        <v/>
+      </c>
+      <c r="M462" t="str">
+        <v/>
+      </c>
+      <c r="N462" t="str">
+        <v>デカバスを呼ぶシャローの雄。強烈波動シャローホグ。 日米トッププロによる共同開発 エバーグリーンアメリカンスタッフ、ブレットハイトとジャスティンカーのリクエストに菊元俊文がインスパイアされ開発がスタート。日本とアメリカ両国の様々なフィールドやコンディションにおいてテストを繰り返し誕生したコンバットクランク・シャローホグは、その独特なスーパーワイドウォブンロールアクションでデカバスに強烈にアピール。並外れた集魚力を持つ、アクションレスポンスに優れた強波動ビッグシャロークランクベイトです。 相反する機能を両立 とはいえ、アメリカンクランクにありがちな動きは良いが投げにくいクランクではありません。高浮力ファットボディ＆スクエアリップがワイドかつキレのあるアクションを生み出す一方、タングステン重心移動システムによる驚異の飛距離を約束。ウッドクランクに匹敵する泳ぎ出しの立ち上がりの早さ＆アクションレスポンスの良さとコンバットクランクシリーズ共通のカッ飛び性能を両立しています。さらには、圧倒的な存在感を持つボディ質量と相まって、軽い力でのキャストアキュラシーにも優れます。これらの相反する機能の両立により、広大なエリアから魚を呼ぶ釣りだけでなくカバークランキングの精度を劇的に高めました。 幅広い対応力で圧倒的パワーを発揮 広大なシャローフラットを効率良く探る。ストライクゾーンの狭い岩盤やリーズ際をタイトに攻める。グラスをカットオフしてリアクションでバイトさせる。ウッド＆ロックカバーをスローに舐める……様々な状況への対応力を持つ絶対的自信作。世界に通用するシャロークランクベイト、コンバットクランク・シャローホグ。その圧倒的なパワーを実感してください。</v>
+      </c>
+      <c r="O462" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/ShallowHawg.html</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>EL1009</v>
+      </c>
+      <c r="B463">
+        <v>15</v>
+      </c>
+      <c r="C463" t="str">
+        <v>コンバットクランク60</v>
+      </c>
+      <c r="D463" t="str">
+        <v/>
+      </c>
+      <c r="E463" t="str">
+        <v/>
+      </c>
+      <c r="F463" t="str">
+        <v/>
+      </c>
+      <c r="G463" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H463" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I463" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J463" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K463" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランク60.jpg</v>
+      </c>
+      <c r="L463" t="str">
+        <v/>
+      </c>
+      <c r="M463" t="str">
+        <v/>
+      </c>
+      <c r="N463" t="str">
+        <v>対デカバス・威嚇型シャロークランクベイト。 シリーズ中最強の波動を持つ「コンバットクランク60」。その最大の特徴は、まるでビッグバスを威嚇するかのように強烈な「スーパーワイドウォブンロールアクション」。他に類を見ない強烈な動きから生み出される凄まじい水押しと明滅が、小ぶりなボディサイズからは想像もできないほどの存在感を放ちバスを引き寄せます。 さらに、その凶暴なまでに強烈なアクションは食い気がないバスのリアクションバイトを誘発。シリーズ共通コンセプトのかっ飛び性能に加え、このルアーの持つファストリトリーブでの抜群の安定性を活かしたロングディスタンス高速巻きは、スレ切ったビッグバスにもプレッシャーを掛けず見切る隙を与えません。 ブッシュ、レイダウン、ウィード、リーズ、リップラップ・・・もちろん、ワイドスクエアリップによるカバー回避能力を生かしたカバークランキングもお手の物。スローリトリーブでもしっかり水をつかみ、狭いプロダクティブゾーンのなかでもそのパワフルなアクションで強烈にアピールします。 他のシャロークランクの追随を許さないアピール力＆リアクションバイト誘発力。ロクマルをはじめ50upの実績は多数。対デカバス・威嚇型シャロークランクベイト、コンバットクランク60。</v>
+      </c>
+      <c r="O463" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Combatcrank60.html</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>EL1010</v>
+      </c>
+      <c r="B464">
+        <v>15</v>
+      </c>
+      <c r="C464" t="str">
+        <v>コンバットクランク120</v>
+      </c>
+      <c r="D464" t="str">
+        <v/>
+      </c>
+      <c r="E464" t="str">
+        <v/>
+      </c>
+      <c r="F464" t="str">
+        <v/>
+      </c>
+      <c r="G464" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H464" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I464" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J464" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K464" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランク120.jpg</v>
+      </c>
+      <c r="L464" t="str">
+        <v/>
+      </c>
+      <c r="M464" t="str">
+        <v/>
+      </c>
+      <c r="N464" t="str">
+        <v>シャローの切り札。陸っぱりでの絶対的アドバンテージ。 コンバットクランク120はタングステン重心移動システムと低重心固定ウエイトの採用及び、ボディ&amp;リップデザインにより、信じられない程の飛距離をたたき出すシャローモデルです。 シリーズ中、特に、陸っぱりアングラーにお薦めのモデルでもあります。ワイドスクエアリップ搭載により、シャローで有効なビビッドウォブリングがシリーズ中、最も強く、石系障害物のみならず、ウッドカバーにも強い回避性能を示します。また、良く飛び、投げ易いという特性は、同時に軽い力でのアキュラシーキャストをより容易に正確に決めてくれるでしょう。 シャロークランクで必須なピンスポットキャスト&amp;タイトトレースがよりイージーになり、逆風、強風をものともしないコンバットクランク120は、ボーター、陸っぱりを問わず、釣果を約束する強い味方です。</v>
+      </c>
+      <c r="O464" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Combatcrank120.html</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>EL1011</v>
+      </c>
+      <c r="B465">
+        <v>15</v>
+      </c>
+      <c r="C465" t="str">
+        <v>コンバットクランク180</v>
+      </c>
+      <c r="D465" t="str">
+        <v/>
+      </c>
+      <c r="E465" t="str">
+        <v/>
+      </c>
+      <c r="F465" t="str">
+        <v/>
+      </c>
+      <c r="G465" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H465" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I465" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J465" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K465" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランク180.jpg</v>
+      </c>
+      <c r="L465" t="str">
+        <v/>
+      </c>
+      <c r="M465" t="str">
+        <v/>
+      </c>
+      <c r="N465" t="str">
+        <v>スーパーカッ飛び君＆かわす君、 コンバットクランク180！！ 琵琶湖のハードベイターが大絶賛「コンバットクランク180」。広範囲をハイテンポでストレスなく探ることができる、バイブレーションプラグの感覚で使えるニュータイプ・シャロークランクベイトです。 その特徴は、コンバットクランクシリーズの真髄である「カッ飛び」性能を、よりパワーアップさせた抜群の遠投性能。さらに、しっかりした引き感＆軽めの引き抵抗をあわせ持ち、1日中快適に投げ続けることができます。 そして何より、コンバットクランク180の最大の特徴は、ズバ抜けた「カバー回避力」にあります。絶妙なスイム姿勢&amp;アクションバランスで、特に厄介なグラス(ウィード)までも高確率で巧みに「かわす」という、他の同レンジクランクベイトとは一味違う能力を発揮。ウィード絡みによるバイトチャンスの減少を防ぎます。 また、クランクベイトならではの存在感のある強い動きは、春や秋に多い水質悪化時（ターンオーバー等）のタフな状況でもしっかりアピール、リアクションバイトを誘います。 広大なシャローエリア、複雑なシャローカバーをストレスフリーでガンガン攻める「スーパーカッ飛び君」＋「かわす君」。天賦の才、コンバットクランク180。オカッパリアングラーにとっても、その能力は最大の武器となるはずです。</v>
+      </c>
+      <c r="O465" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Combatcrank180.html</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>EL1012</v>
+      </c>
+      <c r="B466">
+        <v>15</v>
+      </c>
+      <c r="C466" t="str">
+        <v>コンバットクランク250</v>
+      </c>
+      <c r="D466" t="str">
+        <v/>
+      </c>
+      <c r="E466" t="str">
+        <v/>
+      </c>
+      <c r="F466" t="str">
+        <v/>
+      </c>
+      <c r="G466" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H466" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I466" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J466" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K466" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランク250.jpg</v>
+      </c>
+      <c r="L466" t="str">
+        <v/>
+      </c>
+      <c r="M466" t="str">
+        <v/>
+      </c>
+      <c r="N466" t="str">
+        <v>安定した釣果を約束してくれるベーシッククランクベイト。 誰もが使いやすく信頼して投げ続けられ、安定した釣果を約束してくれるベーシッククランクベイト“コンバットクランク250”。メインウエイトにタングステン重心移動システムを採用し、空気抵抗を極限まで減少させたボディ＆リップデザインにより、逆風時にも低弾道でカッ飛ぶ驚異的な飛距離を実現。同時に、近・中距離で軽い力でのキャストにおいても抜群のアキュラシー性を飛躍的に向上させました。 また、低重心固定サブウエイトシステムの搭載により、従来の重心移動ウエイトシステム搭載のクランクベイトにありがちな立ち上がりの悪さを解消。リトリーブ開始と同時にバスを狂わせる波動を発生し、プロダクティブゾーンの端から端まで効果的にアピールすることができます。 ヘキサゴン（六角形）断面のボディデザインは色覚変化とフラッシング効果を高め、なおかつ決して強すぎない集魚効果抜群のナチュラルビビッドウォブリング・アクションはビッグバスに丸飲みさせる威力を誇ります。誰もが使いやすく信頼して投げ続けられ、安定した釣果を約束してくれるベーシッククランクベイト。それがコンバットクランク250なのです。</v>
+      </c>
+      <c r="O466" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Combatcrank250.html</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>EL1013</v>
+      </c>
+      <c r="B467">
+        <v>15</v>
+      </c>
+      <c r="C467" t="str">
+        <v>コンバットクランク320</v>
+      </c>
+      <c r="D467" t="str">
+        <v/>
+      </c>
+      <c r="E467" t="str">
+        <v/>
+      </c>
+      <c r="F467" t="str">
+        <v/>
+      </c>
+      <c r="G467" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H467" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I467" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J467" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K467" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランク320.jpg</v>
+      </c>
+      <c r="L467" t="str">
+        <v/>
+      </c>
+      <c r="M467" t="str">
+        <v/>
+      </c>
+      <c r="N467" t="str">
+        <v>［新色1色追加 / 4月発売予定 ］ ・#N150 ボーンN ※製造上の都合により発売が遅れる場合もございます。あらかじめご了承ください。 ハイポテンシャル・システムクランクの中核。 シリーズ共通の圧倒的な飛距離を誇るコンバットクランク320。コンパクトな形状にもかかわらず、楽々3ｍレンジへと到達。 バスを狂わせる集魚力とバイト誘発力を発揮する、ナチュラルかつハイピッチなローリング＆ビビッドウォブリングアクションは同シリーズの250よりタイト、480よりワイドな3ｍ前後のレンジで魚を狂わせるアクションを実現。 3ｍオーバー潜行のクランクベイトとして、異常なまでのバイト誘発能力に秀でたアクションのキラーベイトです。特にビッグレイクにおいて風に負けない飛距離は絶対的なアドバンテージとなり、ロングレンジトレースをよりイージーにしました。 また、ウィードがらみのしにくさも特筆モノ。快適に投げ続け、巻き続けられる私達の自信作。釣果が全てを証明する。コンバットクランク320。</v>
+      </c>
+      <c r="O467" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Combatcrank320.html</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>EL1014</v>
+      </c>
+      <c r="B468">
+        <v>15</v>
+      </c>
+      <c r="C468" t="str">
+        <v>コンバットクランク400</v>
+      </c>
+      <c r="D468" t="str">
+        <v/>
+      </c>
+      <c r="E468" t="str">
+        <v/>
+      </c>
+      <c r="F468" t="str">
+        <v/>
+      </c>
+      <c r="G468" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H468" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I468" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J468" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K468" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランク400.jpg</v>
+      </c>
+      <c r="L468" t="str">
+        <v/>
+      </c>
+      <c r="M468" t="str">
+        <v/>
+      </c>
+      <c r="N468" t="str">
+        <v>［新色3色追加 / 4月発売予定 ］ ・#N60 ブラウンバックチャートN ・#N150 ボーンN ・#N230 グローシャッドダズラーN ※製造上の都合により発売が遅れる場合もございます。あらかじめご了承ください。 琵琶湖の新定番。最強4mダイバー、コンバットクランク400。 シリーズ中最長飛距離を誇るコンバットクランク400。横風や逆風にもバランスを崩さず、ディープクランクの絶対条件、圧倒的な飛距離を叩きだします。4mダイバーとして最適に設定されたその動きが、目に見えないディープの世界を手元に伝え、バイトを誘発。 また、驚くほど軽い引き抵抗は、ロッドを選ばず快適に1日中巻き続けることを可能にします。圧倒的な飛距離に加え、「しっかりとした動き」と「快適な引き感」を両立。真の定番、コンバットクランク400。</v>
+      </c>
+      <c r="O468" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/CombatCrank400.html</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>EL1015</v>
+      </c>
+      <c r="B469">
+        <v>15</v>
+      </c>
+      <c r="C469" t="str">
+        <v>コンバットクランク480</v>
+      </c>
+      <c r="D469" t="str">
+        <v/>
+      </c>
+      <c r="E469" t="str">
+        <v/>
+      </c>
+      <c r="F469" t="str">
+        <v/>
+      </c>
+      <c r="G469" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H469" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I469" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J469" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K469" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットクランク480.jpg</v>
+      </c>
+      <c r="L469" t="str">
+        <v/>
+      </c>
+      <c r="M469" t="str">
+        <v/>
+      </c>
+      <c r="N469" t="str">
+        <v>ディープを制する。 巻き倒せる軽さと圧倒的飛距離。 コンバットクランク480は他を凌駕する圧倒的な遠投性能とディープクランクとは思えない程のリトリーブ抵抗の軽さを誇ります。キャスティングでは4ｍ以深（最大潜行4.8ｍ 10lb.ライン）をより広く効率的にサーチすることができ、ドラッギングでは8ｍ以深をもっと広範囲に探ることが可能となりました。 また、テスト中にはボトムノック直後の2次的なイレギュラーなアクションのみならず、中層でのバイトも多発し、いかにバスが、このルアーの本質的なアクションを好んでいるかという証明をし続けました。 ビッグレイク、リザーバー、リバー、ビッグバスが連発するディープクランキングをより高次元かつイージーなものにするコンバットクランク480。「自信が確信に変わった。」と菊元に言わしめた、威力を感じてください。</v>
+      </c>
+      <c r="O469" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Combatcrank480.html</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>EL1016</v>
+      </c>
+      <c r="B470">
+        <v>15</v>
+      </c>
+      <c r="C470" t="str">
+        <v>ゴールドディガー600</v>
+      </c>
+      <c r="D470" t="str">
+        <v/>
+      </c>
+      <c r="E470" t="str">
+        <v/>
+      </c>
+      <c r="F470" t="str">
+        <v/>
+      </c>
+      <c r="G470" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H470" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I470" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J470" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K470" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ゴールドディガー600.jpg</v>
+      </c>
+      <c r="L470" t="str">
+        <v/>
+      </c>
+      <c r="M470" t="str">
+        <v/>
+      </c>
+      <c r="N470" t="str">
+        <v>超ディープの金鉱を掘り当てる シークレット・スーパーディープダイバー。 菊元俊文プロデュース。ゴールドディガーはディープクランクの「未体験ゾーン」6mレンジオーバーを攻略するスーパーディープダイバーです。 その計算し尽されたボディーデザインと重心移動システムは、信じられない程の飛距離をたたき出し、グングン潜ります。 また、その引き心地はズバ抜けた潜行深度に似合わない軽いリトリーブ抵抗を約束。1日中、投げ倒せ、快適に引き倒せるディープクランクです。 スリムに設計されたミノーシェイプボディは、従来のファットなディープクランクにはストライクしないスレたディープのモンスターを惹き付けて止みません。ドラッギングでは10mを楽にクリアーする未体験のレンジキーパーハードベイト。 届かなかったディープのベイトフィッシュの群れを直撃。ワームでは獲れなかったバスを次々と獲るスーパーディープクランク。それが、超ディープの金鉱を掘り当てるシークレットクランク「ゴールドディガー」です。</v>
+      </c>
+      <c r="O470" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/GoldDigger600.html</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>EL1017</v>
+      </c>
+      <c r="B471">
+        <v>15</v>
+      </c>
+      <c r="C471" t="str">
+        <v>リトルマックス</v>
+      </c>
+      <c r="D471" t="str">
+        <v/>
+      </c>
+      <c r="E471" t="str">
+        <v/>
+      </c>
+      <c r="F471" t="str">
+        <v/>
+      </c>
+      <c r="G471" t="str">
+        <v>vib</v>
+      </c>
+      <c r="H471" t="str">
+        <v>metal</v>
+      </c>
+      <c r="I471" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J471" t="str">
+        <v>vibration</v>
+      </c>
+      <c r="K471" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/リトルマックス.jpg</v>
+      </c>
+      <c r="L471" t="str">
+        <v/>
+      </c>
+      <c r="M471" t="str">
+        <v/>
+      </c>
+      <c r="N471" t="str">
+        <v>逆風でも驚異の飛距離を約束。 小さなボディに秘められたMAXな振動。 特に急激な冷え込みや水温低下のタフタイム、バイトが無い時やショートバイトで乗せられない時、絶対的に「これしか釣れない。」と菊元俊文が断言するほどの切り札的存在。 驚異的な飛距離、マックスな震動とスライドするフォールのコンビネーションで、今まで届かなかったバイトが得られる。一口サイズでイージーなフッキング。ダブルフック標準装備で根掛かり率を大幅に減少。これが元祖ジャパニーズメタルバイブレーション。</v>
+      </c>
+      <c r="O471" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Littlemax.html</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>EL1018</v>
+      </c>
+      <c r="B472">
+        <v>15</v>
+      </c>
+      <c r="C472" t="str">
+        <v>リトルマックスヘビーウエイトチューンモデル</v>
+      </c>
+      <c r="D472" t="str">
+        <v/>
+      </c>
+      <c r="E472" t="str">
+        <v/>
+      </c>
+      <c r="F472" t="str">
+        <v/>
+      </c>
+      <c r="G472" t="str">
+        <v>vib</v>
+      </c>
+      <c r="H472" t="str">
+        <v>metal</v>
+      </c>
+      <c r="I472" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J472" t="str">
+        <v>vibration</v>
+      </c>
+      <c r="K472" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/リトルマックスヘビーウエイトチューンモデル.jpg</v>
+      </c>
+      <c r="L472" t="str">
+        <v/>
+      </c>
+      <c r="M472" t="str">
+        <v/>
+      </c>
+      <c r="N472" t="str">
+        <v>リトルマックスヘビーウエイトチューンモデル 前人未到のスポットへ。驚異の遠投性能が未体験ゾーンを直撃。 リトルマックスヘビーウエイトチューン。特筆すべきはその超遠投性能。陸っぱりで誰もが届かなかった未体験ゾーンを楽々攻略します。リトルマックス・オリジナルサイズの「釣れる力」はそのままに、最適なウエイトバランスに再設計。シリーズ共通のマックスなバイブレーションがただ巻きやリフト＆フォール、ハードジャーク等でビッグバイトを誘発します。</v>
+      </c>
+      <c r="O472" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/LittlemaxHeavyWeightTune.html</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>EL1019</v>
+      </c>
+      <c r="B473">
+        <v>15</v>
+      </c>
+      <c r="C473" t="str">
+        <v>リトルマックスTGマッスル</v>
+      </c>
+      <c r="D473" t="str">
+        <v/>
+      </c>
+      <c r="E473" t="str">
+        <v/>
+      </c>
+      <c r="F473" t="str">
+        <v/>
+      </c>
+      <c r="G473" t="str">
+        <v>vib</v>
+      </c>
+      <c r="H473" t="str">
+        <v>metal</v>
+      </c>
+      <c r="I473" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J473" t="str">
+        <v>vibration</v>
+      </c>
+      <c r="K473" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/リトルマックスtgマッスル.jpg</v>
+      </c>
+      <c r="L473" t="str">
+        <v/>
+      </c>
+      <c r="M473" t="str">
+        <v/>
+      </c>
+      <c r="N473" t="str">
+        <v>筋肉の鎧を身に付けた。リトルマックス進化形。 「キング・オブ・メタルバイブ」リトルマックスを筋肉の鎧で武装したリトルマックスTGマッスル。そのオリジナル・リトルマックスと全長は同じままヘビーウエイト化することで遠投性能が劇的に向上。飛距離が要求されるオカッパリやハイプレッシャーフィールド、さらには、メタルバイブの出番となる晩秋から冬場に多い強風下での使用感が大幅にアップしました。 しかし、高比重マテリアル採用によるTGマッスル化の真の目的は、フォールスピードをさらに速くすることにあります。水温低下中や極寒期におけるリトルマックスのリアクションバイト誘発能力は、もはや誰もが知るところ。しかし、コンパクトボディ＆ヘビーウエイト化によりさらなるスピードを手に入れたTGマッスルは、オリジナルを超える強烈なリアクションバイト誘発能力を発揮。オリジナル・リトルマックスでは獲れなかったバスを反応させることが可能になりました。 もちろん、そのフォールスピードアップにより、一般的にスローで時間が掛かるディープの釣りでも速い展開が可能になります。さらには、そのウエイトを利用することで根掛かりが外しやすくなるという副産物を生み出しました。筋肉の鎧を身に付けたスモールボディ。究極のリアクション・メタルバイブ。リトルマックス進化形、リトルマックスTGマッスル。その恐るべき能力を実感してください。</v>
+      </c>
+      <c r="O473" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/LittlemaxTgMuscle.html</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>EL1020</v>
+      </c>
+      <c r="B474">
+        <v>15</v>
+      </c>
+      <c r="C474" t="str">
+        <v>サイドステップ</v>
+      </c>
+      <c r="D474" t="str">
+        <v/>
+      </c>
+      <c r="E474" t="str">
+        <v/>
+      </c>
+      <c r="F474" t="str">
+        <v/>
+      </c>
+      <c r="G474" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H474" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I474" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J474" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K474" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/サイドステップ.jpg</v>
+      </c>
+      <c r="L474" t="str">
+        <v/>
+      </c>
+      <c r="M474" t="str">
+        <v/>
+      </c>
+      <c r="N474" t="str">
+        <v>ジャーク&amp;ライズメソッドの脅威。デカバスが狂う真のジャークベイト。 極めて集魚能力が高く、魚を狂わせ一気にバイトさせる力に優れたジャークベイト、サイドステップ。その名の通り左右へキレ味鋭いステップするように横っ飛びするアクションは、ただ「スッ」と飛ぶのではなく、「ブルブルッ！」と水を動かし「ギラギラッ！」と妖しくフラッシュする。 このダート直後の微妙にロールしながらライジング（浮いてゆく）時が最大のバイトチャンスとなる。固定重心ながら絶妙のボディシェイプとバランス設計により、安定した姿勢で、重心移動と見まちがうかのようにカッ飛んでゆき、広範囲を有効にサーチ出来る。 タフユース対応ストロング設計。そしてストロングカーブドポイントフック（デコイY-S21）3フックシステムは、カバーでのスナッグを減少させ、掛けたバスをバラさないという菊元のこだわりである。釣果こそがその証明。本当のジャークベイト。サイドステップ。</v>
+      </c>
+      <c r="O474" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Sidestep.html</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>EL1021</v>
+      </c>
+      <c r="B475">
+        <v>15</v>
+      </c>
+      <c r="C475" t="str">
+        <v>サイドステップSF</v>
+      </c>
+      <c r="D475" t="str">
+        <v/>
+      </c>
+      <c r="E475" t="str">
+        <v/>
+      </c>
+      <c r="F475" t="str">
+        <v/>
+      </c>
+      <c r="G475" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H475" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I475" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J475" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K475" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/サイドステップsf.jpg</v>
+      </c>
+      <c r="L475" t="str">
+        <v/>
+      </c>
+      <c r="M475" t="str">
+        <v/>
+      </c>
+      <c r="N475" t="str">
+        <v>低水温、タフタイム対応。 スローフローティングモデル誕生。 魚を狂わせ、一気に捕食モードにスィッチを入れるジャークベイト「サイドステップ」に新たにスローフローティングモデルが誕生。オリジナルモデルの切れ味鋭い左右へのステッピングはそのままに、ハイフロートでは追いつけなかった低活性のビッグバスをバイトへと導きます。オールシーズン有効ですが、特に晩秋から春にかけて、超スローに浮いてゆくスローフローティングモデルは強力に機能します。固定重心ながら、絶妙のボディシェィプとバランスデザインによりオリジナルモデル以上のかっとび性能を発揮。広範囲を有効にサーチできます。タフユース対応のストロング設計だからガンガン攻められる。華麗に舞い、幻惑して仕留める。本当のジャークベイトの世界が拡がります。</v>
+      </c>
+      <c r="O475" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/SidestepSf.html</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>EL1022</v>
+      </c>
+      <c r="B476">
+        <v>15</v>
+      </c>
+      <c r="C476" t="str">
+        <v>LBローラー</v>
+      </c>
+      <c r="D476" t="str">
+        <v/>
+      </c>
+      <c r="E476" t="str">
+        <v/>
+      </c>
+      <c r="F476" t="str">
+        <v/>
+      </c>
+      <c r="G476" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H476" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I476" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J476" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K476" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/lbローラー.jpg</v>
+      </c>
+      <c r="L476" t="str">
+        <v/>
+      </c>
+      <c r="M476" t="str">
+        <v/>
+      </c>
+      <c r="N476" t="str">
+        <v>その驚異の飛距離を叩き出すミノーシェイプボディは、フィッシュイーター化し広範囲を動き回るバスのサーチ～バイト誘発にも貢献。さらに、ボディ最前方に低重心固定ウェイトを配置することにより、ロングキャストから素早く立ち上がり急速潜行。ターゲットレンジ（2～2.5m）をより長く引くことができます。 このようにスリムなクランクベイトとしての機能を持つLBローラーなら、同レンジのファットなクランクベイトとのローテーションにも違和感なく対応。シルエットやアクションの違いでバスに飽きさせずに、連続バイトを誘うことや、あと1本を絞り出すことも可能にしました。 もちろん、通常のロングビルミノーとしての使用にも高次元対応。少量のウェイト貼付でサスペンドに調整することができ、冬～春のランカーキラーとしてポンプリトリーブ、クランキング＆ステイ、ジャーク＆ポーズなどのアクションにも敏感に反応します。また、トゥイッチング時の左右上下へのトリッキーアクションはニュートラルなバスのバイトを誘発。ミドルサイズボディながら3フック仕様なので、ロングビルミノーに起こりがちな体当たり系リアクションバイトに対しても高いフッキング率を誇ります。 タダ巻き系クランクベイトとして、低水温期のロングビルミノーとして、シーズンを問わず年中使用できるLBローラーで本当のロングビルクランキングミノーの超絶威力を実感してください。</v>
+      </c>
+      <c r="O476" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/LbRoller.html</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>EL1023</v>
+      </c>
+      <c r="B477">
+        <v>15</v>
+      </c>
+      <c r="C477" t="str">
+        <v>バンクシャッド</v>
+      </c>
+      <c r="D477" t="str">
+        <v/>
+      </c>
+      <c r="E477" t="str">
+        <v/>
+      </c>
+      <c r="F477" t="str">
+        <v/>
+      </c>
+      <c r="G477" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H477" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I477" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J477" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K477" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/バンクシャッド.jpg</v>
+      </c>
+      <c r="L477" t="str">
+        <v/>
+      </c>
+      <c r="M477" t="str">
+        <v/>
+      </c>
+      <c r="N477" t="str">
+        <v>オカッパリの救世主。圧倒的な飛距離。スローに巻くだけでバイトを誘発するシャッド。 Text by 関和学近年、激タフ化したフィールドを攻略するための結論の一つとして、スモールシャッドのただ巻きにたどり着きました。他のシャッドではサスペンドタイプが主流で、超スローリトリーブでは水を掴まなかったりすること。または、フローティングタイプでは、ボディの振りが大きすぎることに不満を感じていました。そこで、「困った時に結果を出す、ただ巻きシャッド」をコンセプトにバンクシャッドの開発がスタートしたのです。そして、2年に及ぶフィールドテストを経て、スローにリトリーブしても「しっかりと水を掴み」かつ「小さなタイトピッチで」「誰にでも引き抵抗を感じられる」シャッドが完成したのです。このサイズのシャッドでは限界に近い極薄のリップに設計し、スローフローティングセッティングにすることで、リトリーブ抵抗と浮き上がろうとする力が絶妙にリンクして超スローでもしっかりと水を掴み、小さなタイトピッチを引き起こしてくれます。それは、低活性や低水温のバスを魅了するアクションと確信できる結果が次々と出ました。そして、特にオカッパリで絶対的なアドバンテージとなる「圧倒的な飛距離」をこのバンクシャッドには持たせました。タングステン重心移動ウエイトシステムを空気抵抗を計算したエアロボディデザインを採用したことで、同クラス最高峰の飛距離を叩き出すことに成功しました。オカッパリアングラーには飛距離を。ボートアングラーには、アキュラシーの向上が体感できる今までになかったシャッド。それが僕の自信作、「バンクシャッド」です。</v>
+      </c>
+      <c r="O477" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/BankShad.html</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>EL1024</v>
+      </c>
+      <c r="B478">
+        <v>15</v>
+      </c>
+      <c r="C478" t="str">
+        <v>バンクシャッドMID</v>
+      </c>
+      <c r="D478" t="str">
+        <v/>
+      </c>
+      <c r="E478" t="str">
+        <v/>
+      </c>
+      <c r="F478" t="str">
+        <v/>
+      </c>
+      <c r="G478" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H478" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I478" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J478" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K478" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/バンクシャッドmid.jpg</v>
+      </c>
+      <c r="L478" t="str">
+        <v/>
+      </c>
+      <c r="M478" t="str">
+        <v/>
+      </c>
+      <c r="N478" t="str">
+        <v>近年特にみられるバスのタフ化。シーズンまっただ中なのに少しのフィールドコンディションの変化によってあらゆるルアーへの反応が消えてしまう… バンクシャッドMIDは、一般的にシャッドが使われる冬場に限らず、極めてシビアな状況に陥ったフィールドを打破するためにつくられました。オリジナルバンクシャッドに比べ微妙にサイズアップしたボディサイズによりベイトタックルでも迷いなくカッ飛ばせる遠投性能と、スローリトリーブ特化型のオリジナルを継承する水押しを抑えたタイトピッチアクションでシビアな状況に完全対応。 ミディアムスピードで中層をただ巻くだけで、タフ化したバスでも口を使いたくなるような微波動を生み出します。さらに、高速巻きでも安定感のあるタイトピッチアクションを維持しリアクション狙いにも威力を発揮します。 もちろん、デッドスローリトリーブでもそのアクションは健在。微波動と快適な引き感を両立しアングラーに安心感を与えてくれます。オリジナルと比べてレンジ、スピードの幅を広げたオールシーズン対応型クランキンシャッド、それがバンクシャッドMIDです。</v>
+      </c>
+      <c r="O478" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/BankShadMid.html</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>EL1025</v>
+      </c>
+      <c r="B479">
+        <v>15</v>
+      </c>
+      <c r="C479" t="str">
+        <v>ウェイクマジック</v>
+      </c>
+      <c r="D479" t="str">
+        <v/>
+      </c>
+      <c r="E479" t="str">
+        <v/>
+      </c>
+      <c r="F479" t="str">
+        <v/>
+      </c>
+      <c r="G479" t="str">
+        <v>topwater_pencil</v>
+      </c>
+      <c r="H479" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I479" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J479" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K479" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ウェイクマジック.jpg</v>
+      </c>
+      <c r="L479" t="str">
+        <v/>
+      </c>
+      <c r="M479" t="str">
+        <v/>
+      </c>
+      <c r="N479" t="str">
+        <v>また意外にも、ただ巻きだけでなく、止めている時にも凄まじい威力を発揮するウェイクマジック。ジャーク後のポーズ、流れを利用したドリフト、さらには止水でも、キャスト後、何もせず水面に浮かべておくだけで……魔法のように魚を吸い寄せバイトに導きます。 カレントを利用して、ルアーを移動させずに1箇所でプロップを高速回転させるテクニックは、警戒心の強いデカバスに水面を割らせるウェイクマジックならではの凄技。 ウェイクマジックの効果的な使用法3選（菊元俊文） 他のトップウォーターでも、巻きでもワームでも釣れない時にビッグバスが釣れるウェイクマジックの使い方……菊元俊文が解説します。 解説全文を見る→</v>
+      </c>
+      <c r="O479" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Wakemagic.html</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>EL1026</v>
+      </c>
+      <c r="B480">
+        <v>15</v>
+      </c>
+      <c r="C480" t="str">
+        <v>プロップマジック75</v>
+      </c>
+      <c r="D480" t="str">
+        <v/>
+      </c>
+      <c r="E480" t="str">
+        <v/>
+      </c>
+      <c r="F480" t="str">
+        <v/>
+      </c>
+      <c r="G480" t="str">
+        <v>topwater_pencil</v>
+      </c>
+      <c r="H480" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I480" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J480" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K480" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/プロップマジック75.jpg</v>
+      </c>
+      <c r="L480" t="str">
+        <v/>
+      </c>
+      <c r="M480" t="str">
+        <v/>
+      </c>
+      <c r="N480" t="str">
+        <v>その釣果、ケタ違い！！ズバ抜けた集魚能力と喰わせ能力を併せ持つ魔法のベイト。 「プロップマジック75」は、ただ巻くだけで小さなボディサイズからは想像できないほどの集魚力を発揮する喰わせのハードベイトです。2ウエイトマグネット重心移動システムを搭載することで、クラス最長の飛距離を実現。一般的なML～Mクラスのベイトタックルで、ストレス無く使用できます。またマグネットが移動ウエイトを固定し、低重心固定メインウエイトとあいまって、着水直後からフラつきのない安定した直進性能を発揮します。このルアーの命ともいえるプロップには、超スローリトリーブでもスムーズに回転する軽さと、変形が少なく回転・泳ぎを安定させる強さを両立したオリジナルプロップを搭載。さらに、ボディサイズに対しやや大きめのプロップを採用することで、集魚力を高めました。そして、最大の特徴がシングルプロップであるということ。これは、「プロップの無い前側からしっかり喰うバスが多くなり、ランディング率がアップする」というシークレットです。プロップの水流・波動でバスを寄せ、安定感のある直線的な泳ぎで見切られる隙を与えず、食べごろサイズのボディで口を使わせる魔法のベイト「プロップマジック75」。ケタ違いの釣果を体験して下さい。</v>
+      </c>
+      <c r="O480" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Propmagic75.html</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>EL1027</v>
+      </c>
+      <c r="B481">
+        <v>15</v>
+      </c>
+      <c r="C481" t="str">
+        <v>プロップマジック95</v>
+      </c>
+      <c r="D481" t="str">
+        <v/>
+      </c>
+      <c r="E481" t="str">
+        <v/>
+      </c>
+      <c r="F481" t="str">
+        <v/>
+      </c>
+      <c r="G481" t="str">
+        <v>topwater_pencil</v>
+      </c>
+      <c r="H481" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I481" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J481" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K481" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/プロップマジック95.jpg</v>
+      </c>
+      <c r="L481" t="str">
+        <v/>
+      </c>
+      <c r="M481" t="str">
+        <v/>
+      </c>
+      <c r="N481" t="str">
+        <v>遠投性能大幅アップ。 より深く、流れに対応したプロップマジック進化形。 プロップマジック95はオリジナルの75より深いレンジを攻められる設計です。また、流れの中でもボディが不自然に揺らぐことない直進性能を高めたことで、バックウォーター攻めにも強力な威力を発揮します。これが最も嬉しい性能だと菊元俊文は語ります。 遠投性能を大幅にアップしたことでバスにアングラーの存在を感じられて見切られることが減少。ミディアムからミディアムヘビーロッドでどこまでもカッ飛んでゆきます。クリアーウォーターのサイトフィッシングにまでその世界を拡げました。 ただ巻くだけでバスを誘う能力はオリジナルを継承。ブレずにノーアクションで真っ直ぐ泳ぐボディと高速回転するリアプロップ。まるで本物のベイトフィッシュを喰うがごとく疑いなくバスがバイトするまさしく魔法のプロップベイトです。</v>
+      </c>
+      <c r="O481" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Propmagic95.html</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>EL1028</v>
+      </c>
+      <c r="B482">
+        <v>15</v>
+      </c>
+      <c r="C482" t="str">
+        <v>オッタークローラー</v>
+      </c>
+      <c r="D482" t="str">
+        <v/>
+      </c>
+      <c r="E482" t="str">
+        <v/>
+      </c>
+      <c r="F482" t="str">
+        <v/>
+      </c>
+      <c r="G482" t="str">
+        <v>topwater_walker</v>
+      </c>
+      <c r="H482" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I482" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J482" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K482" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/オッタークローラー.jpg</v>
+      </c>
+      <c r="L482" t="str">
+        <v/>
+      </c>
+      <c r="M482" t="str">
+        <v/>
+      </c>
+      <c r="N482" t="str">
+        <v>■ 多方向 水押しアピール ウイング、ジョイントボディ、ボディをへこませたコンケーブにより、横方向×下方向への立体的な水押と波動、さらにはスプラッシュ＆バブルを発生。 ■ 広域対応リトリーブスピード デッドスローリトリーブでも敏感に動き、高速リトリーブにも泳ぎが破綻しない。低速、中速、高速、リトリーブスピードの変化でサウンド、水押し、スプラッシュ＆バブルも変化しバイトを誘発。 ■タックルデータ ［ロッド］オライオン OCSC-69H スターゲイザー ［ライン］フロロカーボン 16lb ■タックルデータ ［ロッド］オライオン OCSC-71H+ ブラックローズ ［ライン］バスザイル・マジックハードR 20lb</v>
+      </c>
+      <c r="O482" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/OtterCrawler.html</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>EL1029</v>
+      </c>
+      <c r="B483">
+        <v>15</v>
+      </c>
+      <c r="C483" t="str">
+        <v>コンバットペンシルジャスティーン</v>
+      </c>
+      <c r="D483" t="str">
+        <v/>
+      </c>
+      <c r="E483" t="str">
+        <v/>
+      </c>
+      <c r="F483" t="str">
+        <v/>
+      </c>
+      <c r="G483" t="str">
+        <v>topwater_pencil</v>
+      </c>
+      <c r="H483" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I483" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J483" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K483" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットペンシルジャスティーン.jpg</v>
+      </c>
+      <c r="L483" t="str">
+        <v/>
+      </c>
+      <c r="M483" t="str">
+        <v/>
+      </c>
+      <c r="N483" t="str">
+        <v>クィックドッグウォークで誘い、確実に掛けるナチュラルペンシルベイト。 小型でスリムなボディに秘められた驚異の爆発力。エバーグリーンUSAスタッフ、ジャスティン・カーのリクエストに菊元俊文がインスパイアされて誕生したペンシルベイト、その名もコンバットペンシル・ジャスティーン。 ジャスティンの要求は、クリアウォーターの目の良いバスに見切られずにバイトに持ち込むこと。特にスモールマウスバスの目にも止まらぬファストバイトにもはじき飛ばされず、確実にフッキングにまで持ち込めること。それらに菊元がキャスト性能とバスを寄せる力をプラスしました。 その喰わせ頃サイズのボディとノンラトル仕様がナチュラル感を演出。また、アクションのスライド幅を短めに設定することで、クイックな高速ドッグウォークアクションがよりイージーに。ベイトが逃げまどうような素早い動きがバイトトリガーとなり、かつバスに見切られる隙を与えません。 そして、小型ペンシルベイトにありがちな「バイトは多いが飛ばされやすい」という弱点を克服するため、ウエイト量をボディサイズの割には多めに設計しました。さらに、小型ボディに3フック仕様。止めているときは、45度の浮姿勢により3つのフックの配置バランスが良好に。動いているときは、あえてロールを抑えた設定によりフックが横～上方向に振れることを抑制。不意にフックが水面から飛び出してしまうことを防ぎフッキング率を高めます。 そのうえ、真っ直ぐブレずに美しい姿勢で飛ぶため、小型ボディながら遠投性能、アキュラシー性能ともにアップしプレッシャーを軽減。また、すべてのバランスにより水に絡みつくアクションが生み出され、ナチュラルなスプラッシュ、バブル、サウンドを発生。そのボディサイズに似合わないバスを呼び寄せる力を併せ持ちます。 一見普通の小型ペンシルベイトに見えますが、その潜在能力は圧巻。フィールドテストでは、アメリカのビッグスモールマウスバスはもちろん、日本のタフなバスも魅了し続けました。その圧巻の水面を炸裂させる能力に加え、バイトしてきたバスの95パーセントはキャッチしていると豪語するジャスティン。その圧倒的なフッキング率を活かして、スモールマウスやスクーリングフィッシュのボイルシューティングにも最適です。 ■ 菊元俊文 ジャスティーン・ヒットシーン＆解説 ■関連製品：さらなる遠投性能をプラスしたジャスティーン115はコチラ</v>
+      </c>
+      <c r="O483" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Jastine.html</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>EL1030</v>
+      </c>
+      <c r="B484">
+        <v>15</v>
+      </c>
+      <c r="C484" t="str">
+        <v>コンバットペンシルジャスティーン115</v>
+      </c>
+      <c r="D484" t="str">
+        <v/>
+      </c>
+      <c r="E484" t="str">
+        <v/>
+      </c>
+      <c r="F484" t="str">
+        <v/>
+      </c>
+      <c r="G484" t="str">
+        <v>topwater_pencil</v>
+      </c>
+      <c r="H484" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I484" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J484" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K484" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/コンバットペンシルジャスティーン115.jpg</v>
+      </c>
+      <c r="L484" t="str">
+        <v/>
+      </c>
+      <c r="M484" t="str">
+        <v/>
+      </c>
+      <c r="N484" t="str">
+        <v>より遠くまで。狙ったターゲットは逃さない。 釣れるサイレントペンシルベイト進化形。 フィールドを問わず釣れるナチュラル・サイレントペンシルベイト、オリジナル（95ｍｍ）ジャスティーンのコンセプトはそのままに、さらなる投げやすさ、さらなる遠投性能をプラスしたジャスティーン115。アクションレスポンスとフッキングパフォーマンスにも優れる、扱いやすさと獲るための機能を追求して進化を遂げた、実戦型の釣れるペンシルベイトです。 1.飛距離 オリジナルを超える圧倒的な飛距離。遥か遠くのボイルも迎撃可能な、クリアウォーター・ハイプレッシャーレイク超広域対応型。 2.アクション クィックなドッグウォークがさらにダイナミックにかつイージーに。ノンラトル・サイレント仕様でスプーキーなバスをバイトに持ち込むハイスピード・ナチュラルアクション。 3.フッキング 激しすぎるストライクにも飛ばされず、弱々しいついばみバイトも絡め獲る。誘い出したターゲットは逃さない高いフッキングパフォーマンス。</v>
+      </c>
+      <c r="O484" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Justine115.html</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>EL1031</v>
+      </c>
+      <c r="B485">
+        <v>15</v>
+      </c>
+      <c r="C485" t="str">
+        <v>キッカーフロッグJr</v>
+      </c>
+      <c r="D485" t="str">
+        <v/>
+      </c>
+      <c r="E485" t="str">
+        <v/>
+      </c>
+      <c r="F485" t="str">
+        <v/>
+      </c>
+      <c r="G485" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H485" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I485" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J485" t="str">
+        <v>frog</v>
+      </c>
+      <c r="K485" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/キッカーフロッグjr.jpg</v>
+      </c>
+      <c r="L485" t="str">
+        <v/>
+      </c>
+      <c r="M485" t="str">
+        <v/>
+      </c>
+      <c r="N485" t="str">
+        <v>超コンパクトながら体高のあるボディが特徴的なキッカーフロッグJr。バイトの際、小粒で吸い込みやすいだけでなく、専用設計ワイドギャップフック＆潰れシロ（フックポイントとボディの隙間）を確保した背高形状ボディで劇的なフッキング～ランディング率を誇ります。そして、ボディをただ小さくしただけでは成し得ないキャスタビリティ＆水押しも、体高のあるボディならではの特性です。 中空ソフト素材の自然な着水音。魚を寄せる水押しクイックドッグウォーク。違和感なく吸い込ませるコンパクトさ。オープンウォーターでのトップウォーターゲームを成立させる喰わせの力をベースに、カバーの奥まで送り込みやすい小型ボディ＆スキッピングで強く撃ち込んでもフックがズレにくい設計により、攻撃的なフロッグゲームをストレスフリーで楽しめます。もちろん、枝などを利用した吊るしの釣りにも高次元で対応。 小さいことを武器にしながらも「小型フロッグ」という枠だけでは捉えきれないユニークな仕様で、専用タックルが必要な「いわゆるフロッグ」というカテゴリーにとどまらない様々な可能性を秘めた超コンパクトフロッグ、それがキッカーフロッグJrです。 ▶ キッカーフロッグJr アクション動画 ■ キッカーフロッグシリーズ ラインナップ ・キッカーフロッグ Jr［45mm 8.0g］ ・キッカーフロッグ(オリジナル)［58mm 13.5g］</v>
+      </c>
+      <c r="O485" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/KickerFrogJr.html</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>EL1032</v>
+      </c>
+      <c r="B486">
+        <v>15</v>
+      </c>
+      <c r="C486" t="str">
+        <v>キッカーフロッグ</v>
+      </c>
+      <c r="D486" t="str">
+        <v/>
+      </c>
+      <c r="E486" t="str">
+        <v/>
+      </c>
+      <c r="F486" t="str">
+        <v/>
+      </c>
+      <c r="G486" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H486" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I486" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J486" t="str">
+        <v>frog</v>
+      </c>
+      <c r="K486" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/キッカーフロッグ.jpg</v>
+      </c>
+      <c r="L486" t="str">
+        <v/>
+      </c>
+      <c r="M486" t="str">
+        <v/>
+      </c>
+      <c r="N486" t="str">
+        <v>ハイクォリティーなフロッグゲームを誰にでも可能にしたコンパクトフロッグ。 進化したキッカーフロッグはフロッグゲームをもっと身近なものにするために生まれました。ライギョではなくバス専用のフロッグであるキッカーフロッグはストロングながらやや細身のシングルフックを搭載。フロッグで誰もが悩むフッキング率を飛躍的に向上させ、誰にでも簡単にクイックなドッグウォークが演出できます。バスが好む極めてナチュラルな着水音とキレのあるアクションはオープンウォーターでも威力を発揮します。 今まで、エクストラヘビーの専用タックルが必要とフロッグゲームに尻込みしていたアングラーもオープンウォーターやライトカバーならMH～Hクラスのタックルでフロッグゲームを楽しむことが出来ます。勿論、フッキング性能と相反しがちなウィードレス性能も精度の高い成型技術と絶妙のバランス設計で両立。ヘビータックルでのカバーゲームをより高次元なものにします。 コンパクトなボディーはその芸達者ぶりと相まってタフタイム、スレたフィールドでこそ威力を発揮。キッカーフロッグ。劇的進化。 ■ キッカーフロッグシリーズ ラインナップ ・キッカーフロッグ Jr［45mm 8.0g］ ・キッカーフロッグ(オリジナル)［58mm 13.5g］</v>
+      </c>
+      <c r="O486" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/KickerFrog.html</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>EL1033</v>
+      </c>
+      <c r="B487">
+        <v>15</v>
+      </c>
+      <c r="C487" t="str">
+        <v>ポッパーフロッグ</v>
+      </c>
+      <c r="D487" t="str">
+        <v/>
+      </c>
+      <c r="E487" t="str">
+        <v/>
+      </c>
+      <c r="F487" t="str">
+        <v/>
+      </c>
+      <c r="G487" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H487" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I487" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J487" t="str">
+        <v>frog</v>
+      </c>
+      <c r="K487" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ポッパーフロッグ.jpg</v>
+      </c>
+      <c r="L487" t="str">
+        <v/>
+      </c>
+      <c r="M487" t="str">
+        <v/>
+      </c>
+      <c r="N487" t="str">
+        <v>「フロッグだからこそ釣れるバス」「フロッグだけが狙える場所」を身を持って知る菊元俊文がプロデュースする“ポッパーフロッグ”。中空セルフウィードレスボディ、ダブルフック装着のポッパータイプフロッグです。フロッグチューンに不慣れなアングラーにも安心のパッケージから出して、そのまま使えるノンチューン仕様。 ウィードベッド、リリーパッド攻略。またそれらのエッジ＆ポケットでのポップサウンドによるアピールは強力で、その威力は菊元をして「通常のフロッグで出ない時程、ポッパーならではの威力が分る。」と言わせしめます。 また、ウィードベッドのみならず、通常、ジグやテキサスのステージとなるレイダウンの奥、岸とゴミのスキ間、オーバーハングの奥の奥、桟橋の下へのスキッピング、リザーバーのゴミだまりetc…。ポッパーフロッグの圧倒的ウィードレス性能はそんなステージでこそ威力を発揮するのです。 そして中空ならではの甘い着水音とポップサウンドがバスに違和感を与えず、ストライクを誘発。ポッパーフロッグ。「浮いているからこそ出るバスがいる。」という菊元の主張。貴方は強烈なストライクと同時にその意味を理解するはずである。</v>
+      </c>
+      <c r="O487" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/PopperFrog.html</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>EL1034</v>
+      </c>
+      <c r="B488">
+        <v>15</v>
+      </c>
+      <c r="C488" t="str">
+        <v>ジャングルウォーカー ミニ</v>
+      </c>
+      <c r="D488" t="str">
+        <v/>
+      </c>
+      <c r="E488" t="str">
+        <v/>
+      </c>
+      <c r="F488" t="str">
+        <v/>
+      </c>
+      <c r="G488" t="str">
+        <v>spinnerbait</v>
+      </c>
+      <c r="H488" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I488" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J488" t="str">
+        <v>spin_flash</v>
+      </c>
+      <c r="K488" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジャングルウォーカー_ミニ.jpg</v>
+      </c>
+      <c r="L488" t="str">
+        <v/>
+      </c>
+      <c r="M488" t="str">
+        <v/>
+      </c>
+      <c r="N488" t="str">
+        <v>なにより、スピナーベイトをガツンとひったくるような衝撃バイトは、本当にやみつきになりますよ！」 大西健太Instagram「ジャングルウォーカー ミニ」の釣果投稿 ・霞ヶ浦／おかっぱり → ・四国リザーバー／ボート → ・四国リザーバー／おかっぱり → ・琵琶湖／ボート① → ・琵琶湖／ボート② → ・琵琶湖／ボート③ → ・琵琶湖／ボート④ → ・琵琶湖／ボート⑤ → コンパクトスピナーベイトの代名詞、SRミニ（2020年生産終了）とのサイズ比較</v>
+      </c>
+      <c r="O488" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/JungleWalkerMini.html</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>EL1035</v>
+      </c>
+      <c r="B489">
+        <v>15</v>
+      </c>
+      <c r="C489" t="str">
+        <v>ジャングルウォーカー</v>
+      </c>
+      <c r="D489" t="str">
+        <v/>
+      </c>
+      <c r="E489" t="str">
+        <v/>
+      </c>
+      <c r="F489" t="str">
+        <v/>
+      </c>
+      <c r="G489" t="str">
+        <v>spinnerbait</v>
+      </c>
+      <c r="H489" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I489" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J489" t="str">
+        <v>spin_flash</v>
+      </c>
+      <c r="K489" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジャングルウォーカー.jpg</v>
+      </c>
+      <c r="L489" t="str">
+        <v/>
+      </c>
+      <c r="M489" t="str">
+        <v/>
+      </c>
+      <c r="N489" t="str">
+        <v>大きめのブレードの水押し＆シルエットでアピールしながらも、動きはハイプレッシャーに強い細身で回転角の狭いタイトなバイブレーション。 そのうえ、スピナーベイトの特徴である「障害物回避性能」をさらに高めることで、「アピール力」と「喰わせる力」がより一層向上。 唯一無二のヘッド形状が生み出すこのルアーならではの障害物への当たり方＆かわし方は、カバーへのヒット＆アウェイやハングオフを高次元で成立させ、その際の動きの変化でバスの気を引き、口を使わせます。（詳しくは下部「特徴」をご覧ください） 【PV】超絶回避でバイトチャンスを演出！「ジャングルウォーカー」登場！</v>
+      </c>
+      <c r="O489" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/JungleWalker.html</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>EL1036</v>
+      </c>
+      <c r="B490">
+        <v>15</v>
+      </c>
+      <c r="C490" t="str">
+        <v>ラウドバズ</v>
+      </c>
+      <c r="D490" t="str">
+        <v/>
+      </c>
+      <c r="E490" t="str">
+        <v/>
+      </c>
+      <c r="F490" t="str">
+        <v/>
+      </c>
+      <c r="G490" t="str">
+        <v>buzzbait</v>
+      </c>
+      <c r="H490" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I490" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J490" t="str">
+        <v>spin_flash</v>
+      </c>
+      <c r="K490" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ラウドバズ.jpg</v>
+      </c>
+      <c r="L490" t="str">
+        <v/>
+      </c>
+      <c r="M490" t="str">
+        <v/>
+      </c>
+      <c r="N490" t="str">
+        <v>複雑なサウンド、強烈な波動。新タイプ威嚇系バズベイト。 トラブルの少ないシンプルな構造ながらも、独特な形状のペラにより複雑なサウンド＆強烈な波動を生み出すラウドバズ。圧倒的な浮き上がりの速さでプロダクティブゾーンをスローにロングトレースできることから、そのサウンドで徹底的にバスをイラつかせて水面が爆発するかのような激しいアタックを誘発します。 1.シンプルな構造によりトラブルが減少 バズベイトを構成する基本パーツ（ペラ、ビーズ、リベット等）のみで組み上げたシンプルな構造。付属的なパーツを使用しないことで、キャスト時の抵抗、回転を抑えまっすぐ飛ばしやすい。リトリーブ時にもウィードやゴミ等を拾いにくい。 2.複雑なサウンドでバスをイラつかせる 大量の泡を含む大きく柔らかい低音に、ビーズ、アルミペラ、ステンレスワイヤー、アルミリベットが擦れる金属的な高音＆きしみ音が加わり、複雑なサウンドを発生。 3.浮き上がりが速くスローにリトリーブできる 水掴みの良いペラと水切りが良く横倒れを防ぐ形状のヘッドにより、リトリーブ開始後すぐに浮き上がりプロダクティブゾーンをゆっくりとロングトレースできる。また、アシ際等の短いストライクゾーンもきっちり狙える。</v>
+      </c>
+      <c r="O490" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Loudbuzz.html</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>EL1037</v>
+      </c>
+      <c r="B491">
+        <v>15</v>
+      </c>
+      <c r="C491" t="str">
+        <v>キャスティングジグ シリコンラバーモデル</v>
+      </c>
+      <c r="D491" t="str">
+        <v/>
+      </c>
+      <c r="E491" t="str">
+        <v/>
+      </c>
+      <c r="F491" t="str">
+        <v/>
+      </c>
+      <c r="G491" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H491" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I491" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J491" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K491" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/キャスティングジグ_シリコンラバーモデル.jpg</v>
+      </c>
+      <c r="L491" t="str">
+        <v/>
+      </c>
+      <c r="M491" t="str">
+        <v/>
+      </c>
+      <c r="N491" t="str">
+        <v>キャスティングジグ シリコンラバーモデル キャスティングジグFECO対応モデル登場。 プロフェッショナルジグの名に相応しいクオリティ。キャスティングジグのシリコンラバーモデルはファインラバーオリジナルモデルよりフレアーの水押しが強く、よりナチュラルなカラーリングが魅力のプロモデルです。</v>
+      </c>
+      <c r="O491" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/CastingJigSiliconeRubber.html</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>EL1038</v>
+      </c>
+      <c r="B492">
+        <v>15</v>
+      </c>
+      <c r="C492" t="str">
+        <v>グラスリッパー</v>
+      </c>
+      <c r="D492" t="str">
+        <v/>
+      </c>
+      <c r="E492" t="str">
+        <v/>
+      </c>
+      <c r="F492" t="str">
+        <v/>
+      </c>
+      <c r="G492" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H492" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I492" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J492" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K492" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/グラスリッパー.jpg</v>
+      </c>
+      <c r="L492" t="str">
+        <v/>
+      </c>
+      <c r="M492" t="str">
+        <v/>
+      </c>
+      <c r="N492" t="str">
+        <v>なので、川、野池、リザーバー、どんなタイプのフィールドでも出番があるラバージグでもあります。 こだわり抜いてつくりあげた、今までにない特徴的なヘッド形状のグラスリッパー。 アーキーヘッドの障害物に対してのすり抜けやすさとフットボールヘッドの移動距離を抑えたアクションを併せ持っているので跳ねてもよし。テキサスリグスイミングに近いウィードの抜けと一般的なラバージグ以上の水押し＆ナチュラル感を併せ持っているので巻いてもよし。ウィードに対するアプローチでバスに口を使わせるために必要な要素を自然に、時に意図的に演出できるのがグラスリッパーです。 みなさんぜひ使いこなしてデカバスをたくさん釣ってください。それから、対ウィードラバージグ＝カバージグでもあるので、あらゆるカバーに対して投げてみてくださいね。</v>
+      </c>
+      <c r="O492" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/GrassRipper.html</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>EL1039</v>
+      </c>
+      <c r="B493">
+        <v>15</v>
+      </c>
+      <c r="C493" t="str">
+        <v>フットボールジグ シリコンラバーモデル</v>
+      </c>
+      <c r="D493" t="str">
+        <v/>
+      </c>
+      <c r="E493" t="str">
+        <v/>
+      </c>
+      <c r="F493" t="str">
+        <v/>
+      </c>
+      <c r="G493" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H493" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I493" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J493" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K493" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/フットボールジグ_シリコンラバーモデル.jpg</v>
+      </c>
+      <c r="L493" t="str">
+        <v/>
+      </c>
+      <c r="M493" t="str">
+        <v/>
+      </c>
+      <c r="N493" t="str">
+        <v>デカバス対応フットボールジグにFECOモデル登場。 シリコンラバースカートを採用し、リアルで生き物っぽいテクスチャーを醸し出すフットボールジグ・シリコンラバーモデル。樹脂タングステン素材のフットボールヘッド部に重心を集中させ、より速いフォールと高感度化を実現しました。 さらに、絶妙なサイズ＆線径の特注フックで刺さりの良さとデカバスを獲るための強度を両立。垂直フォール、リフト＆フォール、ホンガリング、ボトムクロール、ボトムステイなどあらゆるフットボールジグのメソッドに応え、確実に掛けて逃がさない、FECO対応プロフェッショナル仕様のフットボールジグです。</v>
+      </c>
+      <c r="O493" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/FootballJigSiliconeRubber.html</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>EL1040</v>
+      </c>
+      <c r="B494">
+        <v>15</v>
+      </c>
+      <c r="C494" t="str">
+        <v>カバークリーパー</v>
+      </c>
+      <c r="D494" t="str">
+        <v/>
+      </c>
+      <c r="E494" t="str">
+        <v/>
+      </c>
+      <c r="F494" t="str">
+        <v/>
+      </c>
+      <c r="G494" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H494" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I494" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J494" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K494" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/カバークリーパー.jpg</v>
+      </c>
+      <c r="L494" t="str">
+        <v/>
+      </c>
+      <c r="M494" t="str">
+        <v/>
+      </c>
+      <c r="N494" t="str">
+        <v>●フルサイズジグのボリューム感を嫌うバスに口を使わせるために。 ●ノーガードやモノガードのスモラバではスタックしてしまうようなカバーを躊躇なく攻めるために。 ●一般的なスモラバの細いフックでは不安な、カバーまわりでの強引なやりとりに対応するために。 ■初期ラインナップ（4サイズ）にコンパクトヘビーモデル（3サイズ）を追加し、対応領域が拡大。詳しくはコチラをご覧ください→</v>
+      </c>
+      <c r="O494" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/CoverCreeper.html</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>EL1041</v>
+      </c>
+      <c r="B495">
+        <v>15</v>
+      </c>
+      <c r="C495" t="str">
+        <v>メタルマスター</v>
+      </c>
+      <c r="D495" t="str">
+        <v/>
+      </c>
+      <c r="E495" t="str">
+        <v/>
+      </c>
+      <c r="F495" t="str">
+        <v/>
+      </c>
+      <c r="G495" t="str">
+        <v>spoon</v>
+      </c>
+      <c r="H495" t="str">
+        <v>metal</v>
+      </c>
+      <c r="I495" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J495" t="str">
+        <v>flutter_fall</v>
+      </c>
+      <c r="K495" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/メタルマスター.jpg</v>
+      </c>
+      <c r="L495" t="str">
+        <v/>
+      </c>
+      <c r="M495" t="str">
+        <v/>
+      </c>
+      <c r="N495" t="str">
+        <v>菊元俊文プロデュース。メタルマスターは滞空時間の長い水平姿勢でのフォーリングに不規則なロールとフラッタリングをプラスしたバイト誘発型ジギングスプーン。バーチカルのみならずキャスティングでも威力を発揮します。 菊元俊文オフィシャルブログ 2018.11.05「メタルマスター」より</v>
+      </c>
+      <c r="O495" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/MetalMaster.html</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>EL1042</v>
+      </c>
+      <c r="B496">
+        <v>15</v>
+      </c>
+      <c r="C496" t="str">
+        <v>クラッチヒッター</v>
+      </c>
+      <c r="D496" t="str">
+        <v/>
+      </c>
+      <c r="E496" t="str">
+        <v/>
+      </c>
+      <c r="F496" t="str">
+        <v/>
+      </c>
+      <c r="G496" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H496" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I496" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J496" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K496" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/クラッチヒッター.jpg</v>
+      </c>
+      <c r="L496" t="str">
+        <v/>
+      </c>
+      <c r="M496" t="str">
+        <v/>
+      </c>
+      <c r="N496" t="str">
+        <v>4.複合低音サウンドでビッグバスにアピール 5.素早い復帰＆自発的アクションでバイト誘発 【動画】クラッチヒッター複合低音サウンド＆余韻アクション バーニング帝国 『第二十一作戦 新人サポート隊 発掘 キャンプDE IN高知』（釣りビジョン：初回放送2016年9月30日）でクラッチヒッターが炸裂！ 50アップをはじめ約30本の爆釣劇を演じました。</v>
+      </c>
+      <c r="O496" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/ClutchHitter.html</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>EL1043</v>
+      </c>
+      <c r="B497">
+        <v>15</v>
+      </c>
+      <c r="C497" t="str">
+        <v>フラットフォース</v>
+      </c>
+      <c r="D497" t="str">
+        <v/>
+      </c>
+      <c r="E497" t="str">
+        <v/>
+      </c>
+      <c r="F497" t="str">
+        <v/>
+      </c>
+      <c r="G497" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H497" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I497" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J497" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K497" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/フラットフォース.jpg</v>
+      </c>
+      <c r="L497" t="str">
+        <v/>
+      </c>
+      <c r="M497" t="str">
+        <v/>
+      </c>
+      <c r="N497" t="str">
+        <v>清水盛三の絶対的コンフィデンス。 タフ＆ハイプレッシャー下のクランキングゲームが劇的進化。 とある低水温期のハイランドリザーバー……アメリカのトップアングラー達がシークレットベイトとして使い続けてきたローカルベイト・ウッド製フラットサイドクランクに圧倒的大差で釣り勝ち、清水盛三の自信を揺るぎないものにした盛三のコンフィデンスベイト、フラットフォース。 喰わせのデッドスローリトリーブからリアクションを誘発するスーパーファストリトリーブまで、ウッド製をも超えるハイピッチのキレとヌメヌメとした柔らさが共存する魅惑的なアクションを実現し、さらには、ウッド製の弱点であったバラつきや投げにくさを解消した高精度プラスチック成形。 ステイン～マディ―ウォーターのクランクベイトが効果的なフィールドでしばしば直面する晴天無風、水温低下等のタフコンディション。常に警戒心MAXレベルのバスが相手となるクリアウォーター＆プアカバーレイク。さらには、高性能魚探・GPSやスマートフォン・SNSの普及によるシークレットスポットの消滅等、タフ＆ハイプレッシャー化が進む昨今のフィールドにおけるクランキングゲームが劇的進化を遂げる。 ◉晴天無風、水温低下等のタフコンディション時 ◉派手な動きやラトルサウンドを嫌うハイプレッシャー時 ◉食べごろサイズのブルーギルをイミテートしたい時……等々 一般的なラウンドクランクが苦手とする状況下で威力を発揮します。 ラウンドタイプクランクとフラットサイドクランクの使い分け</v>
+      </c>
+      <c r="O497" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/FlatForce.html</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
+        <v>EL1044</v>
+      </c>
+      <c r="B498">
+        <v>15</v>
+      </c>
+      <c r="C498" t="str">
+        <v>ピッコロ ダイブシャロー</v>
+      </c>
+      <c r="D498" t="str">
+        <v/>
+      </c>
+      <c r="E498" t="str">
+        <v/>
+      </c>
+      <c r="F498" t="str">
+        <v/>
+      </c>
+      <c r="G498" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H498" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I498" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J498" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K498" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ピッコロ_ダイブシャロー.jpg</v>
+      </c>
+      <c r="L498" t="str">
+        <v/>
+      </c>
+      <c r="M498" t="str">
+        <v/>
+      </c>
+      <c r="N498" t="str">
+        <v>清水盛三の激釣れスモールクランク、ピッコロのシャローモデル。 ベイトタックルで楽々キャスト、スモールクランクの常識を超える圧巻の飛距離を叩き出すオリジナル・ピッコロ（潜行レンジ1.3～1.6ｍ）の性能を継承しながらも、よりシャロー攻めに向く特性を獲得するためのセッティングを施したシャローダイバー・スモールクランク（潜行レンジ0.7～1.0ｍ）。 ルアーを岸側（浅い側）に引いてくる度に根掛かりの恐怖がつきまとうオカッパリのクランキングや、エリアを手早くカバーするだけでなく喰わせの力も必要となる霞ケ浦水系のような広大なハイプレッシャー・シャローレイクで無敵の強さを発揮します。 ▶ピッコロダイブシャロー アクションムービー ▶MoDOの注目シャロクラ「ピッコロダイブシャロー【エバーグリーン】」を清水盛三が生解説 ・ピッコロ ダイブシャロー［40mm 6.4g］ ・ピッコロ(オリジナル)［40mm 6.4g］</v>
+      </c>
+      <c r="O498" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/PiccoloDiveShalllow.html</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>EL1045</v>
+      </c>
+      <c r="B499">
+        <v>15</v>
+      </c>
+      <c r="C499" t="str">
+        <v>ピッコロ</v>
+      </c>
+      <c r="D499" t="str">
+        <v/>
+      </c>
+      <c r="E499" t="str">
+        <v/>
+      </c>
+      <c r="F499" t="str">
+        <v/>
+      </c>
+      <c r="G499" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H499" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I499" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J499" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K499" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ピッコロ.jpg</v>
+      </c>
+      <c r="L499" t="str">
+        <v/>
+      </c>
+      <c r="M499" t="str">
+        <v/>
+      </c>
+      <c r="N499" t="str">
+        <v>釣れるのは当たり前。使いやすさを徹底追及。 クラス最高の飛距離とハイレスポンスアクション。 清水盛三が創り上げた世界基準のスモールクランク・ピッコロ。 ●スモールボディかつ固定ウエイトながらベイトタックルで楽々キャスト……スモールクランクの常識を超える圧巻の飛距離を叩き出す。 ●しっかり水を掴んで水を動かすキレのあるアクション＆ブルブルと手元に伝わる引き感……通常サイズのクランクベイトと同じ感覚で使える。 ●浮力、根掛かり回避性能、急速潜行能力…… スモールクランクとは思えない使用範囲の広さを持つ使い勝手の良いスモールクランクベイト。 ピッコロをひと言で表すと「とにかく釣れるクランクベイト」。「一生釣れ続けるルアー」を目指してつくったからね。「一生釣れ続ける……」は、すべてのモードルアーに流れる基本コンセプト。だから、僕のタックルボックスから今までリリースしたルアーがはぶかれることはない。実際、年々タックルボックスに入れないといけないルアーが増え続けて最近はロケの度に大変なことになっていたのに、またこれで持って行くものが増えてますます大変なことになるね（笑） ・ピッコロ ダイブシャロー［40mm 6.4g］ ・ピッコロ(オリジナル)［40mm 6.4g］</v>
+      </c>
+      <c r="O499" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Piccolo.html</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>EL1046</v>
+      </c>
+      <c r="B500">
+        <v>15</v>
+      </c>
+      <c r="C500" t="str">
+        <v>ゼルク プティ</v>
+      </c>
+      <c r="D500" t="str">
+        <v/>
+      </c>
+      <c r="E500" t="str">
+        <v/>
+      </c>
+      <c r="F500" t="str">
+        <v/>
+      </c>
+      <c r="G500" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H500" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I500" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J500" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K500" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ゼルク_プティ.jpg</v>
+      </c>
+      <c r="L500" t="str">
+        <v/>
+      </c>
+      <c r="M500" t="str">
+        <v/>
+      </c>
+      <c r="N500" t="str">
+        <v>⑤ 不要なプレッシャーを掛けないサイレント仕様 ⑥ 素早い泳ぎ出し＆カバーヒット後の復帰 ▶ゼルク プティ ・サイズ:60mm／13.0g ・潜行レンジ:1.1～1.3m ▶ゼルク (オリジナル) ・サイズ:72mm／19.5g ・潜行レンジ:1.2～1.5m</v>
+      </c>
+      <c r="O500" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/ZeruchPetit.html</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>EL1047</v>
+      </c>
+      <c r="B501">
+        <v>15</v>
+      </c>
+      <c r="C501" t="str">
+        <v>ゼルク</v>
+      </c>
+      <c r="D501" t="str">
+        <v/>
+      </c>
+      <c r="E501" t="str">
+        <v/>
+      </c>
+      <c r="F501" t="str">
+        <v/>
+      </c>
+      <c r="G501" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H501" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I501" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J501" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K501" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ゼルク.jpg</v>
+      </c>
+      <c r="L501" t="str">
+        <v/>
+      </c>
+      <c r="M501" t="str">
+        <v/>
+      </c>
+      <c r="N501" t="str">
+        <v>シャローのビッグフィッシュを選んで釣るために。約10年という気の遠くなるような開発テスト期間を経て、清水盛三が求める理想のアクションを具現化した盛三のフルサイズシャロークランクベイト、ゼルク。 各部に見られる独特な形状は決して奇をてらったものではなく、盛三の言う「釣れるアクション」を生み出すためのカタチ。重心固定＆完全サイレント仕様。弾丸のような飛びとシャロークランクに必要な高浮力という相反する要素を両立。 絶対的に釣れるのはもちろんのこと、使いやすさにも徹底的にこだわり抜いた、オープンウォーター、グラス系カバー、ウッド系カバー、中層、ボトムを問わず信じて引き倒せる絶対的自信作です。 ① 固定ウエイトながら圧巻の飛距離 泳ぎ出しの早さ、アクションのキレ、安定性を求め固定ウエイトを採用しながらも、テールを急激に細く絞った形状により飛行姿勢が安定。固定ウエイトとは思えない飛距離を叩き出すことから、警戒心の強いシャローのビッグフィッシュにプレッシャーを掛けません。 ② ナチュラルなロールアクション モリゾープロデュース、釣れるクランクベイトの代表格であるワイルドハンチゆずりのロールアクションでナチュラルにアピール。フルサイズボディの存在感とロールによりややフラットなボディ側面で水を動かし、シャローのビッグフィッシュに強烈にアピールします。 ③ 速巻きでも抜群の直進安定性 リップだけでなくヘッドのへこみでも水を受けることで、アクションのキレはそのままに直進安定性を高めることに成功。シャローのビッグフィッシュをリアクションバイトさせるのに十分なスピードでルアーをコントロールすることができます。 ④ バスの視覚に訴えかける明滅効果 ラウンドとフラットサイドの中間形状ボディによるロールアクションがフラッシングによる明滅効果を生み出し、クランクベイトの振動、水押しで側線にアピールすることに加え、視覚面からも強烈にアピール。シャローのビッグバス攻略に威力を発揮します。 ⑤ 素早い泳ぎ出し＆カバーヒット後の復帰 ウエイトルームにきっちり収まる形状の低重心固定ウエイトにより着水直後から素早くアクションを開始。同時に、カバーに当たって一瞬バランスを崩した直後には素早く復帰してアクションを開始。ビッグバスに考える隙を与えずストライクへと導きます。 ⑥ 不要なプレッシャーを掛けないサイレント仕様 ウエイトルームにきっちり収まる形状の低重心固定ウエイトによりウエイトの遊びを排除しサイレント化。ボディサイズ＆アクションでアピールし、警戒心の強いビッグバスに不要なプレッシャーを掛けずバイトへと導きます。 ⑦ 状況を選ばない幅広い対応力 スクエア、コフィン、ラウンドのハイブリッド系リップがクセのないナチュラルなアクションを生み出すと同時に、多くの状況、フィールドに対応するオールラウンドな性能を発揮。その泳ぎ＆対応力がビッグフィッシュの確率を高めます。 清水盛三 番組取材で55cmオーバーを仕留める等、ゼルクが絶好調！ ▶ゼルクプティ ・サイズ:60mm／13.0g ・潜行レンジ:1.1～1.3m ▶ゼルク (オリジナル) ・サイズ:72mm／19.5g ・潜行レンジ:1.2～1.5m</v>
+      </c>
+      <c r="O501" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Zeruch.html</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
+        <v>EL1048</v>
+      </c>
+      <c r="B502">
+        <v>15</v>
+      </c>
+      <c r="C502" t="str">
+        <v>ワイルドハンチSR</v>
+      </c>
+      <c r="D502" t="str">
+        <v/>
+      </c>
+      <c r="E502" t="str">
+        <v/>
+      </c>
+      <c r="F502" t="str">
+        <v/>
+      </c>
+      <c r="G502" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H502" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I502" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J502" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K502" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ワイルドハンチsr.jpg</v>
+      </c>
+      <c r="L502" t="str">
+        <v/>
+      </c>
+      <c r="M502" t="str">
+        <v/>
+      </c>
+      <c r="N502" t="str">
+        <v>あのワイルドハンチの血統を受け継ぐシャロークランクの究極形。それが“ワイルドハンチSR”だ。潜行レンジは90cm。オリジナルのハンチよりも60～70cm程浅く設定。シャローウィードレイクや野池のおかっぱりでの操作性とオリジナルを継承した障害物回避性能を誇る。 アメリカ、日本の様々なフィールドで長期に渡りテストが繰り返され、そのアクションと釣るための性能は研ぎ澄まされ、遂にその完成を見た。盛三が徹底的に引き倒し、鍛え上げたのは「巻くだけで強烈に魚を寄せる集魚力とバイト誘発能力」。 本場のトーナメントでシャロー勝負が舞台となる時ほど、ルアーの持つ実力差がモロに出ることを盛三は痛い程知り尽くしている。そんな彼が、とことん信じて引き倒せる新たな切り札がこのワイルドハンチSRなのだ。 ボトムコンタクトさせない中層引きでのこのルアーの威力は凄まじいものがある。王道のシャロークランク“ワイルドハンチSR”。</v>
+      </c>
+      <c r="O502" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/WildhunchSr.html</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>EL1049</v>
+      </c>
+      <c r="B503">
+        <v>15</v>
+      </c>
+      <c r="C503" t="str">
+        <v>ワイルドハンチ</v>
+      </c>
+      <c r="D503" t="str">
+        <v/>
+      </c>
+      <c r="E503" t="str">
+        <v/>
+      </c>
+      <c r="F503" t="str">
+        <v/>
+      </c>
+      <c r="G503" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H503" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I503" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J503" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K503" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ワイルドハンチ.jpg</v>
+      </c>
+      <c r="L503" t="str">
+        <v/>
+      </c>
+      <c r="M503" t="str">
+        <v/>
+      </c>
+      <c r="N503" t="str">
+        <v>もちろんアメリカツアーにおいても、盛三のFLW3位入賞の原動力になるなど次々と実績を重ね続けている。バイト誘発型クランクベイト「ワイルドハンチ」。潜行深度1.5m。根掛かり知らずでバイトを誘う。投げ続け巻き続けるというシンプルな動作を繰り返した者こそがワイルドハンチの絶対的な威力を思い知ることだろう。 巻くだけで「勝てる」クランクベイト、ワイルドハンチは清水盛三さん曰く、「一生投げ続けられるルアー」だと言う。この言葉の真意を誕生当時の話しとともに伺った。 ワイルドハンチ誕生20周年記念特設ページ ワイルドハンチ誕生20周年を記念して特別限定アイテムを発売いたします。</v>
+      </c>
+      <c r="O503" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Wildhunch.html</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>EL1050</v>
+      </c>
+      <c r="B504">
+        <v>15</v>
+      </c>
+      <c r="C504" t="str">
+        <v>ラトルインワイルドハンチ</v>
+      </c>
+      <c r="D504" t="str">
+        <v/>
+      </c>
+      <c r="E504" t="str">
+        <v/>
+      </c>
+      <c r="F504" t="str">
+        <v/>
+      </c>
+      <c r="G504" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H504" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I504" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J504" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K504" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ラトルインワイルドハンチ.jpg</v>
+      </c>
+      <c r="L504" t="str">
+        <v/>
+      </c>
+      <c r="M504" t="str">
+        <v/>
+      </c>
+      <c r="N504" t="str">
+        <v>絶対的クランクに絶妙のサウンドがプラス。 発売以来、不動の人気No.1クランクとしての地位を確立したMo-DO渾身のクランクベイト「ワイルドハンチ」。今更、このクランクベイトの実力に異議を唱えるものは誰もいないだろう。 しかし、清水盛三はクランキングにおいてワンモデルで全ての状況に完全に対応出来ないことは、最初から理解していた。より、セレクティブな状況ではサイレントをラトリンモデルが凌駕することも少なくないと。「ラトルインハンチ」はもうひとつのワイルドハンチとして、最初から盛三の構想の中で存在していたのである。 オリジナルワイルドハンチだけではカバーしきれない、ラトルサウンドがより魚にアトラクティブに訴えかけ、より強い反応を示す状況は必ずある。絶対的なワイルドハンチの魚を引き付けるアクションによりラトルサウンドを共鳴させる為、モールドも専用に設計。ウエイトバランスも全てラトルインモデル専用にチューンナップがなされた。 一生信じて、使い倒せる。盛三の新たなコンフィデンスのかたまり。それがラトルインワイルドハンチだ。</v>
+      </c>
+      <c r="O504" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/RattleInWildhunch.html</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>EL1051</v>
+      </c>
+      <c r="B505">
+        <v>15</v>
+      </c>
+      <c r="C505" t="str">
+        <v>ワイルドハンチ8フッター</v>
+      </c>
+      <c r="D505" t="str">
+        <v/>
+      </c>
+      <c r="E505" t="str">
+        <v/>
+      </c>
+      <c r="F505" t="str">
+        <v/>
+      </c>
+      <c r="G505" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H505" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I505" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J505" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K505" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ワイルドハンチ8フッター.jpg</v>
+      </c>
+      <c r="L505" t="str">
+        <v/>
+      </c>
+      <c r="M505" t="str">
+        <v/>
+      </c>
+      <c r="N505" t="str">
+        <v>説明不要の絶対的威力。2.5ｍダイバーワイルドハンチ。 ワイルドハンチの「バイト誘発型アクション」を継承した、潜行深度約2.5ｍのワイルドハンチ8フッター。1.5ｍ以浅のバスにとって脅威であったオリジナル・ワイルドハンチ、その動きのまま下のレンジを直撃できるので、バスはさらに逃げ場を失うことになる。 もちろん、根掛かり回避能力の高さもオリジナル譲り。その潜行深度を利用して、今まで以上にボトムを果敢に攻めることも可能だ。さらに、オリジナルと比べてボリューム感のあるボディがキャスタビリティーを向上させるとともに、バイト誘発能力にアピール力をプラス。 ■ワイルドハンチシリーズ ラインナップ ・ワイルドハンチSR ・ワイルドハンチ ・ラトルインワイルドハンチ ・ワイルドハンチ8フッター</v>
+      </c>
+      <c r="O505" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Wildhunch8footer.html</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>EL1052</v>
+      </c>
+      <c r="B506">
+        <v>15</v>
+      </c>
+      <c r="C506" t="str">
+        <v>DDエックスオーバー</v>
+      </c>
+      <c r="D506" t="str">
+        <v/>
+      </c>
+      <c r="E506" t="str">
+        <v/>
+      </c>
+      <c r="F506" t="str">
+        <v/>
+      </c>
+      <c r="G506" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H506" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I506" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J506" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K506" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ddエックスオーバー.jpg</v>
+      </c>
+      <c r="L506" t="str">
+        <v/>
+      </c>
+      <c r="M506" t="str">
+        <v/>
+      </c>
+      <c r="N506" t="str">
+        <v>シャローのボトムから超ディープの中層まで、シチュエーション別使用例 ▪オープンウォーターの中層をただ巻き 例えば水深15ｍの中層5ｍにサスペンドするバスを、ただ巻きで喰わせる。シャッドライクな柔らかみのある動きで、物に当てずともバイトを誘発。ソフトベイトと違い、レンジキープが容易かつさらに深いレンジにサスペンドするバスを浮かせるパワーもある。 ▪ウィードフラットを広範囲に探る ウィードトップ3～5ｍのウィードフラットを広範囲に探る。ウィードに当てて浮かせるライザーテクニックが容易に実戦できる。通常のウィード攻略、当てて落とす（スピナーベイトのスローロール、ワームやラバージグの釣り）では反応しない魚が釣れる。 ▪バンクをショートキャストで流す ショートキャストでリザーバーの急深なバンクや河川のリップラップ、消波ブロックを舐めるように流す。ボトムやカバーに沿って隈なく、素早く探ることができる。ワームやラバージグよりも速いテンポで釣ることができるので、バスと巡り合う確率が高まる。</v>
+      </c>
+      <c r="O506" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/DdXOver.html</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>EL1053</v>
+      </c>
+      <c r="B507">
+        <v>15</v>
+      </c>
+      <c r="C507" t="str">
+        <v>ジータ</v>
+      </c>
+      <c r="D507" t="str">
+        <v/>
+      </c>
+      <c r="E507" t="str">
+        <v/>
+      </c>
+      <c r="F507" t="str">
+        <v/>
+      </c>
+      <c r="G507" t="str">
+        <v>vib</v>
+      </c>
+      <c r="H507" t="str">
+        <v>metal</v>
+      </c>
+      <c r="I507" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J507" t="str">
+        <v>vibration</v>
+      </c>
+      <c r="K507" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジータ.jpg</v>
+      </c>
+      <c r="L507" t="str">
+        <v/>
+      </c>
+      <c r="M507" t="str">
+        <v/>
+      </c>
+      <c r="N507" t="str">
+        <v>その力強い泳ぎは少しぐらいグラス（ウィード）が掛かってもアクションし続けるほどパワフル。複数の素材の組み合わせによる複雑なラトル音と相まって、遠くのバスにも気づかせ寄せるサーチベイトとしての役割が最高レベルまで高められています。同時にバスの好奇心や闘争心を刺激し、高活性時のみならずタフコンディション下でのリアクションバイトも誘発。また、その水掴みの良さはスローリトリーブでもしっかりアクションしアングラーの手元にその振動をしっかり伝達、低水温期や低活性バスにも威力を発揮します。 投げて巻くという基本動作はもちろん、これらのハイレスポンスな性能から、グラスに引っかけて切り裂くリッピングをはじめ、ジャーク＆フォール、クランキン＆ポーズなど様々なテクニックに高次元で対応します。さらには、超スローリトリーブやリフト＆フォールとの組み合わせで、従来のバイブレーションでは攻めきれなかったディープレンジも射程圏内に。 広範囲を素早く、狙いのスポットをスローに、クランキングで、ロッドワークで、表層からボトムまで・・・すべてが極限。バイブレーションの常識を超えた、フィールド、季節、コンディションに応じて様々なスピード、テクニック、レンジで使用可能なリップレスクランクベイト究極形、それが「ジータ」です。 ジータ2015クラシック出場記念特別カラー 詳しくはバナーをクリック！</v>
+      </c>
+      <c r="O507" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Zeta.html</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>EL1054</v>
+      </c>
+      <c r="B508">
+        <v>15</v>
+      </c>
+      <c r="C508" t="str">
+        <v>J×Jミノー</v>
+      </c>
+      <c r="D508" t="str">
+        <v/>
+      </c>
+      <c r="E508" t="str">
+        <v/>
+      </c>
+      <c r="F508" t="str">
+        <v/>
+      </c>
+      <c r="G508" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H508" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I508" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J508" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K508" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/j×jミノー.jpg</v>
+      </c>
+      <c r="L508" t="str">
+        <v/>
+      </c>
+      <c r="M508" t="str">
+        <v/>
+      </c>
+      <c r="N508" t="str">
+        <v>■サイズ：70mm・4.5g（スローフローティング） ■推奨タックル： ［ベイト］ Rod：ライト～ミディアムライト6'0"～7'0" Line：6～10lb. ［スピニング］ Rod：ウルトラライト～ライト6'0"～7'0" Line：4～8lb.／PE0.6〜0.8号 ▶投げて巻くだけで超釣れる！「J×Jミノー」清水盛三</v>
+      </c>
+      <c r="O508" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/JjMinnow.html</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>EL1055</v>
+      </c>
+      <c r="B509">
+        <v>15</v>
+      </c>
+      <c r="C509" t="str">
+        <v>エックスオーバー</v>
+      </c>
+      <c r="D509" t="str">
+        <v/>
+      </c>
+      <c r="E509" t="str">
+        <v/>
+      </c>
+      <c r="F509" t="str">
+        <v/>
+      </c>
+      <c r="G509" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H509" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I509" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J509" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K509" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/エックスオーバー.jpg</v>
+      </c>
+      <c r="L509" t="str">
+        <v/>
+      </c>
+      <c r="M509" t="str">
+        <v/>
+      </c>
+      <c r="N509" t="str">
+        <v>例えば、バンクをただ巻きで流しながら中層のバスにアピールし、所々に現れる岩や木、ウィードパッチに対してはその上や横でトゥイッチ＆ポーズを仕掛け、そこからさらに逃げるように高速リトリーブ……今まで仕留めきれなかったバスを獲るために、カテゴリーの境界線を飛び越えて様々なアプローチを可能にしてくれます。 ルアーを結び替えることなくクランクベイトとジャークベイト両方の機能を使えるため、タックルを絞りたいオカッパリアングラーにとっても頼れる存在となるでしょう。 ▪ウエイト固定+αのサイレント化仕様 他のルアーに反応がないタフな状況を想定して、バルサ製ルアーのようなレスポンスの良さとアクションの質を求め採用した完全固定ウエイト方式は、当然サイレント化にも寄与。しかし、実際ノンラトルのルアーでも、フックがボディに当たることでノイズを発している……そんなフックノイズを少しでも弱めるために。タフに対応するためのヌメヌメとした滑らかなアクションに、フックの振れを抑制しボディとの接触を軽減する役割も持たせ、一層のサイレント化を実現。 ▪90mmボディ × 3フックの不満を解消 ジャーキングで起こりがちなショートバイト（じゃれつくバイト、体当たりバイト等）を獲るために、3フックにこだわりました。しかし、90ｍｍという短めのボディにトレブルフックを3個搭載するには、「フック同士が絡まないようにするとフックサイズが小さくなりバラシの原因に、またバラシを防ぐためフックサイズを上げるとフックが絡む」という問題が……ボディに対してワンランク大きめの#6サイズ、ショートシャンクのトレブルマジックが、そんな不満を解消。</v>
+      </c>
+      <c r="O509" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/XOver.html</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>EL1056</v>
+      </c>
+      <c r="B510">
+        <v>15</v>
+      </c>
+      <c r="C510" t="str">
+        <v>フェイス87</v>
+      </c>
+      <c r="D510" t="str">
+        <v/>
+      </c>
+      <c r="E510" t="str">
+        <v/>
+      </c>
+      <c r="F510" t="str">
+        <v/>
+      </c>
+      <c r="G510" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H510" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I510" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J510" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K510" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/フェイス87.jpg</v>
+      </c>
+      <c r="L510" t="str">
+        <v/>
+      </c>
+      <c r="M510" t="str">
+        <v/>
+      </c>
+      <c r="N510" t="str">
+        <v>最強の喰わせ波動を持つ、キラーサイズジャークベイト。 盛三のジャーキング理論を余すところなく注ぎ込んだキラーサイズジャークベイト「フェイス87」。盛三が“信念”とこだわるオリジナル「フェイス」の飛びとアクションはそのままに、さらなるタフコンディション下での使用を想定し、“最強の喰わせ波動”を徹底追及しました。オリジナル譲りのイレギュラー広角ヒラ打ちダートアクション、さらにはポンプリトリーブによるタイトウィグルアクション＆ポーズにおいても、このサイズにしてベイトタックルでの使用を可能にした遠投性能により、さらに威力が倍増。スモールボディから繰り出される“静・動／激・微”の多彩なアクションと最強の喰わせ波動で、魚に見切らせずに一気にストライクまで持ち込むキラーサイズジャークベイトです。</v>
+      </c>
+      <c r="O510" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Faith87.html</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>EL1057</v>
+      </c>
+      <c r="B511">
+        <v>15</v>
+      </c>
+      <c r="C511" t="str">
+        <v>フェイス</v>
+      </c>
+      <c r="D511" t="str">
+        <v/>
+      </c>
+      <c r="E511" t="str">
+        <v/>
+      </c>
+      <c r="F511" t="str">
+        <v/>
+      </c>
+      <c r="G511" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H511" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I511" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J511" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K511" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/フェイス.jpg</v>
+      </c>
+      <c r="L511" t="str">
+        <v/>
+      </c>
+      <c r="M511" t="str">
+        <v/>
+      </c>
+      <c r="N511" t="str">
+        <v>盛三のこだわりを凝縮した究極のグローバルサーチベイト。 勝負師として絶対に釣る自信のある道具だけしか使わないという、強い信念を貫く盛三のこだわりジャークベイト「フェイス」。 ジャークベイトはシーズン、フィールドを問わず様々な状況下で効率よく魚を釣ることができるという“FAITH”（信念）を皆に証明すべく、ボディ形状、リップ構造、アクション、飛距離、潜行力等、全ての面において徹底的にこだわった究極のグローバルサーチベイトです。 独特の波動で水を大きく動かし、遠くの魚、深い魚を引き寄せ、イレギュラーダートで一気にストライクに持ち込む“寄せと喰わせ”の盛三こだわりアクション。広範囲を立体的に探る圧倒的な守備範囲の広さを誇ります。</v>
+      </c>
+      <c r="O511" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Faith.html</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
+        <v>EL1058</v>
+      </c>
+      <c r="B512">
+        <v>15</v>
+      </c>
+      <c r="C512" t="str">
+        <v>シャワーブローズ77.7</v>
+      </c>
+      <c r="D512" t="str">
+        <v/>
+      </c>
+      <c r="E512" t="str">
+        <v/>
+      </c>
+      <c r="F512" t="str">
+        <v/>
+      </c>
+      <c r="G512" t="str">
+        <v>topwater_walker</v>
+      </c>
+      <c r="H512" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I512" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J512" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K512" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/シャワーブローズ77_7.jpg</v>
+      </c>
+      <c r="L512" t="str">
+        <v/>
+      </c>
+      <c r="M512" t="str">
+        <v/>
+      </c>
+      <c r="N512" t="str">
+        <v>▶シャワーブローズ77.7 アクションムービー ▶ MoDOシャワーブローズ77.7トリプルセブンを清水盛三が生解説 ■ シャワーブローズシリーズ ラインナップ ・シャワーブローズ 77.7［77.7mm 9.3g］ ・シャワーブローズ ショーティー［105mm 16.3g］ ・シャワーブローズ (オリジナル)［125mm 26.0g］ ・シャワーブローズ ビッグママ［150mm 44.5g］ ・シャワーブローズ ソフトシェル［77mm 19.0g］</v>
+      </c>
+      <c r="O512" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Showerblows777.html</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>EL1059</v>
+      </c>
+      <c r="B513">
+        <v>15</v>
+      </c>
+      <c r="C513" t="str">
+        <v>シャワーブローズショーティー</v>
+      </c>
+      <c r="D513" t="str">
+        <v/>
+      </c>
+      <c r="E513" t="str">
+        <v/>
+      </c>
+      <c r="F513" t="str">
+        <v/>
+      </c>
+      <c r="G513" t="str">
+        <v>topwater_walker</v>
+      </c>
+      <c r="H513" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I513" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J513" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K513" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/シャワーブローズショーティー.jpg</v>
+      </c>
+      <c r="L513" t="str">
+        <v/>
+      </c>
+      <c r="M513" t="str">
+        <v/>
+      </c>
+      <c r="N513" t="str">
+        <v>オリジナルの威力を継承する喰わせのショーティー。 デカバスキラーの名を欲しいままにしてきた驚異のペンシルベイト“シャワーブローズ”。その圧倒的な集魚パワーを、さらに多くの実戦下で投入したいという盛三の必然的欲求から開発されたのが“シャワーブローズ・ショーティー”だ。 問答無用の水面サーチ能力とキャスタビリティー、クラス最強の「寄せ」と「飛び」性能はそのままに、あと一歩「喰わせる」為のボディサイズを徹底追及。オリジナルとのローテーションにより、幅広い状況に対応した戦略的なゲームが可能となった。 ■ シャワーブローズシリーズ ラインナップ ・シャワーブローズ 77.7［77.7mm 9.3g］ ・シャワーブローズ ショーティー［105mm 16.3g］ ・シャワーブローズ (オリジナル)［125mm 26.0g］ ・シャワーブローズ ビッグママ［150mm 44.5g］ ・シャワーブローズ ソフトシェル［77mm 19.0g］</v>
+      </c>
+      <c r="O513" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/ShowerblowsShorty.html</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>EL1060</v>
+      </c>
+      <c r="B514">
+        <v>15</v>
+      </c>
+      <c r="C514" t="str">
+        <v>シャワーブローズ</v>
+      </c>
+      <c r="D514" t="str">
+        <v/>
+      </c>
+      <c r="E514" t="str">
+        <v/>
+      </c>
+      <c r="F514" t="str">
+        <v/>
+      </c>
+      <c r="G514" t="str">
+        <v>topwater_walker</v>
+      </c>
+      <c r="H514" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I514" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J514" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K514" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/シャワーブローズ.jpg</v>
+      </c>
+      <c r="L514" t="str">
+        <v/>
+      </c>
+      <c r="M514" t="str">
+        <v/>
+      </c>
+      <c r="N514" t="str">
+        <v>超一流の集魚能力。 盛三の水面系サーチベイト。 シャワーブローズ。 独特のビルデザインとフラットサイドボディーから繰り出す強烈なスプラッタースピット＆バブル。大粒タングステンウエイトを配した、“水に突き刺さる”ラトルサウンドは、広大なエリアの魚にアピールし呼びよせます。更に空気抵抗の軽減も意識したボディー形状とウエイトバランスが、逆風下でも驚異的な飛距離を約束し、ワンキャストで探れる範囲がアクション、キャスタビリティーの両面から劇的に広がりました。 テールに装備したフェザーフックは、アクションの“静”と“動”のメリハリの狭間の“余韻”として、魚がブレイクウォーターしにくいコンディションでも、“キスバイト”をストライクに持ち込ませ、フックの吸い込みをサポート。また、ボディーがビンビンに反応するため、アクションの強弱が、僅かなロッドワークでも簡単にアジャスト可能な点も特筆モノ。より遠くの魚を激しいアクションで呼び寄せたい時、ナーバスな魚をソフトな波動で誘いたい時など、その日のコンディションによる、魚のアクションの好みの差もこれ一本で余裕で対応します。 絶妙の水がらみを誇るボディーバランスで、従来、トーナメンターの高等テクとされた、エッジの効いた連続クィックターンをボディーが水面に飛び出すことなく、たやすく演出でき、バスに追われ逃げ惑うベイトフィッシュアクションで、魚のスイッチが強烈に入ります。アングラーの腕への負担を大幅に軽減しながら、いままでやりづらかった“あのアクション”が思いのまま。シャワーブローズの驚きのアビリティーをあなたのものにしてください。 ■ シャワーブローズシリーズ ラインナップ ・シャワーブローズ 77.7［77.7mm 9.3g］ ・シャワーブローズ ショーティー［105mm 16.3g］ ・シャワーブローズ (オリジナル)［125mm 26.0g］ ・シャワーブローズ ビッグママ［150mm 44.5g］ ・シャワーブローズ ソフトシェル［77mm 19.0g］</v>
+      </c>
+      <c r="O514" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Showerblows.html</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>EL1061</v>
+      </c>
+      <c r="B515">
+        <v>15</v>
+      </c>
+      <c r="C515" t="str">
+        <v>シャワーブローズビッグママ</v>
+      </c>
+      <c r="D515" t="str">
+        <v/>
+      </c>
+      <c r="E515" t="str">
+        <v/>
+      </c>
+      <c r="F515" t="str">
+        <v/>
+      </c>
+      <c r="G515" t="str">
+        <v>topwater_walker</v>
+      </c>
+      <c r="H515" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I515" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J515" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K515" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/シャワーブローズビッグママ.jpg</v>
+      </c>
+      <c r="L515" t="str">
+        <v/>
+      </c>
+      <c r="M515" t="str">
+        <v/>
+      </c>
+      <c r="N515" t="str">
+        <v>ビッグフィッシュの闘争本能を煽る規格外の存在感。トップウォーターの死角を排除する圧巻の性能。 150mm・44.5g。シャワーブローズファミリー中最大サイズで最強のアピール力を誇るシャワーブローズ・ビッグママ ---------- ① 圧巻の遠投性能 後方重心かつ空気抵抗の少ないボディ形状に加え、シリーズ中最大サイズ＆質量のボディから生み出される異次元の飛距離。今まで攻めきれなかったスポットや魚にアプローチできます。 ② クイックターンレスポンス 抜群のボディ＆ウエイトバランスにより、その巨大さからは想像できないクイックターンレスポンスでロッドワークに超敏感に反応。圧倒的なサイズ＆質量のボディをイージーに思い通り動かすことができます。 ③ 激しいスピット＆バブル×強烈なラトルサウンド 圧倒的な存在感を放つサイズ＆質量のボディがずっしりと水に絡むことで、激しいスピット＆バブルを発生。さらに、左右への首振りアクションにより2つの大型ラトルが強烈なラトルサウンドを発生。ビッグフィッシュの闘争心に火をつけます。 ---------- ビッグバスを獲る能力はもちろんシリーズ中最強。さらに、他のトップウォータールアーでは手が出せないような強い風や波、流れの中においても圧倒的な存在感を放ち続けます。 ▶ シャワーブローズ ビッグママ アクションムービー ■ シャワーブローズシリーズ ラインナップ ・シャワーブローズ 77.7［77.7mm 9.3g］ ・シャワーブローズ ショーティー［105mm 16.3g］ ・シャワーブローズ (オリジナル)［125mm 26.0g］ ・シャワーブローズ ビッグママ［150mm 44.5g］ ・シャワーブローズ ソフトシェル［77mm 19.0g］</v>
+      </c>
+      <c r="O515" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/ShowerblowsBigMama.html</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>EL1062</v>
+      </c>
+      <c r="B516">
+        <v>15</v>
+      </c>
+      <c r="C516" t="str">
+        <v>ワンズバグ</v>
+      </c>
+      <c r="D516" t="str">
+        <v/>
+      </c>
+      <c r="E516" t="str">
+        <v/>
+      </c>
+      <c r="F516" t="str">
+        <v/>
+      </c>
+      <c r="G516" t="str">
+        <v>topwater_walker</v>
+      </c>
+      <c r="H516" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I516" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J516" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K516" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ワンズバグ.jpg</v>
+      </c>
+      <c r="L516" t="str">
+        <v/>
+      </c>
+      <c r="M516" t="str">
+        <v/>
+      </c>
+      <c r="N516" t="str">
+        <v>攻める。圧倒する。盛三のシークレットポッパー。 “ポッパーは時として他のベイトを圧倒してしまうほどの爆発力を秘めている”。アメリカのビッグトーナメントを転戦する盛三は、ポッパーの凄さ、恐ろしさを嫌というほど経験してきました。 そんな彼がポッパーに求めるノウハウとスキルを全てつぎ込んだ、渾身のポッパー「ワンズバグ」。“トップで釣りたい”からではなく、トップにしか反応しない魚を確実に仕留めるための“攻めのサーフェイスパターン”として、彼はこのポッパーを使います。 テールを跳ね上げたボディデザインが空気抵抗を軽減し、逆風を切り裂き、広範囲を探るためのロングキャスト性能を実現。さらにウエイトのある、やや大きめなボディボリュームによりコントロール性能もアップ。ロングディスタンスで狙ったスポットを正確に攻略することができます。 スピット、バブル、ポップと盛三がポッパーに求める3大要素を高次元で融合。その日の状況に合わせ、スピット、バブル、ポップの強弱が自由自在にコントロールできます。刻々と変化するコンディションにあわせ、その日に一番魚を寄せる泡、音で効率的かつ攻めのサーフェイスゲームを展開してください。 移動距離の少ないターンアクションから、高速トゥイッチまで、多彩なアクションバリエーションを自在に繰り出せます。立ち木や岩盤の際などのピンスポットでスローなアクション、バックウォーターで追われたベイトを演出した高速アクションなど、ロッドワークに敏感に反応。 さらにこのアクションに、このルアーならではの多彩な音と泡の組み合わせが、“ここはポッパー！”という状況下で確実な仕事をこなします。タングステン、ブラス、スチール、グラスの4種の異なる素材のラトルウエイトを装備し、それぞれが異なる周波数のサウンドを発します。このハイブリッドラトルサウンドが様々な状況下でも広く魚にアピールします。</v>
+      </c>
+      <c r="O516" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Onesbug.html</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>EL1063</v>
+      </c>
+      <c r="B517">
+        <v>15</v>
+      </c>
+      <c r="C517" t="str">
+        <v>シャワーブローズ ソフトシェル</v>
+      </c>
+      <c r="D517" t="str">
+        <v/>
+      </c>
+      <c r="E517" t="str">
+        <v/>
+      </c>
+      <c r="F517" t="str">
+        <v/>
+      </c>
+      <c r="G517" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H517" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I517" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J517" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K517" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/シャワーブローズ_ソフトシェル.jpg</v>
+      </c>
+      <c r="L517" t="str">
+        <v/>
+      </c>
+      <c r="M517" t="str">
+        <v/>
+      </c>
+      <c r="N517" t="str">
+        <v>「シャワーブローズ」のクイックターン×スピット＆バブルによる圧倒的集魚力に「フロッグ」のスナッグレス性能＆ソフトな水絡みを融合した、清水盛三のニュータイプベイト。 ●移動距離を抑えた連続クイックターンが得意技。アクションレスポンスに優れ一般的なフロッグと比べて、誰でも簡単に動かせます。 ●ボディ前方・側方の水を叩きながらスピット＆バブルを発生し水を動かし続けるハイアピールアクションとソフト素材ボディならではの柔らかい水当たり、天然素材テールによるナチュラルで自発的な誘いが共存。 ●アクション時はフックのズレを防ぎフックポイントをしっかりガード。バイトに対してはボディがつぶれてフックポイントが出やすく十分な掛かりシロを確保。カバー回避能力と掛けて獲る性能を両立。 ▶ シャワーブローズ ソフトシェル アクションムービー ■ シャワーブローズシリーズ ラインナップ ・シャワーブローズ 77.7［77.7mm 9.3g］ ・シャワーブローズ ショーティー［105mm 16.3g］ ・シャワーブローズ (オリジナル)［125mm 26.0g］ ・シャワーブローズ ビッグママ［150mm 44.5g］ ・シャワーブローズ ソフトシェル［77mm 19.0g］</v>
+      </c>
+      <c r="O517" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/ShowerblowsSoftshell.html</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>EL1064</v>
+      </c>
+      <c r="B518">
+        <v>15</v>
+      </c>
+      <c r="C518" t="str">
+        <v>Dゾーンフライ</v>
+      </c>
+      <c r="D518" t="str">
+        <v/>
+      </c>
+      <c r="E518" t="str">
+        <v/>
+      </c>
+      <c r="F518" t="str">
+        <v/>
+      </c>
+      <c r="G518" t="str">
+        <v>spinnerbait</v>
+      </c>
+      <c r="H518" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I518" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J518" t="str">
+        <v>spin_flash</v>
+      </c>
+      <c r="K518" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/dゾーンフライ.jpg</v>
+      </c>
+      <c r="L518" t="str">
+        <v/>
+      </c>
+      <c r="M518" t="str">
+        <v/>
+      </c>
+      <c r="N518" t="str">
+        <v>とにかく釣れるコンパクトスピナーベイト。それがD-ZONEフライだ。スピナーベイトに自信が持てないアングラーでも、見た目の小ささから安心して使え、なにより投げ続けることで必ず結果を出してくれる。 全体のボリュームをバランス良くコンパクト化したことで、1/4ozクラスながら抜群の飛距離を確保。ベイトフィッシュが小さいレイクや野池でスローなライトリグよりもはるかにイージーかつスピーディーにバスを釣らせてくれる武器。 ガーグリングでもスローローリングでもD-ZONEゆずりの絶妙のバイブレーションとバランスの良さを誇る。野池などでバスが落下する昆虫を捕食するなど、水面を意識している時には、ガーグリングによるハイスピードリアクションメソッドが有効となり、表層がダメならば、レンジを落としてゆっくり巻いてるだけで釣れる。 D-ZONEを生み出した清水盛三が「スピナーベイトは苦手という人にこそ使って欲しい。そしてこれでスピナーベイトに自信を持ってから、D-ZONEでビッグフィッシュ狙いへとステップアップしてくれたらホントに嬉しい」と語る自信作。D-ZONEフライ。とにかく釣れるコンパクトスピナーベイト。</v>
+      </c>
+      <c r="O518" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/DZoneFry.html</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>EL1065</v>
+      </c>
+      <c r="B519">
+        <v>15</v>
+      </c>
+      <c r="C519" t="str">
+        <v>Dゾーン</v>
+      </c>
+      <c r="D519" t="str">
+        <v/>
+      </c>
+      <c r="E519" t="str">
+        <v/>
+      </c>
+      <c r="F519" t="str">
+        <v/>
+      </c>
+      <c r="G519" t="str">
+        <v>spinnerbait</v>
+      </c>
+      <c r="H519" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I519" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J519" t="str">
+        <v>spin_flash</v>
+      </c>
+      <c r="K519" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/dゾーン.jpg</v>
+      </c>
+      <c r="L519" t="str">
+        <v/>
+      </c>
+      <c r="M519" t="str">
+        <v/>
+      </c>
+      <c r="N519" t="str">
+        <v>盛三の自信。競技用スペシャルスピナーベイト。 デカバスを呼ぶ機能を追求した結果、折れる危険性も合わせ持った諸刃の剣。しかし、その威力は完全に弱点を凌駕する…。 1レースのみに照準を絞ったフォーミュラマシンと同一のコンセプトから生まれた、清水盛三が放つトーナメントスペシャルスピナーベイト。 真似の出来ない、デカバスを引きつけてやまない波動。喰ってきたバスを確実に掛けて獲る力。清水盛三の自信。競技用スピナーベイトDゾーン。 ↓↓↓より詳しいDゾーンの解説はコチラ↓↓ ■Dゾーン20周年記念特設ページ スピナーベイトの既成概念を破壊する衝撃のデビューから20年。今なお数多くのアングラーに使い続けられ、そして釣れ続ける本当の実力。 ・Dゾーン ・ＤゾーンTG ・Ｄゾーンパワーブレード ・Ｄゾーンフライ / ＤゾーンフライTG</v>
+      </c>
+      <c r="O519" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/DZone.html</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>EL1066</v>
+      </c>
+      <c r="B520">
+        <v>15</v>
+      </c>
+      <c r="C520" t="str">
+        <v>DゾーンTG</v>
+      </c>
+      <c r="D520" t="str">
+        <v/>
+      </c>
+      <c r="E520" t="str">
+        <v/>
+      </c>
+      <c r="F520" t="str">
+        <v/>
+      </c>
+      <c r="G520" t="str">
+        <v>spinnerbait</v>
+      </c>
+      <c r="H520" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I520" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J520" t="str">
+        <v>spin_flash</v>
+      </c>
+      <c r="K520" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/dゾーンtg.jpg</v>
+      </c>
+      <c r="L520" t="str">
+        <v/>
+      </c>
+      <c r="M520" t="str">
+        <v/>
+      </c>
+      <c r="N520" t="str">
+        <v>発売以来、全国で圧倒的なデカバスに対する威力を見せ続け、盛三のアメリカツアー参戦後には、本場のツアープロがシークレットルアーとして使うなど、日本はおろか、ワールドワイドにD-ZONEの勢力は確実に拡大していきました。 そしてJB・NBCのトーナメントで使用可能な樹脂タングステンヘッド採用の「D-ZONE TG」が追加ラインナップ。真似の出来ない、デカバスを引きつけてやまない波動。喰ってきたバスを確実に掛けて獲る力。清水盛三の自信。 スピナーベイトの既成概念を破壊する衝撃のデビューから20年。 今なお数多くのアングラーに使い続けられ、そして釣れ続ける本当の実力。 Dゾーン20周年記念特設ページはコチラ→ ・Dゾーン ・ＤゾーンTG ・Ｄゾーンパワーブレード ・Ｄゾーンフライ / ＤゾーンフライTG</v>
+      </c>
+      <c r="O520" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/DZoneTg.html</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>EL1067</v>
+      </c>
+      <c r="B521">
+        <v>15</v>
+      </c>
+      <c r="C521" t="str">
+        <v>Dゾーンパワーブレード</v>
+      </c>
+      <c r="D521" t="str">
+        <v/>
+      </c>
+      <c r="E521" t="str">
+        <v/>
+      </c>
+      <c r="F521" t="str">
+        <v/>
+      </c>
+      <c r="G521" t="str">
+        <v>blade_bait</v>
+      </c>
+      <c r="H521" t="str">
+        <v>metal</v>
+      </c>
+      <c r="I521" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J521" t="str">
+        <v>vibration</v>
+      </c>
+      <c r="K521" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/dゾーンパワーブレード.jpg</v>
+      </c>
+      <c r="L521" t="str">
+        <v/>
+      </c>
+      <c r="M521" t="str">
+        <v/>
+      </c>
+      <c r="N521" t="str">
+        <v>ハイアピール＆ハイアプローチ。ワンランク上の集魚力を誇るD-ZONEパワーブレード。 1レースのみに照準を絞ったフォーミュラマシンと同一のコンセプト。デカバスキラーの名をほしいままにし、国内外のトーナメントで華々しい実績を誇るモンスタースピナーベイト“D−ZONE”。その血統を受け継ぎ、よりトルクフルなブレードを装着したものがD-ZONEパワーブレードだ。 トルクフルで抵抗の大きいブレードは、ノーマルモデルより浅いレンジをスローにアプローチすることができ、強烈なフラッシング、強力な波動で広範囲にアピールすることができる。アメリカの広大なトーナメントレイクにおいても絶大な集魚力を誇り、ノーマルモデルと使い分けることで幅広いレンジ攻略を可能にした。 スピナーベイトで確実に結果を残すために繰り返しテストされ生み出された、超実戦型盛三チューンドモデル“D-ZONEパワーブレード”。 スピナーベイトの既成概念を破壊する衝撃のデビューから20年。 今なお数多くのアングラーに使い続けられ、そして釣れ続ける本当の実力。 Dゾーン20周年記念特設ページはコチラ→ ・Dゾーン ・ＤゾーンTG ・Ｄゾーンパワーブレード ・Ｄゾーンフライ / ＤゾーンフライTG</v>
+      </c>
+      <c r="O521" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/DZonePowerblade.html</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>EL1068</v>
+      </c>
+      <c r="B522">
+        <v>15</v>
+      </c>
+      <c r="C522" t="str">
+        <v>バブルトルネード</v>
+      </c>
+      <c r="D522" t="str">
+        <v/>
+      </c>
+      <c r="E522" t="str">
+        <v/>
+      </c>
+      <c r="F522" t="str">
+        <v/>
+      </c>
+      <c r="G522" t="str">
+        <v>spinnerbait</v>
+      </c>
+      <c r="H522" t="str">
+        <v>wire</v>
+      </c>
+      <c r="I522" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J522" t="str">
+        <v>spin_flash</v>
+      </c>
+      <c r="K522" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/バブルトルネード.jpg</v>
+      </c>
+      <c r="L522" t="str">
+        <v/>
+      </c>
+      <c r="M522" t="str">
+        <v/>
+      </c>
+      <c r="N522" t="str">
+        <v>釣り勝てるバズ。驚異の集魚力とバイト誘発性能を手に入れた。 「良く飛ぶこと、真っすぐ引けること、うるさいこと。」盛三の言葉をそのまま引用するとバブルトルネードの開発コンセプトはこうなる。そして彼はこう付け足した。「絶対に釣り勝てるバズ」だと。 双方が逆回転するフロントプロップとリアプロップは直進性能を完璧なものにするだけでなく、プロップエンドにスプリングファンクションをセットすることにより、プロップ同志が接触することで、水中へのサウンド伝達能力を高めた。「カシャカシャ！」という湿った音と「カラカラ…」という乾いた音。そしてそれらがふれ合うハーモニーは、かなりノイジーであり、集魚力のみならず、バイト誘発能力において、明らかな差が出る。 また、バズベイティングにはつきものである、細いウィードやゴミの絡みをアッパーアーム＆ヘッドデザインによって解決。ダブルプロップによる浮き上がりの良さはもちろん、バズベイト最大の弱点であったフッキングの悪さも、フックデザイン、角度、パワーアングル設計によって、「絶妙」のフッキング性能を持たせてしまったのである。 通常2人が同じボートに乗る本場アメリカのトーナメントスタイルで盛三は「釣り負けることの恐さ」そして「釣り勝てるルアーの威力」を身を持って知った。アメリカンツアーでの彼の経験と自信、そして限りなき実戦テストがバブルトルネードを生み出す原動力となった。釣り勝てるバズベイト、清水盛三の自信“バブルトルネード”。</v>
+      </c>
+      <c r="O522" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Bubbletornado.html</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>EL1069</v>
+      </c>
+      <c r="B523">
+        <v>15</v>
+      </c>
+      <c r="C523" t="str">
+        <v>ジャックハンマー</v>
+      </c>
+      <c r="D523" t="str">
+        <v/>
+      </c>
+      <c r="E523" t="str">
+        <v/>
+      </c>
+      <c r="F523" t="str">
+        <v/>
+      </c>
+      <c r="G523" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H523" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I523" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J523" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K523" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジャックハンマー.jpg</v>
+      </c>
+      <c r="L523" t="str">
+        <v/>
+      </c>
+      <c r="M523" t="str">
+        <v/>
+      </c>
+      <c r="N523" t="str">
+        <v>2004年にブレーデッドジグの元祖であるチャターベイトが登場して以来、トップカテゴリートーナメント実戦の場でブレーデッドジグを使い続けてきた清水盛三の経験と、2014FLWツアー＆バスマスターエリートシリーズ両開幕戦でブレーデッドジグを武器に衝撃の2戦連続優勝を成し遂げた、ミスターブレーデッドジグ、ブレット・ハイトのアイデアを融合してつくりあげたブレーデッドジグの核心を突くブレーデッドジグ、その名もジャックハンマー。 その半端ではないこだわりは、心臓部であるブレードやヘッド、さらにはフック、ラバースカート、トレーラーキーパー等のメインパーツはもちろんのこと、果てはブレード穴（スナップ、ヘッドとの接続部）の位置およびサイズのコンマ単位での調整にまで及んだ。 ジャックハンマー（削岩機）という名の由来となった「手元に響く明確な振動」＆「ブレードとヘッドがぶつかり合う低音サウンド」を始め、豊富な実践＆最強の実績によってジャックハンマーに込められたブレーデッドジグの核心とは…… 数多くの機能を備え、それらすべてがハイレベル。圧倒的な使い勝手の良さで釣り勝てる、夢のスーパーブレーデッドジグ、それがジャックハンマー。 ① 基盤リップのウッドクランクベイトを彷彿させるキレキレの超ハイピッチ・ローリング＆ウォブリングアクション ➡ タフバスに効く ② ロッドティップを通じて手元に「ブルブルブル……」と明確な振動を伝える ➡ ルアーの泳ぎから水中をイメージできる ③ 強烈なバイブレーションによりブレードとヘッドがぶつかり合い、衝撃波＆サウンドを発生 ➡ ビッグバスに強烈にアピール ［ジャックハンマー サウンド］ https://www.evergreen-fishing.com/news_html/img/jhb_sound.mp3 ④「振動が強い＝引き抵抗が強い！？」……という常識を覆す、非常に軽いリトリーブ抵抗 ➡ 疲れ知らずで集中してやり切れる ⑤ スローリトリーブでもしっかりアクションし、ファストリトリーブでも飛び出さない ➡ 幅広い状況に対応できる ⑥ 一定リトリーブでは不用意にバランスを崩さず真っ直ぐ泳ぎ続ける ➡ イメージ通りのラインを通すことができる ⑦ 安定感の中に不安定が共存。瞬間的なリトリーブスピードアップに敏感に反応し、一瞬抜けるようなダートアクションを生み出す ➡ 狙ったところで仕掛けることができる ⑧ ボトムやモノに当たると、バランスを崩して一瞬イレギュラーなアクションを演出後、素早く立ち直り軌道修正する ➡ リアクションバイトを誘発できる ⑨ 着水直後、ラインとブレードの絡みを防ぎ、すばやく確実に水を掴みアクション開始。ダート直後も迅速に復帰 ➡ 着水＆ダート直後の一瞬のバイトチャンスを逃さない ⑩ 水面を跳ねる石投げの石のような平たいヘッド形状でオーバーハングの奥にスキッピングさせやすい ➡ 普通は巻き物を通さないコースを釣れる ⑪ 大きめのトレーラーやラフな使用にもダブルワイヤーキーパーでトレーラーをしっかりホールド ➡ ズレを直すストレスが掛からない ⑫ 刺さりやすくバラシにくい形状のヘビーワイヤーフックでビッグフィッシュを逃さない ➡ 障害物周りでの強引なファイトもOK ①～⑫の特徴を下のアクション動画でチェック↓↓↓ ウィードトップ等、狙いの水深に合わせてウエイトを使い分けることで釣果がアップ！ ▶3/8oz：0.3～1ｍ ▶1/2oz：1～2ｍ ▶3/4oz：2～3.5ｍ ▶1.2oz：3.5～6ｍ ※レンジはラインサイズやリトリーブスピード、トレーラー等によって変わります。 ◉ ジャックハンマー・ヘビーウエイトバージョン（3/4oz &amp; 1.2oz）についてはコチラもご覧ください。</v>
+      </c>
+      <c r="O523" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Jackhammer.html</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>EL1070</v>
+      </c>
+      <c r="B524">
+        <v>15</v>
+      </c>
+      <c r="C524" t="str">
+        <v>ジャックハンマーTG</v>
+      </c>
+      <c r="D524" t="str">
+        <v/>
+      </c>
+      <c r="E524" t="str">
+        <v/>
+      </c>
+      <c r="F524" t="str">
+        <v/>
+      </c>
+      <c r="G524" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H524" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I524" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J524" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K524" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジャックハンマーtg.jpg</v>
+      </c>
+      <c r="L524" t="str">
+        <v/>
+      </c>
+      <c r="M524" t="str">
+        <v/>
+      </c>
+      <c r="N524" t="str">
+        <v>清水盛三&amp;ブレットハイト共同開発、トッププロのシークレットベイト「ジャックハンマー」にJB・NBCトーナメントで使用可能な樹脂タングステンヘッドモデルが登場。 数多くの機能を備え、それらすべてがハイレベル。圧倒的な使い勝手の良さで釣り勝てる、夢のスーパーブレーデッドジグ、それがジャックハンマー。 ❶ 基盤リップのウッドクランクベイトを彷彿させるキレキレの超ハイピッチ・ローリング＆ウォブリングアクション ➡ タフバスに効く ❷ ロッドティップを通じて手元に「ブルブルブル……」と明確な振動を伝える ➡ ルアーの泳ぎから水中をイメージできる ❸ 強烈なバイブレーションによりブレードとヘッドがぶつかり合い、衝撃波＆サウンドを発生 ➡ ビッグバスに強烈にアピール ❹「振動が強い＝引き抵抗が強い！？」……という常識を覆す、非常に軽いリトリーブ抵抗 ➡ 疲れ知らずで集中してやり切れる ❺ スローリトリーブでもしっかりアクションし、ファストリトリーブでも飛び出さない ➡ 幅広い状況に対応できる ❻ 一定リトリーブでは不用意にバランスを崩さず真っ直ぐ泳ぎ続ける ➡ イメージ通りのラインを通すことができる ❼ 安定感の中に不安定が共存。瞬間的なリトリーブスピードアップに敏感に反応し、一瞬抜けるようなダートアクションを生み出す ➡ 狙ったところで仕掛けることができる ❽ ボトムやモノに当たると、バランスを崩して一瞬イレギュラーなアクションを演出後、素早く立ち直り軌道修正する ➡ リアクションバイトを誘発できる ❾ 着水直後、ラインとブレードの絡みを防ぎ、すばやく確実に水を掴みアクション開始。ダート直後も迅速に復帰 ➡ 着水＆ダート直後の一瞬のバイトチャンスを逃さない ❿ 水面を跳ねる石投げの石のような平たいヘッド形状でオーバーハングの奥にスキッピングさせやすい ➡ 普通は巻き物を通さないコースを釣れる ⓫ 大きめのトレーラーやラフな使用にもダブルワイヤーキーパーでトレーラーをしっかりホールド ➡ ズレを直すストレスが掛からない ⓬ 刺さりやすくバラシにくい形状のヘビーワイヤーフックでビッグフィッシュを逃さない ➡ 障害物周りでの強引なファイトもOK ジャックハンマーTG/JACK HAMMER TG アクションムービー</v>
+      </c>
+      <c r="O524" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/JackhammerTg.html</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>EL1071</v>
+      </c>
+      <c r="B525">
+        <v>15</v>
+      </c>
+      <c r="C525" t="str">
+        <v>ジャックハンマーSB</v>
+      </c>
+      <c r="D525" t="str">
+        <v/>
+      </c>
+      <c r="E525" t="str">
+        <v/>
+      </c>
+      <c r="F525" t="str">
+        <v/>
+      </c>
+      <c r="G525" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H525" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I525" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J525" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K525" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジャックハンマーsb.jpg</v>
+      </c>
+      <c r="L525" t="str">
+        <v/>
+      </c>
+      <c r="M525" t="str">
+        <v/>
+      </c>
+      <c r="N525" t="str">
+        <v>視界が遮られるウィードエリアでは音はさらに重要な要素になるが、晴天無風時や人が多いエリアで強すぎる人工的なサウンドはバスに嫌われてしまう。 そこでジャックハンマーSB。自然な音でプレッシャーをかけずに気づかせながらも、ルアーをウィードに引っ掛け突然音と存在を消してやる。バスが音の主を気になり始めたところでハングオフ。すると、たまらず反射的にバイト。 これも音の有無にかかわらずよく使われるテクニックであるが、ベイトフィッシュライクなサウンドが付加されることで得られる効果は大きい。 サウンドによるアピール力を持ちながら、ある意味サイレントモデルのルアー以上にローインパクト。シルエット、アクション、サウンドの3要素でベイトフィッシュを演じるブレーデッドジグ、ジャックハンマーSB。ハイプレッシャー下で釣り勝つために。今ここにブレーデッドジグの新たな扉が開かれた。</v>
+      </c>
+      <c r="O525" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/JackhammerSb.html</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>EL1072</v>
+      </c>
+      <c r="B526">
+        <v>15</v>
+      </c>
+      <c r="C526" t="str">
+        <v>ジャックハンマー ベイビージャック</v>
+      </c>
+      <c r="D526" t="str">
+        <v/>
+      </c>
+      <c r="E526" t="str">
+        <v/>
+      </c>
+      <c r="F526" t="str">
+        <v/>
+      </c>
+      <c r="G526" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H526" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I526" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J526" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K526" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジャックハンマー_ベイビージャック.jpg</v>
+      </c>
+      <c r="L526" t="str">
+        <v/>
+      </c>
+      <c r="M526" t="str">
+        <v/>
+      </c>
+      <c r="N526" t="str">
+        <v>釣り勝てるというコンセプトを元に考え抜かれた、その基本性能を継承しながらも、さらなる領域へと活躍の場を広げるために。清水盛三＆ブレットハイトが三度世に問うジャックハンマー、ベイビージャック。 ◉ジャックハンマー（削岩機）の名の通り、ハイピッチかつエッジの効いたバイブレーション＆サウンドだが、強さはジャックハンマー（オリジナル）とジャックハンマーSB（ステルスブレード）の中間。ゆえに、使う場面や状況が多い、先発ラインナップの中心的な存在。 ◉同ウエイトのオリジナルと比較してよりコンパクトなシルエットなので、リトリーブスピードが同じなら深いレンジを、同一レンジなら速く引ける。オリジナルで獲り切れなかったバスを獲るための、抑えの切り札的な存在。 ◉オリジナルと同ウエイトでもコンパクトだからさらに良く飛ぶ。さらに、ジャックハンマー初となる1/4ozをラインナップし浅い場所を釣りやすい。プレッシャーにも強く、オカッパリにも有効なスペシャリスト的存在。</v>
+      </c>
+      <c r="O526" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/JackhammerBabyJack.html</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>EL1073</v>
+      </c>
+      <c r="B527">
+        <v>15</v>
+      </c>
+      <c r="C527" t="str">
+        <v>モード リアクションフットボール</v>
+      </c>
+      <c r="D527" t="str">
+        <v/>
+      </c>
+      <c r="E527" t="str">
+        <v/>
+      </c>
+      <c r="F527" t="str">
+        <v/>
+      </c>
+      <c r="G527" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H527" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I527" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J527" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K527" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/モード_リアクションフットボール.jpg</v>
+      </c>
+      <c r="L527" t="str">
+        <v/>
+      </c>
+      <c r="M527" t="str">
+        <v/>
+      </c>
+      <c r="N527" t="str">
+        <v>デカバスを確実に掛けてバラさないロングシャンクフックは、盛三自らが線材を曲げてデザイン。またトレーラーを確実にホールドし、ズレにくいキーパー形状には彼のこだわりが込められている。 独自のヘッド形状、フック形状、ガードの位置と堅さの調節。盛三いわく、「普通に根掛かりしにくくて、効率良く、デカイのをディープで獲れるジグだ。」と。 ただし、彼の言う、「普通」というレベルが常人とは全く異なる高いレベルだということは、Dゾーン、ワイルドハンチetc…Mo-DOの他のルアーを見れば判るだろう。 アメリカでは試合中にロクマルを仕留め、帰国後の冬のリザーバーでのDVDロケでも入れ食いを演じた、Mo-DOリアクションフットボール。普通のレベルが違うラバージグだ。</v>
+      </c>
+      <c r="O527" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Reactionfootball.html</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>EL1074</v>
+      </c>
+      <c r="B528">
+        <v>15</v>
+      </c>
+      <c r="C528" t="str">
+        <v>IRジグ</v>
+      </c>
+      <c r="D528" t="str">
+        <v/>
+      </c>
+      <c r="E528" t="str">
+        <v/>
+      </c>
+      <c r="F528" t="str">
+        <v/>
+      </c>
+      <c r="G528" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H528" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I528" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J528" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K528" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/irジグ.jpg</v>
+      </c>
+      <c r="L528" t="str">
+        <v/>
+      </c>
+      <c r="M528" t="str">
+        <v/>
+      </c>
+      <c r="N528" t="str">
+        <v>で、僕的にどうしても欲しかったのが1/4oz（7g）と3/8oz（10.5g）の間に位置する5/16oz（8.8g）というウエイト。重すぎず軽すぎずのオールラウンドなウエイトで場所や状況を選ばず一年中どこでも使える。だから、本来は本気のトーナメントであと1本、できればサイズの良いバスを絞り出したい場面で使うためにつくったジグだけどオカッパリにも向いている。タックルも選ばないのでM～MHクラスのバーサタイルロッド1本持ってのオカッパリなんかにも最適。どこに行くにも、とりあえずタックルボックスに入れておけば使いどころは多いので重宝するラバージグだね。 実際の使用例を2、3あげると、2015年のバサーオールスタークラシックのメインベイトとして利根川のクイ、ブッシュ、レイダウンを釣るのにピッチングで使っていた。引っ掛からずにカバーをきっちり釣れるし、テキサスリグなんかと比べてもコンパクトながらもボリューム感があるシルエットでキーパーとビッグフィッシュ両方を狙える。 あと2015年秋のバーニング帝国のロケでは四国のリザーバーで岩盤に付くバスをフォールで釣っていった。5/16ozというウエイトでフットボールよりもゆっくり落とすことができるのに、変形ラウンドヘッドのおかげでフットボール以上に岩盤に沿ってフリーフォールさせやすいので効果的だった。 もうひとつ忘れられないのが2015年2月のバスマスタークラシックでのあの出来事。桟橋の下にサスペンドするバスをスキッピングで狙っていって掛けたスーパービッグだった。あのときは製品版ではなくテストも兼ねてプロトタイプを使っていたのと、極限の極寒状態で体が思うように動かず悔しい思いをしたけど、完成版を持ってリベンジしたいね。テキサスリグよりもスキッピングさせやすいし着水音も抑えやすいから、クリアなハイプレッシャーレイクでも効果的。</v>
+      </c>
+      <c r="O528" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/IrJig.html</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
+        <v>EL1075</v>
+      </c>
+      <c r="B529">
+        <v>15</v>
+      </c>
+      <c r="C529" t="str">
+        <v>スイミングトゥルーパー</v>
+      </c>
+      <c r="D529" t="str">
+        <v/>
+      </c>
+      <c r="E529" t="str">
+        <v/>
+      </c>
+      <c r="F529" t="str">
+        <v/>
+      </c>
+      <c r="G529" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H529" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I529" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J529" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K529" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/スイミングトゥルーパー.jpg</v>
+      </c>
+      <c r="L529" t="str">
+        <v/>
+      </c>
+      <c r="M529" t="str">
+        <v/>
+      </c>
+      <c r="N529" t="str">
+        <v>決められた時間内で結果を出さなければならないトーナメントにおいて、広くエリアをカバーできるルアー、すなわち、素早く広範囲を探ることができ、広範囲のバスにアピールする能力を持つルアーは必要不可欠。とはいえ、フィッシングプレッシャーの掛かったバスをバイトさせる能力も重要なのはもちろん、なおかつビッグフィッシュに強いルアーでなければ勝ちにはつながりません。 これらの一見矛盾する要素をすべて兼ね備えたルアーとして、清水盛三の豊富な知識と経験から導き出された答えはスイミングジグ。「変幻自在なシルエットを持ち、ビッグバスキラーでもあるラバージグをスピナーベイトのようにリトリーブして使うテクニック・ラバージグスイミングは、これからのトーナメントシーンを戦い抜く上でキーになる」と語る盛三の新たな武器、それがスイミングトゥルーパーです。 開発コンセプトは、巻きスピードやトレーラーの形状に左右されずまっすぐ安定して泳ぐこと、高いカバー回避性能を持つこと、そして掛けた魚を確実にランディングできること。これらスイミングジグとしての基本性能を、盛三が求める世界レベルの高い次元でクリアし、フィールドやシチュエーションを選ばない幅広い対応力を備えます。 さらに、そのコンパクトなシルエットかつナチュラルなアクションは、年々熾烈さを増す世界最高峰トーナメントの極限のプレッシャー下において大きな強みとなります。スピナーベイトやチャターベイトにはスレて反応しないビッグフィッシュをターゲットに、あらゆるフィールドを席巻。すべては勝つために。時代の要求に応える盛三の新たな武器、スイミングジグ・スイミングトゥルーパー。</v>
+      </c>
+      <c r="O529" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/SwimmingTrooper.html</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
+        <v>EL1076</v>
+      </c>
+      <c r="B530">
+        <v>15</v>
+      </c>
+      <c r="C530" t="str">
+        <v>ブルポイントシャッド</v>
+      </c>
+      <c r="D530" t="str">
+        <v/>
+      </c>
+      <c r="E530" t="str">
+        <v/>
+      </c>
+      <c r="F530" t="str">
+        <v/>
+      </c>
+      <c r="G530" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H530" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I530" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J530" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K530" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ブルポイントシャッド.jpg</v>
+      </c>
+      <c r="L530" t="str">
+        <v/>
+      </c>
+      <c r="M530" t="str">
+        <v/>
+      </c>
+      <c r="N530" t="str">
+        <v>巻きスピードにかかわらずベストなアクションをキープできる秘密 ボディとテールを繋ぐ位置には3本のスリット。 スローからファストまで使えるジャックハンマーの能力を活かし切るために、水の抵抗に応じて、テールの動きを適正にコントロールする機能も持つ。 ゆっくり巻き（弱い力）でも力が伝わり敏感に動き、速巻き（強い力）では力を程良く逃がしてオーバーな動きを抑え、常にベストな泳ぎをキープ。 ブレーデッドジグの重要なパーツラバースカートをより機能させる秘密 バルキーなボディの効果でスカートがしぼみ過ぎずに広がり、そのうえ深いリブがスカートのボディへの貼り付きを抑制。 スカートを、確実に、生き生きと振動させる……これも専用トレーラーならではの機能。 ▶ マテリアル ＆ フォーミュラ 「圧倒的な飛び」と「ハイピッチで波打つ動き」を両立する「高比重ながら柔らかめ」の独自調合マテリアルに、MoDOオリジナル・スペシャルフォーミュラを配合。 「飛距離」「アクション」「匂い」……ジャックハンマーを、さらに釣れるルアーに進化させるためのこだわりは、素材設定にも。 ※FECO エコタックル認定 JB・NBCのトーナメントでご使用いいただけます。 ・ジャックハンマー（オリジナル） ・ジャックハンマーTG ・ジャックハンマーSB ・ジャックハンマー ベイビージャック</v>
+      </c>
+      <c r="O530" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/BullPointShad.html</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>EL1077</v>
+      </c>
+      <c r="B531">
+        <v>15</v>
+      </c>
+      <c r="C531" t="str">
+        <v>スピンクラフト</v>
+      </c>
+      <c r="D531" t="str">
+        <v/>
+      </c>
+      <c r="E531" t="str">
+        <v/>
+      </c>
+      <c r="F531" t="str">
+        <v/>
+      </c>
+      <c r="G531" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H531" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I531" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J531" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K531" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/スピンクラフト.jpg</v>
+      </c>
+      <c r="L531" t="str">
+        <v/>
+      </c>
+      <c r="M531" t="str">
+        <v/>
+      </c>
+      <c r="N531" t="str">
+        <v>キレキレの超ハイピッチアクション。 小さいだけじゃない、本当の意味でのマイクロクランク。 「自然界で生きていくために、小さい生物は動きが素早いことが多い。だから、小さいルアーで瞬発力のある素早い動きを出せば、捕食する側のバスの潜在意識に訴えかけることができる」この福島健の言葉が意味するところはすなわち、「小さくて素早い動きを出せるルアー」＝「釣れるルアー」ということ。 小型ミノーやシャッド、コンパクトスピナーベイト、あるいはフットボールジグがその代表と言えますが、なかでも「とにかく釣れるし、ライトリグやスモラバ以上の釣果を叩き出すことも多い」とシークレットベイトとして密かに使われているルアーがあります。それがスピニングタックルで扱うほどの超小型クランクベイト、いわゆるマイクロクランクというジャンルのルアー達。 しかし、ルアー設計上の制約から、ボディを小型化すればするほど精度を出しにくくバランスが狂いやすくなってしまうという事実があります。つまり、ただ小型化しただけのクランクベイトは、クイックでキレのあるアクションを出すことが難しくなってしまうため、釣れるには釣れるがその威力が半減している可能性があるのです。 そこで、マイクロサイズであることを本当の意味で活かすために、設計やアクションにも徹底的にこだわり、福島のマイクロサイズ・コンセプトを具現化。 ▶ キレキレの超ハイピッチアクションを生み出す軽量・薄型0.8ｍｍ基盤リップ。 ▶ スロー～ハイスピードリトリーブまで幅広く対応する低重心固定ワンウエイト構造。 ▶ マイクロサイズながらしっかり水を押す扁平ヘッド＆ファットボディ形状。 ただ小さいだけのクランクベイトではなく、アクションが弱く緩慢になりがちというマイクロルアーの泣き所をクリアした本当の意味でのマイクロクランク、スピンクラフト。 ■ シャッドよりも小粒ながら、ハイインパクトなアクション＆心地良い振動。 ■ 巻き初めた瞬間からキレのある俊敏な動きが生み出されるハイレスポンスさ。 ■ ライトリグやスモールラバージグと比べて多くのポイントを短時間で探れる勝負の早さ。 等々を武器に、フィッシングプレッシャーを物ともせずあらゆるサイズのバスをバイトさせてしまう能力でハイプレッシャーなトーナメントであと1本を絞り出す、あるいは、プライベートフィッシングでイージーに数釣りを楽しむ……ライトリグやスモラバを投げるULスピニングタックルそのままで手軽に使用できるのもその魅力。 ただ小さいだけでなく、小さいことを最大限活かす設計で釣ることに特化した、本当の意味でのマイクロクランク、スピンクラフト。「とにかく魚を触りたい」という状況で最も頼りになるルアーの1つだと言えるでしょう。 霞ヶ浦水系のオカッパリを中心としたフィールドテストですでに多数の実績を上げています。</v>
+      </c>
+      <c r="O531" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/SpinCraft.html</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>EL1078</v>
+      </c>
+      <c r="B532">
+        <v>15</v>
+      </c>
+      <c r="C532" t="str">
+        <v>クラフト</v>
+      </c>
+      <c r="D532" t="str">
+        <v/>
+      </c>
+      <c r="E532" t="str">
+        <v/>
+      </c>
+      <c r="F532" t="str">
+        <v/>
+      </c>
+      <c r="G532" t="str">
+        <v>crank</v>
+      </c>
+      <c r="H532" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I532" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J532" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K532" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/クラフト.jpg</v>
+      </c>
+      <c r="L532" t="str">
+        <v/>
+      </c>
+      <c r="M532" t="str">
+        <v/>
+      </c>
+      <c r="N532" t="str">
+        <v>そのためクラフトには軽量・薄型の基盤リップを搭載し、さらにはヘッドをフラットに設計。巻き始めた瞬間から素早く水をつかみ、超ハイピッチロールのキビキビとしたキレのあるアクションを生み出します。また、フラットな背面により形成されるボディ側面とのエッジによるメリハリのある明滅が、そのキレをより一層引き立てます。 さらに、テールにまで及ぶそのファットな形状の効果により、重心移動ウエイトがボディの最後部まで移動し、コンパクトなボディながらもベイトタックルでの十分な飛距離を約束。着水後は移動ウエイトをマグネットで固定することでリトリーブ速度にかかわらずアクションが安定。その優れたアクションレスポンスと相まってたとえ短い距離であっても、福島がタイニークランクに求めた釣れる動き、すなわち自然界に生息する小さな生物をイメージさせる瞬発的なキレのある動きを生み出します。 さらなるウエイト固定の効果として、ボトムやカバーヒット時のアクションも安定。加えて、基盤リップによる感知力とファットなボディによる浮力から得られる高い根掛かり回避性能、さらにはアクションレスポンスの良さを活かして、ボトムを速めに巻いてルアーを跳ねさせリアクションを狙う、あるいはボトムやカバーをスローに舐めるように引いて見せて喰わせる……等、様々なボトム＆カバーコンタクトテクニックにも対応します。 それも福島が徹底的にこだわったサイズ＆アクションがあればこそ。ただコンパクトだから釣れるのではなく、このボディサイズにしてこの動きだからこそ釣れる。釣れるタイニークランクベイト、FACTクラフトが日本中のタフなバス達を狂わせることになるでしょう。</v>
+      </c>
+      <c r="O532" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Craft.html</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>EL1079</v>
+      </c>
+      <c r="B533">
+        <v>15</v>
+      </c>
+      <c r="C533" t="str">
+        <v>グランサーチャー55</v>
+      </c>
+      <c r="D533" t="str">
+        <v/>
+      </c>
+      <c r="E533" t="str">
+        <v/>
+      </c>
+      <c r="F533" t="str">
+        <v/>
+      </c>
+      <c r="G533" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H533" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I533" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J533" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K533" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/グランサーチャー55.jpg</v>
+      </c>
+      <c r="L533" t="str">
+        <v/>
+      </c>
+      <c r="M533" t="str">
+        <v/>
+      </c>
+      <c r="N533" t="str">
+        <v>・強風下、逆風下で遠投が必要とされる状況で ・ライトラインを使用して少しでも深く潜らせたい時に ・ラインスラックを利用したテロテロ・スローリトリーブに ▶ グランサーチャー55 アクションムービー ▶グランサーチャー55 ・サイズ:55mm／5.2g ・潜行レンジ:1.2～1.4m ▶グランサーチャー (オリジナル) ・サイズ:65mm／8.0g ・潜行レンジ:1.8～2.2m</v>
+      </c>
+      <c r="O533" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/GranSearcher55.html</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>EL1080</v>
+      </c>
+      <c r="B534">
+        <v>15</v>
+      </c>
+      <c r="C534" t="str">
+        <v>グランサーチャー</v>
+      </c>
+      <c r="D534" t="str">
+        <v/>
+      </c>
+      <c r="E534" t="str">
+        <v/>
+      </c>
+      <c r="F534" t="str">
+        <v/>
+      </c>
+      <c r="G534" t="str">
+        <v>minnow</v>
+      </c>
+      <c r="H534" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I534" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J534" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K534" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/グランサーチャー.jpg</v>
+      </c>
+      <c r="L534" t="str">
+        <v/>
+      </c>
+      <c r="M534" t="str">
+        <v/>
+      </c>
+      <c r="N534" t="str">
+        <v>冬だけのシャッドじゃない。超スローから超高速巻きまで。 サーチと喰わせの同時進行を実現したクランキングシャッド。 プレッシャーを掛けることなく程良くアピールできる小さすぎず大きすぎずの絶妙なサイズ感。ベイトタックルでカッ飛ぶ圧巻の飛距離。劇的な明滅＆残像効果を生み出す超ハイピッチかつ激タイトなローリングアクション。クランクベイトとは違うナチュラルなシェイプ＆アクションで、クランクベイトには反応しない魚を巻いて獲るための福島健こだわりのクランキングシャッド、それがグランサーチャー。 きめ細やかな波動とベイトフィッシュライクなシルエットによる「シャッドならではのスローに見せて喰わせる能力」に「シャッドのレベルを超えた圧巻の飛距離」をプラスすることで、スレバスや低活性バスにより遠くからアプローチできるため、その喰わせ力が倍増。 さらに、超ファストリトリーブにも対応する超安定性も兼ね備え、スローな喰わせのみならず、高速巻き×ビリビリ系の超振動とナチュラルなシェイプでバスに考える間や違和感を与えず口を使わせることもできます。 その遠投性能＆高速安定性、さらには、6.5cmというシャッドとしてはやや大きめのサイズから、風が吹き抜ける広大なフィールドでの広域高速サーチにも威力を発揮。しかも、ただ広く速く探るだけでなく、釣れるアクション＆シェイプで広く速く探るという「サーチと喰わせの同時進行」を実現。 大場所からピンスポットまで、超スローから超高速巻きまで、サーチにも喰わせにも。誰よりも早く答えにたどり着くために、一流のトーナメントアングラーが求める「魚を探す能力」と「喰わせの能力」を具現化したグランサーチャーは、冬だけでなくオールシーズン対応型のクランキングシャッドです。 ▶グランサーチャー55 ・サイズ:55mm／5.2g ・潜行レンジ:1.2～1.4m ▶グランサーチャー (オリジナル) ・サイズ:65mm／8.0g ・潜行レンジ:1.8～2.2m</v>
+      </c>
+      <c r="O534" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/GranSearcher.html</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>EL1081</v>
+      </c>
+      <c r="B535">
+        <v>15</v>
+      </c>
+      <c r="C535" t="str">
+        <v>ギズモ</v>
+      </c>
+      <c r="D535" t="str">
+        <v/>
+      </c>
+      <c r="E535" t="str">
+        <v/>
+      </c>
+      <c r="F535" t="str">
+        <v/>
+      </c>
+      <c r="G535" t="str">
+        <v>topwater_walker</v>
+      </c>
+      <c r="H535" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I535" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J535" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K535" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ギズモ.jpg</v>
+      </c>
+      <c r="L535" t="str">
+        <v/>
+      </c>
+      <c r="M535" t="str">
+        <v/>
+      </c>
+      <c r="N535" t="str">
+        <v>コンセプトは浮くスモラバ。水面へと誘うリアルな生命感。 見た目のリアルさだけでなく、アクションも。水面に落ちた（落ちる）虫を福島健の目から見たイメージで徹底的にデフォルメしたギズモ。その根底にあるのが、釣れるバスルアーの代表格であるスモラバ（+トレーラー）と同様のラバー+ソフトボディの一体感。 スモールマウスの虫パターン、ラージマウスのちょうちん釣り等、セレクティブかつハイプレッシャーな魚を欺くステージとして水面、そして時には空中までも利用する。そんな、人間がコントロールできる領域を超えた世界への入口の扉を開けるキー、ギズモ。</v>
+      </c>
+      <c r="O535" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Gizmo.html</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>EL1082</v>
+      </c>
+      <c r="B536">
+        <v>15</v>
+      </c>
+      <c r="C536" t="str">
+        <v>ルーフェン</v>
+      </c>
+      <c r="D536" t="str">
+        <v/>
+      </c>
+      <c r="E536" t="str">
+        <v/>
+      </c>
+      <c r="F536" t="str">
+        <v/>
+      </c>
+      <c r="G536" t="str">
+        <v>topwater_walker</v>
+      </c>
+      <c r="H536" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I536" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J536" t="str">
+        <v>walk_pop</v>
+      </c>
+      <c r="K536" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ルーフェン.jpg</v>
+      </c>
+      <c r="L536" t="str">
+        <v/>
+      </c>
+      <c r="M536" t="str">
+        <v/>
+      </c>
+      <c r="N536" t="str">
+        <v>毛筆素材でしか成し得ない 極細微波動で喰わせる I字系プラグ。 まさに神業。毛筆テールフィンの神秘……ついに解禁。 ＜毛筆テールフィン搭載 I字系プラグ・ルーフェン＞ ▶開発コンセプト ・ハイプレッシャー攻略のためのI字系プラグ。 ボディはノーアクションで真っ直ぐ泳ぎながら、テールのみが超微振動する、見切られにくい動き。両立のカギは、コシがありながらも細くてしなやかな毛筆素材のテール。 ▶推奨メソッド ・表層を引き波を立てて一定スピードでただ巻き ・連続トゥイッチ、トゥイッチ＆ポーズ</v>
+      </c>
+      <c r="O536" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Rufen.html</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>EL1083</v>
+      </c>
+      <c r="B537">
+        <v>15</v>
+      </c>
+      <c r="C537" t="str">
+        <v>TGブロー</v>
+      </c>
+      <c r="D537" t="str">
+        <v/>
+      </c>
+      <c r="E537" t="str">
+        <v/>
+      </c>
+      <c r="F537" t="str">
+        <v/>
+      </c>
+      <c r="G537" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H537" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I537" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J537" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K537" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/tgブロー.jpg</v>
+      </c>
+      <c r="L537" t="str">
+        <v/>
+      </c>
+      <c r="M537" t="str">
+        <v/>
+      </c>
+      <c r="N537" t="str">
+        <v>高密度・焼結タングステンヘッドにしか成し得ない、驚異のリアクションバイト誘発力。 ▶ TGブローの特徴 ① 圧倒的なフォールスピード ジグヘッド部に、その製造において技術面・コスト面から難易度が高いとされる高密度・焼結タングステン（比重：約18）を採用し、鉛（比重：約11）や樹脂タングステン（比重：約11～14）と比べてコンパクト化。フットボールジグの最大の武器であるリアクションバイト誘発に必要な圧倒的なフォールスピードを生み出します。 「フォールスピードが速くボトムでの俊敏な動きに加え、バスの本能にスイッチを入れる『カチカチ』というサウンドを発生させることができる……」（福島健ブログより） ▶ EG Extreme Vol.36 福島健 NEWフットボールジグ TGブロー実釣解説</v>
+      </c>
+      <c r="O537" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/TgBlow.html</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>EL1084</v>
+      </c>
+      <c r="B538">
+        <v>15</v>
+      </c>
+      <c r="C538" t="str">
+        <v>C-4ジグ</v>
+      </c>
+      <c r="D538" t="str">
+        <v/>
+      </c>
+      <c r="E538" t="str">
+        <v/>
+      </c>
+      <c r="F538" t="str">
+        <v/>
+      </c>
+      <c r="G538" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H538" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I538" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J538" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K538" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/c_4ジグ.jpg</v>
+      </c>
+      <c r="L538" t="str">
+        <v/>
+      </c>
+      <c r="M538" t="str">
+        <v/>
+      </c>
+      <c r="N538" t="str">
+        <v>実は回収時はバイトチャンスにもなる。回収するスモラバをバスがチェイスしてくることがあって、その際、回転したり一瞬でもバランスを崩したりすると見切られやすくなってしまう。ピックアップ時の安定感はライントラブルを防ぐだけでなく、ピックアップバイトを取るためでもある。トーナメントで結果を出すためには回収時も無駄にできない。 刺さりと強さのバランスを考え、線径＆形状にこだわって一から設計したオリジナルフックを採用している。それに、ヘッド重量とそのウェイトで狙うカバーの濃さを計算し、障害物回避性能とフィネスタックルでのフッキング性能を両立する最適なガード本数を選択した。フッキングが良いだけでなく、（下の動画のような対ビッグフィッシュにおいても）バラシが極端に少ないのも隠れた特長で、トーナメントで信頼して使うことができる。 自身の経験とこだわりを凝縮した究極のフィネスラバージグ 超オールマイティーで場所、用途（テクニック）、魚種（ラージ、スモール）を選ばない。バスに飽きられることなく、これから先もずっと釣れ続くものをつくりたかった。一つひとつは徹底的にこだわり抜いたパーツの集合体だが、一部に特化したものではなく、トータルバランスに優れ、誰が使っても釣れる、そしてトーナメントでも勝てるスモラバに仕上がったと思う。</v>
+      </c>
+      <c r="O538" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/C4Jig.html</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>EL1085</v>
+      </c>
+      <c r="B539">
+        <v>15</v>
+      </c>
+      <c r="C539" t="str">
+        <v>スタビル</v>
+      </c>
+      <c r="D539" t="str">
+        <v/>
+      </c>
+      <c r="E539" t="str">
+        <v/>
+      </c>
+      <c r="F539" t="str">
+        <v/>
+      </c>
+      <c r="G539" t="str">
+        <v>finesse_jig</v>
+      </c>
+      <c r="H539" t="str">
+        <v>jig</v>
+      </c>
+      <c r="I539" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J539" t="str">
+        <v>crawl_creature</v>
+      </c>
+      <c r="K539" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/スタビル.jpg</v>
+      </c>
+      <c r="L539" t="str">
+        <v/>
+      </c>
+      <c r="M539" t="str">
+        <v/>
+      </c>
+      <c r="N539" t="str">
+        <v>リーダーレスダウンショット×ラバージグのハイブリッド種。 21世紀のカバー&amp;ボトム攻略スタンダードとなる新種リグが発生。 ▶開発コンセプト リーダーレスダウンショットとラバージグの長所を融合させることで、さらに釣れるルアーに仕上げる。 ▶スタビル基本特性 ・垂直にフォールさせやすい。 ・ボトムでワームの姿勢が安定する。 ・根掛かりしにくい。 ・浮き上がりにくい。 ・感度が良い。 ・すり抜けが良い。 ・適度なスタック感がある。 ・ワームがズレにくい。 ・ラバーのモザイク効果がある。 ・バスがどの方向からも吸込みやすい。 ・フッキングが良い。</v>
+      </c>
+      <c r="O539" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Stabil.html</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>EL1086</v>
+      </c>
+      <c r="B540">
+        <v>15</v>
+      </c>
+      <c r="C540" t="str">
+        <v>フラッターギズモ</v>
+      </c>
+      <c r="D540" t="str">
+        <v/>
+      </c>
+      <c r="E540" t="str">
+        <v/>
+      </c>
+      <c r="F540" t="str">
+        <v/>
+      </c>
+      <c r="G540" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H540" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I540" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J540" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K540" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/フラッターギズモ.jpg</v>
+      </c>
+      <c r="L540" t="str">
+        <v/>
+      </c>
+      <c r="M540" t="str">
+        <v/>
+      </c>
+      <c r="N540" t="str">
+        <v>▶ ウイングによるパタパタと水中を這いずりまわる動的アクション ▶ 最先端ライブソナーやサイトで、バスの目の前にルアーを送り込んで誘って喰わせる釣りに。ウイングの抵抗で1点アクションも得意。 ▶ バスの居場所が絞り込めていない時や視界が悪いウィードやカバーの中では、ウイングアクションで存在感をアピール。気づかせ寄せて喰わせる釣りにも対応。 多くの水生生物が潜むのは障害物周り。ゆえに障害物周りで使うと、より自然な状態に近づくため、バスに違和感を与えず、喰わせやすくなります。そのためのオフセットフック対応設計ボディ。しかも、フックの存在を隠してセットできるので、より一層自然に見せることが可能になります。</v>
+      </c>
+      <c r="O540" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/FlutterGizmo.html</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>EL1087</v>
+      </c>
+      <c r="B541">
+        <v>15</v>
+      </c>
+      <c r="C541" t="str">
+        <v>ラストエース</v>
+      </c>
+      <c r="D541" t="str">
+        <v/>
+      </c>
+      <c r="E541" t="str">
+        <v/>
+      </c>
+      <c r="F541" t="str">
+        <v/>
+      </c>
+      <c r="G541" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H541" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I541" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J541" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K541" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ラストエース.jpg</v>
+      </c>
+      <c r="L541" t="str">
+        <v/>
+      </c>
+      <c r="M541" t="str">
+        <v/>
+      </c>
+      <c r="N541" t="str">
+        <v>ルアー自体の力で喰わせる……アングラーの演出で襲わせる……クリアーウォーター、サイトフィッシング、ライブサイトのような高度なテクニックが要求される状況で発揮される恐ろしいまでの破壊力。 「普通の状況では大小問わず釣れてしまうので使わない」「本当に釣れない時にだけ使う切り札がこれ」と言い切る福島健の自信作。 ▶ 琵琶湖「マッチザベイト！ラストエースぅーーー！」 ▶ 琵琶湖で釣り勝つ！ラストエース75ノーシンカーリグとは！？</v>
+      </c>
+      <c r="O541" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/LastAce75.html</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>EL1088</v>
+      </c>
+      <c r="B542">
+        <v>15</v>
+      </c>
+      <c r="C542" t="str">
+        <v>ラストエースF(フローティング)</v>
+      </c>
+      <c r="D542" t="str">
+        <v/>
+      </c>
+      <c r="E542" t="str">
+        <v/>
+      </c>
+      <c r="F542" t="str">
+        <v/>
+      </c>
+      <c r="G542" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H542" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I542" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J542" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K542" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ラストエースf_フローティング.jpg</v>
+      </c>
+      <c r="L542" t="str">
+        <v/>
+      </c>
+      <c r="M542" t="str">
+        <v/>
+      </c>
+      <c r="N542" t="str">
+        <v>釣れないときの切り札「ラストエース」のフローティングタイプ。水面付近で見せるその弱々しさ、そしてバスが何の疑いもなく吸い込む様は、まさにベイトフィッシュそのもの。 ●水面で止めておくだけ、もしくはシェイク＆ポーズで瀕死のベイトフィッシュを完全再現。 ●表層をゆっくり引いてくるとフラフラと無防備に泳ぐベイトフィッシュに、高速ジャーク or トゥイッチでは水面に追いつめられ逃げ惑うベイトフィッシュへと変貌。 ●ワンジャークで音を発してダイブ～浮かせることで、今まさに捕食されかかったベイトフィッシュを演出。 ……等々、超リアルな存在感でバスの捕食本能を刺激するフローティングタイプ・シークレットベイト、ラストエースF（フローティング）。</v>
+      </c>
+      <c r="O542" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/LastAce80f.html</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>EL1089</v>
+      </c>
+      <c r="B543">
+        <v>15</v>
+      </c>
+      <c r="C543" t="str">
+        <v>ラストエース168</v>
+      </c>
+      <c r="D543" t="str">
+        <v/>
+      </c>
+      <c r="E543" t="str">
+        <v/>
+      </c>
+      <c r="F543" t="str">
+        <v/>
+      </c>
+      <c r="G543" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H543" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I543" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J543" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K543" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ラストエース168.jpg</v>
+      </c>
+      <c r="L543" t="str">
+        <v/>
+      </c>
+      <c r="M543" t="str">
+        <v/>
+      </c>
+      <c r="N543" t="str">
+        <v>❶ 上側はパイプ位置がわかりにくいため、下側から14lb以上のラインか細めの針金等でボディに穴をあけパイプを貫通させる。 ❷ パイプ上部にあけた穴からラインを通し、下部から抜いて付属のスプリットリングに結ぶ。 ❸ イラストの位置を参考に、トレブルフックの針先1本をボディに埋め込めばセット完了。 ※針先は鋭く大変危険ですので取り扱いには十分ご注意ください。 ▶ ラストエース168 福島流フックセット方法</v>
+      </c>
+      <c r="O543" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/LastAce168.html</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>EL1090</v>
+      </c>
+      <c r="B544">
+        <v>15</v>
+      </c>
+      <c r="C544" t="str">
+        <v>ラストエースS(シンキング)</v>
+      </c>
+      <c r="D544" t="str">
+        <v/>
+      </c>
+      <c r="E544" t="str">
+        <v/>
+      </c>
+      <c r="F544" t="str">
+        <v/>
+      </c>
+      <c r="G544" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H544" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I544" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J544" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K544" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ラストエースs_シンキング.jpg</v>
+      </c>
+      <c r="L544" t="str">
+        <v/>
+      </c>
+      <c r="M544" t="str">
+        <v/>
+      </c>
+      <c r="N544" t="str">
+        <v>ただのナチュラル系とは違う、超ナチュラルなハイアピール。 反り上がったテール（湾曲テール）の絶大な効果で、2つの異なる系統の動きが同時に発生。それが、ボディサイドのフラット面で水を強く押す「パワーロールアクション」と、尾ビレ（薄型フィン）をしなやかにくねらせ水を掻く「ナチュラルスイング」の組み合わせ。 超ナチュラルながらもハイアピールな動きで、気づかせ、寄せて、襲わせる……ただナチュラルなだけでは喰わせられない気難しいバスを獲るための切り札がコレ。 広大なウィードエリア、視界を遮るカバ一周り、風や濁り、あるいは魚の居場所が絞り切れない時のような、ナチュラルなルアーでは物足りない、アピール系ルアーを使いたい状況でありながらも、天候やフィッシングプレッシャーの影響により、強すぎるルアーが嫌われるタフコンディション下で真価を発揮します。</v>
+      </c>
+      <c r="O544" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/LastAce128s.html</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>EL1091</v>
+      </c>
+      <c r="B545">
+        <v>15</v>
+      </c>
+      <c r="C545" t="str">
+        <v>ラストエース140スイム</v>
+      </c>
+      <c r="D545" t="str">
+        <v/>
+      </c>
+      <c r="E545" t="str">
+        <v/>
+      </c>
+      <c r="F545" t="str">
+        <v/>
+      </c>
+      <c r="G545" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H545" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I545" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J545" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K545" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ラストエース140スイム.jpg</v>
+      </c>
+      <c r="L545" t="str">
+        <v/>
+      </c>
+      <c r="M545" t="str">
+        <v/>
+      </c>
+      <c r="N545" t="str">
+        <v>【リアルを追求した福島健のこだわり】 ●魚のヌメリ感、生命感を表現する超リアルカラー＆3Dフィン付リアル形状ボディ。 ●大げさで不自然なロールを抑制するためのスレンダーテーパー形状テール。 ●大げさなロールを抑制するスタビライザー機能と、フックの存在をカモフラージュする役割も持つ3Dリアルフィン。 ●不自然な存在でもあるヘッド部のラインアイを排除。</v>
+      </c>
+      <c r="O545" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/LastAce140Swim.html</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>EL1092</v>
+      </c>
+      <c r="B546">
+        <v>15</v>
+      </c>
+      <c r="C546" t="str">
+        <v>C-4リーチ</v>
+      </c>
+      <c r="D546" t="str">
+        <v/>
+      </c>
+      <c r="E546" t="str">
+        <v/>
+      </c>
+      <c r="F546" t="str">
+        <v/>
+      </c>
+      <c r="G546" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H546" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I546" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J546" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K546" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/c_4リーチ.jpg</v>
+      </c>
+      <c r="L546" t="str">
+        <v/>
+      </c>
+      <c r="M546" t="str">
+        <v/>
+      </c>
+      <c r="N546" t="str">
+        <v>艶めかしくうねるリーチテール。 +αパーツが醸し出す生き物的シェイプ。 フィールドに合わせ様々な水中生物に変身。 ■ 艶めかしくうねるリーチテールと細かい波動のパーツで生き物らしさを演出 ボディサイズに対して長くて幅が広いリーチテールは、精密成型による薄さがもたらすテロテロ感、プリプリ感と相まって、わずかな水流や極軽シェイクでも揺らめきバスにアピールします。さらに、一般的なリーチにはない＋αの付属パーツがリーチテールとは違う細かい波動を発生することで、より複雑な生き物感あふれる動きを生み出します。 ■ コンパクトさの中に秘めたアピール力と喰わせ力 3.1インチというコンパクトサイズならではの喰わせ力に、3.1インチとは思えないアピール力をミックス。全長の半分以上を占めるリーチテールの人工的なわざとらしさを排除した艶めかしくうねる動きで気づかせ、見た目の存在感を抑えたボリューム＆一般的なリーチ+αのパーツによる生き物的シェイプ、さらには生命感のあるカラーでバスにルアーを見切らせず喰わせます。 ■ あなたのフィールドに合わせ様々な水中生物に変身 例えば、ダウンショットリグのシェイキングでは岩に付く苔をついばむ小魚、ネコリグのリフト＆フォールでは水中を飛び跳ねそして漂うエビ、ジグヘッドリグのトゥイッチ＆ステイではボトムに隠れるゴリのように、様々な生き物をイメージした使い方が可能なC-4リーチ。リグやアクションを使い分けることで、あなたのフィールドに合わせたベイトフィッシュに変身させてください。 ▶ C-4リーチ3.1"アクションムービー</v>
+      </c>
+      <c r="O546" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/C4Leech.html</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>EL1093</v>
+      </c>
+      <c r="B547">
+        <v>15</v>
+      </c>
+      <c r="C547" t="str">
+        <v>スカルピン</v>
+      </c>
+      <c r="D547" t="str">
+        <v/>
+      </c>
+      <c r="E547" t="str">
+        <v/>
+      </c>
+      <c r="F547" t="str">
+        <v/>
+      </c>
+      <c r="G547" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H547" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I547" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J547" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K547" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/スカルピン.jpg</v>
+      </c>
+      <c r="L547" t="str">
+        <v/>
+      </c>
+      <c r="M547" t="str">
+        <v/>
+      </c>
+      <c r="N547" t="str">
+        <v>バスの大好物ゴリ。そのシルエットと動きを徹底デフォルメ。 「ゴリ（ハゼ）をイメージさせるのに重要なのはボトムで扱うこと。なので、ゴリワームでは上から見たシルエットに徹底してこだわった。ゴリの形をリアルにコピーしても、バスにゴリをイメージさせられるとは限らない。むしろゴリの特徴をしっかりデフォルメした方がバスにとってはリアルに感じる」と福島健は主張する。 背中を艶消し仕上げにしたのもボトムに同化する自然界の生物へのオマージュ。ボトムに置いてシルエットで見せて喰わせる。素速く動かしてリアクションバイトさせる。速く動かした時だけテールが動く設計。 フットボールジグトレーラーとしての実績大。勿論、C-4ジグトレーラー、ダウンショット、スプリットショット、ジグヘッド、ネコリグなどに対応。 ▶ 福島健 FACT スカルピン3.5解説 ▶ TGブロー水中アクション動画 ■動画中の使用トレーラー：スカルピン3.5インチ TGブロー1/4ozにはスカルピン2.6インチ、3/8oz&amp;1/2ozにはスカルピン3.5インチがベストマッチ。TGブローの俊敏な動きを活かしその性能を最大限引き出すベストなトレーラーです。</v>
+      </c>
+      <c r="O547" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Sculpin.html</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>EL1094</v>
+      </c>
+      <c r="B548">
+        <v>15</v>
+      </c>
+      <c r="C548" t="str">
+        <v>C-4シュリンプ</v>
+      </c>
+      <c r="D548" t="str">
+        <v/>
+      </c>
+      <c r="E548" t="str">
+        <v/>
+      </c>
+      <c r="F548" t="str">
+        <v/>
+      </c>
+      <c r="G548" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H548" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I548" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J548" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K548" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/c_4シュリンプ.jpg</v>
+      </c>
+      <c r="L548" t="str">
+        <v/>
+      </c>
+      <c r="M548" t="str">
+        <v/>
+      </c>
+      <c r="N548" t="str">
+        <v>シルエットだけでバスが喰う。ワールドチャンプ福島健の原動力。 まさにエサだと思ってバスが喰う。福島健デザインの「C-4シュリンプ」は、シルエットとナチュラルを極めた生命感溢れるスモールシュリンプです。 ダブルパドルから触手が出る独特のデザインは、福島のこだわり。理屈ではなく「バスが好むシルエット」と福島が断言するボディデザインと絶妙なボリュームは、動かさなくても置いておくだけでバイトを誘発。 スモラバトレーラー、キャロライナリグ、ドロップショットetc。激タフに勝ち抜く究極のスモールシュリンプ。その威力は福島自身のJBワールドチャンピオン獲得で証明済みです。</v>
+      </c>
+      <c r="O548" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/C4Shrimp.html</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>EL1095</v>
+      </c>
+      <c r="B549">
+        <v>15</v>
+      </c>
+      <c r="C549" t="str">
+        <v>フラップクロー</v>
+      </c>
+      <c r="D549" t="str">
+        <v/>
+      </c>
+      <c r="E549" t="str">
+        <v/>
+      </c>
+      <c r="F549" t="str">
+        <v/>
+      </c>
+      <c r="G549" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H549" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I549" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J549" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K549" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/フラップクロー.jpg</v>
+      </c>
+      <c r="L549" t="str">
+        <v/>
+      </c>
+      <c r="M549" t="str">
+        <v/>
+      </c>
+      <c r="N549" t="str">
+        <v>倒れ込みアクションで強烈な波動を発生。ボトムを這う甲殻類を完全再現。 巨大な爪の超実戦型クローワーム。 福島健がトーナメントで勝つために生み出した渾身のクローワーム、フラップクロー。最大のこだわりは、コンパクトなボディサイズながら、圧倒的な存在感のある大きくかつ分厚くデザインされた爪。そのボリューム感に加え、高密度ソルト配合マテリアルならではの重量を最大限に活かした、着底後に「ドスッ！」と爪～ボディが倒れ込むアクションで強烈な波動を生み出します。とりわけ、視界が遮られるカバーの中やマディな水質での効果は絶大。 その存在感が際立つ巨大な爪は、ボトムからの浮き上がりを制御するよう低重心に設計。さらに爪底面を広くデザインすることで、ボトムに対しての座りが良くなりボディが横倒しになりにくいという効果を発揮。ズル引きした時の、爪を下げた状態で横倒れせずにボトムを這う様は、まさに自然界の甲殻類そのもの。 さらに、ボディにも福島のこだわりを注入。ボディの背中にオフセットフックのフックポイントを埋め込む丘状の盛り上がりをつくることで、簡単かつ確実なウィードレスセッティングが可能に。そして、バイトに対してフックポイントが飛び出す方向にボディの肉等、邪魔するものが何もないため、高いフッキング率を実現。計算し尽くされたボディ形状により、ウィードレス性能とフッキング性能という相反する要素を両立しました。 その他、脚や触角の形状、果ては爪、背、腹の模様等、細部にまで渡る福島のこだわりで、自然界に存在する生き物感を徹底的にデフォルメ。 テキサスリグ、リーダーレスダウンショットリグとの相性が抜群で、特にザリガニの多いフィールドやマディウォーターでは壮絶な釣果を叩き出します。霞ヶ浦・利根川水系のトーナメントで、このフラップクローをリグしたロッド１本のみで戦い抜く……福島の絶大な信頼の証です。 ▶ フラップクロー4"実釣アクションムービー ▶ フラップクロー3.3インチ アクションムービー</v>
+      </c>
+      <c r="O549" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Flopclaw.html</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>EL1096</v>
+      </c>
+      <c r="B550">
+        <v>15</v>
+      </c>
+      <c r="C550" t="str">
+        <v>ゲジー</v>
+      </c>
+      <c r="D550" t="str">
+        <v/>
+      </c>
+      <c r="E550" t="str">
+        <v/>
+      </c>
+      <c r="F550" t="str">
+        <v/>
+      </c>
+      <c r="G550" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H550" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I550" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J550" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K550" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ゲジー.jpg</v>
+      </c>
+      <c r="L550" t="str">
+        <v/>
+      </c>
+      <c r="M550" t="str">
+        <v/>
+      </c>
+      <c r="N550" t="str">
+        <v>不気味なシルエット。うごめく関節肢。 身の毛もよだつリアリズムでバスを虜にする沈む虫、ゲジー。 ▶開発コンセプト ・ノーシンカーで飛距離が出せる。投げやすい。 ・フォールさせるだけでバスを誘える。 ・オフセットフックを使用できる（＝根掛かりにくくバラシにくい）。 ▶推奨フック ・オフセットフック：#1～1/0 ▶推奨メソッド ・フリーフォール ・シェイキング＆トゥイッチング＋ポーズ</v>
+      </c>
+      <c r="O550" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Gezzy.html</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>EL1097</v>
+      </c>
+      <c r="B551">
+        <v>15</v>
+      </c>
+      <c r="C551" t="str">
+        <v>ブザービーター</v>
+      </c>
+      <c r="D551" t="str">
+        <v/>
+      </c>
+      <c r="E551" t="str">
+        <v/>
+      </c>
+      <c r="F551" t="str">
+        <v/>
+      </c>
+      <c r="G551" t="str">
+        <v>vib</v>
+      </c>
+      <c r="H551" t="str">
+        <v>metal</v>
+      </c>
+      <c r="I551" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J551" t="str">
+        <v>vibration</v>
+      </c>
+      <c r="K551" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ブザービーター.jpg</v>
+      </c>
+      <c r="L551" t="str">
+        <v/>
+      </c>
+      <c r="M551" t="str">
+        <v/>
+      </c>
+      <c r="N551" t="str">
+        <v>最後の一投にすべてを賭ける。試合終了のブザーと同時にゴールゲットする最後の切り札。 「ブザービーター」。そのネーミングの由来は試合終了のブザーと同時にゴールゲットするファイナルシュート。最後の期待にこたえるという意味をもちます。その最大の特徴は誰もが簡単に、一定の釣り方で結果を出せる事。 「ブザービーター」は使い手の技量によってポテンシャルを発揮するテクニカルプラグとは対極の位置にあり、極めて広いエリアから誰もがクイックに、イージーに、ただストレートにリトリーブするだけで、バスを見つけ出せる究極のパイロットプラグです。 広大なシャローフラットや漠然としたウィードエリア、また、バスが何処にいるのか解りづらい…、そんな時こそ、「ブザービーター」を投げてみてください。そこから新たなるステージへの扉が開けてくるはずです。</v>
+      </c>
+      <c r="O551" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/BuzzerBeater.html</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>EL1098</v>
+      </c>
+      <c r="B552">
+        <v>15</v>
+      </c>
+      <c r="C552" t="str">
+        <v>M-1 インスパイアミノー</v>
+      </c>
+      <c r="D552" t="str">
+        <v/>
+      </c>
+      <c r="E552" t="str">
+        <v/>
+      </c>
+      <c r="F552" t="str">
+        <v/>
+      </c>
+      <c r="G552" t="str">
+        <v>spy_bait</v>
+      </c>
+      <c r="H552" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I552" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J552" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K552" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/m_1_インスパイアミノー.jpg</v>
+      </c>
+      <c r="L552" t="str">
+        <v/>
+      </c>
+      <c r="M552" t="str">
+        <v/>
+      </c>
+      <c r="N552" t="str">
+        <v>バイトトリガーとなるクイックなヒラ打ちとポーズの組み合わせにより、ワームに反応しない異次元のバスを攻略。特に春先の低水温時にはロングポーズ&amp;トゥイッチによるプリスポーン攻略に絶大な威力を発揮。初夏から秋にかけては連続的なトゥイッチが効果的です。 目安として春ならば2トゥイッチ、1ポーズ約5秒。秋ならば連続トゥイッチ or ジャークの後の2〜3秒のショートポーズが有効です。 水深3mまでのウィードやゴロタ石がらみのワイドシャロー及び野池などのあらゆるシャローエリアでM-1インスパイアミノーは活躍します。 ●イージーなロングキャストを可能にする「重心移動システム搭載モデル」と、キレのある大きなダートアクションを生み出す「Ｃ.Ｂ.Ｓ.搭載 重心固定モデル」の2タイプをラインナップ。</v>
+      </c>
+      <c r="O552" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/M1InspireMinnow.html</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>EL1099</v>
+      </c>
+      <c r="B553">
+        <v>15</v>
+      </c>
+      <c r="C553" t="str">
+        <v>スーパースレッジ</v>
+      </c>
+      <c r="D553" t="str">
+        <v/>
+      </c>
+      <c r="E553" t="str">
+        <v/>
+      </c>
+      <c r="F553" t="str">
+        <v/>
+      </c>
+      <c r="G553" t="str">
+        <v>suspending_minnow</v>
+      </c>
+      <c r="H553" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I553" t="str">
+        <v>Mid (0.5–2m)</v>
+      </c>
+      <c r="J553" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K553" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/スーパースレッジ.jpg</v>
+      </c>
+      <c r="L553" t="str">
+        <v/>
+      </c>
+      <c r="M553" t="str">
+        <v/>
+      </c>
+      <c r="N553" t="str">
+        <v>全てが専用設計された、スレッジ・ダウンサイジングモデル。 すべてが専用設計された「スーパースレッジ」。今江克隆をして「究極のジャークベイト」と言わしめたダウンサイジングトーナメントモデルです。 スーパースレッジは空力抵抗を極限まで抑えた設計により安定した遠投性能を確保。インサートフラッシュプレートとC.B.S.を装備することによって、強烈なイレギュラーダートと、ロッドワークによって最大同方向へ3回跳ばすことのできる通称「三段跳び」を実現しました。 「過去、これ以上のジャークベイトは存在しえなかった」と今江克隆が言い切ったほどのトーナメントウエポン。</v>
+      </c>
+      <c r="O553" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/SuperSledge.html</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>EL1100</v>
+      </c>
+      <c r="B554">
+        <v>15</v>
+      </c>
+      <c r="C554" t="str">
+        <v>ウルトラスレッジ</v>
+      </c>
+      <c r="D554" t="str">
+        <v/>
+      </c>
+      <c r="E554" t="str">
+        <v/>
+      </c>
+      <c r="F554" t="str">
+        <v/>
+      </c>
+      <c r="G554" t="str">
+        <v>suspending_minnow</v>
+      </c>
+      <c r="H554" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I554" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J554" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K554" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ウルトラスレッジ.jpg</v>
+      </c>
+      <c r="L554" t="str">
+        <v/>
+      </c>
+      <c r="M554" t="str">
+        <v/>
+      </c>
+      <c r="N554" t="str">
+        <v>C.B.S.搭載モデルに加え、クラス最高レベルの飛距離を誇る、重心移動システム搭載モデルもラインナップ。そして新たに「ウルトラスレッジ」には、どのような姿勢からも安定したスライドダートを生み出す「スクエア・フラットアイ」を採用しました。 これによって、アクションスタート時の力の支点がアイのスクエアエッジに集中。ルアーの水中姿勢に関わらず、ディープレンジでも予測不能の大きなスライドダートを誰でも簡単に出来るようになりました。 また、ドラッギングでは4～5mラインを攻めることも可能になり、深い水深でも軽いジャークで大きなスライドダートを発生。色調変化を伴う大きなスライドダート、「ウルトラスレッジ」は春のシャローを、そして秋のディープを席巻します。</v>
+      </c>
+      <c r="O554" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/SledgeDownsizingModelUltraSledge.html</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>EL1101</v>
+      </c>
+      <c r="B555">
+        <v>15</v>
+      </c>
+      <c r="C555" t="str">
+        <v>スピンムーブシャッド</v>
+      </c>
+      <c r="D555" t="str">
+        <v/>
+      </c>
+      <c r="E555" t="str">
+        <v/>
+      </c>
+      <c r="F555" t="str">
+        <v/>
+      </c>
+      <c r="G555" t="str">
+        <v>suspending_minnow</v>
+      </c>
+      <c r="H555" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I555" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J555" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K555" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/スピンムーブシャッド.jpg</v>
+      </c>
+      <c r="L555" t="str">
+        <v/>
+      </c>
+      <c r="M555" t="str">
+        <v/>
+      </c>
+      <c r="N555" t="str">
+        <v>ハードビートスモールシャッド。 スレたバスの「リアクション」を誘う。 小粒ながら激しいスピンムーブと、きびきびとしたバイブレーションでスモールシャッドの宿命であるアピール力の低さ、パンチ力の無さを克服しています。この小粒ながら激しい「動」の状態から、一転、姿をくらますかのような「静」（サスペンド）への急転換に、スレ切ったバスや、ルアーへの反応の鈍いバスが反応することを狙った、新しい考えのサスペンドスモールシャッドです。 初心者でも分かり易い使用感と、トゥイッチの苦手な方でも、ただ真っ直ぐに引いてきてピタッと止めるだけで十分な性能を発揮してくれます。キャスト性能も初心者でも遠投の効くアーチ型フルレングス重心移動システムを採用しています。 また、スモールマウスに対する実績の高さは桧原湖のトーナメントでも実証済みでクリアウォーターの超ハイスピードリトリーブ、カバー寸止めはトッププロのシークレットトリックです。トップトーナメンターからサンデーアングラーまで、確実な釣果を約束してくれる。それがスピンムーブの真価なのです。</v>
+      </c>
+      <c r="O555" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/SpinMoveShad.html</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>EL1102</v>
+      </c>
+      <c r="B556">
+        <v>15</v>
+      </c>
+      <c r="C556" t="str">
+        <v>C.C.プレデター</v>
+      </c>
+      <c r="D556" t="str">
+        <v/>
+      </c>
+      <c r="E556" t="str">
+        <v/>
+      </c>
+      <c r="F556" t="str">
+        <v/>
+      </c>
+      <c r="G556" t="str">
+        <v>suspending_minnow</v>
+      </c>
+      <c r="H556" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I556" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J556" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K556" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/c_c_プレデター.jpg</v>
+      </c>
+      <c r="L556" t="str">
+        <v/>
+      </c>
+      <c r="M556" t="str">
+        <v/>
+      </c>
+      <c r="N556" t="str">
+        <v>ロングリップによる徹底したカバー回避性能を発揮する急速潜行シャッド。 バスに静かに近づき、カバーを舐めるように誘い最後に口を使わせる、プラグの概念をうち破るワーミングシャッド、C.C.プレデター。垂直に近い角度で潜行する水中での姿勢と、ボディの半分近くにも達するロングリップによる徹底したカバー回避性能、これによってボトムやカバーに密着して舐めつくすことができます。 アクションはバスの食性に訴えかける必要最小限に抑えられたタイトウィグリングで、低水温などでワームにすら食い込みが甘くなってしまったフッキング不可能なバスに口を使わせる最終兵器となります。 アーチ型フルレングス重心移動システムにより、驚異的な遠投能力を発揮し、その能力は逆風下でも衰えることはありません。バスとのディスタンスをとることができる遠投性能の確保だけでなく、移動ウエイト偏方向ロックシステムを採用することで、よりダイナミックなアクションをイージーに演出。 それと同時にアクション後や障害物回避後の姿勢の乱れを徹底的に制御することが可能。遠距離から攻める静かなる肉食獣、ハードベイト・ソフトベイトというジャンルを超越したところに存在する第3のルアー、それがC.C.プレデターなのです。</v>
+      </c>
+      <c r="O556" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Ccpredatore.html</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>EL1103</v>
+      </c>
+      <c r="B557">
+        <v>15</v>
+      </c>
+      <c r="C557" t="str">
+        <v>キッカーイーター</v>
+      </c>
+      <c r="D557" t="str">
+        <v/>
+      </c>
+      <c r="E557" t="str">
+        <v/>
+      </c>
+      <c r="F557" t="str">
+        <v/>
+      </c>
+      <c r="G557" t="str">
+        <v>suspending_minnow</v>
+      </c>
+      <c r="H557" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I557" t="str">
+        <v>Deep (2m+)</v>
+      </c>
+      <c r="J557" t="str">
+        <v>jerk_dart</v>
+      </c>
+      <c r="K557" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/キッカーイーター.jpg</v>
+      </c>
+      <c r="L557" t="str">
+        <v/>
+      </c>
+      <c r="M557" t="str">
+        <v/>
+      </c>
+      <c r="N557" t="str">
+        <v>インスパイアルアーズきってのビッグフィッシュゲッター「キッカーイーター」。水中でドリルのように細かく、それでいてパワフルにややファットなボディをくねらすドリルロールアクションは他の同クラスのルアーには見当たりません。 また、精密タングステンを2個内蔵したことにより逆風での遠距離アプローチを維持し、同時に安定した潜行能力を備えています。 秋〜冬にかけての低水温期の老獪なビッグフィッシュ、ポストスポーン期の大型バス、また、初夏〜秋にかけてのクランキングでの実績も、もはや言うまでもなく、オールシーズン対応のミノータイプクランクベイトとしての不動の地位を確立しました。 また、ポンプリトリーブを始め、ジャーキング、ストレートリトリーブまで多様な対応能力。優れた障害物回避能力を生かしカバーにヒットさせポーズを取ること、あるいは強いジャークを入れることによって発生するトリッキーな動きはビッグフィッシュに極めて高い効果があります。</v>
+      </c>
+      <c r="O557" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/KickerEater.html</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>EL1104</v>
+      </c>
+      <c r="B558">
+        <v>15</v>
+      </c>
+      <c r="C558" t="str">
+        <v>アイマッチョ</v>
+      </c>
+      <c r="D558" t="str">
+        <v/>
+      </c>
+      <c r="E558" t="str">
+        <v/>
+      </c>
+      <c r="F558" t="str">
+        <v/>
+      </c>
+      <c r="G558" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H558" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I558" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J558" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K558" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/アイマッチョ.jpg</v>
+      </c>
+      <c r="L558" t="str">
+        <v/>
+      </c>
+      <c r="M558" t="str">
+        <v/>
+      </c>
+      <c r="N558" t="str">
+        <v>スイミング時の浮き上がりを抑える水平姿勢を達成し、フラフラと揺れない高度な直進性能を発揮させるための唯一無二の各部位の組み合わせは、まさにI字系ソフトベイトの最終解。 マッチョ独自の鍛え上げられた筋肉のように盛り上がったリブを、水流によって水平姿勢を自然に維持できる45度に傾斜。安定した直進スイミングのための要、テールには垂直尾翼と水平尾翼を天地逆向きに一体化させローリングを抑え込む逆垂直尾翼型に。 さらに、胸ビレに相当する部分には、スイムベイトで長年研究をしつくした「ステルス型水平胸ビレ」を反り上がる形状で配置しスタビライザー機能を追加。ボディリブ、テールとの相乗効果によってさらなる浮き上がり抑止効果＆直進安定性能発揮に貢献します。 このように水平姿勢直進性能を極めたアイマッチョ2.8は、無警戒なベイトフィッシュを演じるノーシンカーI字引きのみならず、フィネス系鉄板のダウンショットリグ、ネコリグ、ジグヘッドリグ、さらには最新釣法の巻きキャロやハンガーテクニックに、水面からボトムまで、あらゆるライトリグへの高度な適応能力を発揮します。</v>
+      </c>
+      <c r="O558" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/IMacho.html</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>EL1105</v>
+      </c>
+      <c r="B559">
+        <v>15</v>
+      </c>
+      <c r="C559" t="str">
+        <v>フラットヘッドミノーレジェンドマッチョ</v>
+      </c>
+      <c r="D559" t="str">
+        <v/>
+      </c>
+      <c r="E559" t="str">
+        <v/>
+      </c>
+      <c r="F559" t="str">
+        <v/>
+      </c>
+      <c r="G559" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H559" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I559" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J559" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K559" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/フラットヘッドミノーレジェンドマッチョ.jpg</v>
+      </c>
+      <c r="L559" t="str">
+        <v/>
+      </c>
+      <c r="M559" t="str">
+        <v/>
+      </c>
+      <c r="N559" t="str">
+        <v>▶ フラットヘッドミノーレジェンドマッチョ 水中アクション動画 ・00:12〜 ダウンショットリグ ・00:46〜 ネコリグ ・01:44〜 ジグヘッドリグ フラットヘッドミノーレジェンドマッチョのおすすめの使用法を解説。 ・推奨リグ・メソッド→ ・アイマッチョ ・フラットヘッドミノーレジェンドマッチョ</v>
+      </c>
+      <c r="O559" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/FlatHeadMinnowLegendMacho.html</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>EL1106</v>
+      </c>
+      <c r="B560">
+        <v>15</v>
+      </c>
+      <c r="C560" t="str">
+        <v>ゾワゾワ</v>
+      </c>
+      <c r="D560" t="str">
+        <v/>
+      </c>
+      <c r="E560" t="str">
+        <v/>
+      </c>
+      <c r="F560" t="str">
+        <v/>
+      </c>
+      <c r="G560" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H560" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I560" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J560" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K560" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ゾワゾワ.jpg</v>
+      </c>
+      <c r="L560" t="str">
+        <v/>
+      </c>
+      <c r="M560" t="str">
+        <v/>
+      </c>
+      <c r="N560" t="str">
+        <v>▪3.5インチ あまりにもバイトが遠いので、どうしてもアカン時に使うとすぐ釣れる「アレ」を投入。最近の菊元的お助け、カバークリーパー5.8g &amp; ゾワゾワ3.5インチのライトジグストセッティング。使い出してすぐに……ホントに来た！かなりピンチな時間が続いたロケで、ゾワゾワ君が助けてくれました。 タックルデータ ［ロッド］オライオン OCSC-67ML+ ライトニングストライク ［ライン］バスザイル・マジックハードR 14lb ［ルアー］カバークリーパー 5.8g + ゾワゾワ 3.5インチ ▪4.5インチ 喰ってからグングン走るバイトを、大きなストロークでフルフッキング。バスの重みを感じた瞬間はたまりません。ゾワゾワ大（4.5インチ）は「なかなか着底しないな～と思ったら走ってました」的な、イニシャルフォールや着底直後に喰って走るバイトがとても多い印象。ルアーパワーがあります。 タックルデータ ［ロッド］オライオン OCSC-69H スターゲイザー ［ライン］バスザイル・マジックハードR 16lb ［ルアー］ゾワゾワ 4.5インチ 3/8ozフットボールリグ</v>
+      </c>
+      <c r="O560" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Zowazowa.html</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>EL1107</v>
+      </c>
+      <c r="B561">
+        <v>15</v>
+      </c>
+      <c r="C561" t="str">
+        <v>キッカーバグ</v>
+      </c>
+      <c r="D561" t="str">
+        <v/>
+      </c>
+      <c r="E561" t="str">
+        <v/>
+      </c>
+      <c r="F561" t="str">
+        <v/>
+      </c>
+      <c r="G561" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H561" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I561" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J561" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K561" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/キッカーバグ.jpg</v>
+      </c>
+      <c r="L561" t="str">
+        <v/>
+      </c>
+      <c r="M561" t="str">
+        <v/>
+      </c>
+      <c r="N561" t="str">
+        <v>デカバスキラーの異次元生命体「キッカーバグ」。 菊元俊文デザイン「キッカーバグ」は、摩訶不思議な各パーツが各々別の動きを演じるバルキークローです。先端がボール状のレッグは独特の微振動を生み、フラッピンシザースは大きく水を動かし、着底後の倒れ込みでバイトを誘発。そのシルエットと独特のアクションはデカバスの本能を刺激し、強く深いバイトを誘発します。 ジグトレーラーは勿論、テキサスリグ、ヘビーダウンショット、ヘビーキャロライナからノーシンカー、ネコリグまであらゆるリグでデカバスの実績を誇ります。デカバスキラーの異次元生命体「キッカーバグ」。 ▶キッカーバグ4インチ アクションムービー ■3.3インチ ファットベイビー （7本入）</v>
+      </c>
+      <c r="O561" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/KickerBug.html</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>EL1108</v>
+      </c>
+      <c r="B562">
+        <v>15</v>
+      </c>
+      <c r="C562" t="str">
+        <v>ボウワーム</v>
+      </c>
+      <c r="D562" t="str">
+        <v/>
+      </c>
+      <c r="E562" t="str">
+        <v/>
+      </c>
+      <c r="F562" t="str">
+        <v/>
+      </c>
+      <c r="G562" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H562" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I562" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J562" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K562" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ボウワーム.jpg</v>
+      </c>
+      <c r="L562" t="str">
+        <v/>
+      </c>
+      <c r="M562" t="str">
+        <v/>
+      </c>
+      <c r="N562" t="str">
+        <v>前後逆リブ構造が水を掴み動かすランカーキラーのストレート。 菊元俊文デザイン「ボウワーム」は、前後逆リブ構造が水を掴み動かすストレートワームです。ボウ（弓）のごとくしなり、着底後の倒れ込むアクションと微振動は、デカバスを魅了します。 ■4.2インチ 福島健のこだわりから生まれた、ハイプレッシャー・タフコンディション対応スリムボディ。 ・福島健インプレッションを見る→ ■5インチ ネイルシンカーホール搭載。ベイトフィネス、スピニングでの繊細な釣りに。 ■6インチ バルキーさを抑えたオールラウンダー。 ■7インチ リーダーレスドロップショットでのグラスエリア攻略で最高のポテンシャルを発揮。フォール時にボディを大きくくねらせてアピール。 ■8インチ バルキーなボディによる存在感＆ロングキャスト性能。 ■8インチ高浮力 素材が違う！高浮力マテリアルによるテキサスリグ・ラバージグトレーラーで驚異のボトムスタンドアップアクションを実現。 鰻リグにもベストマッチ。 ■12インチ 遠くからデカバスを寄せるボウワーム最強のアピール力。 ■12インチ高浮力 素材が違う！高浮力マテリアルによるテキサスリグ・ラバージグトレーラーで驚異のボトムスタンドアップアクションを実現。 鰻リグにもベストマッチ。</v>
+      </c>
+      <c r="O562" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/BowWorm.html</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>EL1109</v>
+      </c>
+      <c r="B563">
+        <v>15</v>
+      </c>
+      <c r="C563" t="str">
+        <v>ボウワームヌードル</v>
+      </c>
+      <c r="D563" t="str">
+        <v/>
+      </c>
+      <c r="E563" t="str">
+        <v/>
+      </c>
+      <c r="F563" t="str">
+        <v/>
+      </c>
+      <c r="G563" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H563" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I563" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J563" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K563" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ボウワームヌードル.jpg</v>
+      </c>
+      <c r="L563" t="str">
+        <v/>
+      </c>
+      <c r="M563" t="str">
+        <v/>
+      </c>
+      <c r="N563" t="str">
+        <v>ボウワームヌードル8インチ プロスタッフレビュー プロスタッフ6名がボウワームヌードル8インチの効果的な使い方やタックルを解説 詳細を見る→ 菊元俊文 紀ノ川 ボウワームヌードル。おると思ったところに入れたらやっぱり「おったなぁ！」木の枝越しに掛けましたが出て来てくれた。…… 動画投稿を見る→ 菊元俊文 解説 ▪ロングワーム講座 池原ダムBIGBITEロケのケーススタディです。ロケMVPは12インチボウワームヌードル。12インチヌードルで主に使ったのはスナッグレスネイルリグ。通称菊元リグです。…… 投稿全文を見る→ ▪ボウワームヌードル12"菊元リグの作り方 とにかく根掛かりしにくい。バイトが多い。フッキングが良いリグです。ロングワーム講座補足です。…… 投稿全文を見る→</v>
+      </c>
+      <c r="O563" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/BowWormNoodle.html</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>EL1110</v>
+      </c>
+      <c r="B564">
+        <v>15</v>
+      </c>
+      <c r="C564" t="str">
+        <v>ビビッドテール</v>
+      </c>
+      <c r="D564" t="str">
+        <v/>
+      </c>
+      <c r="E564" t="str">
+        <v/>
+      </c>
+      <c r="F564" t="str">
+        <v/>
+      </c>
+      <c r="G564" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H564" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I564" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J564" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K564" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ビビッドテール.jpg</v>
+      </c>
+      <c r="L564" t="str">
+        <v/>
+      </c>
+      <c r="M564" t="str">
+        <v/>
+      </c>
+      <c r="N564" t="str">
+        <v>一世を風靡した爆釣小型シャッドテールの王道。菊元俊文プロデュース。ビビッドテールがE.G.プロデザインワームで遂に復活。ソルト＆ガーリック、シュリンプのスペシャルフォーミュラ配合でさらにパワーアップしました。 数釣りは勿論、タフコンディションのビッグフィッシュにもバイトさせる実力充分のビビッドなアクション。ノーシンカー、ドロップショット、スプリット、キャロとあらゆるリグに対応。勿論、C.C.ラウンドやC-4ジグなどのトレーラーとしても極めて優秀な結果を生み出します。</v>
+      </c>
+      <c r="O564" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/VividTail.html</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>EL1111</v>
+      </c>
+      <c r="B565">
+        <v>15</v>
+      </c>
+      <c r="C565" t="str">
+        <v>ダブルモーション</v>
+      </c>
+      <c r="D565" t="str">
+        <v/>
+      </c>
+      <c r="E565" t="str">
+        <v/>
+      </c>
+      <c r="F565" t="str">
+        <v/>
+      </c>
+      <c r="G565" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H565" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I565" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J565" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K565" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ダブルモーション.jpg</v>
+      </c>
+      <c r="L565" t="str">
+        <v/>
+      </c>
+      <c r="M565" t="str">
+        <v/>
+      </c>
+      <c r="N565" t="str">
+        <v>霞の豪腕蛯原英夫プロデュース。浅く、濁った霞でのフリップ＆ピッチで落ちる距離と時間が短い中でいかにアピールさせ気付かせバイトさせるか？ バタバタと激しく水をかき回すハンドとダブルカーリーのアクションのどちらも最大限に活かした究極の落ちパク系クローが遂に完成しました。 テキサスリグやゼロダン（ジカリグ）での接近戦での威力は凄まじいものがあります。さらに濁ったシャローカバーでのジグトレーラーとして、あるいはディープのフットボールジグトレーラーとしてもテストでは抜群の結果を残しました。 ▶ 関連動画：ジャックハンマー・トレーラー別アクション動画 ■関連製品：ジャックハンマー</v>
+      </c>
+      <c r="O565" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/DoubleMotion.html</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>EL1112</v>
+      </c>
+      <c r="B566">
+        <v>15</v>
+      </c>
+      <c r="C566" t="str">
+        <v>クローモーション</v>
+      </c>
+      <c r="D566" t="str">
+        <v/>
+      </c>
+      <c r="E566" t="str">
+        <v/>
+      </c>
+      <c r="F566" t="str">
+        <v/>
+      </c>
+      <c r="G566" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H566" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I566" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J566" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K566" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/クローモーション.jpg</v>
+      </c>
+      <c r="L566" t="str">
+        <v/>
+      </c>
+      <c r="M566" t="str">
+        <v/>
+      </c>
+      <c r="N566" t="str">
+        <v>着底直後にバイトがなければ、ロッドアクションで誘いを入れる。すると静のフォールから一転、アームが付け根から横に開いて素早く閉じるというユニークな動きで、さらにその存在をアピール。 また、テキサスリグやリーダーレスダウンショットリグにセットすると、フォール時に爪をバタバタと動かすハイインパクトなベイトへと変貌する。 【対応リグ】 ▪ノーシンカーバックスライド ▪テキサスリグ ▪リーダーレスダウンショットリグ ▪フリーリグ ▪キャロライナリグ ▪ラバージグトレーラー ▪ブレーデッドジグトレーラー ▶ コンパクトバルキー＆超高比重クローワーム「クローモーション」 カバー撃ちの名手として知られる蛯原英夫の豊富な経験を凝縮した究極のカバー攻略ツール、それがクローモーション。 ■蛯原英夫タックルセッティング ［ロッド］オライオン OCSC-69MH ムーンゲイザー ［ライン］バスザイル・マジックハードR 14lb ［フック］デコイ・キロフック3/0</v>
+      </c>
+      <c r="O566" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/ClawMotion.html</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>EL1113</v>
+      </c>
+      <c r="B567">
+        <v>15</v>
+      </c>
+      <c r="C567" t="str">
+        <v>ヘッドシェイカー</v>
+      </c>
+      <c r="D567" t="str">
+        <v/>
+      </c>
+      <c r="E567" t="str">
+        <v/>
+      </c>
+      <c r="F567" t="str">
+        <v/>
+      </c>
+      <c r="G567" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H567" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I567" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J567" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K567" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ヘッドシェイカー.jpg</v>
+      </c>
+      <c r="L567" t="str">
+        <v/>
+      </c>
+      <c r="M567" t="str">
+        <v/>
+      </c>
+      <c r="N567" t="str">
+        <v>大西健太プロデュースのヘッドシェイカーは強烈な集魚力のみならずバイト誘発力が極めて高いシャッドテールワームです。その名の通り、頭を小刻みに振りながらボディ全体がくねるような独特な動きは、大西の強いこだわり。テールのみならずボディ側面での水押しによるアピール力とベイトフィッシュの泳ぎをイメージさせるリアルさで、バスを誘い出しバイトに持ち込みます。 そして、ノーシンカーでの超スローリトリーブでもしっかりアクション、速巻きでも安定したスイミング姿勢を保ちます。あらゆるリトリーブスピードに幅広く対応するその能力により、ウエイテッドフックリグやスイミングジグトレーラーでは自由自在なレンジコントロールを可能にしてくれます。特にグラスリッパーとのコンビネーションはベストマッチ。お互いのルアーの特性を活かした釣れる艶かしいスイミングアクションを生み出します。 フィールドテストでのデカバス実績は枚挙にいとまがありません。デカバスがあさっての方向からすっ飛んで来て喰うバイトが何度あったかわからない程の破壊力を見せつけてくれました。ヘッドシェイカー。明らかにデカバスを狂わせる波動。強烈なストライクが貴方を待っています。 ▶ ヘッドシェイカー5" ノーシンカーリグ 水中アクション</v>
+      </c>
+      <c r="O567" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/HeadShaker.html</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>EL1114</v>
+      </c>
+      <c r="B568">
+        <v>15</v>
+      </c>
+      <c r="C568" t="str">
+        <v>ツインテールリンガー</v>
+      </c>
+      <c r="D568" t="str">
+        <v/>
+      </c>
+      <c r="E568" t="str">
+        <v/>
+      </c>
+      <c r="F568" t="str">
+        <v/>
+      </c>
+      <c r="G568" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H568" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I568" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J568" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K568" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ツインテールリンガー.jpg</v>
+      </c>
+      <c r="L568" t="str">
+        <v/>
+      </c>
+      <c r="M568" t="str">
+        <v/>
+      </c>
+      <c r="N568" t="str">
+        <v>ツインテールリンガーはボディ部のリングデザインのみならず、細身のテール部にもマイクロリングデザインを施したツインテール・リングワームです。 ネコリグ、ドロップショットリグ、テキサスリグ、キャロライナリグ、スプリットショットリグ、ノーシンカーリグからラバージグトレーラーとして、あらゆるリグに幅広く対応。適度に張りのある高比重ソルトボディとリングリブで水を掴んで動かします。さらに、水を掴みやすい形状のリングテールは、左右別々に微振動することでバスの本能を確実に刺激します。その姿はバスからは喰いやすい手長エビや、時には襲うべき逃げ惑うベイトフィッシュに見えているに違いありません。 また、シュリンプ、イカ、ベイトフィッシュのスペシャルフォーミュラを配合。視覚だけでなく嗅覚も刺激することで、さらなるバイトを誘発するだけでなく、バスが口に入れたときに生物的感触を持つリング形状と相まって、バスが離しにくくミスバイトを減少させる効果も高めました。 張りのあるボディ＆複雑な微振動を生み出すツインテールはスピナーベイトやブレーデッドジグのトレーラーとしても最適。ハードな使用に対応しながらも、複雑にうねるようなアクションでバスを魅了します。 ▶ ツインテールリンガーアクションムービー この動画では以下のリグの水中アクションがご覧いただけます。 ① ノーシンカーリグ（0:04〜） ② ドロップショットリグ（0:35〜） ③ ネコリグ（0:54〜） ④ ジグヘッドワッキーリグ（1:13〜） ⑤ C-4ジグトレーラー（1:29〜） ⑥ ジャックハンマートレーラー（1:56〜） ▶ 関連動画：ジャックハンマー 詳細特徴動画 ▶ 関連動画：ジャックハンマー・トレーラー別アクション動画 ▶ 関連動画：ツインテールリンガー3.8インチ アクションムービー</v>
+      </c>
+      <c r="O568" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/TwintailRinger.html</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>EL1115</v>
+      </c>
+      <c r="B569">
+        <v>15</v>
+      </c>
+      <c r="C569" t="str">
+        <v>アントライオン</v>
+      </c>
+      <c r="D569" t="str">
+        <v/>
+      </c>
+      <c r="E569" t="str">
+        <v/>
+      </c>
+      <c r="F569" t="str">
+        <v/>
+      </c>
+      <c r="G569" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H569" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I569" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J569" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K569" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/アントライオン.jpg</v>
+      </c>
+      <c r="L569" t="str">
+        <v/>
+      </c>
+      <c r="M569" t="str">
+        <v/>
+      </c>
+      <c r="N569" t="str">
+        <v>エビ喰い、ハゼ喰い、さらにはワカサギ喰いにも口を使わせる。 バスの本能を刺激するアリジゴクの誘惑。 菊元俊文プロデュース、アントライオン。ジグ番長・菊元俊文がラバージグのトレーラーとしてつくりあげたカタチはただコンパクトなだけでなく、バスの本能を刺激するギミックを備える本格派。 後方（ツメ側）重心設計から来るコンパクトベイトとしては破格の投げやすさ、そして抜群の飛距離。頭部から突き出たウサギの耳状のツメとボディ上部から出たツメといった別形状の2種類のツメが生み出す複雑な水流。さらには着底後のポーズで、それぞれのツメがタイムラグのある倒れ込みアクション等々……バスをバイトさせる数々の仕掛けを詰め込みました。なかでもコンパクトジグと組み合わせてボトムジャークすると、左右へのドッグウォークアクションを実現。バスにその存在をアピールします。 もちろんトレーラーとしてではなく、ドロップショットリグやキャロライナリグ等での単体使用も効果的。ツメによるアピールに加え、ボディサイドの4本の触手と2本のヒゲが各々別に微振動しバスの本能を刺激。スレたラージマウスバスのみならず、タフコンディション下のスモールマウスバスにも効く切り札となります。また、これらの細かいパーツは、ラインヨレの原因となるリグの回転やボトムで根掛かる原因となる横倒し防止のバランサーとしての役割も併せ持ちます。 スピニングタックルでもベイトタックルでも使える汎用性を持ち、実戦テストでは、クリアーウォーター、マディーシャロー、カレントの中、シャロー、ディープ、ボトム、中層、対ラージマウス、対スモールマウス等様々なフィールドで実績を重ねてきました。落ちパク、ズル引き、ポーズ、ミドスト、さらには裏技の速巻き等あらゆるメソッドで。エビ喰いにもハゼ喰いにも。さらにはワカサギ喰いのバスにさえ口を使わせる威力がこのコンパクトなボディに秘められているのです。 ちなみにアントライオンと言うのはアリジゴクの意。アリジゴクに落ちたアリのように、ひとたびアントライオンの射程圏内に入ってしまったバスは、アントライオンに引き寄せられ逃れることができなくなるというのがネーミングの由来です。 【対応リグ】 ●ラバージグトレーラー ●ドロップショットリグ ●キャロライナリグ ●スプリットショットリグ ●ライトテキサスリグ etc… ▶ EG EXTREME Vol.35 菊元俊文 真冬の合川ダムでNEWワーム炸裂</v>
+      </c>
+      <c r="O569" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Antlion.html</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>EL1116</v>
+      </c>
+      <c r="B570">
+        <v>15</v>
+      </c>
+      <c r="C570" t="str">
+        <v>バスエネミー</v>
+      </c>
+      <c r="D570" t="str">
+        <v/>
+      </c>
+      <c r="E570" t="str">
+        <v/>
+      </c>
+      <c r="F570" t="str">
+        <v/>
+      </c>
+      <c r="G570" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H570" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I570" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J570" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K570" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/バスエネミー.jpg</v>
+      </c>
+      <c r="L570" t="str">
+        <v/>
+      </c>
+      <c r="M570" t="str">
+        <v/>
+      </c>
+      <c r="N570" t="str">
+        <v>【開発コンセプト】 高比重スティックベイトの喰わせ能力（揺れながら水平姿勢で垂直にフォール）を損なわずに、魚を惹きつけるアピール力（テールのはためき）を合わせ持つニュータイプ高比重スティックベイト。 【推奨リグ】 ▶ノーシンカー（テールの先端が上になるようフックをセット） マディウォーターや薄暗いカバーの中で威力を発揮 ハイプレッシャーなクリアウォーターレイクで威力を発揮 バスのスイッチを入れるだけでなく追いつかせる間を持つため低活性な魚に威力を発揮</v>
+      </c>
+      <c r="O570" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Bassenemy.html</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>EL1117</v>
+      </c>
+      <c r="B571">
+        <v>15</v>
+      </c>
+      <c r="C571" t="str">
+        <v>バスエネミースティック</v>
+      </c>
+      <c r="D571" t="str">
+        <v/>
+      </c>
+      <c r="E571" t="str">
+        <v/>
+      </c>
+      <c r="F571" t="str">
+        <v/>
+      </c>
+      <c r="G571" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H571" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I571" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J571" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K571" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/バスエネミースティック.jpg</v>
+      </c>
+      <c r="L571" t="str">
+        <v/>
+      </c>
+      <c r="M571" t="str">
+        <v/>
+      </c>
+      <c r="N571" t="str">
+        <v>バスエネミースティックの使用法を解説。 ・3インチ／4インチ 推奨リグ・メソッド ・5インチ 推奨リグ・メソッド ・琵琶湖プロガイドおすすめリグ ▶ バスエネミースティックアクションムービー ▶ バスエネミースティック琵琶湖爆釣セッティング実釣解説！これがムラッチ刺しだ！ ※「ムラッチ刺し」について詳しくはコチラをご覧ください。</v>
+      </c>
+      <c r="O571" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/BassenemyStick.html</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>EL1118</v>
+      </c>
+      <c r="B572">
+        <v>15</v>
+      </c>
+      <c r="C572" t="str">
+        <v>エッジブレイカー</v>
+      </c>
+      <c r="D572" t="str">
+        <v/>
+      </c>
+      <c r="E572" t="str">
+        <v/>
+      </c>
+      <c r="F572" t="str">
+        <v/>
+      </c>
+      <c r="G572" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H572" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I572" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J572" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K572" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/エッジブレイカー.jpg</v>
+      </c>
+      <c r="L572" t="str">
+        <v/>
+      </c>
+      <c r="M572" t="str">
+        <v/>
+      </c>
+      <c r="N572" t="str">
+        <v>デカバスが好んで喰うザリガニにもブルーギルにも化ける扁平ボディ。デカバスを騙しやすい素早いリアクションとスローな喰わせの両極端な釣りを1つでこなす二刀流。 琵琶湖プロガイド大西健太の豊富な経験から導き出された釣れるカタチ。琵琶湖はもちろん、ザリガニやブルーギルが多い各地のフィールドで。さらに、その対応範囲の広さは、多くのルアーを持ち歩きたくないアクティブなオカッパリアングラーにとっても強い味方になるでしょう。 【対応リグ】 ●フリーリグ ●テキサスリグ ●パンチショットリグ ●ラバージグジグトレーラー ●ノーシンカーリグ ●ネイルリグ etc... 【エッジブレイカー】大西健太プロデュース！新種クローワームの超実績三大リグを徹底解剖 ルアーニュースR 記事を読む→</v>
+      </c>
+      <c r="O572" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/EdgeBreaker.html</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>EL1119</v>
+      </c>
+      <c r="B573">
+        <v>15</v>
+      </c>
+      <c r="C573" t="str">
+        <v>クラップバザー</v>
+      </c>
+      <c r="D573" t="str">
+        <v/>
+      </c>
+      <c r="E573" t="str">
+        <v/>
+      </c>
+      <c r="F573" t="str">
+        <v/>
+      </c>
+      <c r="G573" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H573" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I573" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J573" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K573" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/クラップバザー.jpg</v>
+      </c>
+      <c r="L573" t="str">
+        <v/>
+      </c>
+      <c r="M573" t="str">
+        <v/>
+      </c>
+      <c r="N573" t="str">
+        <v>推奨リグ ＆ メソッド ② リーダーレスダウンショットリグ、テキサスリグ ❶ ただ巻き、速巻き、ズル引き ノーシンカー、ネイルリグ、ウエイテッドリグとスイミングレンジやスイミングスピードの違いで使い分ける。ボトムを狙う場合はロッドでズル引く。シンカーを重くするほど深いレンジを釣れるだけでなく、浅いレンジを速巻きできるようになり、かつ物への当たりも強くなるためリアクション効果が高まる。 ［ 場所 ＆ ターゲット例 ］▪あらゆるフィールドの中層～ボトム ▪リザーバーの立木にサスペンドするバス ▪ボトムの変化に付くバス etc... ❷ リフト ＆ フォール フォールでボトムに着いた瞬間にテールの動きがピタっと止まり、リフトすると急激にテールが動き出す。そのアクションのメリハリで口を使わせる。 ［ 場所 ＆ ターゲット例 ］▪ウィードやゴロタ石の点在するフラット ▪ハンプやブレイク等の地形変化 ▪立木や橋脚等の縦のカバー etc... ❸ ハングオン、ハングオフ 狙いのカバーまでズル引き、カバーに軽くスタックさせポーズ。テールの動きを止めて喰わせの間をつくる。バイトがなければ、ロッドを煽ってカバーから外すと、テールが突然動き出しリアクションバイトを誘発する。 ［ 場所 ＆ ターゲット例 ］▪あらゆるボトムの沈み物 ▪地形変化を伴うハードボトム ▪立木やレイダウン etc... ▶ 6/0以上のワイドギャップオフセットフック ※テールの先端が下向きになるようにフックをセットしてください。 ビッグバスをターゲットに本堂靖尚がプロデュースしたクラップバザー6インチ。その狙い通り、開発段階での実釣テストや取材において、菊元俊文BIG BITEロケでの七色ダムロクマルをはじめ、各地で様々なリグ＆メソッドで50アップを叩き出しています。 詳細を見る→</v>
+      </c>
+      <c r="O573" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/ClapBuzzer.html</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>EL1120</v>
+      </c>
+      <c r="B574">
+        <v>15</v>
+      </c>
+      <c r="C574" t="str">
+        <v>ルーシー</v>
+      </c>
+      <c r="D574" t="str">
+        <v/>
+      </c>
+      <c r="E574" t="str">
+        <v/>
+      </c>
+      <c r="F574" t="str">
+        <v/>
+      </c>
+      <c r="G574" t="str">
+        <v>weightless_soft_bait</v>
+      </c>
+      <c r="H574" t="str">
+        <v>soft</v>
+      </c>
+      <c r="I574" t="str">
+        <v>Bottom</v>
+      </c>
+      <c r="J574" t="str">
+        <v>worm</v>
+      </c>
+      <c r="K574" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ルーシー.jpg</v>
+      </c>
+      <c r="L574" t="str">
+        <v/>
+      </c>
+      <c r="M574" t="str">
+        <v/>
+      </c>
+      <c r="N574" t="str">
+        <v>［ロッド］ 65Lクラス スピニング（フェイズ PCSS-65L+ スピットファイア等） ［フック］ 基本はマスバリ#2ちょん掛け ウィードが濃い場所はオフセットフック#3 ［シンカー］ 水深2.5mまでは2.7g 2.5m〜3.5mは3.5g 3.5mより深いレンジは5g リーダーは約20cmが基準 琵琶湖はもちろんリザーバーや河川でも、ボートでもオカッパリでも、サイズ問わず好釣果を記録！ 続きを見る→</v>
+      </c>
+      <c r="O574" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Lucy.html</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>EL1121</v>
+      </c>
+      <c r="B575">
+        <v>15</v>
+      </c>
+      <c r="C575" t="str">
+        <v>バラム300・エバーグリーンスペシャルエディション</v>
+      </c>
+      <c r="D575" t="str">
+        <v/>
+      </c>
+      <c r="E575" t="str">
+        <v/>
+      </c>
+      <c r="F575" t="str">
+        <v/>
+      </c>
+      <c r="G575" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H575" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I575" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J575" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K575" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/バラム300・エバーグリーンスペシャルエディション.jpg</v>
+      </c>
+      <c r="L575" t="str">
+        <v/>
+      </c>
+      <c r="M575" t="str">
+        <v/>
+      </c>
+      <c r="N575" t="str">
+        <v>この釣力は“魔力”、バラム300。 ファストリトリーブ時の凄まじい動きの“ライブ感”。 デッドスティッキング時の“静の中の動”。 そしてエイトトラップ®という狂気的な“魔力を持った釣法”。 この3つの魔力を持ったジャイアントベイト。 今までのジャイアントベイトに無かった超高速リトリーブを多連結ボディで可能にし、高速巻きでも安定したスイム姿勢をキープすることで逃げ惑うベイトを極限まで演出。ストラクチャーに潜む早い動きにしか反応しないデカバスを仕留めます。 デッドスティッキング時には多連結ボディとシリコンテールが生物的で艶めかしい動きを演出し、スレたデカバスを誘いだしショートバイトも逃さない3フックシステム搭載でデカバスを仕留めます。 そして特に強い魔力を持ったエイトトラップ®釣法（8の字釣法）。足元まで追いかけて来たデカバスを完全に狂わせ、今まで完全に諦めてきた全てのフィッシュイーターにもう一度スイッチを入れさせることができる釣力はまさに魔力。 これから始まる『ジャイアントベイトの新境地』。覚醒した貴方に逃げ道は無くなる!!! Produced by SATAN SHIMADA ※「エイトトラップ®」は（有）マドネスジャパンの登録商標です。 破壊神バラム。菊元俊文スペシャルカラー降臨。</v>
+      </c>
+      <c r="O575" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Baram300.html</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>EL1122</v>
+      </c>
+      <c r="B576">
+        <v>15</v>
+      </c>
+      <c r="C576" t="str">
+        <v>バラム245・エバーグリーンスペシャルエディション</v>
+      </c>
+      <c r="D576" t="str">
+        <v/>
+      </c>
+      <c r="E576" t="str">
+        <v/>
+      </c>
+      <c r="F576" t="str">
+        <v/>
+      </c>
+      <c r="G576" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H576" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I576" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J576" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K576" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/バラム245・エバーグリーンスペシャルエディション.jpg</v>
+      </c>
+      <c r="L576" t="str">
+        <v/>
+      </c>
+      <c r="M576" t="str">
+        <v/>
+      </c>
+      <c r="N576" t="str">
+        <v>今までのジャイアントベイトに無かった超高速リトリーブを多連結ボディで可能にし、高速巻きでも安定したスイム姿勢をキープすることで逃げ惑うベイトを極限まで演出、ストラクチャーに潜む早い動きにしか反応しないデカバスを仕留めます。 更にタイトで超ハイピッチなスイムアクションと多連結ボディが可動時に発するサウンドでスレたデカバスを誘い出し、デッドスティッキング時には多連結ボディとシリコンテールの生物的で艶めかしい動きがスレたデカバスのバイトを誘発させます。 そして狂気の魔力を持ったエイトトラップ®釣法（8の字釣法）。足元まで追いかけて来たデカバスを完全に狂わせ、今まで完全に諦めてきた全てのフィッシュイーターにもう一度スイッチを入れさせることができる釣力はまさに魔力。 『ジャイアントベイトの新境地』…… 魔力の封印を解き放つのは貴方だ!!! Produced by SATAN SHIMADA ※商標「エイトトラップ」は有限会社マドネスジャパンの登録商標です。 ▶【島田一也】ブラックローズ×バラム245 プロモーションムービー 破壊神バラム。菊元俊文スペシャルカラー降臨。</v>
+      </c>
+      <c r="O576" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Balam245.html</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>EL1123</v>
+      </c>
+      <c r="B577">
+        <v>15</v>
+      </c>
+      <c r="C577" t="str">
+        <v>バラム200・エバーグリーンスペシャルエディション</v>
+      </c>
+      <c r="D577" t="str">
+        <v/>
+      </c>
+      <c r="E577" t="str">
+        <v/>
+      </c>
+      <c r="F577" t="str">
+        <v/>
+      </c>
+      <c r="G577" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H577" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I577" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J577" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K577" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/バラム200・エバーグリーンスペシャルエディション.jpg</v>
+      </c>
+      <c r="L577" t="str">
+        <v/>
+      </c>
+      <c r="M577" t="str">
+        <v/>
+      </c>
+      <c r="N577" t="str">
+        <v>限界ギリギリのウエイト調整を行い、高速リトリーブ直後のトリッキーなアクションも可能に！ “魔力”は伝承され、更に強力なものとなった。投げ続けた者だけが見ることを許された。“魔力”の扉への鍵 BALAM200生誕。 Produced by SATAN SHIMADA 破壊神バラム。菊元俊文スペシャルカラー降臨。</v>
+      </c>
+      <c r="O577" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Balam200.html</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>EL1124</v>
+      </c>
+      <c r="B578">
+        <v>15</v>
+      </c>
+      <c r="C578" t="str">
+        <v>ジョインテッドクロー178F・エバーグリーンスペシャルエディション</v>
+      </c>
+      <c r="D578" t="str">
+        <v/>
+      </c>
+      <c r="E578" t="str">
+        <v/>
+      </c>
+      <c r="F578" t="str">
+        <v/>
+      </c>
+      <c r="G578" t="str">
+        <v>swimbait</v>
+      </c>
+      <c r="H578" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I578" t="str">
+        <v>Topwater</v>
+      </c>
+      <c r="J578" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K578" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジョインテッドクロー178f・エバーグリーンスペシャルエディション.jpg</v>
+      </c>
+      <c r="L578" t="str">
+        <v/>
+      </c>
+      <c r="M578" t="str">
+        <v/>
+      </c>
+      <c r="N578" t="str">
+        <v>コンバットスティック・オライオンの世界観を纏うマット仕上げのスペシャルカラー。ブラック×ホワイトの強いコントラストが、水中で際立つ存在感を放つ最強カラー。 #EG04 ORIONブラックフラッシュ 黒系モノトーンのオライオンカラーをモチーフに、シルバー反射プレートを内蔵。シルエットが際立つだけでなく、フラッシングの明滅も取り入れた実戦的カラー。 通常のリップ付ルアーでは、リップで水の抵抗を受けることにより、ウォブリングやローリングといったアクションを生み出します。 しかし、このリップレスルアー「鮎邪・ジョインテッドクロー」は、既存のルアーには存在しない、と言うよりも「出すことのできなかった」、Ｓ字の軌道を描くアクションをただ巻くだけで演出します。 この「Ｓ字アクション」は、バスに強烈なバージンインパクトを与え、かなり離れたスポットからでもバスを呼び寄せて、バイトに持ち込むことを可能にします。 また、この動きはバスの捕食本能を駆り立て、一度や二度ミスバイトした魚も再び襲いかかるといった、ルアーを完全に「獲物」として捉えているかのような、反応を示させることに成功しました。 （ガンクラフト公式HPより転載）</v>
+      </c>
+      <c r="O578" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/JointedClaw178f.html</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>EL1125</v>
+      </c>
+      <c r="B579">
+        <v>15</v>
+      </c>
+      <c r="C579" t="str">
+        <v>ナム</v>
+      </c>
+      <c r="D579" t="str">
+        <v/>
+      </c>
+      <c r="E579" t="str">
+        <v/>
+      </c>
+      <c r="F579" t="str">
+        <v/>
+      </c>
+      <c r="G579" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H579" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I579" t="str">
+        <v>Variable</v>
+      </c>
+      <c r="J579" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K579" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ナム.jpg</v>
+      </c>
+      <c r="L579" t="str">
+        <v/>
+      </c>
+      <c r="M579" t="str">
+        <v/>
+      </c>
+      <c r="N579" t="str">
+        <v>オーバーで不規則な動きから生じる不自然さを排除したことで、プレッシャーのかかる魚にも違和感を与えず、バイトに持ち込みます。 また、通常は規則的な一定の動きだからこそ、アングラーの意図するイレギュラー（ロッドワークや巻きのテクニック）を、的確かつ効果的に入れられるのもその強み。巻くだけでは口を使わない状況にも、しっかり対応できます。 その守備範囲の広さから、魚の活性やフィールドコンディションに合わせたスプーンローテーションの中軸となる存在、「ナム」。トーナメントシーンにおける数々の実績が、その実力を物語ります。 ■ スプーンローテの中軸を担うマイクロスプーン「ナム」【トラウト新製品】</v>
+      </c>
+      <c r="O579" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Namu.html</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>EL1126</v>
+      </c>
+      <c r="B580">
+        <v>15</v>
+      </c>
+      <c r="C580" t="str">
+        <v>キラーバグ23</v>
+      </c>
+      <c r="D580" t="str">
+        <v/>
+      </c>
+      <c r="E580" t="str">
+        <v/>
+      </c>
+      <c r="F580" t="str">
+        <v/>
+      </c>
+      <c r="G580" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H580" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I580" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J580" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K580" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/キラーバグ23.jpg</v>
+      </c>
+      <c r="L580" t="str">
+        <v/>
+      </c>
+      <c r="M580" t="str">
+        <v/>
+      </c>
+      <c r="N580" t="str">
+        <v>アクションは水面～水面直下を小気味良くブリブリと泳ぐワイドウォブリングアクション。リップを含めた幅広フェイス面で水を強く押し、喰わせの小ぶりボディでありながらも魚に広くその存在をアピールする力を持っています。 まず、甲虫が水面に落ちた時のような「ペチッ」という着水音でアピール。2～3秒ステイしてバイトチャンスを作りだし、バイトがなければ少し巻いてブリブリとアピール。そして再びステイでバイトチャンスを作るという繰り返し。「巻きでアピールしてステイで喰わせる」というメリハリを付けることがキモです。 ほかにも、ロッドを立ててデッドスローに巻けば水面に波紋を出しながら泳ぐウェイキング、ティップを震わせるような超小刻みなシェイクでは水面でもがき苦しむ虫のような演出も可能です。 ■ キラーバグ23解説動画 「トラウトキング選手権」マイスター獲得経験者・指宿侑帆（いぶすき ゆうほ）プロがルアー特徴・使い方・タックルセッティングを解説。</v>
+      </c>
+      <c r="O580" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/KillerBug23.html</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>EL1127</v>
+      </c>
+      <c r="B581">
+        <v>15</v>
+      </c>
+      <c r="C581" t="str">
+        <v>ブルーコ50</v>
+      </c>
+      <c r="D581" t="str">
+        <v/>
+      </c>
+      <c r="E581" t="str">
+        <v/>
+      </c>
+      <c r="F581" t="str">
+        <v/>
+      </c>
+      <c r="G581" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H581" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I581" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J581" t="str">
+        <v>wobble_roll</v>
+      </c>
+      <c r="K581" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ブルーコ50.jpg</v>
+      </c>
+      <c r="L581" t="str">
+        <v/>
+      </c>
+      <c r="M581" t="str">
+        <v/>
+      </c>
+      <c r="N581" t="str">
+        <v>その日その時の魚が好むスピードを見つけることができれば、ひとり爆釣も。 ■ 効果的な使用法【2】 一定巻きに追いかけてくるものの、あと一歩で喰いきらない魚に対しては、「加速巻き」「減速巻き」といったスピード変化を織り交ぜるテクニックが効果的。 ニョロ系クランクの枠を超えた対応巻きスピード領域の広いブルーコ50だからこそのなせるワザ。 ■ ニョロ系クランク「ブルーコ50」さらなる釣果を絞り出す！</v>
+      </c>
+      <c r="O581" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Bruco50.html</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>EL1128</v>
+      </c>
+      <c r="B582">
+        <v>15</v>
+      </c>
+      <c r="C582" t="str">
+        <v>ジェットビーター30</v>
+      </c>
+      <c r="D582" t="str">
+        <v/>
+      </c>
+      <c r="E582" t="str">
+        <v/>
+      </c>
+      <c r="F582" t="str">
+        <v/>
+      </c>
+      <c r="G582" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H582" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I582" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J582" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K582" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ジェットビーター30.jpg</v>
+      </c>
+      <c r="L582" t="str">
+        <v/>
+      </c>
+      <c r="M582" t="str">
+        <v/>
+      </c>
+      <c r="N582" t="str">
+        <v>喰わせのコンパクトボディを、今までコンパクトルアーでは手が出せなかった領域へと送り込める効果は絶大。着水後は一直線に素早くフォールし、ボトムでは横倒れすることなくスタンド姿勢をキープ。そしてロッドワークにクイックに反応してボディがプルプルッと振動……リフト＆フォール、ボトムバンピングを中心にシェイキング、デジ巻き、ズル引きといったボトムメソッドに高次元で対応し、メリハリのある動きでバイトチャンスを創造します。 また、ボトムステイ中に横倒れしない → 沈殿物に埋もれにくい → 魚がルアーを見失いにくい、という流れでバイトチャンスが増加。さらには、リアフックもボトムに倒れないため、フックがマスの口に触れやすくなりフッキング率が各段にアップ。 ボトムを攻略するために考え抜かれた機能で、並の飛距離では勝負にならない奥底にへばりついた魚を引きずり出すことを可能にしたボトムバイブレーション、それがジェットビーター30です。 ■ 未踏のポイント奥底へ！ボトムバイブレーション「ジェットビーター30」</v>
+      </c>
+      <c r="O582" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/JetBeater30.html</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>EL1129</v>
+      </c>
+      <c r="B583">
+        <v>15</v>
+      </c>
+      <c r="C583" t="str">
+        <v>ネルメッツォ50FS</v>
+      </c>
+      <c r="D583" t="str">
+        <v/>
+      </c>
+      <c r="E583" t="str">
+        <v/>
+      </c>
+      <c r="F583" t="str">
+        <v/>
+      </c>
+      <c r="G583" t="str">
+        <v>special_lure</v>
+      </c>
+      <c r="H583" t="str">
+        <v>hardbait</v>
+      </c>
+      <c r="I583" t="str">
+        <v>Subsurface (0–0.5m)</v>
+      </c>
+      <c r="J583" t="str">
+        <v>glide</v>
+      </c>
+      <c r="K583" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/evergreen_lures/ネルメッツォ50fs.jpg</v>
+      </c>
+      <c r="L583" t="str">
+        <v/>
+      </c>
+      <c r="M583" t="str">
+        <v/>
+      </c>
+      <c r="N583" t="str">
+        <v>鋭くアクションするミノーを激しく追尾してきたが、突然Uターン……ルアーという物体の動きが止まる一瞬の間で、野生に生きる魚に、口にしてはならない異物と認識されてしまうから。渓流魚との駆け引きで頻繁に起こる現象だ。 こんな状況を打破するために、徹底的に鱒達の反応をテストしながらつくり上げたミノーが、ネルメッツォ50FS。 トゥイッチング、ジャーキングで流れの中で視覚に訴えかけ反応させる。アクションの一瞬の間には、水に絡むように揺らめき、単なる物体が生命体「らしい波動」を発することで見切らせない。 視覚と側線（波動）の両方に働きかける要素を詰め込み、渓流における我々の釣りのど真ん中を行くシンキングミノー。だからネルメッツォ（Nel mezzo）。</v>
+      </c>
+      <c r="O583" t="str">
+        <v>https://www.evergreen-fishing.com/goods_list/Nelmezzo50fs.html</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O453"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O583"/>
   </ignoredErrors>
 </worksheet>
 </file>